--- a/analisis_acciones.xlsx
+++ b/analisis_acciones.xlsx
@@ -413,9 +413,442 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:J11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Accion</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Precio actual</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Probabilidad tecnica</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Entrada min</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Entrada max</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Stop loss</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Objetivo</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>RSI</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Riesgo</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Senal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>220.42</v>
+      </c>
+      <c r="C2" t="n">
+        <v>85</v>
+      </c>
+      <c r="D2" t="n">
+        <v>217.11</v>
+      </c>
+      <c r="E2" t="n">
+        <v>222.62</v>
+      </c>
+      <c r="F2" t="n">
+        <v>209.4</v>
+      </c>
+      <c r="G2" t="n">
+        <v>238.05</v>
+      </c>
+      <c r="H2" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>MEDIO</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>POSIBLE COMPRA</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>AMD</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>458.83</v>
+      </c>
+      <c r="C3" t="n">
+        <v>85</v>
+      </c>
+      <c r="D3" t="n">
+        <v>451.95</v>
+      </c>
+      <c r="E3" t="n">
+        <v>463.42</v>
+      </c>
+      <c r="F3" t="n">
+        <v>435.89</v>
+      </c>
+      <c r="G3" t="n">
+        <v>495.54</v>
+      </c>
+      <c r="H3" t="n">
+        <v>4.36</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>ALTO</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>POSIBLE COMPRA</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>AVGO</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>429.86</v>
+      </c>
+      <c r="C4" t="n">
+        <v>85</v>
+      </c>
+      <c r="D4" t="n">
+        <v>423.41</v>
+      </c>
+      <c r="E4" t="n">
+        <v>434.16</v>
+      </c>
+      <c r="F4" t="n">
+        <v>408.37</v>
+      </c>
+      <c r="G4" t="n">
+        <v>464.25</v>
+      </c>
+      <c r="H4" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>MEDIO</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>POSIBLE COMPRA</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>292.67</v>
+      </c>
+      <c r="C5" t="n">
+        <v>85</v>
+      </c>
+      <c r="D5" t="n">
+        <v>288.28</v>
+      </c>
+      <c r="E5" t="n">
+        <v>295.6</v>
+      </c>
+      <c r="F5" t="n">
+        <v>278.04</v>
+      </c>
+      <c r="G5" t="n">
+        <v>316.08</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>BAJO</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>POSIBLE COMPRA</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>TSLA</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>421.45</v>
+      </c>
+      <c r="C6" t="n">
+        <v>85</v>
+      </c>
+      <c r="D6" t="n">
+        <v>415.13</v>
+      </c>
+      <c r="E6" t="n">
+        <v>425.66</v>
+      </c>
+      <c r="F6" t="n">
+        <v>400.38</v>
+      </c>
+      <c r="G6" t="n">
+        <v>455.17</v>
+      </c>
+      <c r="H6" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>MEDIO</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>POSIBLE COMPRA</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>GOOGL</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>394.42</v>
+      </c>
+      <c r="C7" t="n">
+        <v>85</v>
+      </c>
+      <c r="D7" t="n">
+        <v>388.5</v>
+      </c>
+      <c r="E7" t="n">
+        <v>398.36</v>
+      </c>
+      <c r="F7" t="n">
+        <v>374.69</v>
+      </c>
+      <c r="G7" t="n">
+        <v>425.97</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>BAJO</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>POSIBLE COMPRA</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>AMZN</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>271.16</v>
+      </c>
+      <c r="C8" t="n">
+        <v>75</v>
+      </c>
+      <c r="D8" t="n">
+        <v>267.09</v>
+      </c>
+      <c r="E8" t="n">
+        <v>273.87</v>
+      </c>
+      <c r="F8" t="n">
+        <v>257.6</v>
+      </c>
+      <c r="G8" t="n">
+        <v>292.85</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>BAJO</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>POSIBLE COMPRA</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>409.38</v>
+      </c>
+      <c r="C9" t="n">
+        <v>65</v>
+      </c>
+      <c r="D9" t="n">
+        <v>403.23</v>
+      </c>
+      <c r="E9" t="n">
+        <v>413.47</v>
+      </c>
+      <c r="F9" t="n">
+        <v>388.91</v>
+      </c>
+      <c r="G9" t="n">
+        <v>442.13</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>BAJO</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>VIGILAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>600.84</v>
+      </c>
+      <c r="C10" t="n">
+        <v>65</v>
+      </c>
+      <c r="D10" t="n">
+        <v>591.83</v>
+      </c>
+      <c r="E10" t="n">
+        <v>606.85</v>
+      </c>
+      <c r="F10" t="n">
+        <v>570.8</v>
+      </c>
+      <c r="G10" t="n">
+        <v>648.91</v>
+      </c>
+      <c r="H10" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>MEDIO</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>VIGILAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>PLTR</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>134.79</v>
+      </c>
+      <c r="C11" t="n">
+        <v>50</v>
+      </c>
+      <c r="D11" t="n">
+        <v>132.76</v>
+      </c>
+      <c r="E11" t="n">
+        <v>136.13</v>
+      </c>
+      <c r="F11" t="n">
+        <v>128.05</v>
+      </c>
+      <c r="G11" t="n">
+        <v>145.57</v>
+      </c>
+      <c r="H11" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>MEDIO</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>NO COMPRAR</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/analisis_acciones.xlsx
+++ b/analisis_acciones.xlsx
@@ -475,25 +475,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>220.42</v>
+        <v>221.9</v>
       </c>
       <c r="C2" t="n">
         <v>85</v>
       </c>
       <c r="D2" t="n">
-        <v>217.11</v>
+        <v>218.57</v>
       </c>
       <c r="E2" t="n">
-        <v>222.62</v>
+        <v>224.12</v>
       </c>
       <c r="F2" t="n">
-        <v>209.4</v>
+        <v>210.8</v>
       </c>
       <c r="G2" t="n">
-        <v>238.05</v>
+        <v>239.65</v>
       </c>
       <c r="H2" t="n">
-        <v>2.23</v>
+        <v>2.24</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -513,22 +513,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>458.83</v>
+        <v>464.94</v>
       </c>
       <c r="C3" t="n">
         <v>85</v>
       </c>
       <c r="D3" t="n">
-        <v>451.95</v>
+        <v>457.97</v>
       </c>
       <c r="E3" t="n">
-        <v>463.42</v>
+        <v>469.59</v>
       </c>
       <c r="F3" t="n">
-        <v>435.89</v>
+        <v>441.69</v>
       </c>
       <c r="G3" t="n">
-        <v>495.54</v>
+        <v>502.14</v>
       </c>
       <c r="H3" t="n">
         <v>4.36</v>
@@ -551,22 +551,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>429.86</v>
+        <v>430.3</v>
       </c>
       <c r="C4" t="n">
         <v>85</v>
       </c>
       <c r="D4" t="n">
-        <v>423.41</v>
+        <v>423.85</v>
       </c>
       <c r="E4" t="n">
-        <v>434.16</v>
+        <v>434.6</v>
       </c>
       <c r="F4" t="n">
-        <v>408.37</v>
+        <v>408.78</v>
       </c>
       <c r="G4" t="n">
-        <v>464.25</v>
+        <v>464.72</v>
       </c>
       <c r="H4" t="n">
         <v>2.88</v>
@@ -589,22 +589,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>292.67</v>
+        <v>292.83</v>
       </c>
       <c r="C5" t="n">
         <v>85</v>
       </c>
       <c r="D5" t="n">
-        <v>288.28</v>
+        <v>288.44</v>
       </c>
       <c r="E5" t="n">
-        <v>295.6</v>
+        <v>295.76</v>
       </c>
       <c r="F5" t="n">
-        <v>278.04</v>
+        <v>278.19</v>
       </c>
       <c r="G5" t="n">
-        <v>316.08</v>
+        <v>316.26</v>
       </c>
       <c r="H5" t="n">
         <v>1.41</v>
@@ -623,33 +623,33 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>TSLA</t>
+          <t>AMZN</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>421.45</v>
+        <v>272.41</v>
       </c>
       <c r="C6" t="n">
         <v>85</v>
       </c>
       <c r="D6" t="n">
-        <v>415.13</v>
+        <v>268.32</v>
       </c>
       <c r="E6" t="n">
-        <v>425.66</v>
+        <v>275.13</v>
       </c>
       <c r="F6" t="n">
-        <v>400.38</v>
+        <v>258.79</v>
       </c>
       <c r="G6" t="n">
-        <v>455.17</v>
+        <v>294.2</v>
       </c>
       <c r="H6" t="n">
-        <v>2.47</v>
+        <v>1.84</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>MEDIO</t>
+          <t>BAJO</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -661,33 +661,33 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>GOOGL</t>
+          <t>TSLA</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>394.42</v>
+        <v>437.86</v>
       </c>
       <c r="C7" t="n">
         <v>85</v>
       </c>
       <c r="D7" t="n">
-        <v>388.5</v>
+        <v>431.29</v>
       </c>
       <c r="E7" t="n">
-        <v>398.36</v>
+        <v>442.24</v>
       </c>
       <c r="F7" t="n">
-        <v>374.69</v>
+        <v>415.97</v>
       </c>
       <c r="G7" t="n">
-        <v>425.97</v>
+        <v>472.89</v>
       </c>
       <c r="H7" t="n">
-        <v>1.93</v>
+        <v>2.47</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>BAJO</t>
+          <t>MEDIO</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -699,29 +699,29 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>AMZN</t>
+          <t>GOOGL</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>271.16</v>
+        <v>394.61</v>
       </c>
       <c r="C8" t="n">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="D8" t="n">
-        <v>267.09</v>
+        <v>388.69</v>
       </c>
       <c r="E8" t="n">
-        <v>273.87</v>
+        <v>398.56</v>
       </c>
       <c r="F8" t="n">
-        <v>257.6</v>
+        <v>374.88</v>
       </c>
       <c r="G8" t="n">
-        <v>292.85</v>
+        <v>426.18</v>
       </c>
       <c r="H8" t="n">
-        <v>1.84</v>
+        <v>1.93</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -741,22 +741,22 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>409.38</v>
+        <v>410.58</v>
       </c>
       <c r="C9" t="n">
         <v>65</v>
       </c>
       <c r="D9" t="n">
-        <v>403.23</v>
+        <v>404.42</v>
       </c>
       <c r="E9" t="n">
-        <v>413.47</v>
+        <v>414.69</v>
       </c>
       <c r="F9" t="n">
-        <v>388.91</v>
+        <v>390.05</v>
       </c>
       <c r="G9" t="n">
-        <v>442.13</v>
+        <v>443.43</v>
       </c>
       <c r="H9" t="n">
         <v>1.85</v>
@@ -779,22 +779,22 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>600.84</v>
+        <v>603.52</v>
       </c>
       <c r="C10" t="n">
         <v>65</v>
       </c>
       <c r="D10" t="n">
-        <v>591.83</v>
+        <v>594.47</v>
       </c>
       <c r="E10" t="n">
-        <v>606.85</v>
+        <v>609.5599999999999</v>
       </c>
       <c r="F10" t="n">
-        <v>570.8</v>
+        <v>573.34</v>
       </c>
       <c r="G10" t="n">
-        <v>648.91</v>
+        <v>651.8</v>
       </c>
       <c r="H10" t="n">
         <v>2.36</v>
@@ -817,22 +817,22 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>134.79</v>
+        <v>135.05</v>
       </c>
       <c r="C11" t="n">
         <v>50</v>
       </c>
       <c r="D11" t="n">
-        <v>132.76</v>
+        <v>133.02</v>
       </c>
       <c r="E11" t="n">
-        <v>136.13</v>
+        <v>136.4</v>
       </c>
       <c r="F11" t="n">
-        <v>128.05</v>
+        <v>128.3</v>
       </c>
       <c r="G11" t="n">
-        <v>145.57</v>
+        <v>145.85</v>
       </c>
       <c r="H11" t="n">
         <v>3.26</v>

--- a/analisis_acciones.xlsx
+++ b/analisis_acciones.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J11"/>
+  <dimension ref="A1:K37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -424,45 +424,50 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
+          <t>Sector</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
           <t>Precio actual</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Probabilidad tecnica</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Entrada min</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Entrada max</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Stop loss</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Objetivo</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>RSI</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Riesgo</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Senal</t>
         </is>
@@ -474,33 +479,38 @@
           <t>NVDA</t>
         </is>
       </c>
-      <c r="B2" t="n">
-        <v>221.9</v>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>IA / Chips</t>
+        </is>
       </c>
       <c r="C2" t="n">
-        <v>85</v>
+        <v>221.85</v>
       </c>
       <c r="D2" t="n">
-        <v>218.57</v>
+        <v>85</v>
       </c>
       <c r="E2" t="n">
-        <v>224.12</v>
+        <v>218.52</v>
       </c>
       <c r="F2" t="n">
-        <v>210.8</v>
+        <v>224.07</v>
       </c>
       <c r="G2" t="n">
-        <v>239.65</v>
+        <v>210.76</v>
       </c>
       <c r="H2" t="n">
+        <v>239.6</v>
+      </c>
+      <c r="I2" t="n">
         <v>2.24</v>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>MEDIO</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>POSIBLE COMPRA</t>
         </is>
@@ -512,33 +522,38 @@
           <t>AMD</t>
         </is>
       </c>
-      <c r="B3" t="n">
-        <v>464.94</v>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>IA / Chips</t>
+        </is>
       </c>
       <c r="C3" t="n">
-        <v>85</v>
+        <v>463.71</v>
       </c>
       <c r="D3" t="n">
-        <v>457.97</v>
+        <v>85</v>
       </c>
       <c r="E3" t="n">
-        <v>469.59</v>
+        <v>456.75</v>
       </c>
       <c r="F3" t="n">
-        <v>441.69</v>
+        <v>468.35</v>
       </c>
       <c r="G3" t="n">
-        <v>502.14</v>
+        <v>440.52</v>
       </c>
       <c r="H3" t="n">
+        <v>500.81</v>
+      </c>
+      <c r="I3" t="n">
         <v>4.36</v>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>ALTO</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>POSIBLE COMPRA</t>
         </is>
@@ -550,33 +565,38 @@
           <t>AVGO</t>
         </is>
       </c>
-      <c r="B4" t="n">
-        <v>430.3</v>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>IA / Chips</t>
+        </is>
       </c>
       <c r="C4" t="n">
-        <v>85</v>
+        <v>430</v>
       </c>
       <c r="D4" t="n">
-        <v>423.85</v>
+        <v>85</v>
       </c>
       <c r="E4" t="n">
-        <v>434.6</v>
+        <v>423.55</v>
       </c>
       <c r="F4" t="n">
-        <v>408.78</v>
+        <v>434.3</v>
       </c>
       <c r="G4" t="n">
-        <v>464.72</v>
+        <v>408.5</v>
       </c>
       <c r="H4" t="n">
+        <v>464.4</v>
+      </c>
+      <c r="I4" t="n">
         <v>2.88</v>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>MEDIO</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>POSIBLE COMPRA</t>
         </is>
@@ -588,33 +608,38 @@
           <t>AAPL</t>
         </is>
       </c>
-      <c r="B5" t="n">
-        <v>292.83</v>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Tecnología</t>
+        </is>
       </c>
       <c r="C5" t="n">
-        <v>85</v>
+        <v>292.26</v>
       </c>
       <c r="D5" t="n">
-        <v>288.44</v>
+        <v>85</v>
       </c>
       <c r="E5" t="n">
-        <v>295.76</v>
+        <v>287.88</v>
       </c>
       <c r="F5" t="n">
-        <v>278.19</v>
+        <v>295.18</v>
       </c>
       <c r="G5" t="n">
-        <v>316.26</v>
+        <v>277.65</v>
       </c>
       <c r="H5" t="n">
+        <v>315.64</v>
+      </c>
+      <c r="I5" t="n">
         <v>1.41</v>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>BAJO</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>POSIBLE COMPRA</t>
         </is>
@@ -626,33 +651,38 @@
           <t>AMZN</t>
         </is>
       </c>
-      <c r="B6" t="n">
-        <v>272.41</v>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Tecnología</t>
+        </is>
       </c>
       <c r="C6" t="n">
-        <v>85</v>
+        <v>272.33</v>
       </c>
       <c r="D6" t="n">
-        <v>268.32</v>
+        <v>85</v>
       </c>
       <c r="E6" t="n">
-        <v>275.13</v>
+        <v>268.25</v>
       </c>
       <c r="F6" t="n">
-        <v>258.79</v>
+        <v>275.05</v>
       </c>
       <c r="G6" t="n">
-        <v>294.2</v>
+        <v>258.71</v>
       </c>
       <c r="H6" t="n">
+        <v>294.12</v>
+      </c>
+      <c r="I6" t="n">
         <v>1.84</v>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t>BAJO</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>POSIBLE COMPRA</t>
         </is>
@@ -661,36 +691,41 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>TSLA</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>437.86</v>
+          <t>GOOGL</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Tecnología</t>
+        </is>
       </c>
       <c r="C7" t="n">
-        <v>85</v>
+        <v>393.75</v>
       </c>
       <c r="D7" t="n">
-        <v>431.29</v>
+        <v>85</v>
       </c>
       <c r="E7" t="n">
-        <v>442.24</v>
+        <v>387.84</v>
       </c>
       <c r="F7" t="n">
-        <v>415.97</v>
+        <v>397.69</v>
       </c>
       <c r="G7" t="n">
-        <v>472.89</v>
+        <v>374.06</v>
       </c>
       <c r="H7" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>MEDIO</t>
-        </is>
+        <v>425.25</v>
+      </c>
+      <c r="I7" t="n">
+        <v>1.93</v>
       </c>
       <c r="J7" t="inlineStr">
+        <is>
+          <t>BAJO</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
         <is>
           <t>POSIBLE COMPRA</t>
         </is>
@@ -699,36 +734,41 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>GOOGL</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>394.61</v>
+          <t>TSLA</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Autos / Tech</t>
+        </is>
       </c>
       <c r="C8" t="n">
-        <v>85</v>
+        <v>439.74</v>
       </c>
       <c r="D8" t="n">
-        <v>388.69</v>
+        <v>85</v>
       </c>
       <c r="E8" t="n">
-        <v>398.56</v>
+        <v>433.14</v>
       </c>
       <c r="F8" t="n">
-        <v>374.88</v>
+        <v>444.14</v>
       </c>
       <c r="G8" t="n">
-        <v>426.18</v>
+        <v>417.75</v>
       </c>
       <c r="H8" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>BAJO</t>
-        </is>
+        <v>474.92</v>
+      </c>
+      <c r="I8" t="n">
+        <v>2.48</v>
       </c>
       <c r="J8" t="inlineStr">
+        <is>
+          <t>MEDIO</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
         <is>
           <t>POSIBLE COMPRA</t>
         </is>
@@ -737,112 +777,1245 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>MSFT</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>410.58</v>
+          <t>SMCI</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Servidores IA</t>
+        </is>
       </c>
       <c r="C9" t="n">
-        <v>65</v>
+        <v>35.23</v>
       </c>
       <c r="D9" t="n">
-        <v>404.42</v>
+        <v>85</v>
       </c>
       <c r="E9" t="n">
-        <v>414.69</v>
+        <v>34.7</v>
       </c>
       <c r="F9" t="n">
-        <v>390.05</v>
+        <v>35.58</v>
       </c>
       <c r="G9" t="n">
-        <v>443.43</v>
+        <v>33.47</v>
       </c>
       <c r="H9" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>BAJO</t>
-        </is>
+        <v>38.05</v>
+      </c>
+      <c r="I9" t="n">
+        <v>5.54</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>VIGILAR</t>
+          <t>ALTO</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>POSIBLE COMPRA</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>META</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>603.52</v>
+          <t>MU</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Memoria / Chips</t>
+        </is>
       </c>
       <c r="C10" t="n">
-        <v>65</v>
+        <v>793.66</v>
       </c>
       <c r="D10" t="n">
-        <v>594.47</v>
+        <v>85</v>
       </c>
       <c r="E10" t="n">
-        <v>609.5599999999999</v>
+        <v>781.76</v>
       </c>
       <c r="F10" t="n">
-        <v>573.34</v>
+        <v>801.6</v>
       </c>
       <c r="G10" t="n">
-        <v>651.8</v>
+        <v>753.98</v>
       </c>
       <c r="H10" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>MEDIO</t>
-        </is>
+        <v>857.15</v>
+      </c>
+      <c r="I10" t="n">
+        <v>4.68</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>VIGILAR</t>
+          <t>ALTO</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>POSIBLE COMPRA</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>ARM</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Chips</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>212.46</v>
+      </c>
+      <c r="D11" t="n">
+        <v>85</v>
+      </c>
+      <c r="E11" t="n">
+        <v>209.27</v>
+      </c>
+      <c r="F11" t="n">
+        <v>214.58</v>
+      </c>
+      <c r="G11" t="n">
+        <v>201.84</v>
+      </c>
+      <c r="H11" t="n">
+        <v>229.46</v>
+      </c>
+      <c r="I11" t="n">
+        <v>4.14</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>ALTO</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>POSIBLE COMPRA</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>QCOM</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Chips</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>239.16</v>
+      </c>
+      <c r="D12" t="n">
+        <v>85</v>
+      </c>
+      <c r="E12" t="n">
+        <v>235.57</v>
+      </c>
+      <c r="F12" t="n">
+        <v>241.55</v>
+      </c>
+      <c r="G12" t="n">
+        <v>227.2</v>
+      </c>
+      <c r="H12" t="n">
+        <v>258.29</v>
+      </c>
+      <c r="I12" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>MEDIO</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>POSIBLE COMPRA</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>INTC</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Chips</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>127.71</v>
+      </c>
+      <c r="D13" t="n">
+        <v>85</v>
+      </c>
+      <c r="E13" t="n">
+        <v>125.79</v>
+      </c>
+      <c r="F13" t="n">
+        <v>128.99</v>
+      </c>
+      <c r="G13" t="n">
+        <v>121.32</v>
+      </c>
+      <c r="H13" t="n">
+        <v>137.93</v>
+      </c>
+      <c r="I13" t="n">
+        <v>5.14</v>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>ALTO</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>POSIBLE COMPRA</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>TSM</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Chips</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>405.61</v>
+      </c>
+      <c r="D14" t="n">
+        <v>85</v>
+      </c>
+      <c r="E14" t="n">
+        <v>399.53</v>
+      </c>
+      <c r="F14" t="n">
+        <v>409.67</v>
+      </c>
+      <c r="G14" t="n">
+        <v>385.33</v>
+      </c>
+      <c r="H14" t="n">
+        <v>438.06</v>
+      </c>
+      <c r="I14" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>MEDIO</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>POSIBLE COMPRA</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>ASML</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Chips</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>1547.07</v>
+      </c>
+      <c r="D15" t="n">
+        <v>85</v>
+      </c>
+      <c r="E15" t="n">
+        <v>1523.86</v>
+      </c>
+      <c r="F15" t="n">
+        <v>1562.54</v>
+      </c>
+      <c r="G15" t="n">
+        <v>1469.71</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1670.83</v>
+      </c>
+      <c r="I15" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>MEDIO</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>POSIBLE COMPRA</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>AMAT</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Equipos chips</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>446.87</v>
+      </c>
+      <c r="D16" t="n">
+        <v>85</v>
+      </c>
+      <c r="E16" t="n">
+        <v>440.17</v>
+      </c>
+      <c r="F16" t="n">
+        <v>451.34</v>
+      </c>
+      <c r="G16" t="n">
+        <v>424.53</v>
+      </c>
+      <c r="H16" t="n">
+        <v>482.62</v>
+      </c>
+      <c r="I16" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>MEDIO</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>POSIBLE COMPRA</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>LRCX</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Equipos chips</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>298.13</v>
+      </c>
+      <c r="D17" t="n">
+        <v>85</v>
+      </c>
+      <c r="E17" t="n">
+        <v>293.66</v>
+      </c>
+      <c r="F17" t="n">
+        <v>301.11</v>
+      </c>
+      <c r="G17" t="n">
+        <v>283.22</v>
+      </c>
+      <c r="H17" t="n">
+        <v>321.98</v>
+      </c>
+      <c r="I17" t="n">
+        <v>3.63</v>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>MEDIO</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>POSIBLE COMPRA</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>KLAC</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Equipos chips</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>1886.23</v>
+      </c>
+      <c r="D18" t="n">
+        <v>85</v>
+      </c>
+      <c r="E18" t="n">
+        <v>1857.94</v>
+      </c>
+      <c r="F18" t="n">
+        <v>1905.09</v>
+      </c>
+      <c r="G18" t="n">
+        <v>1791.92</v>
+      </c>
+      <c r="H18" t="n">
+        <v>2037.13</v>
+      </c>
+      <c r="I18" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>MEDIO</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>POSIBLE COMPRA</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>COIN</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Cripto / Trading</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>209.51</v>
+      </c>
+      <c r="D19" t="n">
+        <v>85</v>
+      </c>
+      <c r="E19" t="n">
+        <v>206.37</v>
+      </c>
+      <c r="F19" t="n">
+        <v>211.6</v>
+      </c>
+      <c r="G19" t="n">
+        <v>199.03</v>
+      </c>
+      <c r="H19" t="n">
+        <v>226.27</v>
+      </c>
+      <c r="I19" t="n">
+        <v>4.59</v>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>ALTO</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>POSIBLE COMPRA</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>SPY</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>ETF Mercado</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>740.17</v>
+      </c>
+      <c r="D20" t="n">
+        <v>85</v>
+      </c>
+      <c r="E20" t="n">
+        <v>729.0700000000001</v>
+      </c>
+      <c r="F20" t="n">
+        <v>747.5700000000001</v>
+      </c>
+      <c r="G20" t="n">
+        <v>703.16</v>
+      </c>
+      <c r="H20" t="n">
+        <v>799.38</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>BAJO</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>POSIBLE COMPRA</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>QQQ</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>ETF Nasdaq</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>714.38</v>
+      </c>
+      <c r="D21" t="n">
+        <v>85</v>
+      </c>
+      <c r="E21" t="n">
+        <v>703.66</v>
+      </c>
+      <c r="F21" t="n">
+        <v>721.52</v>
+      </c>
+      <c r="G21" t="n">
+        <v>678.66</v>
+      </c>
+      <c r="H21" t="n">
+        <v>771.53</v>
+      </c>
+      <c r="I21" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>BAJO</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>POSIBLE COMPRA</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>SOXX</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>ETF Chips</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>531.89</v>
+      </c>
+      <c r="D22" t="n">
+        <v>85</v>
+      </c>
+      <c r="E22" t="n">
+        <v>523.91</v>
+      </c>
+      <c r="F22" t="n">
+        <v>537.21</v>
+      </c>
+      <c r="G22" t="n">
+        <v>505.3</v>
+      </c>
+      <c r="H22" t="n">
+        <v>574.4400000000001</v>
+      </c>
+      <c r="I22" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>MEDIO</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>POSIBLE COMPRA</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>RKLB</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Espacial</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>119.46</v>
+      </c>
+      <c r="D23" t="n">
+        <v>85</v>
+      </c>
+      <c r="E23" t="n">
+        <v>117.67</v>
+      </c>
+      <c r="F23" t="n">
+        <v>120.66</v>
+      </c>
+      <c r="G23" t="n">
+        <v>113.49</v>
+      </c>
+      <c r="H23" t="n">
+        <v>129.02</v>
+      </c>
+      <c r="I23" t="n">
+        <v>6.57</v>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>ALTO</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>POSIBLE COMPRA</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>IONQ</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Computación cuántica</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>56.71</v>
+      </c>
+      <c r="D24" t="n">
+        <v>85</v>
+      </c>
+      <c r="E24" t="n">
+        <v>55.86</v>
+      </c>
+      <c r="F24" t="n">
+        <v>57.28</v>
+      </c>
+      <c r="G24" t="n">
+        <v>53.87</v>
+      </c>
+      <c r="H24" t="n">
+        <v>61.25</v>
+      </c>
+      <c r="I24" t="n">
+        <v>6.26</v>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>ALTO</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>POSIBLE COMPRA</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>IA</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>9.630000000000001</v>
+      </c>
+      <c r="D25" t="n">
+        <v>85</v>
+      </c>
+      <c r="E25" t="n">
+        <v>9.48</v>
+      </c>
+      <c r="F25" t="n">
+        <v>9.73</v>
+      </c>
+      <c r="G25" t="n">
+        <v>9.15</v>
+      </c>
+      <c r="H25" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="I25" t="n">
+        <v>4.11</v>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>ALTO</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>POSIBLE COMPRA</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>HOOD</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Trading</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>79.15000000000001</v>
+      </c>
+      <c r="D26" t="n">
+        <v>75</v>
+      </c>
+      <c r="E26" t="n">
+        <v>77.95999999999999</v>
+      </c>
+      <c r="F26" t="n">
+        <v>79.94</v>
+      </c>
+      <c r="G26" t="n">
+        <v>75.19</v>
+      </c>
+      <c r="H26" t="n">
+        <v>85.48</v>
+      </c>
+      <c r="I26" t="n">
+        <v>4.49</v>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>ALTO</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>POSIBLE COMPRA</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>SOUN</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>IA</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="D27" t="n">
+        <v>75</v>
+      </c>
+      <c r="E27" t="n">
+        <v>8.470000000000001</v>
+      </c>
+      <c r="F27" t="n">
+        <v>8.68</v>
+      </c>
+      <c r="G27" t="n">
+        <v>8.17</v>
+      </c>
+      <c r="H27" t="n">
+        <v>9.279999999999999</v>
+      </c>
+      <c r="I27" t="n">
+        <v>4.74</v>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>ALTO</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>POSIBLE COMPRA</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Tecnología</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>410.49</v>
+      </c>
+      <c r="D28" t="n">
+        <v>65</v>
+      </c>
+      <c r="E28" t="n">
+        <v>404.33</v>
+      </c>
+      <c r="F28" t="n">
+        <v>414.59</v>
+      </c>
+      <c r="G28" t="n">
+        <v>389.97</v>
+      </c>
+      <c r="H28" t="n">
+        <v>443.33</v>
+      </c>
+      <c r="I28" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>BAJO</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>VIGILAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Tecnología</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>602.24</v>
+      </c>
+      <c r="D29" t="n">
+        <v>65</v>
+      </c>
+      <c r="E29" t="n">
+        <v>593.21</v>
+      </c>
+      <c r="F29" t="n">
+        <v>608.26</v>
+      </c>
+      <c r="G29" t="n">
+        <v>572.13</v>
+      </c>
+      <c r="H29" t="n">
+        <v>650.42</v>
+      </c>
+      <c r="I29" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>MEDIO</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>VIGILAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>SOFI</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Fintech</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>16.03</v>
+      </c>
+      <c r="D30" t="n">
+        <v>65</v>
+      </c>
+      <c r="E30" t="n">
+        <v>15.79</v>
+      </c>
+      <c r="F30" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="G30" t="n">
+        <v>15.23</v>
+      </c>
+      <c r="H30" t="n">
+        <v>17.32</v>
+      </c>
+      <c r="I30" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>MEDIO</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>VIGILAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>PYPL</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Pagos</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>45.2</v>
+      </c>
+      <c r="D31" t="n">
+        <v>65</v>
+      </c>
+      <c r="E31" t="n">
+        <v>44.52</v>
+      </c>
+      <c r="F31" t="n">
+        <v>45.65</v>
+      </c>
+      <c r="G31" t="n">
+        <v>42.94</v>
+      </c>
+      <c r="H31" t="n">
+        <v>48.82</v>
+      </c>
+      <c r="I31" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>MEDIO</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>VIGILAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>SLB</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Energía</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>54.31</v>
+      </c>
+      <c r="D32" t="n">
+        <v>65</v>
+      </c>
+      <c r="E32" t="n">
+        <v>53.49</v>
+      </c>
+      <c r="F32" t="n">
+        <v>54.85</v>
+      </c>
+      <c r="G32" t="n">
+        <v>51.59</v>
+      </c>
+      <c r="H32" t="n">
+        <v>58.65</v>
+      </c>
+      <c r="I32" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>MEDIO</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>VIGILAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>UPST</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Fintech IA</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>28.92</v>
+      </c>
+      <c r="D33" t="n">
+        <v>65</v>
+      </c>
+      <c r="E33" t="n">
+        <v>28.49</v>
+      </c>
+      <c r="F33" t="n">
+        <v>29.21</v>
+      </c>
+      <c r="G33" t="n">
+        <v>27.47</v>
+      </c>
+      <c r="H33" t="n">
+        <v>31.23</v>
+      </c>
+      <c r="I33" t="n">
+        <v>4.43</v>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>ALTO</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>VIGILAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
           <t>PLTR</t>
         </is>
       </c>
-      <c r="B11" t="n">
-        <v>135.05</v>
-      </c>
-      <c r="C11" t="n">
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>IA / Software</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>135.97</v>
+      </c>
+      <c r="D34" t="n">
         <v>50</v>
       </c>
-      <c r="D11" t="n">
-        <v>133.02</v>
-      </c>
-      <c r="E11" t="n">
-        <v>136.4</v>
-      </c>
-      <c r="F11" t="n">
-        <v>128.3</v>
-      </c>
-      <c r="G11" t="n">
-        <v>145.85</v>
-      </c>
-      <c r="H11" t="n">
+      <c r="E34" t="n">
+        <v>133.93</v>
+      </c>
+      <c r="F34" t="n">
+        <v>137.33</v>
+      </c>
+      <c r="G34" t="n">
+        <v>129.17</v>
+      </c>
+      <c r="H34" t="n">
+        <v>146.85</v>
+      </c>
+      <c r="I34" t="n">
         <v>3.26</v>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="J34" t="inlineStr">
         <is>
           <t>MEDIO</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>NO COMPRAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>XOM</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Energía</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>148.15</v>
+      </c>
+      <c r="D35" t="n">
+        <v>50</v>
+      </c>
+      <c r="E35" t="n">
+        <v>145.93</v>
+      </c>
+      <c r="F35" t="n">
+        <v>149.64</v>
+      </c>
+      <c r="G35" t="n">
+        <v>140.75</v>
+      </c>
+      <c r="H35" t="n">
+        <v>160.01</v>
+      </c>
+      <c r="I35" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>BAJO</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>NO COMPRAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>CVX</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Energía</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>184.23</v>
+      </c>
+      <c r="D36" t="n">
+        <v>50</v>
+      </c>
+      <c r="E36" t="n">
+        <v>181.47</v>
+      </c>
+      <c r="F36" t="n">
+        <v>186.07</v>
+      </c>
+      <c r="G36" t="n">
+        <v>175.02</v>
+      </c>
+      <c r="H36" t="n">
+        <v>198.97</v>
+      </c>
+      <c r="I36" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>BAJO</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>NO COMPRAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>OXY</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Energía</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>55.28</v>
+      </c>
+      <c r="D37" t="n">
+        <v>50</v>
+      </c>
+      <c r="E37" t="n">
+        <v>54.45</v>
+      </c>
+      <c r="F37" t="n">
+        <v>55.83</v>
+      </c>
+      <c r="G37" t="n">
+        <v>52.52</v>
+      </c>
+      <c r="H37" t="n">
+        <v>59.7</v>
+      </c>
+      <c r="I37" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>MEDIO</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
         <is>
           <t>NO COMPRAR</t>
         </is>

--- a/analisis_acciones.xlsx
+++ b/analisis_acciones.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K37"/>
+  <dimension ref="A1:N37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -439,35 +439,50 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
+          <t>Momentum</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Volumen relativo</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
           <t>Entrada min</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Entrada max</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Stop loss</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Objetivo</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>RSI</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Riesgo</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>Hot Score</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
         <is>
           <t>Senal</t>
         </is>
@@ -485,32 +500,43 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>221.85</v>
+        <v>221.37</v>
       </c>
       <c r="D2" t="n">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="E2" t="n">
-        <v>218.52</v>
+        <v>11.53</v>
       </c>
       <c r="F2" t="n">
-        <v>224.07</v>
+        <v>0.63</v>
       </c>
       <c r="G2" t="n">
-        <v>210.76</v>
+        <v>218.05</v>
       </c>
       <c r="H2" t="n">
-        <v>239.6</v>
+        <v>223.58</v>
       </c>
       <c r="I2" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="J2" t="inlineStr">
+        <v>210.3</v>
+      </c>
+      <c r="J2" t="n">
+        <v>239.08</v>
+      </c>
+      <c r="K2" t="n">
+        <v>65.92</v>
+      </c>
+      <c r="L2" t="inlineStr">
         <is>
           <t>MEDIO</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>🔥🔥</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
         <is>
           <t>POSIBLE COMPRA</t>
         </is>
@@ -519,41 +545,52 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>ASML</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>IA / Chips</t>
+          <t>Chips</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>463.71</v>
+        <v>1547.67</v>
       </c>
       <c r="D3" t="n">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="E3" t="n">
-        <v>456.75</v>
+        <v>11.65</v>
       </c>
       <c r="F3" t="n">
-        <v>468.35</v>
+        <v>0.72</v>
       </c>
       <c r="G3" t="n">
-        <v>440.52</v>
+        <v>1524.45</v>
       </c>
       <c r="H3" t="n">
-        <v>500.81</v>
+        <v>1563.15</v>
       </c>
       <c r="I3" t="n">
-        <v>4.36</v>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>ALTO</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
+        <v>1470.29</v>
+      </c>
+      <c r="J3" t="n">
+        <v>1671.48</v>
+      </c>
+      <c r="K3" t="n">
+        <v>58.14</v>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>MEDIO</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>🔥🔥</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
         <is>
           <t>POSIBLE COMPRA</t>
         </is>
@@ -571,32 +608,43 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>430</v>
+        <v>428.08</v>
       </c>
       <c r="D4" t="n">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="E4" t="n">
-        <v>423.55</v>
+        <v>2.78</v>
       </c>
       <c r="F4" t="n">
-        <v>434.3</v>
+        <v>0.38</v>
       </c>
       <c r="G4" t="n">
-        <v>408.5</v>
+        <v>421.66</v>
       </c>
       <c r="H4" t="n">
-        <v>464.4</v>
+        <v>432.37</v>
       </c>
       <c r="I4" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>MEDIO</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
+        <v>406.68</v>
+      </c>
+      <c r="J4" t="n">
+        <v>462.33</v>
+      </c>
+      <c r="K4" t="n">
+        <v>60.78</v>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>BAJO</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>🔥🔥</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
         <is>
           <t>POSIBLE COMPRA</t>
         </is>
@@ -605,41 +653,52 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>ARM</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Tecnología</t>
+          <t>Chips</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>292.26</v>
+        <v>210.24</v>
       </c>
       <c r="D5" t="n">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="E5" t="n">
-        <v>287.88</v>
+        <v>3.43</v>
       </c>
       <c r="F5" t="n">
-        <v>295.18</v>
+        <v>0.6</v>
       </c>
       <c r="G5" t="n">
-        <v>277.65</v>
+        <v>207.09</v>
       </c>
       <c r="H5" t="n">
-        <v>315.64</v>
+        <v>212.34</v>
       </c>
       <c r="I5" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="J5" t="inlineStr">
+        <v>199.73</v>
+      </c>
+      <c r="J5" t="n">
+        <v>227.06</v>
+      </c>
+      <c r="K5" t="n">
+        <v>59.81</v>
+      </c>
+      <c r="L5" t="inlineStr">
         <is>
           <t>BAJO</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>🔥🔥</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
         <is>
           <t>POSIBLE COMPRA</t>
         </is>
@@ -648,41 +707,52 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AMZN</t>
+          <t>COIN</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Tecnología</t>
+          <t>Cripto / Trading</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>272.33</v>
+        <v>210.88</v>
       </c>
       <c r="D6" t="n">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="E6" t="n">
-        <v>268.25</v>
+        <v>3.88</v>
       </c>
       <c r="F6" t="n">
-        <v>275.05</v>
+        <v>0.65</v>
       </c>
       <c r="G6" t="n">
-        <v>258.71</v>
+        <v>207.71</v>
       </c>
       <c r="H6" t="n">
-        <v>294.12</v>
+        <v>212.98</v>
       </c>
       <c r="I6" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="J6" t="inlineStr">
+        <v>200.33</v>
+      </c>
+      <c r="J6" t="n">
+        <v>227.75</v>
+      </c>
+      <c r="K6" t="n">
+        <v>58.47</v>
+      </c>
+      <c r="L6" t="inlineStr">
         <is>
           <t>BAJO</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>🔥🔥</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
         <is>
           <t>POSIBLE COMPRA</t>
         </is>
@@ -691,41 +761,52 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>GOOGL</t>
+          <t>AI</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Tecnología</t>
+          <t>IA</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>393.75</v>
+        <v>9.57</v>
       </c>
       <c r="D7" t="n">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="E7" t="n">
-        <v>387.84</v>
+        <v>3.85</v>
       </c>
       <c r="F7" t="n">
-        <v>397.69</v>
+        <v>0.44</v>
       </c>
       <c r="G7" t="n">
-        <v>374.06</v>
+        <v>9.43</v>
       </c>
       <c r="H7" t="n">
-        <v>425.25</v>
+        <v>9.67</v>
       </c>
       <c r="I7" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="J7" t="inlineStr">
+        <v>9.1</v>
+      </c>
+      <c r="J7" t="n">
+        <v>10.34</v>
+      </c>
+      <c r="K7" t="n">
+        <v>56.28</v>
+      </c>
+      <c r="L7" t="inlineStr">
         <is>
           <t>BAJO</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>🔥🔥</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
         <is>
           <t>POSIBLE COMPRA</t>
         </is>
@@ -734,41 +815,52 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>TSLA</t>
+          <t>KLAC</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Autos / Tech</t>
+          <t>Equipos chips</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>439.74</v>
+        <v>1879.45</v>
       </c>
       <c r="D8" t="n">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="E8" t="n">
-        <v>433.14</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="F8" t="n">
-        <v>444.14</v>
+        <v>0.42</v>
       </c>
       <c r="G8" t="n">
-        <v>417.75</v>
+        <v>1851.26</v>
       </c>
       <c r="H8" t="n">
-        <v>474.92</v>
+        <v>1898.24</v>
       </c>
       <c r="I8" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="J8" t="inlineStr">
+        <v>1785.48</v>
+      </c>
+      <c r="J8" t="n">
+        <v>2029.81</v>
+      </c>
+      <c r="K8" t="n">
+        <v>57.15</v>
+      </c>
+      <c r="L8" t="inlineStr">
         <is>
           <t>MEDIO</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>🔥🔥</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
         <is>
           <t>POSIBLE COMPRA</t>
         </is>
@@ -777,41 +869,52 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SMCI</t>
+          <t>TSM</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Servidores IA</t>
+          <t>Chips</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>35.23</v>
+        <v>404.67</v>
       </c>
       <c r="D9" t="n">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="E9" t="n">
-        <v>34.7</v>
+        <v>0.76</v>
       </c>
       <c r="F9" t="n">
-        <v>35.58</v>
+        <v>0.62</v>
       </c>
       <c r="G9" t="n">
-        <v>33.47</v>
+        <v>398.6</v>
       </c>
       <c r="H9" t="n">
-        <v>38.05</v>
+        <v>408.72</v>
       </c>
       <c r="I9" t="n">
-        <v>5.54</v>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>ALTO</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
+        <v>384.44</v>
+      </c>
+      <c r="J9" t="n">
+        <v>437.04</v>
+      </c>
+      <c r="K9" t="n">
+        <v>65.84</v>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>BAJO</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>🔥</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
         <is>
           <t>POSIBLE COMPRA</t>
         </is>
@@ -820,41 +923,52 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>MU</t>
+          <t>SLB</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Memoria / Chips</t>
+          <t>Energía</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>793.66</v>
+        <v>54.52</v>
       </c>
       <c r="D10" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="E10" t="n">
-        <v>781.76</v>
+        <v>-1.99</v>
       </c>
       <c r="F10" t="n">
-        <v>801.6</v>
+        <v>0.24</v>
       </c>
       <c r="G10" t="n">
-        <v>753.98</v>
+        <v>53.7</v>
       </c>
       <c r="H10" t="n">
-        <v>857.15</v>
+        <v>55.07</v>
       </c>
       <c r="I10" t="n">
-        <v>4.68</v>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>ALTO</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
+        <v>51.79</v>
+      </c>
+      <c r="J10" t="n">
+        <v>58.88</v>
+      </c>
+      <c r="K10" t="n">
+        <v>57.19</v>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>BAJO</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>🔥</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
         <is>
           <t>POSIBLE COMPRA</t>
         </is>
@@ -863,41 +977,52 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ARM</t>
+          <t>SOUN</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Chips</t>
+          <t>IA</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>212.46</v>
+        <v>8.52</v>
       </c>
       <c r="D11" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="E11" t="n">
-        <v>209.27</v>
+        <v>-10.08</v>
       </c>
       <c r="F11" t="n">
-        <v>214.58</v>
+        <v>0.58</v>
       </c>
       <c r="G11" t="n">
-        <v>201.84</v>
+        <v>8.390000000000001</v>
       </c>
       <c r="H11" t="n">
-        <v>229.46</v>
+        <v>8.6</v>
       </c>
       <c r="I11" t="n">
-        <v>4.14</v>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>ALTO</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
+        <v>8.09</v>
+      </c>
+      <c r="J11" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="K11" t="n">
+        <v>56.05</v>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>BAJO</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>🔥</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
         <is>
           <t>POSIBLE COMPRA</t>
         </is>
@@ -906,729 +1031,880 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>QCOM</t>
+          <t>HOOD</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Chips</t>
+          <t>Trading</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>239.16</v>
+        <v>79.59</v>
       </c>
       <c r="D12" t="n">
-        <v>85</v>
+        <v>58</v>
       </c>
       <c r="E12" t="n">
-        <v>235.57</v>
+        <v>3.97</v>
       </c>
       <c r="F12" t="n">
-        <v>241.55</v>
+        <v>0.4</v>
       </c>
       <c r="G12" t="n">
-        <v>227.2</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="H12" t="n">
-        <v>258.29</v>
+        <v>80.39</v>
       </c>
       <c r="I12" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>MEDIO</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>POSIBLE COMPRA</t>
+        <v>75.61</v>
+      </c>
+      <c r="J12" t="n">
+        <v>85.95999999999999</v>
+      </c>
+      <c r="K12" t="n">
+        <v>40.37</v>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>BAJO</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>🔥</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>NO COMPRAR</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>INTC</t>
+          <t>XOM</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Chips</t>
+          <t>Energía</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>127.71</v>
+        <v>148.57</v>
       </c>
       <c r="D13" t="n">
-        <v>85</v>
+        <v>62</v>
       </c>
       <c r="E13" t="n">
-        <v>125.79</v>
+        <v>-3.33</v>
       </c>
       <c r="F13" t="n">
-        <v>128.99</v>
+        <v>0.3</v>
       </c>
       <c r="G13" t="n">
-        <v>121.32</v>
+        <v>146.34</v>
       </c>
       <c r="H13" t="n">
-        <v>137.93</v>
+        <v>150.06</v>
       </c>
       <c r="I13" t="n">
-        <v>5.14</v>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>ALTO</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>POSIBLE COMPRA</t>
+        <v>141.14</v>
+      </c>
+      <c r="J13" t="n">
+        <v>160.46</v>
+      </c>
+      <c r="K13" t="n">
+        <v>50.36</v>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>BAJO</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>VIGILAR</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Chips</t>
+          <t>Tecnología</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>405.61</v>
+        <v>410.6</v>
       </c>
       <c r="D14" t="n">
-        <v>85</v>
+        <v>50</v>
       </c>
       <c r="E14" t="n">
-        <v>399.53</v>
+        <v>-0.73</v>
       </c>
       <c r="F14" t="n">
-        <v>409.67</v>
+        <v>0.41</v>
       </c>
       <c r="G14" t="n">
-        <v>385.33</v>
+        <v>404.44</v>
       </c>
       <c r="H14" t="n">
-        <v>438.06</v>
+        <v>414.71</v>
       </c>
       <c r="I14" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>MEDIO</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>POSIBLE COMPRA</t>
+        <v>390.07</v>
+      </c>
+      <c r="J14" t="n">
+        <v>443.45</v>
+      </c>
+      <c r="K14" t="n">
+        <v>42.48</v>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>BAJO</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>NO COMPRAR</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ASML</t>
+          <t>CVX</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Chips</t>
+          <t>Energía</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1547.07</v>
+        <v>184.49</v>
       </c>
       <c r="D15" t="n">
-        <v>85</v>
+        <v>50</v>
       </c>
       <c r="E15" t="n">
-        <v>1523.86</v>
+        <v>-4.05</v>
       </c>
       <c r="F15" t="n">
-        <v>1562.54</v>
+        <v>0.27</v>
       </c>
       <c r="G15" t="n">
-        <v>1469.71</v>
+        <v>181.72</v>
       </c>
       <c r="H15" t="n">
-        <v>1670.83</v>
+        <v>186.33</v>
       </c>
       <c r="I15" t="n">
-        <v>2.87</v>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>MEDIO</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>POSIBLE COMPRA</t>
+        <v>175.27</v>
+      </c>
+      <c r="J15" t="n">
+        <v>199.25</v>
+      </c>
+      <c r="K15" t="n">
+        <v>47.64</v>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>BAJO</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>NO COMPRAR</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>AMAT</t>
+          <t>OXY</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Equipos chips</t>
+          <t>Energía</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>446.87</v>
+        <v>55.24</v>
       </c>
       <c r="D16" t="n">
-        <v>85</v>
+        <v>50</v>
       </c>
       <c r="E16" t="n">
-        <v>440.17</v>
+        <v>-8.34</v>
       </c>
       <c r="F16" t="n">
-        <v>451.34</v>
+        <v>0.5</v>
       </c>
       <c r="G16" t="n">
-        <v>424.53</v>
+        <v>54.42</v>
       </c>
       <c r="H16" t="n">
-        <v>482.62</v>
+        <v>55.8</v>
       </c>
       <c r="I16" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>MEDIO</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>POSIBLE COMPRA</t>
+        <v>52.48</v>
+      </c>
+      <c r="J16" t="n">
+        <v>59.66</v>
+      </c>
+      <c r="K16" t="n">
+        <v>47.13</v>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>BAJO</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>NO COMPRAR</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>LRCX</t>
+          <t>META</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Equipos chips</t>
+          <t>Tecnología</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>298.13</v>
+        <v>603.48</v>
       </c>
       <c r="D17" t="n">
-        <v>85</v>
+        <v>42</v>
       </c>
       <c r="E17" t="n">
-        <v>293.66</v>
+        <v>-1.14</v>
       </c>
       <c r="F17" t="n">
-        <v>301.11</v>
+        <v>0.47</v>
       </c>
       <c r="G17" t="n">
-        <v>283.22</v>
+        <v>594.4299999999999</v>
       </c>
       <c r="H17" t="n">
-        <v>321.98</v>
+        <v>609.51</v>
       </c>
       <c r="I17" t="n">
-        <v>3.63</v>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>MEDIO</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>POSIBLE COMPRA</t>
+        <v>573.3099999999999</v>
+      </c>
+      <c r="J17" t="n">
+        <v>651.76</v>
+      </c>
+      <c r="K17" t="n">
+        <v>27.16</v>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>BAJO</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>NO COMPRAR</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>KLAC</t>
+          <t>SOFI</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Equipos chips</t>
+          <t>Fintech</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>1886.23</v>
+        <v>16.02</v>
       </c>
       <c r="D18" t="n">
-        <v>85</v>
+        <v>42</v>
       </c>
       <c r="E18" t="n">
-        <v>1857.94</v>
+        <v>-1.11</v>
       </c>
       <c r="F18" t="n">
-        <v>1905.09</v>
+        <v>0.57</v>
       </c>
       <c r="G18" t="n">
-        <v>1791.92</v>
+        <v>15.78</v>
       </c>
       <c r="H18" t="n">
-        <v>2037.13</v>
+        <v>16.18</v>
       </c>
       <c r="I18" t="n">
-        <v>3.29</v>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>MEDIO</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>POSIBLE COMPRA</t>
+        <v>15.22</v>
+      </c>
+      <c r="J18" t="n">
+        <v>17.3</v>
+      </c>
+      <c r="K18" t="n">
+        <v>30.1</v>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>BAJO</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>NO COMPRAR</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>COIN</t>
+          <t>PYPL</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Cripto / Trading</t>
+          <t>Pagos</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>209.51</v>
+        <v>45.32</v>
       </c>
       <c r="D19" t="n">
-        <v>85</v>
+        <v>42</v>
       </c>
       <c r="E19" t="n">
-        <v>206.37</v>
+        <v>-10.06</v>
       </c>
       <c r="F19" t="n">
-        <v>211.6</v>
+        <v>0.38</v>
       </c>
       <c r="G19" t="n">
-        <v>199.03</v>
+        <v>44.64</v>
       </c>
       <c r="H19" t="n">
-        <v>226.27</v>
+        <v>45.77</v>
       </c>
       <c r="I19" t="n">
-        <v>4.59</v>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>ALTO</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>POSIBLE COMPRA</t>
+        <v>43.05</v>
+      </c>
+      <c r="J19" t="n">
+        <v>48.95</v>
+      </c>
+      <c r="K19" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>BAJO</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>NO COMPRAR</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>SPY</t>
+          <t>UPST</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>ETF Mercado</t>
+          <t>Fintech IA</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>740.17</v>
+        <v>28.98</v>
       </c>
       <c r="D20" t="n">
-        <v>85</v>
+        <v>42</v>
       </c>
       <c r="E20" t="n">
-        <v>729.0700000000001</v>
+        <v>-9.66</v>
       </c>
       <c r="F20" t="n">
-        <v>747.5700000000001</v>
+        <v>0.42</v>
       </c>
       <c r="G20" t="n">
-        <v>703.16</v>
+        <v>28.55</v>
       </c>
       <c r="H20" t="n">
-        <v>799.38</v>
+        <v>29.27</v>
       </c>
       <c r="I20" t="n">
-        <v>0.84</v>
-      </c>
-      <c r="J20" t="inlineStr">
+        <v>27.53</v>
+      </c>
+      <c r="J20" t="n">
+        <v>31.3</v>
+      </c>
+      <c r="K20" t="n">
+        <v>34.71</v>
+      </c>
+      <c r="L20" t="inlineStr">
         <is>
           <t>BAJO</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>POSIBLE COMPRA</t>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>NO COMPRAR</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>QQQ</t>
+          <t>PLTR</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>ETF Nasdaq</t>
+          <t>IA / Software</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>714.38</v>
+        <v>135.47</v>
       </c>
       <c r="D21" t="n">
-        <v>85</v>
+        <v>32</v>
       </c>
       <c r="E21" t="n">
-        <v>703.66</v>
+        <v>-7.23</v>
       </c>
       <c r="F21" t="n">
-        <v>721.52</v>
+        <v>0.51</v>
       </c>
       <c r="G21" t="n">
-        <v>678.66</v>
+        <v>133.44</v>
       </c>
       <c r="H21" t="n">
-        <v>771.53</v>
+        <v>136.82</v>
       </c>
       <c r="I21" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="J21" t="inlineStr">
+        <v>128.7</v>
+      </c>
+      <c r="J21" t="n">
+        <v>146.31</v>
+      </c>
+      <c r="K21" t="n">
+        <v>39.71</v>
+      </c>
+      <c r="L21" t="inlineStr">
         <is>
           <t>BAJO</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>POSIBLE COMPRA</t>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>NO COMPRAR</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>SOXX</t>
+          <t>RKLB</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>ETF Chips</t>
+          <t>Espacial</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>531.89</v>
+        <v>117.1</v>
       </c>
       <c r="D22" t="n">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="E22" t="n">
-        <v>523.91</v>
+        <v>45.81</v>
       </c>
       <c r="F22" t="n">
-        <v>537.21</v>
+        <v>1.25</v>
       </c>
       <c r="G22" t="n">
-        <v>505.3</v>
+        <v>115.34</v>
       </c>
       <c r="H22" t="n">
-        <v>574.4400000000001</v>
+        <v>118.27</v>
       </c>
       <c r="I22" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>MEDIO</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>POSIBLE COMPRA</t>
+        <v>111.24</v>
+      </c>
+      <c r="J22" t="n">
+        <v>126.47</v>
+      </c>
+      <c r="K22" t="n">
+        <v>68.05</v>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>ALTO</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>🔥🔥</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>VIGILAR</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>RKLB</t>
+          <t>AMAT</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Espacial</t>
+          <t>Equipos chips</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>119.46</v>
+        <v>445.83</v>
       </c>
       <c r="D23" t="n">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="E23" t="n">
-        <v>117.67</v>
+        <v>13.91</v>
       </c>
       <c r="F23" t="n">
-        <v>120.66</v>
+        <v>0.53</v>
       </c>
       <c r="G23" t="n">
-        <v>113.49</v>
+        <v>439.15</v>
       </c>
       <c r="H23" t="n">
-        <v>129.02</v>
+        <v>450.29</v>
       </c>
       <c r="I23" t="n">
-        <v>6.57</v>
-      </c>
-      <c r="J23" t="inlineStr">
+        <v>423.54</v>
+      </c>
+      <c r="J23" t="n">
+        <v>481.5</v>
+      </c>
+      <c r="K23" t="n">
+        <v>65.14</v>
+      </c>
+      <c r="L23" t="inlineStr">
         <is>
           <t>ALTO</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>POSIBLE COMPRA</t>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>🔥</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>VIGILAR</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>IONQ</t>
+          <t>LRCX</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Computación cuántica</t>
+          <t>Equipos chips</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>56.71</v>
+        <v>297.07</v>
       </c>
       <c r="D24" t="n">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="E24" t="n">
-        <v>55.86</v>
+        <v>14.89</v>
       </c>
       <c r="F24" t="n">
-        <v>57.28</v>
+        <v>0.33</v>
       </c>
       <c r="G24" t="n">
-        <v>53.87</v>
+        <v>292.61</v>
       </c>
       <c r="H24" t="n">
-        <v>61.25</v>
+        <v>300.04</v>
       </c>
       <c r="I24" t="n">
-        <v>6.26</v>
-      </c>
-      <c r="J24" t="inlineStr">
+        <v>282.22</v>
+      </c>
+      <c r="J24" t="n">
+        <v>320.84</v>
+      </c>
+      <c r="K24" t="n">
+        <v>66.93000000000001</v>
+      </c>
+      <c r="L24" t="inlineStr">
         <is>
           <t>ALTO</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>POSIBLE COMPRA</t>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>🔥</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>VIGILAR</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>AI</t>
+          <t>IONQ</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>IA</t>
+          <t>Computación cuántica</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>9.630000000000001</v>
+        <v>56.6</v>
       </c>
       <c r="D25" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="E25" t="n">
-        <v>9.48</v>
+        <v>23.72</v>
       </c>
       <c r="F25" t="n">
-        <v>9.73</v>
+        <v>0.9</v>
       </c>
       <c r="G25" t="n">
-        <v>9.15</v>
+        <v>55.75</v>
       </c>
       <c r="H25" t="n">
-        <v>10.4</v>
+        <v>57.17</v>
       </c>
       <c r="I25" t="n">
-        <v>4.11</v>
-      </c>
-      <c r="J25" t="inlineStr">
+        <v>53.77</v>
+      </c>
+      <c r="J25" t="n">
+        <v>61.13</v>
+      </c>
+      <c r="K25" t="n">
+        <v>65.27</v>
+      </c>
+      <c r="L25" t="inlineStr">
         <is>
           <t>ALTO</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>POSIBLE COMPRA</t>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>🔥</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>VIGILAR</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>HOOD</t>
+          <t>AAPL</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Trading</t>
+          <t>Tecnología</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>79.15000000000001</v>
+        <v>292.46</v>
       </c>
       <c r="D26" t="n">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="E26" t="n">
-        <v>77.95999999999999</v>
+        <v>5.65</v>
       </c>
       <c r="F26" t="n">
-        <v>79.94</v>
+        <v>0.37</v>
       </c>
       <c r="G26" t="n">
-        <v>75.19</v>
+        <v>288.07</v>
       </c>
       <c r="H26" t="n">
-        <v>85.48</v>
+        <v>295.38</v>
       </c>
       <c r="I26" t="n">
-        <v>4.49</v>
-      </c>
-      <c r="J26" t="inlineStr">
+        <v>277.84</v>
+      </c>
+      <c r="J26" t="n">
+        <v>315.86</v>
+      </c>
+      <c r="K26" t="n">
+        <v>77.68000000000001</v>
+      </c>
+      <c r="L26" t="inlineStr">
         <is>
           <t>ALTO</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>POSIBLE COMPRA</t>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>🔥</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>VIGILAR</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>SOUN</t>
+          <t>GOOGL</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>IA</t>
+          <t>Tecnología</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>8.6</v>
+        <v>394.09</v>
       </c>
       <c r="D27" t="n">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="E27" t="n">
-        <v>8.470000000000001</v>
+        <v>2.83</v>
       </c>
       <c r="F27" t="n">
-        <v>8.68</v>
+        <v>0.43</v>
       </c>
       <c r="G27" t="n">
-        <v>8.17</v>
+        <v>388.18</v>
       </c>
       <c r="H27" t="n">
-        <v>9.279999999999999</v>
+        <v>398.03</v>
       </c>
       <c r="I27" t="n">
-        <v>4.74</v>
-      </c>
-      <c r="J27" t="inlineStr">
+        <v>374.39</v>
+      </c>
+      <c r="J27" t="n">
+        <v>425.62</v>
+      </c>
+      <c r="K27" t="n">
+        <v>87.59999999999999</v>
+      </c>
+      <c r="L27" t="inlineStr">
         <is>
           <t>ALTO</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>POSIBLE COMPRA</t>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>🔥</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>VIGILAR</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>SMCI</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Tecnología</t>
+          <t>Servidores IA</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>410.49</v>
+        <v>35.04</v>
       </c>
       <c r="D28" t="n">
-        <v>65</v>
+        <v>82</v>
       </c>
       <c r="E28" t="n">
-        <v>404.33</v>
+        <v>25.51</v>
       </c>
       <c r="F28" t="n">
-        <v>414.59</v>
+        <v>0.55</v>
       </c>
       <c r="G28" t="n">
-        <v>389.97</v>
+        <v>34.52</v>
       </c>
       <c r="H28" t="n">
-        <v>443.33</v>
+        <v>35.39</v>
       </c>
       <c r="I28" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>BAJO</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
+        <v>33.29</v>
+      </c>
+      <c r="J28" t="n">
+        <v>37.84</v>
+      </c>
+      <c r="K28" t="n">
+        <v>66.09999999999999</v>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>ALTO</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>🔥</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
         <is>
           <t>VIGILAR</t>
         </is>
@@ -1637,41 +1913,52 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>META</t>
+          <t>SPY</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Tecnología</t>
+          <t>ETF Mercado</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>602.24</v>
+        <v>740.12</v>
       </c>
       <c r="D29" t="n">
-        <v>65</v>
+        <v>82</v>
       </c>
       <c r="E29" t="n">
-        <v>593.21</v>
+        <v>3.08</v>
       </c>
       <c r="F29" t="n">
-        <v>608.26</v>
+        <v>0.38</v>
       </c>
       <c r="G29" t="n">
-        <v>572.13</v>
+        <v>729.02</v>
       </c>
       <c r="H29" t="n">
-        <v>650.42</v>
+        <v>747.52</v>
       </c>
       <c r="I29" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>MEDIO</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
+        <v>703.11</v>
+      </c>
+      <c r="J29" t="n">
+        <v>799.33</v>
+      </c>
+      <c r="K29" t="n">
+        <v>80.79000000000001</v>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>ALTO</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>🔥</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
         <is>
           <t>VIGILAR</t>
         </is>
@@ -1680,41 +1967,52 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>SOFI</t>
+          <t>QQQ</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Fintech</t>
+          <t>ETF Nasdaq</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>16.03</v>
+        <v>713.5599999999999</v>
       </c>
       <c r="D30" t="n">
-        <v>65</v>
+        <v>82</v>
       </c>
       <c r="E30" t="n">
-        <v>15.79</v>
+        <v>6.05</v>
       </c>
       <c r="F30" t="n">
-        <v>16.2</v>
+        <v>0.47</v>
       </c>
       <c r="G30" t="n">
-        <v>15.23</v>
+        <v>702.86</v>
       </c>
       <c r="H30" t="n">
-        <v>17.32</v>
+        <v>720.7</v>
       </c>
       <c r="I30" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>MEDIO</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
+        <v>677.88</v>
+      </c>
+      <c r="J30" t="n">
+        <v>770.64</v>
+      </c>
+      <c r="K30" t="n">
+        <v>86.76000000000001</v>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>ALTO</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>🔥</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
         <is>
           <t>VIGILAR</t>
         </is>
@@ -1723,41 +2021,48 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>PYPL</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Pagos</t>
+          <t>IA / Chips</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>45.2</v>
+        <v>465.59</v>
       </c>
       <c r="D31" t="n">
-        <v>65</v>
+        <v>76</v>
       </c>
       <c r="E31" t="n">
-        <v>44.52</v>
+        <v>36.32</v>
       </c>
       <c r="F31" t="n">
-        <v>45.65</v>
+        <v>0.6</v>
       </c>
       <c r="G31" t="n">
-        <v>42.94</v>
+        <v>458.6</v>
       </c>
       <c r="H31" t="n">
-        <v>48.82</v>
+        <v>470.24</v>
       </c>
       <c r="I31" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>MEDIO</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
+        <v>442.31</v>
+      </c>
+      <c r="J31" t="n">
+        <v>502.83</v>
+      </c>
+      <c r="K31" t="n">
+        <v>80.78</v>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>ALTO</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr">
         <is>
           <t>VIGILAR</t>
         </is>
@@ -1766,41 +2071,48 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>SLB</t>
+          <t>SOXX</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Energía</t>
+          <t>ETF Chips</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>54.31</v>
+        <v>529.71</v>
       </c>
       <c r="D32" t="n">
-        <v>65</v>
+        <v>76</v>
       </c>
       <c r="E32" t="n">
-        <v>53.49</v>
+        <v>14.64</v>
       </c>
       <c r="F32" t="n">
-        <v>54.85</v>
+        <v>0.65</v>
       </c>
       <c r="G32" t="n">
-        <v>51.59</v>
+        <v>521.76</v>
       </c>
       <c r="H32" t="n">
-        <v>58.65</v>
+        <v>535.01</v>
       </c>
       <c r="I32" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>MEDIO</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
+        <v>503.22</v>
+      </c>
+      <c r="J32" t="n">
+        <v>572.09</v>
+      </c>
+      <c r="K32" t="n">
+        <v>78.51000000000001</v>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>ALTO</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr">
         <is>
           <t>VIGILAR</t>
         </is>
@@ -1809,41 +2121,48 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>UPST</t>
+          <t>MU</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Fintech IA</t>
+          <t>Memoria / Chips</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>28.92</v>
+        <v>789.1</v>
       </c>
       <c r="D33" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="E33" t="n">
-        <v>28.49</v>
+        <v>36.89</v>
       </c>
       <c r="F33" t="n">
-        <v>29.21</v>
+        <v>0.99</v>
       </c>
       <c r="G33" t="n">
-        <v>27.47</v>
+        <v>777.26</v>
       </c>
       <c r="H33" t="n">
-        <v>31.23</v>
+        <v>796.99</v>
       </c>
       <c r="I33" t="n">
-        <v>4.43</v>
-      </c>
-      <c r="J33" t="inlineStr">
+        <v>749.64</v>
+      </c>
+      <c r="J33" t="n">
+        <v>852.23</v>
+      </c>
+      <c r="K33" t="n">
+        <v>89.11</v>
+      </c>
+      <c r="L33" t="inlineStr">
         <is>
           <t>ALTO</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr">
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr">
         <is>
           <t>VIGILAR</t>
         </is>
@@ -1852,127 +2171,148 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>PLTR</t>
+          <t>INTC</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>IA / Software</t>
+          <t>Chips</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>135.97</v>
+        <v>126.42</v>
       </c>
       <c r="D34" t="n">
-        <v>50</v>
+        <v>68</v>
       </c>
       <c r="E34" t="n">
-        <v>133.93</v>
+        <v>31.99</v>
       </c>
       <c r="F34" t="n">
-        <v>137.33</v>
+        <v>0.75</v>
       </c>
       <c r="G34" t="n">
-        <v>129.17</v>
+        <v>124.52</v>
       </c>
       <c r="H34" t="n">
-        <v>146.85</v>
+        <v>127.68</v>
       </c>
       <c r="I34" t="n">
-        <v>3.26</v>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>MEDIO</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>NO COMPRAR</t>
+        <v>120.1</v>
+      </c>
+      <c r="J34" t="n">
+        <v>136.53</v>
+      </c>
+      <c r="K34" t="n">
+        <v>88.52</v>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>ALTO</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>VIGILAR</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>XOM</t>
+          <t>TSLA</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Energía</t>
+          <t>Autos / Tech</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>148.15</v>
+        <v>440.35</v>
       </c>
       <c r="D35" t="n">
-        <v>50</v>
+        <v>66</v>
       </c>
       <c r="E35" t="n">
-        <v>145.93</v>
+        <v>12.19</v>
       </c>
       <c r="F35" t="n">
-        <v>149.64</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="G35" t="n">
-        <v>140.75</v>
+        <v>433.74</v>
       </c>
       <c r="H35" t="n">
-        <v>160.01</v>
+        <v>444.75</v>
       </c>
       <c r="I35" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>BAJO</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>NO COMPRAR</t>
+        <v>418.33</v>
+      </c>
+      <c r="J35" t="n">
+        <v>475.58</v>
+      </c>
+      <c r="K35" t="n">
+        <v>77.09</v>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>ALTO</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>VIGILAR</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>CVX</t>
+          <t>QCOM</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Energía</t>
+          <t>Chips</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>184.23</v>
+        <v>231.81</v>
       </c>
       <c r="D36" t="n">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="E36" t="n">
-        <v>181.47</v>
+        <v>37.67</v>
       </c>
       <c r="F36" t="n">
-        <v>186.07</v>
+        <v>1.09</v>
       </c>
       <c r="G36" t="n">
-        <v>175.02</v>
+        <v>228.33</v>
       </c>
       <c r="H36" t="n">
-        <v>198.97</v>
+        <v>234.13</v>
       </c>
       <c r="I36" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>BAJO</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
+        <v>220.22</v>
+      </c>
+      <c r="J36" t="n">
+        <v>250.35</v>
+      </c>
+      <c r="K36" t="n">
+        <v>89</v>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>ALTO</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="inlineStr">
         <is>
           <t>NO COMPRAR</t>
         </is>
@@ -1981,41 +2321,48 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>OXY</t>
+          <t>AMZN</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Energía</t>
+          <t>Tecnología</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>55.28</v>
+        <v>272.02</v>
       </c>
       <c r="D37" t="n">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="E37" t="n">
-        <v>54.45</v>
+        <v>-0.01</v>
       </c>
       <c r="F37" t="n">
-        <v>55.83</v>
+        <v>0.34</v>
       </c>
       <c r="G37" t="n">
-        <v>52.52</v>
+        <v>267.93</v>
       </c>
       <c r="H37" t="n">
-        <v>59.7</v>
+        <v>274.74</v>
       </c>
       <c r="I37" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>MEDIO</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
+        <v>258.41</v>
+      </c>
+      <c r="J37" t="n">
+        <v>293.78</v>
+      </c>
+      <c r="K37" t="n">
+        <v>77.48</v>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>ALTO</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" t="inlineStr">
         <is>
           <t>NO COMPRAR</t>
         </is>

--- a/analisis_acciones.xlsx
+++ b/analisis_acciones.xlsx
@@ -500,31 +500,31 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>221.37</v>
+        <v>220.77</v>
       </c>
       <c r="D2" t="n">
         <v>95</v>
       </c>
       <c r="E2" t="n">
-        <v>11.53</v>
+        <v>11.23</v>
       </c>
       <c r="F2" t="n">
-        <v>0.63</v>
+        <v>0.65</v>
       </c>
       <c r="G2" t="n">
-        <v>218.05</v>
+        <v>217.46</v>
       </c>
       <c r="H2" t="n">
-        <v>223.58</v>
+        <v>222.98</v>
       </c>
       <c r="I2" t="n">
-        <v>210.3</v>
+        <v>209.74</v>
       </c>
       <c r="J2" t="n">
-        <v>239.08</v>
+        <v>238.44</v>
       </c>
       <c r="K2" t="n">
-        <v>65.92</v>
+        <v>65.62</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -554,31 +554,31 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1547.67</v>
+        <v>1550.03</v>
       </c>
       <c r="D3" t="n">
         <v>92</v>
       </c>
       <c r="E3" t="n">
-        <v>11.65</v>
+        <v>11.82</v>
       </c>
       <c r="F3" t="n">
-        <v>0.72</v>
+        <v>0.74</v>
       </c>
       <c r="G3" t="n">
-        <v>1524.45</v>
+        <v>1526.78</v>
       </c>
       <c r="H3" t="n">
-        <v>1563.15</v>
+        <v>1565.53</v>
       </c>
       <c r="I3" t="n">
-        <v>1470.29</v>
+        <v>1472.53</v>
       </c>
       <c r="J3" t="n">
-        <v>1671.48</v>
+        <v>1674.03</v>
       </c>
       <c r="K3" t="n">
-        <v>58.14</v>
+        <v>58.38</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
@@ -608,31 +608,31 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>428.08</v>
+        <v>428.58</v>
       </c>
       <c r="D4" t="n">
         <v>88</v>
       </c>
       <c r="E4" t="n">
-        <v>2.78</v>
+        <v>2.9</v>
       </c>
       <c r="F4" t="n">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="G4" t="n">
-        <v>421.66</v>
+        <v>422.16</v>
       </c>
       <c r="H4" t="n">
-        <v>432.37</v>
+        <v>432.87</v>
       </c>
       <c r="I4" t="n">
-        <v>406.68</v>
+        <v>407.16</v>
       </c>
       <c r="J4" t="n">
-        <v>462.33</v>
+        <v>462.87</v>
       </c>
       <c r="K4" t="n">
-        <v>60.78</v>
+        <v>61.04</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
@@ -662,31 +662,31 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>210.24</v>
+        <v>210.63</v>
       </c>
       <c r="D5" t="n">
         <v>88</v>
       </c>
       <c r="E5" t="n">
-        <v>3.43</v>
+        <v>3.63</v>
       </c>
       <c r="F5" t="n">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="G5" t="n">
-        <v>207.09</v>
+        <v>207.48</v>
       </c>
       <c r="H5" t="n">
-        <v>212.34</v>
+        <v>212.74</v>
       </c>
       <c r="I5" t="n">
-        <v>199.73</v>
+        <v>200.1</v>
       </c>
       <c r="J5" t="n">
-        <v>227.06</v>
+        <v>227.49</v>
       </c>
       <c r="K5" t="n">
-        <v>59.81</v>
+        <v>59.95</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -722,19 +722,19 @@
         <v>88</v>
       </c>
       <c r="E6" t="n">
-        <v>3.88</v>
+        <v>3.89</v>
       </c>
       <c r="F6" t="n">
-        <v>0.65</v>
+        <v>0.67</v>
       </c>
       <c r="G6" t="n">
-        <v>207.71</v>
+        <v>207.72</v>
       </c>
       <c r="H6" t="n">
-        <v>212.98</v>
+        <v>212.99</v>
       </c>
       <c r="I6" t="n">
-        <v>200.33</v>
+        <v>200.34</v>
       </c>
       <c r="J6" t="n">
         <v>227.75</v>
@@ -770,31 +770,31 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>9.57</v>
+        <v>9.56</v>
       </c>
       <c r="D7" t="n">
         <v>88</v>
       </c>
       <c r="E7" t="n">
-        <v>3.85</v>
+        <v>3.69</v>
       </c>
       <c r="F7" t="n">
-        <v>0.44</v>
+        <v>0.47</v>
       </c>
       <c r="G7" t="n">
-        <v>9.43</v>
+        <v>9.42</v>
       </c>
       <c r="H7" t="n">
-        <v>9.67</v>
+        <v>9.66</v>
       </c>
       <c r="I7" t="n">
-        <v>9.1</v>
+        <v>9.08</v>
       </c>
       <c r="J7" t="n">
-        <v>10.34</v>
+        <v>10.32</v>
       </c>
       <c r="K7" t="n">
-        <v>56.28</v>
+        <v>56</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
@@ -824,31 +824,31 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1879.45</v>
+        <v>1879.67</v>
       </c>
       <c r="D8" t="n">
         <v>82</v>
       </c>
       <c r="E8" t="n">
-        <v>9.699999999999999</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="F8" t="n">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="G8" t="n">
-        <v>1851.26</v>
+        <v>1851.47</v>
       </c>
       <c r="H8" t="n">
-        <v>1898.24</v>
+        <v>1898.47</v>
       </c>
       <c r="I8" t="n">
-        <v>1785.48</v>
+        <v>1785.69</v>
       </c>
       <c r="J8" t="n">
-        <v>2029.81</v>
+        <v>2030.04</v>
       </c>
       <c r="K8" t="n">
-        <v>57.15</v>
+        <v>57.16</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
@@ -878,31 +878,31 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>404.67</v>
+        <v>404.47</v>
       </c>
       <c r="D9" t="n">
         <v>95</v>
       </c>
       <c r="E9" t="n">
-        <v>0.76</v>
+        <v>0.71</v>
       </c>
       <c r="F9" t="n">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="G9" t="n">
-        <v>398.6</v>
+        <v>398.4</v>
       </c>
       <c r="H9" t="n">
-        <v>408.72</v>
+        <v>408.51</v>
       </c>
       <c r="I9" t="n">
-        <v>384.44</v>
+        <v>384.25</v>
       </c>
       <c r="J9" t="n">
-        <v>437.04</v>
+        <v>436.83</v>
       </c>
       <c r="K9" t="n">
-        <v>65.84</v>
+        <v>65.73</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
@@ -932,7 +932,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>54.52</v>
+        <v>54.53</v>
       </c>
       <c r="D10" t="n">
         <v>80</v>
@@ -941,22 +941,22 @@
         <v>-1.99</v>
       </c>
       <c r="F10" t="n">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="G10" t="n">
-        <v>53.7</v>
+        <v>53.71</v>
       </c>
       <c r="H10" t="n">
         <v>55.07</v>
       </c>
       <c r="I10" t="n">
-        <v>51.79</v>
+        <v>51.8</v>
       </c>
       <c r="J10" t="n">
-        <v>58.88</v>
+        <v>58.89</v>
       </c>
       <c r="K10" t="n">
-        <v>57.19</v>
+        <v>57.21</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
@@ -986,31 +986,31 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>8.52</v>
+        <v>8.48</v>
       </c>
       <c r="D11" t="n">
         <v>80</v>
       </c>
       <c r="E11" t="n">
-        <v>-10.08</v>
+        <v>-10.4</v>
       </c>
       <c r="F11" t="n">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="G11" t="n">
-        <v>8.390000000000001</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="H11" t="n">
-        <v>8.6</v>
+        <v>8.57</v>
       </c>
       <c r="I11" t="n">
-        <v>8.09</v>
+        <v>8.06</v>
       </c>
       <c r="J11" t="n">
-        <v>9.199999999999999</v>
+        <v>9.16</v>
       </c>
       <c r="K11" t="n">
-        <v>56.05</v>
+        <v>55.75</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
@@ -1040,31 +1040,31 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>79.59</v>
+        <v>79.43000000000001</v>
       </c>
       <c r="D12" t="n">
         <v>58</v>
       </c>
       <c r="E12" t="n">
-        <v>3.97</v>
+        <v>3.76</v>
       </c>
       <c r="F12" t="n">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="G12" t="n">
-        <v>78.40000000000001</v>
+        <v>78.23999999999999</v>
       </c>
       <c r="H12" t="n">
-        <v>80.39</v>
+        <v>80.22</v>
       </c>
       <c r="I12" t="n">
-        <v>75.61</v>
+        <v>75.45999999999999</v>
       </c>
       <c r="J12" t="n">
-        <v>85.95999999999999</v>
+        <v>85.78</v>
       </c>
       <c r="K12" t="n">
-        <v>40.37</v>
+        <v>40.1</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
@@ -1094,31 +1094,31 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>148.57</v>
+        <v>148.71</v>
       </c>
       <c r="D13" t="n">
         <v>62</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.33</v>
+        <v>-3.24</v>
       </c>
       <c r="F13" t="n">
-        <v>0.3</v>
+        <v>0.32</v>
       </c>
       <c r="G13" t="n">
-        <v>146.34</v>
+        <v>146.48</v>
       </c>
       <c r="H13" t="n">
-        <v>150.06</v>
+        <v>150.2</v>
       </c>
       <c r="I13" t="n">
-        <v>141.14</v>
+        <v>141.27</v>
       </c>
       <c r="J13" t="n">
-        <v>160.46</v>
+        <v>160.61</v>
       </c>
       <c r="K13" t="n">
-        <v>50.36</v>
+        <v>50.59</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
@@ -1144,31 +1144,31 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>410.6</v>
+        <v>410.36</v>
       </c>
       <c r="D14" t="n">
         <v>50</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.73</v>
+        <v>-0.79</v>
       </c>
       <c r="F14" t="n">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="G14" t="n">
-        <v>404.44</v>
+        <v>404.2</v>
       </c>
       <c r="H14" t="n">
-        <v>414.71</v>
+        <v>414.46</v>
       </c>
       <c r="I14" t="n">
-        <v>390.07</v>
+        <v>389.84</v>
       </c>
       <c r="J14" t="n">
-        <v>443.45</v>
+        <v>443.18</v>
       </c>
       <c r="K14" t="n">
-        <v>42.48</v>
+        <v>42.37</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
@@ -1194,31 +1194,31 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>184.49</v>
+        <v>184.57</v>
       </c>
       <c r="D15" t="n">
         <v>50</v>
       </c>
       <c r="E15" t="n">
-        <v>-4.05</v>
+        <v>-4.01</v>
       </c>
       <c r="F15" t="n">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="G15" t="n">
-        <v>181.72</v>
+        <v>181.8</v>
       </c>
       <c r="H15" t="n">
-        <v>186.33</v>
+        <v>186.42</v>
       </c>
       <c r="I15" t="n">
-        <v>175.27</v>
+        <v>175.34</v>
       </c>
       <c r="J15" t="n">
-        <v>199.25</v>
+        <v>199.34</v>
       </c>
       <c r="K15" t="n">
-        <v>47.64</v>
+        <v>47.77</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
@@ -1244,31 +1244,31 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>55.24</v>
+        <v>55.31</v>
       </c>
       <c r="D16" t="n">
         <v>50</v>
       </c>
       <c r="E16" t="n">
-        <v>-8.34</v>
+        <v>-8.24</v>
       </c>
       <c r="F16" t="n">
-        <v>0.5</v>
+        <v>0.52</v>
       </c>
       <c r="G16" t="n">
-        <v>54.42</v>
+        <v>54.48</v>
       </c>
       <c r="H16" t="n">
-        <v>55.8</v>
+        <v>55.86</v>
       </c>
       <c r="I16" t="n">
-        <v>52.48</v>
+        <v>52.54</v>
       </c>
       <c r="J16" t="n">
-        <v>59.66</v>
+        <v>59.73</v>
       </c>
       <c r="K16" t="n">
-        <v>47.13</v>
+        <v>47.3</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
@@ -1294,28 +1294,28 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>603.48</v>
+        <v>603.49</v>
       </c>
       <c r="D17" t="n">
         <v>42</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.14</v>
+        <v>-1.13</v>
       </c>
       <c r="F17" t="n">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="G17" t="n">
-        <v>594.4299999999999</v>
+        <v>594.4400000000001</v>
       </c>
       <c r="H17" t="n">
-        <v>609.51</v>
+        <v>609.52</v>
       </c>
       <c r="I17" t="n">
         <v>573.3099999999999</v>
       </c>
       <c r="J17" t="n">
-        <v>651.76</v>
+        <v>651.77</v>
       </c>
       <c r="K17" t="n">
         <v>27.16</v>
@@ -1350,25 +1350,25 @@
         <v>42</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.11</v>
+        <v>-1.08</v>
       </c>
       <c r="F18" t="n">
-        <v>0.57</v>
+        <v>0.58</v>
       </c>
       <c r="G18" t="n">
         <v>15.78</v>
       </c>
       <c r="H18" t="n">
-        <v>16.18</v>
+        <v>16.19</v>
       </c>
       <c r="I18" t="n">
         <v>15.22</v>
       </c>
       <c r="J18" t="n">
-        <v>17.3</v>
+        <v>17.31</v>
       </c>
       <c r="K18" t="n">
-        <v>30.1</v>
+        <v>30.15</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
@@ -1394,31 +1394,31 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>45.32</v>
+        <v>45.29</v>
       </c>
       <c r="D19" t="n">
         <v>42</v>
       </c>
       <c r="E19" t="n">
-        <v>-10.06</v>
+        <v>-10.11</v>
       </c>
       <c r="F19" t="n">
         <v>0.38</v>
       </c>
       <c r="G19" t="n">
-        <v>44.64</v>
+        <v>44.62</v>
       </c>
       <c r="H19" t="n">
-        <v>45.77</v>
+        <v>45.75</v>
       </c>
       <c r="I19" t="n">
-        <v>43.05</v>
+        <v>43.03</v>
       </c>
       <c r="J19" t="n">
-        <v>48.95</v>
+        <v>48.92</v>
       </c>
       <c r="K19" t="n">
-        <v>24.5</v>
+        <v>24.44</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
@@ -1494,31 +1494,31 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>135.47</v>
+        <v>135.02</v>
       </c>
       <c r="D21" t="n">
         <v>32</v>
       </c>
       <c r="E21" t="n">
-        <v>-7.23</v>
+        <v>-7.54</v>
       </c>
       <c r="F21" t="n">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="G21" t="n">
-        <v>133.44</v>
+        <v>132.99</v>
       </c>
       <c r="H21" t="n">
-        <v>136.82</v>
+        <v>136.37</v>
       </c>
       <c r="I21" t="n">
-        <v>128.7</v>
+        <v>128.27</v>
       </c>
       <c r="J21" t="n">
-        <v>146.31</v>
+        <v>145.82</v>
       </c>
       <c r="K21" t="n">
-        <v>39.71</v>
+        <v>39.36</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
@@ -1544,31 +1544,31 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>117.1</v>
+        <v>118.24</v>
       </c>
       <c r="D22" t="n">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="E22" t="n">
-        <v>45.81</v>
+        <v>47.23</v>
       </c>
       <c r="F22" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="G22" t="n">
-        <v>115.34</v>
+        <v>116.47</v>
       </c>
       <c r="H22" t="n">
-        <v>118.27</v>
+        <v>119.42</v>
       </c>
       <c r="I22" t="n">
-        <v>111.24</v>
+        <v>112.33</v>
       </c>
       <c r="J22" t="n">
-        <v>126.47</v>
+        <v>127.7</v>
       </c>
       <c r="K22" t="n">
-        <v>68.05</v>
+        <v>68.48</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
@@ -1598,31 +1598,31 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>445.83</v>
+        <v>446.3</v>
       </c>
       <c r="D23" t="n">
         <v>95</v>
       </c>
       <c r="E23" t="n">
-        <v>13.91</v>
+        <v>14.03</v>
       </c>
       <c r="F23" t="n">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="G23" t="n">
-        <v>439.15</v>
+        <v>439.6</v>
       </c>
       <c r="H23" t="n">
-        <v>450.29</v>
+        <v>450.76</v>
       </c>
       <c r="I23" t="n">
-        <v>423.54</v>
+        <v>423.98</v>
       </c>
       <c r="J23" t="n">
-        <v>481.5</v>
+        <v>482</v>
       </c>
       <c r="K23" t="n">
-        <v>65.14</v>
+        <v>65.23</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
@@ -1652,31 +1652,31 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>297.07</v>
+        <v>297.2</v>
       </c>
       <c r="D24" t="n">
         <v>95</v>
       </c>
       <c r="E24" t="n">
-        <v>14.89</v>
+        <v>14.94</v>
       </c>
       <c r="F24" t="n">
         <v>0.33</v>
       </c>
       <c r="G24" t="n">
-        <v>292.61</v>
+        <v>292.74</v>
       </c>
       <c r="H24" t="n">
-        <v>300.04</v>
+        <v>300.17</v>
       </c>
       <c r="I24" t="n">
-        <v>282.22</v>
+        <v>282.34</v>
       </c>
       <c r="J24" t="n">
-        <v>320.84</v>
+        <v>320.98</v>
       </c>
       <c r="K24" t="n">
-        <v>66.93000000000001</v>
+        <v>66.95999999999999</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
@@ -1706,31 +1706,31 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>56.6</v>
+        <v>56.76</v>
       </c>
       <c r="D25" t="n">
         <v>90</v>
       </c>
       <c r="E25" t="n">
-        <v>23.72</v>
+        <v>24.05</v>
       </c>
       <c r="F25" t="n">
-        <v>0.9</v>
+        <v>0.92</v>
       </c>
       <c r="G25" t="n">
-        <v>55.75</v>
+        <v>55.9</v>
       </c>
       <c r="H25" t="n">
-        <v>57.17</v>
+        <v>57.32</v>
       </c>
       <c r="I25" t="n">
-        <v>53.77</v>
+        <v>53.92</v>
       </c>
       <c r="J25" t="n">
-        <v>61.13</v>
+        <v>61.3</v>
       </c>
       <c r="K25" t="n">
-        <v>65.27</v>
+        <v>65.42</v>
       </c>
       <c r="L25" t="inlineStr">
         <is>
@@ -1760,31 +1760,31 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>292.46</v>
+        <v>291.33</v>
       </c>
       <c r="D26" t="n">
         <v>82</v>
       </c>
       <c r="E26" t="n">
-        <v>5.65</v>
+        <v>5.24</v>
       </c>
       <c r="F26" t="n">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="G26" t="n">
-        <v>288.07</v>
+        <v>286.96</v>
       </c>
       <c r="H26" t="n">
-        <v>295.38</v>
+        <v>294.24</v>
       </c>
       <c r="I26" t="n">
-        <v>277.84</v>
+        <v>276.76</v>
       </c>
       <c r="J26" t="n">
-        <v>315.86</v>
+        <v>314.64</v>
       </c>
       <c r="K26" t="n">
-        <v>77.68000000000001</v>
+        <v>75.87</v>
       </c>
       <c r="L26" t="inlineStr">
         <is>
@@ -1805,40 +1805,40 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>GOOGL</t>
+          <t>SMCI</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Tecnología</t>
+          <t>Servidores IA</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>394.09</v>
+        <v>34.97</v>
       </c>
       <c r="D27" t="n">
         <v>82</v>
       </c>
       <c r="E27" t="n">
-        <v>2.83</v>
+        <v>25.25</v>
       </c>
       <c r="F27" t="n">
-        <v>0.43</v>
+        <v>0.57</v>
       </c>
       <c r="G27" t="n">
-        <v>388.18</v>
+        <v>34.45</v>
       </c>
       <c r="H27" t="n">
-        <v>398.03</v>
+        <v>35.32</v>
       </c>
       <c r="I27" t="n">
-        <v>374.39</v>
+        <v>33.22</v>
       </c>
       <c r="J27" t="n">
-        <v>425.62</v>
+        <v>37.77</v>
       </c>
       <c r="K27" t="n">
-        <v>87.59999999999999</v>
+        <v>65.87</v>
       </c>
       <c r="L27" t="inlineStr">
         <is>
@@ -1859,40 +1859,40 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>SMCI</t>
+          <t>SPY</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Servidores IA</t>
+          <t>ETF Mercado</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>35.04</v>
+        <v>739.87</v>
       </c>
       <c r="D28" t="n">
         <v>82</v>
       </c>
       <c r="E28" t="n">
-        <v>25.51</v>
+        <v>3.04</v>
       </c>
       <c r="F28" t="n">
-        <v>0.55</v>
+        <v>0.41</v>
       </c>
       <c r="G28" t="n">
-        <v>34.52</v>
+        <v>728.77</v>
       </c>
       <c r="H28" t="n">
-        <v>35.39</v>
+        <v>747.27</v>
       </c>
       <c r="I28" t="n">
-        <v>33.29</v>
+        <v>702.88</v>
       </c>
       <c r="J28" t="n">
-        <v>37.84</v>
+        <v>799.0599999999999</v>
       </c>
       <c r="K28" t="n">
-        <v>66.09999999999999</v>
+        <v>80.70999999999999</v>
       </c>
       <c r="L28" t="inlineStr">
         <is>
@@ -1913,40 +1913,40 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>SPY</t>
+          <t>QQQ</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>ETF Mercado</t>
+          <t>ETF Nasdaq</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>740.12</v>
+        <v>713.34</v>
       </c>
       <c r="D29" t="n">
         <v>82</v>
       </c>
       <c r="E29" t="n">
-        <v>3.08</v>
+        <v>6.01</v>
       </c>
       <c r="F29" t="n">
-        <v>0.38</v>
+        <v>0.49</v>
       </c>
       <c r="G29" t="n">
-        <v>729.02</v>
+        <v>702.64</v>
       </c>
       <c r="H29" t="n">
-        <v>747.52</v>
+        <v>720.47</v>
       </c>
       <c r="I29" t="n">
-        <v>703.11</v>
+        <v>677.67</v>
       </c>
       <c r="J29" t="n">
-        <v>799.33</v>
+        <v>770.41</v>
       </c>
       <c r="K29" t="n">
-        <v>80.79000000000001</v>
+        <v>86.73</v>
       </c>
       <c r="L29" t="inlineStr">
         <is>
@@ -1967,51 +1967,47 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>QQQ</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>ETF Nasdaq</t>
+          <t>IA / Chips</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>713.5599999999999</v>
+        <v>464.22</v>
       </c>
       <c r="D30" t="n">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="E30" t="n">
-        <v>6.05</v>
+        <v>35.92</v>
       </c>
       <c r="F30" t="n">
-        <v>0.47</v>
+        <v>0.61</v>
       </c>
       <c r="G30" t="n">
-        <v>702.86</v>
+        <v>457.26</v>
       </c>
       <c r="H30" t="n">
-        <v>720.7</v>
+        <v>468.86</v>
       </c>
       <c r="I30" t="n">
-        <v>677.88</v>
+        <v>441.01</v>
       </c>
       <c r="J30" t="n">
-        <v>770.64</v>
+        <v>501.36</v>
       </c>
       <c r="K30" t="n">
-        <v>86.76000000000001</v>
+        <v>80.69</v>
       </c>
       <c r="L30" t="inlineStr">
         <is>
           <t>ALTO</t>
         </is>
       </c>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>🔥</t>
-        </is>
-      </c>
+      <c r="M30" t="inlineStr"/>
       <c r="N30" t="inlineStr">
         <is>
           <t>VIGILAR</t>
@@ -2021,40 +2017,40 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>SOXX</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>IA / Chips</t>
+          <t>ETF Chips</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>465.59</v>
+        <v>530.61</v>
       </c>
       <c r="D31" t="n">
         <v>76</v>
       </c>
       <c r="E31" t="n">
-        <v>36.32</v>
+        <v>14.84</v>
       </c>
       <c r="F31" t="n">
-        <v>0.6</v>
+        <v>0.67</v>
       </c>
       <c r="G31" t="n">
-        <v>458.6</v>
+        <v>522.66</v>
       </c>
       <c r="H31" t="n">
-        <v>470.24</v>
+        <v>535.92</v>
       </c>
       <c r="I31" t="n">
-        <v>442.31</v>
+        <v>504.08</v>
       </c>
       <c r="J31" t="n">
-        <v>502.83</v>
+        <v>573.0599999999999</v>
       </c>
       <c r="K31" t="n">
-        <v>80.78</v>
+        <v>78.61</v>
       </c>
       <c r="L31" t="inlineStr">
         <is>
@@ -2071,40 +2067,40 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>SOXX</t>
+          <t>GOOGL</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>ETF Chips</t>
+          <t>Tecnología</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>529.71</v>
+        <v>393.93</v>
       </c>
       <c r="D32" t="n">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E32" t="n">
-        <v>14.64</v>
+        <v>2.79</v>
       </c>
       <c r="F32" t="n">
-        <v>0.65</v>
+        <v>0.44</v>
       </c>
       <c r="G32" t="n">
-        <v>521.76</v>
+        <v>388.02</v>
       </c>
       <c r="H32" t="n">
-        <v>535.01</v>
+        <v>397.87</v>
       </c>
       <c r="I32" t="n">
-        <v>503.22</v>
+        <v>374.23</v>
       </c>
       <c r="J32" t="n">
-        <v>572.09</v>
+        <v>425.44</v>
       </c>
       <c r="K32" t="n">
-        <v>78.51000000000001</v>
+        <v>87.43000000000001</v>
       </c>
       <c r="L32" t="inlineStr">
         <is>
@@ -2130,31 +2126,31 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>789.1</v>
+        <v>793.75</v>
       </c>
       <c r="D33" t="n">
         <v>68</v>
       </c>
       <c r="E33" t="n">
-        <v>36.89</v>
+        <v>37.7</v>
       </c>
       <c r="F33" t="n">
-        <v>0.99</v>
+        <v>1.01</v>
       </c>
       <c r="G33" t="n">
-        <v>777.26</v>
+        <v>781.84</v>
       </c>
       <c r="H33" t="n">
-        <v>796.99</v>
+        <v>801.6900000000001</v>
       </c>
       <c r="I33" t="n">
-        <v>749.64</v>
+        <v>754.0599999999999</v>
       </c>
       <c r="J33" t="n">
-        <v>852.23</v>
+        <v>857.25</v>
       </c>
       <c r="K33" t="n">
-        <v>89.11</v>
+        <v>89.23</v>
       </c>
       <c r="L33" t="inlineStr">
         <is>
@@ -2180,31 +2176,31 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>126.42</v>
+        <v>126.84</v>
       </c>
       <c r="D34" t="n">
         <v>68</v>
       </c>
       <c r="E34" t="n">
-        <v>31.99</v>
+        <v>32.43</v>
       </c>
       <c r="F34" t="n">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="G34" t="n">
-        <v>124.52</v>
+        <v>124.94</v>
       </c>
       <c r="H34" t="n">
-        <v>127.68</v>
+        <v>128.11</v>
       </c>
       <c r="I34" t="n">
-        <v>120.1</v>
+        <v>120.5</v>
       </c>
       <c r="J34" t="n">
-        <v>136.53</v>
+        <v>136.99</v>
       </c>
       <c r="K34" t="n">
-        <v>88.52</v>
+        <v>88.59</v>
       </c>
       <c r="L34" t="inlineStr">
         <is>
@@ -2230,31 +2226,31 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>440.35</v>
+        <v>438.78</v>
       </c>
       <c r="D35" t="n">
         <v>66</v>
       </c>
       <c r="E35" t="n">
-        <v>12.19</v>
+        <v>11.79</v>
       </c>
       <c r="F35" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="G35" t="n">
-        <v>433.74</v>
+        <v>432.2</v>
       </c>
       <c r="H35" t="n">
-        <v>444.75</v>
+        <v>443.17</v>
       </c>
       <c r="I35" t="n">
-        <v>418.33</v>
+        <v>416.84</v>
       </c>
       <c r="J35" t="n">
-        <v>475.58</v>
+        <v>473.88</v>
       </c>
       <c r="K35" t="n">
-        <v>77.09</v>
+        <v>76.73</v>
       </c>
       <c r="L35" t="inlineStr">
         <is>
@@ -2271,40 +2267,40 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>QCOM</t>
+          <t>AMZN</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Chips</t>
+          <t>Tecnología</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>231.81</v>
+        <v>272.12</v>
       </c>
       <c r="D36" t="n">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="E36" t="n">
-        <v>37.67</v>
+        <v>0.03</v>
       </c>
       <c r="F36" t="n">
-        <v>1.09</v>
+        <v>0.35</v>
       </c>
       <c r="G36" t="n">
-        <v>228.33</v>
+        <v>268.04</v>
       </c>
       <c r="H36" t="n">
-        <v>234.13</v>
+        <v>274.84</v>
       </c>
       <c r="I36" t="n">
-        <v>220.22</v>
+        <v>258.51</v>
       </c>
       <c r="J36" t="n">
-        <v>250.35</v>
+        <v>293.89</v>
       </c>
       <c r="K36" t="n">
-        <v>89</v>
+        <v>77.69</v>
       </c>
       <c r="L36" t="inlineStr">
         <is>
@@ -2314,47 +2310,47 @@
       <c r="M36" t="inlineStr"/>
       <c r="N36" t="inlineStr">
         <is>
-          <t>NO COMPRAR</t>
+          <t>VIGILAR</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>AMZN</t>
+          <t>QCOM</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Tecnología</t>
+          <t>Chips</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>272.02</v>
+        <v>234.09</v>
       </c>
       <c r="D37" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="E37" t="n">
-        <v>-0.01</v>
+        <v>39.02</v>
       </c>
       <c r="F37" t="n">
-        <v>0.34</v>
+        <v>1.12</v>
       </c>
       <c r="G37" t="n">
-        <v>267.93</v>
+        <v>230.58</v>
       </c>
       <c r="H37" t="n">
-        <v>274.74</v>
+        <v>236.43</v>
       </c>
       <c r="I37" t="n">
-        <v>258.41</v>
+        <v>222.39</v>
       </c>
       <c r="J37" t="n">
-        <v>293.78</v>
+        <v>252.82</v>
       </c>
       <c r="K37" t="n">
-        <v>77.48</v>
+        <v>89.2</v>
       </c>
       <c r="L37" t="inlineStr">
         <is>

--- a/analisis_acciones.xlsx
+++ b/analisis_acciones.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N37"/>
+  <dimension ref="A1:P37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -449,40 +449,50 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
+          <t>ATR</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>ATR %</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
           <t>Entrada min</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Entrada max</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Stop loss</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Objetivo</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>RSI</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Riesgo</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Hot Score</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Senal</t>
         </is>
@@ -500,43 +510,49 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>220.77</v>
+        <v>220</v>
       </c>
       <c r="D2" t="n">
         <v>95</v>
       </c>
       <c r="E2" t="n">
-        <v>11.23</v>
+        <v>10.84</v>
       </c>
       <c r="F2" t="n">
-        <v>0.65</v>
+        <v>0.67</v>
       </c>
       <c r="G2" t="n">
-        <v>217.46</v>
+        <v>7.7</v>
       </c>
       <c r="H2" t="n">
-        <v>222.98</v>
+        <v>3.5</v>
       </c>
       <c r="I2" t="n">
-        <v>209.74</v>
+        <v>216.92</v>
       </c>
       <c r="J2" t="n">
-        <v>238.44</v>
+        <v>221.92</v>
       </c>
       <c r="K2" t="n">
-        <v>65.62</v>
-      </c>
-      <c r="L2" t="inlineStr">
+        <v>208.46</v>
+      </c>
+      <c r="L2" t="n">
+        <v>239.24</v>
+      </c>
+      <c r="M2" t="n">
+        <v>65.20999999999999</v>
+      </c>
+      <c r="N2" t="inlineStr">
         <is>
           <t>MEDIO</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>🔥🔥</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>POSIBLE COMPRA</t>
         </is>
@@ -545,52 +561,58 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ASML</t>
+          <t>AVGO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Chips</t>
+          <t>IA / Chips</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1550.03</v>
+        <v>429.25</v>
       </c>
       <c r="D3" t="n">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="E3" t="n">
-        <v>11.82</v>
+        <v>3.06</v>
       </c>
       <c r="F3" t="n">
-        <v>0.74</v>
+        <v>0.41</v>
       </c>
       <c r="G3" t="n">
-        <v>1526.78</v>
+        <v>15.4</v>
       </c>
       <c r="H3" t="n">
-        <v>1565.53</v>
+        <v>3.59</v>
       </c>
       <c r="I3" t="n">
-        <v>1472.53</v>
+        <v>423.09</v>
       </c>
       <c r="J3" t="n">
-        <v>1674.03</v>
+        <v>433.1</v>
       </c>
       <c r="K3" t="n">
-        <v>58.38</v>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>MEDIO</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
+        <v>406.15</v>
+      </c>
+      <c r="L3" t="n">
+        <v>467.75</v>
+      </c>
+      <c r="M3" t="n">
+        <v>61.38</v>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>BAJO</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
         <is>
           <t>🔥🔥</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>POSIBLE COMPRA</t>
         </is>
@@ -599,52 +621,58 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AVGO</t>
+          <t>ASML</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>IA / Chips</t>
+          <t>Chips</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>428.58</v>
+        <v>1552.29</v>
       </c>
       <c r="D4" t="n">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="E4" t="n">
-        <v>2.9</v>
+        <v>11.98</v>
       </c>
       <c r="F4" t="n">
-        <v>0.39</v>
+        <v>0.77</v>
       </c>
       <c r="G4" t="n">
-        <v>422.16</v>
+        <v>61.22</v>
       </c>
       <c r="H4" t="n">
-        <v>432.87</v>
+        <v>3.94</v>
       </c>
       <c r="I4" t="n">
-        <v>407.16</v>
+        <v>1527.8</v>
       </c>
       <c r="J4" t="n">
-        <v>462.87</v>
+        <v>1567.6</v>
       </c>
       <c r="K4" t="n">
-        <v>61.04</v>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>BAJO</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
+        <v>1460.46</v>
+      </c>
+      <c r="L4" t="n">
+        <v>1705.34</v>
+      </c>
+      <c r="M4" t="n">
+        <v>58.62</v>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>MEDIO</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
         <is>
           <t>🔥🔥</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>POSIBLE COMPRA</t>
         </is>
@@ -653,52 +681,58 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ARM</t>
+          <t>AI</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Chips</t>
+          <t>IA</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>210.63</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="D5" t="n">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="E5" t="n">
-        <v>3.63</v>
+        <v>2.66</v>
       </c>
       <c r="F5" t="n">
-        <v>0.61</v>
+        <v>0.51</v>
       </c>
       <c r="G5" t="n">
-        <v>207.48</v>
+        <v>0.43</v>
       </c>
       <c r="H5" t="n">
-        <v>212.74</v>
+        <v>4.58</v>
       </c>
       <c r="I5" t="n">
-        <v>200.1</v>
+        <v>9.289999999999999</v>
       </c>
       <c r="J5" t="n">
-        <v>227.49</v>
+        <v>9.57</v>
       </c>
       <c r="K5" t="n">
-        <v>59.95</v>
-      </c>
-      <c r="L5" t="inlineStr">
+        <v>8.81</v>
+      </c>
+      <c r="L5" t="n">
+        <v>10.55</v>
+      </c>
+      <c r="M5" t="n">
+        <v>54.28</v>
+      </c>
+      <c r="N5" t="inlineStr">
         <is>
           <t>BAJO</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>🔥🔥</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>POSIBLE COMPRA</t>
         </is>
@@ -707,52 +741,58 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>COIN</t>
+          <t>KLAC</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Cripto / Trading</t>
+          <t>Equipos chips</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>210.88</v>
+        <v>1876.74</v>
       </c>
       <c r="D6" t="n">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E6" t="n">
-        <v>3.89</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="F6" t="n">
-        <v>0.67</v>
+        <v>0.46</v>
       </c>
       <c r="G6" t="n">
-        <v>207.72</v>
+        <v>82.78</v>
       </c>
       <c r="H6" t="n">
-        <v>212.99</v>
+        <v>4.41</v>
       </c>
       <c r="I6" t="n">
-        <v>200.34</v>
+        <v>1843.63</v>
       </c>
       <c r="J6" t="n">
-        <v>227.75</v>
+        <v>1897.43</v>
       </c>
       <c r="K6" t="n">
-        <v>58.47</v>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>BAJO</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
+        <v>1752.58</v>
+      </c>
+      <c r="L6" t="n">
+        <v>2083.68</v>
+      </c>
+      <c r="M6" t="n">
+        <v>56.97</v>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>MEDIO</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
         <is>
           <t>🔥🔥</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>POSIBLE COMPRA</t>
         </is>
@@ -761,52 +801,58 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AI</t>
+          <t>COIN</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>IA</t>
+          <t>Cripto / Trading</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>9.56</v>
+        <v>210.26</v>
       </c>
       <c r="D7" t="n">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="E7" t="n">
-        <v>3.69</v>
+        <v>3.58</v>
       </c>
       <c r="F7" t="n">
-        <v>0.47</v>
+        <v>0.7</v>
       </c>
       <c r="G7" t="n">
-        <v>9.42</v>
+        <v>11.88</v>
       </c>
       <c r="H7" t="n">
-        <v>9.66</v>
+        <v>5.65</v>
       </c>
       <c r="I7" t="n">
-        <v>9.08</v>
+        <v>205.51</v>
       </c>
       <c r="J7" t="n">
-        <v>10.32</v>
+        <v>213.23</v>
       </c>
       <c r="K7" t="n">
-        <v>56</v>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>BAJO</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
+        <v>192.44</v>
+      </c>
+      <c r="L7" t="n">
+        <v>239.96</v>
+      </c>
+      <c r="M7" t="n">
+        <v>58.18</v>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>MEDIO</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
         <is>
           <t>🔥🔥</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>POSIBLE COMPRA</t>
         </is>
@@ -815,52 +861,58 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>KLAC</t>
+          <t>TSM</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Equipos chips</t>
+          <t>Chips</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1879.67</v>
+        <v>405.14</v>
       </c>
       <c r="D8" t="n">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="E8" t="n">
-        <v>9.710000000000001</v>
+        <v>0.88</v>
       </c>
       <c r="F8" t="n">
-        <v>0.43</v>
+        <v>0.66</v>
       </c>
       <c r="G8" t="n">
-        <v>1851.47</v>
+        <v>15.67</v>
       </c>
       <c r="H8" t="n">
-        <v>1898.47</v>
+        <v>3.87</v>
       </c>
       <c r="I8" t="n">
-        <v>1785.69</v>
+        <v>398.87</v>
       </c>
       <c r="J8" t="n">
-        <v>2030.04</v>
+        <v>409.05</v>
       </c>
       <c r="K8" t="n">
-        <v>57.16</v>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>MEDIO</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>🔥🔥</t>
-        </is>
+        <v>381.63</v>
+      </c>
+      <c r="L8" t="n">
+        <v>444.32</v>
+      </c>
+      <c r="M8" t="n">
+        <v>66.11</v>
       </c>
       <c r="N8" t="inlineStr">
+        <is>
+          <t>BAJO</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>🔥</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
         <is>
           <t>POSIBLE COMPRA</t>
         </is>
@@ -869,52 +921,58 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>SLB</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Chips</t>
+          <t>Energía</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>404.47</v>
+        <v>54.57</v>
       </c>
       <c r="D9" t="n">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="E9" t="n">
-        <v>0.71</v>
+        <v>-1.91</v>
       </c>
       <c r="F9" t="n">
-        <v>0.63</v>
+        <v>0.28</v>
       </c>
       <c r="G9" t="n">
-        <v>398.4</v>
+        <v>1.66</v>
       </c>
       <c r="H9" t="n">
-        <v>408.51</v>
+        <v>3.05</v>
       </c>
       <c r="I9" t="n">
-        <v>384.25</v>
+        <v>53.9</v>
       </c>
       <c r="J9" t="n">
-        <v>436.83</v>
+        <v>54.99</v>
       </c>
       <c r="K9" t="n">
-        <v>65.73</v>
-      </c>
-      <c r="L9" t="inlineStr">
+        <v>52.08</v>
+      </c>
+      <c r="L9" t="n">
+        <v>58.73</v>
+      </c>
+      <c r="M9" t="n">
+        <v>57.36</v>
+      </c>
+      <c r="N9" t="inlineStr">
         <is>
           <t>BAJO</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>🔥</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="P9" t="inlineStr">
         <is>
           <t>POSIBLE COMPRA</t>
         </is>
@@ -923,52 +981,54 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SLB</t>
+          <t>SOUN</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Energía</t>
+          <t>IA</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>54.53</v>
+        <v>8.390000000000001</v>
       </c>
       <c r="D10" t="n">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.99</v>
+        <v>-11.41</v>
       </c>
       <c r="F10" t="n">
-        <v>0.25</v>
+        <v>0.66</v>
       </c>
       <c r="G10" t="n">
-        <v>53.71</v>
+        <v>0.65</v>
       </c>
       <c r="H10" t="n">
-        <v>55.07</v>
+        <v>7.7</v>
       </c>
       <c r="I10" t="n">
-        <v>51.8</v>
+        <v>8.130000000000001</v>
       </c>
       <c r="J10" t="n">
-        <v>58.89</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="K10" t="n">
-        <v>57.21</v>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>BAJO</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>🔥</t>
-        </is>
+        <v>7.42</v>
+      </c>
+      <c r="L10" t="n">
+        <v>10</v>
+      </c>
+      <c r="M10" t="n">
+        <v>54.8</v>
       </c>
       <c r="N10" t="inlineStr">
+        <is>
+          <t>MEDIO</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
         <is>
           <t>POSIBLE COMPRA</t>
         </is>
@@ -977,206 +1037,226 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SOUN</t>
+          <t>HOOD</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>IA</t>
+          <t>Trading</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>8.48</v>
+        <v>79.22</v>
       </c>
       <c r="D11" t="n">
-        <v>80</v>
+        <v>46</v>
       </c>
       <c r="E11" t="n">
-        <v>-10.4</v>
+        <v>3.49</v>
       </c>
       <c r="F11" t="n">
-        <v>0.59</v>
+        <v>0.43</v>
       </c>
       <c r="G11" t="n">
-        <v>8.359999999999999</v>
+        <v>4.15</v>
       </c>
       <c r="H11" t="n">
-        <v>8.57</v>
+        <v>5.23</v>
       </c>
       <c r="I11" t="n">
-        <v>8.06</v>
+        <v>77.56999999999999</v>
       </c>
       <c r="J11" t="n">
-        <v>9.16</v>
+        <v>80.26000000000001</v>
       </c>
       <c r="K11" t="n">
-        <v>55.75</v>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>BAJO</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
+        <v>73.01000000000001</v>
+      </c>
+      <c r="L11" t="n">
+        <v>89.59</v>
+      </c>
+      <c r="M11" t="n">
+        <v>39.75</v>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>MEDIO</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
         <is>
           <t>🔥</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>POSIBLE COMPRA</t>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>NO COMPRAR</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>HOOD</t>
+          <t>XOM</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Trading</t>
+          <t>Energía</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>79.43000000000001</v>
+        <v>149.1</v>
       </c>
       <c r="D12" t="n">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="E12" t="n">
-        <v>3.76</v>
+        <v>-2.99</v>
       </c>
       <c r="F12" t="n">
-        <v>0.41</v>
+        <v>0.35</v>
       </c>
       <c r="G12" t="n">
-        <v>78.23999999999999</v>
+        <v>4.01</v>
       </c>
       <c r="H12" t="n">
-        <v>80.22</v>
+        <v>2.69</v>
       </c>
       <c r="I12" t="n">
-        <v>75.45999999999999</v>
+        <v>147.5</v>
       </c>
       <c r="J12" t="n">
-        <v>85.78</v>
+        <v>150.1</v>
       </c>
       <c r="K12" t="n">
-        <v>40.1</v>
-      </c>
-      <c r="L12" t="inlineStr">
+        <v>143.09</v>
+      </c>
+      <c r="L12" t="n">
+        <v>159.11</v>
+      </c>
+      <c r="M12" t="n">
+        <v>51.24</v>
+      </c>
+      <c r="N12" t="inlineStr">
         <is>
           <t>BAJO</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>🔥</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>NO COMPRAR</t>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>VIGILAR</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>XOM</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Energía</t>
+          <t>Tecnología</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>148.71</v>
+        <v>408.84</v>
       </c>
       <c r="D13" t="n">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.24</v>
+        <v>-1.16</v>
       </c>
       <c r="F13" t="n">
-        <v>0.32</v>
+        <v>0.46</v>
       </c>
       <c r="G13" t="n">
-        <v>146.48</v>
+        <v>11.8</v>
       </c>
       <c r="H13" t="n">
-        <v>150.2</v>
+        <v>2.89</v>
       </c>
       <c r="I13" t="n">
-        <v>141.27</v>
+        <v>404.12</v>
       </c>
       <c r="J13" t="n">
-        <v>160.61</v>
+        <v>411.79</v>
       </c>
       <c r="K13" t="n">
-        <v>50.59</v>
-      </c>
-      <c r="L13" t="inlineStr">
+        <v>391.14</v>
+      </c>
+      <c r="L13" t="n">
+        <v>438.34</v>
+      </c>
+      <c r="M13" t="n">
+        <v>41.67</v>
+      </c>
+      <c r="N13" t="inlineStr">
         <is>
           <t>BAJO</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>VIGILAR</t>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>NO COMPRAR</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>CVX</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Tecnología</t>
+          <t>Energía</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>410.36</v>
+        <v>184.61</v>
       </c>
       <c r="D14" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.79</v>
+        <v>-3.99</v>
       </c>
       <c r="F14" t="n">
-        <v>0.42</v>
+        <v>0.31</v>
       </c>
       <c r="G14" t="n">
-        <v>404.2</v>
+        <v>4.61</v>
       </c>
       <c r="H14" t="n">
-        <v>414.46</v>
+        <v>2.5</v>
       </c>
       <c r="I14" t="n">
-        <v>389.84</v>
+        <v>182.77</v>
       </c>
       <c r="J14" t="n">
-        <v>443.18</v>
+        <v>185.76</v>
       </c>
       <c r="K14" t="n">
-        <v>42.37</v>
-      </c>
-      <c r="L14" t="inlineStr">
+        <v>177.7</v>
+      </c>
+      <c r="L14" t="n">
+        <v>196.13</v>
+      </c>
+      <c r="M14" t="n">
+        <v>47.84</v>
+      </c>
+      <c r="N14" t="inlineStr">
         <is>
           <t>BAJO</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr">
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
         <is>
           <t>NO COMPRAR</t>
         </is>
@@ -1185,7 +1265,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>CVX</t>
+          <t>OXY</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1194,39 +1274,45 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>184.57</v>
+        <v>55.24</v>
       </c>
       <c r="D15" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="E15" t="n">
-        <v>-4.01</v>
+        <v>-8.34</v>
       </c>
       <c r="F15" t="n">
-        <v>0.28</v>
+        <v>0.54</v>
       </c>
       <c r="G15" t="n">
-        <v>181.8</v>
+        <v>1.85</v>
       </c>
       <c r="H15" t="n">
-        <v>186.42</v>
+        <v>3.35</v>
       </c>
       <c r="I15" t="n">
-        <v>175.34</v>
+        <v>54.5</v>
       </c>
       <c r="J15" t="n">
-        <v>199.34</v>
+        <v>55.7</v>
       </c>
       <c r="K15" t="n">
-        <v>47.77</v>
-      </c>
-      <c r="L15" t="inlineStr">
+        <v>52.47</v>
+      </c>
+      <c r="L15" t="n">
+        <v>59.87</v>
+      </c>
+      <c r="M15" t="n">
+        <v>47.12</v>
+      </c>
+      <c r="N15" t="inlineStr">
         <is>
           <t>BAJO</t>
         </is>
       </c>
-      <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr">
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
         <is>
           <t>NO COMPRAR</t>
         </is>
@@ -1235,48 +1321,54 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>OXY</t>
+          <t>META</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Energía</t>
+          <t>Tecnología</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>55.31</v>
+        <v>600.71</v>
       </c>
       <c r="D16" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="E16" t="n">
-        <v>-8.24</v>
+        <v>-1.59</v>
       </c>
       <c r="F16" t="n">
         <v>0.52</v>
       </c>
       <c r="G16" t="n">
-        <v>54.48</v>
+        <v>18.2</v>
       </c>
       <c r="H16" t="n">
-        <v>55.86</v>
+        <v>3.03</v>
       </c>
       <c r="I16" t="n">
-        <v>52.54</v>
+        <v>593.4299999999999</v>
       </c>
       <c r="J16" t="n">
-        <v>59.73</v>
+        <v>605.26</v>
       </c>
       <c r="K16" t="n">
-        <v>47.3</v>
-      </c>
-      <c r="L16" t="inlineStr">
+        <v>573.41</v>
+      </c>
+      <c r="L16" t="n">
+        <v>646.21</v>
+      </c>
+      <c r="M16" t="n">
+        <v>26.64</v>
+      </c>
+      <c r="N16" t="inlineStr">
         <is>
           <t>BAJO</t>
         </is>
       </c>
-      <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr">
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
         <is>
           <t>NO COMPRAR</t>
         </is>
@@ -1285,48 +1377,54 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>META</t>
+          <t>PYPL</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Tecnología</t>
+          <t>Pagos</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>603.49</v>
+        <v>45.16</v>
       </c>
       <c r="D17" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.13</v>
+        <v>-10.38</v>
       </c>
       <c r="F17" t="n">
-        <v>0.48</v>
+        <v>0.42</v>
       </c>
       <c r="G17" t="n">
-        <v>594.4400000000001</v>
+        <v>1.56</v>
       </c>
       <c r="H17" t="n">
-        <v>609.52</v>
+        <v>3.45</v>
       </c>
       <c r="I17" t="n">
-        <v>573.3099999999999</v>
+        <v>44.54</v>
       </c>
       <c r="J17" t="n">
-        <v>651.77</v>
+        <v>45.55</v>
       </c>
       <c r="K17" t="n">
-        <v>27.16</v>
-      </c>
-      <c r="L17" t="inlineStr">
+        <v>42.82</v>
+      </c>
+      <c r="L17" t="n">
+        <v>49.06</v>
+      </c>
+      <c r="M17" t="n">
+        <v>24.14</v>
+      </c>
+      <c r="N17" t="inlineStr">
         <is>
           <t>BAJO</t>
         </is>
       </c>
-      <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr">
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
         <is>
           <t>NO COMPRAR</t>
         </is>
@@ -1344,39 +1442,45 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>16.02</v>
+        <v>15.98</v>
       </c>
       <c r="D18" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.08</v>
+        <v>-1.33</v>
       </c>
       <c r="F18" t="n">
-        <v>0.58</v>
+        <v>0.62</v>
       </c>
       <c r="G18" t="n">
-        <v>15.78</v>
+        <v>0.82</v>
       </c>
       <c r="H18" t="n">
+        <v>5.11</v>
+      </c>
+      <c r="I18" t="n">
+        <v>15.66</v>
+      </c>
+      <c r="J18" t="n">
         <v>16.19</v>
       </c>
-      <c r="I18" t="n">
-        <v>15.22</v>
-      </c>
-      <c r="J18" t="n">
-        <v>17.31</v>
-      </c>
       <c r="K18" t="n">
-        <v>30.15</v>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>BAJO</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr"/>
+        <v>14.76</v>
+      </c>
+      <c r="L18" t="n">
+        <v>18.03</v>
+      </c>
+      <c r="M18" t="n">
+        <v>29.75</v>
+      </c>
       <c r="N18" t="inlineStr">
+        <is>
+          <t>MEDIO</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
         <is>
           <t>NO COMPRAR</t>
         </is>
@@ -1385,48 +1489,54 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>PYPL</t>
+          <t>UPST</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Pagos</t>
+          <t>Fintech IA</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>45.29</v>
+        <v>28.75</v>
       </c>
       <c r="D19" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="E19" t="n">
-        <v>-10.11</v>
+        <v>-10.38</v>
       </c>
       <c r="F19" t="n">
-        <v>0.38</v>
+        <v>0.45</v>
       </c>
       <c r="G19" t="n">
-        <v>44.62</v>
+        <v>1.81</v>
       </c>
       <c r="H19" t="n">
-        <v>45.75</v>
+        <v>6.28</v>
       </c>
       <c r="I19" t="n">
-        <v>43.03</v>
+        <v>28.03</v>
       </c>
       <c r="J19" t="n">
-        <v>48.92</v>
+        <v>29.2</v>
       </c>
       <c r="K19" t="n">
-        <v>24.44</v>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>BAJO</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr"/>
+        <v>26.04</v>
+      </c>
+      <c r="L19" t="n">
+        <v>33.27</v>
+      </c>
+      <c r="M19" t="n">
+        <v>34.1</v>
+      </c>
       <c r="N19" t="inlineStr">
+        <is>
+          <t>MEDIO</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
         <is>
           <t>NO COMPRAR</t>
         </is>
@@ -1435,48 +1545,54 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>UPST</t>
+          <t>PLTR</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Fintech IA</t>
+          <t>IA / Software</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>28.98</v>
+        <v>134.91</v>
       </c>
       <c r="D20" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E20" t="n">
-        <v>-9.66</v>
+        <v>-7.61</v>
       </c>
       <c r="F20" t="n">
-        <v>0.42</v>
+        <v>0.55</v>
       </c>
       <c r="G20" t="n">
-        <v>28.55</v>
+        <v>6.24</v>
       </c>
       <c r="H20" t="n">
-        <v>29.27</v>
+        <v>4.63</v>
       </c>
       <c r="I20" t="n">
-        <v>27.53</v>
+        <v>132.42</v>
       </c>
       <c r="J20" t="n">
-        <v>31.3</v>
+        <v>136.48</v>
       </c>
       <c r="K20" t="n">
-        <v>34.71</v>
-      </c>
-      <c r="L20" t="inlineStr">
+        <v>125.55</v>
+      </c>
+      <c r="L20" t="n">
+        <v>150.52</v>
+      </c>
+      <c r="M20" t="n">
+        <v>39.28</v>
+      </c>
+      <c r="N20" t="inlineStr">
         <is>
           <t>BAJO</t>
         </is>
       </c>
-      <c r="M20" t="inlineStr"/>
-      <c r="N20" t="inlineStr">
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
         <is>
           <t>NO COMPRAR</t>
         </is>
@@ -1485,102 +1601,118 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>PLTR</t>
+          <t>RKLB</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>IA / Software</t>
+          <t>Espacial</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>135.02</v>
+        <v>117.7</v>
       </c>
       <c r="D21" t="n">
-        <v>32</v>
+        <v>88</v>
       </c>
       <c r="E21" t="n">
-        <v>-7.54</v>
+        <v>46.56</v>
       </c>
       <c r="F21" t="n">
-        <v>0.52</v>
+        <v>1.34</v>
       </c>
       <c r="G21" t="n">
-        <v>132.99</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="H21" t="n">
-        <v>136.37</v>
+        <v>7.12</v>
       </c>
       <c r="I21" t="n">
-        <v>128.27</v>
+        <v>114.35</v>
       </c>
       <c r="J21" t="n">
-        <v>145.82</v>
+        <v>119.8</v>
       </c>
       <c r="K21" t="n">
-        <v>39.36</v>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>BAJO</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr"/>
+        <v>105.13</v>
+      </c>
+      <c r="L21" t="n">
+        <v>138.65</v>
+      </c>
+      <c r="M21" t="n">
+        <v>68.28</v>
+      </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>NO COMPRAR</t>
+          <t>ALTO</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>🔥🔥</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>VIGILAR</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>RKLB</t>
+          <t>AMAT</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Espacial</t>
+          <t>Equipos chips</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>118.24</v>
+        <v>447.37</v>
       </c>
       <c r="D22" t="n">
         <v>95</v>
       </c>
       <c r="E22" t="n">
-        <v>47.23</v>
+        <v>14.31</v>
       </c>
       <c r="F22" t="n">
-        <v>1.28</v>
+        <v>0.58</v>
       </c>
       <c r="G22" t="n">
-        <v>116.47</v>
+        <v>17.86</v>
       </c>
       <c r="H22" t="n">
-        <v>119.42</v>
+        <v>3.99</v>
       </c>
       <c r="I22" t="n">
-        <v>112.33</v>
+        <v>440.22</v>
       </c>
       <c r="J22" t="n">
-        <v>127.7</v>
+        <v>451.84</v>
       </c>
       <c r="K22" t="n">
-        <v>68.48</v>
-      </c>
-      <c r="L22" t="inlineStr">
+        <v>420.57</v>
+      </c>
+      <c r="L22" t="n">
+        <v>492.03</v>
+      </c>
+      <c r="M22" t="n">
+        <v>65.45</v>
+      </c>
+      <c r="N22" t="inlineStr">
         <is>
           <t>ALTO</t>
         </is>
       </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>🔥🔥</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr">
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>🔥</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
         <is>
           <t>VIGILAR</t>
         </is>
@@ -1589,7 +1721,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>AMAT</t>
+          <t>LRCX</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1598,43 +1730,49 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>446.3</v>
+        <v>297.85</v>
       </c>
       <c r="D23" t="n">
         <v>95</v>
       </c>
       <c r="E23" t="n">
-        <v>14.03</v>
+        <v>15.19</v>
       </c>
       <c r="F23" t="n">
-        <v>0.54</v>
+        <v>0.36</v>
       </c>
       <c r="G23" t="n">
-        <v>439.6</v>
+        <v>13.7</v>
       </c>
       <c r="H23" t="n">
-        <v>450.76</v>
+        <v>4.6</v>
       </c>
       <c r="I23" t="n">
-        <v>423.98</v>
+        <v>292.36</v>
       </c>
       <c r="J23" t="n">
-        <v>482</v>
+        <v>301.27</v>
       </c>
       <c r="K23" t="n">
-        <v>65.23</v>
-      </c>
-      <c r="L23" t="inlineStr">
+        <v>277.29</v>
+      </c>
+      <c r="L23" t="n">
+        <v>332.1</v>
+      </c>
+      <c r="M23" t="n">
+        <v>67.15000000000001</v>
+      </c>
+      <c r="N23" t="inlineStr">
         <is>
           <t>ALTO</t>
         </is>
       </c>
-      <c r="M23" t="inlineStr">
+      <c r="O23" t="inlineStr">
         <is>
           <t>🔥</t>
         </is>
       </c>
-      <c r="N23" t="inlineStr">
+      <c r="P23" t="inlineStr">
         <is>
           <t>VIGILAR</t>
         </is>
@@ -1643,52 +1781,58 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>LRCX</t>
+          <t>AAPL</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Equipos chips</t>
+          <t>Tecnología</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>297.2</v>
+        <v>291.51</v>
       </c>
       <c r="D24" t="n">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="E24" t="n">
-        <v>14.94</v>
+        <v>5.3</v>
       </c>
       <c r="F24" t="n">
-        <v>0.33</v>
+        <v>0.42</v>
       </c>
       <c r="G24" t="n">
-        <v>292.74</v>
+        <v>6.64</v>
       </c>
       <c r="H24" t="n">
-        <v>300.17</v>
+        <v>2.28</v>
       </c>
       <c r="I24" t="n">
-        <v>282.34</v>
+        <v>288.85</v>
       </c>
       <c r="J24" t="n">
-        <v>320.98</v>
+        <v>293.17</v>
       </c>
       <c r="K24" t="n">
-        <v>66.95999999999999</v>
-      </c>
-      <c r="L24" t="inlineStr">
+        <v>281.55</v>
+      </c>
+      <c r="L24" t="n">
+        <v>308.1</v>
+      </c>
+      <c r="M24" t="n">
+        <v>76.16</v>
+      </c>
+      <c r="N24" t="inlineStr">
         <is>
           <t>ALTO</t>
         </is>
       </c>
-      <c r="M24" t="inlineStr">
+      <c r="O24" t="inlineStr">
         <is>
           <t>🔥</t>
         </is>
       </c>
-      <c r="N24" t="inlineStr">
+      <c r="P24" t="inlineStr">
         <is>
           <t>VIGILAR</t>
         </is>
@@ -1706,43 +1850,49 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>56.76</v>
+        <v>56.44</v>
       </c>
       <c r="D25" t="n">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="E25" t="n">
-        <v>24.05</v>
+        <v>23.37</v>
       </c>
       <c r="F25" t="n">
-        <v>0.92</v>
+        <v>0.96</v>
       </c>
       <c r="G25" t="n">
-        <v>55.9</v>
+        <v>4.22</v>
       </c>
       <c r="H25" t="n">
-        <v>57.32</v>
+        <v>7.47</v>
       </c>
       <c r="I25" t="n">
-        <v>53.92</v>
+        <v>54.75</v>
       </c>
       <c r="J25" t="n">
-        <v>61.3</v>
+        <v>57.49</v>
       </c>
       <c r="K25" t="n">
-        <v>65.42</v>
-      </c>
-      <c r="L25" t="inlineStr">
+        <v>50.12</v>
+      </c>
+      <c r="L25" t="n">
+        <v>66.98</v>
+      </c>
+      <c r="M25" t="n">
+        <v>65.09999999999999</v>
+      </c>
+      <c r="N25" t="inlineStr">
         <is>
           <t>ALTO</t>
         </is>
       </c>
-      <c r="M25" t="inlineStr">
+      <c r="O25" t="inlineStr">
         <is>
           <t>🔥</t>
         </is>
       </c>
-      <c r="N25" t="inlineStr">
+      <c r="P25" t="inlineStr">
         <is>
           <t>VIGILAR</t>
         </is>
@@ -1751,52 +1901,58 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>SPY</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Tecnología</t>
+          <t>ETF Mercado</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>291.33</v>
+        <v>739.02</v>
       </c>
       <c r="D26" t="n">
         <v>82</v>
       </c>
       <c r="E26" t="n">
-        <v>5.24</v>
+        <v>2.93</v>
       </c>
       <c r="F26" t="n">
-        <v>0.38</v>
+        <v>0.45</v>
       </c>
       <c r="G26" t="n">
-        <v>286.96</v>
+        <v>6.71</v>
       </c>
       <c r="H26" t="n">
-        <v>294.24</v>
+        <v>0.91</v>
       </c>
       <c r="I26" t="n">
-        <v>276.76</v>
+        <v>736.33</v>
       </c>
       <c r="J26" t="n">
-        <v>314.64</v>
+        <v>740.7</v>
       </c>
       <c r="K26" t="n">
-        <v>75.87</v>
-      </c>
-      <c r="L26" t="inlineStr">
+        <v>728.95</v>
+      </c>
+      <c r="L26" t="n">
+        <v>755.79</v>
+      </c>
+      <c r="M26" t="n">
+        <v>80.42</v>
+      </c>
+      <c r="N26" t="inlineStr">
         <is>
           <t>ALTO</t>
         </is>
       </c>
-      <c r="M26" t="inlineStr">
+      <c r="O26" t="inlineStr">
         <is>
           <t>🔥</t>
         </is>
       </c>
-      <c r="N26" t="inlineStr">
+      <c r="P26" t="inlineStr">
         <is>
           <t>VIGILAR</t>
         </is>
@@ -1805,52 +1961,58 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>SMCI</t>
+          <t>QQQ</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Servidores IA</t>
+          <t>ETF Nasdaq</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>34.97</v>
+        <v>712.28</v>
       </c>
       <c r="D27" t="n">
         <v>82</v>
       </c>
       <c r="E27" t="n">
-        <v>25.25</v>
+        <v>5.86</v>
       </c>
       <c r="F27" t="n">
-        <v>0.57</v>
+        <v>0.52</v>
       </c>
       <c r="G27" t="n">
-        <v>34.45</v>
+        <v>9.84</v>
       </c>
       <c r="H27" t="n">
-        <v>35.32</v>
+        <v>1.38</v>
       </c>
       <c r="I27" t="n">
-        <v>33.22</v>
+        <v>708.34</v>
       </c>
       <c r="J27" t="n">
-        <v>37.77</v>
+        <v>714.74</v>
       </c>
       <c r="K27" t="n">
-        <v>65.87</v>
-      </c>
-      <c r="L27" t="inlineStr">
+        <v>697.51</v>
+      </c>
+      <c r="L27" t="n">
+        <v>736.89</v>
+      </c>
+      <c r="M27" t="n">
+        <v>86.58</v>
+      </c>
+      <c r="N27" t="inlineStr">
         <is>
           <t>ALTO</t>
         </is>
       </c>
-      <c r="M27" t="inlineStr">
+      <c r="O27" t="inlineStr">
         <is>
           <t>🔥</t>
         </is>
       </c>
-      <c r="N27" t="inlineStr">
+      <c r="P27" t="inlineStr">
         <is>
           <t>VIGILAR</t>
         </is>
@@ -1859,52 +2021,58 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>SPY</t>
+          <t>ARM</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>ETF Mercado</t>
+          <t>Chips</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>739.87</v>
+        <v>210.86</v>
       </c>
       <c r="D28" t="n">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="E28" t="n">
-        <v>3.04</v>
+        <v>3.74</v>
       </c>
       <c r="F28" t="n">
-        <v>0.41</v>
+        <v>0.65</v>
       </c>
       <c r="G28" t="n">
-        <v>728.77</v>
+        <v>18.49</v>
       </c>
       <c r="H28" t="n">
-        <v>747.27</v>
+        <v>8.77</v>
       </c>
       <c r="I28" t="n">
-        <v>702.88</v>
+        <v>203.46</v>
       </c>
       <c r="J28" t="n">
-        <v>799.0599999999999</v>
+        <v>215.48</v>
       </c>
       <c r="K28" t="n">
-        <v>80.70999999999999</v>
-      </c>
-      <c r="L28" t="inlineStr">
+        <v>183.12</v>
+      </c>
+      <c r="L28" t="n">
+        <v>257.09</v>
+      </c>
+      <c r="M28" t="n">
+        <v>60.02</v>
+      </c>
+      <c r="N28" t="inlineStr">
         <is>
           <t>ALTO</t>
         </is>
       </c>
-      <c r="M28" t="inlineStr">
+      <c r="O28" t="inlineStr">
         <is>
           <t>🔥</t>
         </is>
       </c>
-      <c r="N28" t="inlineStr">
+      <c r="P28" t="inlineStr">
         <is>
           <t>VIGILAR</t>
         </is>
@@ -1913,52 +2081,58 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>QQQ</t>
+          <t>SOXX</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>ETF Nasdaq</t>
+          <t>ETF Chips</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>713.34</v>
+        <v>529.76</v>
       </c>
       <c r="D29" t="n">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="E29" t="n">
-        <v>6.01</v>
+        <v>14.65</v>
       </c>
       <c r="F29" t="n">
-        <v>0.49</v>
+        <v>0.7</v>
       </c>
       <c r="G29" t="n">
-        <v>702.64</v>
+        <v>17.31</v>
       </c>
       <c r="H29" t="n">
-        <v>720.47</v>
+        <v>3.27</v>
       </c>
       <c r="I29" t="n">
-        <v>677.67</v>
+        <v>522.83</v>
       </c>
       <c r="J29" t="n">
-        <v>770.41</v>
+        <v>534.09</v>
       </c>
       <c r="K29" t="n">
-        <v>86.73</v>
-      </c>
-      <c r="L29" t="inlineStr">
+        <v>503.79</v>
+      </c>
+      <c r="L29" t="n">
+        <v>573.04</v>
+      </c>
+      <c r="M29" t="n">
+        <v>78.51000000000001</v>
+      </c>
+      <c r="N29" t="inlineStr">
         <is>
           <t>ALTO</t>
         </is>
       </c>
-      <c r="M29" t="inlineStr">
+      <c r="O29" t="inlineStr">
         <is>
           <t>🔥</t>
         </is>
       </c>
-      <c r="N29" t="inlineStr">
+      <c r="P29" t="inlineStr">
         <is>
           <t>VIGILAR</t>
         </is>
@@ -1967,48 +2141,54 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>GOOGL</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>IA / Chips</t>
+          <t>Tecnología</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>464.22</v>
+        <v>393.32</v>
       </c>
       <c r="D30" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="E30" t="n">
-        <v>35.92</v>
+        <v>2.63</v>
       </c>
       <c r="F30" t="n">
-        <v>0.61</v>
+        <v>0.46</v>
       </c>
       <c r="G30" t="n">
-        <v>457.26</v>
+        <v>10.42</v>
       </c>
       <c r="H30" t="n">
-        <v>468.86</v>
+        <v>2.65</v>
       </c>
       <c r="I30" t="n">
-        <v>441.01</v>
+        <v>389.15</v>
       </c>
       <c r="J30" t="n">
-        <v>501.36</v>
+        <v>395.93</v>
       </c>
       <c r="K30" t="n">
-        <v>80.69</v>
-      </c>
-      <c r="L30" t="inlineStr">
+        <v>377.69</v>
+      </c>
+      <c r="L30" t="n">
+        <v>419.38</v>
+      </c>
+      <c r="M30" t="n">
+        <v>86.79000000000001</v>
+      </c>
+      <c r="N30" t="inlineStr">
         <is>
           <t>ALTO</t>
         </is>
       </c>
-      <c r="M30" t="inlineStr"/>
-      <c r="N30" t="inlineStr">
+      <c r="O30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
         <is>
           <t>VIGILAR</t>
         </is>
@@ -2017,48 +2197,54 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>SOXX</t>
+          <t>SMCI</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>ETF Chips</t>
+          <t>Servidores IA</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>530.61</v>
+        <v>34.74</v>
       </c>
       <c r="D31" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="E31" t="n">
-        <v>14.84</v>
+        <v>24.43</v>
       </c>
       <c r="F31" t="n">
-        <v>0.67</v>
+        <v>0.61</v>
       </c>
       <c r="G31" t="n">
-        <v>522.66</v>
+        <v>2.25</v>
       </c>
       <c r="H31" t="n">
-        <v>535.92</v>
+        <v>6.48</v>
       </c>
       <c r="I31" t="n">
-        <v>504.08</v>
+        <v>33.84</v>
       </c>
       <c r="J31" t="n">
-        <v>573.0599999999999</v>
+        <v>35.3</v>
       </c>
       <c r="K31" t="n">
-        <v>78.61</v>
-      </c>
-      <c r="L31" t="inlineStr">
+        <v>31.37</v>
+      </c>
+      <c r="L31" t="n">
+        <v>40.36</v>
+      </c>
+      <c r="M31" t="n">
+        <v>65.15000000000001</v>
+      </c>
+      <c r="N31" t="inlineStr">
         <is>
           <t>ALTO</t>
         </is>
       </c>
-      <c r="M31" t="inlineStr"/>
-      <c r="N31" t="inlineStr">
+      <c r="O31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
         <is>
           <t>VIGILAR</t>
         </is>
@@ -2067,48 +2253,54 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>GOOGL</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Tecnología</t>
+          <t>IA / Chips</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>393.93</v>
+        <v>463.73</v>
       </c>
       <c r="D32" t="n">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="E32" t="n">
-        <v>2.79</v>
+        <v>35.78</v>
       </c>
       <c r="F32" t="n">
-        <v>0.44</v>
+        <v>0.64</v>
       </c>
       <c r="G32" t="n">
-        <v>388.02</v>
+        <v>27.28</v>
       </c>
       <c r="H32" t="n">
-        <v>397.87</v>
+        <v>5.88</v>
       </c>
       <c r="I32" t="n">
-        <v>374.23</v>
+        <v>452.82</v>
       </c>
       <c r="J32" t="n">
-        <v>425.44</v>
+        <v>470.55</v>
       </c>
       <c r="K32" t="n">
-        <v>87.43000000000001</v>
-      </c>
-      <c r="L32" t="inlineStr">
+        <v>422.81</v>
+      </c>
+      <c r="L32" t="n">
+        <v>531.9299999999999</v>
+      </c>
+      <c r="M32" t="n">
+        <v>80.66</v>
+      </c>
+      <c r="N32" t="inlineStr">
         <is>
           <t>ALTO</t>
         </is>
       </c>
-      <c r="M32" t="inlineStr"/>
-      <c r="N32" t="inlineStr">
+      <c r="O32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
         <is>
           <t>VIGILAR</t>
         </is>
@@ -2117,48 +2309,54 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>MU</t>
+          <t>TSLA</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Memoria / Chips</t>
+          <t>Autos / Tech</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>793.75</v>
+        <v>438.65</v>
       </c>
       <c r="D33" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="E33" t="n">
-        <v>37.7</v>
+        <v>11.76</v>
       </c>
       <c r="F33" t="n">
-        <v>1.01</v>
+        <v>0.76</v>
       </c>
       <c r="G33" t="n">
-        <v>781.84</v>
+        <v>15.07</v>
       </c>
       <c r="H33" t="n">
-        <v>801.6900000000001</v>
+        <v>3.44</v>
       </c>
       <c r="I33" t="n">
-        <v>754.0599999999999</v>
+        <v>432.62</v>
       </c>
       <c r="J33" t="n">
-        <v>857.25</v>
+        <v>442.42</v>
       </c>
       <c r="K33" t="n">
-        <v>89.23</v>
-      </c>
-      <c r="L33" t="inlineStr">
+        <v>416.04</v>
+      </c>
+      <c r="L33" t="n">
+        <v>476.33</v>
+      </c>
+      <c r="M33" t="n">
+        <v>76.69</v>
+      </c>
+      <c r="N33" t="inlineStr">
         <is>
           <t>ALTO</t>
         </is>
       </c>
-      <c r="M33" t="inlineStr"/>
-      <c r="N33" t="inlineStr">
+      <c r="O33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
         <is>
           <t>VIGILAR</t>
         </is>
@@ -2167,48 +2365,54 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>INTC</t>
+          <t>MU</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Chips</t>
+          <t>Memoria / Chips</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>126.84</v>
+        <v>797.75</v>
       </c>
       <c r="D34" t="n">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="E34" t="n">
-        <v>32.43</v>
+        <v>38.39</v>
       </c>
       <c r="F34" t="n">
-        <v>0.77</v>
+        <v>1.07</v>
       </c>
       <c r="G34" t="n">
-        <v>124.94</v>
+        <v>45.86</v>
       </c>
       <c r="H34" t="n">
-        <v>128.11</v>
+        <v>5.75</v>
       </c>
       <c r="I34" t="n">
-        <v>120.5</v>
+        <v>779.4</v>
       </c>
       <c r="J34" t="n">
-        <v>136.99</v>
+        <v>809.22</v>
       </c>
       <c r="K34" t="n">
-        <v>88.59</v>
-      </c>
-      <c r="L34" t="inlineStr">
+        <v>728.95</v>
+      </c>
+      <c r="L34" t="n">
+        <v>912.41</v>
+      </c>
+      <c r="M34" t="n">
+        <v>89.31999999999999</v>
+      </c>
+      <c r="N34" t="inlineStr">
         <is>
           <t>ALTO</t>
         </is>
       </c>
-      <c r="M34" t="inlineStr"/>
-      <c r="N34" t="inlineStr">
+      <c r="O34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
         <is>
           <t>VIGILAR</t>
         </is>
@@ -2217,48 +2421,54 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>TSLA</t>
+          <t>INTC</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Autos / Tech</t>
+          <t>Chips</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>438.78</v>
+        <v>125.89</v>
       </c>
       <c r="D35" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="E35" t="n">
-        <v>11.79</v>
+        <v>31.44</v>
       </c>
       <c r="F35" t="n">
-        <v>0.71</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="G35" t="n">
-        <v>432.2</v>
+        <v>8.390000000000001</v>
       </c>
       <c r="H35" t="n">
-        <v>443.17</v>
+        <v>6.66</v>
       </c>
       <c r="I35" t="n">
-        <v>416.84</v>
+        <v>122.53</v>
       </c>
       <c r="J35" t="n">
-        <v>473.88</v>
+        <v>127.99</v>
       </c>
       <c r="K35" t="n">
-        <v>76.73</v>
-      </c>
-      <c r="L35" t="inlineStr">
+        <v>113.31</v>
+      </c>
+      <c r="L35" t="n">
+        <v>146.86</v>
+      </c>
+      <c r="M35" t="n">
+        <v>88.45</v>
+      </c>
+      <c r="N35" t="inlineStr">
         <is>
           <t>ALTO</t>
         </is>
       </c>
-      <c r="M35" t="inlineStr"/>
-      <c r="N35" t="inlineStr">
+      <c r="O35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
         <is>
           <t>VIGILAR</t>
         </is>
@@ -2276,39 +2486,45 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>272.12</v>
+        <v>271.44</v>
       </c>
       <c r="D36" t="n">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="E36" t="n">
-        <v>0.03</v>
+        <v>-0.22</v>
       </c>
       <c r="F36" t="n">
-        <v>0.35</v>
+        <v>0.38</v>
       </c>
       <c r="G36" t="n">
-        <v>268.04</v>
+        <v>7.18</v>
       </c>
       <c r="H36" t="n">
-        <v>274.84</v>
+        <v>2.65</v>
       </c>
       <c r="I36" t="n">
-        <v>258.51</v>
+        <v>268.57</v>
       </c>
       <c r="J36" t="n">
-        <v>293.89</v>
+        <v>273.24</v>
       </c>
       <c r="K36" t="n">
-        <v>77.69</v>
-      </c>
-      <c r="L36" t="inlineStr">
+        <v>260.66</v>
+      </c>
+      <c r="L36" t="n">
+        <v>289.4</v>
+      </c>
+      <c r="M36" t="n">
+        <v>76.39</v>
+      </c>
+      <c r="N36" t="inlineStr">
         <is>
           <t>ALTO</t>
         </is>
       </c>
-      <c r="M36" t="inlineStr"/>
-      <c r="N36" t="inlineStr">
+      <c r="O36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
         <is>
           <t>VIGILAR</t>
         </is>
@@ -2326,39 +2542,45 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>234.09</v>
+        <v>234.51</v>
       </c>
       <c r="D37" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="E37" t="n">
-        <v>39.02</v>
+        <v>39.27</v>
       </c>
       <c r="F37" t="n">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="G37" t="n">
-        <v>230.58</v>
+        <v>16.45</v>
       </c>
       <c r="H37" t="n">
-        <v>236.43</v>
+        <v>7.01</v>
       </c>
       <c r="I37" t="n">
-        <v>222.39</v>
+        <v>227.93</v>
       </c>
       <c r="J37" t="n">
-        <v>252.82</v>
+        <v>238.62</v>
       </c>
       <c r="K37" t="n">
-        <v>89.2</v>
-      </c>
-      <c r="L37" t="inlineStr">
+        <v>209.83</v>
+      </c>
+      <c r="L37" t="n">
+        <v>275.64</v>
+      </c>
+      <c r="M37" t="n">
+        <v>89.23</v>
+      </c>
+      <c r="N37" t="inlineStr">
         <is>
           <t>ALTO</t>
         </is>
       </c>
-      <c r="M37" t="inlineStr"/>
-      <c r="N37" t="inlineStr">
+      <c r="O37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
         <is>
           <t>NO COMPRAR</t>
         </is>

--- a/analisis_acciones.xlsx
+++ b/analisis_acciones.xlsx
@@ -510,37 +510,37 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>220</v>
+        <v>220.64</v>
       </c>
       <c r="D2" t="n">
         <v>95</v>
       </c>
       <c r="E2" t="n">
-        <v>10.84</v>
+        <v>11.16</v>
       </c>
       <c r="F2" t="n">
-        <v>0.67</v>
+        <v>0.72</v>
       </c>
       <c r="G2" t="n">
         <v>7.7</v>
       </c>
       <c r="H2" t="n">
-        <v>3.5</v>
+        <v>3.49</v>
       </c>
       <c r="I2" t="n">
-        <v>216.92</v>
+        <v>217.56</v>
       </c>
       <c r="J2" t="n">
-        <v>221.92</v>
+        <v>222.56</v>
       </c>
       <c r="K2" t="n">
-        <v>208.46</v>
+        <v>209.1</v>
       </c>
       <c r="L2" t="n">
-        <v>239.24</v>
+        <v>239.88</v>
       </c>
       <c r="M2" t="n">
-        <v>65.20999999999999</v>
+        <v>65.55</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -570,16 +570,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>429.25</v>
+        <v>429.48</v>
       </c>
       <c r="D3" t="n">
         <v>95</v>
       </c>
       <c r="E3" t="n">
-        <v>3.06</v>
+        <v>3.12</v>
       </c>
       <c r="F3" t="n">
-        <v>0.41</v>
+        <v>0.46</v>
       </c>
       <c r="G3" t="n">
         <v>15.4</v>
@@ -588,19 +588,19 @@
         <v>3.59</v>
       </c>
       <c r="I3" t="n">
-        <v>423.09</v>
+        <v>423.32</v>
       </c>
       <c r="J3" t="n">
-        <v>433.1</v>
+        <v>433.33</v>
       </c>
       <c r="K3" t="n">
-        <v>406.15</v>
+        <v>406.38</v>
       </c>
       <c r="L3" t="n">
-        <v>467.75</v>
+        <v>467.98</v>
       </c>
       <c r="M3" t="n">
-        <v>61.38</v>
+        <v>61.5</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -621,46 +621,46 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ASML</t>
+          <t>COIN</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Chips</t>
+          <t>Cripto / Trading</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1552.29</v>
+        <v>214.54</v>
       </c>
       <c r="D4" t="n">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="E4" t="n">
-        <v>11.98</v>
+        <v>5.69</v>
       </c>
       <c r="F4" t="n">
-        <v>0.77</v>
+        <v>0.79</v>
       </c>
       <c r="G4" t="n">
-        <v>61.22</v>
+        <v>11.99</v>
       </c>
       <c r="H4" t="n">
-        <v>3.94</v>
+        <v>5.59</v>
       </c>
       <c r="I4" t="n">
-        <v>1527.8</v>
+        <v>209.74</v>
       </c>
       <c r="J4" t="n">
-        <v>1567.6</v>
+        <v>217.53</v>
       </c>
       <c r="K4" t="n">
-        <v>1460.46</v>
+        <v>196.55</v>
       </c>
       <c r="L4" t="n">
-        <v>1705.34</v>
+        <v>244.51</v>
       </c>
       <c r="M4" t="n">
-        <v>58.62</v>
+        <v>60.13</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -690,37 +690,37 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>9.470000000000001</v>
+        <v>9.52</v>
       </c>
       <c r="D5" t="n">
         <v>92</v>
       </c>
       <c r="E5" t="n">
-        <v>2.66</v>
+        <v>3.2</v>
       </c>
       <c r="F5" t="n">
-        <v>0.51</v>
+        <v>0.58</v>
       </c>
       <c r="G5" t="n">
         <v>0.43</v>
       </c>
       <c r="H5" t="n">
-        <v>4.58</v>
+        <v>4.56</v>
       </c>
       <c r="I5" t="n">
-        <v>9.289999999999999</v>
+        <v>9.34</v>
       </c>
       <c r="J5" t="n">
-        <v>9.57</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="K5" t="n">
-        <v>8.81</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="L5" t="n">
-        <v>10.55</v>
+        <v>10.6</v>
       </c>
       <c r="M5" t="n">
-        <v>54.28</v>
+        <v>55.17</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
@@ -750,37 +750,37 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1876.74</v>
+        <v>1861.92</v>
       </c>
       <c r="D6" t="n">
         <v>86</v>
       </c>
       <c r="E6" t="n">
-        <v>9.539999999999999</v>
+        <v>8.67</v>
       </c>
       <c r="F6" t="n">
-        <v>0.46</v>
+        <v>0.57</v>
       </c>
       <c r="G6" t="n">
         <v>82.78</v>
       </c>
       <c r="H6" t="n">
-        <v>4.41</v>
+        <v>4.45</v>
       </c>
       <c r="I6" t="n">
-        <v>1843.63</v>
+        <v>1828.8</v>
       </c>
       <c r="J6" t="n">
-        <v>1897.43</v>
+        <v>1882.61</v>
       </c>
       <c r="K6" t="n">
-        <v>1752.58</v>
+        <v>1737.75</v>
       </c>
       <c r="L6" t="n">
-        <v>2083.68</v>
+        <v>2068.86</v>
       </c>
       <c r="M6" t="n">
-        <v>56.97</v>
+        <v>55.84</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
@@ -801,55 +801,55 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>COIN</t>
+          <t>TSM</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Cripto / Trading</t>
+          <t>Chips</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>210.26</v>
+        <v>404.6</v>
       </c>
       <c r="D7" t="n">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="E7" t="n">
-        <v>3.58</v>
+        <v>0.74</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7</v>
+        <v>0.71</v>
       </c>
       <c r="G7" t="n">
-        <v>11.88</v>
+        <v>15.67</v>
       </c>
       <c r="H7" t="n">
-        <v>5.65</v>
+        <v>3.87</v>
       </c>
       <c r="I7" t="n">
-        <v>205.51</v>
+        <v>398.33</v>
       </c>
       <c r="J7" t="n">
-        <v>213.23</v>
+        <v>408.52</v>
       </c>
       <c r="K7" t="n">
-        <v>192.44</v>
+        <v>381.09</v>
       </c>
       <c r="L7" t="n">
-        <v>239.96</v>
+        <v>443.78</v>
       </c>
       <c r="M7" t="n">
-        <v>58.18</v>
+        <v>65.8</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>MEDIO</t>
+          <t>BAJO</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -861,46 +861,46 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>SLB</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Chips</t>
+          <t>Energía</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>405.14</v>
+        <v>54.79</v>
       </c>
       <c r="D8" t="n">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="E8" t="n">
-        <v>0.88</v>
+        <v>-1.51</v>
       </c>
       <c r="F8" t="n">
-        <v>0.66</v>
+        <v>0.32</v>
       </c>
       <c r="G8" t="n">
-        <v>15.67</v>
+        <v>1.68</v>
       </c>
       <c r="H8" t="n">
-        <v>3.87</v>
+        <v>3.07</v>
       </c>
       <c r="I8" t="n">
-        <v>398.87</v>
+        <v>54.12</v>
       </c>
       <c r="J8" t="n">
-        <v>409.05</v>
+        <v>55.21</v>
       </c>
       <c r="K8" t="n">
-        <v>381.63</v>
+        <v>52.27</v>
       </c>
       <c r="L8" t="n">
-        <v>444.32</v>
+        <v>58.99</v>
       </c>
       <c r="M8" t="n">
-        <v>66.11</v>
+        <v>58.12</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
@@ -921,57 +921,53 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SLB</t>
+          <t>SOUN</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Energía</t>
+          <t>IA</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>54.57</v>
+        <v>8.5</v>
       </c>
       <c r="D9" t="n">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.91</v>
+        <v>-10.24</v>
       </c>
       <c r="F9" t="n">
-        <v>0.28</v>
+        <v>0.74</v>
       </c>
       <c r="G9" t="n">
-        <v>1.66</v>
+        <v>0.65</v>
       </c>
       <c r="H9" t="n">
-        <v>3.05</v>
+        <v>7.6</v>
       </c>
       <c r="I9" t="n">
-        <v>53.9</v>
+        <v>8.24</v>
       </c>
       <c r="J9" t="n">
-        <v>54.99</v>
+        <v>8.66</v>
       </c>
       <c r="K9" t="n">
-        <v>52.08</v>
+        <v>7.53</v>
       </c>
       <c r="L9" t="n">
-        <v>58.73</v>
+        <v>10.12</v>
       </c>
       <c r="M9" t="n">
-        <v>57.36</v>
+        <v>55.9</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>BAJO</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>🔥</t>
-        </is>
-      </c>
+          <t>MEDIO</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>POSIBLE COMPRA</t>
@@ -981,162 +977,162 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SOUN</t>
+          <t>HOOD</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>IA</t>
+          <t>Trading</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>8.390000000000001</v>
+        <v>80.22</v>
       </c>
       <c r="D10" t="n">
-        <v>76</v>
+        <v>54</v>
       </c>
       <c r="E10" t="n">
-        <v>-11.41</v>
+        <v>4.79</v>
       </c>
       <c r="F10" t="n">
-        <v>0.66</v>
+        <v>0.51</v>
       </c>
       <c r="G10" t="n">
-        <v>0.65</v>
+        <v>4.2</v>
       </c>
       <c r="H10" t="n">
-        <v>7.7</v>
+        <v>5.24</v>
       </c>
       <c r="I10" t="n">
-        <v>8.130000000000001</v>
+        <v>78.54000000000001</v>
       </c>
       <c r="J10" t="n">
-        <v>8.550000000000001</v>
+        <v>81.27</v>
       </c>
       <c r="K10" t="n">
-        <v>7.42</v>
+        <v>73.92</v>
       </c>
       <c r="L10" t="n">
-        <v>10</v>
+        <v>90.73</v>
       </c>
       <c r="M10" t="n">
-        <v>54.8</v>
+        <v>41.41</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
           <t>MEDIO</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr"/>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>🔥</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>POSIBLE COMPRA</t>
+          <t>NO COMPRAR</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>HOOD</t>
+          <t>XOM</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Trading</t>
+          <t>Energía</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>79.22</v>
+        <v>149.15</v>
       </c>
       <c r="D11" t="n">
-        <v>46</v>
+        <v>66</v>
       </c>
       <c r="E11" t="n">
-        <v>3.49</v>
+        <v>-2.95</v>
       </c>
       <c r="F11" t="n">
-        <v>0.43</v>
+        <v>0.4</v>
       </c>
       <c r="G11" t="n">
-        <v>4.15</v>
+        <v>4.02</v>
       </c>
       <c r="H11" t="n">
-        <v>5.23</v>
+        <v>2.69</v>
       </c>
       <c r="I11" t="n">
-        <v>77.56999999999999</v>
+        <v>147.55</v>
       </c>
       <c r="J11" t="n">
-        <v>80.26000000000001</v>
+        <v>150.16</v>
       </c>
       <c r="K11" t="n">
-        <v>73.01000000000001</v>
+        <v>143.13</v>
       </c>
       <c r="L11" t="n">
-        <v>89.59</v>
+        <v>159.19</v>
       </c>
       <c r="M11" t="n">
-        <v>39.75</v>
+        <v>51.33</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>MEDIO</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>🔥</t>
-        </is>
-      </c>
+          <t>BAJO</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>NO COMPRAR</t>
+          <t>VIGILAR</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>XOM</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Energía</t>
+          <t>Tecnología</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>149.1</v>
+        <v>411.66</v>
       </c>
       <c r="D12" t="n">
-        <v>66</v>
+        <v>54</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.99</v>
+        <v>-0.47</v>
       </c>
       <c r="F12" t="n">
-        <v>0.35</v>
+        <v>0.51</v>
       </c>
       <c r="G12" t="n">
-        <v>4.01</v>
+        <v>11.8</v>
       </c>
       <c r="H12" t="n">
-        <v>2.69</v>
+        <v>2.87</v>
       </c>
       <c r="I12" t="n">
-        <v>147.5</v>
+        <v>406.94</v>
       </c>
       <c r="J12" t="n">
-        <v>150.1</v>
+        <v>414.61</v>
       </c>
       <c r="K12" t="n">
-        <v>143.09</v>
+        <v>393.96</v>
       </c>
       <c r="L12" t="n">
-        <v>159.11</v>
+        <v>441.16</v>
       </c>
       <c r="M12" t="n">
-        <v>51.24</v>
+        <v>42.99</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
@@ -1146,53 +1142,53 @@
       <c r="O12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>VIGILAR</t>
+          <t>NO COMPRAR</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>CVX</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Tecnología</t>
+          <t>Energía</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>408.84</v>
+        <v>184.75</v>
       </c>
       <c r="D13" t="n">
         <v>54</v>
       </c>
       <c r="E13" t="n">
-        <v>-1.16</v>
+        <v>-3.91</v>
       </c>
       <c r="F13" t="n">
-        <v>0.46</v>
+        <v>0.36</v>
       </c>
       <c r="G13" t="n">
-        <v>11.8</v>
+        <v>4.61</v>
       </c>
       <c r="H13" t="n">
-        <v>2.89</v>
+        <v>2.49</v>
       </c>
       <c r="I13" t="n">
-        <v>404.12</v>
+        <v>182.91</v>
       </c>
       <c r="J13" t="n">
-        <v>411.79</v>
+        <v>185.91</v>
       </c>
       <c r="K13" t="n">
-        <v>391.14</v>
+        <v>177.84</v>
       </c>
       <c r="L13" t="n">
-        <v>438.34</v>
+        <v>196.28</v>
       </c>
       <c r="M13" t="n">
-        <v>41.67</v>
+        <v>48.07</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
@@ -1209,7 +1205,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>CVX</t>
+          <t>OXY</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1218,37 +1214,37 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>184.61</v>
+        <v>55.19</v>
       </c>
       <c r="D14" t="n">
         <v>54</v>
       </c>
       <c r="E14" t="n">
-        <v>-3.99</v>
+        <v>-8.44</v>
       </c>
       <c r="F14" t="n">
-        <v>0.31</v>
+        <v>0.6</v>
       </c>
       <c r="G14" t="n">
-        <v>4.61</v>
+        <v>1.85</v>
       </c>
       <c r="H14" t="n">
-        <v>2.5</v>
+        <v>3.35</v>
       </c>
       <c r="I14" t="n">
-        <v>182.77</v>
+        <v>54.45</v>
       </c>
       <c r="J14" t="n">
-        <v>185.76</v>
+        <v>55.65</v>
       </c>
       <c r="K14" t="n">
-        <v>177.7</v>
+        <v>52.41</v>
       </c>
       <c r="L14" t="n">
-        <v>196.13</v>
+        <v>59.81</v>
       </c>
       <c r="M14" t="n">
-        <v>47.84</v>
+        <v>46.96</v>
       </c>
       <c r="N14" t="inlineStr">
         <is>
@@ -1265,46 +1261,46 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>OXY</t>
+          <t>META</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Energía</t>
+          <t>Tecnología</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>55.24</v>
+        <v>603.33</v>
       </c>
       <c r="D15" t="n">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="E15" t="n">
-        <v>-8.34</v>
+        <v>-1.16</v>
       </c>
       <c r="F15" t="n">
-        <v>0.54</v>
+        <v>0.59</v>
       </c>
       <c r="G15" t="n">
-        <v>1.85</v>
+        <v>18.2</v>
       </c>
       <c r="H15" t="n">
-        <v>3.35</v>
+        <v>3.02</v>
       </c>
       <c r="I15" t="n">
-        <v>54.5</v>
+        <v>596.05</v>
       </c>
       <c r="J15" t="n">
-        <v>55.7</v>
+        <v>607.87</v>
       </c>
       <c r="K15" t="n">
-        <v>52.47</v>
+        <v>576.03</v>
       </c>
       <c r="L15" t="n">
-        <v>59.87</v>
+        <v>648.8200000000001</v>
       </c>
       <c r="M15" t="n">
-        <v>47.12</v>
+        <v>27.13</v>
       </c>
       <c r="N15" t="inlineStr">
         <is>
@@ -1321,46 +1317,46 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>META</t>
+          <t>PYPL</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Tecnología</t>
+          <t>Pagos</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>600.71</v>
+        <v>45.29</v>
       </c>
       <c r="D16" t="n">
         <v>46</v>
       </c>
       <c r="E16" t="n">
-        <v>-1.59</v>
+        <v>-10.12</v>
       </c>
       <c r="F16" t="n">
-        <v>0.52</v>
+        <v>0.48</v>
       </c>
       <c r="G16" t="n">
-        <v>18.2</v>
+        <v>1.56</v>
       </c>
       <c r="H16" t="n">
-        <v>3.03</v>
+        <v>3.44</v>
       </c>
       <c r="I16" t="n">
-        <v>593.4299999999999</v>
+        <v>44.67</v>
       </c>
       <c r="J16" t="n">
-        <v>605.26</v>
+        <v>45.68</v>
       </c>
       <c r="K16" t="n">
-        <v>573.41</v>
+        <v>42.95</v>
       </c>
       <c r="L16" t="n">
-        <v>646.21</v>
+        <v>49.19</v>
       </c>
       <c r="M16" t="n">
-        <v>26.64</v>
+        <v>24.43</v>
       </c>
       <c r="N16" t="inlineStr">
         <is>
@@ -1377,50 +1373,50 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>PYPL</t>
+          <t>SOFI</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Pagos</t>
+          <t>Fintech</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>45.16</v>
+        <v>16.07</v>
       </c>
       <c r="D17" t="n">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="E17" t="n">
-        <v>-10.38</v>
+        <v>-0.83</v>
       </c>
       <c r="F17" t="n">
-        <v>0.42</v>
+        <v>0.7</v>
       </c>
       <c r="G17" t="n">
-        <v>1.56</v>
+        <v>0.82</v>
       </c>
       <c r="H17" t="n">
-        <v>3.45</v>
+        <v>5.08</v>
       </c>
       <c r="I17" t="n">
-        <v>44.54</v>
+        <v>15.74</v>
       </c>
       <c r="J17" t="n">
-        <v>45.55</v>
+        <v>16.27</v>
       </c>
       <c r="K17" t="n">
-        <v>42.82</v>
+        <v>14.84</v>
       </c>
       <c r="L17" t="n">
-        <v>49.06</v>
+        <v>18.11</v>
       </c>
       <c r="M17" t="n">
-        <v>24.14</v>
+        <v>30.54</v>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>BAJO</t>
+          <t>MEDIO</t>
         </is>
       </c>
       <c r="O17" t="inlineStr"/>
@@ -1433,46 +1429,46 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>SOFI</t>
+          <t>UPST</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Fintech</t>
+          <t>Fintech IA</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>15.98</v>
+        <v>29</v>
       </c>
       <c r="D18" t="n">
         <v>38</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.33</v>
+        <v>-9.6</v>
       </c>
       <c r="F18" t="n">
-        <v>0.62</v>
+        <v>0.5</v>
       </c>
       <c r="G18" t="n">
-        <v>0.82</v>
+        <v>1.81</v>
       </c>
       <c r="H18" t="n">
-        <v>5.11</v>
+        <v>6.23</v>
       </c>
       <c r="I18" t="n">
-        <v>15.66</v>
+        <v>28.28</v>
       </c>
       <c r="J18" t="n">
-        <v>16.19</v>
+        <v>29.45</v>
       </c>
       <c r="K18" t="n">
-        <v>14.76</v>
+        <v>26.29</v>
       </c>
       <c r="L18" t="n">
-        <v>18.03</v>
+        <v>33.52</v>
       </c>
       <c r="M18" t="n">
-        <v>29.75</v>
+        <v>34.8</v>
       </c>
       <c r="N18" t="inlineStr">
         <is>
@@ -1489,50 +1485,50 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>UPST</t>
+          <t>PLTR</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Fintech IA</t>
+          <t>IA / Software</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>28.75</v>
+        <v>135.61</v>
       </c>
       <c r="D19" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E19" t="n">
-        <v>-10.38</v>
+        <v>-7.14</v>
       </c>
       <c r="F19" t="n">
-        <v>0.45</v>
+        <v>0.6</v>
       </c>
       <c r="G19" t="n">
-        <v>1.81</v>
+        <v>6.24</v>
       </c>
       <c r="H19" t="n">
-        <v>6.28</v>
+        <v>4.6</v>
       </c>
       <c r="I19" t="n">
-        <v>28.03</v>
+        <v>133.11</v>
       </c>
       <c r="J19" t="n">
-        <v>29.2</v>
+        <v>137.17</v>
       </c>
       <c r="K19" t="n">
-        <v>26.04</v>
+        <v>126.25</v>
       </c>
       <c r="L19" t="n">
-        <v>33.27</v>
+        <v>151.21</v>
       </c>
       <c r="M19" t="n">
-        <v>34.1</v>
+        <v>39.82</v>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>MEDIO</t>
+          <t>BAJO</t>
         </is>
       </c>
       <c r="O19" t="inlineStr"/>
@@ -1545,102 +1541,106 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>PLTR</t>
+          <t>RKLB</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>IA / Software</t>
+          <t>Espacial</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>134.91</v>
+        <v>119.4</v>
       </c>
       <c r="D20" t="n">
-        <v>36</v>
+        <v>95</v>
       </c>
       <c r="E20" t="n">
-        <v>-7.61</v>
+        <v>48.67</v>
       </c>
       <c r="F20" t="n">
-        <v>0.55</v>
+        <v>1.44</v>
       </c>
       <c r="G20" t="n">
-        <v>6.24</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="H20" t="n">
-        <v>4.63</v>
+        <v>7.02</v>
       </c>
       <c r="I20" t="n">
-        <v>132.42</v>
+        <v>116.05</v>
       </c>
       <c r="J20" t="n">
-        <v>136.48</v>
+        <v>121.49</v>
       </c>
       <c r="K20" t="n">
-        <v>125.55</v>
+        <v>106.83</v>
       </c>
       <c r="L20" t="n">
-        <v>150.52</v>
+        <v>140.35</v>
       </c>
       <c r="M20" t="n">
-        <v>39.28</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>BAJO</t>
-        </is>
-      </c>
-      <c r="O20" t="inlineStr"/>
+          <t>ALTO</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>🔥🔥</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>NO COMPRAR</t>
+          <t>VIGILAR</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>RKLB</t>
+          <t>ASML</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Espacial</t>
+          <t>Chips</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>117.7</v>
+        <v>1560.12</v>
       </c>
       <c r="D21" t="n">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="E21" t="n">
-        <v>46.56</v>
+        <v>12.55</v>
       </c>
       <c r="F21" t="n">
-        <v>1.34</v>
+        <v>0.83</v>
       </c>
       <c r="G21" t="n">
-        <v>8.380000000000001</v>
+        <v>61.22</v>
       </c>
       <c r="H21" t="n">
-        <v>7.12</v>
+        <v>3.92</v>
       </c>
       <c r="I21" t="n">
-        <v>114.35</v>
+        <v>1535.63</v>
       </c>
       <c r="J21" t="n">
-        <v>119.8</v>
+        <v>1575.43</v>
       </c>
       <c r="K21" t="n">
-        <v>105.13</v>
+        <v>1468.29</v>
       </c>
       <c r="L21" t="n">
-        <v>138.65</v>
+        <v>1713.17</v>
       </c>
       <c r="M21" t="n">
-        <v>68.28</v>
+        <v>59.45</v>
       </c>
       <c r="N21" t="inlineStr">
         <is>
@@ -1649,7 +1649,7 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -1670,37 +1670,37 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>447.37</v>
+        <v>445.8</v>
       </c>
       <c r="D22" t="n">
         <v>95</v>
       </c>
       <c r="E22" t="n">
-        <v>14.31</v>
+        <v>13.9</v>
       </c>
       <c r="F22" t="n">
-        <v>0.58</v>
+        <v>0.64</v>
       </c>
       <c r="G22" t="n">
-        <v>17.86</v>
+        <v>17.89</v>
       </c>
       <c r="H22" t="n">
-        <v>3.99</v>
+        <v>4.01</v>
       </c>
       <c r="I22" t="n">
-        <v>440.22</v>
+        <v>438.64</v>
       </c>
       <c r="J22" t="n">
-        <v>451.84</v>
+        <v>450.27</v>
       </c>
       <c r="K22" t="n">
-        <v>420.57</v>
+        <v>418.96</v>
       </c>
       <c r="L22" t="n">
-        <v>492.03</v>
+        <v>490.53</v>
       </c>
       <c r="M22" t="n">
-        <v>65.45</v>
+        <v>65.13</v>
       </c>
       <c r="N22" t="inlineStr">
         <is>
@@ -1730,37 +1730,37 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>297.85</v>
+        <v>296.46</v>
       </c>
       <c r="D23" t="n">
         <v>95</v>
       </c>
       <c r="E23" t="n">
-        <v>15.19</v>
+        <v>14.66</v>
       </c>
       <c r="F23" t="n">
-        <v>0.36</v>
+        <v>0.42</v>
       </c>
       <c r="G23" t="n">
         <v>13.7</v>
       </c>
       <c r="H23" t="n">
-        <v>4.6</v>
+        <v>4.62</v>
       </c>
       <c r="I23" t="n">
-        <v>292.36</v>
+        <v>290.98</v>
       </c>
       <c r="J23" t="n">
-        <v>301.27</v>
+        <v>299.89</v>
       </c>
       <c r="K23" t="n">
-        <v>277.29</v>
+        <v>275.91</v>
       </c>
       <c r="L23" t="n">
-        <v>332.1</v>
+        <v>330.72</v>
       </c>
       <c r="M23" t="n">
-        <v>67.15000000000001</v>
+        <v>66.75</v>
       </c>
       <c r="N23" t="inlineStr">
         <is>
@@ -1790,37 +1790,37 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>291.51</v>
+        <v>292.82</v>
       </c>
       <c r="D24" t="n">
         <v>86</v>
       </c>
       <c r="E24" t="n">
-        <v>5.3</v>
+        <v>5.78</v>
       </c>
       <c r="F24" t="n">
-        <v>0.42</v>
+        <v>0.46</v>
       </c>
       <c r="G24" t="n">
         <v>6.64</v>
       </c>
       <c r="H24" t="n">
-        <v>2.28</v>
+        <v>2.27</v>
       </c>
       <c r="I24" t="n">
-        <v>288.85</v>
+        <v>290.16</v>
       </c>
       <c r="J24" t="n">
-        <v>293.17</v>
+        <v>294.48</v>
       </c>
       <c r="K24" t="n">
-        <v>281.55</v>
+        <v>282.86</v>
       </c>
       <c r="L24" t="n">
-        <v>308.1</v>
+        <v>309.41</v>
       </c>
       <c r="M24" t="n">
-        <v>76.16</v>
+        <v>78.27</v>
       </c>
       <c r="N24" t="inlineStr">
         <is>
@@ -1850,37 +1850,37 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>56.44</v>
+        <v>56.81</v>
       </c>
       <c r="D25" t="n">
         <v>86</v>
       </c>
       <c r="E25" t="n">
-        <v>23.37</v>
+        <v>24.17</v>
       </c>
       <c r="F25" t="n">
-        <v>0.96</v>
+        <v>1.02</v>
       </c>
       <c r="G25" t="n">
         <v>4.22</v>
       </c>
       <c r="H25" t="n">
-        <v>7.47</v>
+        <v>7.42</v>
       </c>
       <c r="I25" t="n">
-        <v>54.75</v>
+        <v>55.12</v>
       </c>
       <c r="J25" t="n">
-        <v>57.49</v>
+        <v>57.86</v>
       </c>
       <c r="K25" t="n">
-        <v>50.12</v>
+        <v>50.49</v>
       </c>
       <c r="L25" t="n">
-        <v>66.98</v>
+        <v>67.34999999999999</v>
       </c>
       <c r="M25" t="n">
-        <v>65.09999999999999</v>
+        <v>65.48</v>
       </c>
       <c r="N25" t="inlineStr">
         <is>
@@ -1910,37 +1910,37 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>739.02</v>
+        <v>740.6</v>
       </c>
       <c r="D26" t="n">
         <v>82</v>
       </c>
       <c r="E26" t="n">
-        <v>2.93</v>
+        <v>3.15</v>
       </c>
       <c r="F26" t="n">
-        <v>0.45</v>
+        <v>0.52</v>
       </c>
       <c r="G26" t="n">
-        <v>6.71</v>
+        <v>6.73</v>
       </c>
       <c r="H26" t="n">
         <v>0.91</v>
       </c>
       <c r="I26" t="n">
-        <v>736.33</v>
+        <v>737.91</v>
       </c>
       <c r="J26" t="n">
-        <v>740.7</v>
+        <v>742.29</v>
       </c>
       <c r="K26" t="n">
-        <v>728.95</v>
+        <v>730.51</v>
       </c>
       <c r="L26" t="n">
-        <v>755.79</v>
+        <v>757.4400000000001</v>
       </c>
       <c r="M26" t="n">
-        <v>80.42</v>
+        <v>80.95</v>
       </c>
       <c r="N26" t="inlineStr">
         <is>
@@ -1970,16 +1970,16 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>712.28</v>
+        <v>714.05</v>
       </c>
       <c r="D27" t="n">
         <v>82</v>
       </c>
       <c r="E27" t="n">
-        <v>5.86</v>
+        <v>6.12</v>
       </c>
       <c r="F27" t="n">
-        <v>0.52</v>
+        <v>0.58</v>
       </c>
       <c r="G27" t="n">
         <v>9.84</v>
@@ -1988,19 +1988,19 @@
         <v>1.38</v>
       </c>
       <c r="I27" t="n">
-        <v>708.34</v>
+        <v>710.11</v>
       </c>
       <c r="J27" t="n">
-        <v>714.74</v>
+        <v>716.51</v>
       </c>
       <c r="K27" t="n">
-        <v>697.51</v>
+        <v>699.28</v>
       </c>
       <c r="L27" t="n">
-        <v>736.89</v>
+        <v>738.66</v>
       </c>
       <c r="M27" t="n">
-        <v>86.58</v>
+        <v>86.83</v>
       </c>
       <c r="N27" t="inlineStr">
         <is>
@@ -2030,37 +2030,37 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>210.86</v>
+        <v>214.35</v>
       </c>
       <c r="D28" t="n">
         <v>80</v>
       </c>
       <c r="E28" t="n">
-        <v>3.74</v>
+        <v>5.45</v>
       </c>
       <c r="F28" t="n">
-        <v>0.65</v>
+        <v>0.71</v>
       </c>
       <c r="G28" t="n">
         <v>18.49</v>
       </c>
       <c r="H28" t="n">
-        <v>8.77</v>
+        <v>8.630000000000001</v>
       </c>
       <c r="I28" t="n">
-        <v>203.46</v>
+        <v>206.95</v>
       </c>
       <c r="J28" t="n">
-        <v>215.48</v>
+        <v>218.97</v>
       </c>
       <c r="K28" t="n">
-        <v>183.12</v>
+        <v>186.61</v>
       </c>
       <c r="L28" t="n">
-        <v>257.09</v>
+        <v>260.57</v>
       </c>
       <c r="M28" t="n">
-        <v>60.02</v>
+        <v>61.1</v>
       </c>
       <c r="N28" t="inlineStr">
         <is>
@@ -2090,37 +2090,37 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>529.76</v>
+        <v>531.23</v>
       </c>
       <c r="D29" t="n">
         <v>80</v>
       </c>
       <c r="E29" t="n">
-        <v>14.65</v>
+        <v>14.97</v>
       </c>
       <c r="F29" t="n">
-        <v>0.7</v>
+        <v>0.76</v>
       </c>
       <c r="G29" t="n">
-        <v>17.31</v>
+        <v>17.34</v>
       </c>
       <c r="H29" t="n">
-        <v>3.27</v>
+        <v>3.26</v>
       </c>
       <c r="I29" t="n">
-        <v>522.83</v>
+        <v>524.29</v>
       </c>
       <c r="J29" t="n">
-        <v>534.09</v>
+        <v>535.5700000000001</v>
       </c>
       <c r="K29" t="n">
-        <v>503.79</v>
+        <v>505.22</v>
       </c>
       <c r="L29" t="n">
-        <v>573.04</v>
+        <v>574.58</v>
       </c>
       <c r="M29" t="n">
-        <v>78.51000000000001</v>
+        <v>78.68000000000001</v>
       </c>
       <c r="N29" t="inlineStr">
         <is>
@@ -2141,53 +2141,57 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>GOOGL</t>
+          <t>QCOM</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Tecnología</t>
+          <t>Chips</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>393.32</v>
+        <v>235.31</v>
       </c>
       <c r="D30" t="n">
-        <v>78</v>
+        <v>61</v>
       </c>
       <c r="E30" t="n">
-        <v>2.63</v>
+        <v>39.75</v>
       </c>
       <c r="F30" t="n">
-        <v>0.46</v>
+        <v>1.27</v>
       </c>
       <c r="G30" t="n">
-        <v>10.42</v>
+        <v>16.45</v>
       </c>
       <c r="H30" t="n">
-        <v>2.65</v>
+        <v>6.99</v>
       </c>
       <c r="I30" t="n">
-        <v>389.15</v>
+        <v>228.73</v>
       </c>
       <c r="J30" t="n">
-        <v>395.93</v>
+        <v>239.42</v>
       </c>
       <c r="K30" t="n">
-        <v>377.69</v>
+        <v>210.63</v>
       </c>
       <c r="L30" t="n">
-        <v>419.38</v>
+        <v>276.44</v>
       </c>
       <c r="M30" t="n">
-        <v>86.79000000000001</v>
+        <v>89.3</v>
       </c>
       <c r="N30" t="inlineStr">
         <is>
           <t>ALTO</t>
         </is>
       </c>
-      <c r="O30" t="inlineStr"/>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>🔥</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>VIGILAR</t>
@@ -2197,46 +2201,46 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>SMCI</t>
+          <t>GOOGL</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Servidores IA</t>
+          <t>Tecnología</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>34.74</v>
+        <v>393.07</v>
       </c>
       <c r="D31" t="n">
         <v>78</v>
       </c>
       <c r="E31" t="n">
-        <v>24.43</v>
+        <v>2.56</v>
       </c>
       <c r="F31" t="n">
-        <v>0.61</v>
+        <v>0.52</v>
       </c>
       <c r="G31" t="n">
-        <v>2.25</v>
+        <v>10.42</v>
       </c>
       <c r="H31" t="n">
-        <v>6.48</v>
+        <v>2.65</v>
       </c>
       <c r="I31" t="n">
-        <v>33.84</v>
+        <v>388.9</v>
       </c>
       <c r="J31" t="n">
-        <v>35.3</v>
+        <v>395.67</v>
       </c>
       <c r="K31" t="n">
-        <v>31.37</v>
+        <v>377.43</v>
       </c>
       <c r="L31" t="n">
-        <v>40.36</v>
+        <v>419.12</v>
       </c>
       <c r="M31" t="n">
-        <v>65.15000000000001</v>
+        <v>86.52</v>
       </c>
       <c r="N31" t="inlineStr">
         <is>
@@ -2253,46 +2257,46 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>SMCI</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>IA / Chips</t>
+          <t>Servidores IA</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>463.73</v>
+        <v>34.48</v>
       </c>
       <c r="D32" t="n">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="E32" t="n">
-        <v>35.78</v>
+        <v>23.5</v>
       </c>
       <c r="F32" t="n">
-        <v>0.64</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="G32" t="n">
-        <v>27.28</v>
+        <v>2.27</v>
       </c>
       <c r="H32" t="n">
-        <v>5.88</v>
+        <v>6.59</v>
       </c>
       <c r="I32" t="n">
-        <v>452.82</v>
+        <v>33.57</v>
       </c>
       <c r="J32" t="n">
-        <v>470.55</v>
+        <v>35.05</v>
       </c>
       <c r="K32" t="n">
-        <v>422.81</v>
+        <v>31.07</v>
       </c>
       <c r="L32" t="n">
-        <v>531.9299999999999</v>
+        <v>40.16</v>
       </c>
       <c r="M32" t="n">
-        <v>80.66</v>
+        <v>64.34</v>
       </c>
       <c r="N32" t="inlineStr">
         <is>
@@ -2309,46 +2313,46 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>TSLA</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Autos / Tech</t>
+          <t>IA / Chips</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>438.65</v>
+        <v>466.71</v>
       </c>
       <c r="D33" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E33" t="n">
-        <v>11.76</v>
+        <v>36.65</v>
       </c>
       <c r="F33" t="n">
-        <v>0.76</v>
+        <v>0.7</v>
       </c>
       <c r="G33" t="n">
-        <v>15.07</v>
+        <v>27.29</v>
       </c>
       <c r="H33" t="n">
-        <v>3.44</v>
+        <v>5.85</v>
       </c>
       <c r="I33" t="n">
-        <v>432.62</v>
+        <v>455.79</v>
       </c>
       <c r="J33" t="n">
-        <v>442.42</v>
+        <v>473.53</v>
       </c>
       <c r="K33" t="n">
-        <v>416.04</v>
+        <v>425.77</v>
       </c>
       <c r="L33" t="n">
-        <v>476.33</v>
+        <v>534.9400000000001</v>
       </c>
       <c r="M33" t="n">
-        <v>76.69</v>
+        <v>80.86</v>
       </c>
       <c r="N33" t="inlineStr">
         <is>
@@ -2365,46 +2369,46 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>MU</t>
+          <t>TSLA</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Memoria / Chips</t>
+          <t>Autos / Tech</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>797.75</v>
+        <v>445.05</v>
       </c>
       <c r="D34" t="n">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="E34" t="n">
-        <v>38.39</v>
+        <v>13.39</v>
       </c>
       <c r="F34" t="n">
-        <v>1.07</v>
+        <v>0.85</v>
       </c>
       <c r="G34" t="n">
-        <v>45.86</v>
+        <v>15.21</v>
       </c>
       <c r="H34" t="n">
-        <v>5.75</v>
+        <v>3.42</v>
       </c>
       <c r="I34" t="n">
-        <v>779.4</v>
+        <v>438.97</v>
       </c>
       <c r="J34" t="n">
-        <v>809.22</v>
+        <v>448.85</v>
       </c>
       <c r="K34" t="n">
-        <v>728.95</v>
+        <v>422.24</v>
       </c>
       <c r="L34" t="n">
-        <v>912.41</v>
+        <v>483.07</v>
       </c>
       <c r="M34" t="n">
-        <v>89.31999999999999</v>
+        <v>78.13</v>
       </c>
       <c r="N34" t="inlineStr">
         <is>
@@ -2421,46 +2425,46 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>INTC</t>
+          <t>MU</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Chips</t>
+          <t>Memoria / Chips</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>125.89</v>
+        <v>799.2</v>
       </c>
       <c r="D35" t="n">
         <v>64</v>
       </c>
       <c r="E35" t="n">
-        <v>31.44</v>
+        <v>38.64</v>
       </c>
       <c r="F35" t="n">
-        <v>0.8100000000000001</v>
+        <v>1.17</v>
       </c>
       <c r="G35" t="n">
-        <v>8.390000000000001</v>
+        <v>45.86</v>
       </c>
       <c r="H35" t="n">
-        <v>6.66</v>
+        <v>5.74</v>
       </c>
       <c r="I35" t="n">
-        <v>122.53</v>
+        <v>780.86</v>
       </c>
       <c r="J35" t="n">
-        <v>127.99</v>
+        <v>810.67</v>
       </c>
       <c r="K35" t="n">
-        <v>113.31</v>
+        <v>730.41</v>
       </c>
       <c r="L35" t="n">
-        <v>146.86</v>
+        <v>913.86</v>
       </c>
       <c r="M35" t="n">
-        <v>88.45</v>
+        <v>89.36</v>
       </c>
       <c r="N35" t="inlineStr">
         <is>
@@ -2477,46 +2481,46 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>AMZN</t>
+          <t>INTC</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Tecnología</t>
+          <t>Chips</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>271.44</v>
+        <v>126.87</v>
       </c>
       <c r="D36" t="n">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.22</v>
+        <v>32.46</v>
       </c>
       <c r="F36" t="n">
-        <v>0.38</v>
+        <v>0.87</v>
       </c>
       <c r="G36" t="n">
-        <v>7.18</v>
+        <v>8.390000000000001</v>
       </c>
       <c r="H36" t="n">
-        <v>2.65</v>
+        <v>6.61</v>
       </c>
       <c r="I36" t="n">
-        <v>268.57</v>
+        <v>123.51</v>
       </c>
       <c r="J36" t="n">
-        <v>273.24</v>
+        <v>128.97</v>
       </c>
       <c r="K36" t="n">
-        <v>260.66</v>
+        <v>114.29</v>
       </c>
       <c r="L36" t="n">
-        <v>289.4</v>
+        <v>147.84</v>
       </c>
       <c r="M36" t="n">
-        <v>76.39</v>
+        <v>88.59</v>
       </c>
       <c r="N36" t="inlineStr">
         <is>
@@ -2533,46 +2537,46 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>QCOM</t>
+          <t>AMZN</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Chips</t>
+          <t>Tecnología</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>234.51</v>
+        <v>271.02</v>
       </c>
       <c r="D37" t="n">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="E37" t="n">
-        <v>39.27</v>
+        <v>-0.38</v>
       </c>
       <c r="F37" t="n">
-        <v>1.18</v>
+        <v>0.42</v>
       </c>
       <c r="G37" t="n">
-        <v>16.45</v>
+        <v>7.18</v>
       </c>
       <c r="H37" t="n">
-        <v>7.01</v>
+        <v>2.65</v>
       </c>
       <c r="I37" t="n">
-        <v>227.93</v>
+        <v>268.15</v>
       </c>
       <c r="J37" t="n">
-        <v>238.62</v>
+        <v>272.82</v>
       </c>
       <c r="K37" t="n">
-        <v>209.83</v>
+        <v>260.24</v>
       </c>
       <c r="L37" t="n">
-        <v>275.64</v>
+        <v>288.98</v>
       </c>
       <c r="M37" t="n">
-        <v>89.23</v>
+        <v>75.61</v>
       </c>
       <c r="N37" t="inlineStr">
         <is>
@@ -2582,7 +2586,7 @@
       <c r="O37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>NO COMPRAR</t>
+          <t>VIGILAR</t>
         </is>
       </c>
     </row>

--- a/analisis_acciones.xlsx
+++ b/analisis_acciones.xlsx
@@ -510,13 +510,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>220.64</v>
+        <v>220.68</v>
       </c>
       <c r="D2" t="n">
         <v>95</v>
       </c>
       <c r="E2" t="n">
-        <v>11.16</v>
+        <v>11.19</v>
       </c>
       <c r="F2" t="n">
         <v>0.72</v>
@@ -528,19 +528,19 @@
         <v>3.49</v>
       </c>
       <c r="I2" t="n">
-        <v>217.56</v>
+        <v>217.6</v>
       </c>
       <c r="J2" t="n">
-        <v>222.56</v>
+        <v>222.6</v>
       </c>
       <c r="K2" t="n">
-        <v>209.1</v>
+        <v>209.14</v>
       </c>
       <c r="L2" t="n">
-        <v>239.88</v>
+        <v>239.92</v>
       </c>
       <c r="M2" t="n">
-        <v>65.55</v>
+        <v>65.56999999999999</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -570,16 +570,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>429.48</v>
+        <v>429.46</v>
       </c>
       <c r="D3" t="n">
         <v>95</v>
       </c>
       <c r="E3" t="n">
-        <v>3.12</v>
+        <v>3.11</v>
       </c>
       <c r="F3" t="n">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="G3" t="n">
         <v>15.4</v>
@@ -588,19 +588,19 @@
         <v>3.59</v>
       </c>
       <c r="I3" t="n">
-        <v>423.32</v>
+        <v>423.3</v>
       </c>
       <c r="J3" t="n">
-        <v>433.33</v>
+        <v>433.31</v>
       </c>
       <c r="K3" t="n">
-        <v>406.38</v>
+        <v>406.36</v>
       </c>
       <c r="L3" t="n">
-        <v>467.98</v>
+        <v>467.96</v>
       </c>
       <c r="M3" t="n">
-        <v>61.5</v>
+        <v>61.48</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -630,13 +630,13 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>214.54</v>
+        <v>214.11</v>
       </c>
       <c r="D4" t="n">
         <v>92</v>
       </c>
       <c r="E4" t="n">
-        <v>5.69</v>
+        <v>5.48</v>
       </c>
       <c r="F4" t="n">
         <v>0.79</v>
@@ -645,22 +645,22 @@
         <v>11.99</v>
       </c>
       <c r="H4" t="n">
-        <v>5.59</v>
+        <v>5.6</v>
       </c>
       <c r="I4" t="n">
-        <v>209.74</v>
+        <v>209.31</v>
       </c>
       <c r="J4" t="n">
-        <v>217.53</v>
+        <v>217.11</v>
       </c>
       <c r="K4" t="n">
-        <v>196.55</v>
+        <v>196.13</v>
       </c>
       <c r="L4" t="n">
-        <v>244.51</v>
+        <v>244.08</v>
       </c>
       <c r="M4" t="n">
-        <v>60.13</v>
+        <v>59.94</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -690,13 +690,13 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>9.52</v>
+        <v>9.51</v>
       </c>
       <c r="D5" t="n">
         <v>92</v>
       </c>
       <c r="E5" t="n">
-        <v>3.2</v>
+        <v>3.09</v>
       </c>
       <c r="F5" t="n">
         <v>0.58</v>
@@ -708,19 +708,19 @@
         <v>4.56</v>
       </c>
       <c r="I5" t="n">
-        <v>9.34</v>
+        <v>9.33</v>
       </c>
       <c r="J5" t="n">
-        <v>9.619999999999999</v>
+        <v>9.609999999999999</v>
       </c>
       <c r="K5" t="n">
-        <v>8.859999999999999</v>
+        <v>8.85</v>
       </c>
       <c r="L5" t="n">
-        <v>10.6</v>
+        <v>10.59</v>
       </c>
       <c r="M5" t="n">
-        <v>55.17</v>
+        <v>54.99</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
@@ -750,13 +750,13 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1861.92</v>
+        <v>1862.03</v>
       </c>
       <c r="D6" t="n">
         <v>86</v>
       </c>
       <c r="E6" t="n">
-        <v>8.67</v>
+        <v>8.68</v>
       </c>
       <c r="F6" t="n">
         <v>0.57</v>
@@ -768,19 +768,19 @@
         <v>4.45</v>
       </c>
       <c r="I6" t="n">
-        <v>1828.8</v>
+        <v>1828.91</v>
       </c>
       <c r="J6" t="n">
-        <v>1882.61</v>
+        <v>1882.72</v>
       </c>
       <c r="K6" t="n">
-        <v>1737.75</v>
+        <v>1737.86</v>
       </c>
       <c r="L6" t="n">
-        <v>2068.86</v>
+        <v>2068.97</v>
       </c>
       <c r="M6" t="n">
-        <v>55.84</v>
+        <v>55.85</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
@@ -810,16 +810,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>404.6</v>
+        <v>404.8</v>
       </c>
       <c r="D7" t="n">
         <v>95</v>
       </c>
       <c r="E7" t="n">
-        <v>0.74</v>
+        <v>0.79</v>
       </c>
       <c r="F7" t="n">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="G7" t="n">
         <v>15.67</v>
@@ -828,19 +828,19 @@
         <v>3.87</v>
       </c>
       <c r="I7" t="n">
-        <v>398.33</v>
+        <v>398.53</v>
       </c>
       <c r="J7" t="n">
-        <v>408.52</v>
+        <v>408.72</v>
       </c>
       <c r="K7" t="n">
-        <v>381.09</v>
+        <v>381.29</v>
       </c>
       <c r="L7" t="n">
-        <v>443.78</v>
+        <v>443.98</v>
       </c>
       <c r="M7" t="n">
-        <v>65.8</v>
+        <v>65.92</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -876,7 +876,7 @@
         <v>84</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.51</v>
+        <v>-1.5</v>
       </c>
       <c r="F8" t="n">
         <v>0.32</v>
@@ -900,7 +900,7 @@
         <v>58.99</v>
       </c>
       <c r="M8" t="n">
-        <v>58.12</v>
+        <v>58.14</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
@@ -930,13 +930,13 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>8.5</v>
+        <v>8.49</v>
       </c>
       <c r="D9" t="n">
         <v>76</v>
       </c>
       <c r="E9" t="n">
-        <v>-10.24</v>
+        <v>-10.3</v>
       </c>
       <c r="F9" t="n">
         <v>0.74</v>
@@ -945,7 +945,7 @@
         <v>0.65</v>
       </c>
       <c r="H9" t="n">
-        <v>7.6</v>
+        <v>7.61</v>
       </c>
       <c r="I9" t="n">
         <v>8.24</v>
@@ -957,10 +957,10 @@
         <v>7.53</v>
       </c>
       <c r="L9" t="n">
-        <v>10.12</v>
+        <v>10.11</v>
       </c>
       <c r="M9" t="n">
-        <v>55.9</v>
+        <v>55.85</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
@@ -986,13 +986,13 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>80.22</v>
+        <v>80.12</v>
       </c>
       <c r="D10" t="n">
         <v>54</v>
       </c>
       <c r="E10" t="n">
-        <v>4.79</v>
+        <v>4.66</v>
       </c>
       <c r="F10" t="n">
         <v>0.51</v>
@@ -1001,22 +1001,22 @@
         <v>4.2</v>
       </c>
       <c r="H10" t="n">
-        <v>5.24</v>
+        <v>5.25</v>
       </c>
       <c r="I10" t="n">
-        <v>78.54000000000001</v>
+        <v>78.44</v>
       </c>
       <c r="J10" t="n">
-        <v>81.27</v>
+        <v>81.17</v>
       </c>
       <c r="K10" t="n">
-        <v>73.92</v>
+        <v>73.81999999999999</v>
       </c>
       <c r="L10" t="n">
-        <v>90.73</v>
+        <v>90.63</v>
       </c>
       <c r="M10" t="n">
-        <v>41.41</v>
+        <v>41.24</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
@@ -1046,13 +1046,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>149.15</v>
+        <v>149.1</v>
       </c>
       <c r="D11" t="n">
         <v>66</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.95</v>
+        <v>-2.99</v>
       </c>
       <c r="F11" t="n">
         <v>0.4</v>
@@ -1064,19 +1064,19 @@
         <v>2.69</v>
       </c>
       <c r="I11" t="n">
-        <v>147.55</v>
+        <v>147.49</v>
       </c>
       <c r="J11" t="n">
-        <v>150.16</v>
+        <v>150.1</v>
       </c>
       <c r="K11" t="n">
-        <v>143.13</v>
+        <v>143.08</v>
       </c>
       <c r="L11" t="n">
-        <v>159.19</v>
+        <v>159.14</v>
       </c>
       <c r="M11" t="n">
-        <v>51.33</v>
+        <v>51.24</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
@@ -1102,13 +1102,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>411.66</v>
+        <v>411.33</v>
       </c>
       <c r="D12" t="n">
         <v>54</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.47</v>
+        <v>-0.55</v>
       </c>
       <c r="F12" t="n">
         <v>0.51</v>
@@ -1120,19 +1120,19 @@
         <v>2.87</v>
       </c>
       <c r="I12" t="n">
-        <v>406.94</v>
+        <v>406.61</v>
       </c>
       <c r="J12" t="n">
-        <v>414.61</v>
+        <v>414.29</v>
       </c>
       <c r="K12" t="n">
-        <v>393.96</v>
+        <v>393.63</v>
       </c>
       <c r="L12" t="n">
-        <v>441.16</v>
+        <v>440.84</v>
       </c>
       <c r="M12" t="n">
-        <v>42.99</v>
+        <v>42.83</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
@@ -1158,13 +1158,13 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>184.75</v>
+        <v>184.66</v>
       </c>
       <c r="D13" t="n">
         <v>54</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.91</v>
+        <v>-3.96</v>
       </c>
       <c r="F13" t="n">
         <v>0.36</v>
@@ -1173,22 +1173,22 @@
         <v>4.61</v>
       </c>
       <c r="H13" t="n">
-        <v>2.49</v>
+        <v>2.5</v>
       </c>
       <c r="I13" t="n">
-        <v>182.91</v>
+        <v>182.82</v>
       </c>
       <c r="J13" t="n">
-        <v>185.91</v>
+        <v>185.81</v>
       </c>
       <c r="K13" t="n">
-        <v>177.84</v>
+        <v>177.75</v>
       </c>
       <c r="L13" t="n">
-        <v>196.28</v>
+        <v>196.18</v>
       </c>
       <c r="M13" t="n">
-        <v>48.07</v>
+        <v>47.92</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
@@ -1214,13 +1214,13 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>55.19</v>
+        <v>55.17</v>
       </c>
       <c r="D14" t="n">
         <v>54</v>
       </c>
       <c r="E14" t="n">
-        <v>-8.44</v>
+        <v>-8.470000000000001</v>
       </c>
       <c r="F14" t="n">
         <v>0.6</v>
@@ -1232,19 +1232,19 @@
         <v>3.35</v>
       </c>
       <c r="I14" t="n">
-        <v>54.45</v>
+        <v>54.43</v>
       </c>
       <c r="J14" t="n">
-        <v>55.65</v>
+        <v>55.63</v>
       </c>
       <c r="K14" t="n">
-        <v>52.41</v>
+        <v>52.39</v>
       </c>
       <c r="L14" t="n">
-        <v>59.81</v>
+        <v>59.79</v>
       </c>
       <c r="M14" t="n">
-        <v>46.96</v>
+        <v>46.91</v>
       </c>
       <c r="N14" t="inlineStr">
         <is>
@@ -1270,13 +1270,13 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>603.33</v>
+        <v>602.95</v>
       </c>
       <c r="D15" t="n">
         <v>46</v>
       </c>
       <c r="E15" t="n">
-        <v>-1.16</v>
+        <v>-1.22</v>
       </c>
       <c r="F15" t="n">
         <v>0.59</v>
@@ -1288,19 +1288,19 @@
         <v>3.02</v>
       </c>
       <c r="I15" t="n">
-        <v>596.05</v>
+        <v>595.67</v>
       </c>
       <c r="J15" t="n">
-        <v>607.87</v>
+        <v>607.5</v>
       </c>
       <c r="K15" t="n">
-        <v>576.03</v>
+        <v>575.65</v>
       </c>
       <c r="L15" t="n">
-        <v>648.8200000000001</v>
+        <v>648.45</v>
       </c>
       <c r="M15" t="n">
-        <v>27.13</v>
+        <v>27.06</v>
       </c>
       <c r="N15" t="inlineStr">
         <is>
@@ -1326,13 +1326,13 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>45.29</v>
+        <v>45.26</v>
       </c>
       <c r="D16" t="n">
         <v>46</v>
       </c>
       <c r="E16" t="n">
-        <v>-10.12</v>
+        <v>-10.17</v>
       </c>
       <c r="F16" t="n">
         <v>0.48</v>
@@ -1341,22 +1341,22 @@
         <v>1.56</v>
       </c>
       <c r="H16" t="n">
-        <v>3.44</v>
+        <v>3.45</v>
       </c>
       <c r="I16" t="n">
-        <v>44.67</v>
+        <v>44.64</v>
       </c>
       <c r="J16" t="n">
-        <v>45.68</v>
+        <v>45.65</v>
       </c>
       <c r="K16" t="n">
-        <v>42.95</v>
+        <v>42.93</v>
       </c>
       <c r="L16" t="n">
-        <v>49.19</v>
+        <v>49.16</v>
       </c>
       <c r="M16" t="n">
-        <v>24.43</v>
+        <v>24.37</v>
       </c>
       <c r="N16" t="inlineStr">
         <is>
@@ -1382,13 +1382,13 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>16.07</v>
+        <v>16.05</v>
       </c>
       <c r="D17" t="n">
         <v>38</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.83</v>
+        <v>-0.96</v>
       </c>
       <c r="F17" t="n">
         <v>0.7</v>
@@ -1397,22 +1397,22 @@
         <v>0.82</v>
       </c>
       <c r="H17" t="n">
-        <v>5.08</v>
+        <v>5.09</v>
       </c>
       <c r="I17" t="n">
-        <v>15.74</v>
+        <v>15.72</v>
       </c>
       <c r="J17" t="n">
-        <v>16.27</v>
+        <v>16.25</v>
       </c>
       <c r="K17" t="n">
-        <v>14.84</v>
+        <v>14.82</v>
       </c>
       <c r="L17" t="n">
-        <v>18.11</v>
+        <v>18.09</v>
       </c>
       <c r="M17" t="n">
-        <v>30.54</v>
+        <v>30.35</v>
       </c>
       <c r="N17" t="inlineStr">
         <is>
@@ -1438,13 +1438,13 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>29</v>
+        <v>28.99</v>
       </c>
       <c r="D18" t="n">
         <v>38</v>
       </c>
       <c r="E18" t="n">
-        <v>-9.6</v>
+        <v>-9.630000000000001</v>
       </c>
       <c r="F18" t="n">
         <v>0.5</v>
@@ -1453,22 +1453,22 @@
         <v>1.81</v>
       </c>
       <c r="H18" t="n">
-        <v>6.23</v>
+        <v>6.24</v>
       </c>
       <c r="I18" t="n">
-        <v>28.28</v>
+        <v>28.27</v>
       </c>
       <c r="J18" t="n">
-        <v>29.45</v>
+        <v>29.44</v>
       </c>
       <c r="K18" t="n">
-        <v>26.29</v>
+        <v>26.28</v>
       </c>
       <c r="L18" t="n">
-        <v>33.52</v>
+        <v>33.51</v>
       </c>
       <c r="M18" t="n">
-        <v>34.8</v>
+        <v>34.76</v>
       </c>
       <c r="N18" t="inlineStr">
         <is>
@@ -1494,13 +1494,13 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>135.61</v>
+        <v>135.5</v>
       </c>
       <c r="D19" t="n">
         <v>36</v>
       </c>
       <c r="E19" t="n">
-        <v>-7.14</v>
+        <v>-7.21</v>
       </c>
       <c r="F19" t="n">
         <v>0.6</v>
@@ -1509,22 +1509,22 @@
         <v>6.24</v>
       </c>
       <c r="H19" t="n">
-        <v>4.6</v>
+        <v>4.61</v>
       </c>
       <c r="I19" t="n">
-        <v>133.11</v>
+        <v>133</v>
       </c>
       <c r="J19" t="n">
-        <v>137.17</v>
+        <v>137.06</v>
       </c>
       <c r="K19" t="n">
-        <v>126.25</v>
+        <v>126.14</v>
       </c>
       <c r="L19" t="n">
-        <v>151.21</v>
+        <v>151.1</v>
       </c>
       <c r="M19" t="n">
-        <v>39.82</v>
+        <v>39.73</v>
       </c>
       <c r="N19" t="inlineStr">
         <is>
@@ -1550,13 +1550,13 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>119.4</v>
+        <v>119.64</v>
       </c>
       <c r="D20" t="n">
         <v>95</v>
       </c>
       <c r="E20" t="n">
-        <v>48.67</v>
+        <v>48.97</v>
       </c>
       <c r="F20" t="n">
         <v>1.44</v>
@@ -1565,22 +1565,22 @@
         <v>8.380000000000001</v>
       </c>
       <c r="H20" t="n">
-        <v>7.02</v>
+        <v>7</v>
       </c>
       <c r="I20" t="n">
-        <v>116.05</v>
+        <v>116.29</v>
       </c>
       <c r="J20" t="n">
-        <v>121.49</v>
+        <v>121.73</v>
       </c>
       <c r="K20" t="n">
-        <v>106.83</v>
+        <v>107.07</v>
       </c>
       <c r="L20" t="n">
-        <v>140.35</v>
+        <v>140.59</v>
       </c>
       <c r="M20" t="n">
-        <v>68.90000000000001</v>
+        <v>68.98999999999999</v>
       </c>
       <c r="N20" t="inlineStr">
         <is>
@@ -1610,13 +1610,13 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>1560.12</v>
+        <v>1562.61</v>
       </c>
       <c r="D21" t="n">
         <v>95</v>
       </c>
       <c r="E21" t="n">
-        <v>12.55</v>
+        <v>12.73</v>
       </c>
       <c r="F21" t="n">
         <v>0.83</v>
@@ -1628,19 +1628,19 @@
         <v>3.92</v>
       </c>
       <c r="I21" t="n">
-        <v>1535.63</v>
+        <v>1538.12</v>
       </c>
       <c r="J21" t="n">
-        <v>1575.43</v>
+        <v>1577.92</v>
       </c>
       <c r="K21" t="n">
-        <v>1468.29</v>
+        <v>1470.78</v>
       </c>
       <c r="L21" t="n">
-        <v>1713.17</v>
+        <v>1715.66</v>
       </c>
       <c r="M21" t="n">
-        <v>59.45</v>
+        <v>59.72</v>
       </c>
       <c r="N21" t="inlineStr">
         <is>
@@ -1670,13 +1670,13 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>445.8</v>
+        <v>446.07</v>
       </c>
       <c r="D22" t="n">
         <v>95</v>
       </c>
       <c r="E22" t="n">
-        <v>13.9</v>
+        <v>13.97</v>
       </c>
       <c r="F22" t="n">
         <v>0.64</v>
@@ -1688,19 +1688,19 @@
         <v>4.01</v>
       </c>
       <c r="I22" t="n">
-        <v>438.64</v>
+        <v>438.91</v>
       </c>
       <c r="J22" t="n">
-        <v>450.27</v>
+        <v>450.54</v>
       </c>
       <c r="K22" t="n">
-        <v>418.96</v>
+        <v>419.23</v>
       </c>
       <c r="L22" t="n">
-        <v>490.53</v>
+        <v>490.8</v>
       </c>
       <c r="M22" t="n">
-        <v>65.13</v>
+        <v>65.18000000000001</v>
       </c>
       <c r="N22" t="inlineStr">
         <is>
@@ -1730,16 +1730,16 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>296.46</v>
+        <v>296.53</v>
       </c>
       <c r="D23" t="n">
         <v>95</v>
       </c>
       <c r="E23" t="n">
-        <v>14.66</v>
+        <v>14.68</v>
       </c>
       <c r="F23" t="n">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="G23" t="n">
         <v>13.7</v>
@@ -1748,19 +1748,19 @@
         <v>4.62</v>
       </c>
       <c r="I23" t="n">
-        <v>290.98</v>
+        <v>291.05</v>
       </c>
       <c r="J23" t="n">
-        <v>299.89</v>
+        <v>299.96</v>
       </c>
       <c r="K23" t="n">
-        <v>275.91</v>
+        <v>275.98</v>
       </c>
       <c r="L23" t="n">
-        <v>330.72</v>
+        <v>330.78</v>
       </c>
       <c r="M23" t="n">
-        <v>66.75</v>
+        <v>66.77</v>
       </c>
       <c r="N23" t="inlineStr">
         <is>
@@ -1790,16 +1790,16 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>292.82</v>
+        <v>292.96</v>
       </c>
       <c r="D24" t="n">
         <v>86</v>
       </c>
       <c r="E24" t="n">
-        <v>5.78</v>
+        <v>5.83</v>
       </c>
       <c r="F24" t="n">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="G24" t="n">
         <v>6.64</v>
@@ -1808,19 +1808,19 @@
         <v>2.27</v>
       </c>
       <c r="I24" t="n">
-        <v>290.16</v>
+        <v>290.3</v>
       </c>
       <c r="J24" t="n">
-        <v>294.48</v>
+        <v>294.62</v>
       </c>
       <c r="K24" t="n">
-        <v>282.86</v>
+        <v>283</v>
       </c>
       <c r="L24" t="n">
-        <v>309.41</v>
+        <v>309.55</v>
       </c>
       <c r="M24" t="n">
-        <v>78.27</v>
+        <v>78.51000000000001</v>
       </c>
       <c r="N24" t="inlineStr">
         <is>
@@ -1850,13 +1850,13 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>56.81</v>
+        <v>56.95</v>
       </c>
       <c r="D25" t="n">
         <v>86</v>
       </c>
       <c r="E25" t="n">
-        <v>24.17</v>
+        <v>24.48</v>
       </c>
       <c r="F25" t="n">
         <v>1.02</v>
@@ -1865,22 +1865,22 @@
         <v>4.22</v>
       </c>
       <c r="H25" t="n">
-        <v>7.42</v>
+        <v>7.4</v>
       </c>
       <c r="I25" t="n">
-        <v>55.12</v>
+        <v>55.26</v>
       </c>
       <c r="J25" t="n">
-        <v>57.86</v>
+        <v>58</v>
       </c>
       <c r="K25" t="n">
-        <v>50.49</v>
+        <v>50.63</v>
       </c>
       <c r="L25" t="n">
-        <v>67.34999999999999</v>
+        <v>67.48999999999999</v>
       </c>
       <c r="M25" t="n">
-        <v>65.48</v>
+        <v>65.62</v>
       </c>
       <c r="N25" t="inlineStr">
         <is>
@@ -1910,13 +1910,13 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>740.6</v>
+        <v>740.5599999999999</v>
       </c>
       <c r="D26" t="n">
         <v>82</v>
       </c>
       <c r="E26" t="n">
-        <v>3.15</v>
+        <v>3.14</v>
       </c>
       <c r="F26" t="n">
         <v>0.52</v>
@@ -1928,19 +1928,19 @@
         <v>0.91</v>
       </c>
       <c r="I26" t="n">
-        <v>737.91</v>
+        <v>737.87</v>
       </c>
       <c r="J26" t="n">
-        <v>742.29</v>
+        <v>742.24</v>
       </c>
       <c r="K26" t="n">
-        <v>730.51</v>
+        <v>730.46</v>
       </c>
       <c r="L26" t="n">
-        <v>757.4400000000001</v>
+        <v>757.39</v>
       </c>
       <c r="M26" t="n">
-        <v>80.95</v>
+        <v>80.94</v>
       </c>
       <c r="N26" t="inlineStr">
         <is>
@@ -1970,13 +1970,13 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>714.05</v>
+        <v>714.27</v>
       </c>
       <c r="D27" t="n">
         <v>82</v>
       </c>
       <c r="E27" t="n">
-        <v>6.12</v>
+        <v>6.15</v>
       </c>
       <c r="F27" t="n">
         <v>0.58</v>
@@ -1988,19 +1988,19 @@
         <v>1.38</v>
       </c>
       <c r="I27" t="n">
-        <v>710.11</v>
+        <v>710.33</v>
       </c>
       <c r="J27" t="n">
-        <v>716.51</v>
+        <v>716.73</v>
       </c>
       <c r="K27" t="n">
-        <v>699.28</v>
+        <v>699.5</v>
       </c>
       <c r="L27" t="n">
-        <v>738.66</v>
+        <v>738.88</v>
       </c>
       <c r="M27" t="n">
-        <v>86.83</v>
+        <v>86.86</v>
       </c>
       <c r="N27" t="inlineStr">
         <is>
@@ -2030,37 +2030,37 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>214.35</v>
+        <v>214.89</v>
       </c>
       <c r="D28" t="n">
         <v>80</v>
       </c>
       <c r="E28" t="n">
-        <v>5.45</v>
+        <v>5.72</v>
       </c>
       <c r="F28" t="n">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="G28" t="n">
         <v>18.49</v>
       </c>
       <c r="H28" t="n">
-        <v>8.630000000000001</v>
+        <v>8.609999999999999</v>
       </c>
       <c r="I28" t="n">
-        <v>206.95</v>
+        <v>207.49</v>
       </c>
       <c r="J28" t="n">
-        <v>218.97</v>
+        <v>219.51</v>
       </c>
       <c r="K28" t="n">
-        <v>186.61</v>
+        <v>187.15</v>
       </c>
       <c r="L28" t="n">
-        <v>260.57</v>
+        <v>261.12</v>
       </c>
       <c r="M28" t="n">
-        <v>61.1</v>
+        <v>61.22</v>
       </c>
       <c r="N28" t="inlineStr">
         <is>
@@ -2090,13 +2090,13 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>531.23</v>
+        <v>532.1799999999999</v>
       </c>
       <c r="D29" t="n">
         <v>80</v>
       </c>
       <c r="E29" t="n">
-        <v>14.97</v>
+        <v>15.18</v>
       </c>
       <c r="F29" t="n">
         <v>0.76</v>
@@ -2108,19 +2108,19 @@
         <v>3.26</v>
       </c>
       <c r="I29" t="n">
-        <v>524.29</v>
+        <v>525.24</v>
       </c>
       <c r="J29" t="n">
-        <v>535.5700000000001</v>
+        <v>536.52</v>
       </c>
       <c r="K29" t="n">
-        <v>505.22</v>
+        <v>506.17</v>
       </c>
       <c r="L29" t="n">
-        <v>574.58</v>
+        <v>575.53</v>
       </c>
       <c r="M29" t="n">
-        <v>78.68000000000001</v>
+        <v>78.78</v>
       </c>
       <c r="N29" t="inlineStr">
         <is>
@@ -2150,37 +2150,37 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>235.31</v>
+        <v>236.96</v>
       </c>
       <c r="D30" t="n">
         <v>61</v>
       </c>
       <c r="E30" t="n">
-        <v>39.75</v>
+        <v>40.73</v>
       </c>
       <c r="F30" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="G30" t="n">
         <v>16.45</v>
       </c>
       <c r="H30" t="n">
-        <v>6.99</v>
+        <v>6.94</v>
       </c>
       <c r="I30" t="n">
-        <v>228.73</v>
+        <v>230.38</v>
       </c>
       <c r="J30" t="n">
-        <v>239.42</v>
+        <v>241.07</v>
       </c>
       <c r="K30" t="n">
-        <v>210.63</v>
+        <v>212.28</v>
       </c>
       <c r="L30" t="n">
-        <v>276.44</v>
+        <v>278.09</v>
       </c>
       <c r="M30" t="n">
-        <v>89.3</v>
+        <v>89.44</v>
       </c>
       <c r="N30" t="inlineStr">
         <is>
@@ -2210,16 +2210,16 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>393.07</v>
+        <v>393</v>
       </c>
       <c r="D31" t="n">
         <v>78</v>
       </c>
       <c r="E31" t="n">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="F31" t="n">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="G31" t="n">
         <v>10.42</v>
@@ -2228,19 +2228,19 @@
         <v>2.65</v>
       </c>
       <c r="I31" t="n">
-        <v>388.9</v>
+        <v>388.83</v>
       </c>
       <c r="J31" t="n">
-        <v>395.67</v>
+        <v>395.61</v>
       </c>
       <c r="K31" t="n">
-        <v>377.43</v>
+        <v>377.37</v>
       </c>
       <c r="L31" t="n">
-        <v>419.12</v>
+        <v>419.06</v>
       </c>
       <c r="M31" t="n">
-        <v>86.52</v>
+        <v>86.45</v>
       </c>
       <c r="N31" t="inlineStr">
         <is>
@@ -2266,37 +2266,37 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>34.48</v>
+        <v>34.46</v>
       </c>
       <c r="D32" t="n">
         <v>78</v>
       </c>
       <c r="E32" t="n">
-        <v>23.5</v>
+        <v>23.42</v>
       </c>
       <c r="F32" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.7</v>
       </c>
       <c r="G32" t="n">
         <v>2.27</v>
       </c>
       <c r="H32" t="n">
-        <v>6.59</v>
+        <v>6.6</v>
       </c>
       <c r="I32" t="n">
-        <v>33.57</v>
+        <v>33.55</v>
       </c>
       <c r="J32" t="n">
-        <v>35.05</v>
+        <v>35.03</v>
       </c>
       <c r="K32" t="n">
-        <v>31.07</v>
+        <v>31.05</v>
       </c>
       <c r="L32" t="n">
-        <v>40.16</v>
+        <v>40.14</v>
       </c>
       <c r="M32" t="n">
-        <v>64.34</v>
+        <v>64.28</v>
       </c>
       <c r="N32" t="inlineStr">
         <is>
@@ -2322,37 +2322,37 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>466.71</v>
+        <v>468.5</v>
       </c>
       <c r="D33" t="n">
         <v>72</v>
       </c>
       <c r="E33" t="n">
-        <v>36.65</v>
+        <v>37.17</v>
       </c>
       <c r="F33" t="n">
-        <v>0.7</v>
+        <v>0.71</v>
       </c>
       <c r="G33" t="n">
-        <v>27.29</v>
+        <v>27.34</v>
       </c>
       <c r="H33" t="n">
-        <v>5.85</v>
+        <v>5.84</v>
       </c>
       <c r="I33" t="n">
-        <v>455.79</v>
+        <v>457.57</v>
       </c>
       <c r="J33" t="n">
-        <v>473.53</v>
+        <v>475.33</v>
       </c>
       <c r="K33" t="n">
-        <v>425.77</v>
+        <v>427.49</v>
       </c>
       <c r="L33" t="n">
-        <v>534.9400000000001</v>
+        <v>536.84</v>
       </c>
       <c r="M33" t="n">
-        <v>80.86</v>
+        <v>80.97</v>
       </c>
       <c r="N33" t="inlineStr">
         <is>
@@ -2378,37 +2378,37 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>445.05</v>
+        <v>444.88</v>
       </c>
       <c r="D34" t="n">
         <v>70</v>
       </c>
       <c r="E34" t="n">
-        <v>13.39</v>
+        <v>13.34</v>
       </c>
       <c r="F34" t="n">
         <v>0.85</v>
       </c>
       <c r="G34" t="n">
-        <v>15.21</v>
+        <v>15.22</v>
       </c>
       <c r="H34" t="n">
         <v>3.42</v>
       </c>
       <c r="I34" t="n">
-        <v>438.97</v>
+        <v>438.79</v>
       </c>
       <c r="J34" t="n">
-        <v>448.85</v>
+        <v>448.68</v>
       </c>
       <c r="K34" t="n">
-        <v>422.24</v>
+        <v>422.06</v>
       </c>
       <c r="L34" t="n">
-        <v>483.07</v>
+        <v>482.92</v>
       </c>
       <c r="M34" t="n">
-        <v>78.13</v>
+        <v>78.09</v>
       </c>
       <c r="N34" t="inlineStr">
         <is>
@@ -2434,37 +2434,37 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>799.2</v>
+        <v>800.6799999999999</v>
       </c>
       <c r="D35" t="n">
         <v>64</v>
       </c>
       <c r="E35" t="n">
-        <v>38.64</v>
+        <v>38.9</v>
       </c>
       <c r="F35" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="G35" t="n">
         <v>45.86</v>
       </c>
       <c r="H35" t="n">
-        <v>5.74</v>
+        <v>5.73</v>
       </c>
       <c r="I35" t="n">
-        <v>780.86</v>
+        <v>782.34</v>
       </c>
       <c r="J35" t="n">
-        <v>810.67</v>
+        <v>812.15</v>
       </c>
       <c r="K35" t="n">
-        <v>730.41</v>
+        <v>731.89</v>
       </c>
       <c r="L35" t="n">
-        <v>913.86</v>
+        <v>915.34</v>
       </c>
       <c r="M35" t="n">
-        <v>89.36</v>
+        <v>89.39</v>
       </c>
       <c r="N35" t="inlineStr">
         <is>
@@ -2490,37 +2490,37 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>126.87</v>
+        <v>126.78</v>
       </c>
       <c r="D36" t="n">
         <v>64</v>
       </c>
       <c r="E36" t="n">
-        <v>32.46</v>
+        <v>32.36</v>
       </c>
       <c r="F36" t="n">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="G36" t="n">
         <v>8.390000000000001</v>
       </c>
       <c r="H36" t="n">
-        <v>6.61</v>
+        <v>6.62</v>
       </c>
       <c r="I36" t="n">
-        <v>123.51</v>
+        <v>123.42</v>
       </c>
       <c r="J36" t="n">
-        <v>128.97</v>
+        <v>128.87</v>
       </c>
       <c r="K36" t="n">
-        <v>114.29</v>
+        <v>114.19</v>
       </c>
       <c r="L36" t="n">
-        <v>147.84</v>
+        <v>147.74</v>
       </c>
       <c r="M36" t="n">
-        <v>88.59</v>
+        <v>88.58</v>
       </c>
       <c r="N36" t="inlineStr">
         <is>
@@ -2546,7 +2546,7 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>271.02</v>
+        <v>271.01</v>
       </c>
       <c r="D37" t="n">
         <v>60</v>
@@ -2555,7 +2555,7 @@
         <v>-0.38</v>
       </c>
       <c r="F37" t="n">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="G37" t="n">
         <v>7.18</v>
@@ -2564,19 +2564,19 @@
         <v>2.65</v>
       </c>
       <c r="I37" t="n">
-        <v>268.15</v>
+        <v>268.13</v>
       </c>
       <c r="J37" t="n">
-        <v>272.82</v>
+        <v>272.8</v>
       </c>
       <c r="K37" t="n">
-        <v>260.24</v>
+        <v>260.23</v>
       </c>
       <c r="L37" t="n">
-        <v>288.98</v>
+        <v>288.97</v>
       </c>
       <c r="M37" t="n">
-        <v>75.61</v>
+        <v>75.59</v>
       </c>
       <c r="N37" t="inlineStr">
         <is>

--- a/analisis_acciones.xlsx
+++ b/analisis_acciones.xlsx
@@ -510,16 +510,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>220.68</v>
+        <v>220.78</v>
       </c>
       <c r="D2" t="n">
         <v>95</v>
       </c>
       <c r="E2" t="n">
-        <v>11.19</v>
+        <v>11.24</v>
       </c>
       <c r="F2" t="n">
-        <v>0.72</v>
+        <v>0.74</v>
       </c>
       <c r="G2" t="n">
         <v>7.7</v>
@@ -528,19 +528,19 @@
         <v>3.49</v>
       </c>
       <c r="I2" t="n">
-        <v>217.6</v>
+        <v>217.7</v>
       </c>
       <c r="J2" t="n">
-        <v>222.6</v>
+        <v>222.7</v>
       </c>
       <c r="K2" t="n">
-        <v>209.14</v>
+        <v>209.24</v>
       </c>
       <c r="L2" t="n">
-        <v>239.92</v>
+        <v>240.02</v>
       </c>
       <c r="M2" t="n">
-        <v>65.56999999999999</v>
+        <v>65.62</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -570,37 +570,37 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>429.46</v>
+        <v>429.55</v>
       </c>
       <c r="D3" t="n">
         <v>95</v>
       </c>
       <c r="E3" t="n">
-        <v>3.11</v>
+        <v>3.13</v>
       </c>
       <c r="F3" t="n">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="G3" t="n">
         <v>15.4</v>
       </c>
       <c r="H3" t="n">
-        <v>3.59</v>
+        <v>3.58</v>
       </c>
       <c r="I3" t="n">
-        <v>423.3</v>
+        <v>423.39</v>
       </c>
       <c r="J3" t="n">
-        <v>433.31</v>
+        <v>433.4</v>
       </c>
       <c r="K3" t="n">
-        <v>406.36</v>
+        <v>406.45</v>
       </c>
       <c r="L3" t="n">
-        <v>467.96</v>
+        <v>468.05</v>
       </c>
       <c r="M3" t="n">
-        <v>61.48</v>
+        <v>61.53</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -621,46 +621,46 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>COIN</t>
+          <t>KLAC</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Cripto / Trading</t>
+          <t>Equipos chips</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>214.11</v>
+        <v>1850.14</v>
       </c>
       <c r="D4" t="n">
         <v>92</v>
       </c>
       <c r="E4" t="n">
-        <v>5.48</v>
+        <v>7.99</v>
       </c>
       <c r="F4" t="n">
-        <v>0.79</v>
+        <v>0.6</v>
       </c>
       <c r="G4" t="n">
-        <v>11.99</v>
+        <v>82.87</v>
       </c>
       <c r="H4" t="n">
-        <v>5.6</v>
+        <v>4.48</v>
       </c>
       <c r="I4" t="n">
-        <v>209.31</v>
+        <v>1816.99</v>
       </c>
       <c r="J4" t="n">
-        <v>217.11</v>
+        <v>1870.86</v>
       </c>
       <c r="K4" t="n">
-        <v>196.13</v>
+        <v>1725.84</v>
       </c>
       <c r="L4" t="n">
-        <v>244.08</v>
+        <v>2057.31</v>
       </c>
       <c r="M4" t="n">
-        <v>59.94</v>
+        <v>54.86</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -681,50 +681,50 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AI</t>
+          <t>COIN</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>IA</t>
+          <t>Cripto / Trading</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>9.51</v>
+        <v>215.61</v>
       </c>
       <c r="D5" t="n">
         <v>92</v>
       </c>
       <c r="E5" t="n">
-        <v>3.09</v>
+        <v>6.22</v>
       </c>
       <c r="F5" t="n">
-        <v>0.58</v>
+        <v>0.83</v>
       </c>
       <c r="G5" t="n">
-        <v>0.43</v>
+        <v>12.06</v>
       </c>
       <c r="H5" t="n">
-        <v>4.56</v>
+        <v>5.59</v>
       </c>
       <c r="I5" t="n">
-        <v>9.33</v>
+        <v>210.79</v>
       </c>
       <c r="J5" t="n">
-        <v>9.609999999999999</v>
+        <v>218.62</v>
       </c>
       <c r="K5" t="n">
-        <v>8.85</v>
+        <v>197.52</v>
       </c>
       <c r="L5" t="n">
-        <v>10.59</v>
+        <v>245.75</v>
       </c>
       <c r="M5" t="n">
-        <v>54.99</v>
+        <v>60.59</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>BAJO</t>
+          <t>MEDIO</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -741,50 +741,50 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>KLAC</t>
+          <t>AI</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Equipos chips</t>
+          <t>IA</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1862.03</v>
+        <v>9.52</v>
       </c>
       <c r="D6" t="n">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="E6" t="n">
-        <v>8.68</v>
+        <v>3.25</v>
       </c>
       <c r="F6" t="n">
-        <v>0.57</v>
+        <v>0.61</v>
       </c>
       <c r="G6" t="n">
-        <v>82.78</v>
+        <v>0.43</v>
       </c>
       <c r="H6" t="n">
-        <v>4.45</v>
+        <v>4.55</v>
       </c>
       <c r="I6" t="n">
-        <v>1828.91</v>
+        <v>9.35</v>
       </c>
       <c r="J6" t="n">
-        <v>1882.72</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="K6" t="n">
-        <v>1737.86</v>
+        <v>8.869999999999999</v>
       </c>
       <c r="L6" t="n">
-        <v>2068.97</v>
+        <v>10.6</v>
       </c>
       <c r="M6" t="n">
-        <v>55.85</v>
+        <v>55.26</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>MEDIO</t>
+          <t>BAJO</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -810,37 +810,37 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>404.8</v>
+        <v>404.31</v>
       </c>
       <c r="D7" t="n">
         <v>95</v>
       </c>
       <c r="E7" t="n">
-        <v>0.79</v>
+        <v>0.67</v>
       </c>
       <c r="F7" t="n">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="G7" t="n">
         <v>15.67</v>
       </c>
       <c r="H7" t="n">
-        <v>3.87</v>
+        <v>3.88</v>
       </c>
       <c r="I7" t="n">
-        <v>398.53</v>
+        <v>398.04</v>
       </c>
       <c r="J7" t="n">
-        <v>408.72</v>
+        <v>408.23</v>
       </c>
       <c r="K7" t="n">
-        <v>381.29</v>
+        <v>380.8</v>
       </c>
       <c r="L7" t="n">
-        <v>443.98</v>
+        <v>443.49</v>
       </c>
       <c r="M7" t="n">
-        <v>65.92</v>
+        <v>65.64</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -870,37 +870,37 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>54.79</v>
+        <v>54.88</v>
       </c>
       <c r="D8" t="n">
         <v>84</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.5</v>
+        <v>-1.35</v>
       </c>
       <c r="F8" t="n">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="G8" t="n">
         <v>1.68</v>
       </c>
       <c r="H8" t="n">
-        <v>3.07</v>
+        <v>3.06</v>
       </c>
       <c r="I8" t="n">
-        <v>54.12</v>
+        <v>54.21</v>
       </c>
       <c r="J8" t="n">
-        <v>55.21</v>
+        <v>55.3</v>
       </c>
       <c r="K8" t="n">
-        <v>52.27</v>
+        <v>52.36</v>
       </c>
       <c r="L8" t="n">
-        <v>58.99</v>
+        <v>59.08</v>
       </c>
       <c r="M8" t="n">
-        <v>58.14</v>
+        <v>58.42</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
@@ -921,46 +921,46 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SOUN</t>
+          <t>AMZN</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>IA</t>
+          <t>Tecnología</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>8.49</v>
+        <v>270.41</v>
       </c>
       <c r="D9" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E9" t="n">
-        <v>-10.3</v>
+        <v>-0.6</v>
       </c>
       <c r="F9" t="n">
-        <v>0.74</v>
+        <v>0.44</v>
       </c>
       <c r="G9" t="n">
-        <v>0.65</v>
+        <v>7.18</v>
       </c>
       <c r="H9" t="n">
-        <v>7.61</v>
+        <v>2.66</v>
       </c>
       <c r="I9" t="n">
-        <v>8.24</v>
+        <v>267.54</v>
       </c>
       <c r="J9" t="n">
-        <v>8.66</v>
+        <v>272.21</v>
       </c>
       <c r="K9" t="n">
-        <v>7.53</v>
+        <v>259.63</v>
       </c>
       <c r="L9" t="n">
-        <v>10.11</v>
+        <v>288.37</v>
       </c>
       <c r="M9" t="n">
-        <v>55.85</v>
+        <v>74.51000000000001</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
@@ -977,162 +977,162 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>HOOD</t>
+          <t>SOUN</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Trading</t>
+          <t>IA</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>80.12</v>
+        <v>8.56</v>
       </c>
       <c r="D10" t="n">
-        <v>54</v>
+        <v>76</v>
       </c>
       <c r="E10" t="n">
-        <v>4.66</v>
+        <v>-9.66</v>
       </c>
       <c r="F10" t="n">
-        <v>0.51</v>
+        <v>0.77</v>
       </c>
       <c r="G10" t="n">
-        <v>4.2</v>
+        <v>0.65</v>
       </c>
       <c r="H10" t="n">
-        <v>5.25</v>
+        <v>7.55</v>
       </c>
       <c r="I10" t="n">
-        <v>78.44</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J10" t="n">
-        <v>81.17</v>
+        <v>8.720000000000001</v>
       </c>
       <c r="K10" t="n">
-        <v>73.81999999999999</v>
+        <v>7.59</v>
       </c>
       <c r="L10" t="n">
-        <v>90.63</v>
+        <v>10.17</v>
       </c>
       <c r="M10" t="n">
-        <v>41.24</v>
+        <v>56.46</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
           <t>MEDIO</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>🔥</t>
-        </is>
-      </c>
+      <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>NO COMPRAR</t>
+          <t>POSIBLE COMPRA</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>XOM</t>
+          <t>HOOD</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Energía</t>
+          <t>Trading</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>149.1</v>
+        <v>80.18000000000001</v>
       </c>
       <c r="D11" t="n">
-        <v>66</v>
+        <v>54</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.99</v>
+        <v>4.74</v>
       </c>
       <c r="F11" t="n">
-        <v>0.4</v>
+        <v>0.52</v>
       </c>
       <c r="G11" t="n">
-        <v>4.02</v>
+        <v>4.2</v>
       </c>
       <c r="H11" t="n">
-        <v>2.69</v>
+        <v>5.24</v>
       </c>
       <c r="I11" t="n">
-        <v>147.49</v>
+        <v>78.5</v>
       </c>
       <c r="J11" t="n">
-        <v>150.1</v>
+        <v>81.23</v>
       </c>
       <c r="K11" t="n">
-        <v>143.08</v>
+        <v>73.88</v>
       </c>
       <c r="L11" t="n">
-        <v>159.14</v>
+        <v>90.69</v>
       </c>
       <c r="M11" t="n">
-        <v>51.24</v>
+        <v>41.34</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>BAJO</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr"/>
+          <t>MEDIO</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>🔥</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>VIGILAR</t>
+          <t>NO COMPRAR</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>XOM</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Tecnología</t>
+          <t>Energía</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>411.33</v>
+        <v>149.24</v>
       </c>
       <c r="D12" t="n">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.55</v>
+        <v>-2.9</v>
       </c>
       <c r="F12" t="n">
-        <v>0.51</v>
+        <v>0.42</v>
       </c>
       <c r="G12" t="n">
-        <v>11.8</v>
+        <v>4.02</v>
       </c>
       <c r="H12" t="n">
-        <v>2.87</v>
+        <v>2.69</v>
       </c>
       <c r="I12" t="n">
-        <v>406.61</v>
+        <v>147.63</v>
       </c>
       <c r="J12" t="n">
-        <v>414.29</v>
+        <v>150.24</v>
       </c>
       <c r="K12" t="n">
-        <v>393.63</v>
+        <v>143.21</v>
       </c>
       <c r="L12" t="n">
-        <v>440.84</v>
+        <v>159.28</v>
       </c>
       <c r="M12" t="n">
-        <v>42.83</v>
+        <v>51.47</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
@@ -1142,53 +1142,53 @@
       <c r="O12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>NO COMPRAR</t>
+          <t>VIGILAR</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>CVX</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Energía</t>
+          <t>Tecnología</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>184.66</v>
+        <v>411.47</v>
       </c>
       <c r="D13" t="n">
         <v>54</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.96</v>
+        <v>-0.52</v>
       </c>
       <c r="F13" t="n">
-        <v>0.36</v>
+        <v>0.52</v>
       </c>
       <c r="G13" t="n">
-        <v>4.61</v>
+        <v>11.8</v>
       </c>
       <c r="H13" t="n">
-        <v>2.5</v>
+        <v>2.87</v>
       </c>
       <c r="I13" t="n">
-        <v>182.82</v>
+        <v>406.75</v>
       </c>
       <c r="J13" t="n">
-        <v>185.81</v>
+        <v>414.42</v>
       </c>
       <c r="K13" t="n">
-        <v>177.75</v>
+        <v>393.77</v>
       </c>
       <c r="L13" t="n">
-        <v>196.18</v>
+        <v>440.97</v>
       </c>
       <c r="M13" t="n">
-        <v>47.92</v>
+        <v>42.9</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
@@ -1205,7 +1205,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>OXY</t>
+          <t>CVX</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1214,37 +1214,37 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>55.17</v>
+        <v>184.86</v>
       </c>
       <c r="D14" t="n">
         <v>54</v>
       </c>
       <c r="E14" t="n">
-        <v>-8.470000000000001</v>
+        <v>-3.86</v>
       </c>
       <c r="F14" t="n">
-        <v>0.6</v>
+        <v>0.38</v>
       </c>
       <c r="G14" t="n">
-        <v>1.85</v>
+        <v>4.61</v>
       </c>
       <c r="H14" t="n">
-        <v>3.35</v>
+        <v>2.49</v>
       </c>
       <c r="I14" t="n">
-        <v>54.43</v>
+        <v>183.02</v>
       </c>
       <c r="J14" t="n">
-        <v>55.63</v>
+        <v>186.01</v>
       </c>
       <c r="K14" t="n">
-        <v>52.39</v>
+        <v>177.95</v>
       </c>
       <c r="L14" t="n">
-        <v>59.79</v>
+        <v>196.38</v>
       </c>
       <c r="M14" t="n">
-        <v>46.91</v>
+        <v>48.25</v>
       </c>
       <c r="N14" t="inlineStr">
         <is>
@@ -1261,46 +1261,46 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>META</t>
+          <t>OXY</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Tecnología</t>
+          <t>Energía</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>602.95</v>
+        <v>55.31</v>
       </c>
       <c r="D15" t="n">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="E15" t="n">
-        <v>-1.22</v>
+        <v>-8.23</v>
       </c>
       <c r="F15" t="n">
-        <v>0.59</v>
+        <v>0.62</v>
       </c>
       <c r="G15" t="n">
-        <v>18.2</v>
+        <v>1.85</v>
       </c>
       <c r="H15" t="n">
-        <v>3.02</v>
+        <v>3.34</v>
       </c>
       <c r="I15" t="n">
-        <v>595.67</v>
+        <v>54.57</v>
       </c>
       <c r="J15" t="n">
-        <v>607.5</v>
+        <v>55.77</v>
       </c>
       <c r="K15" t="n">
-        <v>575.65</v>
+        <v>52.54</v>
       </c>
       <c r="L15" t="n">
-        <v>648.45</v>
+        <v>59.94</v>
       </c>
       <c r="M15" t="n">
-        <v>27.06</v>
+        <v>47.31</v>
       </c>
       <c r="N15" t="inlineStr">
         <is>
@@ -1317,46 +1317,46 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>PYPL</t>
+          <t>META</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Pagos</t>
+          <t>Tecnología</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>45.26</v>
+        <v>601.26</v>
       </c>
       <c r="D16" t="n">
         <v>46</v>
       </c>
       <c r="E16" t="n">
-        <v>-10.17</v>
+        <v>-1.5</v>
       </c>
       <c r="F16" t="n">
-        <v>0.48</v>
+        <v>0.61</v>
       </c>
       <c r="G16" t="n">
-        <v>1.56</v>
+        <v>18.2</v>
       </c>
       <c r="H16" t="n">
-        <v>3.45</v>
+        <v>3.03</v>
       </c>
       <c r="I16" t="n">
-        <v>44.64</v>
+        <v>593.98</v>
       </c>
       <c r="J16" t="n">
-        <v>45.65</v>
+        <v>605.8099999999999</v>
       </c>
       <c r="K16" t="n">
-        <v>42.93</v>
+        <v>573.96</v>
       </c>
       <c r="L16" t="n">
-        <v>49.16</v>
+        <v>646.76</v>
       </c>
       <c r="M16" t="n">
-        <v>24.37</v>
+        <v>26.74</v>
       </c>
       <c r="N16" t="inlineStr">
         <is>
@@ -1373,50 +1373,50 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>SOFI</t>
+          <t>PYPL</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Fintech</t>
+          <t>Pagos</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>16.05</v>
+        <v>45.27</v>
       </c>
       <c r="D17" t="n">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.96</v>
+        <v>-10.16</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7</v>
+        <v>0.49</v>
       </c>
       <c r="G17" t="n">
-        <v>0.82</v>
+        <v>1.56</v>
       </c>
       <c r="H17" t="n">
-        <v>5.09</v>
+        <v>3.45</v>
       </c>
       <c r="I17" t="n">
-        <v>15.72</v>
+        <v>44.65</v>
       </c>
       <c r="J17" t="n">
-        <v>16.25</v>
+        <v>45.66</v>
       </c>
       <c r="K17" t="n">
-        <v>14.82</v>
+        <v>42.93</v>
       </c>
       <c r="L17" t="n">
-        <v>18.09</v>
+        <v>49.17</v>
       </c>
       <c r="M17" t="n">
-        <v>30.35</v>
+        <v>24.38</v>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>MEDIO</t>
+          <t>BAJO</t>
         </is>
       </c>
       <c r="O17" t="inlineStr"/>
@@ -1429,46 +1429,46 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>UPST</t>
+          <t>SOFI</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Fintech IA</t>
+          <t>Fintech</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>28.99</v>
+        <v>16.04</v>
       </c>
       <c r="D18" t="n">
         <v>38</v>
       </c>
       <c r="E18" t="n">
-        <v>-9.630000000000001</v>
+        <v>-0.99</v>
       </c>
       <c r="F18" t="n">
-        <v>0.5</v>
+        <v>0.71</v>
       </c>
       <c r="G18" t="n">
-        <v>1.81</v>
+        <v>0.82</v>
       </c>
       <c r="H18" t="n">
-        <v>6.24</v>
+        <v>5.09</v>
       </c>
       <c r="I18" t="n">
-        <v>28.27</v>
+        <v>15.71</v>
       </c>
       <c r="J18" t="n">
-        <v>29.44</v>
+        <v>16.24</v>
       </c>
       <c r="K18" t="n">
-        <v>26.28</v>
+        <v>14.82</v>
       </c>
       <c r="L18" t="n">
-        <v>33.51</v>
+        <v>18.08</v>
       </c>
       <c r="M18" t="n">
-        <v>34.76</v>
+        <v>30.29</v>
       </c>
       <c r="N18" t="inlineStr">
         <is>
@@ -1485,50 +1485,50 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>PLTR</t>
+          <t>UPST</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>IA / Software</t>
+          <t>Fintech IA</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>135.5</v>
+        <v>28.99</v>
       </c>
       <c r="D19" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E19" t="n">
-        <v>-7.21</v>
+        <v>-9.630000000000001</v>
       </c>
       <c r="F19" t="n">
-        <v>0.6</v>
+        <v>0.51</v>
       </c>
       <c r="G19" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="H19" t="n">
         <v>6.24</v>
       </c>
-      <c r="H19" t="n">
-        <v>4.61</v>
-      </c>
       <c r="I19" t="n">
-        <v>133</v>
+        <v>28.27</v>
       </c>
       <c r="J19" t="n">
-        <v>137.06</v>
+        <v>29.44</v>
       </c>
       <c r="K19" t="n">
-        <v>126.14</v>
+        <v>26.28</v>
       </c>
       <c r="L19" t="n">
-        <v>151.1</v>
+        <v>33.51</v>
       </c>
       <c r="M19" t="n">
-        <v>39.73</v>
+        <v>34.76</v>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>BAJO</t>
+          <t>MEDIO</t>
         </is>
       </c>
       <c r="O19" t="inlineStr"/>
@@ -1541,106 +1541,102 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>RKLB</t>
+          <t>PLTR</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Espacial</t>
+          <t>IA / Software</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>119.64</v>
+        <v>135.53</v>
       </c>
       <c r="D20" t="n">
-        <v>95</v>
+        <v>36</v>
       </c>
       <c r="E20" t="n">
-        <v>48.97</v>
+        <v>-7.19</v>
       </c>
       <c r="F20" t="n">
-        <v>1.44</v>
+        <v>0.61</v>
       </c>
       <c r="G20" t="n">
-        <v>8.380000000000001</v>
+        <v>6.24</v>
       </c>
       <c r="H20" t="n">
-        <v>7</v>
+        <v>4.6</v>
       </c>
       <c r="I20" t="n">
-        <v>116.29</v>
+        <v>133.03</v>
       </c>
       <c r="J20" t="n">
-        <v>121.73</v>
+        <v>137.09</v>
       </c>
       <c r="K20" t="n">
-        <v>107.07</v>
+        <v>126.16</v>
       </c>
       <c r="L20" t="n">
-        <v>140.59</v>
+        <v>151.13</v>
       </c>
       <c r="M20" t="n">
-        <v>68.98999999999999</v>
+        <v>39.75</v>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>ALTO</t>
-        </is>
-      </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>🔥🔥</t>
-        </is>
-      </c>
+          <t>BAJO</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>VIGILAR</t>
+          <t>NO COMPRAR</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>ASML</t>
+          <t>RKLB</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Chips</t>
+          <t>Espacial</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>1562.61</v>
+        <v>121.4</v>
       </c>
       <c r="D21" t="n">
         <v>95</v>
       </c>
       <c r="E21" t="n">
-        <v>12.73</v>
+        <v>51.17</v>
       </c>
       <c r="F21" t="n">
-        <v>0.83</v>
+        <v>1.48</v>
       </c>
       <c r="G21" t="n">
-        <v>61.22</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="H21" t="n">
-        <v>3.92</v>
+        <v>6.97</v>
       </c>
       <c r="I21" t="n">
-        <v>1538.12</v>
+        <v>118.02</v>
       </c>
       <c r="J21" t="n">
-        <v>1577.92</v>
+        <v>123.52</v>
       </c>
       <c r="K21" t="n">
-        <v>1470.78</v>
+        <v>108.71</v>
       </c>
       <c r="L21" t="n">
-        <v>1715.66</v>
+        <v>142.56</v>
       </c>
       <c r="M21" t="n">
-        <v>59.72</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="N21" t="inlineStr">
         <is>
@@ -1649,7 +1645,7 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -1661,46 +1657,46 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>AMAT</t>
+          <t>ASML</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Equipos chips</t>
+          <t>Chips</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>446.07</v>
+        <v>1562.29</v>
       </c>
       <c r="D22" t="n">
         <v>95</v>
       </c>
       <c r="E22" t="n">
-        <v>13.97</v>
+        <v>12.7</v>
       </c>
       <c r="F22" t="n">
-        <v>0.64</v>
+        <v>0.86</v>
       </c>
       <c r="G22" t="n">
-        <v>17.89</v>
+        <v>61.22</v>
       </c>
       <c r="H22" t="n">
-        <v>4.01</v>
+        <v>3.92</v>
       </c>
       <c r="I22" t="n">
-        <v>438.91</v>
+        <v>1537.8</v>
       </c>
       <c r="J22" t="n">
-        <v>450.54</v>
+        <v>1577.6</v>
       </c>
       <c r="K22" t="n">
-        <v>419.23</v>
+        <v>1470.46</v>
       </c>
       <c r="L22" t="n">
-        <v>490.8</v>
+        <v>1715.34</v>
       </c>
       <c r="M22" t="n">
-        <v>65.18000000000001</v>
+        <v>59.68</v>
       </c>
       <c r="N22" t="inlineStr">
         <is>
@@ -1721,7 +1717,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>LRCX</t>
+          <t>AMAT</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1730,37 +1726,37 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>296.53</v>
+        <v>444.92</v>
       </c>
       <c r="D23" t="n">
         <v>95</v>
       </c>
       <c r="E23" t="n">
-        <v>14.68</v>
+        <v>13.68</v>
       </c>
       <c r="F23" t="n">
-        <v>0.43</v>
+        <v>0.66</v>
       </c>
       <c r="G23" t="n">
-        <v>13.7</v>
+        <v>17.89</v>
       </c>
       <c r="H23" t="n">
-        <v>4.62</v>
+        <v>4.02</v>
       </c>
       <c r="I23" t="n">
-        <v>291.05</v>
+        <v>437.76</v>
       </c>
       <c r="J23" t="n">
-        <v>299.96</v>
+        <v>449.39</v>
       </c>
       <c r="K23" t="n">
-        <v>275.98</v>
+        <v>418.08</v>
       </c>
       <c r="L23" t="n">
-        <v>330.78</v>
+        <v>489.65</v>
       </c>
       <c r="M23" t="n">
-        <v>66.77</v>
+        <v>64.95</v>
       </c>
       <c r="N23" t="inlineStr">
         <is>
@@ -1781,46 +1777,46 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>LRCX</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Tecnología</t>
+          <t>Equipos chips</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>292.96</v>
+        <v>296.05</v>
       </c>
       <c r="D24" t="n">
-        <v>86</v>
+        <v>95</v>
       </c>
       <c r="E24" t="n">
-        <v>5.83</v>
+        <v>14.5</v>
       </c>
       <c r="F24" t="n">
-        <v>0.47</v>
+        <v>0.44</v>
       </c>
       <c r="G24" t="n">
-        <v>6.64</v>
+        <v>13.7</v>
       </c>
       <c r="H24" t="n">
-        <v>2.27</v>
+        <v>4.63</v>
       </c>
       <c r="I24" t="n">
-        <v>290.3</v>
+        <v>290.57</v>
       </c>
       <c r="J24" t="n">
-        <v>294.62</v>
+        <v>299.48</v>
       </c>
       <c r="K24" t="n">
-        <v>283</v>
+        <v>275.5</v>
       </c>
       <c r="L24" t="n">
-        <v>309.55</v>
+        <v>330.31</v>
       </c>
       <c r="M24" t="n">
-        <v>78.51000000000001</v>
+        <v>66.63</v>
       </c>
       <c r="N24" t="inlineStr">
         <is>
@@ -1841,46 +1837,46 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>IONQ</t>
+          <t>AAPL</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Computación cuántica</t>
+          <t>Tecnología</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>56.95</v>
+        <v>292.32</v>
       </c>
       <c r="D25" t="n">
         <v>86</v>
       </c>
       <c r="E25" t="n">
-        <v>24.48</v>
+        <v>5.59</v>
       </c>
       <c r="F25" t="n">
-        <v>1.02</v>
+        <v>0.48</v>
       </c>
       <c r="G25" t="n">
-        <v>4.22</v>
+        <v>6.64</v>
       </c>
       <c r="H25" t="n">
-        <v>7.4</v>
+        <v>2.27</v>
       </c>
       <c r="I25" t="n">
-        <v>55.26</v>
+        <v>289.66</v>
       </c>
       <c r="J25" t="n">
-        <v>58</v>
+        <v>293.97</v>
       </c>
       <c r="K25" t="n">
-        <v>50.63</v>
+        <v>282.36</v>
       </c>
       <c r="L25" t="n">
-        <v>67.48999999999999</v>
+        <v>308.91</v>
       </c>
       <c r="M25" t="n">
-        <v>65.62</v>
+        <v>77.44</v>
       </c>
       <c r="N25" t="inlineStr">
         <is>
@@ -1901,46 +1897,46 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>SPY</t>
+          <t>IONQ</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>ETF Mercado</t>
+          <t>Computación cuántica</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>740.5599999999999</v>
+        <v>58.17</v>
       </c>
       <c r="D26" t="n">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="E26" t="n">
-        <v>3.14</v>
+        <v>27.16</v>
       </c>
       <c r="F26" t="n">
-        <v>0.52</v>
+        <v>1.06</v>
       </c>
       <c r="G26" t="n">
-        <v>6.73</v>
+        <v>4.28</v>
       </c>
       <c r="H26" t="n">
-        <v>0.91</v>
+        <v>7.35</v>
       </c>
       <c r="I26" t="n">
-        <v>737.87</v>
+        <v>56.46</v>
       </c>
       <c r="J26" t="n">
-        <v>742.24</v>
+        <v>59.24</v>
       </c>
       <c r="K26" t="n">
-        <v>730.46</v>
+        <v>51.76</v>
       </c>
       <c r="L26" t="n">
-        <v>757.39</v>
+        <v>68.87</v>
       </c>
       <c r="M26" t="n">
-        <v>80.94</v>
+        <v>66.81</v>
       </c>
       <c r="N26" t="inlineStr">
         <is>
@@ -1961,46 +1957,46 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>QQQ</t>
+          <t>SPY</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>ETF Nasdaq</t>
+          <t>ETF Mercado</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>714.27</v>
+        <v>740.42</v>
       </c>
       <c r="D27" t="n">
         <v>82</v>
       </c>
       <c r="E27" t="n">
-        <v>6.15</v>
+        <v>3.12</v>
       </c>
       <c r="F27" t="n">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="G27" t="n">
-        <v>9.84</v>
+        <v>6.73</v>
       </c>
       <c r="H27" t="n">
-        <v>1.38</v>
+        <v>0.91</v>
       </c>
       <c r="I27" t="n">
-        <v>710.33</v>
+        <v>737.72</v>
       </c>
       <c r="J27" t="n">
-        <v>716.73</v>
+        <v>742.1</v>
       </c>
       <c r="K27" t="n">
-        <v>699.5</v>
+        <v>730.3200000000001</v>
       </c>
       <c r="L27" t="n">
-        <v>738.88</v>
+        <v>757.25</v>
       </c>
       <c r="M27" t="n">
-        <v>86.86</v>
+        <v>80.89</v>
       </c>
       <c r="N27" t="inlineStr">
         <is>
@@ -2021,46 +2017,46 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>ARM</t>
+          <t>QQQ</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Chips</t>
+          <t>ETF Nasdaq</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>214.89</v>
+        <v>714.22</v>
       </c>
       <c r="D28" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="E28" t="n">
-        <v>5.72</v>
+        <v>6.14</v>
       </c>
       <c r="F28" t="n">
-        <v>0.72</v>
+        <v>0.6</v>
       </c>
       <c r="G28" t="n">
-        <v>18.49</v>
+        <v>9.84</v>
       </c>
       <c r="H28" t="n">
-        <v>8.609999999999999</v>
+        <v>1.38</v>
       </c>
       <c r="I28" t="n">
-        <v>207.49</v>
+        <v>710.28</v>
       </c>
       <c r="J28" t="n">
-        <v>219.51</v>
+        <v>716.6799999999999</v>
       </c>
       <c r="K28" t="n">
-        <v>187.15</v>
+        <v>699.45</v>
       </c>
       <c r="L28" t="n">
-        <v>261.12</v>
+        <v>738.83</v>
       </c>
       <c r="M28" t="n">
-        <v>61.22</v>
+        <v>86.84999999999999</v>
       </c>
       <c r="N28" t="inlineStr">
         <is>
@@ -2081,46 +2077,46 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>SOXX</t>
+          <t>ARM</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>ETF Chips</t>
+          <t>Chips</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>532.1799999999999</v>
+        <v>214.38</v>
       </c>
       <c r="D29" t="n">
         <v>80</v>
       </c>
       <c r="E29" t="n">
-        <v>15.18</v>
+        <v>5.47</v>
       </c>
       <c r="F29" t="n">
-        <v>0.76</v>
+        <v>0.74</v>
       </c>
       <c r="G29" t="n">
-        <v>17.34</v>
+        <v>18.49</v>
       </c>
       <c r="H29" t="n">
-        <v>3.26</v>
+        <v>8.630000000000001</v>
       </c>
       <c r="I29" t="n">
-        <v>525.24</v>
+        <v>206.98</v>
       </c>
       <c r="J29" t="n">
-        <v>536.52</v>
+        <v>219</v>
       </c>
       <c r="K29" t="n">
-        <v>506.17</v>
+        <v>186.64</v>
       </c>
       <c r="L29" t="n">
-        <v>575.53</v>
+        <v>260.6</v>
       </c>
       <c r="M29" t="n">
-        <v>78.78</v>
+        <v>61.1</v>
       </c>
       <c r="N29" t="inlineStr">
         <is>
@@ -2141,46 +2137,46 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>QCOM</t>
+          <t>SOXX</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Chips</t>
+          <t>ETF Chips</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>236.96</v>
+        <v>532.4400000000001</v>
       </c>
       <c r="D30" t="n">
-        <v>61</v>
+        <v>80</v>
       </c>
       <c r="E30" t="n">
-        <v>40.73</v>
+        <v>15.23</v>
       </c>
       <c r="F30" t="n">
-        <v>1.28</v>
+        <v>0.78</v>
       </c>
       <c r="G30" t="n">
-        <v>16.45</v>
+        <v>17.35</v>
       </c>
       <c r="H30" t="n">
-        <v>6.94</v>
+        <v>3.26</v>
       </c>
       <c r="I30" t="n">
-        <v>230.38</v>
+        <v>525.5</v>
       </c>
       <c r="J30" t="n">
-        <v>241.07</v>
+        <v>536.78</v>
       </c>
       <c r="K30" t="n">
-        <v>212.28</v>
+        <v>506.41</v>
       </c>
       <c r="L30" t="n">
-        <v>278.09</v>
+        <v>575.8200000000001</v>
       </c>
       <c r="M30" t="n">
-        <v>89.44</v>
+        <v>78.81</v>
       </c>
       <c r="N30" t="inlineStr">
         <is>
@@ -2201,53 +2197,57 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>GOOGL</t>
+          <t>QCOM</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Tecnología</t>
+          <t>Chips</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>393</v>
+        <v>236.15</v>
       </c>
       <c r="D31" t="n">
-        <v>78</v>
+        <v>61</v>
       </c>
       <c r="E31" t="n">
-        <v>2.54</v>
+        <v>40.25</v>
       </c>
       <c r="F31" t="n">
-        <v>0.53</v>
+        <v>1.31</v>
       </c>
       <c r="G31" t="n">
-        <v>10.42</v>
+        <v>16.45</v>
       </c>
       <c r="H31" t="n">
-        <v>2.65</v>
+        <v>6.97</v>
       </c>
       <c r="I31" t="n">
-        <v>388.83</v>
+        <v>229.56</v>
       </c>
       <c r="J31" t="n">
-        <v>395.61</v>
+        <v>240.26</v>
       </c>
       <c r="K31" t="n">
-        <v>377.37</v>
+        <v>211.47</v>
       </c>
       <c r="L31" t="n">
-        <v>419.06</v>
+        <v>277.27</v>
       </c>
       <c r="M31" t="n">
-        <v>86.45</v>
+        <v>89.37</v>
       </c>
       <c r="N31" t="inlineStr">
         <is>
           <t>ALTO</t>
         </is>
       </c>
-      <c r="O31" t="inlineStr"/>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>🔥</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>VIGILAR</t>
@@ -2257,46 +2257,46 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>SMCI</t>
+          <t>GOOGL</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Servidores IA</t>
+          <t>Tecnología</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>34.46</v>
+        <v>392.75</v>
       </c>
       <c r="D32" t="n">
         <v>78</v>
       </c>
       <c r="E32" t="n">
-        <v>23.42</v>
+        <v>2.48</v>
       </c>
       <c r="F32" t="n">
-        <v>0.7</v>
+        <v>0.54</v>
       </c>
       <c r="G32" t="n">
-        <v>2.27</v>
+        <v>10.42</v>
       </c>
       <c r="H32" t="n">
-        <v>6.6</v>
+        <v>2.65</v>
       </c>
       <c r="I32" t="n">
-        <v>33.55</v>
+        <v>388.58</v>
       </c>
       <c r="J32" t="n">
-        <v>35.03</v>
+        <v>395.36</v>
       </c>
       <c r="K32" t="n">
-        <v>31.05</v>
+        <v>377.12</v>
       </c>
       <c r="L32" t="n">
-        <v>40.14</v>
+        <v>418.81</v>
       </c>
       <c r="M32" t="n">
-        <v>64.28</v>
+        <v>86.2</v>
       </c>
       <c r="N32" t="inlineStr">
         <is>
@@ -2313,46 +2313,46 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>SMCI</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>IA / Chips</t>
+          <t>Servidores IA</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>468.5</v>
+        <v>34.6</v>
       </c>
       <c r="D33" t="n">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="E33" t="n">
-        <v>37.17</v>
+        <v>23.93</v>
       </c>
       <c r="F33" t="n">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="G33" t="n">
-        <v>27.34</v>
+        <v>2.27</v>
       </c>
       <c r="H33" t="n">
-        <v>5.84</v>
+        <v>6.57</v>
       </c>
       <c r="I33" t="n">
-        <v>457.57</v>
+        <v>33.69</v>
       </c>
       <c r="J33" t="n">
-        <v>475.33</v>
+        <v>35.17</v>
       </c>
       <c r="K33" t="n">
-        <v>427.49</v>
+        <v>31.19</v>
       </c>
       <c r="L33" t="n">
-        <v>536.84</v>
+        <v>40.28</v>
       </c>
       <c r="M33" t="n">
-        <v>80.97</v>
+        <v>64.70999999999999</v>
       </c>
       <c r="N33" t="inlineStr">
         <is>
@@ -2369,46 +2369,46 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>TSLA</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Autos / Tech</t>
+          <t>IA / Chips</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>444.88</v>
+        <v>468.35</v>
       </c>
       <c r="D34" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E34" t="n">
-        <v>13.34</v>
+        <v>37.13</v>
       </c>
       <c r="F34" t="n">
-        <v>0.85</v>
+        <v>0.72</v>
       </c>
       <c r="G34" t="n">
-        <v>15.22</v>
+        <v>27.39</v>
       </c>
       <c r="H34" t="n">
-        <v>3.42</v>
+        <v>5.85</v>
       </c>
       <c r="I34" t="n">
-        <v>438.79</v>
+        <v>457.39</v>
       </c>
       <c r="J34" t="n">
-        <v>448.68</v>
+        <v>475.2</v>
       </c>
       <c r="K34" t="n">
-        <v>422.06</v>
+        <v>427.27</v>
       </c>
       <c r="L34" t="n">
-        <v>482.92</v>
+        <v>536.8200000000001</v>
       </c>
       <c r="M34" t="n">
-        <v>78.09</v>
+        <v>80.95999999999999</v>
       </c>
       <c r="N34" t="inlineStr">
         <is>
@@ -2434,37 +2434,37 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>800.6799999999999</v>
+        <v>804.59</v>
       </c>
       <c r="D35" t="n">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="E35" t="n">
-        <v>38.9</v>
+        <v>39.58</v>
       </c>
       <c r="F35" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="G35" t="n">
         <v>45.86</v>
       </c>
       <c r="H35" t="n">
-        <v>5.73</v>
+        <v>5.7</v>
       </c>
       <c r="I35" t="n">
-        <v>782.34</v>
+        <v>786.24</v>
       </c>
       <c r="J35" t="n">
-        <v>812.15</v>
+        <v>816.0599999999999</v>
       </c>
       <c r="K35" t="n">
-        <v>731.89</v>
+        <v>735.79</v>
       </c>
       <c r="L35" t="n">
-        <v>915.34</v>
+        <v>919.25</v>
       </c>
       <c r="M35" t="n">
-        <v>89.39</v>
+        <v>89.48999999999999</v>
       </c>
       <c r="N35" t="inlineStr">
         <is>
@@ -2481,46 +2481,46 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>INTC</t>
+          <t>TSLA</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Chips</t>
+          <t>Autos / Tech</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>126.78</v>
+        <v>445.06</v>
       </c>
       <c r="D36" t="n">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="E36" t="n">
-        <v>32.36</v>
+        <v>13.39</v>
       </c>
       <c r="F36" t="n">
         <v>0.88</v>
       </c>
       <c r="G36" t="n">
-        <v>8.390000000000001</v>
+        <v>15.22</v>
       </c>
       <c r="H36" t="n">
-        <v>6.62</v>
+        <v>3.42</v>
       </c>
       <c r="I36" t="n">
-        <v>123.42</v>
+        <v>438.97</v>
       </c>
       <c r="J36" t="n">
-        <v>128.87</v>
+        <v>448.87</v>
       </c>
       <c r="K36" t="n">
-        <v>114.19</v>
+        <v>422.22</v>
       </c>
       <c r="L36" t="n">
-        <v>147.74</v>
+        <v>483.12</v>
       </c>
       <c r="M36" t="n">
-        <v>88.58</v>
+        <v>78.13</v>
       </c>
       <c r="N36" t="inlineStr">
         <is>
@@ -2537,46 +2537,46 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>AMZN</t>
+          <t>INTC</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Tecnología</t>
+          <t>Chips</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>271.01</v>
+        <v>128.03</v>
       </c>
       <c r="D37" t="n">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="E37" t="n">
-        <v>-0.38</v>
+        <v>33.67</v>
       </c>
       <c r="F37" t="n">
-        <v>0.43</v>
+        <v>0.89</v>
       </c>
       <c r="G37" t="n">
-        <v>7.18</v>
+        <v>8.390000000000001</v>
       </c>
       <c r="H37" t="n">
-        <v>2.65</v>
+        <v>6.55</v>
       </c>
       <c r="I37" t="n">
-        <v>268.13</v>
+        <v>124.67</v>
       </c>
       <c r="J37" t="n">
-        <v>272.8</v>
+        <v>130.13</v>
       </c>
       <c r="K37" t="n">
-        <v>260.23</v>
+        <v>115.45</v>
       </c>
       <c r="L37" t="n">
-        <v>288.97</v>
+        <v>149</v>
       </c>
       <c r="M37" t="n">
-        <v>75.59</v>
+        <v>88.76000000000001</v>
       </c>
       <c r="N37" t="inlineStr">
         <is>

--- a/analisis_acciones.xlsx
+++ b/analisis_acciones.xlsx
@@ -510,37 +510,37 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>220.78</v>
+        <v>221.38</v>
       </c>
       <c r="D2" t="n">
         <v>95</v>
       </c>
       <c r="E2" t="n">
-        <v>11.24</v>
+        <v>11.54</v>
       </c>
       <c r="F2" t="n">
-        <v>0.74</v>
+        <v>0.76</v>
       </c>
       <c r="G2" t="n">
         <v>7.7</v>
       </c>
       <c r="H2" t="n">
-        <v>3.49</v>
+        <v>3.48</v>
       </c>
       <c r="I2" t="n">
-        <v>217.7</v>
+        <v>218.3</v>
       </c>
       <c r="J2" t="n">
-        <v>222.7</v>
+        <v>223.3</v>
       </c>
       <c r="K2" t="n">
-        <v>209.24</v>
+        <v>209.84</v>
       </c>
       <c r="L2" t="n">
-        <v>240.02</v>
+        <v>240.62</v>
       </c>
       <c r="M2" t="n">
-        <v>65.62</v>
+        <v>65.93000000000001</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -570,37 +570,37 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>429.55</v>
+        <v>429.26</v>
       </c>
       <c r="D3" t="n">
         <v>95</v>
       </c>
       <c r="E3" t="n">
-        <v>3.13</v>
+        <v>3.06</v>
       </c>
       <c r="F3" t="n">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="G3" t="n">
         <v>15.4</v>
       </c>
       <c r="H3" t="n">
-        <v>3.58</v>
+        <v>3.59</v>
       </c>
       <c r="I3" t="n">
-        <v>423.39</v>
+        <v>423.1</v>
       </c>
       <c r="J3" t="n">
-        <v>433.4</v>
+        <v>433.11</v>
       </c>
       <c r="K3" t="n">
-        <v>406.45</v>
+        <v>406.16</v>
       </c>
       <c r="L3" t="n">
-        <v>468.05</v>
+        <v>467.76</v>
       </c>
       <c r="M3" t="n">
-        <v>61.53</v>
+        <v>61.38</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -621,46 +621,46 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>KLAC</t>
+          <t>COIN</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Equipos chips</t>
+          <t>Cripto / Trading</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1850.14</v>
+        <v>217.56</v>
       </c>
       <c r="D4" t="n">
         <v>92</v>
       </c>
       <c r="E4" t="n">
-        <v>7.99</v>
+        <v>7.18</v>
       </c>
       <c r="F4" t="n">
-        <v>0.6</v>
+        <v>0.87</v>
       </c>
       <c r="G4" t="n">
-        <v>82.87</v>
+        <v>12.2</v>
       </c>
       <c r="H4" t="n">
-        <v>4.48</v>
+        <v>5.61</v>
       </c>
       <c r="I4" t="n">
-        <v>1816.99</v>
+        <v>212.68</v>
       </c>
       <c r="J4" t="n">
-        <v>1870.86</v>
+        <v>220.61</v>
       </c>
       <c r="K4" t="n">
-        <v>1725.84</v>
+        <v>199.26</v>
       </c>
       <c r="L4" t="n">
-        <v>2057.31</v>
+        <v>248.05</v>
       </c>
       <c r="M4" t="n">
-        <v>54.86</v>
+        <v>61.4</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -681,50 +681,50 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>COIN</t>
+          <t>AI</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Cripto / Trading</t>
+          <t>IA</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>215.61</v>
+        <v>9.52</v>
       </c>
       <c r="D5" t="n">
         <v>92</v>
       </c>
       <c r="E5" t="n">
-        <v>6.22</v>
+        <v>3.31</v>
       </c>
       <c r="F5" t="n">
-        <v>0.83</v>
+        <v>0.64</v>
       </c>
       <c r="G5" t="n">
-        <v>12.06</v>
+        <v>0.43</v>
       </c>
       <c r="H5" t="n">
-        <v>5.59</v>
+        <v>4.55</v>
       </c>
       <c r="I5" t="n">
-        <v>210.79</v>
+        <v>9.35</v>
       </c>
       <c r="J5" t="n">
-        <v>218.62</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="K5" t="n">
-        <v>197.52</v>
+        <v>8.869999999999999</v>
       </c>
       <c r="L5" t="n">
-        <v>245.75</v>
+        <v>10.61</v>
       </c>
       <c r="M5" t="n">
-        <v>60.59</v>
+        <v>55.35</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>MEDIO</t>
+          <t>BAJO</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -741,50 +741,50 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AI</t>
+          <t>KLAC</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>IA</t>
+          <t>Equipos chips</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>9.52</v>
+        <v>1850.58</v>
       </c>
       <c r="D6" t="n">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="E6" t="n">
-        <v>3.25</v>
+        <v>8.01</v>
       </c>
       <c r="F6" t="n">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="G6" t="n">
-        <v>0.43</v>
+        <v>82.87</v>
       </c>
       <c r="H6" t="n">
-        <v>4.55</v>
+        <v>4.48</v>
       </c>
       <c r="I6" t="n">
-        <v>9.35</v>
+        <v>1817.43</v>
       </c>
       <c r="J6" t="n">
-        <v>9.630000000000001</v>
+        <v>1871.3</v>
       </c>
       <c r="K6" t="n">
-        <v>8.869999999999999</v>
+        <v>1726.28</v>
       </c>
       <c r="L6" t="n">
-        <v>10.6</v>
+        <v>2057.75</v>
       </c>
       <c r="M6" t="n">
-        <v>55.26</v>
+        <v>54.89</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>BAJO</t>
+          <t>MEDIO</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -810,37 +810,37 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>404.31</v>
+        <v>404.84</v>
       </c>
       <c r="D7" t="n">
         <v>95</v>
       </c>
       <c r="E7" t="n">
-        <v>0.67</v>
+        <v>0.8</v>
       </c>
       <c r="F7" t="n">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="G7" t="n">
         <v>15.67</v>
       </c>
       <c r="H7" t="n">
-        <v>3.88</v>
+        <v>3.87</v>
       </c>
       <c r="I7" t="n">
-        <v>398.04</v>
+        <v>398.57</v>
       </c>
       <c r="J7" t="n">
-        <v>408.23</v>
+        <v>408.76</v>
       </c>
       <c r="K7" t="n">
-        <v>380.8</v>
+        <v>381.33</v>
       </c>
       <c r="L7" t="n">
-        <v>443.49</v>
+        <v>444.02</v>
       </c>
       <c r="M7" t="n">
-        <v>65.64</v>
+        <v>65.94</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -870,16 +870,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>54.88</v>
+        <v>54.84</v>
       </c>
       <c r="D8" t="n">
         <v>84</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.35</v>
+        <v>-1.42</v>
       </c>
       <c r="F8" t="n">
-        <v>0.33</v>
+        <v>0.35</v>
       </c>
       <c r="G8" t="n">
         <v>1.68</v>
@@ -888,19 +888,19 @@
         <v>3.06</v>
       </c>
       <c r="I8" t="n">
-        <v>54.21</v>
+        <v>54.17</v>
       </c>
       <c r="J8" t="n">
-        <v>55.3</v>
+        <v>55.26</v>
       </c>
       <c r="K8" t="n">
-        <v>52.36</v>
+        <v>52.32</v>
       </c>
       <c r="L8" t="n">
-        <v>59.08</v>
+        <v>59.04</v>
       </c>
       <c r="M8" t="n">
-        <v>58.42</v>
+        <v>58.29</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
@@ -930,16 +930,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>270.41</v>
+        <v>269.94</v>
       </c>
       <c r="D9" t="n">
         <v>77</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.6</v>
+        <v>-0.78</v>
       </c>
       <c r="F9" t="n">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="G9" t="n">
         <v>7.18</v>
@@ -948,19 +948,19 @@
         <v>2.66</v>
       </c>
       <c r="I9" t="n">
-        <v>267.54</v>
+        <v>267.07</v>
       </c>
       <c r="J9" t="n">
-        <v>272.21</v>
+        <v>271.74</v>
       </c>
       <c r="K9" t="n">
-        <v>259.63</v>
+        <v>259.16</v>
       </c>
       <c r="L9" t="n">
-        <v>288.37</v>
+        <v>287.9</v>
       </c>
       <c r="M9" t="n">
-        <v>74.51000000000001</v>
+        <v>73.68000000000001</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
@@ -986,37 +986,37 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>8.56</v>
+        <v>8.51</v>
       </c>
       <c r="D10" t="n">
         <v>76</v>
       </c>
       <c r="E10" t="n">
-        <v>-9.66</v>
+        <v>-10.14</v>
       </c>
       <c r="F10" t="n">
-        <v>0.77</v>
+        <v>0.79</v>
       </c>
       <c r="G10" t="n">
         <v>0.65</v>
       </c>
       <c r="H10" t="n">
-        <v>7.55</v>
+        <v>7.59</v>
       </c>
       <c r="I10" t="n">
-        <v>8.300000000000001</v>
+        <v>8.25</v>
       </c>
       <c r="J10" t="n">
-        <v>8.720000000000001</v>
+        <v>8.67</v>
       </c>
       <c r="K10" t="n">
-        <v>7.59</v>
+        <v>7.54</v>
       </c>
       <c r="L10" t="n">
-        <v>10.17</v>
+        <v>10.13</v>
       </c>
       <c r="M10" t="n">
-        <v>56.46</v>
+        <v>56</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
@@ -1042,37 +1042,37 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>80.18000000000001</v>
+        <v>80.5</v>
       </c>
       <c r="D11" t="n">
         <v>54</v>
       </c>
       <c r="E11" t="n">
-        <v>4.74</v>
+        <v>5.16</v>
       </c>
       <c r="F11" t="n">
-        <v>0.52</v>
+        <v>0.54</v>
       </c>
       <c r="G11" t="n">
         <v>4.2</v>
       </c>
       <c r="H11" t="n">
-        <v>5.24</v>
+        <v>5.22</v>
       </c>
       <c r="I11" t="n">
-        <v>78.5</v>
+        <v>78.81999999999999</v>
       </c>
       <c r="J11" t="n">
-        <v>81.23</v>
+        <v>81.55</v>
       </c>
       <c r="K11" t="n">
-        <v>73.88</v>
+        <v>74.19</v>
       </c>
       <c r="L11" t="n">
-        <v>90.69</v>
+        <v>91.01000000000001</v>
       </c>
       <c r="M11" t="n">
-        <v>41.34</v>
+        <v>41.85</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
@@ -1102,16 +1102,16 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>149.24</v>
+        <v>149.19</v>
       </c>
       <c r="D12" t="n">
         <v>66</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.9</v>
+        <v>-2.93</v>
       </c>
       <c r="F12" t="n">
-        <v>0.42</v>
+        <v>0.44</v>
       </c>
       <c r="G12" t="n">
         <v>4.02</v>
@@ -1120,19 +1120,19 @@
         <v>2.69</v>
       </c>
       <c r="I12" t="n">
-        <v>147.63</v>
+        <v>147.58</v>
       </c>
       <c r="J12" t="n">
-        <v>150.24</v>
+        <v>150.19</v>
       </c>
       <c r="K12" t="n">
-        <v>143.21</v>
+        <v>143.16</v>
       </c>
       <c r="L12" t="n">
-        <v>159.28</v>
+        <v>159.23</v>
       </c>
       <c r="M12" t="n">
-        <v>51.47</v>
+        <v>51.38</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
@@ -1158,37 +1158,37 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>411.47</v>
+        <v>410.46</v>
       </c>
       <c r="D13" t="n">
         <v>54</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.52</v>
+        <v>-0.76</v>
       </c>
       <c r="F13" t="n">
-        <v>0.52</v>
+        <v>0.54</v>
       </c>
       <c r="G13" t="n">
         <v>11.8</v>
       </c>
       <c r="H13" t="n">
-        <v>2.87</v>
+        <v>2.88</v>
       </c>
       <c r="I13" t="n">
-        <v>406.75</v>
+        <v>405.74</v>
       </c>
       <c r="J13" t="n">
-        <v>414.42</v>
+        <v>413.41</v>
       </c>
       <c r="K13" t="n">
-        <v>393.77</v>
+        <v>392.76</v>
       </c>
       <c r="L13" t="n">
-        <v>440.97</v>
+        <v>439.96</v>
       </c>
       <c r="M13" t="n">
-        <v>42.9</v>
+        <v>42.42</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
@@ -1214,16 +1214,16 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>184.86</v>
+        <v>184.83</v>
       </c>
       <c r="D14" t="n">
         <v>54</v>
       </c>
       <c r="E14" t="n">
-        <v>-3.86</v>
+        <v>-3.87</v>
       </c>
       <c r="F14" t="n">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="G14" t="n">
         <v>4.61</v>
@@ -1232,19 +1232,19 @@
         <v>2.49</v>
       </c>
       <c r="I14" t="n">
-        <v>183.02</v>
+        <v>182.99</v>
       </c>
       <c r="J14" t="n">
-        <v>186.01</v>
+        <v>185.98</v>
       </c>
       <c r="K14" t="n">
-        <v>177.95</v>
+        <v>177.92</v>
       </c>
       <c r="L14" t="n">
-        <v>196.38</v>
+        <v>196.35</v>
       </c>
       <c r="M14" t="n">
-        <v>48.25</v>
+        <v>48.2</v>
       </c>
       <c r="N14" t="inlineStr">
         <is>
@@ -1270,37 +1270,37 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>55.31</v>
+        <v>55.23</v>
       </c>
       <c r="D15" t="n">
         <v>54</v>
       </c>
       <c r="E15" t="n">
-        <v>-8.23</v>
+        <v>-8.359999999999999</v>
       </c>
       <c r="F15" t="n">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="G15" t="n">
         <v>1.85</v>
       </c>
       <c r="H15" t="n">
-        <v>3.34</v>
+        <v>3.35</v>
       </c>
       <c r="I15" t="n">
-        <v>54.57</v>
+        <v>54.49</v>
       </c>
       <c r="J15" t="n">
-        <v>55.77</v>
+        <v>55.69</v>
       </c>
       <c r="K15" t="n">
-        <v>52.54</v>
+        <v>52.45</v>
       </c>
       <c r="L15" t="n">
-        <v>59.94</v>
+        <v>59.85</v>
       </c>
       <c r="M15" t="n">
-        <v>47.31</v>
+        <v>47.09</v>
       </c>
       <c r="N15" t="inlineStr">
         <is>
@@ -1326,37 +1326,37 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>601.26</v>
+        <v>599.1900000000001</v>
       </c>
       <c r="D16" t="n">
         <v>46</v>
       </c>
       <c r="E16" t="n">
-        <v>-1.5</v>
+        <v>-1.84</v>
       </c>
       <c r="F16" t="n">
-        <v>0.61</v>
+        <v>0.64</v>
       </c>
       <c r="G16" t="n">
-        <v>18.2</v>
+        <v>18.25</v>
       </c>
       <c r="H16" t="n">
-        <v>3.03</v>
+        <v>3.05</v>
       </c>
       <c r="I16" t="n">
-        <v>593.98</v>
+        <v>591.89</v>
       </c>
       <c r="J16" t="n">
-        <v>605.8099999999999</v>
+        <v>603.75</v>
       </c>
       <c r="K16" t="n">
-        <v>573.96</v>
+        <v>571.8200000000001</v>
       </c>
       <c r="L16" t="n">
-        <v>646.76</v>
+        <v>644.8099999999999</v>
       </c>
       <c r="M16" t="n">
-        <v>26.74</v>
+        <v>26.37</v>
       </c>
       <c r="N16" t="inlineStr">
         <is>
@@ -1382,16 +1382,16 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>45.27</v>
+        <v>45.24</v>
       </c>
       <c r="D17" t="n">
         <v>46</v>
       </c>
       <c r="E17" t="n">
-        <v>-10.16</v>
+        <v>-10.23</v>
       </c>
       <c r="F17" t="n">
-        <v>0.49</v>
+        <v>0.51</v>
       </c>
       <c r="G17" t="n">
         <v>1.56</v>
@@ -1400,19 +1400,19 @@
         <v>3.45</v>
       </c>
       <c r="I17" t="n">
-        <v>44.65</v>
+        <v>44.61</v>
       </c>
       <c r="J17" t="n">
-        <v>45.66</v>
+        <v>45.62</v>
       </c>
       <c r="K17" t="n">
-        <v>42.93</v>
+        <v>42.9</v>
       </c>
       <c r="L17" t="n">
-        <v>49.17</v>
+        <v>49.13</v>
       </c>
       <c r="M17" t="n">
-        <v>24.38</v>
+        <v>24.31</v>
       </c>
       <c r="N17" t="inlineStr">
         <is>
@@ -1438,37 +1438,37 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>16.04</v>
+        <v>16.08</v>
       </c>
       <c r="D18" t="n">
         <v>38</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.99</v>
+        <v>-0.77</v>
       </c>
       <c r="F18" t="n">
-        <v>0.71</v>
+        <v>0.73</v>
       </c>
       <c r="G18" t="n">
         <v>0.82</v>
       </c>
       <c r="H18" t="n">
-        <v>5.09</v>
+        <v>5.08</v>
       </c>
       <c r="I18" t="n">
-        <v>15.71</v>
+        <v>15.75</v>
       </c>
       <c r="J18" t="n">
-        <v>16.24</v>
+        <v>16.28</v>
       </c>
       <c r="K18" t="n">
-        <v>14.82</v>
+        <v>14.85</v>
       </c>
       <c r="L18" t="n">
-        <v>18.08</v>
+        <v>18.12</v>
       </c>
       <c r="M18" t="n">
-        <v>30.29</v>
+        <v>30.64</v>
       </c>
       <c r="N18" t="inlineStr">
         <is>
@@ -1494,37 +1494,37 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>28.99</v>
+        <v>28.94</v>
       </c>
       <c r="D19" t="n">
         <v>38</v>
       </c>
       <c r="E19" t="n">
-        <v>-9.630000000000001</v>
+        <v>-9.77</v>
       </c>
       <c r="F19" t="n">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="G19" t="n">
         <v>1.81</v>
       </c>
       <c r="H19" t="n">
-        <v>6.24</v>
+        <v>6.25</v>
       </c>
       <c r="I19" t="n">
-        <v>28.27</v>
+        <v>28.22</v>
       </c>
       <c r="J19" t="n">
-        <v>29.44</v>
+        <v>29.4</v>
       </c>
       <c r="K19" t="n">
-        <v>26.28</v>
+        <v>26.23</v>
       </c>
       <c r="L19" t="n">
-        <v>33.51</v>
+        <v>33.46</v>
       </c>
       <c r="M19" t="n">
-        <v>34.76</v>
+        <v>34.58</v>
       </c>
       <c r="N19" t="inlineStr">
         <is>
@@ -1550,16 +1550,16 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>135.53</v>
+        <v>135.65</v>
       </c>
       <c r="D20" t="n">
         <v>36</v>
       </c>
       <c r="E20" t="n">
-        <v>-7.19</v>
+        <v>-7.11</v>
       </c>
       <c r="F20" t="n">
-        <v>0.61</v>
+        <v>0.64</v>
       </c>
       <c r="G20" t="n">
         <v>6.24</v>
@@ -1568,19 +1568,19 @@
         <v>4.6</v>
       </c>
       <c r="I20" t="n">
-        <v>133.03</v>
+        <v>133.15</v>
       </c>
       <c r="J20" t="n">
-        <v>137.09</v>
+        <v>137.21</v>
       </c>
       <c r="K20" t="n">
-        <v>126.16</v>
+        <v>126.29</v>
       </c>
       <c r="L20" t="n">
-        <v>151.13</v>
+        <v>151.25</v>
       </c>
       <c r="M20" t="n">
-        <v>39.75</v>
+        <v>39.85</v>
       </c>
       <c r="N20" t="inlineStr">
         <is>
@@ -1606,37 +1606,37 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>121.4</v>
+        <v>122.74</v>
       </c>
       <c r="D21" t="n">
         <v>95</v>
       </c>
       <c r="E21" t="n">
-        <v>51.17</v>
+        <v>52.83</v>
       </c>
       <c r="F21" t="n">
-        <v>1.48</v>
+        <v>1.55</v>
       </c>
       <c r="G21" t="n">
-        <v>8.460000000000001</v>
+        <v>8.57</v>
       </c>
       <c r="H21" t="n">
-        <v>6.97</v>
+        <v>6.98</v>
       </c>
       <c r="I21" t="n">
-        <v>118.02</v>
+        <v>119.31</v>
       </c>
       <c r="J21" t="n">
-        <v>123.52</v>
+        <v>124.88</v>
       </c>
       <c r="K21" t="n">
-        <v>108.71</v>
+        <v>109.89</v>
       </c>
       <c r="L21" t="n">
-        <v>142.56</v>
+        <v>144.16</v>
       </c>
       <c r="M21" t="n">
-        <v>69.59999999999999</v>
+        <v>70.06</v>
       </c>
       <c r="N21" t="inlineStr">
         <is>
@@ -1666,7 +1666,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>1562.29</v>
+        <v>1562.3</v>
       </c>
       <c r="D22" t="n">
         <v>95</v>
@@ -1675,7 +1675,7 @@
         <v>12.7</v>
       </c>
       <c r="F22" t="n">
-        <v>0.86</v>
+        <v>0.88</v>
       </c>
       <c r="G22" t="n">
         <v>61.22</v>
@@ -1684,16 +1684,16 @@
         <v>3.92</v>
       </c>
       <c r="I22" t="n">
-        <v>1537.8</v>
+        <v>1537.81</v>
       </c>
       <c r="J22" t="n">
-        <v>1577.6</v>
+        <v>1577.61</v>
       </c>
       <c r="K22" t="n">
-        <v>1470.46</v>
+        <v>1470.47</v>
       </c>
       <c r="L22" t="n">
-        <v>1715.34</v>
+        <v>1715.35</v>
       </c>
       <c r="M22" t="n">
         <v>59.68</v>
@@ -1726,16 +1726,16 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>444.92</v>
+        <v>445.37</v>
       </c>
       <c r="D23" t="n">
         <v>95</v>
       </c>
       <c r="E23" t="n">
-        <v>13.68</v>
+        <v>13.79</v>
       </c>
       <c r="F23" t="n">
-        <v>0.66</v>
+        <v>0.68</v>
       </c>
       <c r="G23" t="n">
         <v>17.89</v>
@@ -1744,19 +1744,19 @@
         <v>4.02</v>
       </c>
       <c r="I23" t="n">
-        <v>437.76</v>
+        <v>438.21</v>
       </c>
       <c r="J23" t="n">
-        <v>449.39</v>
+        <v>449.84</v>
       </c>
       <c r="K23" t="n">
-        <v>418.08</v>
+        <v>418.53</v>
       </c>
       <c r="L23" t="n">
-        <v>489.65</v>
+        <v>490.1</v>
       </c>
       <c r="M23" t="n">
-        <v>64.95</v>
+        <v>65.04000000000001</v>
       </c>
       <c r="N23" t="inlineStr">
         <is>
@@ -1786,37 +1786,37 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>296.05</v>
+        <v>296.9</v>
       </c>
       <c r="D24" t="n">
         <v>95</v>
       </c>
       <c r="E24" t="n">
-        <v>14.5</v>
+        <v>14.82</v>
       </c>
       <c r="F24" t="n">
-        <v>0.44</v>
+        <v>0.46</v>
       </c>
       <c r="G24" t="n">
         <v>13.7</v>
       </c>
       <c r="H24" t="n">
-        <v>4.63</v>
+        <v>4.61</v>
       </c>
       <c r="I24" t="n">
-        <v>290.57</v>
+        <v>291.42</v>
       </c>
       <c r="J24" t="n">
-        <v>299.48</v>
+        <v>300.33</v>
       </c>
       <c r="K24" t="n">
-        <v>275.5</v>
+        <v>276.35</v>
       </c>
       <c r="L24" t="n">
-        <v>330.31</v>
+        <v>331.15</v>
       </c>
       <c r="M24" t="n">
-        <v>66.63</v>
+        <v>66.88</v>
       </c>
       <c r="N24" t="inlineStr">
         <is>
@@ -1846,16 +1846,16 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>292.32</v>
+        <v>291.88</v>
       </c>
       <c r="D25" t="n">
         <v>86</v>
       </c>
       <c r="E25" t="n">
-        <v>5.59</v>
+        <v>5.44</v>
       </c>
       <c r="F25" t="n">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="G25" t="n">
         <v>6.64</v>
@@ -1864,19 +1864,19 @@
         <v>2.27</v>
       </c>
       <c r="I25" t="n">
-        <v>289.66</v>
+        <v>289.22</v>
       </c>
       <c r="J25" t="n">
-        <v>293.97</v>
+        <v>293.54</v>
       </c>
       <c r="K25" t="n">
-        <v>282.36</v>
+        <v>281.92</v>
       </c>
       <c r="L25" t="n">
-        <v>308.91</v>
+        <v>308.47</v>
       </c>
       <c r="M25" t="n">
-        <v>77.44</v>
+        <v>76.73999999999999</v>
       </c>
       <c r="N25" t="inlineStr">
         <is>
@@ -1906,37 +1906,37 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>58.17</v>
+        <v>57.86</v>
       </c>
       <c r="D26" t="n">
         <v>86</v>
       </c>
       <c r="E26" t="n">
-        <v>27.16</v>
+        <v>26.47</v>
       </c>
       <c r="F26" t="n">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="G26" t="n">
-        <v>4.28</v>
+        <v>4.3</v>
       </c>
       <c r="H26" t="n">
-        <v>7.35</v>
+        <v>7.43</v>
       </c>
       <c r="I26" t="n">
-        <v>56.46</v>
+        <v>56.14</v>
       </c>
       <c r="J26" t="n">
-        <v>59.24</v>
+        <v>58.94</v>
       </c>
       <c r="K26" t="n">
-        <v>51.76</v>
+        <v>51.41</v>
       </c>
       <c r="L26" t="n">
-        <v>68.87</v>
+        <v>68.61</v>
       </c>
       <c r="M26" t="n">
-        <v>66.81</v>
+        <v>66.51000000000001</v>
       </c>
       <c r="N26" t="inlineStr">
         <is>
@@ -1966,16 +1966,16 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>740.42</v>
+        <v>740.12</v>
       </c>
       <c r="D27" t="n">
         <v>82</v>
       </c>
       <c r="E27" t="n">
-        <v>3.12</v>
+        <v>3.08</v>
       </c>
       <c r="F27" t="n">
-        <v>0.54</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="G27" t="n">
         <v>6.73</v>
@@ -1984,19 +1984,19 @@
         <v>0.91</v>
       </c>
       <c r="I27" t="n">
-        <v>737.72</v>
+        <v>737.4299999999999</v>
       </c>
       <c r="J27" t="n">
-        <v>742.1</v>
+        <v>741.8</v>
       </c>
       <c r="K27" t="n">
-        <v>730.3200000000001</v>
+        <v>730.02</v>
       </c>
       <c r="L27" t="n">
-        <v>757.25</v>
+        <v>756.95</v>
       </c>
       <c r="M27" t="n">
-        <v>80.89</v>
+        <v>80.79000000000001</v>
       </c>
       <c r="N27" t="inlineStr">
         <is>
@@ -2026,16 +2026,16 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>714.22</v>
+        <v>714.25</v>
       </c>
       <c r="D28" t="n">
         <v>82</v>
       </c>
       <c r="E28" t="n">
-        <v>6.14</v>
+        <v>6.15</v>
       </c>
       <c r="F28" t="n">
-        <v>0.6</v>
+        <v>0.63</v>
       </c>
       <c r="G28" t="n">
         <v>9.84</v>
@@ -2044,16 +2044,16 @@
         <v>1.38</v>
       </c>
       <c r="I28" t="n">
-        <v>710.28</v>
+        <v>710.3099999999999</v>
       </c>
       <c r="J28" t="n">
-        <v>716.6799999999999</v>
+        <v>716.71</v>
       </c>
       <c r="K28" t="n">
-        <v>699.45</v>
+        <v>699.48</v>
       </c>
       <c r="L28" t="n">
-        <v>738.83</v>
+        <v>738.86</v>
       </c>
       <c r="M28" t="n">
         <v>86.84999999999999</v>
@@ -2086,37 +2086,37 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>214.38</v>
+        <v>213.61</v>
       </c>
       <c r="D29" t="n">
         <v>80</v>
       </c>
       <c r="E29" t="n">
-        <v>5.47</v>
+        <v>5.09</v>
       </c>
       <c r="F29" t="n">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="G29" t="n">
         <v>18.49</v>
       </c>
       <c r="H29" t="n">
-        <v>8.630000000000001</v>
+        <v>8.66</v>
       </c>
       <c r="I29" t="n">
-        <v>206.98</v>
+        <v>206.22</v>
       </c>
       <c r="J29" t="n">
-        <v>219</v>
+        <v>218.24</v>
       </c>
       <c r="K29" t="n">
-        <v>186.64</v>
+        <v>185.88</v>
       </c>
       <c r="L29" t="n">
-        <v>260.6</v>
+        <v>259.84</v>
       </c>
       <c r="M29" t="n">
-        <v>61.1</v>
+        <v>60.93</v>
       </c>
       <c r="N29" t="inlineStr">
         <is>
@@ -2146,37 +2146,37 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>532.4400000000001</v>
+        <v>533.4299999999999</v>
       </c>
       <c r="D30" t="n">
         <v>80</v>
       </c>
       <c r="E30" t="n">
-        <v>15.23</v>
+        <v>15.45</v>
       </c>
       <c r="F30" t="n">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="G30" t="n">
-        <v>17.35</v>
+        <v>17.4</v>
       </c>
       <c r="H30" t="n">
         <v>3.26</v>
       </c>
       <c r="I30" t="n">
-        <v>525.5</v>
+        <v>526.47</v>
       </c>
       <c r="J30" t="n">
-        <v>536.78</v>
+        <v>537.78</v>
       </c>
       <c r="K30" t="n">
-        <v>506.41</v>
+        <v>507.33</v>
       </c>
       <c r="L30" t="n">
-        <v>575.8200000000001</v>
+        <v>576.92</v>
       </c>
       <c r="M30" t="n">
-        <v>78.81</v>
+        <v>78.92</v>
       </c>
       <c r="N30" t="inlineStr">
         <is>
@@ -2197,46 +2197,46 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>QCOM</t>
+          <t>MU</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Chips</t>
+          <t>Memoria / Chips</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>236.15</v>
+        <v>815.08</v>
       </c>
       <c r="D31" t="n">
-        <v>61</v>
+        <v>79</v>
       </c>
       <c r="E31" t="n">
-        <v>40.25</v>
+        <v>41.4</v>
       </c>
       <c r="F31" t="n">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="G31" t="n">
-        <v>16.45</v>
+        <v>45.86</v>
       </c>
       <c r="H31" t="n">
-        <v>6.97</v>
+        <v>5.63</v>
       </c>
       <c r="I31" t="n">
-        <v>229.56</v>
+        <v>796.73</v>
       </c>
       <c r="J31" t="n">
-        <v>240.26</v>
+        <v>826.54</v>
       </c>
       <c r="K31" t="n">
-        <v>211.47</v>
+        <v>746.28</v>
       </c>
       <c r="L31" t="n">
-        <v>277.27</v>
+        <v>929.73</v>
       </c>
       <c r="M31" t="n">
-        <v>89.37</v>
+        <v>89.73</v>
       </c>
       <c r="N31" t="inlineStr">
         <is>
@@ -2257,53 +2257,57 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>GOOGL</t>
+          <t>QCOM</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Tecnología</t>
+          <t>Chips</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>392.75</v>
+        <v>238.6</v>
       </c>
       <c r="D32" t="n">
-        <v>78</v>
+        <v>61</v>
       </c>
       <c r="E32" t="n">
-        <v>2.48</v>
+        <v>41.7</v>
       </c>
       <c r="F32" t="n">
-        <v>0.54</v>
+        <v>1.34</v>
       </c>
       <c r="G32" t="n">
-        <v>10.42</v>
+        <v>16.45</v>
       </c>
       <c r="H32" t="n">
-        <v>2.65</v>
+        <v>6.89</v>
       </c>
       <c r="I32" t="n">
-        <v>388.58</v>
+        <v>232.02</v>
       </c>
       <c r="J32" t="n">
-        <v>395.36</v>
+        <v>242.71</v>
       </c>
       <c r="K32" t="n">
-        <v>377.12</v>
+        <v>213.92</v>
       </c>
       <c r="L32" t="n">
-        <v>418.81</v>
+        <v>279.73</v>
       </c>
       <c r="M32" t="n">
-        <v>86.2</v>
+        <v>89.56999999999999</v>
       </c>
       <c r="N32" t="inlineStr">
         <is>
           <t>ALTO</t>
         </is>
       </c>
-      <c r="O32" t="inlineStr"/>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>🔥</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>VIGILAR</t>
@@ -2313,46 +2317,46 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>SMCI</t>
+          <t>GOOGL</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Servidores IA</t>
+          <t>Tecnología</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>34.6</v>
+        <v>391.95</v>
       </c>
       <c r="D33" t="n">
         <v>78</v>
       </c>
       <c r="E33" t="n">
-        <v>23.93</v>
+        <v>2.27</v>
       </c>
       <c r="F33" t="n">
-        <v>0.72</v>
+        <v>0.55</v>
       </c>
       <c r="G33" t="n">
-        <v>2.27</v>
+        <v>10.42</v>
       </c>
       <c r="H33" t="n">
-        <v>6.57</v>
+        <v>2.66</v>
       </c>
       <c r="I33" t="n">
-        <v>33.69</v>
+        <v>387.78</v>
       </c>
       <c r="J33" t="n">
-        <v>35.17</v>
+        <v>394.56</v>
       </c>
       <c r="K33" t="n">
-        <v>31.19</v>
+        <v>376.32</v>
       </c>
       <c r="L33" t="n">
-        <v>40.28</v>
+        <v>418.01</v>
       </c>
       <c r="M33" t="n">
-        <v>64.70999999999999</v>
+        <v>85.38</v>
       </c>
       <c r="N33" t="inlineStr">
         <is>
@@ -2369,46 +2373,46 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>SMCI</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>IA / Chips</t>
+          <t>Servidores IA</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>468.35</v>
+        <v>34.74</v>
       </c>
       <c r="D34" t="n">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="E34" t="n">
-        <v>37.13</v>
+        <v>24.43</v>
       </c>
       <c r="F34" t="n">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="G34" t="n">
-        <v>27.39</v>
+        <v>2.27</v>
       </c>
       <c r="H34" t="n">
-        <v>5.85</v>
+        <v>6.54</v>
       </c>
       <c r="I34" t="n">
-        <v>457.39</v>
+        <v>33.83</v>
       </c>
       <c r="J34" t="n">
-        <v>475.2</v>
+        <v>35.31</v>
       </c>
       <c r="K34" t="n">
-        <v>427.27</v>
+        <v>31.33</v>
       </c>
       <c r="L34" t="n">
-        <v>536.8200000000001</v>
+        <v>40.42</v>
       </c>
       <c r="M34" t="n">
-        <v>80.95999999999999</v>
+        <v>65.15000000000001</v>
       </c>
       <c r="N34" t="inlineStr">
         <is>
@@ -2425,46 +2429,46 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>MU</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Memoria / Chips</t>
+          <t>IA / Chips</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>804.59</v>
+        <v>464.89</v>
       </c>
       <c r="D35" t="n">
         <v>72</v>
       </c>
       <c r="E35" t="n">
-        <v>39.58</v>
+        <v>36.12</v>
       </c>
       <c r="F35" t="n">
-        <v>1.2</v>
+        <v>0.74</v>
       </c>
       <c r="G35" t="n">
-        <v>45.86</v>
+        <v>27.39</v>
       </c>
       <c r="H35" t="n">
-        <v>5.7</v>
+        <v>5.89</v>
       </c>
       <c r="I35" t="n">
-        <v>786.24</v>
+        <v>453.94</v>
       </c>
       <c r="J35" t="n">
-        <v>816.0599999999999</v>
+        <v>471.74</v>
       </c>
       <c r="K35" t="n">
-        <v>735.79</v>
+        <v>423.81</v>
       </c>
       <c r="L35" t="n">
-        <v>919.25</v>
+        <v>533.36</v>
       </c>
       <c r="M35" t="n">
-        <v>89.48999999999999</v>
+        <v>80.73999999999999</v>
       </c>
       <c r="N35" t="inlineStr">
         <is>
@@ -2490,37 +2494,37 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>445.06</v>
+        <v>446.36</v>
       </c>
       <c r="D36" t="n">
         <v>70</v>
       </c>
       <c r="E36" t="n">
-        <v>13.39</v>
+        <v>13.72</v>
       </c>
       <c r="F36" t="n">
-        <v>0.88</v>
+        <v>0.93</v>
       </c>
       <c r="G36" t="n">
-        <v>15.22</v>
+        <v>15.37</v>
       </c>
       <c r="H36" t="n">
-        <v>3.42</v>
+        <v>3.44</v>
       </c>
       <c r="I36" t="n">
-        <v>438.97</v>
+        <v>440.21</v>
       </c>
       <c r="J36" t="n">
-        <v>448.87</v>
+        <v>450.21</v>
       </c>
       <c r="K36" t="n">
-        <v>422.22</v>
+        <v>423.3</v>
       </c>
       <c r="L36" t="n">
-        <v>483.12</v>
+        <v>484.8</v>
       </c>
       <c r="M36" t="n">
-        <v>78.13</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="N36" t="inlineStr">
         <is>
@@ -2546,37 +2550,37 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>128.03</v>
+        <v>128.56</v>
       </c>
       <c r="D37" t="n">
         <v>64</v>
       </c>
       <c r="E37" t="n">
-        <v>33.67</v>
+        <v>34.23</v>
       </c>
       <c r="F37" t="n">
-        <v>0.89</v>
+        <v>0.92</v>
       </c>
       <c r="G37" t="n">
         <v>8.390000000000001</v>
       </c>
       <c r="H37" t="n">
-        <v>6.55</v>
+        <v>6.52</v>
       </c>
       <c r="I37" t="n">
-        <v>124.67</v>
+        <v>125.21</v>
       </c>
       <c r="J37" t="n">
-        <v>130.13</v>
+        <v>130.66</v>
       </c>
       <c r="K37" t="n">
-        <v>115.45</v>
+        <v>115.98</v>
       </c>
       <c r="L37" t="n">
-        <v>149</v>
+        <v>149.53</v>
       </c>
       <c r="M37" t="n">
-        <v>88.76000000000001</v>
+        <v>88.83</v>
       </c>
       <c r="N37" t="inlineStr">
         <is>

--- a/analisis_acciones.xlsx
+++ b/analisis_acciones.xlsx
@@ -510,37 +510,37 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>221.38</v>
+        <v>220.33</v>
       </c>
       <c r="D2" t="n">
         <v>95</v>
       </c>
       <c r="E2" t="n">
-        <v>11.54</v>
+        <v>11.01</v>
       </c>
       <c r="F2" t="n">
-        <v>0.76</v>
+        <v>0.8</v>
       </c>
       <c r="G2" t="n">
         <v>7.7</v>
       </c>
       <c r="H2" t="n">
-        <v>3.48</v>
+        <v>3.49</v>
       </c>
       <c r="I2" t="n">
-        <v>218.3</v>
+        <v>217.25</v>
       </c>
       <c r="J2" t="n">
-        <v>223.3</v>
+        <v>222.25</v>
       </c>
       <c r="K2" t="n">
-        <v>209.84</v>
+        <v>208.79</v>
       </c>
       <c r="L2" t="n">
-        <v>240.62</v>
+        <v>239.57</v>
       </c>
       <c r="M2" t="n">
-        <v>65.93000000000001</v>
+        <v>65.39</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -570,16 +570,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>429.26</v>
+        <v>428.83</v>
       </c>
       <c r="D3" t="n">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="E3" t="n">
-        <v>3.06</v>
+        <v>2.96</v>
       </c>
       <c r="F3" t="n">
-        <v>0.49</v>
+        <v>0.52</v>
       </c>
       <c r="G3" t="n">
         <v>15.4</v>
@@ -588,19 +588,19 @@
         <v>3.59</v>
       </c>
       <c r="I3" t="n">
-        <v>423.1</v>
+        <v>422.67</v>
       </c>
       <c r="J3" t="n">
-        <v>433.11</v>
+        <v>432.68</v>
       </c>
       <c r="K3" t="n">
-        <v>406.16</v>
+        <v>405.73</v>
       </c>
       <c r="L3" t="n">
-        <v>467.76</v>
+        <v>467.33</v>
       </c>
       <c r="M3" t="n">
-        <v>61.38</v>
+        <v>61.16</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -621,46 +621,46 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>COIN</t>
+          <t>KLAC</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Cripto / Trading</t>
+          <t>Equipos chips</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>217.56</v>
+        <v>1847.31</v>
       </c>
       <c r="D4" t="n">
         <v>92</v>
       </c>
       <c r="E4" t="n">
-        <v>7.18</v>
+        <v>7.82</v>
       </c>
       <c r="F4" t="n">
-        <v>0.87</v>
+        <v>0.68</v>
       </c>
       <c r="G4" t="n">
-        <v>12.2</v>
+        <v>83.20999999999999</v>
       </c>
       <c r="H4" t="n">
-        <v>5.61</v>
+        <v>4.5</v>
       </c>
       <c r="I4" t="n">
-        <v>212.68</v>
+        <v>1814.02</v>
       </c>
       <c r="J4" t="n">
-        <v>220.61</v>
+        <v>1868.11</v>
       </c>
       <c r="K4" t="n">
-        <v>199.26</v>
+        <v>1722.49</v>
       </c>
       <c r="L4" t="n">
-        <v>248.05</v>
+        <v>2055.35</v>
       </c>
       <c r="M4" t="n">
-        <v>61.4</v>
+        <v>54.63</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -681,50 +681,50 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AI</t>
+          <t>COIN</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>IA</t>
+          <t>Cripto / Trading</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>9.52</v>
+        <v>215.92</v>
       </c>
       <c r="D5" t="n">
         <v>92</v>
       </c>
       <c r="E5" t="n">
-        <v>3.31</v>
+        <v>6.37</v>
       </c>
       <c r="F5" t="n">
-        <v>0.64</v>
+        <v>0.96</v>
       </c>
       <c r="G5" t="n">
-        <v>0.43</v>
+        <v>12.22</v>
       </c>
       <c r="H5" t="n">
-        <v>4.55</v>
+        <v>5.66</v>
       </c>
       <c r="I5" t="n">
-        <v>9.35</v>
+        <v>211.03</v>
       </c>
       <c r="J5" t="n">
-        <v>9.630000000000001</v>
+        <v>218.97</v>
       </c>
       <c r="K5" t="n">
-        <v>8.869999999999999</v>
+        <v>197.59</v>
       </c>
       <c r="L5" t="n">
-        <v>10.61</v>
+        <v>246.46</v>
       </c>
       <c r="M5" t="n">
-        <v>55.35</v>
+        <v>60.72</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>BAJO</t>
+          <t>MEDIO</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -741,50 +741,50 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>KLAC</t>
+          <t>AI</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Equipos chips</t>
+          <t>IA</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1850.58</v>
+        <v>9.52</v>
       </c>
       <c r="D6" t="n">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="E6" t="n">
-        <v>8.01</v>
+        <v>3.2</v>
       </c>
       <c r="F6" t="n">
-        <v>0.62</v>
+        <v>0.68</v>
       </c>
       <c r="G6" t="n">
-        <v>82.87</v>
+        <v>0.43</v>
       </c>
       <c r="H6" t="n">
-        <v>4.48</v>
+        <v>4.56</v>
       </c>
       <c r="I6" t="n">
-        <v>1817.43</v>
+        <v>9.34</v>
       </c>
       <c r="J6" t="n">
-        <v>1871.3</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="K6" t="n">
-        <v>1726.28</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="L6" t="n">
-        <v>2057.75</v>
+        <v>10.6</v>
       </c>
       <c r="M6" t="n">
-        <v>54.89</v>
+        <v>55.17</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>MEDIO</t>
+          <t>BAJO</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -810,16 +810,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>404.84</v>
+        <v>404.66</v>
       </c>
       <c r="D7" t="n">
         <v>95</v>
       </c>
       <c r="E7" t="n">
-        <v>0.8</v>
+        <v>0.76</v>
       </c>
       <c r="F7" t="n">
-        <v>0.75</v>
+        <v>0.79</v>
       </c>
       <c r="G7" t="n">
         <v>15.67</v>
@@ -828,19 +828,19 @@
         <v>3.87</v>
       </c>
       <c r="I7" t="n">
-        <v>398.57</v>
+        <v>398.39</v>
       </c>
       <c r="J7" t="n">
-        <v>408.76</v>
+        <v>408.58</v>
       </c>
       <c r="K7" t="n">
-        <v>381.33</v>
+        <v>381.15</v>
       </c>
       <c r="L7" t="n">
-        <v>444.02</v>
+        <v>443.84</v>
       </c>
       <c r="M7" t="n">
-        <v>65.94</v>
+        <v>65.84</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -870,16 +870,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>54.84</v>
+        <v>54.81</v>
       </c>
       <c r="D8" t="n">
         <v>84</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.42</v>
+        <v>-1.47</v>
       </c>
       <c r="F8" t="n">
-        <v>0.35</v>
+        <v>0.38</v>
       </c>
       <c r="G8" t="n">
         <v>1.68</v>
@@ -888,19 +888,19 @@
         <v>3.06</v>
       </c>
       <c r="I8" t="n">
-        <v>54.17</v>
+        <v>54.14</v>
       </c>
       <c r="J8" t="n">
-        <v>55.26</v>
+        <v>55.23</v>
       </c>
       <c r="K8" t="n">
-        <v>52.32</v>
+        <v>52.29</v>
       </c>
       <c r="L8" t="n">
-        <v>59.04</v>
+        <v>59.01</v>
       </c>
       <c r="M8" t="n">
-        <v>58.29</v>
+        <v>58.2</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
@@ -930,37 +930,37 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>269.94</v>
+        <v>269.47</v>
       </c>
       <c r="D9" t="n">
         <v>77</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.78</v>
+        <v>-0.95</v>
       </c>
       <c r="F9" t="n">
-        <v>0.45</v>
+        <v>0.49</v>
       </c>
       <c r="G9" t="n">
         <v>7.18</v>
       </c>
       <c r="H9" t="n">
-        <v>2.66</v>
+        <v>2.67</v>
       </c>
       <c r="I9" t="n">
-        <v>267.07</v>
+        <v>266.6</v>
       </c>
       <c r="J9" t="n">
-        <v>271.74</v>
+        <v>271.27</v>
       </c>
       <c r="K9" t="n">
-        <v>259.16</v>
+        <v>258.69</v>
       </c>
       <c r="L9" t="n">
-        <v>287.9</v>
+        <v>287.43</v>
       </c>
       <c r="M9" t="n">
-        <v>73.68000000000001</v>
+        <v>72.87</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
@@ -986,37 +986,37 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>8.51</v>
+        <v>8.44</v>
       </c>
       <c r="D10" t="n">
         <v>76</v>
       </c>
       <c r="E10" t="n">
-        <v>-10.14</v>
+        <v>-10.82</v>
       </c>
       <c r="F10" t="n">
-        <v>0.79</v>
+        <v>0.85</v>
       </c>
       <c r="G10" t="n">
         <v>0.65</v>
       </c>
       <c r="H10" t="n">
-        <v>7.59</v>
+        <v>7.65</v>
       </c>
       <c r="I10" t="n">
-        <v>8.25</v>
+        <v>8.19</v>
       </c>
       <c r="J10" t="n">
-        <v>8.67</v>
+        <v>8.609999999999999</v>
       </c>
       <c r="K10" t="n">
-        <v>7.54</v>
+        <v>7.48</v>
       </c>
       <c r="L10" t="n">
-        <v>10.13</v>
+        <v>10.06</v>
       </c>
       <c r="M10" t="n">
-        <v>56</v>
+        <v>55.35</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
@@ -1042,37 +1042,37 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>80.5</v>
+        <v>80.76000000000001</v>
       </c>
       <c r="D11" t="n">
         <v>54</v>
       </c>
       <c r="E11" t="n">
-        <v>5.16</v>
+        <v>5.5</v>
       </c>
       <c r="F11" t="n">
-        <v>0.54</v>
+        <v>0.58</v>
       </c>
       <c r="G11" t="n">
-        <v>4.2</v>
+        <v>4.22</v>
       </c>
       <c r="H11" t="n">
-        <v>5.22</v>
+        <v>5.23</v>
       </c>
       <c r="I11" t="n">
-        <v>78.81999999999999</v>
+        <v>79.06999999999999</v>
       </c>
       <c r="J11" t="n">
-        <v>81.55</v>
+        <v>81.81999999999999</v>
       </c>
       <c r="K11" t="n">
-        <v>74.19</v>
+        <v>74.43000000000001</v>
       </c>
       <c r="L11" t="n">
-        <v>91.01000000000001</v>
+        <v>91.31</v>
       </c>
       <c r="M11" t="n">
-        <v>41.85</v>
+        <v>42.27</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
@@ -1102,37 +1102,37 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>149.19</v>
+        <v>149.15</v>
       </c>
       <c r="D12" t="n">
         <v>66</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.93</v>
+        <v>-2.95</v>
       </c>
       <c r="F12" t="n">
-        <v>0.44</v>
+        <v>0.47</v>
       </c>
       <c r="G12" t="n">
         <v>4.02</v>
       </c>
       <c r="H12" t="n">
-        <v>2.69</v>
+        <v>2.7</v>
       </c>
       <c r="I12" t="n">
-        <v>147.58</v>
+        <v>147.54</v>
       </c>
       <c r="J12" t="n">
-        <v>150.19</v>
+        <v>150.15</v>
       </c>
       <c r="K12" t="n">
-        <v>143.16</v>
+        <v>143.12</v>
       </c>
       <c r="L12" t="n">
-        <v>159.23</v>
+        <v>159.2</v>
       </c>
       <c r="M12" t="n">
-        <v>51.38</v>
+        <v>51.32</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
@@ -1158,16 +1158,16 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>410.46</v>
+        <v>410.11</v>
       </c>
       <c r="D13" t="n">
         <v>54</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.76</v>
+        <v>-0.85</v>
       </c>
       <c r="F13" t="n">
-        <v>0.54</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="G13" t="n">
         <v>11.8</v>
@@ -1176,19 +1176,19 @@
         <v>2.88</v>
       </c>
       <c r="I13" t="n">
-        <v>405.74</v>
+        <v>405.39</v>
       </c>
       <c r="J13" t="n">
-        <v>413.41</v>
+        <v>413.06</v>
       </c>
       <c r="K13" t="n">
-        <v>392.76</v>
+        <v>392.41</v>
       </c>
       <c r="L13" t="n">
-        <v>439.96</v>
+        <v>439.61</v>
       </c>
       <c r="M13" t="n">
-        <v>42.42</v>
+        <v>42.25</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
@@ -1214,37 +1214,37 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>184.83</v>
+        <v>184.48</v>
       </c>
       <c r="D14" t="n">
         <v>54</v>
       </c>
       <c r="E14" t="n">
-        <v>-3.87</v>
+        <v>-4.06</v>
       </c>
       <c r="F14" t="n">
-        <v>0.39</v>
+        <v>0.43</v>
       </c>
       <c r="G14" t="n">
         <v>4.61</v>
       </c>
       <c r="H14" t="n">
-        <v>2.49</v>
+        <v>2.5</v>
       </c>
       <c r="I14" t="n">
-        <v>182.99</v>
+        <v>182.64</v>
       </c>
       <c r="J14" t="n">
-        <v>185.98</v>
+        <v>185.63</v>
       </c>
       <c r="K14" t="n">
-        <v>177.92</v>
+        <v>177.57</v>
       </c>
       <c r="L14" t="n">
-        <v>196.35</v>
+        <v>196</v>
       </c>
       <c r="M14" t="n">
-        <v>48.2</v>
+        <v>47.62</v>
       </c>
       <c r="N14" t="inlineStr">
         <is>
@@ -1270,37 +1270,37 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>55.23</v>
+        <v>54.98</v>
       </c>
       <c r="D15" t="n">
         <v>54</v>
       </c>
       <c r="E15" t="n">
-        <v>-8.359999999999999</v>
+        <v>-8.779999999999999</v>
       </c>
       <c r="F15" t="n">
-        <v>0.63</v>
+        <v>0.68</v>
       </c>
       <c r="G15" t="n">
         <v>1.85</v>
       </c>
       <c r="H15" t="n">
-        <v>3.35</v>
+        <v>3.36</v>
       </c>
       <c r="I15" t="n">
-        <v>54.49</v>
+        <v>54.24</v>
       </c>
       <c r="J15" t="n">
-        <v>55.69</v>
+        <v>55.44</v>
       </c>
       <c r="K15" t="n">
-        <v>52.45</v>
+        <v>52.2</v>
       </c>
       <c r="L15" t="n">
-        <v>59.85</v>
+        <v>59.6</v>
       </c>
       <c r="M15" t="n">
-        <v>47.09</v>
+        <v>46.38</v>
       </c>
       <c r="N15" t="inlineStr">
         <is>
@@ -1326,37 +1326,37 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>599.1900000000001</v>
+        <v>598.72</v>
       </c>
       <c r="D16" t="n">
         <v>46</v>
       </c>
       <c r="E16" t="n">
-        <v>-1.84</v>
+        <v>-1.92</v>
       </c>
       <c r="F16" t="n">
-        <v>0.64</v>
+        <v>0.7</v>
       </c>
       <c r="G16" t="n">
-        <v>18.25</v>
+        <v>18.28</v>
       </c>
       <c r="H16" t="n">
         <v>3.05</v>
       </c>
       <c r="I16" t="n">
-        <v>591.89</v>
+        <v>591.41</v>
       </c>
       <c r="J16" t="n">
-        <v>603.75</v>
+        <v>603.29</v>
       </c>
       <c r="K16" t="n">
-        <v>571.8200000000001</v>
+        <v>571.3</v>
       </c>
       <c r="L16" t="n">
-        <v>644.8099999999999</v>
+        <v>644.42</v>
       </c>
       <c r="M16" t="n">
-        <v>26.37</v>
+        <v>26.29</v>
       </c>
       <c r="N16" t="inlineStr">
         <is>
@@ -1373,50 +1373,50 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>PYPL</t>
+          <t>SOFI</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Pagos</t>
+          <t>Fintech</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>45.24</v>
+        <v>16.23</v>
       </c>
       <c r="D17" t="n">
         <v>46</v>
       </c>
       <c r="E17" t="n">
-        <v>-10.23</v>
+        <v>0.19</v>
       </c>
       <c r="F17" t="n">
-        <v>0.51</v>
+        <v>0.83</v>
       </c>
       <c r="G17" t="n">
-        <v>1.56</v>
+        <v>0.82</v>
       </c>
       <c r="H17" t="n">
-        <v>3.45</v>
+        <v>5.03</v>
       </c>
       <c r="I17" t="n">
-        <v>44.61</v>
+        <v>15.9</v>
       </c>
       <c r="J17" t="n">
-        <v>45.62</v>
+        <v>16.43</v>
       </c>
       <c r="K17" t="n">
-        <v>42.9</v>
+        <v>15.01</v>
       </c>
       <c r="L17" t="n">
-        <v>49.13</v>
+        <v>18.27</v>
       </c>
       <c r="M17" t="n">
-        <v>24.31</v>
+        <v>32.12</v>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>BAJO</t>
+          <t>MEDIO</t>
         </is>
       </c>
       <c r="O17" t="inlineStr"/>
@@ -1429,50 +1429,50 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>SOFI</t>
+          <t>PYPL</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Fintech</t>
+          <t>Pagos</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>16.08</v>
+        <v>45.07</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.77</v>
+        <v>-10.56</v>
       </c>
       <c r="F18" t="n">
-        <v>0.73</v>
+        <v>0.54</v>
       </c>
       <c r="G18" t="n">
-        <v>0.82</v>
+        <v>1.56</v>
       </c>
       <c r="H18" t="n">
-        <v>5.08</v>
+        <v>3.46</v>
       </c>
       <c r="I18" t="n">
-        <v>15.75</v>
+        <v>44.45</v>
       </c>
       <c r="J18" t="n">
-        <v>16.28</v>
+        <v>45.46</v>
       </c>
       <c r="K18" t="n">
-        <v>14.85</v>
+        <v>42.73</v>
       </c>
       <c r="L18" t="n">
-        <v>18.12</v>
+        <v>48.97</v>
       </c>
       <c r="M18" t="n">
-        <v>30.64</v>
+        <v>23.95</v>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>MEDIO</t>
+          <t>BAJO</t>
         </is>
       </c>
       <c r="O18" t="inlineStr"/>
@@ -1485,50 +1485,50 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>UPST</t>
+          <t>PLTR</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Fintech IA</t>
+          <t>IA / Software</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>28.94</v>
+        <v>136.38</v>
       </c>
       <c r="D19" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="E19" t="n">
-        <v>-9.77</v>
+        <v>-6.61</v>
       </c>
       <c r="F19" t="n">
-        <v>0.52</v>
+        <v>0.68</v>
       </c>
       <c r="G19" t="n">
-        <v>1.81</v>
+        <v>6.24</v>
       </c>
       <c r="H19" t="n">
-        <v>6.25</v>
+        <v>4.58</v>
       </c>
       <c r="I19" t="n">
-        <v>28.22</v>
+        <v>133.88</v>
       </c>
       <c r="J19" t="n">
-        <v>29.4</v>
+        <v>137.94</v>
       </c>
       <c r="K19" t="n">
-        <v>26.23</v>
+        <v>127.02</v>
       </c>
       <c r="L19" t="n">
-        <v>33.46</v>
+        <v>151.98</v>
       </c>
       <c r="M19" t="n">
-        <v>34.58</v>
+        <v>40.43</v>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>MEDIO</t>
+          <t>BAJO</t>
         </is>
       </c>
       <c r="O19" t="inlineStr"/>
@@ -1541,50 +1541,50 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>PLTR</t>
+          <t>UPST</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>IA / Software</t>
+          <t>Fintech IA</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>135.65</v>
+        <v>28.96</v>
       </c>
       <c r="D20" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E20" t="n">
-        <v>-7.11</v>
+        <v>-9.73</v>
       </c>
       <c r="F20" t="n">
-        <v>0.64</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="G20" t="n">
-        <v>6.24</v>
+        <v>1.81</v>
       </c>
       <c r="H20" t="n">
-        <v>4.6</v>
+        <v>6.25</v>
       </c>
       <c r="I20" t="n">
-        <v>133.15</v>
+        <v>28.24</v>
       </c>
       <c r="J20" t="n">
-        <v>137.21</v>
+        <v>29.41</v>
       </c>
       <c r="K20" t="n">
-        <v>126.29</v>
+        <v>26.24</v>
       </c>
       <c r="L20" t="n">
-        <v>151.25</v>
+        <v>33.49</v>
       </c>
       <c r="M20" t="n">
-        <v>39.85</v>
+        <v>34.62</v>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>BAJO</t>
+          <t>MEDIO</t>
         </is>
       </c>
       <c r="O20" t="inlineStr"/>
@@ -1606,37 +1606,37 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>122.74</v>
+        <v>122.46</v>
       </c>
       <c r="D21" t="n">
         <v>95</v>
       </c>
       <c r="E21" t="n">
-        <v>52.83</v>
+        <v>52.48</v>
       </c>
       <c r="F21" t="n">
-        <v>1.55</v>
+        <v>1.65</v>
       </c>
       <c r="G21" t="n">
-        <v>8.57</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="H21" t="n">
-        <v>6.98</v>
+        <v>7.06</v>
       </c>
       <c r="I21" t="n">
-        <v>119.31</v>
+        <v>119</v>
       </c>
       <c r="J21" t="n">
-        <v>124.88</v>
+        <v>124.62</v>
       </c>
       <c r="K21" t="n">
-        <v>109.89</v>
+        <v>109.5</v>
       </c>
       <c r="L21" t="n">
-        <v>144.16</v>
+        <v>144.06</v>
       </c>
       <c r="M21" t="n">
-        <v>70.06</v>
+        <v>69.95999999999999</v>
       </c>
       <c r="N21" t="inlineStr">
         <is>
@@ -1666,37 +1666,37 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>1562.3</v>
+        <v>1564.29</v>
       </c>
       <c r="D22" t="n">
         <v>95</v>
       </c>
       <c r="E22" t="n">
-        <v>12.7</v>
+        <v>12.85</v>
       </c>
       <c r="F22" t="n">
-        <v>0.88</v>
+        <v>0.92</v>
       </c>
       <c r="G22" t="n">
         <v>61.22</v>
       </c>
       <c r="H22" t="n">
-        <v>3.92</v>
+        <v>3.91</v>
       </c>
       <c r="I22" t="n">
-        <v>1537.81</v>
+        <v>1539.8</v>
       </c>
       <c r="J22" t="n">
-        <v>1577.61</v>
+        <v>1579.6</v>
       </c>
       <c r="K22" t="n">
-        <v>1470.47</v>
+        <v>1472.46</v>
       </c>
       <c r="L22" t="n">
-        <v>1715.35</v>
+        <v>1717.35</v>
       </c>
       <c r="M22" t="n">
-        <v>59.68</v>
+        <v>59.9</v>
       </c>
       <c r="N22" t="inlineStr">
         <is>
@@ -1726,16 +1726,16 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>445.37</v>
+        <v>444.77</v>
       </c>
       <c r="D23" t="n">
         <v>95</v>
       </c>
       <c r="E23" t="n">
-        <v>13.79</v>
+        <v>13.64</v>
       </c>
       <c r="F23" t="n">
-        <v>0.68</v>
+        <v>0.72</v>
       </c>
       <c r="G23" t="n">
         <v>17.89</v>
@@ -1744,19 +1744,19 @@
         <v>4.02</v>
       </c>
       <c r="I23" t="n">
-        <v>438.21</v>
+        <v>437.61</v>
       </c>
       <c r="J23" t="n">
-        <v>449.84</v>
+        <v>449.24</v>
       </c>
       <c r="K23" t="n">
-        <v>418.53</v>
+        <v>417.93</v>
       </c>
       <c r="L23" t="n">
-        <v>490.1</v>
+        <v>489.5</v>
       </c>
       <c r="M23" t="n">
-        <v>65.04000000000001</v>
+        <v>64.92</v>
       </c>
       <c r="N23" t="inlineStr">
         <is>
@@ -1786,37 +1786,37 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>296.9</v>
+        <v>295.9</v>
       </c>
       <c r="D24" t="n">
         <v>95</v>
       </c>
       <c r="E24" t="n">
-        <v>14.82</v>
+        <v>14.44</v>
       </c>
       <c r="F24" t="n">
-        <v>0.46</v>
+        <v>0.49</v>
       </c>
       <c r="G24" t="n">
         <v>13.7</v>
       </c>
       <c r="H24" t="n">
-        <v>4.61</v>
+        <v>4.63</v>
       </c>
       <c r="I24" t="n">
-        <v>291.42</v>
+        <v>290.42</v>
       </c>
       <c r="J24" t="n">
-        <v>300.33</v>
+        <v>299.33</v>
       </c>
       <c r="K24" t="n">
-        <v>276.35</v>
+        <v>275.35</v>
       </c>
       <c r="L24" t="n">
-        <v>331.15</v>
+        <v>330.15</v>
       </c>
       <c r="M24" t="n">
-        <v>66.88</v>
+        <v>66.58</v>
       </c>
       <c r="N24" t="inlineStr">
         <is>
@@ -1846,37 +1846,37 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>291.88</v>
+        <v>291.39</v>
       </c>
       <c r="D25" t="n">
         <v>86</v>
       </c>
       <c r="E25" t="n">
-        <v>5.44</v>
+        <v>5.26</v>
       </c>
       <c r="F25" t="n">
-        <v>0.49</v>
+        <v>0.52</v>
       </c>
       <c r="G25" t="n">
         <v>6.64</v>
       </c>
       <c r="H25" t="n">
-        <v>2.27</v>
+        <v>2.28</v>
       </c>
       <c r="I25" t="n">
-        <v>289.22</v>
+        <v>288.73</v>
       </c>
       <c r="J25" t="n">
-        <v>293.54</v>
+        <v>293.05</v>
       </c>
       <c r="K25" t="n">
-        <v>281.92</v>
+        <v>281.43</v>
       </c>
       <c r="L25" t="n">
-        <v>308.47</v>
+        <v>307.98</v>
       </c>
       <c r="M25" t="n">
-        <v>76.73999999999999</v>
+        <v>75.97</v>
       </c>
       <c r="N25" t="inlineStr">
         <is>
@@ -1906,37 +1906,37 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>57.86</v>
+        <v>57.71</v>
       </c>
       <c r="D26" t="n">
         <v>86</v>
       </c>
       <c r="E26" t="n">
-        <v>26.47</v>
+        <v>26.14</v>
       </c>
       <c r="F26" t="n">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="G26" t="n">
         <v>4.3</v>
       </c>
       <c r="H26" t="n">
-        <v>7.43</v>
+        <v>7.45</v>
       </c>
       <c r="I26" t="n">
-        <v>56.14</v>
+        <v>55.99</v>
       </c>
       <c r="J26" t="n">
-        <v>58.94</v>
+        <v>58.79</v>
       </c>
       <c r="K26" t="n">
-        <v>51.41</v>
+        <v>51.26</v>
       </c>
       <c r="L26" t="n">
-        <v>68.61</v>
+        <v>68.45999999999999</v>
       </c>
       <c r="M26" t="n">
-        <v>66.51000000000001</v>
+        <v>66.37</v>
       </c>
       <c r="N26" t="inlineStr">
         <is>
@@ -1966,16 +1966,16 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>740.12</v>
+        <v>738.89</v>
       </c>
       <c r="D27" t="n">
         <v>82</v>
       </c>
       <c r="E27" t="n">
-        <v>3.08</v>
+        <v>2.91</v>
       </c>
       <c r="F27" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.63</v>
       </c>
       <c r="G27" t="n">
         <v>6.73</v>
@@ -1984,19 +1984,19 @@
         <v>0.91</v>
       </c>
       <c r="I27" t="n">
-        <v>737.4299999999999</v>
+        <v>736.2</v>
       </c>
       <c r="J27" t="n">
-        <v>741.8</v>
+        <v>740.5700000000001</v>
       </c>
       <c r="K27" t="n">
-        <v>730.02</v>
+        <v>728.79</v>
       </c>
       <c r="L27" t="n">
-        <v>756.95</v>
+        <v>755.72</v>
       </c>
       <c r="M27" t="n">
-        <v>80.79000000000001</v>
+        <v>80.38</v>
       </c>
       <c r="N27" t="inlineStr">
         <is>
@@ -2026,16 +2026,16 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>714.25</v>
+        <v>713.13</v>
       </c>
       <c r="D28" t="n">
         <v>82</v>
       </c>
       <c r="E28" t="n">
-        <v>6.15</v>
+        <v>5.98</v>
       </c>
       <c r="F28" t="n">
-        <v>0.63</v>
+        <v>0.68</v>
       </c>
       <c r="G28" t="n">
         <v>9.84</v>
@@ -2044,19 +2044,19 @@
         <v>1.38</v>
       </c>
       <c r="I28" t="n">
-        <v>710.3099999999999</v>
+        <v>709.1900000000001</v>
       </c>
       <c r="J28" t="n">
-        <v>716.71</v>
+        <v>715.59</v>
       </c>
       <c r="K28" t="n">
-        <v>699.48</v>
+        <v>698.36</v>
       </c>
       <c r="L28" t="n">
-        <v>738.86</v>
+        <v>737.74</v>
       </c>
       <c r="M28" t="n">
-        <v>86.84999999999999</v>
+        <v>86.7</v>
       </c>
       <c r="N28" t="inlineStr">
         <is>
@@ -2086,37 +2086,37 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>213.61</v>
+        <v>214.25</v>
       </c>
       <c r="D29" t="n">
         <v>80</v>
       </c>
       <c r="E29" t="n">
-        <v>5.09</v>
+        <v>5.41</v>
       </c>
       <c r="F29" t="n">
-        <v>0.75</v>
+        <v>0.79</v>
       </c>
       <c r="G29" t="n">
         <v>18.49</v>
       </c>
       <c r="H29" t="n">
-        <v>8.66</v>
+        <v>8.630000000000001</v>
       </c>
       <c r="I29" t="n">
-        <v>206.22</v>
+        <v>206.85</v>
       </c>
       <c r="J29" t="n">
-        <v>218.24</v>
+        <v>218.87</v>
       </c>
       <c r="K29" t="n">
-        <v>185.88</v>
+        <v>186.51</v>
       </c>
       <c r="L29" t="n">
-        <v>259.84</v>
+        <v>260.48</v>
       </c>
       <c r="M29" t="n">
-        <v>60.93</v>
+        <v>61.08</v>
       </c>
       <c r="N29" t="inlineStr">
         <is>
@@ -2146,37 +2146,37 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>533.4299999999999</v>
+        <v>532.89</v>
       </c>
       <c r="D30" t="n">
         <v>80</v>
       </c>
       <c r="E30" t="n">
-        <v>15.45</v>
+        <v>15.33</v>
       </c>
       <c r="F30" t="n">
-        <v>0.8</v>
+        <v>0.87</v>
       </c>
       <c r="G30" t="n">
         <v>17.4</v>
       </c>
       <c r="H30" t="n">
-        <v>3.26</v>
+        <v>3.27</v>
       </c>
       <c r="I30" t="n">
-        <v>526.47</v>
+        <v>525.9299999999999</v>
       </c>
       <c r="J30" t="n">
-        <v>537.78</v>
+        <v>537.24</v>
       </c>
       <c r="K30" t="n">
-        <v>507.33</v>
+        <v>506.78</v>
       </c>
       <c r="L30" t="n">
-        <v>576.92</v>
+        <v>576.4</v>
       </c>
       <c r="M30" t="n">
-        <v>78.92</v>
+        <v>78.86</v>
       </c>
       <c r="N30" t="inlineStr">
         <is>
@@ -2206,37 +2206,37 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>815.08</v>
+        <v>810.64</v>
       </c>
       <c r="D31" t="n">
         <v>79</v>
       </c>
       <c r="E31" t="n">
-        <v>41.4</v>
+        <v>40.63</v>
       </c>
       <c r="F31" t="n">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="G31" t="n">
         <v>45.86</v>
       </c>
       <c r="H31" t="n">
-        <v>5.63</v>
+        <v>5.66</v>
       </c>
       <c r="I31" t="n">
-        <v>796.73</v>
+        <v>792.29</v>
       </c>
       <c r="J31" t="n">
-        <v>826.54</v>
+        <v>822.11</v>
       </c>
       <c r="K31" t="n">
-        <v>746.28</v>
+        <v>741.84</v>
       </c>
       <c r="L31" t="n">
-        <v>929.73</v>
+        <v>925.3</v>
       </c>
       <c r="M31" t="n">
-        <v>89.73</v>
+        <v>89.63</v>
       </c>
       <c r="N31" t="inlineStr">
         <is>
@@ -2266,37 +2266,37 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>238.6</v>
+        <v>236.73</v>
       </c>
       <c r="D32" t="n">
         <v>61</v>
       </c>
       <c r="E32" t="n">
-        <v>41.7</v>
+        <v>40.59</v>
       </c>
       <c r="F32" t="n">
-        <v>1.34</v>
+        <v>1.39</v>
       </c>
       <c r="G32" t="n">
         <v>16.45</v>
       </c>
       <c r="H32" t="n">
-        <v>6.89</v>
+        <v>6.95</v>
       </c>
       <c r="I32" t="n">
-        <v>232.02</v>
+        <v>230.15</v>
       </c>
       <c r="J32" t="n">
-        <v>242.71</v>
+        <v>240.84</v>
       </c>
       <c r="K32" t="n">
-        <v>213.92</v>
+        <v>212.05</v>
       </c>
       <c r="L32" t="n">
-        <v>279.73</v>
+        <v>277.86</v>
       </c>
       <c r="M32" t="n">
-        <v>89.56999999999999</v>
+        <v>89.42</v>
       </c>
       <c r="N32" t="inlineStr">
         <is>
@@ -2326,37 +2326,37 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>391.95</v>
+        <v>390.91</v>
       </c>
       <c r="D33" t="n">
         <v>78</v>
       </c>
       <c r="E33" t="n">
-        <v>2.27</v>
+        <v>2</v>
       </c>
       <c r="F33" t="n">
-        <v>0.55</v>
+        <v>0.6</v>
       </c>
       <c r="G33" t="n">
-        <v>10.42</v>
+        <v>10.49</v>
       </c>
       <c r="H33" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="I33" t="n">
-        <v>387.78</v>
+        <v>386.72</v>
       </c>
       <c r="J33" t="n">
-        <v>394.56</v>
+        <v>393.53</v>
       </c>
       <c r="K33" t="n">
-        <v>376.32</v>
+        <v>375.18</v>
       </c>
       <c r="L33" t="n">
-        <v>418.01</v>
+        <v>417.13</v>
       </c>
       <c r="M33" t="n">
-        <v>85.38</v>
+        <v>84.34</v>
       </c>
       <c r="N33" t="inlineStr">
         <is>
@@ -2382,37 +2382,37 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>34.74</v>
+        <v>34.3</v>
       </c>
       <c r="D34" t="n">
         <v>78</v>
       </c>
       <c r="E34" t="n">
-        <v>24.43</v>
+        <v>22.85</v>
       </c>
       <c r="F34" t="n">
-        <v>0.73</v>
+        <v>0.78</v>
       </c>
       <c r="G34" t="n">
-        <v>2.27</v>
+        <v>2.29</v>
       </c>
       <c r="H34" t="n">
-        <v>6.54</v>
+        <v>6.67</v>
       </c>
       <c r="I34" t="n">
-        <v>33.83</v>
+        <v>33.38</v>
       </c>
       <c r="J34" t="n">
-        <v>35.31</v>
+        <v>34.87</v>
       </c>
       <c r="K34" t="n">
-        <v>31.33</v>
+        <v>30.87</v>
       </c>
       <c r="L34" t="n">
-        <v>40.42</v>
+        <v>40.02</v>
       </c>
       <c r="M34" t="n">
-        <v>65.15000000000001</v>
+        <v>63.8</v>
       </c>
       <c r="N34" t="inlineStr">
         <is>
@@ -2438,16 +2438,16 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>464.89</v>
+        <v>464.83</v>
       </c>
       <c r="D35" t="n">
         <v>72</v>
       </c>
       <c r="E35" t="n">
-        <v>36.12</v>
+        <v>36.1</v>
       </c>
       <c r="F35" t="n">
-        <v>0.74</v>
+        <v>0.78</v>
       </c>
       <c r="G35" t="n">
         <v>27.39</v>
@@ -2456,19 +2456,19 @@
         <v>5.89</v>
       </c>
       <c r="I35" t="n">
-        <v>453.94</v>
+        <v>453.87</v>
       </c>
       <c r="J35" t="n">
-        <v>471.74</v>
+        <v>471.67</v>
       </c>
       <c r="K35" t="n">
-        <v>423.81</v>
+        <v>423.74</v>
       </c>
       <c r="L35" t="n">
-        <v>533.36</v>
+        <v>533.3</v>
       </c>
       <c r="M35" t="n">
-        <v>80.73999999999999</v>
+        <v>80.73</v>
       </c>
       <c r="N35" t="inlineStr">
         <is>
@@ -2494,16 +2494,16 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>446.36</v>
+        <v>446.8</v>
       </c>
       <c r="D36" t="n">
         <v>70</v>
       </c>
       <c r="E36" t="n">
-        <v>13.72</v>
+        <v>13.83</v>
       </c>
       <c r="F36" t="n">
-        <v>0.93</v>
+        <v>0.99</v>
       </c>
       <c r="G36" t="n">
         <v>15.37</v>
@@ -2512,19 +2512,19 @@
         <v>3.44</v>
       </c>
       <c r="I36" t="n">
-        <v>440.21</v>
+        <v>440.65</v>
       </c>
       <c r="J36" t="n">
-        <v>450.21</v>
+        <v>450.64</v>
       </c>
       <c r="K36" t="n">
-        <v>423.3</v>
+        <v>423.74</v>
       </c>
       <c r="L36" t="n">
-        <v>484.8</v>
+        <v>485.24</v>
       </c>
       <c r="M36" t="n">
-        <v>78.40000000000001</v>
+        <v>78.48999999999999</v>
       </c>
       <c r="N36" t="inlineStr">
         <is>
@@ -2550,37 +2550,37 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>128.56</v>
+        <v>128</v>
       </c>
       <c r="D37" t="n">
         <v>64</v>
       </c>
       <c r="E37" t="n">
-        <v>34.23</v>
+        <v>33.64</v>
       </c>
       <c r="F37" t="n">
-        <v>0.92</v>
+        <v>0.95</v>
       </c>
       <c r="G37" t="n">
         <v>8.390000000000001</v>
       </c>
       <c r="H37" t="n">
-        <v>6.52</v>
+        <v>6.55</v>
       </c>
       <c r="I37" t="n">
-        <v>125.21</v>
+        <v>124.64</v>
       </c>
       <c r="J37" t="n">
-        <v>130.66</v>
+        <v>130.1</v>
       </c>
       <c r="K37" t="n">
-        <v>115.98</v>
+        <v>115.42</v>
       </c>
       <c r="L37" t="n">
-        <v>149.53</v>
+        <v>148.97</v>
       </c>
       <c r="M37" t="n">
-        <v>88.83</v>
+        <v>88.75</v>
       </c>
       <c r="N37" t="inlineStr">
         <is>

--- a/analisis_acciones.xlsx
+++ b/analisis_acciones.xlsx
@@ -501,46 +501,46 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>NVDA</t>
+          <t>COIN</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>IA / Chips</t>
+          <t>Cripto / Trading</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>220.33</v>
+        <v>216.6</v>
       </c>
       <c r="D2" t="n">
         <v>95</v>
       </c>
       <c r="E2" t="n">
-        <v>11.01</v>
+        <v>6.7</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8</v>
+        <v>1.31</v>
       </c>
       <c r="G2" t="n">
-        <v>7.7</v>
+        <v>12.22</v>
       </c>
       <c r="H2" t="n">
-        <v>3.49</v>
+        <v>5.64</v>
       </c>
       <c r="I2" t="n">
-        <v>217.25</v>
+        <v>211.71</v>
       </c>
       <c r="J2" t="n">
-        <v>222.25</v>
+        <v>219.65</v>
       </c>
       <c r="K2" t="n">
-        <v>208.79</v>
+        <v>198.27</v>
       </c>
       <c r="L2" t="n">
-        <v>239.57</v>
+        <v>247.14</v>
       </c>
       <c r="M2" t="n">
-        <v>65.39</v>
+        <v>61</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -549,7 +549,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>🔥🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -561,7 +561,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AVGO</t>
+          <t>NVDA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -570,41 +570,41 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>428.83</v>
+        <v>219.44</v>
       </c>
       <c r="D3" t="n">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="E3" t="n">
-        <v>2.96</v>
+        <v>10.56</v>
       </c>
       <c r="F3" t="n">
-        <v>0.52</v>
+        <v>1.03</v>
       </c>
       <c r="G3" t="n">
-        <v>15.4</v>
+        <v>7.7</v>
       </c>
       <c r="H3" t="n">
-        <v>3.59</v>
+        <v>3.51</v>
       </c>
       <c r="I3" t="n">
-        <v>422.67</v>
+        <v>216.36</v>
       </c>
       <c r="J3" t="n">
-        <v>432.68</v>
+        <v>221.36</v>
       </c>
       <c r="K3" t="n">
-        <v>405.73</v>
+        <v>207.9</v>
       </c>
       <c r="L3" t="n">
-        <v>467.33</v>
+        <v>238.68</v>
       </c>
       <c r="M3" t="n">
-        <v>61.16</v>
+        <v>64.92</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>BAJO</t>
+          <t>MEDIO</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -621,50 +621,50 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>KLAC</t>
+          <t>AVGO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Equipos chips</t>
+          <t>IA / Chips</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1847.31</v>
+        <v>428.43</v>
       </c>
       <c r="D4" t="n">
         <v>92</v>
       </c>
       <c r="E4" t="n">
-        <v>7.82</v>
+        <v>2.86</v>
       </c>
       <c r="F4" t="n">
-        <v>0.68</v>
+        <v>0.83</v>
       </c>
       <c r="G4" t="n">
-        <v>83.20999999999999</v>
+        <v>15.4</v>
       </c>
       <c r="H4" t="n">
-        <v>4.5</v>
+        <v>3.59</v>
       </c>
       <c r="I4" t="n">
-        <v>1814.02</v>
+        <v>422.27</v>
       </c>
       <c r="J4" t="n">
-        <v>1868.11</v>
+        <v>432.28</v>
       </c>
       <c r="K4" t="n">
-        <v>1722.49</v>
+        <v>405.33</v>
       </c>
       <c r="L4" t="n">
-        <v>2055.35</v>
+        <v>466.93</v>
       </c>
       <c r="M4" t="n">
-        <v>54.63</v>
+        <v>60.96</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>MEDIO</t>
+          <t>BAJO</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -681,46 +681,46 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>COIN</t>
+          <t>KLAC</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Cripto / Trading</t>
+          <t>Equipos chips</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>215.92</v>
+        <v>1845.19</v>
       </c>
       <c r="D5" t="n">
         <v>92</v>
       </c>
       <c r="E5" t="n">
-        <v>6.37</v>
+        <v>7.7</v>
       </c>
       <c r="F5" t="n">
-        <v>0.96</v>
+        <v>1.16</v>
       </c>
       <c r="G5" t="n">
-        <v>12.22</v>
+        <v>83.20999999999999</v>
       </c>
       <c r="H5" t="n">
-        <v>5.66</v>
+        <v>4.51</v>
       </c>
       <c r="I5" t="n">
-        <v>211.03</v>
+        <v>1811.9</v>
       </c>
       <c r="J5" t="n">
-        <v>218.97</v>
+        <v>1865.99</v>
       </c>
       <c r="K5" t="n">
-        <v>197.59</v>
+        <v>1720.37</v>
       </c>
       <c r="L5" t="n">
-        <v>246.46</v>
+        <v>2053.23</v>
       </c>
       <c r="M5" t="n">
-        <v>60.72</v>
+        <v>54.45</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
@@ -750,37 +750,37 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>9.52</v>
+        <v>9.48</v>
       </c>
       <c r="D6" t="n">
         <v>92</v>
       </c>
       <c r="E6" t="n">
-        <v>3.2</v>
+        <v>2.82</v>
       </c>
       <c r="F6" t="n">
-        <v>0.68</v>
+        <v>0.9</v>
       </c>
       <c r="G6" t="n">
         <v>0.43</v>
       </c>
       <c r="H6" t="n">
-        <v>4.56</v>
+        <v>4.57</v>
       </c>
       <c r="I6" t="n">
-        <v>9.34</v>
+        <v>9.31</v>
       </c>
       <c r="J6" t="n">
-        <v>9.619999999999999</v>
+        <v>9.59</v>
       </c>
       <c r="K6" t="n">
-        <v>8.859999999999999</v>
+        <v>8.83</v>
       </c>
       <c r="L6" t="n">
-        <v>10.6</v>
+        <v>10.56</v>
       </c>
       <c r="M6" t="n">
-        <v>55.17</v>
+        <v>54.55</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
@@ -810,16 +810,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>404.66</v>
+        <v>404.54</v>
       </c>
       <c r="D7" t="n">
         <v>95</v>
       </c>
       <c r="E7" t="n">
-        <v>0.76</v>
+        <v>0.73</v>
       </c>
       <c r="F7" t="n">
-        <v>0.79</v>
+        <v>0.98</v>
       </c>
       <c r="G7" t="n">
         <v>15.67</v>
@@ -828,19 +828,19 @@
         <v>3.87</v>
       </c>
       <c r="I7" t="n">
-        <v>398.39</v>
+        <v>398.27</v>
       </c>
       <c r="J7" t="n">
-        <v>408.58</v>
+        <v>408.46</v>
       </c>
       <c r="K7" t="n">
-        <v>381.15</v>
+        <v>381.03</v>
       </c>
       <c r="L7" t="n">
-        <v>443.84</v>
+        <v>443.72</v>
       </c>
       <c r="M7" t="n">
-        <v>65.84</v>
+        <v>65.77</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -870,37 +870,37 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>54.81</v>
+        <v>54.93</v>
       </c>
       <c r="D8" t="n">
         <v>84</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.47</v>
+        <v>-1.26</v>
       </c>
       <c r="F8" t="n">
-        <v>0.38</v>
+        <v>0.68</v>
       </c>
       <c r="G8" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="H8" t="n">
-        <v>3.06</v>
+        <v>3.08</v>
       </c>
       <c r="I8" t="n">
-        <v>54.14</v>
+        <v>54.25</v>
       </c>
       <c r="J8" t="n">
-        <v>55.23</v>
+        <v>55.35</v>
       </c>
       <c r="K8" t="n">
-        <v>52.29</v>
+        <v>52.39</v>
       </c>
       <c r="L8" t="n">
-        <v>59.01</v>
+        <v>59.16</v>
       </c>
       <c r="M8" t="n">
-        <v>58.2</v>
+        <v>58.59</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
@@ -930,37 +930,37 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>269.47</v>
+        <v>268.99</v>
       </c>
       <c r="D9" t="n">
         <v>77</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.95</v>
+        <v>-1.12</v>
       </c>
       <c r="F9" t="n">
-        <v>0.49</v>
+        <v>0.77</v>
       </c>
       <c r="G9" t="n">
-        <v>7.18</v>
+        <v>7.23</v>
       </c>
       <c r="H9" t="n">
-        <v>2.67</v>
+        <v>2.69</v>
       </c>
       <c r="I9" t="n">
-        <v>266.6</v>
+        <v>266.1</v>
       </c>
       <c r="J9" t="n">
-        <v>271.27</v>
+        <v>270.8</v>
       </c>
       <c r="K9" t="n">
-        <v>258.69</v>
+        <v>258.14</v>
       </c>
       <c r="L9" t="n">
-        <v>287.43</v>
+        <v>287.07</v>
       </c>
       <c r="M9" t="n">
-        <v>72.87</v>
+        <v>72.06</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
@@ -986,16 +986,16 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>8.44</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="D10" t="n">
         <v>76</v>
       </c>
       <c r="E10" t="n">
-        <v>-10.82</v>
+        <v>-10.77</v>
       </c>
       <c r="F10" t="n">
-        <v>0.85</v>
+        <v>0.97</v>
       </c>
       <c r="G10" t="n">
         <v>0.65</v>
@@ -1013,10 +1013,10 @@
         <v>7.48</v>
       </c>
       <c r="L10" t="n">
-        <v>10.06</v>
+        <v>10.07</v>
       </c>
       <c r="M10" t="n">
-        <v>55.35</v>
+        <v>55.4</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
@@ -1042,16 +1042,16 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>80.76000000000001</v>
+        <v>80.78</v>
       </c>
       <c r="D11" t="n">
         <v>54</v>
       </c>
       <c r="E11" t="n">
-        <v>5.5</v>
+        <v>5.53</v>
       </c>
       <c r="F11" t="n">
-        <v>0.58</v>
+        <v>0.74</v>
       </c>
       <c r="G11" t="n">
         <v>4.22</v>
@@ -1060,19 +1060,19 @@
         <v>5.23</v>
       </c>
       <c r="I11" t="n">
-        <v>79.06999999999999</v>
+        <v>79.09</v>
       </c>
       <c r="J11" t="n">
-        <v>81.81999999999999</v>
+        <v>81.84</v>
       </c>
       <c r="K11" t="n">
-        <v>74.43000000000001</v>
+        <v>74.45</v>
       </c>
       <c r="L11" t="n">
-        <v>91.31</v>
+        <v>91.33</v>
       </c>
       <c r="M11" t="n">
-        <v>42.27</v>
+        <v>42.3</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
@@ -1102,37 +1102,37 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>149.15</v>
+        <v>149.68</v>
       </c>
       <c r="D12" t="n">
         <v>66</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.95</v>
+        <v>-2.61</v>
       </c>
       <c r="F12" t="n">
-        <v>0.47</v>
+        <v>0.82</v>
       </c>
       <c r="G12" t="n">
-        <v>4.02</v>
+        <v>4.05</v>
       </c>
       <c r="H12" t="n">
-        <v>2.7</v>
+        <v>2.71</v>
       </c>
       <c r="I12" t="n">
-        <v>147.54</v>
+        <v>148.06</v>
       </c>
       <c r="J12" t="n">
-        <v>150.15</v>
+        <v>150.69</v>
       </c>
       <c r="K12" t="n">
-        <v>143.12</v>
+        <v>143.61</v>
       </c>
       <c r="L12" t="n">
-        <v>159.2</v>
+        <v>159.8</v>
       </c>
       <c r="M12" t="n">
-        <v>51.32</v>
+        <v>52.17</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
@@ -1158,37 +1158,37 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>410.11</v>
+        <v>412.66</v>
       </c>
       <c r="D13" t="n">
         <v>54</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.85</v>
+        <v>-0.23</v>
       </c>
       <c r="F13" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.96</v>
       </c>
       <c r="G13" t="n">
         <v>11.8</v>
       </c>
       <c r="H13" t="n">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="I13" t="n">
-        <v>405.39</v>
+        <v>407.94</v>
       </c>
       <c r="J13" t="n">
-        <v>413.06</v>
+        <v>415.61</v>
       </c>
       <c r="K13" t="n">
-        <v>392.41</v>
+        <v>394.96</v>
       </c>
       <c r="L13" t="n">
-        <v>439.61</v>
+        <v>442.16</v>
       </c>
       <c r="M13" t="n">
-        <v>42.25</v>
+        <v>43.47</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
@@ -1214,37 +1214,37 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>184.48</v>
+        <v>184.74</v>
       </c>
       <c r="D14" t="n">
         <v>54</v>
       </c>
       <c r="E14" t="n">
-        <v>-4.06</v>
+        <v>-3.92</v>
       </c>
       <c r="F14" t="n">
-        <v>0.43</v>
+        <v>1.16</v>
       </c>
       <c r="G14" t="n">
         <v>4.61</v>
       </c>
       <c r="H14" t="n">
-        <v>2.5</v>
+        <v>2.49</v>
       </c>
       <c r="I14" t="n">
-        <v>182.64</v>
+        <v>182.9</v>
       </c>
       <c r="J14" t="n">
-        <v>185.63</v>
+        <v>185.89</v>
       </c>
       <c r="K14" t="n">
-        <v>177.57</v>
+        <v>177.83</v>
       </c>
       <c r="L14" t="n">
-        <v>196</v>
+        <v>196.26</v>
       </c>
       <c r="M14" t="n">
-        <v>47.62</v>
+        <v>48.05</v>
       </c>
       <c r="N14" t="inlineStr">
         <is>
@@ -1270,16 +1270,16 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>54.98</v>
+        <v>55.14</v>
       </c>
       <c r="D15" t="n">
         <v>54</v>
       </c>
       <c r="E15" t="n">
-        <v>-8.779999999999999</v>
+        <v>-8.51</v>
       </c>
       <c r="F15" t="n">
-        <v>0.68</v>
+        <v>1.04</v>
       </c>
       <c r="G15" t="n">
         <v>1.85</v>
@@ -1288,19 +1288,19 @@
         <v>3.36</v>
       </c>
       <c r="I15" t="n">
-        <v>54.24</v>
+        <v>54.4</v>
       </c>
       <c r="J15" t="n">
-        <v>55.44</v>
+        <v>55.6</v>
       </c>
       <c r="K15" t="n">
-        <v>52.2</v>
+        <v>52.36</v>
       </c>
       <c r="L15" t="n">
-        <v>59.6</v>
+        <v>59.76</v>
       </c>
       <c r="M15" t="n">
-        <v>46.38</v>
+        <v>46.84</v>
       </c>
       <c r="N15" t="inlineStr">
         <is>
@@ -1326,37 +1326,37 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>598.72</v>
+        <v>598.86</v>
       </c>
       <c r="D16" t="n">
         <v>46</v>
       </c>
       <c r="E16" t="n">
-        <v>-1.92</v>
+        <v>-1.89</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7</v>
+        <v>0.92</v>
       </c>
       <c r="G16" t="n">
-        <v>18.28</v>
+        <v>18.32</v>
       </c>
       <c r="H16" t="n">
-        <v>3.05</v>
+        <v>3.06</v>
       </c>
       <c r="I16" t="n">
-        <v>591.41</v>
+        <v>591.53</v>
       </c>
       <c r="J16" t="n">
-        <v>603.29</v>
+        <v>603.4400000000001</v>
       </c>
       <c r="K16" t="n">
-        <v>571.3</v>
+        <v>571.38</v>
       </c>
       <c r="L16" t="n">
-        <v>644.42</v>
+        <v>644.67</v>
       </c>
       <c r="M16" t="n">
-        <v>26.29</v>
+        <v>26.31</v>
       </c>
       <c r="N16" t="inlineStr">
         <is>
@@ -1382,37 +1382,37 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>16.23</v>
+        <v>16.26</v>
       </c>
       <c r="D17" t="n">
         <v>46</v>
       </c>
       <c r="E17" t="n">
-        <v>0.19</v>
+        <v>0.37</v>
       </c>
       <c r="F17" t="n">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="G17" t="n">
         <v>0.82</v>
       </c>
       <c r="H17" t="n">
-        <v>5.03</v>
+        <v>5.02</v>
       </c>
       <c r="I17" t="n">
-        <v>15.9</v>
+        <v>15.93</v>
       </c>
       <c r="J17" t="n">
-        <v>16.43</v>
+        <v>16.46</v>
       </c>
       <c r="K17" t="n">
-        <v>15.01</v>
+        <v>15.04</v>
       </c>
       <c r="L17" t="n">
-        <v>18.27</v>
+        <v>18.3</v>
       </c>
       <c r="M17" t="n">
-        <v>32.12</v>
+        <v>32.4</v>
       </c>
       <c r="N17" t="inlineStr">
         <is>
@@ -1447,7 +1447,7 @@
         <v>-10.56</v>
       </c>
       <c r="F18" t="n">
-        <v>0.54</v>
+        <v>1.12</v>
       </c>
       <c r="G18" t="n">
         <v>1.56</v>
@@ -1494,37 +1494,37 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>136.38</v>
+        <v>136.89</v>
       </c>
       <c r="D19" t="n">
         <v>44</v>
       </c>
       <c r="E19" t="n">
-        <v>-6.61</v>
+        <v>-6.26</v>
       </c>
       <c r="F19" t="n">
-        <v>0.68</v>
+        <v>0.89</v>
       </c>
       <c r="G19" t="n">
         <v>6.24</v>
       </c>
       <c r="H19" t="n">
-        <v>4.58</v>
+        <v>4.56</v>
       </c>
       <c r="I19" t="n">
-        <v>133.88</v>
+        <v>134.39</v>
       </c>
       <c r="J19" t="n">
-        <v>137.94</v>
+        <v>138.45</v>
       </c>
       <c r="K19" t="n">
-        <v>127.02</v>
+        <v>127.53</v>
       </c>
       <c r="L19" t="n">
-        <v>151.98</v>
+        <v>152.49</v>
       </c>
       <c r="M19" t="n">
-        <v>40.43</v>
+        <v>40.84</v>
       </c>
       <c r="N19" t="inlineStr">
         <is>
@@ -1550,37 +1550,37 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>28.96</v>
+        <v>28.69</v>
       </c>
       <c r="D20" t="n">
         <v>38</v>
       </c>
       <c r="E20" t="n">
-        <v>-9.73</v>
+        <v>-10.57</v>
       </c>
       <c r="F20" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.74</v>
       </c>
       <c r="G20" t="n">
         <v>1.81</v>
       </c>
       <c r="H20" t="n">
-        <v>6.25</v>
+        <v>6.31</v>
       </c>
       <c r="I20" t="n">
-        <v>28.24</v>
+        <v>27.97</v>
       </c>
       <c r="J20" t="n">
-        <v>29.41</v>
+        <v>29.14</v>
       </c>
       <c r="K20" t="n">
-        <v>26.24</v>
+        <v>25.97</v>
       </c>
       <c r="L20" t="n">
-        <v>33.49</v>
+        <v>33.22</v>
       </c>
       <c r="M20" t="n">
-        <v>34.62</v>
+        <v>33.95</v>
       </c>
       <c r="N20" t="inlineStr">
         <is>
@@ -1606,37 +1606,37 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>122.46</v>
+        <v>117.35</v>
       </c>
       <c r="D21" t="n">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="E21" t="n">
-        <v>52.48</v>
+        <v>46.12</v>
       </c>
       <c r="F21" t="n">
-        <v>1.65</v>
+        <v>2.02</v>
       </c>
       <c r="G21" t="n">
         <v>8.640000000000001</v>
       </c>
       <c r="H21" t="n">
-        <v>7.06</v>
+        <v>7.36</v>
       </c>
       <c r="I21" t="n">
-        <v>119</v>
+        <v>113.89</v>
       </c>
       <c r="J21" t="n">
-        <v>124.62</v>
+        <v>119.51</v>
       </c>
       <c r="K21" t="n">
-        <v>109.5</v>
+        <v>104.39</v>
       </c>
       <c r="L21" t="n">
-        <v>144.06</v>
+        <v>138.95</v>
       </c>
       <c r="M21" t="n">
-        <v>69.95999999999999</v>
+        <v>68.15000000000001</v>
       </c>
       <c r="N21" t="inlineStr">
         <is>
@@ -1657,46 +1657,46 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>ASML</t>
+          <t>IONQ</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Chips</t>
+          <t>Computación cuántica</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>1564.29</v>
+        <v>56.89</v>
       </c>
       <c r="D22" t="n">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="E22" t="n">
-        <v>12.85</v>
+        <v>24.35</v>
       </c>
       <c r="F22" t="n">
-        <v>0.92</v>
+        <v>1.47</v>
       </c>
       <c r="G22" t="n">
-        <v>61.22</v>
+        <v>4.3</v>
       </c>
       <c r="H22" t="n">
-        <v>3.91</v>
+        <v>7.56</v>
       </c>
       <c r="I22" t="n">
-        <v>1539.8</v>
+        <v>55.17</v>
       </c>
       <c r="J22" t="n">
-        <v>1579.6</v>
+        <v>57.97</v>
       </c>
       <c r="K22" t="n">
-        <v>1472.46</v>
+        <v>50.44</v>
       </c>
       <c r="L22" t="n">
-        <v>1717.35</v>
+        <v>67.64</v>
       </c>
       <c r="M22" t="n">
-        <v>59.9</v>
+        <v>65.56</v>
       </c>
       <c r="N22" t="inlineStr">
         <is>
@@ -1705,7 +1705,7 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -1717,46 +1717,46 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>AMAT</t>
+          <t>ASML</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Equipos chips</t>
+          <t>Chips</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>444.77</v>
+        <v>1565.81</v>
       </c>
       <c r="D23" t="n">
         <v>95</v>
       </c>
       <c r="E23" t="n">
-        <v>13.64</v>
+        <v>12.96</v>
       </c>
       <c r="F23" t="n">
-        <v>0.72</v>
+        <v>1.16</v>
       </c>
       <c r="G23" t="n">
-        <v>17.89</v>
+        <v>61.22</v>
       </c>
       <c r="H23" t="n">
-        <v>4.02</v>
+        <v>3.91</v>
       </c>
       <c r="I23" t="n">
-        <v>437.61</v>
+        <v>1541.32</v>
       </c>
       <c r="J23" t="n">
-        <v>449.24</v>
+        <v>1581.12</v>
       </c>
       <c r="K23" t="n">
-        <v>417.93</v>
+        <v>1473.98</v>
       </c>
       <c r="L23" t="n">
-        <v>489.5</v>
+        <v>1718.86</v>
       </c>
       <c r="M23" t="n">
-        <v>64.92</v>
+        <v>60.07</v>
       </c>
       <c r="N23" t="inlineStr">
         <is>
@@ -1777,7 +1777,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>LRCX</t>
+          <t>AMAT</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1786,37 +1786,37 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>295.9</v>
+        <v>443.62</v>
       </c>
       <c r="D24" t="n">
         <v>95</v>
       </c>
       <c r="E24" t="n">
-        <v>14.44</v>
+        <v>13.35</v>
       </c>
       <c r="F24" t="n">
-        <v>0.49</v>
+        <v>1.18</v>
       </c>
       <c r="G24" t="n">
-        <v>13.7</v>
+        <v>17.89</v>
       </c>
       <c r="H24" t="n">
-        <v>4.63</v>
+        <v>4.03</v>
       </c>
       <c r="I24" t="n">
-        <v>290.42</v>
+        <v>436.46</v>
       </c>
       <c r="J24" t="n">
-        <v>299.33</v>
+        <v>448.09</v>
       </c>
       <c r="K24" t="n">
-        <v>275.35</v>
+        <v>416.78</v>
       </c>
       <c r="L24" t="n">
-        <v>330.15</v>
+        <v>488.35</v>
       </c>
       <c r="M24" t="n">
-        <v>66.58</v>
+        <v>64.68000000000001</v>
       </c>
       <c r="N24" t="inlineStr">
         <is>
@@ -1837,46 +1837,46 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>LRCX</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Tecnología</t>
+          <t>Equipos chips</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>291.39</v>
+        <v>296.05</v>
       </c>
       <c r="D25" t="n">
-        <v>86</v>
+        <v>95</v>
       </c>
       <c r="E25" t="n">
-        <v>5.26</v>
+        <v>14.5</v>
       </c>
       <c r="F25" t="n">
-        <v>0.52</v>
+        <v>0.86</v>
       </c>
       <c r="G25" t="n">
-        <v>6.64</v>
+        <v>13.7</v>
       </c>
       <c r="H25" t="n">
-        <v>2.28</v>
+        <v>4.63</v>
       </c>
       <c r="I25" t="n">
-        <v>288.73</v>
+        <v>290.57</v>
       </c>
       <c r="J25" t="n">
-        <v>293.05</v>
+        <v>299.48</v>
       </c>
       <c r="K25" t="n">
-        <v>281.43</v>
+        <v>275.5</v>
       </c>
       <c r="L25" t="n">
-        <v>307.98</v>
+        <v>330.3</v>
       </c>
       <c r="M25" t="n">
-        <v>75.97</v>
+        <v>66.63</v>
       </c>
       <c r="N25" t="inlineStr">
         <is>
@@ -1897,46 +1897,46 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>IONQ</t>
+          <t>AAPL</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Computación cuántica</t>
+          <t>Tecnología</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>57.71</v>
+        <v>292.68</v>
       </c>
       <c r="D26" t="n">
         <v>86</v>
       </c>
       <c r="E26" t="n">
-        <v>26.14</v>
+        <v>5.73</v>
       </c>
       <c r="F26" t="n">
-        <v>1.14</v>
+        <v>0.8</v>
       </c>
       <c r="G26" t="n">
-        <v>4.3</v>
+        <v>6.64</v>
       </c>
       <c r="H26" t="n">
-        <v>7.45</v>
+        <v>2.27</v>
       </c>
       <c r="I26" t="n">
-        <v>55.99</v>
+        <v>290.02</v>
       </c>
       <c r="J26" t="n">
-        <v>58.79</v>
+        <v>294.34</v>
       </c>
       <c r="K26" t="n">
-        <v>51.26</v>
+        <v>282.72</v>
       </c>
       <c r="L26" t="n">
-        <v>68.45999999999999</v>
+        <v>309.27</v>
       </c>
       <c r="M26" t="n">
-        <v>66.37</v>
+        <v>78.04000000000001</v>
       </c>
       <c r="N26" t="inlineStr">
         <is>
@@ -1966,16 +1966,16 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>738.89</v>
+        <v>739.3</v>
       </c>
       <c r="D27" t="n">
         <v>82</v>
       </c>
       <c r="E27" t="n">
-        <v>2.91</v>
+        <v>2.97</v>
       </c>
       <c r="F27" t="n">
-        <v>0.63</v>
+        <v>0.85</v>
       </c>
       <c r="G27" t="n">
         <v>6.73</v>
@@ -1984,19 +1984,19 @@
         <v>0.91</v>
       </c>
       <c r="I27" t="n">
-        <v>736.2</v>
+        <v>736.61</v>
       </c>
       <c r="J27" t="n">
-        <v>740.5700000000001</v>
+        <v>740.98</v>
       </c>
       <c r="K27" t="n">
-        <v>728.79</v>
+        <v>729.2</v>
       </c>
       <c r="L27" t="n">
-        <v>755.72</v>
+        <v>756.13</v>
       </c>
       <c r="M27" t="n">
-        <v>80.38</v>
+        <v>80.52</v>
       </c>
       <c r="N27" t="inlineStr">
         <is>
@@ -2026,16 +2026,16 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>713.13</v>
+        <v>713.29</v>
       </c>
       <c r="D28" t="n">
         <v>82</v>
       </c>
       <c r="E28" t="n">
-        <v>5.98</v>
+        <v>6.01</v>
       </c>
       <c r="F28" t="n">
-        <v>0.68</v>
+        <v>0.88</v>
       </c>
       <c r="G28" t="n">
         <v>9.84</v>
@@ -2044,19 +2044,19 @@
         <v>1.38</v>
       </c>
       <c r="I28" t="n">
-        <v>709.1900000000001</v>
+        <v>709.35</v>
       </c>
       <c r="J28" t="n">
-        <v>715.59</v>
+        <v>715.75</v>
       </c>
       <c r="K28" t="n">
-        <v>698.36</v>
+        <v>698.52</v>
       </c>
       <c r="L28" t="n">
-        <v>737.74</v>
+        <v>737.9</v>
       </c>
       <c r="M28" t="n">
-        <v>86.7</v>
+        <v>86.72</v>
       </c>
       <c r="N28" t="inlineStr">
         <is>
@@ -2086,37 +2086,37 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>214.25</v>
+        <v>212.65</v>
       </c>
       <c r="D29" t="n">
         <v>80</v>
       </c>
       <c r="E29" t="n">
-        <v>5.41</v>
+        <v>4.62</v>
       </c>
       <c r="F29" t="n">
-        <v>0.79</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="G29" t="n">
         <v>18.49</v>
       </c>
       <c r="H29" t="n">
-        <v>8.630000000000001</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="I29" t="n">
-        <v>206.85</v>
+        <v>205.25</v>
       </c>
       <c r="J29" t="n">
-        <v>218.87</v>
+        <v>217.27</v>
       </c>
       <c r="K29" t="n">
-        <v>186.51</v>
+        <v>184.91</v>
       </c>
       <c r="L29" t="n">
-        <v>260.48</v>
+        <v>258.88</v>
       </c>
       <c r="M29" t="n">
-        <v>61.08</v>
+        <v>60.64</v>
       </c>
       <c r="N29" t="inlineStr">
         <is>
@@ -2146,16 +2146,16 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>532.89</v>
+        <v>532.76</v>
       </c>
       <c r="D30" t="n">
         <v>80</v>
       </c>
       <c r="E30" t="n">
-        <v>15.33</v>
+        <v>15.3</v>
       </c>
       <c r="F30" t="n">
-        <v>0.87</v>
+        <v>1.08</v>
       </c>
       <c r="G30" t="n">
         <v>17.4</v>
@@ -2164,19 +2164,19 @@
         <v>3.27</v>
       </c>
       <c r="I30" t="n">
-        <v>525.9299999999999</v>
+        <v>525.8</v>
       </c>
       <c r="J30" t="n">
-        <v>537.24</v>
+        <v>537.11</v>
       </c>
       <c r="K30" t="n">
-        <v>506.78</v>
+        <v>506.65</v>
       </c>
       <c r="L30" t="n">
-        <v>576.4</v>
+        <v>576.27</v>
       </c>
       <c r="M30" t="n">
-        <v>78.86</v>
+        <v>78.84999999999999</v>
       </c>
       <c r="N30" t="inlineStr">
         <is>
@@ -2206,37 +2206,37 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>810.64</v>
+        <v>795.33</v>
       </c>
       <c r="D31" t="n">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="E31" t="n">
-        <v>40.63</v>
+        <v>37.97</v>
       </c>
       <c r="F31" t="n">
-        <v>1.32</v>
+        <v>1.56</v>
       </c>
       <c r="G31" t="n">
         <v>45.86</v>
       </c>
       <c r="H31" t="n">
-        <v>5.66</v>
+        <v>5.77</v>
       </c>
       <c r="I31" t="n">
-        <v>792.29</v>
+        <v>776.98</v>
       </c>
       <c r="J31" t="n">
-        <v>822.11</v>
+        <v>806.8</v>
       </c>
       <c r="K31" t="n">
-        <v>741.84</v>
+        <v>726.53</v>
       </c>
       <c r="L31" t="n">
-        <v>925.3</v>
+        <v>909.99</v>
       </c>
       <c r="M31" t="n">
-        <v>89.63</v>
+        <v>89.27</v>
       </c>
       <c r="N31" t="inlineStr">
         <is>
@@ -2266,37 +2266,37 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>236.73</v>
+        <v>237.53</v>
       </c>
       <c r="D32" t="n">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="E32" t="n">
-        <v>40.59</v>
+        <v>41.07</v>
       </c>
       <c r="F32" t="n">
-        <v>1.39</v>
+        <v>1.73</v>
       </c>
       <c r="G32" t="n">
         <v>16.45</v>
       </c>
       <c r="H32" t="n">
-        <v>6.95</v>
+        <v>6.93</v>
       </c>
       <c r="I32" t="n">
-        <v>230.15</v>
+        <v>230.95</v>
       </c>
       <c r="J32" t="n">
-        <v>240.84</v>
+        <v>241.64</v>
       </c>
       <c r="K32" t="n">
-        <v>212.05</v>
+        <v>212.85</v>
       </c>
       <c r="L32" t="n">
-        <v>277.86</v>
+        <v>278.66</v>
       </c>
       <c r="M32" t="n">
-        <v>89.42</v>
+        <v>89.48</v>
       </c>
       <c r="N32" t="inlineStr">
         <is>
@@ -2326,37 +2326,37 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>390.91</v>
+        <v>388.64</v>
       </c>
       <c r="D33" t="n">
         <v>78</v>
       </c>
       <c r="E33" t="n">
-        <v>2</v>
+        <v>1.41</v>
       </c>
       <c r="F33" t="n">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
       <c r="G33" t="n">
-        <v>10.49</v>
+        <v>10.65</v>
       </c>
       <c r="H33" t="n">
-        <v>2.68</v>
+        <v>2.74</v>
       </c>
       <c r="I33" t="n">
-        <v>386.72</v>
+        <v>384.38</v>
       </c>
       <c r="J33" t="n">
-        <v>393.53</v>
+        <v>391.3</v>
       </c>
       <c r="K33" t="n">
-        <v>375.18</v>
+        <v>372.67</v>
       </c>
       <c r="L33" t="n">
-        <v>417.13</v>
+        <v>415.27</v>
       </c>
       <c r="M33" t="n">
-        <v>84.34</v>
+        <v>82.15000000000001</v>
       </c>
       <c r="N33" t="inlineStr">
         <is>
@@ -2382,37 +2382,37 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>34.3</v>
+        <v>33.52</v>
       </c>
       <c r="D34" t="n">
         <v>78</v>
       </c>
       <c r="E34" t="n">
-        <v>22.85</v>
+        <v>20.06</v>
       </c>
       <c r="F34" t="n">
-        <v>0.78</v>
+        <v>1.02</v>
       </c>
       <c r="G34" t="n">
-        <v>2.29</v>
+        <v>2.34</v>
       </c>
       <c r="H34" t="n">
-        <v>6.67</v>
+        <v>6.98</v>
       </c>
       <c r="I34" t="n">
-        <v>33.38</v>
+        <v>32.58</v>
       </c>
       <c r="J34" t="n">
-        <v>34.87</v>
+        <v>34.1</v>
       </c>
       <c r="K34" t="n">
-        <v>30.87</v>
+        <v>30.01</v>
       </c>
       <c r="L34" t="n">
-        <v>40.02</v>
+        <v>39.37</v>
       </c>
       <c r="M34" t="n">
-        <v>63.8</v>
+        <v>61.54</v>
       </c>
       <c r="N34" t="inlineStr">
         <is>
@@ -2429,46 +2429,46 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>TSLA</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>IA / Chips</t>
+          <t>Autos / Tech</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>464.83</v>
+        <v>445</v>
       </c>
       <c r="D35" t="n">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E35" t="n">
-        <v>36.1</v>
+        <v>13.37</v>
       </c>
       <c r="F35" t="n">
-        <v>0.78</v>
+        <v>1.17</v>
       </c>
       <c r="G35" t="n">
-        <v>27.39</v>
+        <v>15.49</v>
       </c>
       <c r="H35" t="n">
-        <v>5.89</v>
+        <v>3.48</v>
       </c>
       <c r="I35" t="n">
-        <v>453.87</v>
+        <v>438.81</v>
       </c>
       <c r="J35" t="n">
-        <v>471.67</v>
+        <v>448.87</v>
       </c>
       <c r="K35" t="n">
-        <v>423.74</v>
+        <v>421.77</v>
       </c>
       <c r="L35" t="n">
-        <v>533.3</v>
+        <v>483.72</v>
       </c>
       <c r="M35" t="n">
-        <v>80.73</v>
+        <v>78.11</v>
       </c>
       <c r="N35" t="inlineStr">
         <is>
@@ -2485,46 +2485,46 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>TSLA</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Autos / Tech</t>
+          <t>IA / Chips</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>446.8</v>
+        <v>458.79</v>
       </c>
       <c r="D36" t="n">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="E36" t="n">
-        <v>13.83</v>
+        <v>34.33</v>
       </c>
       <c r="F36" t="n">
-        <v>0.99</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="G36" t="n">
-        <v>15.37</v>
+        <v>27.39</v>
       </c>
       <c r="H36" t="n">
-        <v>3.44</v>
+        <v>5.97</v>
       </c>
       <c r="I36" t="n">
-        <v>440.65</v>
+        <v>447.83</v>
       </c>
       <c r="J36" t="n">
-        <v>450.64</v>
+        <v>465.64</v>
       </c>
       <c r="K36" t="n">
-        <v>423.74</v>
+        <v>417.71</v>
       </c>
       <c r="L36" t="n">
-        <v>485.24</v>
+        <v>527.26</v>
       </c>
       <c r="M36" t="n">
-        <v>78.48999999999999</v>
+        <v>80.33</v>
       </c>
       <c r="N36" t="inlineStr">
         <is>
@@ -2550,37 +2550,37 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>128</v>
+        <v>129.44</v>
       </c>
       <c r="D37" t="n">
         <v>64</v>
       </c>
       <c r="E37" t="n">
-        <v>33.64</v>
+        <v>35.14</v>
       </c>
       <c r="F37" t="n">
-        <v>0.95</v>
+        <v>1.18</v>
       </c>
       <c r="G37" t="n">
         <v>8.390000000000001</v>
       </c>
       <c r="H37" t="n">
-        <v>6.55</v>
+        <v>6.48</v>
       </c>
       <c r="I37" t="n">
-        <v>124.64</v>
+        <v>126.08</v>
       </c>
       <c r="J37" t="n">
-        <v>130.1</v>
+        <v>131.54</v>
       </c>
       <c r="K37" t="n">
-        <v>115.42</v>
+        <v>116.86</v>
       </c>
       <c r="L37" t="n">
-        <v>148.97</v>
+        <v>150.41</v>
       </c>
       <c r="M37" t="n">
-        <v>88.75</v>
+        <v>88.95</v>
       </c>
       <c r="N37" t="inlineStr">
         <is>

--- a/analisis_acciones.xlsx
+++ b/analisis_acciones.xlsx
@@ -501,46 +501,46 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>COIN</t>
+          <t>SOXX</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Cripto / Trading</t>
+          <t>ETF Chips</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>216.6</v>
+        <v>509.67</v>
       </c>
       <c r="D2" t="n">
         <v>95</v>
       </c>
       <c r="E2" t="n">
-        <v>6.7</v>
+        <v>5.58</v>
       </c>
       <c r="F2" t="n">
-        <v>1.31</v>
+        <v>1.72</v>
       </c>
       <c r="G2" t="n">
-        <v>12.22</v>
+        <v>19.23</v>
       </c>
       <c r="H2" t="n">
-        <v>5.64</v>
+        <v>3.77</v>
       </c>
       <c r="I2" t="n">
-        <v>211.71</v>
+        <v>501.98</v>
       </c>
       <c r="J2" t="n">
-        <v>219.65</v>
+        <v>514.48</v>
       </c>
       <c r="K2" t="n">
-        <v>198.27</v>
+        <v>480.82</v>
       </c>
       <c r="L2" t="n">
-        <v>247.14</v>
+        <v>557.75</v>
       </c>
       <c r="M2" t="n">
-        <v>61</v>
+        <v>68.88</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -561,50 +561,50 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>NVDA</t>
+          <t>ASML</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>IA / Chips</t>
+          <t>Chips</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>219.44</v>
+        <v>1508.08</v>
       </c>
       <c r="D3" t="n">
         <v>95</v>
       </c>
       <c r="E3" t="n">
-        <v>10.56</v>
+        <v>4.52</v>
       </c>
       <c r="F3" t="n">
-        <v>1.03</v>
+        <v>0.79</v>
       </c>
       <c r="G3" t="n">
-        <v>7.7</v>
+        <v>60.71</v>
       </c>
       <c r="H3" t="n">
-        <v>3.51</v>
+        <v>4.03</v>
       </c>
       <c r="I3" t="n">
-        <v>216.36</v>
+        <v>1483.8</v>
       </c>
       <c r="J3" t="n">
-        <v>221.36</v>
+        <v>1523.26</v>
       </c>
       <c r="K3" t="n">
-        <v>207.9</v>
+        <v>1417.02</v>
       </c>
       <c r="L3" t="n">
-        <v>238.68</v>
+        <v>1659.85</v>
       </c>
       <c r="M3" t="n">
-        <v>64.92</v>
+        <v>55.74</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>MEDIO</t>
+          <t>BAJO</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -621,46 +621,46 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AVGO</t>
+          <t>AMAT</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>IA / Chips</t>
+          <t>Equipos chips</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>428.43</v>
+        <v>427.8</v>
       </c>
       <c r="D4" t="n">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="E4" t="n">
-        <v>2.86</v>
+        <v>4.13</v>
       </c>
       <c r="F4" t="n">
-        <v>0.83</v>
+        <v>0.79</v>
       </c>
       <c r="G4" t="n">
-        <v>15.4</v>
+        <v>18.91</v>
       </c>
       <c r="H4" t="n">
-        <v>3.59</v>
+        <v>4.42</v>
       </c>
       <c r="I4" t="n">
-        <v>422.27</v>
+        <v>420.24</v>
       </c>
       <c r="J4" t="n">
-        <v>432.28</v>
+        <v>432.53</v>
       </c>
       <c r="K4" t="n">
-        <v>405.33</v>
+        <v>399.44</v>
       </c>
       <c r="L4" t="n">
-        <v>466.93</v>
+        <v>475.07</v>
       </c>
       <c r="M4" t="n">
-        <v>60.96</v>
+        <v>56.97</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -681,7 +681,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>KLAC</t>
+          <t>LRCX</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -690,37 +690,37 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1845.19</v>
+        <v>287.08</v>
       </c>
       <c r="D5" t="n">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="E5" t="n">
-        <v>7.7</v>
+        <v>4.09</v>
       </c>
       <c r="F5" t="n">
-        <v>1.16</v>
+        <v>0.53</v>
       </c>
       <c r="G5" t="n">
-        <v>83.20999999999999</v>
+        <v>14.39</v>
       </c>
       <c r="H5" t="n">
-        <v>4.51</v>
+        <v>5.01</v>
       </c>
       <c r="I5" t="n">
-        <v>1811.9</v>
+        <v>281.33</v>
       </c>
       <c r="J5" t="n">
-        <v>1865.99</v>
+        <v>290.68</v>
       </c>
       <c r="K5" t="n">
-        <v>1720.37</v>
+        <v>265.49</v>
       </c>
       <c r="L5" t="n">
-        <v>2053.23</v>
+        <v>323.07</v>
       </c>
       <c r="M5" t="n">
-        <v>54.45</v>
+        <v>59.36</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
@@ -741,46 +741,46 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AI</t>
+          <t>SLB</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>IA</t>
+          <t>Energía</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>9.48</v>
+        <v>56.19</v>
       </c>
       <c r="D6" t="n">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="E6" t="n">
-        <v>2.82</v>
+        <v>0.34</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9</v>
+        <v>0.48</v>
       </c>
       <c r="G6" t="n">
-        <v>0.43</v>
+        <v>1.65</v>
       </c>
       <c r="H6" t="n">
-        <v>4.57</v>
+        <v>2.94</v>
       </c>
       <c r="I6" t="n">
-        <v>9.31</v>
+        <v>55.53</v>
       </c>
       <c r="J6" t="n">
-        <v>9.59</v>
+        <v>56.6</v>
       </c>
       <c r="K6" t="n">
-        <v>8.83</v>
+        <v>53.71</v>
       </c>
       <c r="L6" t="n">
-        <v>10.56</v>
+        <v>60.32</v>
       </c>
       <c r="M6" t="n">
-        <v>54.55</v>
+        <v>57.5</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -801,50 +801,50 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>SPY</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Chips</t>
+          <t>ETF Mercado</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>404.54</v>
+        <v>736.9299999999999</v>
       </c>
       <c r="D7" t="n">
         <v>95</v>
       </c>
       <c r="E7" t="n">
-        <v>0.73</v>
+        <v>1.82</v>
       </c>
       <c r="F7" t="n">
-        <v>0.98</v>
+        <v>0.76</v>
       </c>
       <c r="G7" t="n">
-        <v>15.67</v>
+        <v>6.74</v>
       </c>
       <c r="H7" t="n">
-        <v>3.87</v>
+        <v>0.91</v>
       </c>
       <c r="I7" t="n">
-        <v>398.27</v>
+        <v>734.23</v>
       </c>
       <c r="J7" t="n">
-        <v>408.46</v>
+        <v>738.62</v>
       </c>
       <c r="K7" t="n">
-        <v>381.03</v>
+        <v>726.8200000000001</v>
       </c>
       <c r="L7" t="n">
-        <v>443.72</v>
+        <v>753.79</v>
       </c>
       <c r="M7" t="n">
-        <v>65.77</v>
+        <v>74.29000000000001</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>BAJO</t>
+          <t>MEDIO</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -861,46 +861,46 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SLB</t>
+          <t>TSM</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Energía</t>
+          <t>Chips</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>54.93</v>
+        <v>395.91</v>
       </c>
       <c r="D8" t="n">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.26</v>
+        <v>0.38</v>
       </c>
       <c r="F8" t="n">
-        <v>0.68</v>
+        <v>1.03</v>
       </c>
       <c r="G8" t="n">
-        <v>1.69</v>
+        <v>15.57</v>
       </c>
       <c r="H8" t="n">
-        <v>3.08</v>
+        <v>3.93</v>
       </c>
       <c r="I8" t="n">
-        <v>54.25</v>
+        <v>389.68</v>
       </c>
       <c r="J8" t="n">
-        <v>55.35</v>
+        <v>399.8</v>
       </c>
       <c r="K8" t="n">
-        <v>52.39</v>
+        <v>372.55</v>
       </c>
       <c r="L8" t="n">
-        <v>59.16</v>
+        <v>434.84</v>
       </c>
       <c r="M8" t="n">
-        <v>58.59</v>
+        <v>54.04</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
@@ -930,44 +930,48 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>268.99</v>
+        <v>265.05</v>
       </c>
       <c r="D9" t="n">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.12</v>
+        <v>-3.11</v>
       </c>
       <c r="F9" t="n">
-        <v>0.77</v>
+        <v>0.52</v>
       </c>
       <c r="G9" t="n">
-        <v>7.23</v>
+        <v>7.26</v>
       </c>
       <c r="H9" t="n">
-        <v>2.69</v>
+        <v>2.74</v>
       </c>
       <c r="I9" t="n">
-        <v>266.1</v>
+        <v>262.15</v>
       </c>
       <c r="J9" t="n">
-        <v>270.8</v>
+        <v>266.86</v>
       </c>
       <c r="K9" t="n">
-        <v>258.14</v>
+        <v>254.17</v>
       </c>
       <c r="L9" t="n">
-        <v>287.07</v>
+        <v>283.19</v>
       </c>
       <c r="M9" t="n">
-        <v>72.06</v>
+        <v>61.61</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>MEDIO</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr"/>
+          <t>BAJO</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>🔥</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>POSIBLE COMPRA</t>
@@ -977,53 +981,57 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SOUN</t>
+          <t>TSLA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>IA</t>
+          <t>Autos / Tech</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>8.449999999999999</v>
+        <v>432.46</v>
       </c>
       <c r="D10" t="n">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="E10" t="n">
-        <v>-10.77</v>
+        <v>11.07</v>
       </c>
       <c r="F10" t="n">
-        <v>0.97</v>
+        <v>0.78</v>
       </c>
       <c r="G10" t="n">
-        <v>0.65</v>
+        <v>16.76</v>
       </c>
       <c r="H10" t="n">
-        <v>7.65</v>
+        <v>3.88</v>
       </c>
       <c r="I10" t="n">
-        <v>8.19</v>
+        <v>425.76</v>
       </c>
       <c r="J10" t="n">
-        <v>8.609999999999999</v>
+        <v>436.66</v>
       </c>
       <c r="K10" t="n">
-        <v>7.48</v>
+        <v>407.32</v>
       </c>
       <c r="L10" t="n">
-        <v>10.07</v>
+        <v>474.37</v>
       </c>
       <c r="M10" t="n">
-        <v>55.4</v>
+        <v>69.44</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
           <t>MEDIO</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr"/>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>🔥</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>POSIBLE COMPRA</t>
@@ -1033,50 +1041,50 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>HOOD</t>
+          <t>KLAC</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Trading</t>
+          <t>Equipos chips</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>80.78</v>
+        <v>1779.93</v>
       </c>
       <c r="D11" t="n">
-        <v>54</v>
+        <v>72</v>
       </c>
       <c r="E11" t="n">
-        <v>5.53</v>
+        <v>2.71</v>
       </c>
       <c r="F11" t="n">
-        <v>0.74</v>
+        <v>0.64</v>
       </c>
       <c r="G11" t="n">
-        <v>4.22</v>
+        <v>87.83</v>
       </c>
       <c r="H11" t="n">
-        <v>5.23</v>
+        <v>4.93</v>
       </c>
       <c r="I11" t="n">
-        <v>79.09</v>
+        <v>1744.8</v>
       </c>
       <c r="J11" t="n">
-        <v>81.84</v>
+        <v>1801.89</v>
       </c>
       <c r="K11" t="n">
-        <v>74.45</v>
+        <v>1648.18</v>
       </c>
       <c r="L11" t="n">
-        <v>91.33</v>
+        <v>1999.52</v>
       </c>
       <c r="M11" t="n">
-        <v>42.3</v>
+        <v>47.74</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>MEDIO</t>
+          <t>BAJO</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1086,60 +1094,64 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>NO COMPRAR</t>
+          <t>VIGILAR</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>XOM</t>
+          <t>COIN</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Energía</t>
+          <t>Cripto / Trading</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>149.68</v>
+        <v>204.79</v>
       </c>
       <c r="D12" t="n">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.61</v>
+        <v>3.56</v>
       </c>
       <c r="F12" t="n">
-        <v>0.82</v>
+        <v>0.71</v>
       </c>
       <c r="G12" t="n">
-        <v>4.05</v>
+        <v>12.37</v>
       </c>
       <c r="H12" t="n">
-        <v>2.71</v>
+        <v>6.04</v>
       </c>
       <c r="I12" t="n">
-        <v>148.06</v>
+        <v>199.84</v>
       </c>
       <c r="J12" t="n">
-        <v>150.69</v>
+        <v>207.88</v>
       </c>
       <c r="K12" t="n">
-        <v>143.61</v>
+        <v>186.23</v>
       </c>
       <c r="L12" t="n">
-        <v>159.8</v>
+        <v>235.73</v>
       </c>
       <c r="M12" t="n">
-        <v>52.17</v>
+        <v>49.24</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>BAJO</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr"/>
+          <t>MEDIO</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>🔥</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>VIGILAR</t>
@@ -1149,46 +1161,46 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>XOM</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Tecnología</t>
+          <t>Energía</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>412.66</v>
+        <v>151.27</v>
       </c>
       <c r="D13" t="n">
-        <v>54</v>
+        <v>74</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.23</v>
+        <v>-2.33</v>
       </c>
       <c r="F13" t="n">
-        <v>0.96</v>
+        <v>0.58</v>
       </c>
       <c r="G13" t="n">
-        <v>11.8</v>
+        <v>4.02</v>
       </c>
       <c r="H13" t="n">
-        <v>2.86</v>
+        <v>2.66</v>
       </c>
       <c r="I13" t="n">
-        <v>407.94</v>
+        <v>149.67</v>
       </c>
       <c r="J13" t="n">
-        <v>415.61</v>
+        <v>152.28</v>
       </c>
       <c r="K13" t="n">
-        <v>394.96</v>
+        <v>145.24</v>
       </c>
       <c r="L13" t="n">
-        <v>442.16</v>
+        <v>161.33</v>
       </c>
       <c r="M13" t="n">
-        <v>43.47</v>
+        <v>52.87</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
@@ -1198,53 +1210,53 @@
       <c r="O13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>NO COMPRAR</t>
+          <t>VIGILAR</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>CVX</t>
+          <t>AVGO</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Energía</t>
+          <t>IA / Chips</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>184.74</v>
+        <v>415.84</v>
       </c>
       <c r="D14" t="n">
-        <v>54</v>
+        <v>72</v>
       </c>
       <c r="E14" t="n">
-        <v>-3.92</v>
+        <v>-2.7</v>
       </c>
       <c r="F14" t="n">
-        <v>1.16</v>
+        <v>0.65</v>
       </c>
       <c r="G14" t="n">
-        <v>4.61</v>
+        <v>15.39</v>
       </c>
       <c r="H14" t="n">
-        <v>2.49</v>
+        <v>3.7</v>
       </c>
       <c r="I14" t="n">
-        <v>182.9</v>
+        <v>409.68</v>
       </c>
       <c r="J14" t="n">
-        <v>185.89</v>
+        <v>419.69</v>
       </c>
       <c r="K14" t="n">
-        <v>177.83</v>
+        <v>392.75</v>
       </c>
       <c r="L14" t="n">
-        <v>196.26</v>
+        <v>454.32</v>
       </c>
       <c r="M14" t="n">
-        <v>48.05</v>
+        <v>46.96</v>
       </c>
       <c r="N14" t="inlineStr">
         <is>
@@ -1254,14 +1266,14 @@
       <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>NO COMPRAR</t>
+          <t>VIGILAR</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>OXY</t>
+          <t>CVX</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1270,37 +1282,37 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>55.14</v>
+        <v>186.4</v>
       </c>
       <c r="D15" t="n">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="E15" t="n">
-        <v>-8.51</v>
+        <v>-3.24</v>
       </c>
       <c r="F15" t="n">
-        <v>1.04</v>
+        <v>0.45</v>
       </c>
       <c r="G15" t="n">
-        <v>1.85</v>
+        <v>4.52</v>
       </c>
       <c r="H15" t="n">
-        <v>3.36</v>
+        <v>2.43</v>
       </c>
       <c r="I15" t="n">
-        <v>54.4</v>
+        <v>184.59</v>
       </c>
       <c r="J15" t="n">
-        <v>55.6</v>
+        <v>187.53</v>
       </c>
       <c r="K15" t="n">
-        <v>52.36</v>
+        <v>179.62</v>
       </c>
       <c r="L15" t="n">
-        <v>59.76</v>
+        <v>197.71</v>
       </c>
       <c r="M15" t="n">
-        <v>46.84</v>
+        <v>50.12</v>
       </c>
       <c r="N15" t="inlineStr">
         <is>
@@ -1310,57 +1322,57 @@
       <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>NO COMPRAR</t>
+          <t>VIGILAR</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>META</t>
+          <t>AI</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Tecnología</t>
+          <t>IA</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>598.86</v>
+        <v>8.82</v>
       </c>
       <c r="D16" t="n">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="E16" t="n">
-        <v>-1.89</v>
+        <v>-6.27</v>
       </c>
       <c r="F16" t="n">
-        <v>0.92</v>
+        <v>1</v>
       </c>
       <c r="G16" t="n">
-        <v>18.32</v>
+        <v>0.47</v>
       </c>
       <c r="H16" t="n">
-        <v>3.06</v>
+        <v>5.27</v>
       </c>
       <c r="I16" t="n">
-        <v>591.53</v>
+        <v>8.630000000000001</v>
       </c>
       <c r="J16" t="n">
-        <v>603.4400000000001</v>
+        <v>8.94</v>
       </c>
       <c r="K16" t="n">
-        <v>571.38</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="L16" t="n">
-        <v>644.67</v>
+        <v>9.98</v>
       </c>
       <c r="M16" t="n">
-        <v>26.31</v>
+        <v>41.97</v>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>BAJO</t>
+          <t>MEDIO</t>
         </is>
       </c>
       <c r="O16" t="inlineStr"/>
@@ -1373,50 +1385,50 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>SOFI</t>
+          <t>OXY</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Fintech</t>
+          <t>Energía</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>16.26</v>
+        <v>56.31</v>
       </c>
       <c r="D17" t="n">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="E17" t="n">
-        <v>0.37</v>
+        <v>-5.11</v>
       </c>
       <c r="F17" t="n">
-        <v>1</v>
+        <v>0.55</v>
       </c>
       <c r="G17" t="n">
-        <v>0.82</v>
+        <v>1.88</v>
       </c>
       <c r="H17" t="n">
-        <v>5.02</v>
+        <v>3.33</v>
       </c>
       <c r="I17" t="n">
-        <v>15.93</v>
+        <v>55.56</v>
       </c>
       <c r="J17" t="n">
-        <v>16.46</v>
+        <v>56.78</v>
       </c>
       <c r="K17" t="n">
-        <v>15.04</v>
+        <v>53.49</v>
       </c>
       <c r="L17" t="n">
-        <v>18.3</v>
+        <v>61</v>
       </c>
       <c r="M17" t="n">
-        <v>32.4</v>
+        <v>48.08</v>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>MEDIO</t>
+          <t>BAJO</t>
         </is>
       </c>
       <c r="O17" t="inlineStr"/>
@@ -1429,46 +1441,46 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>PYPL</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Pagos</t>
+          <t>Tecnología</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>45.07</v>
+        <v>408.36</v>
       </c>
       <c r="D18" t="n">
         <v>46</v>
       </c>
       <c r="E18" t="n">
-        <v>-10.56</v>
+        <v>-0.73</v>
       </c>
       <c r="F18" t="n">
-        <v>1.12</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="G18" t="n">
-        <v>1.56</v>
+        <v>11.72</v>
       </c>
       <c r="H18" t="n">
-        <v>3.46</v>
+        <v>2.87</v>
       </c>
       <c r="I18" t="n">
-        <v>44.45</v>
+        <v>403.67</v>
       </c>
       <c r="J18" t="n">
-        <v>45.46</v>
+        <v>411.29</v>
       </c>
       <c r="K18" t="n">
-        <v>42.73</v>
+        <v>390.78</v>
       </c>
       <c r="L18" t="n">
-        <v>48.97</v>
+        <v>437.65</v>
       </c>
       <c r="M18" t="n">
-        <v>23.95</v>
+        <v>35.32</v>
       </c>
       <c r="N18" t="inlineStr">
         <is>
@@ -1485,46 +1497,46 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>PLTR</t>
+          <t>META</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>IA / Software</t>
+          <t>Tecnología</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>136.89</v>
+        <v>601.4</v>
       </c>
       <c r="D19" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="E19" t="n">
-        <v>-6.26</v>
+        <v>-0.59</v>
       </c>
       <c r="F19" t="n">
-        <v>0.89</v>
+        <v>0.52</v>
       </c>
       <c r="G19" t="n">
-        <v>6.24</v>
+        <v>18.43</v>
       </c>
       <c r="H19" t="n">
-        <v>4.56</v>
+        <v>3.07</v>
       </c>
       <c r="I19" t="n">
-        <v>134.39</v>
+        <v>594.03</v>
       </c>
       <c r="J19" t="n">
-        <v>138.45</v>
+        <v>606.01</v>
       </c>
       <c r="K19" t="n">
-        <v>127.53</v>
+        <v>573.75</v>
       </c>
       <c r="L19" t="n">
-        <v>152.49</v>
+        <v>647.48</v>
       </c>
       <c r="M19" t="n">
-        <v>40.84</v>
+        <v>24.61</v>
       </c>
       <c r="N19" t="inlineStr">
         <is>
@@ -1541,46 +1553,46 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>UPST</t>
+          <t>HOOD</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Fintech IA</t>
+          <t>Trading</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>28.69</v>
+        <v>77.69</v>
       </c>
       <c r="D20" t="n">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="E20" t="n">
-        <v>-10.57</v>
+        <v>0.86</v>
       </c>
       <c r="F20" t="n">
-        <v>0.74</v>
+        <v>0.42</v>
       </c>
       <c r="G20" t="n">
-        <v>1.81</v>
+        <v>4.26</v>
       </c>
       <c r="H20" t="n">
-        <v>6.31</v>
+        <v>5.49</v>
       </c>
       <c r="I20" t="n">
-        <v>27.97</v>
+        <v>75.98</v>
       </c>
       <c r="J20" t="n">
-        <v>29.14</v>
+        <v>78.76000000000001</v>
       </c>
       <c r="K20" t="n">
-        <v>25.97</v>
+        <v>71.29000000000001</v>
       </c>
       <c r="L20" t="n">
-        <v>33.22</v>
+        <v>88.34999999999999</v>
       </c>
       <c r="M20" t="n">
-        <v>33.95</v>
+        <v>35.79</v>
       </c>
       <c r="N20" t="inlineStr">
         <is>
@@ -1597,286 +1609,270 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>RKLB</t>
+          <t>PYPL</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Espacial</t>
+          <t>Pagos</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>117.35</v>
+        <v>45.56</v>
       </c>
       <c r="D21" t="n">
-        <v>93</v>
+        <v>46</v>
       </c>
       <c r="E21" t="n">
-        <v>46.12</v>
+        <v>-2.01</v>
       </c>
       <c r="F21" t="n">
-        <v>2.02</v>
+        <v>1.17</v>
       </c>
       <c r="G21" t="n">
-        <v>8.640000000000001</v>
+        <v>1.61</v>
       </c>
       <c r="H21" t="n">
-        <v>7.36</v>
+        <v>3.53</v>
       </c>
       <c r="I21" t="n">
-        <v>113.89</v>
+        <v>44.91</v>
       </c>
       <c r="J21" t="n">
-        <v>119.51</v>
+        <v>45.96</v>
       </c>
       <c r="K21" t="n">
-        <v>104.39</v>
+        <v>43.14</v>
       </c>
       <c r="L21" t="n">
-        <v>138.95</v>
+        <v>49.57</v>
       </c>
       <c r="M21" t="n">
-        <v>68.15000000000001</v>
+        <v>24.92</v>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>ALTO</t>
-        </is>
-      </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>🔥🔥</t>
-        </is>
-      </c>
+          <t>BAJO</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>VIGILAR</t>
+          <t>NO COMPRAR</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>IONQ</t>
+          <t>SOFI</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Computación cuántica</t>
+          <t>Fintech</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>56.89</v>
+        <v>15.77</v>
       </c>
       <c r="D22" t="n">
-        <v>85</v>
+        <v>38</v>
       </c>
       <c r="E22" t="n">
-        <v>24.35</v>
+        <v>-1.57</v>
       </c>
       <c r="F22" t="n">
-        <v>1.47</v>
+        <v>0.76</v>
       </c>
       <c r="G22" t="n">
-        <v>4.3</v>
+        <v>0.83</v>
       </c>
       <c r="H22" t="n">
-        <v>7.56</v>
+        <v>5.25</v>
       </c>
       <c r="I22" t="n">
-        <v>55.17</v>
+        <v>15.44</v>
       </c>
       <c r="J22" t="n">
-        <v>57.97</v>
+        <v>15.98</v>
       </c>
       <c r="K22" t="n">
-        <v>50.44</v>
+        <v>14.53</v>
       </c>
       <c r="L22" t="n">
-        <v>67.64</v>
+        <v>17.84</v>
       </c>
       <c r="M22" t="n">
-        <v>65.56</v>
+        <v>28.24</v>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>ALTO</t>
-        </is>
-      </c>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t>🔥🔥</t>
-        </is>
-      </c>
+          <t>MEDIO</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>VIGILAR</t>
+          <t>NO COMPRAR</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>ASML</t>
+          <t>UPST</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Chips</t>
+          <t>Fintech IA</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>1565.81</v>
+        <v>27.87</v>
       </c>
       <c r="D23" t="n">
-        <v>95</v>
+        <v>38</v>
       </c>
       <c r="E23" t="n">
-        <v>12.96</v>
+        <v>-10.59</v>
       </c>
       <c r="F23" t="n">
-        <v>1.16</v>
+        <v>0.5</v>
       </c>
       <c r="G23" t="n">
-        <v>61.22</v>
+        <v>1.76</v>
       </c>
       <c r="H23" t="n">
-        <v>3.91</v>
+        <v>6.33</v>
       </c>
       <c r="I23" t="n">
-        <v>1541.32</v>
+        <v>27.16</v>
       </c>
       <c r="J23" t="n">
-        <v>1581.12</v>
+        <v>28.31</v>
       </c>
       <c r="K23" t="n">
-        <v>1473.98</v>
+        <v>25.22</v>
       </c>
       <c r="L23" t="n">
-        <v>1718.86</v>
+        <v>32.28</v>
       </c>
       <c r="M23" t="n">
-        <v>60.07</v>
+        <v>24.23</v>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>ALTO</t>
-        </is>
-      </c>
-      <c r="O23" t="inlineStr">
-        <is>
-          <t>🔥</t>
-        </is>
-      </c>
+          <t>MEDIO</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>VIGILAR</t>
+          <t>NO COMPRAR</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>AMAT</t>
+          <t>PLTR</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Equipos chips</t>
+          <t>IA / Software</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>443.62</v>
+        <v>133.98</v>
       </c>
       <c r="D24" t="n">
-        <v>95</v>
+        <v>36</v>
       </c>
       <c r="E24" t="n">
-        <v>13.35</v>
+        <v>-1.42</v>
       </c>
       <c r="F24" t="n">
-        <v>1.18</v>
+        <v>0.65</v>
       </c>
       <c r="G24" t="n">
-        <v>17.89</v>
+        <v>6.04</v>
       </c>
       <c r="H24" t="n">
-        <v>4.03</v>
+        <v>4.51</v>
       </c>
       <c r="I24" t="n">
-        <v>436.46</v>
+        <v>131.56</v>
       </c>
       <c r="J24" t="n">
-        <v>448.09</v>
+        <v>135.49</v>
       </c>
       <c r="K24" t="n">
-        <v>416.78</v>
+        <v>124.91</v>
       </c>
       <c r="L24" t="n">
-        <v>488.35</v>
+        <v>149.09</v>
       </c>
       <c r="M24" t="n">
-        <v>64.68000000000001</v>
+        <v>29.67</v>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>ALTO</t>
-        </is>
-      </c>
-      <c r="O24" t="inlineStr">
-        <is>
-          <t>🔥</t>
-        </is>
-      </c>
+          <t>BAJO</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>VIGILAR</t>
+          <t>NO COMPRAR</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>LRCX</t>
+          <t>NVDA</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Equipos chips</t>
+          <t>IA / Chips</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>296.05</v>
+        <v>220.52</v>
       </c>
       <c r="D25" t="n">
         <v>95</v>
       </c>
       <c r="E25" t="n">
-        <v>14.5</v>
+        <v>12.22</v>
       </c>
       <c r="F25" t="n">
-        <v>0.86</v>
+        <v>0.84</v>
       </c>
       <c r="G25" t="n">
-        <v>13.7</v>
+        <v>8.08</v>
       </c>
       <c r="H25" t="n">
-        <v>4.63</v>
+        <v>3.66</v>
       </c>
       <c r="I25" t="n">
-        <v>290.57</v>
+        <v>217.29</v>
       </c>
       <c r="J25" t="n">
-        <v>299.48</v>
+        <v>222.54</v>
       </c>
       <c r="K25" t="n">
-        <v>275.5</v>
+        <v>208.41</v>
       </c>
       <c r="L25" t="n">
-        <v>330.3</v>
+        <v>240.71</v>
       </c>
       <c r="M25" t="n">
-        <v>66.63</v>
+        <v>64.06999999999999</v>
       </c>
       <c r="N25" t="inlineStr">
         <is>
@@ -1897,46 +1893,46 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>RKLB</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Tecnología</t>
+          <t>Espacial</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>292.68</v>
+        <v>118.74</v>
       </c>
       <c r="D26" t="n">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="E26" t="n">
-        <v>5.73</v>
+        <v>50.76</v>
       </c>
       <c r="F26" t="n">
-        <v>0.8</v>
+        <v>1.05</v>
       </c>
       <c r="G26" t="n">
-        <v>6.64</v>
+        <v>8.81</v>
       </c>
       <c r="H26" t="n">
-        <v>2.27</v>
+        <v>7.42</v>
       </c>
       <c r="I26" t="n">
-        <v>290.02</v>
+        <v>115.21</v>
       </c>
       <c r="J26" t="n">
-        <v>294.34</v>
+        <v>120.94</v>
       </c>
       <c r="K26" t="n">
-        <v>282.72</v>
+        <v>105.53</v>
       </c>
       <c r="L26" t="n">
-        <v>309.27</v>
+        <v>140.75</v>
       </c>
       <c r="M26" t="n">
-        <v>78.04000000000001</v>
+        <v>67.37</v>
       </c>
       <c r="N26" t="inlineStr">
         <is>
@@ -1957,46 +1953,46 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>SPY</t>
+          <t>AAPL</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>ETF Mercado</t>
+          <t>Tecnología</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>739.3</v>
+        <v>294.38</v>
       </c>
       <c r="D27" t="n">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="E27" t="n">
-        <v>2.97</v>
+        <v>3.68</v>
       </c>
       <c r="F27" t="n">
-        <v>0.85</v>
+        <v>0.57</v>
       </c>
       <c r="G27" t="n">
-        <v>6.73</v>
+        <v>6.25</v>
       </c>
       <c r="H27" t="n">
-        <v>0.91</v>
+        <v>2.12</v>
       </c>
       <c r="I27" t="n">
-        <v>736.61</v>
+        <v>291.88</v>
       </c>
       <c r="J27" t="n">
-        <v>740.98</v>
+        <v>295.94</v>
       </c>
       <c r="K27" t="n">
-        <v>729.2</v>
+        <v>285</v>
       </c>
       <c r="L27" t="n">
-        <v>756.13</v>
+        <v>310.02</v>
       </c>
       <c r="M27" t="n">
-        <v>80.52</v>
+        <v>75.76000000000001</v>
       </c>
       <c r="N27" t="inlineStr">
         <is>
@@ -2026,37 +2022,37 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>713.29</v>
+        <v>703.9</v>
       </c>
       <c r="D28" t="n">
         <v>82</v>
       </c>
       <c r="E28" t="n">
-        <v>6.01</v>
+        <v>3.27</v>
       </c>
       <c r="F28" t="n">
-        <v>0.88</v>
+        <v>0.92</v>
       </c>
       <c r="G28" t="n">
-        <v>9.84</v>
+        <v>10.25</v>
       </c>
       <c r="H28" t="n">
-        <v>1.38</v>
+        <v>1.46</v>
       </c>
       <c r="I28" t="n">
-        <v>709.35</v>
+        <v>699.8</v>
       </c>
       <c r="J28" t="n">
-        <v>715.75</v>
+        <v>706.46</v>
       </c>
       <c r="K28" t="n">
-        <v>698.52</v>
+        <v>688.53</v>
       </c>
       <c r="L28" t="n">
-        <v>737.9</v>
+        <v>729.52</v>
       </c>
       <c r="M28" t="n">
-        <v>86.72</v>
+        <v>76.37</v>
       </c>
       <c r="N28" t="inlineStr">
         <is>
@@ -2077,46 +2073,46 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>ARM</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Chips</t>
+          <t>IA / Chips</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>212.65</v>
+        <v>439.85</v>
       </c>
       <c r="D29" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E29" t="n">
-        <v>4.62</v>
+        <v>23.81</v>
       </c>
       <c r="F29" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.68</v>
       </c>
       <c r="G29" t="n">
-        <v>18.49</v>
+        <v>28.31</v>
       </c>
       <c r="H29" t="n">
-        <v>8.699999999999999</v>
+        <v>6.44</v>
       </c>
       <c r="I29" t="n">
-        <v>205.25</v>
+        <v>428.53</v>
       </c>
       <c r="J29" t="n">
-        <v>217.27</v>
+        <v>446.93</v>
       </c>
       <c r="K29" t="n">
-        <v>184.91</v>
+        <v>397.39</v>
       </c>
       <c r="L29" t="n">
-        <v>258.88</v>
+        <v>510.63</v>
       </c>
       <c r="M29" t="n">
-        <v>60.64</v>
+        <v>73.73999999999999</v>
       </c>
       <c r="N29" t="inlineStr">
         <is>
@@ -2137,46 +2133,46 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>SOXX</t>
+          <t>MU</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>ETF Chips</t>
+          <t>Memoria / Chips</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>532.76</v>
+        <v>749.3200000000001</v>
       </c>
       <c r="D30" t="n">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="E30" t="n">
-        <v>15.3</v>
+        <v>17.05</v>
       </c>
       <c r="F30" t="n">
-        <v>1.08</v>
+        <v>1.41</v>
       </c>
       <c r="G30" t="n">
-        <v>17.4</v>
+        <v>49.16</v>
       </c>
       <c r="H30" t="n">
-        <v>3.27</v>
+        <v>6.56</v>
       </c>
       <c r="I30" t="n">
-        <v>525.8</v>
+        <v>729.66</v>
       </c>
       <c r="J30" t="n">
-        <v>537.11</v>
+        <v>761.61</v>
       </c>
       <c r="K30" t="n">
-        <v>506.65</v>
+        <v>675.59</v>
       </c>
       <c r="L30" t="n">
-        <v>576.27</v>
+        <v>872.22</v>
       </c>
       <c r="M30" t="n">
-        <v>78.84999999999999</v>
+        <v>79.19</v>
       </c>
       <c r="N30" t="inlineStr">
         <is>
@@ -2197,57 +2193,53 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>MU</t>
+          <t>SMCI</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Memoria / Chips</t>
+          <t>Servidores IA</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>795.33</v>
+        <v>32.45</v>
       </c>
       <c r="D31" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="E31" t="n">
-        <v>37.97</v>
+        <v>16.6</v>
       </c>
       <c r="F31" t="n">
-        <v>1.56</v>
+        <v>0.72</v>
       </c>
       <c r="G31" t="n">
-        <v>45.86</v>
+        <v>2.43</v>
       </c>
       <c r="H31" t="n">
-        <v>5.77</v>
+        <v>7.49</v>
       </c>
       <c r="I31" t="n">
-        <v>776.98</v>
+        <v>31.48</v>
       </c>
       <c r="J31" t="n">
-        <v>806.8</v>
+        <v>33.06</v>
       </c>
       <c r="K31" t="n">
-        <v>726.53</v>
+        <v>28.81</v>
       </c>
       <c r="L31" t="n">
-        <v>909.99</v>
+        <v>38.52</v>
       </c>
       <c r="M31" t="n">
-        <v>89.27</v>
+        <v>57.31</v>
       </c>
       <c r="N31" t="inlineStr">
         <is>
           <t>ALTO</t>
         </is>
       </c>
-      <c r="O31" t="inlineStr">
-        <is>
-          <t>🔥</t>
-        </is>
-      </c>
+      <c r="O31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>VIGILAR</t>
@@ -2257,57 +2249,53 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>QCOM</t>
+          <t>IONQ</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Chips</t>
+          <t>Computación cuántica</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>237.53</v>
+        <v>54.74</v>
       </c>
       <c r="D32" t="n">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="E32" t="n">
-        <v>41.07</v>
+        <v>14.04</v>
       </c>
       <c r="F32" t="n">
-        <v>1.73</v>
+        <v>0.92</v>
       </c>
       <c r="G32" t="n">
-        <v>16.45</v>
+        <v>4.6</v>
       </c>
       <c r="H32" t="n">
-        <v>6.93</v>
+        <v>8.4</v>
       </c>
       <c r="I32" t="n">
-        <v>230.95</v>
+        <v>52.9</v>
       </c>
       <c r="J32" t="n">
-        <v>241.64</v>
+        <v>55.89</v>
       </c>
       <c r="K32" t="n">
-        <v>212.85</v>
+        <v>47.84</v>
       </c>
       <c r="L32" t="n">
-        <v>278.66</v>
+        <v>66.23</v>
       </c>
       <c r="M32" t="n">
-        <v>89.48</v>
+        <v>60.49</v>
       </c>
       <c r="N32" t="inlineStr">
         <is>
           <t>ALTO</t>
         </is>
       </c>
-      <c r="O32" t="inlineStr">
-        <is>
-          <t>🔥</t>
-        </is>
-      </c>
+      <c r="O32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>VIGILAR</t>
@@ -2317,46 +2305,46 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>GOOGL</t>
+          <t>ARM</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Tecnología</t>
+          <t>Chips</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>388.64</v>
+        <v>205.02</v>
       </c>
       <c r="D33" t="n">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="E33" t="n">
-        <v>1.41</v>
+        <v>-1.83</v>
       </c>
       <c r="F33" t="n">
-        <v>1.1</v>
+        <v>0.59</v>
       </c>
       <c r="G33" t="n">
-        <v>10.65</v>
+        <v>18.09</v>
       </c>
       <c r="H33" t="n">
-        <v>2.74</v>
+        <v>8.83</v>
       </c>
       <c r="I33" t="n">
-        <v>384.38</v>
+        <v>197.78</v>
       </c>
       <c r="J33" t="n">
-        <v>391.3</v>
+        <v>209.54</v>
       </c>
       <c r="K33" t="n">
-        <v>372.67</v>
+        <v>177.88</v>
       </c>
       <c r="L33" t="n">
-        <v>415.27</v>
+        <v>250.25</v>
       </c>
       <c r="M33" t="n">
-        <v>82.15000000000001</v>
+        <v>52.62</v>
       </c>
       <c r="N33" t="inlineStr">
         <is>
@@ -2373,46 +2361,46 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>SMCI</t>
+          <t>GOOGL</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Servidores IA</t>
+          <t>Tecnología</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>33.52</v>
+        <v>385.93</v>
       </c>
       <c r="D34" t="n">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="E34" t="n">
-        <v>20.06</v>
+        <v>-0.64</v>
       </c>
       <c r="F34" t="n">
-        <v>1.02</v>
+        <v>0.6</v>
       </c>
       <c r="G34" t="n">
-        <v>2.34</v>
+        <v>10.53</v>
       </c>
       <c r="H34" t="n">
-        <v>6.98</v>
+        <v>2.73</v>
       </c>
       <c r="I34" t="n">
-        <v>32.58</v>
+        <v>381.72</v>
       </c>
       <c r="J34" t="n">
-        <v>34.1</v>
+        <v>388.56</v>
       </c>
       <c r="K34" t="n">
-        <v>30.01</v>
+        <v>370.13</v>
       </c>
       <c r="L34" t="n">
-        <v>39.37</v>
+        <v>412.26</v>
       </c>
       <c r="M34" t="n">
-        <v>61.54</v>
+        <v>77.97</v>
       </c>
       <c r="N34" t="inlineStr">
         <is>
@@ -2429,46 +2417,46 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>TSLA</t>
+          <t>QCOM</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Autos / Tech</t>
+          <t>Chips</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>445</v>
+        <v>208.97</v>
       </c>
       <c r="D35" t="n">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="E35" t="n">
-        <v>13.37</v>
+        <v>12.02</v>
       </c>
       <c r="F35" t="n">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="G35" t="n">
-        <v>15.49</v>
+        <v>18.85</v>
       </c>
       <c r="H35" t="n">
-        <v>3.48</v>
+        <v>9.02</v>
       </c>
       <c r="I35" t="n">
-        <v>438.81</v>
+        <v>201.43</v>
       </c>
       <c r="J35" t="n">
-        <v>448.87</v>
+        <v>213.68</v>
       </c>
       <c r="K35" t="n">
-        <v>421.77</v>
+        <v>180.7</v>
       </c>
       <c r="L35" t="n">
-        <v>483.72</v>
+        <v>256.1</v>
       </c>
       <c r="M35" t="n">
-        <v>78.11</v>
+        <v>73.19</v>
       </c>
       <c r="N35" t="inlineStr">
         <is>
@@ -2485,46 +2473,46 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>INTC</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>IA / Chips</t>
+          <t>Chips</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>458.79</v>
+        <v>118.52</v>
       </c>
       <c r="D36" t="n">
         <v>64</v>
       </c>
       <c r="E36" t="n">
-        <v>34.33</v>
+        <v>9.59</v>
       </c>
       <c r="F36" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.96</v>
       </c>
       <c r="G36" t="n">
-        <v>27.39</v>
+        <v>9.15</v>
       </c>
       <c r="H36" t="n">
-        <v>5.97</v>
+        <v>7.72</v>
       </c>
       <c r="I36" t="n">
-        <v>447.83</v>
+        <v>114.86</v>
       </c>
       <c r="J36" t="n">
-        <v>465.64</v>
+        <v>120.81</v>
       </c>
       <c r="K36" t="n">
-        <v>417.71</v>
+        <v>104.8</v>
       </c>
       <c r="L36" t="n">
-        <v>527.26</v>
+        <v>141.39</v>
       </c>
       <c r="M36" t="n">
-        <v>80.33</v>
+        <v>79.25</v>
       </c>
       <c r="N36" t="inlineStr">
         <is>
@@ -2541,46 +2529,46 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>INTC</t>
+          <t>SOUN</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Chips</t>
+          <t>IA</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>129.44</v>
+        <v>7.99</v>
       </c>
       <c r="D37" t="n">
-        <v>64</v>
+        <v>42</v>
       </c>
       <c r="E37" t="n">
-        <v>35.14</v>
+        <v>-12.58</v>
       </c>
       <c r="F37" t="n">
-        <v>1.18</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="G37" t="n">
-        <v>8.390000000000001</v>
+        <v>0.65</v>
       </c>
       <c r="H37" t="n">
-        <v>6.48</v>
+        <v>8.1</v>
       </c>
       <c r="I37" t="n">
-        <v>126.08</v>
+        <v>7.73</v>
       </c>
       <c r="J37" t="n">
-        <v>131.54</v>
+        <v>8.15</v>
       </c>
       <c r="K37" t="n">
-        <v>116.86</v>
+        <v>7.02</v>
       </c>
       <c r="L37" t="n">
-        <v>150.41</v>
+        <v>9.609999999999999</v>
       </c>
       <c r="M37" t="n">
-        <v>88.95</v>
+        <v>47.96</v>
       </c>
       <c r="N37" t="inlineStr">
         <is>
@@ -2590,7 +2578,7 @@
       <c r="O37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>VIGILAR</t>
+          <t>NO COMPRAR</t>
         </is>
       </c>
     </row>

--- a/analisis_acciones.xlsx
+++ b/analisis_acciones.xlsx
@@ -501,46 +501,46 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>SOXX</t>
+          <t>NVDA</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>ETF Chips</t>
+          <t>IA / Chips</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>509.67</v>
+        <v>226.59</v>
       </c>
       <c r="D2" t="n">
         <v>95</v>
       </c>
       <c r="E2" t="n">
-        <v>5.58</v>
+        <v>9.029999999999999</v>
       </c>
       <c r="F2" t="n">
-        <v>1.72</v>
+        <v>0.8</v>
       </c>
       <c r="G2" t="n">
-        <v>19.23</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="H2" t="n">
-        <v>3.77</v>
+        <v>3.58</v>
       </c>
       <c r="I2" t="n">
-        <v>501.98</v>
+        <v>223.35</v>
       </c>
       <c r="J2" t="n">
-        <v>514.48</v>
+        <v>228.62</v>
       </c>
       <c r="K2" t="n">
-        <v>480.82</v>
+        <v>214.43</v>
       </c>
       <c r="L2" t="n">
-        <v>557.75</v>
+        <v>246.86</v>
       </c>
       <c r="M2" t="n">
-        <v>68.88</v>
+        <v>70.04000000000001</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -549,7 +549,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥🔥</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -570,37 +570,37 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1508.08</v>
+        <v>1580.47</v>
       </c>
       <c r="D3" t="n">
         <v>95</v>
       </c>
       <c r="E3" t="n">
-        <v>4.52</v>
+        <v>2.31</v>
       </c>
       <c r="F3" t="n">
-        <v>0.79</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="G3" t="n">
-        <v>60.71</v>
+        <v>62.71</v>
       </c>
       <c r="H3" t="n">
-        <v>4.03</v>
+        <v>3.97</v>
       </c>
       <c r="I3" t="n">
-        <v>1483.8</v>
+        <v>1555.39</v>
       </c>
       <c r="J3" t="n">
-        <v>1523.26</v>
+        <v>1596.15</v>
       </c>
       <c r="K3" t="n">
-        <v>1417.02</v>
+        <v>1486.41</v>
       </c>
       <c r="L3" t="n">
-        <v>1659.85</v>
+        <v>1737.24</v>
       </c>
       <c r="M3" t="n">
-        <v>55.74</v>
+        <v>63.59</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -630,37 +630,37 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>427.8</v>
+        <v>437.23</v>
       </c>
       <c r="D4" t="n">
         <v>95</v>
       </c>
       <c r="E4" t="n">
-        <v>4.13</v>
+        <v>2.01</v>
       </c>
       <c r="F4" t="n">
-        <v>0.79</v>
+        <v>0.62</v>
       </c>
       <c r="G4" t="n">
-        <v>18.91</v>
+        <v>19.02</v>
       </c>
       <c r="H4" t="n">
-        <v>4.42</v>
+        <v>4.35</v>
       </c>
       <c r="I4" t="n">
-        <v>420.24</v>
+        <v>429.62</v>
       </c>
       <c r="J4" t="n">
-        <v>432.53</v>
+        <v>441.98</v>
       </c>
       <c r="K4" t="n">
-        <v>399.44</v>
+        <v>408.71</v>
       </c>
       <c r="L4" t="n">
-        <v>475.07</v>
+        <v>484.77</v>
       </c>
       <c r="M4" t="n">
-        <v>56.97</v>
+        <v>59.42</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -681,46 +681,46 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>LRCX</t>
+          <t>SOXX</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Equipos chips</t>
+          <t>ETF Chips</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>287.08</v>
+        <v>530.0700000000001</v>
       </c>
       <c r="D5" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E5" t="n">
-        <v>4.09</v>
+        <v>4.58</v>
       </c>
       <c r="F5" t="n">
-        <v>0.53</v>
+        <v>0.82</v>
       </c>
       <c r="G5" t="n">
-        <v>14.39</v>
+        <v>19.33</v>
       </c>
       <c r="H5" t="n">
-        <v>5.01</v>
+        <v>3.65</v>
       </c>
       <c r="I5" t="n">
-        <v>281.33</v>
+        <v>522.34</v>
       </c>
       <c r="J5" t="n">
-        <v>290.68</v>
+        <v>534.9</v>
       </c>
       <c r="K5" t="n">
-        <v>265.49</v>
+        <v>501.07</v>
       </c>
       <c r="L5" t="n">
-        <v>323.07</v>
+        <v>578.41</v>
       </c>
       <c r="M5" t="n">
-        <v>59.36</v>
+        <v>71.75</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
@@ -741,46 +741,46 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SLB</t>
+          <t>KLAC</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Energía</t>
+          <t>Equipos chips</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>56.19</v>
+        <v>1859.29</v>
       </c>
       <c r="D6" t="n">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="E6" t="n">
-        <v>0.34</v>
+        <v>2.37</v>
       </c>
       <c r="F6" t="n">
-        <v>0.48</v>
+        <v>0.51</v>
       </c>
       <c r="G6" t="n">
-        <v>1.65</v>
+        <v>88.45</v>
       </c>
       <c r="H6" t="n">
-        <v>2.94</v>
+        <v>4.76</v>
       </c>
       <c r="I6" t="n">
-        <v>55.53</v>
+        <v>1823.91</v>
       </c>
       <c r="J6" t="n">
-        <v>56.6</v>
+        <v>1881.4</v>
       </c>
       <c r="K6" t="n">
-        <v>53.71</v>
+        <v>1726.61</v>
       </c>
       <c r="L6" t="n">
-        <v>60.32</v>
+        <v>2080.42</v>
       </c>
       <c r="M6" t="n">
-        <v>57.5</v>
+        <v>53.03</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -801,46 +801,46 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SPY</t>
+          <t>COIN</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ETF Mercado</t>
+          <t>Cripto / Trading</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>736.9299999999999</v>
+        <v>202.08</v>
       </c>
       <c r="D7" t="n">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="E7" t="n">
-        <v>1.82</v>
+        <v>2.08</v>
       </c>
       <c r="F7" t="n">
-        <v>0.76</v>
+        <v>0.62</v>
       </c>
       <c r="G7" t="n">
-        <v>6.74</v>
+        <v>12.22</v>
       </c>
       <c r="H7" t="n">
-        <v>0.91</v>
+        <v>6.05</v>
       </c>
       <c r="I7" t="n">
-        <v>734.23</v>
+        <v>197.19</v>
       </c>
       <c r="J7" t="n">
-        <v>738.62</v>
+        <v>205.13</v>
       </c>
       <c r="K7" t="n">
-        <v>726.8200000000001</v>
+        <v>183.75</v>
       </c>
       <c r="L7" t="n">
-        <v>753.79</v>
+        <v>232.63</v>
       </c>
       <c r="M7" t="n">
-        <v>74.29000000000001</v>
+        <v>52.31</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -849,7 +849,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -861,46 +861,46 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>LRCX</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Chips</t>
+          <t>Equipos chips</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>395.91</v>
+        <v>297.34</v>
       </c>
       <c r="D8" t="n">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="E8" t="n">
-        <v>0.38</v>
+        <v>0.06</v>
       </c>
       <c r="F8" t="n">
-        <v>1.03</v>
+        <v>0.45</v>
       </c>
       <c r="G8" t="n">
-        <v>15.57</v>
+        <v>13.84</v>
       </c>
       <c r="H8" t="n">
-        <v>3.93</v>
+        <v>4.65</v>
       </c>
       <c r="I8" t="n">
-        <v>389.68</v>
+        <v>291.8</v>
       </c>
       <c r="J8" t="n">
-        <v>399.8</v>
+        <v>300.8</v>
       </c>
       <c r="K8" t="n">
-        <v>372.55</v>
+        <v>276.58</v>
       </c>
       <c r="L8" t="n">
-        <v>434.84</v>
+        <v>331.94</v>
       </c>
       <c r="M8" t="n">
-        <v>54.04</v>
+        <v>67</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
@@ -921,46 +921,46 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>AMZN</t>
+          <t>XOM</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Tecnología</t>
+          <t>Energía</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>265.05</v>
+        <v>151.4</v>
       </c>
       <c r="D9" t="n">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.11</v>
+        <v>1.82</v>
       </c>
       <c r="F9" t="n">
-        <v>0.52</v>
+        <v>0.43</v>
       </c>
       <c r="G9" t="n">
-        <v>7.26</v>
+        <v>3.98</v>
       </c>
       <c r="H9" t="n">
-        <v>2.74</v>
+        <v>2.63</v>
       </c>
       <c r="I9" t="n">
-        <v>262.15</v>
+        <v>149.8</v>
       </c>
       <c r="J9" t="n">
-        <v>266.86</v>
+        <v>152.39</v>
       </c>
       <c r="K9" t="n">
-        <v>254.17</v>
+        <v>145.43</v>
       </c>
       <c r="L9" t="n">
-        <v>283.19</v>
+        <v>161.34</v>
       </c>
       <c r="M9" t="n">
-        <v>61.61</v>
+        <v>51.44</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
@@ -981,50 +981,50 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>TSLA</t>
+          <t>SLB</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Autos / Tech</t>
+          <t>Energía</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>432.46</v>
+        <v>55.54</v>
       </c>
       <c r="D10" t="n">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="E10" t="n">
-        <v>11.07</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="F10" t="n">
-        <v>0.78</v>
+        <v>0.37</v>
       </c>
       <c r="G10" t="n">
-        <v>16.76</v>
+        <v>1.65</v>
       </c>
       <c r="H10" t="n">
-        <v>3.88</v>
+        <v>2.98</v>
       </c>
       <c r="I10" t="n">
-        <v>425.76</v>
+        <v>54.88</v>
       </c>
       <c r="J10" t="n">
-        <v>436.66</v>
+        <v>55.95</v>
       </c>
       <c r="K10" t="n">
-        <v>407.32</v>
+        <v>53.06</v>
       </c>
       <c r="L10" t="n">
-        <v>474.37</v>
+        <v>59.67</v>
       </c>
       <c r="M10" t="n">
-        <v>69.44</v>
+        <v>53.5</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>MEDIO</t>
+          <t>BAJO</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1041,46 +1041,46 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>KLAC</t>
+          <t>AMZN</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Equipos chips</t>
+          <t>Tecnología</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1779.93</v>
+        <v>269.49</v>
       </c>
       <c r="D11" t="n">
-        <v>72</v>
+        <v>84</v>
       </c>
       <c r="E11" t="n">
-        <v>2.71</v>
+        <v>-2</v>
       </c>
       <c r="F11" t="n">
-        <v>0.64</v>
+        <v>0.57</v>
       </c>
       <c r="G11" t="n">
-        <v>87.83</v>
+        <v>7.36</v>
       </c>
       <c r="H11" t="n">
-        <v>4.93</v>
+        <v>2.73</v>
       </c>
       <c r="I11" t="n">
-        <v>1744.8</v>
+        <v>266.55</v>
       </c>
       <c r="J11" t="n">
-        <v>1801.89</v>
+        <v>271.33</v>
       </c>
       <c r="K11" t="n">
-        <v>1648.18</v>
+        <v>258.45</v>
       </c>
       <c r="L11" t="n">
-        <v>1999.52</v>
+        <v>287.9</v>
       </c>
       <c r="M11" t="n">
-        <v>47.74</v>
+        <v>66.25</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
@@ -1094,57 +1094,57 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>VIGILAR</t>
+          <t>POSIBLE COMPRA</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>COIN</t>
+          <t>TSM</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Cripto / Trading</t>
+          <t>Chips</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>204.79</v>
+        <v>400.82</v>
       </c>
       <c r="D12" t="n">
-        <v>72</v>
+        <v>84</v>
       </c>
       <c r="E12" t="n">
-        <v>3.56</v>
+        <v>-4.45</v>
       </c>
       <c r="F12" t="n">
-        <v>0.71</v>
+        <v>0.68</v>
       </c>
       <c r="G12" t="n">
-        <v>12.37</v>
+        <v>15.59</v>
       </c>
       <c r="H12" t="n">
-        <v>6.04</v>
+        <v>3.89</v>
       </c>
       <c r="I12" t="n">
-        <v>199.84</v>
+        <v>394.58</v>
       </c>
       <c r="J12" t="n">
-        <v>207.88</v>
+        <v>404.71</v>
       </c>
       <c r="K12" t="n">
-        <v>186.23</v>
+        <v>377.43</v>
       </c>
       <c r="L12" t="n">
-        <v>235.73</v>
+        <v>439.79</v>
       </c>
       <c r="M12" t="n">
-        <v>49.24</v>
+        <v>58.88</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>MEDIO</t>
+          <t>BAJO</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -1154,63 +1154,63 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>VIGILAR</t>
+          <t>POSIBLE COMPRA</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>XOM</t>
+          <t>SMCI</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Energía</t>
+          <t>Servidores IA</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>151.27</v>
+        <v>32.2</v>
       </c>
       <c r="D13" t="n">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.33</v>
+        <v>-7.1</v>
       </c>
       <c r="F13" t="n">
-        <v>0.58</v>
+        <v>0.51</v>
       </c>
       <c r="G13" t="n">
-        <v>4.02</v>
+        <v>2.29</v>
       </c>
       <c r="H13" t="n">
-        <v>2.66</v>
+        <v>7.12</v>
       </c>
       <c r="I13" t="n">
-        <v>149.67</v>
+        <v>31.28</v>
       </c>
       <c r="J13" t="n">
-        <v>152.28</v>
+        <v>32.77</v>
       </c>
       <c r="K13" t="n">
-        <v>145.24</v>
+        <v>28.76</v>
       </c>
       <c r="L13" t="n">
-        <v>161.33</v>
+        <v>37.93</v>
       </c>
       <c r="M13" t="n">
-        <v>52.87</v>
+        <v>63.5</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>BAJO</t>
+          <t>MEDIO</t>
         </is>
       </c>
       <c r="O13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>VIGILAR</t>
+          <t>POSIBLE COMPRA</t>
         </is>
       </c>
     </row>
@@ -1226,37 +1226,37 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>415.84</v>
+        <v>418.32</v>
       </c>
       <c r="D14" t="n">
         <v>72</v>
       </c>
       <c r="E14" t="n">
-        <v>-2.7</v>
+        <v>-1.67</v>
       </c>
       <c r="F14" t="n">
-        <v>0.65</v>
+        <v>0.59</v>
       </c>
       <c r="G14" t="n">
-        <v>15.39</v>
+        <v>15.61</v>
       </c>
       <c r="H14" t="n">
-        <v>3.7</v>
+        <v>3.73</v>
       </c>
       <c r="I14" t="n">
-        <v>409.68</v>
+        <v>412.08</v>
       </c>
       <c r="J14" t="n">
-        <v>419.69</v>
+        <v>422.22</v>
       </c>
       <c r="K14" t="n">
-        <v>392.75</v>
+        <v>394.91</v>
       </c>
       <c r="L14" t="n">
-        <v>454.32</v>
+        <v>457.33</v>
       </c>
       <c r="M14" t="n">
-        <v>46.96</v>
+        <v>49.24</v>
       </c>
       <c r="N14" t="inlineStr">
         <is>
@@ -1273,46 +1273,46 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>CVX</t>
+          <t>AI</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Energía</t>
+          <t>IA</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>186.4</v>
+        <v>8.69</v>
       </c>
       <c r="D15" t="n">
         <v>66</v>
       </c>
       <c r="E15" t="n">
-        <v>-3.24</v>
+        <v>-9.529999999999999</v>
       </c>
       <c r="F15" t="n">
-        <v>0.45</v>
+        <v>0.65</v>
       </c>
       <c r="G15" t="n">
-        <v>4.52</v>
+        <v>0.43</v>
       </c>
       <c r="H15" t="n">
-        <v>2.43</v>
+        <v>4.91</v>
       </c>
       <c r="I15" t="n">
-        <v>184.59</v>
+        <v>8.51</v>
       </c>
       <c r="J15" t="n">
-        <v>187.53</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="K15" t="n">
-        <v>179.62</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="L15" t="n">
-        <v>197.71</v>
+        <v>9.75</v>
       </c>
       <c r="M15" t="n">
-        <v>50.12</v>
+        <v>52.56</v>
       </c>
       <c r="N15" t="inlineStr">
         <is>
@@ -1329,56 +1329,56 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>AI</t>
+          <t>CVX</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>IA</t>
+          <t>Energía</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>8.82</v>
+        <v>185.47</v>
       </c>
       <c r="D16" t="n">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="E16" t="n">
-        <v>-6.27</v>
+        <v>0.17</v>
       </c>
       <c r="F16" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="G16" t="n">
-        <v>0.47</v>
+        <v>4.46</v>
       </c>
       <c r="H16" t="n">
-        <v>5.27</v>
+        <v>2.4</v>
       </c>
       <c r="I16" t="n">
-        <v>8.630000000000001</v>
+        <v>183.69</v>
       </c>
       <c r="J16" t="n">
-        <v>8.94</v>
+        <v>186.58</v>
       </c>
       <c r="K16" t="n">
-        <v>8.119999999999999</v>
+        <v>178.78</v>
       </c>
       <c r="L16" t="n">
-        <v>9.98</v>
+        <v>196.62</v>
       </c>
       <c r="M16" t="n">
-        <v>41.97</v>
+        <v>46.66</v>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>MEDIO</t>
+          <t>BAJO</t>
         </is>
       </c>
       <c r="O16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>NO COMPRAR</t>
+          <t>VIGILAR</t>
         </is>
       </c>
     </row>
@@ -1394,37 +1394,37 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>56.31</v>
+        <v>56.17</v>
       </c>
       <c r="D17" t="n">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="E17" t="n">
-        <v>-5.11</v>
+        <v>1.9</v>
       </c>
       <c r="F17" t="n">
-        <v>0.55</v>
+        <v>0.36</v>
       </c>
       <c r="G17" t="n">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="H17" t="n">
-        <v>3.33</v>
+        <v>3.3</v>
       </c>
       <c r="I17" t="n">
-        <v>55.56</v>
+        <v>55.43</v>
       </c>
       <c r="J17" t="n">
-        <v>56.78</v>
+        <v>56.63</v>
       </c>
       <c r="K17" t="n">
-        <v>53.49</v>
+        <v>53.39</v>
       </c>
       <c r="L17" t="n">
-        <v>61</v>
+        <v>60.8</v>
       </c>
       <c r="M17" t="n">
-        <v>48.08</v>
+        <v>45.52</v>
       </c>
       <c r="N17" t="inlineStr">
         <is>
@@ -1434,57 +1434,57 @@
       <c r="O17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>NO COMPRAR</t>
+          <t>VIGILAR</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>SOUN</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Tecnología</t>
+          <t>IA</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>408.36</v>
+        <v>8.44</v>
       </c>
       <c r="D18" t="n">
-        <v>46</v>
+        <v>58</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.73</v>
+        <v>-9.93</v>
       </c>
       <c r="F18" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.64</v>
       </c>
       <c r="G18" t="n">
-        <v>11.72</v>
+        <v>0.66</v>
       </c>
       <c r="H18" t="n">
-        <v>2.87</v>
+        <v>7.83</v>
       </c>
       <c r="I18" t="n">
-        <v>403.67</v>
+        <v>8.18</v>
       </c>
       <c r="J18" t="n">
-        <v>411.29</v>
+        <v>8.609999999999999</v>
       </c>
       <c r="K18" t="n">
-        <v>390.78</v>
+        <v>7.45</v>
       </c>
       <c r="L18" t="n">
-        <v>437.65</v>
+        <v>10.09</v>
       </c>
       <c r="M18" t="n">
-        <v>35.32</v>
+        <v>55.58</v>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>BAJO</t>
+          <t>MEDIO</t>
         </is>
       </c>
       <c r="O18" t="inlineStr"/>
@@ -1497,7 +1497,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>META</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1506,37 +1506,37 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>601.4</v>
+        <v>404.81</v>
       </c>
       <c r="D19" t="n">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.59</v>
+        <v>-2.21</v>
       </c>
       <c r="F19" t="n">
         <v>0.52</v>
       </c>
       <c r="G19" t="n">
-        <v>18.43</v>
+        <v>10.66</v>
       </c>
       <c r="H19" t="n">
-        <v>3.07</v>
+        <v>2.63</v>
       </c>
       <c r="I19" t="n">
-        <v>594.03</v>
+        <v>400.54</v>
       </c>
       <c r="J19" t="n">
-        <v>606.01</v>
+        <v>407.48</v>
       </c>
       <c r="K19" t="n">
-        <v>573.75</v>
+        <v>388.82</v>
       </c>
       <c r="L19" t="n">
-        <v>647.48</v>
+        <v>431.47</v>
       </c>
       <c r="M19" t="n">
-        <v>24.61</v>
+        <v>42.19</v>
       </c>
       <c r="N19" t="inlineStr">
         <is>
@@ -1553,50 +1553,50 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>HOOD</t>
+          <t>META</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Trading</t>
+          <t>Tecnología</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>77.69</v>
+        <v>616.34</v>
       </c>
       <c r="D20" t="n">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="E20" t="n">
-        <v>0.86</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="F20" t="n">
-        <v>0.42</v>
+        <v>0.7</v>
       </c>
       <c r="G20" t="n">
-        <v>4.26</v>
+        <v>18.55</v>
       </c>
       <c r="H20" t="n">
-        <v>5.49</v>
+        <v>3.01</v>
       </c>
       <c r="I20" t="n">
-        <v>75.98</v>
+        <v>608.92</v>
       </c>
       <c r="J20" t="n">
-        <v>78.76000000000001</v>
+        <v>620.98</v>
       </c>
       <c r="K20" t="n">
-        <v>71.29000000000001</v>
+        <v>588.52</v>
       </c>
       <c r="L20" t="n">
-        <v>88.34999999999999</v>
+        <v>662.71</v>
       </c>
       <c r="M20" t="n">
-        <v>35.79</v>
+        <v>35.11</v>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>MEDIO</t>
+          <t>BAJO</t>
         </is>
       </c>
       <c r="O20" t="inlineStr"/>
@@ -1609,50 +1609,50 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>PYPL</t>
+          <t>HOOD</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Pagos</t>
+          <t>Trading</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>45.56</v>
+        <v>76.87</v>
       </c>
       <c r="D21" t="n">
         <v>46</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.01</v>
+        <v>-2.76</v>
       </c>
       <c r="F21" t="n">
-        <v>1.17</v>
+        <v>0.39</v>
       </c>
       <c r="G21" t="n">
-        <v>1.61</v>
+        <v>4</v>
       </c>
       <c r="H21" t="n">
-        <v>3.53</v>
+        <v>5.2</v>
       </c>
       <c r="I21" t="n">
-        <v>44.91</v>
+        <v>75.27</v>
       </c>
       <c r="J21" t="n">
-        <v>45.96</v>
+        <v>77.87</v>
       </c>
       <c r="K21" t="n">
-        <v>43.14</v>
+        <v>70.88</v>
       </c>
       <c r="L21" t="n">
-        <v>49.57</v>
+        <v>86.86</v>
       </c>
       <c r="M21" t="n">
-        <v>24.92</v>
+        <v>40.11</v>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>BAJO</t>
+          <t>MEDIO</t>
         </is>
       </c>
       <c r="O21" t="inlineStr"/>
@@ -1665,50 +1665,50 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>SOFI</t>
+          <t>PYPL</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Fintech</t>
+          <t>Pagos</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>15.77</v>
+        <v>45.57</v>
       </c>
       <c r="D22" t="n">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.57</v>
+        <v>-1.51</v>
       </c>
       <c r="F22" t="n">
-        <v>0.76</v>
+        <v>0.72</v>
       </c>
       <c r="G22" t="n">
-        <v>0.83</v>
+        <v>1.54</v>
       </c>
       <c r="H22" t="n">
-        <v>5.25</v>
+        <v>3.39</v>
       </c>
       <c r="I22" t="n">
-        <v>15.44</v>
+        <v>44.95</v>
       </c>
       <c r="J22" t="n">
-        <v>15.98</v>
+        <v>45.96</v>
       </c>
       <c r="K22" t="n">
-        <v>14.53</v>
+        <v>43.25</v>
       </c>
       <c r="L22" t="n">
-        <v>17.84</v>
+        <v>49.43</v>
       </c>
       <c r="M22" t="n">
-        <v>28.24</v>
+        <v>28.76</v>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>MEDIO</t>
+          <t>BAJO</t>
         </is>
       </c>
       <c r="O22" t="inlineStr"/>
@@ -1721,46 +1721,46 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>UPST</t>
+          <t>SOFI</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Fintech IA</t>
+          <t>Fintech</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>27.87</v>
+        <v>15.39</v>
       </c>
       <c r="D23" t="n">
         <v>38</v>
       </c>
       <c r="E23" t="n">
-        <v>-10.59</v>
+        <v>-5.61</v>
       </c>
       <c r="F23" t="n">
-        <v>0.5</v>
+        <v>0.72</v>
       </c>
       <c r="G23" t="n">
-        <v>1.76</v>
+        <v>0.8</v>
       </c>
       <c r="H23" t="n">
-        <v>6.33</v>
+        <v>5.17</v>
       </c>
       <c r="I23" t="n">
-        <v>27.16</v>
+        <v>15.07</v>
       </c>
       <c r="J23" t="n">
-        <v>28.31</v>
+        <v>15.58</v>
       </c>
       <c r="K23" t="n">
-        <v>25.22</v>
+        <v>14.19</v>
       </c>
       <c r="L23" t="n">
-        <v>32.28</v>
+        <v>17.37</v>
       </c>
       <c r="M23" t="n">
-        <v>24.23</v>
+        <v>29.63</v>
       </c>
       <c r="N23" t="inlineStr">
         <is>
@@ -1777,50 +1777,50 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>PLTR</t>
+          <t>UPST</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>IA / Software</t>
+          <t>Fintech IA</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>133.98</v>
+        <v>26.85</v>
       </c>
       <c r="D24" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.42</v>
+        <v>-6.43</v>
       </c>
       <c r="F24" t="n">
-        <v>0.65</v>
+        <v>0.73</v>
       </c>
       <c r="G24" t="n">
-        <v>6.04</v>
+        <v>1.68</v>
       </c>
       <c r="H24" t="n">
-        <v>4.51</v>
+        <v>6.27</v>
       </c>
       <c r="I24" t="n">
-        <v>131.56</v>
+        <v>26.18</v>
       </c>
       <c r="J24" t="n">
-        <v>135.49</v>
+        <v>27.28</v>
       </c>
       <c r="K24" t="n">
-        <v>124.91</v>
+        <v>24.33</v>
       </c>
       <c r="L24" t="n">
-        <v>149.09</v>
+        <v>31.06</v>
       </c>
       <c r="M24" t="n">
-        <v>29.67</v>
+        <v>26</v>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>BAJO</t>
+          <t>MEDIO</t>
         </is>
       </c>
       <c r="O24" t="inlineStr"/>
@@ -1833,60 +1833,56 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>NVDA</t>
+          <t>PLTR</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>IA / Chips</t>
+          <t>IA / Software</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>220.52</v>
+        <v>130.12</v>
       </c>
       <c r="D25" t="n">
-        <v>95</v>
+        <v>36</v>
       </c>
       <c r="E25" t="n">
-        <v>12.22</v>
+        <v>-2.74</v>
       </c>
       <c r="F25" t="n">
-        <v>0.84</v>
+        <v>1.02</v>
       </c>
       <c r="G25" t="n">
-        <v>8.08</v>
+        <v>5.73</v>
       </c>
       <c r="H25" t="n">
-        <v>3.66</v>
+        <v>4.4</v>
       </c>
       <c r="I25" t="n">
-        <v>217.29</v>
+        <v>127.83</v>
       </c>
       <c r="J25" t="n">
-        <v>222.54</v>
+        <v>131.55</v>
       </c>
       <c r="K25" t="n">
-        <v>208.41</v>
+        <v>121.53</v>
       </c>
       <c r="L25" t="n">
-        <v>240.71</v>
+        <v>144.44</v>
       </c>
       <c r="M25" t="n">
-        <v>64.06999999999999</v>
+        <v>35.19</v>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>ALTO</t>
-        </is>
-      </c>
-      <c r="O25" t="inlineStr">
-        <is>
-          <t>🔥</t>
-        </is>
-      </c>
+          <t>BAJO</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>VIGILAR</t>
+          <t>NO COMPRAR</t>
         </is>
       </c>
     </row>
@@ -1902,37 +1898,37 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>118.74</v>
+        <v>126.77</v>
       </c>
       <c r="D26" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E26" t="n">
-        <v>50.76</v>
+        <v>49.76</v>
       </c>
       <c r="F26" t="n">
-        <v>1.05</v>
+        <v>0.83</v>
       </c>
       <c r="G26" t="n">
-        <v>8.81</v>
+        <v>8.94</v>
       </c>
       <c r="H26" t="n">
-        <v>7.42</v>
+        <v>7.05</v>
       </c>
       <c r="I26" t="n">
-        <v>115.21</v>
+        <v>123.19</v>
       </c>
       <c r="J26" t="n">
-        <v>120.94</v>
+        <v>129.01</v>
       </c>
       <c r="K26" t="n">
-        <v>105.53</v>
+        <v>113.36</v>
       </c>
       <c r="L26" t="n">
-        <v>140.75</v>
+        <v>149.12</v>
       </c>
       <c r="M26" t="n">
-        <v>67.37</v>
+        <v>74.75</v>
       </c>
       <c r="N26" t="inlineStr">
         <is>
@@ -1962,37 +1958,37 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>294.38</v>
+        <v>298.7</v>
       </c>
       <c r="D27" t="n">
         <v>86</v>
       </c>
       <c r="E27" t="n">
-        <v>3.68</v>
+        <v>3.99</v>
       </c>
       <c r="F27" t="n">
-        <v>0.57</v>
+        <v>0.71</v>
       </c>
       <c r="G27" t="n">
-        <v>6.25</v>
+        <v>6.52</v>
       </c>
       <c r="H27" t="n">
-        <v>2.12</v>
+        <v>2.18</v>
       </c>
       <c r="I27" t="n">
-        <v>291.88</v>
+        <v>296.09</v>
       </c>
       <c r="J27" t="n">
-        <v>295.94</v>
+        <v>300.33</v>
       </c>
       <c r="K27" t="n">
-        <v>285</v>
+        <v>288.92</v>
       </c>
       <c r="L27" t="n">
-        <v>310.02</v>
+        <v>314.99</v>
       </c>
       <c r="M27" t="n">
-        <v>75.76000000000001</v>
+        <v>77.91</v>
       </c>
       <c r="N27" t="inlineStr">
         <is>
@@ -2022,37 +2018,37 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>703.9</v>
+        <v>715.5</v>
       </c>
       <c r="D28" t="n">
         <v>82</v>
       </c>
       <c r="E28" t="n">
-        <v>3.27</v>
+        <v>2.84</v>
       </c>
       <c r="F28" t="n">
-        <v>0.92</v>
+        <v>0.79</v>
       </c>
       <c r="G28" t="n">
-        <v>10.25</v>
+        <v>10.28</v>
       </c>
       <c r="H28" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="I28" t="n">
-        <v>699.8</v>
+        <v>711.39</v>
       </c>
       <c r="J28" t="n">
-        <v>706.46</v>
+        <v>718.0700000000001</v>
       </c>
       <c r="K28" t="n">
-        <v>688.53</v>
+        <v>700.08</v>
       </c>
       <c r="L28" t="n">
-        <v>729.52</v>
+        <v>741.2</v>
       </c>
       <c r="M28" t="n">
-        <v>76.37</v>
+        <v>84.18000000000001</v>
       </c>
       <c r="N28" t="inlineStr">
         <is>
@@ -2073,46 +2069,46 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>IONQ</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>IA / Chips</t>
+          <t>Computación cuántica</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>439.85</v>
+        <v>54.84</v>
       </c>
       <c r="D29" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E29" t="n">
-        <v>23.81</v>
+        <v>4.32</v>
       </c>
       <c r="F29" t="n">
-        <v>0.68</v>
+        <v>0.54</v>
       </c>
       <c r="G29" t="n">
-        <v>28.31</v>
+        <v>4.41</v>
       </c>
       <c r="H29" t="n">
-        <v>6.44</v>
+        <v>8.029999999999999</v>
       </c>
       <c r="I29" t="n">
-        <v>428.53</v>
+        <v>53.08</v>
       </c>
       <c r="J29" t="n">
-        <v>446.93</v>
+        <v>55.94</v>
       </c>
       <c r="K29" t="n">
-        <v>397.39</v>
+        <v>48.23</v>
       </c>
       <c r="L29" t="n">
-        <v>510.63</v>
+        <v>65.84999999999999</v>
       </c>
       <c r="M29" t="n">
-        <v>73.73999999999999</v>
+        <v>67.89</v>
       </c>
       <c r="N29" t="inlineStr">
         <is>
@@ -2133,57 +2129,53 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>MU</t>
+          <t>GOOGL</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Memoria / Chips</t>
+          <t>Tecnología</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>749.3200000000001</v>
+        <v>402.45</v>
       </c>
       <c r="D30" t="n">
-        <v>71</v>
+        <v>86</v>
       </c>
       <c r="E30" t="n">
-        <v>17.05</v>
+        <v>1.11</v>
       </c>
       <c r="F30" t="n">
-        <v>1.41</v>
+        <v>0.71</v>
       </c>
       <c r="G30" t="n">
-        <v>49.16</v>
+        <v>11.45</v>
       </c>
       <c r="H30" t="n">
-        <v>6.56</v>
+        <v>2.85</v>
       </c>
       <c r="I30" t="n">
-        <v>729.66</v>
+        <v>397.87</v>
       </c>
       <c r="J30" t="n">
-        <v>761.61</v>
+        <v>405.31</v>
       </c>
       <c r="K30" t="n">
-        <v>675.59</v>
+        <v>385.27</v>
       </c>
       <c r="L30" t="n">
-        <v>872.22</v>
+        <v>431.08</v>
       </c>
       <c r="M30" t="n">
-        <v>79.19</v>
+        <v>82.91</v>
       </c>
       <c r="N30" t="inlineStr">
         <is>
           <t>ALTO</t>
         </is>
       </c>
-      <c r="O30" t="inlineStr">
-        <is>
-          <t>🔥</t>
-        </is>
-      </c>
+      <c r="O30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>VIGILAR</t>
@@ -2193,46 +2185,46 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>SMCI</t>
+          <t>SPY</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Servidores IA</t>
+          <t>ETF Mercado</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>32.45</v>
+        <v>743.28</v>
       </c>
       <c r="D31" t="n">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="E31" t="n">
-        <v>16.6</v>
+        <v>1.29</v>
       </c>
       <c r="F31" t="n">
-        <v>0.72</v>
+        <v>0.59</v>
       </c>
       <c r="G31" t="n">
-        <v>2.43</v>
+        <v>6.62</v>
       </c>
       <c r="H31" t="n">
-        <v>7.49</v>
+        <v>0.89</v>
       </c>
       <c r="I31" t="n">
-        <v>31.48</v>
+        <v>740.63</v>
       </c>
       <c r="J31" t="n">
-        <v>33.06</v>
+        <v>744.9400000000001</v>
       </c>
       <c r="K31" t="n">
-        <v>28.81</v>
+        <v>733.34</v>
       </c>
       <c r="L31" t="n">
-        <v>38.52</v>
+        <v>759.84</v>
       </c>
       <c r="M31" t="n">
-        <v>57.31</v>
+        <v>82.23</v>
       </c>
       <c r="N31" t="inlineStr">
         <is>
@@ -2249,46 +2241,46 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>IONQ</t>
+          <t>MU</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Computación cuántica</t>
+          <t>Memoria / Chips</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>54.74</v>
+        <v>805.39</v>
       </c>
       <c r="D32" t="n">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="E32" t="n">
-        <v>14.04</v>
+        <v>20.82</v>
       </c>
       <c r="F32" t="n">
-        <v>0.92</v>
+        <v>1</v>
       </c>
       <c r="G32" t="n">
-        <v>4.6</v>
+        <v>51.05</v>
       </c>
       <c r="H32" t="n">
-        <v>8.4</v>
+        <v>6.34</v>
       </c>
       <c r="I32" t="n">
-        <v>52.9</v>
+        <v>784.97</v>
       </c>
       <c r="J32" t="n">
-        <v>55.89</v>
+        <v>818.15</v>
       </c>
       <c r="K32" t="n">
-        <v>47.84</v>
+        <v>728.8099999999999</v>
       </c>
       <c r="L32" t="n">
-        <v>66.23</v>
+        <v>933.03</v>
       </c>
       <c r="M32" t="n">
-        <v>60.49</v>
+        <v>84.86</v>
       </c>
       <c r="N32" t="inlineStr">
         <is>
@@ -2314,37 +2306,37 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>205.02</v>
+        <v>220.32</v>
       </c>
       <c r="D33" t="n">
         <v>72</v>
       </c>
       <c r="E33" t="n">
-        <v>-1.83</v>
+        <v>-7.16</v>
       </c>
       <c r="F33" t="n">
-        <v>0.59</v>
+        <v>0.65</v>
       </c>
       <c r="G33" t="n">
-        <v>18.09</v>
+        <v>17.81</v>
       </c>
       <c r="H33" t="n">
-        <v>8.83</v>
+        <v>8.08</v>
       </c>
       <c r="I33" t="n">
-        <v>197.78</v>
+        <v>213.19</v>
       </c>
       <c r="J33" t="n">
-        <v>209.54</v>
+        <v>224.77</v>
       </c>
       <c r="K33" t="n">
-        <v>177.88</v>
+        <v>193.61</v>
       </c>
       <c r="L33" t="n">
-        <v>250.25</v>
+        <v>264.83</v>
       </c>
       <c r="M33" t="n">
-        <v>52.62</v>
+        <v>54.83</v>
       </c>
       <c r="N33" t="inlineStr">
         <is>
@@ -2361,46 +2353,46 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>GOOGL</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Tecnología</t>
+          <t>IA / Chips</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>385.93</v>
+        <v>447.81</v>
       </c>
       <c r="D34" t="n">
         <v>70</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.64</v>
+        <v>6.27</v>
       </c>
       <c r="F34" t="n">
-        <v>0.6</v>
+        <v>0.47</v>
       </c>
       <c r="G34" t="n">
-        <v>10.53</v>
+        <v>29.48</v>
       </c>
       <c r="H34" t="n">
-        <v>2.73</v>
+        <v>6.58</v>
       </c>
       <c r="I34" t="n">
-        <v>381.72</v>
+        <v>436.02</v>
       </c>
       <c r="J34" t="n">
-        <v>388.56</v>
+        <v>455.18</v>
       </c>
       <c r="K34" t="n">
-        <v>370.13</v>
+        <v>403.59</v>
       </c>
       <c r="L34" t="n">
-        <v>412.26</v>
+        <v>521.52</v>
       </c>
       <c r="M34" t="n">
-        <v>77.97</v>
+        <v>75.67</v>
       </c>
       <c r="N34" t="inlineStr">
         <is>
@@ -2417,7 +2409,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>QCOM</t>
+          <t>INTC</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2426,37 +2418,37 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>208.97</v>
+        <v>121.17</v>
       </c>
       <c r="D35" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="E35" t="n">
-        <v>12.02</v>
+        <v>7.22</v>
       </c>
       <c r="F35" t="n">
-        <v>1.19</v>
+        <v>0.62</v>
       </c>
       <c r="G35" t="n">
-        <v>18.85</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="H35" t="n">
-        <v>9.02</v>
+        <v>7.88</v>
       </c>
       <c r="I35" t="n">
-        <v>201.43</v>
+        <v>117.35</v>
       </c>
       <c r="J35" t="n">
-        <v>213.68</v>
+        <v>123.55</v>
       </c>
       <c r="K35" t="n">
-        <v>180.7</v>
+        <v>106.84</v>
       </c>
       <c r="L35" t="n">
-        <v>256.1</v>
+        <v>145.03</v>
       </c>
       <c r="M35" t="n">
-        <v>73.19</v>
+        <v>80.91</v>
       </c>
       <c r="N35" t="inlineStr">
         <is>
@@ -2473,46 +2465,46 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>INTC</t>
+          <t>TSLA</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Chips</t>
+          <t>Autos / Tech</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>118.52</v>
+        <v>444.27</v>
       </c>
       <c r="D36" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E36" t="n">
-        <v>9.59</v>
+        <v>11.42</v>
       </c>
       <c r="F36" t="n">
-        <v>0.96</v>
+        <v>0.92</v>
       </c>
       <c r="G36" t="n">
-        <v>9.15</v>
+        <v>17.05</v>
       </c>
       <c r="H36" t="n">
-        <v>7.72</v>
+        <v>3.84</v>
       </c>
       <c r="I36" t="n">
-        <v>114.86</v>
+        <v>437.45</v>
       </c>
       <c r="J36" t="n">
-        <v>120.81</v>
+        <v>448.53</v>
       </c>
       <c r="K36" t="n">
-        <v>104.8</v>
+        <v>418.69</v>
       </c>
       <c r="L36" t="n">
-        <v>141.39</v>
+        <v>486.9</v>
       </c>
       <c r="M36" t="n">
-        <v>79.25</v>
+        <v>81.59</v>
       </c>
       <c r="N36" t="inlineStr">
         <is>
@@ -2529,46 +2521,46 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>SOUN</t>
+          <t>QCOM</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>IA</t>
+          <t>Chips</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>7.99</v>
+        <v>213.94</v>
       </c>
       <c r="D37" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="E37" t="n">
-        <v>-12.58</v>
+        <v>11.1</v>
       </c>
       <c r="F37" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.73</v>
       </c>
       <c r="G37" t="n">
-        <v>0.65</v>
+        <v>19.38</v>
       </c>
       <c r="H37" t="n">
-        <v>8.1</v>
+        <v>9.06</v>
       </c>
       <c r="I37" t="n">
-        <v>7.73</v>
+        <v>206.19</v>
       </c>
       <c r="J37" t="n">
-        <v>8.15</v>
+        <v>218.78</v>
       </c>
       <c r="K37" t="n">
-        <v>7.02</v>
+        <v>184.87</v>
       </c>
       <c r="L37" t="n">
-        <v>9.609999999999999</v>
+        <v>262.39</v>
       </c>
       <c r="M37" t="n">
-        <v>47.96</v>
+        <v>75.42</v>
       </c>
       <c r="N37" t="inlineStr">
         <is>

--- a/analisis_acciones.xlsx
+++ b/analisis_acciones.xlsx
@@ -510,37 +510,37 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>226.59</v>
+        <v>235.61</v>
       </c>
       <c r="D2" t="n">
         <v>95</v>
       </c>
       <c r="E2" t="n">
-        <v>9.029999999999999</v>
+        <v>11.4</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8</v>
+        <v>0.98</v>
       </c>
       <c r="G2" t="n">
-        <v>8.109999999999999</v>
+        <v>8.07</v>
       </c>
       <c r="H2" t="n">
-        <v>3.58</v>
+        <v>3.42</v>
       </c>
       <c r="I2" t="n">
-        <v>223.35</v>
+        <v>232.38</v>
       </c>
       <c r="J2" t="n">
-        <v>228.62</v>
+        <v>237.63</v>
       </c>
       <c r="K2" t="n">
-        <v>214.43</v>
+        <v>223.51</v>
       </c>
       <c r="L2" t="n">
-        <v>246.86</v>
+        <v>255.77</v>
       </c>
       <c r="M2" t="n">
-        <v>70.04000000000001</v>
+        <v>70.22</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -561,50 +561,50 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ASML</t>
+          <t>AVGO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Chips</t>
+          <t>IA / Chips</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1580.47</v>
+        <v>441.21</v>
       </c>
       <c r="D3" t="n">
         <v>95</v>
       </c>
       <c r="E3" t="n">
-        <v>2.31</v>
+        <v>6.94</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.73</v>
       </c>
       <c r="G3" t="n">
-        <v>62.71</v>
+        <v>16.29</v>
       </c>
       <c r="H3" t="n">
-        <v>3.97</v>
+        <v>3.69</v>
       </c>
       <c r="I3" t="n">
-        <v>1555.39</v>
+        <v>434.69</v>
       </c>
       <c r="J3" t="n">
-        <v>1596.15</v>
+        <v>445.28</v>
       </c>
       <c r="K3" t="n">
-        <v>1486.41</v>
+        <v>416.77</v>
       </c>
       <c r="L3" t="n">
-        <v>1737.24</v>
+        <v>481.94</v>
       </c>
       <c r="M3" t="n">
-        <v>63.59</v>
+        <v>57.1</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>BAJO</t>
+          <t>MEDIO</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -621,46 +621,46 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AMAT</t>
+          <t>ASML</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Equipos chips</t>
+          <t>Chips</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>437.23</v>
+        <v>1595.13</v>
       </c>
       <c r="D4" t="n">
         <v>95</v>
       </c>
       <c r="E4" t="n">
-        <v>2.01</v>
+        <v>5.18</v>
       </c>
       <c r="F4" t="n">
-        <v>0.62</v>
+        <v>0.66</v>
       </c>
       <c r="G4" t="n">
-        <v>19.02</v>
+        <v>61.67</v>
       </c>
       <c r="H4" t="n">
-        <v>4.35</v>
+        <v>3.87</v>
       </c>
       <c r="I4" t="n">
-        <v>429.62</v>
+        <v>1570.46</v>
       </c>
       <c r="J4" t="n">
-        <v>441.98</v>
+        <v>1610.55</v>
       </c>
       <c r="K4" t="n">
-        <v>408.71</v>
+        <v>1502.62</v>
       </c>
       <c r="L4" t="n">
-        <v>484.77</v>
+        <v>1749.31</v>
       </c>
       <c r="M4" t="n">
-        <v>59.42</v>
+        <v>62.03</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -681,46 +681,46 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SOXX</t>
+          <t>AMAT</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ETF Chips</t>
+          <t>Equipos chips</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>530.0700000000001</v>
+        <v>445.04</v>
       </c>
       <c r="D5" t="n">
         <v>95</v>
       </c>
       <c r="E5" t="n">
-        <v>4.58</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="F5" t="n">
-        <v>0.82</v>
+        <v>1.11</v>
       </c>
       <c r="G5" t="n">
-        <v>19.33</v>
+        <v>18.68</v>
       </c>
       <c r="H5" t="n">
-        <v>3.65</v>
+        <v>4.2</v>
       </c>
       <c r="I5" t="n">
-        <v>522.34</v>
+        <v>437.57</v>
       </c>
       <c r="J5" t="n">
-        <v>534.9</v>
+        <v>449.71</v>
       </c>
       <c r="K5" t="n">
-        <v>501.07</v>
+        <v>417.02</v>
       </c>
       <c r="L5" t="n">
-        <v>578.41</v>
+        <v>491.73</v>
       </c>
       <c r="M5" t="n">
-        <v>71.75</v>
+        <v>58.16</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
@@ -741,7 +741,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>KLAC</t>
+          <t>LRCX</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -750,37 +750,37 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1859.29</v>
+        <v>300.22</v>
       </c>
       <c r="D6" t="n">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="E6" t="n">
-        <v>2.37</v>
+        <v>4.78</v>
       </c>
       <c r="F6" t="n">
-        <v>0.51</v>
+        <v>0.36</v>
       </c>
       <c r="G6" t="n">
-        <v>88.45</v>
+        <v>13.25</v>
       </c>
       <c r="H6" t="n">
-        <v>4.76</v>
+        <v>4.41</v>
       </c>
       <c r="I6" t="n">
-        <v>1823.91</v>
+        <v>294.92</v>
       </c>
       <c r="J6" t="n">
-        <v>1881.4</v>
+        <v>303.53</v>
       </c>
       <c r="K6" t="n">
-        <v>1726.61</v>
+        <v>280.35</v>
       </c>
       <c r="L6" t="n">
-        <v>2080.42</v>
+        <v>333.34</v>
       </c>
       <c r="M6" t="n">
-        <v>53.03</v>
+        <v>65.06</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
@@ -801,50 +801,50 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>COIN</t>
+          <t>XOM</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Cripto / Trading</t>
+          <t>Energía</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>202.08</v>
+        <v>152.6</v>
       </c>
       <c r="D7" t="n">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="E7" t="n">
-        <v>2.08</v>
+        <v>4.11</v>
       </c>
       <c r="F7" t="n">
-        <v>0.62</v>
+        <v>0.39</v>
       </c>
       <c r="G7" t="n">
-        <v>12.22</v>
+        <v>3.86</v>
       </c>
       <c r="H7" t="n">
-        <v>6.05</v>
+        <v>2.53</v>
       </c>
       <c r="I7" t="n">
-        <v>197.19</v>
+        <v>151.06</v>
       </c>
       <c r="J7" t="n">
-        <v>205.13</v>
+        <v>153.57</v>
       </c>
       <c r="K7" t="n">
-        <v>183.75</v>
+        <v>146.82</v>
       </c>
       <c r="L7" t="n">
-        <v>232.63</v>
+        <v>162.24</v>
       </c>
       <c r="M7" t="n">
-        <v>52.31</v>
+        <v>56.24</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>MEDIO</t>
+          <t>BAJO</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -861,55 +861,55 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>LRCX</t>
+          <t>SOXX</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Equipos chips</t>
+          <t>ETF Chips</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>297.34</v>
+        <v>532.11</v>
       </c>
       <c r="D8" t="n">
         <v>95</v>
       </c>
       <c r="E8" t="n">
-        <v>0.06</v>
+        <v>8.07</v>
       </c>
       <c r="F8" t="n">
-        <v>0.45</v>
+        <v>0.6</v>
       </c>
       <c r="G8" t="n">
-        <v>13.84</v>
+        <v>18.48</v>
       </c>
       <c r="H8" t="n">
-        <v>4.65</v>
+        <v>3.47</v>
       </c>
       <c r="I8" t="n">
-        <v>291.8</v>
+        <v>524.72</v>
       </c>
       <c r="J8" t="n">
-        <v>300.8</v>
+        <v>536.73</v>
       </c>
       <c r="K8" t="n">
-        <v>276.58</v>
+        <v>504.39</v>
       </c>
       <c r="L8" t="n">
-        <v>331.94</v>
+        <v>578.3099999999999</v>
       </c>
       <c r="M8" t="n">
-        <v>67</v>
+        <v>68.93000000000001</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>BAJO</t>
+          <t>MEDIO</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -921,55 +921,55 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>XOM</t>
+          <t>KLAC</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Energía</t>
+          <t>Equipos chips</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>151.4</v>
+        <v>1902.8</v>
       </c>
       <c r="D9" t="n">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="E9" t="n">
-        <v>1.82</v>
+        <v>7.91</v>
       </c>
       <c r="F9" t="n">
-        <v>0.43</v>
+        <v>0.49</v>
       </c>
       <c r="G9" t="n">
-        <v>3.98</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="H9" t="n">
-        <v>2.63</v>
+        <v>4.5</v>
       </c>
       <c r="I9" t="n">
-        <v>149.8</v>
+        <v>1868.51</v>
       </c>
       <c r="J9" t="n">
-        <v>152.39</v>
+        <v>1924.22</v>
       </c>
       <c r="K9" t="n">
-        <v>145.43</v>
+        <v>1774.23</v>
       </c>
       <c r="L9" t="n">
-        <v>161.34</v>
+        <v>2117.06</v>
       </c>
       <c r="M9" t="n">
-        <v>51.44</v>
+        <v>47.51</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>BAJO</t>
+          <t>MEDIO</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -981,55 +981,55 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SLB</t>
+          <t>INTC</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Energía</t>
+          <t>Chips</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>55.54</v>
+        <v>116.06</v>
       </c>
       <c r="D10" t="n">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="E10" t="n">
-        <v>0.6899999999999999</v>
+        <v>5.87</v>
       </c>
       <c r="F10" t="n">
-        <v>0.37</v>
+        <v>0.63</v>
       </c>
       <c r="G10" t="n">
-        <v>1.65</v>
+        <v>8.74</v>
       </c>
       <c r="H10" t="n">
-        <v>2.98</v>
+        <v>7.53</v>
       </c>
       <c r="I10" t="n">
-        <v>54.88</v>
+        <v>112.56</v>
       </c>
       <c r="J10" t="n">
-        <v>55.95</v>
+        <v>118.24</v>
       </c>
       <c r="K10" t="n">
-        <v>53.06</v>
+        <v>102.95</v>
       </c>
       <c r="L10" t="n">
-        <v>59.67</v>
+        <v>137.91</v>
       </c>
       <c r="M10" t="n">
-        <v>53.5</v>
+        <v>71.98999999999999</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>BAJO</t>
+          <t>MEDIO</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1041,55 +1041,55 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>AMZN</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Tecnología</t>
+          <t>IA / Chips</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>269.49</v>
+        <v>449.41</v>
       </c>
       <c r="D11" t="n">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="E11" t="n">
-        <v>-2</v>
+        <v>10.03</v>
       </c>
       <c r="F11" t="n">
-        <v>0.57</v>
+        <v>0.45</v>
       </c>
       <c r="G11" t="n">
-        <v>7.36</v>
+        <v>27.34</v>
       </c>
       <c r="H11" t="n">
-        <v>2.73</v>
+        <v>6.08</v>
       </c>
       <c r="I11" t="n">
-        <v>266.55</v>
+        <v>438.48</v>
       </c>
       <c r="J11" t="n">
-        <v>271.33</v>
+        <v>456.24</v>
       </c>
       <c r="K11" t="n">
-        <v>258.45</v>
+        <v>408.4</v>
       </c>
       <c r="L11" t="n">
-        <v>287.9</v>
+        <v>517.75</v>
       </c>
       <c r="M11" t="n">
-        <v>66.25</v>
+        <v>71.06</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>BAJO</t>
+          <t>MEDIO</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1101,46 +1101,46 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>SLB</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Chips</t>
+          <t>Energía</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>400.82</v>
+        <v>55.74</v>
       </c>
       <c r="D12" t="n">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.45</v>
+        <v>5.18</v>
       </c>
       <c r="F12" t="n">
-        <v>0.68</v>
+        <v>0.22</v>
       </c>
       <c r="G12" t="n">
-        <v>15.59</v>
+        <v>1.5</v>
       </c>
       <c r="H12" t="n">
-        <v>3.89</v>
+        <v>2.69</v>
       </c>
       <c r="I12" t="n">
-        <v>394.58</v>
+        <v>55.15</v>
       </c>
       <c r="J12" t="n">
-        <v>404.71</v>
+        <v>56.12</v>
       </c>
       <c r="K12" t="n">
-        <v>377.43</v>
+        <v>53.5</v>
       </c>
       <c r="L12" t="n">
-        <v>439.79</v>
+        <v>59.49</v>
       </c>
       <c r="M12" t="n">
-        <v>58.88</v>
+        <v>48.08</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
@@ -1149,7 +1149,7 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1161,53 +1161,57 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>SMCI</t>
+          <t>TSM</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Servidores IA</t>
+          <t>Chips</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>32.2</v>
+        <v>420.31</v>
       </c>
       <c r="D13" t="n">
-        <v>76</v>
+        <v>95</v>
       </c>
       <c r="E13" t="n">
-        <v>-7.1</v>
+        <v>1.49</v>
       </c>
       <c r="F13" t="n">
-        <v>0.51</v>
+        <v>1.06</v>
       </c>
       <c r="G13" t="n">
-        <v>2.29</v>
+        <v>15.26</v>
       </c>
       <c r="H13" t="n">
-        <v>7.12</v>
+        <v>3.63</v>
       </c>
       <c r="I13" t="n">
-        <v>31.28</v>
+        <v>414.21</v>
       </c>
       <c r="J13" t="n">
-        <v>32.77</v>
+        <v>424.12</v>
       </c>
       <c r="K13" t="n">
-        <v>28.76</v>
+        <v>397.42</v>
       </c>
       <c r="L13" t="n">
-        <v>37.93</v>
+        <v>458.45</v>
       </c>
       <c r="M13" t="n">
-        <v>63.5</v>
+        <v>58.75</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>MEDIO</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr"/>
+          <t>BAJO</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>🔥</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>POSIBLE COMPRA</t>
@@ -1217,112 +1221,116 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>AVGO</t>
+          <t>AMZN</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>IA / Chips</t>
+          <t>Tecnología</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>418.32</v>
+        <v>268.05</v>
       </c>
       <c r="D14" t="n">
-        <v>72</v>
+        <v>84</v>
       </c>
       <c r="E14" t="n">
-        <v>-1.67</v>
+        <v>-1.15</v>
       </c>
       <c r="F14" t="n">
-        <v>0.59</v>
+        <v>0.45</v>
       </c>
       <c r="G14" t="n">
-        <v>15.61</v>
+        <v>6.98</v>
       </c>
       <c r="H14" t="n">
-        <v>3.73</v>
+        <v>2.6</v>
       </c>
       <c r="I14" t="n">
-        <v>412.08</v>
+        <v>265.26</v>
       </c>
       <c r="J14" t="n">
-        <v>422.22</v>
+        <v>269.79</v>
       </c>
       <c r="K14" t="n">
-        <v>394.91</v>
+        <v>257.58</v>
       </c>
       <c r="L14" t="n">
-        <v>457.33</v>
+        <v>285.5</v>
       </c>
       <c r="M14" t="n">
-        <v>49.24</v>
+        <v>55.32</v>
       </c>
       <c r="N14" t="inlineStr">
         <is>
           <t>BAJO</t>
         </is>
       </c>
-      <c r="O14" t="inlineStr"/>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>🔥</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>VIGILAR</t>
+          <t>POSIBLE COMPRA</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>AI</t>
+          <t>SMCI</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>IA</t>
+          <t>Servidores IA</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>8.69</v>
+        <v>32.75</v>
       </c>
       <c r="D15" t="n">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="E15" t="n">
-        <v>-9.529999999999999</v>
+        <v>-2.59</v>
       </c>
       <c r="F15" t="n">
-        <v>0.65</v>
+        <v>0.72</v>
       </c>
       <c r="G15" t="n">
-        <v>0.43</v>
+        <v>2.26</v>
       </c>
       <c r="H15" t="n">
-        <v>4.91</v>
+        <v>6.91</v>
       </c>
       <c r="I15" t="n">
-        <v>8.51</v>
+        <v>31.85</v>
       </c>
       <c r="J15" t="n">
-        <v>8.789999999999999</v>
+        <v>33.32</v>
       </c>
       <c r="K15" t="n">
-        <v>8.050000000000001</v>
+        <v>29.36</v>
       </c>
       <c r="L15" t="n">
-        <v>9.75</v>
+        <v>38.41</v>
       </c>
       <c r="M15" t="n">
-        <v>52.56</v>
+        <v>59.76</v>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>BAJO</t>
+          <t>MEDIO</t>
         </is>
       </c>
       <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>VIGILAR</t>
+          <t>POSIBLE COMPRA</t>
         </is>
       </c>
     </row>
@@ -1338,44 +1346,48 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>185.47</v>
+        <v>186.5</v>
       </c>
       <c r="D16" t="n">
-        <v>62</v>
+        <v>74</v>
       </c>
       <c r="E16" t="n">
-        <v>0.17</v>
+        <v>2.19</v>
       </c>
       <c r="F16" t="n">
-        <v>0.4</v>
+        <v>0.35</v>
       </c>
       <c r="G16" t="n">
-        <v>4.46</v>
+        <v>4.31</v>
       </c>
       <c r="H16" t="n">
-        <v>2.4</v>
+        <v>2.31</v>
       </c>
       <c r="I16" t="n">
-        <v>183.69</v>
+        <v>184.77</v>
       </c>
       <c r="J16" t="n">
-        <v>186.58</v>
+        <v>187.57</v>
       </c>
       <c r="K16" t="n">
-        <v>178.78</v>
+        <v>180.03</v>
       </c>
       <c r="L16" t="n">
-        <v>196.62</v>
+        <v>197.28</v>
       </c>
       <c r="M16" t="n">
-        <v>46.66</v>
+        <v>52.18</v>
       </c>
       <c r="N16" t="inlineStr">
         <is>
           <t>BAJO</t>
         </is>
       </c>
-      <c r="O16" t="inlineStr"/>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>🔥</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>VIGILAR</t>
@@ -1385,53 +1397,57 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>OXY</t>
+          <t>ARM</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Energía</t>
+          <t>Chips</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>56.17</v>
+        <v>225.73</v>
       </c>
       <c r="D17" t="n">
-        <v>62</v>
+        <v>72</v>
       </c>
       <c r="E17" t="n">
-        <v>1.9</v>
+        <v>5.82</v>
       </c>
       <c r="F17" t="n">
-        <v>0.36</v>
+        <v>0.57</v>
       </c>
       <c r="G17" t="n">
-        <v>1.85</v>
+        <v>16.35</v>
       </c>
       <c r="H17" t="n">
-        <v>3.3</v>
+        <v>7.24</v>
       </c>
       <c r="I17" t="n">
-        <v>55.43</v>
+        <v>219.19</v>
       </c>
       <c r="J17" t="n">
-        <v>56.63</v>
+        <v>229.82</v>
       </c>
       <c r="K17" t="n">
-        <v>53.39</v>
+        <v>201.2</v>
       </c>
       <c r="L17" t="n">
-        <v>60.8</v>
+        <v>266.61</v>
       </c>
       <c r="M17" t="n">
-        <v>45.52</v>
+        <v>46.71</v>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>BAJO</t>
-        </is>
-      </c>
-      <c r="O17" t="inlineStr"/>
+          <t>MEDIO</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>🔥</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>VIGILAR</t>
@@ -1441,158 +1457,166 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>SOUN</t>
+          <t>HOOD</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>IA</t>
+          <t>Trading</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>8.44</v>
+        <v>81.04000000000001</v>
       </c>
       <c r="D18" t="n">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="E18" t="n">
-        <v>-9.93</v>
+        <v>6.24</v>
       </c>
       <c r="F18" t="n">
-        <v>0.64</v>
+        <v>0.77</v>
       </c>
       <c r="G18" t="n">
-        <v>0.66</v>
+        <v>4.32</v>
       </c>
       <c r="H18" t="n">
-        <v>7.83</v>
+        <v>5.33</v>
       </c>
       <c r="I18" t="n">
-        <v>8.18</v>
+        <v>79.31</v>
       </c>
       <c r="J18" t="n">
-        <v>8.609999999999999</v>
+        <v>82.12</v>
       </c>
       <c r="K18" t="n">
-        <v>7.45</v>
+        <v>74.56</v>
       </c>
       <c r="L18" t="n">
-        <v>10.09</v>
+        <v>91.84999999999999</v>
       </c>
       <c r="M18" t="n">
-        <v>55.58</v>
+        <v>45.03</v>
       </c>
       <c r="N18" t="inlineStr">
         <is>
           <t>MEDIO</t>
         </is>
       </c>
-      <c r="O18" t="inlineStr"/>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>🔥</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>NO COMPRAR</t>
+          <t>VIGILAR</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>OXY</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Tecnología</t>
+          <t>Energía</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>404.81</v>
+        <v>56.9</v>
       </c>
       <c r="D19" t="n">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.21</v>
+        <v>5.5</v>
       </c>
       <c r="F19" t="n">
-        <v>0.52</v>
+        <v>0.5</v>
       </c>
       <c r="G19" t="n">
-        <v>10.66</v>
+        <v>1.87</v>
       </c>
       <c r="H19" t="n">
-        <v>2.63</v>
+        <v>3.28</v>
       </c>
       <c r="I19" t="n">
-        <v>400.54</v>
+        <v>56.16</v>
       </c>
       <c r="J19" t="n">
-        <v>407.48</v>
+        <v>57.37</v>
       </c>
       <c r="K19" t="n">
-        <v>388.82</v>
+        <v>54.11</v>
       </c>
       <c r="L19" t="n">
-        <v>431.47</v>
+        <v>61.57</v>
       </c>
       <c r="M19" t="n">
-        <v>42.19</v>
+        <v>49.42</v>
       </c>
       <c r="N19" t="inlineStr">
         <is>
           <t>BAJO</t>
         </is>
       </c>
-      <c r="O19" t="inlineStr"/>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>🔥</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>NO COMPRAR</t>
+          <t>VIGILAR</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>META</t>
+          <t>AI</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Tecnología</t>
+          <t>IA</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>616.34</v>
+        <v>8.970000000000001</v>
       </c>
       <c r="D20" t="n">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="E20" t="n">
-        <v>0.5600000000000001</v>
+        <v>-6.4</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7</v>
+        <v>0.93</v>
       </c>
       <c r="G20" t="n">
-        <v>18.55</v>
+        <v>0.45</v>
       </c>
       <c r="H20" t="n">
-        <v>3.01</v>
+        <v>4.97</v>
       </c>
       <c r="I20" t="n">
-        <v>608.92</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="J20" t="n">
-        <v>620.98</v>
+        <v>9.08</v>
       </c>
       <c r="K20" t="n">
-        <v>588.52</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="L20" t="n">
-        <v>662.71</v>
+        <v>10.08</v>
       </c>
       <c r="M20" t="n">
-        <v>35.11</v>
+        <v>55.29</v>
       </c>
       <c r="N20" t="inlineStr">
         <is>
@@ -1602,53 +1626,53 @@
       <c r="O20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>NO COMPRAR</t>
+          <t>VIGILAR</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>HOOD</t>
+          <t>SOUN</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Trading</t>
+          <t>IA</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>76.87</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="D21" t="n">
-        <v>46</v>
+        <v>58</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.76</v>
+        <v>-13.19</v>
       </c>
       <c r="F21" t="n">
-        <v>0.39</v>
+        <v>0.41</v>
       </c>
       <c r="G21" t="n">
-        <v>4</v>
+        <v>0.64</v>
       </c>
       <c r="H21" t="n">
-        <v>5.2</v>
+        <v>7.66</v>
       </c>
       <c r="I21" t="n">
-        <v>75.27</v>
+        <v>8.1</v>
       </c>
       <c r="J21" t="n">
-        <v>77.87</v>
+        <v>8.52</v>
       </c>
       <c r="K21" t="n">
-        <v>70.88</v>
+        <v>7.4</v>
       </c>
       <c r="L21" t="n">
-        <v>86.86</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="M21" t="n">
-        <v>40.11</v>
+        <v>51.63</v>
       </c>
       <c r="N21" t="inlineStr">
         <is>
@@ -1665,46 +1689,46 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>PYPL</t>
+          <t>META</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Pagos</t>
+          <t>Tecnología</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>45.57</v>
+        <v>617.3</v>
       </c>
       <c r="D22" t="n">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.51</v>
+        <v>0.08</v>
       </c>
       <c r="F22" t="n">
-        <v>0.72</v>
+        <v>0.51</v>
       </c>
       <c r="G22" t="n">
-        <v>1.54</v>
+        <v>17.26</v>
       </c>
       <c r="H22" t="n">
-        <v>3.39</v>
+        <v>2.8</v>
       </c>
       <c r="I22" t="n">
-        <v>44.95</v>
+        <v>610.4</v>
       </c>
       <c r="J22" t="n">
-        <v>45.96</v>
+        <v>621.62</v>
       </c>
       <c r="K22" t="n">
-        <v>43.25</v>
+        <v>591.42</v>
       </c>
       <c r="L22" t="n">
-        <v>49.43</v>
+        <v>660.45</v>
       </c>
       <c r="M22" t="n">
-        <v>28.76</v>
+        <v>27.59</v>
       </c>
       <c r="N22" t="inlineStr">
         <is>
@@ -1721,50 +1745,50 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>SOFI</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Fintech</t>
+          <t>Tecnología</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>15.39</v>
+        <v>409.6</v>
       </c>
       <c r="D23" t="n">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="E23" t="n">
-        <v>-5.61</v>
+        <v>-2.66</v>
       </c>
       <c r="F23" t="n">
-        <v>0.72</v>
+        <v>0.54</v>
       </c>
       <c r="G23" t="n">
-        <v>0.8</v>
+        <v>10.79</v>
       </c>
       <c r="H23" t="n">
-        <v>5.17</v>
+        <v>2.63</v>
       </c>
       <c r="I23" t="n">
-        <v>15.07</v>
+        <v>405.28</v>
       </c>
       <c r="J23" t="n">
-        <v>15.58</v>
+        <v>412.29</v>
       </c>
       <c r="K23" t="n">
-        <v>14.19</v>
+        <v>393.41</v>
       </c>
       <c r="L23" t="n">
-        <v>17.37</v>
+        <v>436.57</v>
       </c>
       <c r="M23" t="n">
-        <v>29.63</v>
+        <v>38.47</v>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>MEDIO</t>
+          <t>BAJO</t>
         </is>
       </c>
       <c r="O23" t="inlineStr"/>
@@ -1777,50 +1801,50 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>UPST</t>
+          <t>PYPL</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Fintech IA</t>
+          <t>Pagos</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>26.85</v>
+        <v>45.13</v>
       </c>
       <c r="D24" t="n">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="E24" t="n">
-        <v>-6.43</v>
+        <v>-2.35</v>
       </c>
       <c r="F24" t="n">
-        <v>0.73</v>
+        <v>0.43</v>
       </c>
       <c r="G24" t="n">
-        <v>1.68</v>
+        <v>1.55</v>
       </c>
       <c r="H24" t="n">
-        <v>6.27</v>
+        <v>3.44</v>
       </c>
       <c r="I24" t="n">
-        <v>26.18</v>
+        <v>44.51</v>
       </c>
       <c r="J24" t="n">
-        <v>27.28</v>
+        <v>45.52</v>
       </c>
       <c r="K24" t="n">
-        <v>24.33</v>
+        <v>42.8</v>
       </c>
       <c r="L24" t="n">
-        <v>31.06</v>
+        <v>49.02</v>
       </c>
       <c r="M24" t="n">
-        <v>26</v>
+        <v>21.22</v>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>MEDIO</t>
+          <t>BAJO</t>
         </is>
       </c>
       <c r="O24" t="inlineStr"/>
@@ -1833,50 +1857,50 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>PLTR</t>
+          <t>UPST</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>IA / Software</t>
+          <t>Fintech IA</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>130.12</v>
+        <v>29.23</v>
       </c>
       <c r="D25" t="n">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="E25" t="n">
-        <v>-2.74</v>
+        <v>0.79</v>
       </c>
       <c r="F25" t="n">
-        <v>1.02</v>
+        <v>0.71</v>
       </c>
       <c r="G25" t="n">
-        <v>5.73</v>
+        <v>1.78</v>
       </c>
       <c r="H25" t="n">
-        <v>4.4</v>
+        <v>6.09</v>
       </c>
       <c r="I25" t="n">
-        <v>127.83</v>
+        <v>28.52</v>
       </c>
       <c r="J25" t="n">
-        <v>131.55</v>
+        <v>29.67</v>
       </c>
       <c r="K25" t="n">
-        <v>121.53</v>
+        <v>26.56</v>
       </c>
       <c r="L25" t="n">
-        <v>144.44</v>
+        <v>33.68</v>
       </c>
       <c r="M25" t="n">
-        <v>35.19</v>
+        <v>34.63</v>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>BAJO</t>
+          <t>MEDIO</t>
         </is>
       </c>
       <c r="O25" t="inlineStr"/>
@@ -1889,166 +1913,158 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>RKLB</t>
+          <t>SOFI</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Espacial</t>
+          <t>Fintech</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>126.77</v>
+        <v>15.88</v>
       </c>
       <c r="D26" t="n">
-        <v>89</v>
+        <v>38</v>
       </c>
       <c r="E26" t="n">
-        <v>49.76</v>
+        <v>-0.78</v>
       </c>
       <c r="F26" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="G26" t="n">
         <v>0.83</v>
       </c>
-      <c r="G26" t="n">
-        <v>8.94</v>
-      </c>
       <c r="H26" t="n">
-        <v>7.05</v>
+        <v>5.21</v>
       </c>
       <c r="I26" t="n">
-        <v>123.19</v>
+        <v>15.54</v>
       </c>
       <c r="J26" t="n">
-        <v>129.01</v>
+        <v>16.08</v>
       </c>
       <c r="K26" t="n">
-        <v>113.36</v>
+        <v>14.64</v>
       </c>
       <c r="L26" t="n">
-        <v>149.12</v>
+        <v>17.94</v>
       </c>
       <c r="M26" t="n">
-        <v>74.75</v>
+        <v>33.4</v>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>ALTO</t>
-        </is>
-      </c>
-      <c r="O26" t="inlineStr">
-        <is>
-          <t>🔥</t>
-        </is>
-      </c>
+          <t>MEDIO</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>VIGILAR</t>
+          <t>NO COMPRAR</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>PLTR</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Tecnología</t>
+          <t>IA / Software</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>298.7</v>
+        <v>133.52</v>
       </c>
       <c r="D27" t="n">
-        <v>86</v>
+        <v>36</v>
       </c>
       <c r="E27" t="n">
-        <v>3.99</v>
+        <v>-2.58</v>
       </c>
       <c r="F27" t="n">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="G27" t="n">
-        <v>6.52</v>
+        <v>5.77</v>
       </c>
       <c r="H27" t="n">
-        <v>2.18</v>
+        <v>4.32</v>
       </c>
       <c r="I27" t="n">
-        <v>296.09</v>
+        <v>131.21</v>
       </c>
       <c r="J27" t="n">
-        <v>300.33</v>
+        <v>134.96</v>
       </c>
       <c r="K27" t="n">
-        <v>288.92</v>
+        <v>124.86</v>
       </c>
       <c r="L27" t="n">
-        <v>314.99</v>
+        <v>147.95</v>
       </c>
       <c r="M27" t="n">
-        <v>77.91</v>
+        <v>38.23</v>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>ALTO</t>
-        </is>
-      </c>
-      <c r="O27" t="inlineStr">
-        <is>
-          <t>🔥</t>
-        </is>
-      </c>
+          <t>BAJO</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>VIGILAR</t>
+          <t>NO COMPRAR</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>QQQ</t>
+          <t>COIN</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>ETF Nasdaq</t>
+          <t>Cripto / Trading</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>715.5</v>
+        <v>216.42</v>
       </c>
       <c r="D28" t="n">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="E28" t="n">
-        <v>2.84</v>
+        <v>12.16</v>
       </c>
       <c r="F28" t="n">
-        <v>0.79</v>
+        <v>1.34</v>
       </c>
       <c r="G28" t="n">
-        <v>10.28</v>
+        <v>13.74</v>
       </c>
       <c r="H28" t="n">
-        <v>1.44</v>
+        <v>6.35</v>
       </c>
       <c r="I28" t="n">
-        <v>711.39</v>
+        <v>210.92</v>
       </c>
       <c r="J28" t="n">
-        <v>718.0700000000001</v>
+        <v>219.85</v>
       </c>
       <c r="K28" t="n">
-        <v>700.08</v>
+        <v>195.81</v>
       </c>
       <c r="L28" t="n">
-        <v>741.2</v>
+        <v>250.77</v>
       </c>
       <c r="M28" t="n">
-        <v>84.18000000000001</v>
+        <v>58.1</v>
       </c>
       <c r="N28" t="inlineStr">
         <is>
@@ -2057,7 +2073,7 @@
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -2069,46 +2085,46 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>IONQ</t>
+          <t>AAPL</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Computación cuántica</t>
+          <t>Tecnología</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>54.84</v>
+        <v>298.99</v>
       </c>
       <c r="D29" t="n">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="E29" t="n">
-        <v>4.32</v>
+        <v>4.12</v>
       </c>
       <c r="F29" t="n">
-        <v>0.54</v>
+        <v>0.49</v>
       </c>
       <c r="G29" t="n">
-        <v>4.41</v>
+        <v>6.61</v>
       </c>
       <c r="H29" t="n">
-        <v>8.029999999999999</v>
+        <v>2.21</v>
       </c>
       <c r="I29" t="n">
-        <v>53.08</v>
+        <v>296.35</v>
       </c>
       <c r="J29" t="n">
-        <v>55.94</v>
+        <v>300.65</v>
       </c>
       <c r="K29" t="n">
-        <v>48.23</v>
+        <v>289.09</v>
       </c>
       <c r="L29" t="n">
-        <v>65.84999999999999</v>
+        <v>315.51</v>
       </c>
       <c r="M29" t="n">
-        <v>67.89</v>
+        <v>82.28</v>
       </c>
       <c r="N29" t="inlineStr">
         <is>
@@ -2129,53 +2145,57 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>GOOGL</t>
+          <t>SPY</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Tecnología</t>
+          <t>ETF Mercado</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>402.45</v>
+        <v>748.45</v>
       </c>
       <c r="D30" t="n">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="E30" t="n">
-        <v>1.11</v>
+        <v>2.31</v>
       </c>
       <c r="F30" t="n">
-        <v>0.71</v>
+        <v>0.64</v>
       </c>
       <c r="G30" t="n">
-        <v>11.45</v>
+        <v>6.71</v>
       </c>
       <c r="H30" t="n">
-        <v>2.85</v>
+        <v>0.9</v>
       </c>
       <c r="I30" t="n">
-        <v>397.87</v>
+        <v>745.77</v>
       </c>
       <c r="J30" t="n">
-        <v>405.31</v>
+        <v>750.13</v>
       </c>
       <c r="K30" t="n">
-        <v>385.27</v>
+        <v>738.38</v>
       </c>
       <c r="L30" t="n">
-        <v>431.08</v>
+        <v>765.23</v>
       </c>
       <c r="M30" t="n">
-        <v>82.91</v>
+        <v>82.13</v>
       </c>
       <c r="N30" t="inlineStr">
         <is>
           <t>ALTO</t>
         </is>
       </c>
-      <c r="O30" t="inlineStr"/>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>🔥</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>VIGILAR</t>
@@ -2185,53 +2205,57 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>SPY</t>
+          <t>QQQ</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>ETF Mercado</t>
+          <t>ETF Nasdaq</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>743.28</v>
+        <v>720.47</v>
       </c>
       <c r="D31" t="n">
         <v>82</v>
       </c>
       <c r="E31" t="n">
-        <v>1.29</v>
+        <v>3.67</v>
       </c>
       <c r="F31" t="n">
-        <v>0.59</v>
+        <v>0.7</v>
       </c>
       <c r="G31" t="n">
-        <v>6.62</v>
+        <v>9.9</v>
       </c>
       <c r="H31" t="n">
-        <v>0.89</v>
+        <v>1.37</v>
       </c>
       <c r="I31" t="n">
-        <v>740.63</v>
+        <v>716.51</v>
       </c>
       <c r="J31" t="n">
-        <v>744.9400000000001</v>
+        <v>722.95</v>
       </c>
       <c r="K31" t="n">
-        <v>733.34</v>
+        <v>705.62</v>
       </c>
       <c r="L31" t="n">
-        <v>759.84</v>
+        <v>745.22</v>
       </c>
       <c r="M31" t="n">
-        <v>82.23</v>
+        <v>82.81</v>
       </c>
       <c r="N31" t="inlineStr">
         <is>
           <t>ALTO</t>
         </is>
       </c>
-      <c r="O31" t="inlineStr"/>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>🔥</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>VIGILAR</t>
@@ -2241,46 +2265,46 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>MU</t>
+          <t>GOOGL</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Memoria / Chips</t>
+          <t>Tecnología</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>805.39</v>
+        <v>401.02</v>
       </c>
       <c r="D32" t="n">
-        <v>72</v>
+        <v>86</v>
       </c>
       <c r="E32" t="n">
-        <v>20.82</v>
+        <v>0.76</v>
       </c>
       <c r="F32" t="n">
-        <v>1</v>
+        <v>0.59</v>
       </c>
       <c r="G32" t="n">
-        <v>51.05</v>
+        <v>11.26</v>
       </c>
       <c r="H32" t="n">
-        <v>6.34</v>
+        <v>2.81</v>
       </c>
       <c r="I32" t="n">
-        <v>784.97</v>
+        <v>396.52</v>
       </c>
       <c r="J32" t="n">
-        <v>818.15</v>
+        <v>403.83</v>
       </c>
       <c r="K32" t="n">
-        <v>728.8099999999999</v>
+        <v>384.14</v>
       </c>
       <c r="L32" t="n">
-        <v>933.03</v>
+        <v>429.16</v>
       </c>
       <c r="M32" t="n">
-        <v>84.86</v>
+        <v>80.5</v>
       </c>
       <c r="N32" t="inlineStr">
         <is>
@@ -2297,46 +2321,46 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>ARM</t>
+          <t>TSLA</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Chips</t>
+          <t>Autos / Tech</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>220.32</v>
+        <v>444.58</v>
       </c>
       <c r="D33" t="n">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="E33" t="n">
-        <v>-7.16</v>
+        <v>7.96</v>
       </c>
       <c r="F33" t="n">
-        <v>0.65</v>
+        <v>0.64</v>
       </c>
       <c r="G33" t="n">
-        <v>17.81</v>
+        <v>16.96</v>
       </c>
       <c r="H33" t="n">
-        <v>8.08</v>
+        <v>3.82</v>
       </c>
       <c r="I33" t="n">
-        <v>213.19</v>
+        <v>437.79</v>
       </c>
       <c r="J33" t="n">
-        <v>224.77</v>
+        <v>448.82</v>
       </c>
       <c r="K33" t="n">
-        <v>193.61</v>
+        <v>419.13</v>
       </c>
       <c r="L33" t="n">
-        <v>264.83</v>
+        <v>486.99</v>
       </c>
       <c r="M33" t="n">
-        <v>54.83</v>
+        <v>80.81999999999999</v>
       </c>
       <c r="N33" t="inlineStr">
         <is>
@@ -2353,46 +2377,46 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>QCOM</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>IA / Chips</t>
+          <t>Chips</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>447.81</v>
+        <v>201.46</v>
       </c>
       <c r="D34" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E34" t="n">
-        <v>6.27</v>
+        <v>-0.54</v>
       </c>
       <c r="F34" t="n">
-        <v>0.47</v>
+        <v>0.67</v>
       </c>
       <c r="G34" t="n">
-        <v>29.48</v>
+        <v>19.09</v>
       </c>
       <c r="H34" t="n">
-        <v>6.58</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="I34" t="n">
-        <v>436.02</v>
+        <v>193.82</v>
       </c>
       <c r="J34" t="n">
-        <v>455.18</v>
+        <v>206.23</v>
       </c>
       <c r="K34" t="n">
-        <v>403.59</v>
+        <v>172.82</v>
       </c>
       <c r="L34" t="n">
-        <v>521.52</v>
+        <v>249.17</v>
       </c>
       <c r="M34" t="n">
-        <v>75.67</v>
+        <v>67.15000000000001</v>
       </c>
       <c r="N34" t="inlineStr">
         <is>
@@ -2409,46 +2433,46 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>INTC</t>
+          <t>RKLB</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Chips</t>
+          <t>Espacial</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>121.17</v>
+        <v>131.71</v>
       </c>
       <c r="D35" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E35" t="n">
-        <v>7.22</v>
+        <v>67.61</v>
       </c>
       <c r="F35" t="n">
-        <v>0.62</v>
+        <v>0.79</v>
       </c>
       <c r="G35" t="n">
-        <v>9.550000000000001</v>
+        <v>9.27</v>
       </c>
       <c r="H35" t="n">
-        <v>7.88</v>
+        <v>7.04</v>
       </c>
       <c r="I35" t="n">
-        <v>117.35</v>
+        <v>128</v>
       </c>
       <c r="J35" t="n">
-        <v>123.55</v>
+        <v>134.03</v>
       </c>
       <c r="K35" t="n">
-        <v>106.84</v>
+        <v>117.81</v>
       </c>
       <c r="L35" t="n">
-        <v>145.03</v>
+        <v>154.88</v>
       </c>
       <c r="M35" t="n">
-        <v>80.91</v>
+        <v>80.53</v>
       </c>
       <c r="N35" t="inlineStr">
         <is>
@@ -2465,46 +2489,46 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>TSLA</t>
+          <t>IONQ</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Autos / Tech</t>
+          <t>Computación cuántica</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>444.27</v>
+        <v>57.48</v>
       </c>
       <c r="D36" t="n">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="E36" t="n">
-        <v>11.42</v>
+        <v>20.55</v>
       </c>
       <c r="F36" t="n">
-        <v>0.92</v>
+        <v>0.6</v>
       </c>
       <c r="G36" t="n">
-        <v>17.05</v>
+        <v>4.49</v>
       </c>
       <c r="H36" t="n">
-        <v>3.84</v>
+        <v>7.81</v>
       </c>
       <c r="I36" t="n">
-        <v>437.45</v>
+        <v>55.69</v>
       </c>
       <c r="J36" t="n">
-        <v>448.53</v>
+        <v>58.6</v>
       </c>
       <c r="K36" t="n">
-        <v>418.69</v>
+        <v>50.75</v>
       </c>
       <c r="L36" t="n">
-        <v>486.9</v>
+        <v>68.7</v>
       </c>
       <c r="M36" t="n">
-        <v>81.59</v>
+        <v>72.97</v>
       </c>
       <c r="N36" t="inlineStr">
         <is>
@@ -2521,46 +2545,46 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>QCOM</t>
+          <t>MU</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Chips</t>
+          <t>Memoria / Chips</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>213.94</v>
+        <v>791.45</v>
       </c>
       <c r="D37" t="n">
-        <v>50</v>
+        <v>64</v>
       </c>
       <c r="E37" t="n">
-        <v>11.1</v>
+        <v>22.4</v>
       </c>
       <c r="F37" t="n">
-        <v>0.73</v>
+        <v>0.76</v>
       </c>
       <c r="G37" t="n">
-        <v>19.38</v>
+        <v>51.82</v>
       </c>
       <c r="H37" t="n">
-        <v>9.06</v>
+        <v>6.55</v>
       </c>
       <c r="I37" t="n">
-        <v>206.19</v>
+        <v>770.72</v>
       </c>
       <c r="J37" t="n">
-        <v>218.78</v>
+        <v>804.4</v>
       </c>
       <c r="K37" t="n">
-        <v>184.87</v>
+        <v>713.72</v>
       </c>
       <c r="L37" t="n">
-        <v>262.39</v>
+        <v>921</v>
       </c>
       <c r="M37" t="n">
-        <v>75.42</v>
+        <v>82.06</v>
       </c>
       <c r="N37" t="inlineStr">
         <is>
@@ -2570,7 +2594,7 @@
       <c r="O37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>NO COMPRAR</t>
+          <t>VIGILAR</t>
         </is>
       </c>
     </row>

--- a/analisis_acciones.xlsx
+++ b/analisis_acciones.xlsx
@@ -510,41 +510,41 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>235.61</v>
+        <v>228.06</v>
       </c>
       <c r="D2" t="n">
         <v>95</v>
       </c>
       <c r="E2" t="n">
-        <v>11.4</v>
+        <v>5.98</v>
       </c>
       <c r="F2" t="n">
-        <v>0.98</v>
+        <v>0.83</v>
       </c>
       <c r="G2" t="n">
-        <v>8.07</v>
+        <v>8.210000000000001</v>
       </c>
       <c r="H2" t="n">
-        <v>3.42</v>
+        <v>3.6</v>
       </c>
       <c r="I2" t="n">
-        <v>232.38</v>
+        <v>224.78</v>
       </c>
       <c r="J2" t="n">
-        <v>237.63</v>
+        <v>230.11</v>
       </c>
       <c r="K2" t="n">
-        <v>223.51</v>
+        <v>215.74</v>
       </c>
       <c r="L2" t="n">
-        <v>255.77</v>
+        <v>248.59</v>
       </c>
       <c r="M2" t="n">
-        <v>70.22</v>
+        <v>58.53</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>MEDIO</t>
+          <t>BAJO</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -561,50 +561,50 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AVGO</t>
+          <t>AMAT</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>IA / Chips</t>
+          <t>Equipos chips</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>441.21</v>
+        <v>441.09</v>
       </c>
       <c r="D3" t="n">
         <v>95</v>
       </c>
       <c r="E3" t="n">
-        <v>6.94</v>
+        <v>1.3</v>
       </c>
       <c r="F3" t="n">
-        <v>0.73</v>
+        <v>1.26</v>
       </c>
       <c r="G3" t="n">
-        <v>16.29</v>
+        <v>18.71</v>
       </c>
       <c r="H3" t="n">
-        <v>3.69</v>
+        <v>4.24</v>
       </c>
       <c r="I3" t="n">
-        <v>434.69</v>
+        <v>433.61</v>
       </c>
       <c r="J3" t="n">
-        <v>445.28</v>
+        <v>445.77</v>
       </c>
       <c r="K3" t="n">
-        <v>416.77</v>
+        <v>413.03</v>
       </c>
       <c r="L3" t="n">
-        <v>481.94</v>
+        <v>487.86</v>
       </c>
       <c r="M3" t="n">
-        <v>57.1</v>
+        <v>61.66</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>MEDIO</t>
+          <t>BAJO</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -621,46 +621,46 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ASML</t>
+          <t>CVX</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Chips</t>
+          <t>Energía</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1595.13</v>
+        <v>190.26</v>
       </c>
       <c r="D4" t="n">
         <v>95</v>
       </c>
       <c r="E4" t="n">
-        <v>5.18</v>
+        <v>4.76</v>
       </c>
       <c r="F4" t="n">
-        <v>0.66</v>
+        <v>0.58</v>
       </c>
       <c r="G4" t="n">
-        <v>61.67</v>
+        <v>4.25</v>
       </c>
       <c r="H4" t="n">
-        <v>3.87</v>
+        <v>2.23</v>
       </c>
       <c r="I4" t="n">
-        <v>1570.46</v>
+        <v>188.56</v>
       </c>
       <c r="J4" t="n">
-        <v>1610.55</v>
+        <v>191.32</v>
       </c>
       <c r="K4" t="n">
-        <v>1502.62</v>
+        <v>183.89</v>
       </c>
       <c r="L4" t="n">
-        <v>1749.31</v>
+        <v>200.88</v>
       </c>
       <c r="M4" t="n">
-        <v>62.03</v>
+        <v>58.33</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -681,46 +681,46 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AMAT</t>
+          <t>XOM</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Equipos chips</t>
+          <t>Energía</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>445.04</v>
+        <v>157.05</v>
       </c>
       <c r="D5" t="n">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E5" t="n">
-        <v>8.380000000000001</v>
+        <v>8.630000000000001</v>
       </c>
       <c r="F5" t="n">
-        <v>1.11</v>
+        <v>0.86</v>
       </c>
       <c r="G5" t="n">
-        <v>18.68</v>
+        <v>3.94</v>
       </c>
       <c r="H5" t="n">
-        <v>4.2</v>
+        <v>2.51</v>
       </c>
       <c r="I5" t="n">
-        <v>437.57</v>
+        <v>155.47</v>
       </c>
       <c r="J5" t="n">
-        <v>449.71</v>
+        <v>158.04</v>
       </c>
       <c r="K5" t="n">
-        <v>417.02</v>
+        <v>151.14</v>
       </c>
       <c r="L5" t="n">
-        <v>491.73</v>
+        <v>166.9</v>
       </c>
       <c r="M5" t="n">
-        <v>58.16</v>
+        <v>63.3</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
@@ -741,46 +741,46 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>LRCX</t>
+          <t>SLB</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Equipos chips</t>
+          <t>Energía</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>300.22</v>
+        <v>55.49</v>
       </c>
       <c r="D6" t="n">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="E6" t="n">
-        <v>4.78</v>
+        <v>4.18</v>
       </c>
       <c r="F6" t="n">
-        <v>0.36</v>
+        <v>0.45</v>
       </c>
       <c r="G6" t="n">
-        <v>13.25</v>
+        <v>1.44</v>
       </c>
       <c r="H6" t="n">
-        <v>4.41</v>
+        <v>2.59</v>
       </c>
       <c r="I6" t="n">
-        <v>294.92</v>
+        <v>54.92</v>
       </c>
       <c r="J6" t="n">
-        <v>303.53</v>
+        <v>55.85</v>
       </c>
       <c r="K6" t="n">
-        <v>280.35</v>
+        <v>53.34</v>
       </c>
       <c r="L6" t="n">
-        <v>333.34</v>
+        <v>59.08</v>
       </c>
       <c r="M6" t="n">
-        <v>65.06</v>
+        <v>51.34</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
@@ -801,46 +801,46 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>XOM</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Energía</t>
+          <t>Tecnología</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>152.6</v>
+        <v>425.05</v>
       </c>
       <c r="D7" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="E7" t="n">
-        <v>4.11</v>
+        <v>2.39</v>
       </c>
       <c r="F7" t="n">
-        <v>0.39</v>
+        <v>1.03</v>
       </c>
       <c r="G7" t="n">
-        <v>3.86</v>
+        <v>11.41</v>
       </c>
       <c r="H7" t="n">
-        <v>2.53</v>
+        <v>2.68</v>
       </c>
       <c r="I7" t="n">
-        <v>151.06</v>
+        <v>420.49</v>
       </c>
       <c r="J7" t="n">
-        <v>153.57</v>
+        <v>427.9</v>
       </c>
       <c r="K7" t="n">
-        <v>146.82</v>
+        <v>407.94</v>
       </c>
       <c r="L7" t="n">
-        <v>162.24</v>
+        <v>453.57</v>
       </c>
       <c r="M7" t="n">
-        <v>56.24</v>
+        <v>50.14</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -861,46 +861,46 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SOXX</t>
+          <t>OXY</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>ETF Chips</t>
+          <t>Energía</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>532.11</v>
+        <v>59.08</v>
       </c>
       <c r="D8" t="n">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="E8" t="n">
-        <v>8.07</v>
+        <v>11.41</v>
       </c>
       <c r="F8" t="n">
-        <v>0.6</v>
+        <v>0.93</v>
       </c>
       <c r="G8" t="n">
-        <v>18.48</v>
+        <v>1.97</v>
       </c>
       <c r="H8" t="n">
-        <v>3.47</v>
+        <v>3.33</v>
       </c>
       <c r="I8" t="n">
-        <v>524.72</v>
+        <v>58.29</v>
       </c>
       <c r="J8" t="n">
-        <v>536.73</v>
+        <v>59.57</v>
       </c>
       <c r="K8" t="n">
-        <v>504.39</v>
+        <v>56.13</v>
       </c>
       <c r="L8" t="n">
-        <v>578.3099999999999</v>
+        <v>64</v>
       </c>
       <c r="M8" t="n">
-        <v>68.93000000000001</v>
+        <v>54.4</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
@@ -921,46 +921,46 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>KLAC</t>
+          <t>SPY</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Equipos chips</t>
+          <t>ETF Mercado</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1902.8</v>
+        <v>740.63</v>
       </c>
       <c r="D9" t="n">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="E9" t="n">
-        <v>7.91</v>
+        <v>0.41</v>
       </c>
       <c r="F9" t="n">
-        <v>0.49</v>
+        <v>0.77</v>
       </c>
       <c r="G9" t="n">
-        <v>85.70999999999999</v>
+        <v>7.2</v>
       </c>
       <c r="H9" t="n">
-        <v>4.5</v>
+        <v>0.97</v>
       </c>
       <c r="I9" t="n">
-        <v>1868.51</v>
+        <v>737.75</v>
       </c>
       <c r="J9" t="n">
-        <v>1924.22</v>
+        <v>742.4299999999999</v>
       </c>
       <c r="K9" t="n">
-        <v>1774.23</v>
+        <v>729.83</v>
       </c>
       <c r="L9" t="n">
-        <v>2117.06</v>
+        <v>758.64</v>
       </c>
       <c r="M9" t="n">
-        <v>47.51</v>
+        <v>71.31</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -981,7 +981,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>INTC</t>
+          <t>ASML</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -990,46 +990,46 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>116.06</v>
+        <v>1513.92</v>
       </c>
       <c r="D10" t="n">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="E10" t="n">
-        <v>5.87</v>
+        <v>-4.91</v>
       </c>
       <c r="F10" t="n">
-        <v>0.63</v>
+        <v>0.8</v>
       </c>
       <c r="G10" t="n">
-        <v>8.74</v>
+        <v>65.62</v>
       </c>
       <c r="H10" t="n">
-        <v>7.53</v>
+        <v>4.33</v>
       </c>
       <c r="I10" t="n">
-        <v>112.56</v>
+        <v>1487.67</v>
       </c>
       <c r="J10" t="n">
-        <v>118.24</v>
+        <v>1530.32</v>
       </c>
       <c r="K10" t="n">
-        <v>102.95</v>
+        <v>1415.5</v>
       </c>
       <c r="L10" t="n">
-        <v>137.91</v>
+        <v>1677.96</v>
       </c>
       <c r="M10" t="n">
-        <v>71.98999999999999</v>
+        <v>56.55</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>MEDIO</t>
+          <t>BAJO</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1041,55 +1041,55 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>LRCX</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>IA / Chips</t>
+          <t>Equipos chips</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>449.41</v>
+        <v>286.91</v>
       </c>
       <c r="D11" t="n">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="E11" t="n">
-        <v>10.03</v>
+        <v>-2.43</v>
       </c>
       <c r="F11" t="n">
-        <v>0.45</v>
+        <v>0.66</v>
       </c>
       <c r="G11" t="n">
-        <v>27.34</v>
+        <v>13.74</v>
       </c>
       <c r="H11" t="n">
-        <v>6.08</v>
+        <v>4.79</v>
       </c>
       <c r="I11" t="n">
-        <v>438.48</v>
+        <v>281.42</v>
       </c>
       <c r="J11" t="n">
-        <v>456.24</v>
+        <v>290.34</v>
       </c>
       <c r="K11" t="n">
-        <v>408.4</v>
+        <v>266.31</v>
       </c>
       <c r="L11" t="n">
-        <v>517.75</v>
+        <v>321.25</v>
       </c>
       <c r="M11" t="n">
-        <v>71.06</v>
+        <v>62.41</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>MEDIO</t>
+          <t>BAJO</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1101,46 +1101,46 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SLB</t>
+          <t>SOXX</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Energía</t>
+          <t>ETF Chips</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>55.74</v>
+        <v>513.9</v>
       </c>
       <c r="D12" t="n">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="E12" t="n">
-        <v>5.18</v>
+        <v>-1.23</v>
       </c>
       <c r="F12" t="n">
-        <v>0.22</v>
+        <v>0.93</v>
       </c>
       <c r="G12" t="n">
-        <v>1.5</v>
+        <v>19.17</v>
       </c>
       <c r="H12" t="n">
-        <v>2.69</v>
+        <v>3.73</v>
       </c>
       <c r="I12" t="n">
-        <v>55.15</v>
+        <v>506.23</v>
       </c>
       <c r="J12" t="n">
-        <v>56.12</v>
+        <v>518.6900000000001</v>
       </c>
       <c r="K12" t="n">
-        <v>53.5</v>
+        <v>485.14</v>
       </c>
       <c r="L12" t="n">
-        <v>59.49</v>
+        <v>561.83</v>
       </c>
       <c r="M12" t="n">
-        <v>48.08</v>
+        <v>65.06999999999999</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
@@ -1149,7 +1149,7 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1161,46 +1161,46 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>AVGO</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Chips</t>
+          <t>IA / Chips</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>420.31</v>
+        <v>426.39</v>
       </c>
       <c r="D13" t="n">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="E13" t="n">
-        <v>1.49</v>
+        <v>-0.84</v>
       </c>
       <c r="F13" t="n">
-        <v>1.06</v>
+        <v>0.58</v>
       </c>
       <c r="G13" t="n">
-        <v>15.26</v>
+        <v>17.05</v>
       </c>
       <c r="H13" t="n">
-        <v>3.63</v>
+        <v>4</v>
       </c>
       <c r="I13" t="n">
-        <v>414.21</v>
+        <v>419.56</v>
       </c>
       <c r="J13" t="n">
-        <v>424.12</v>
+        <v>430.65</v>
       </c>
       <c r="K13" t="n">
-        <v>397.42</v>
+        <v>400.8</v>
       </c>
       <c r="L13" t="n">
-        <v>458.45</v>
+        <v>469.02</v>
       </c>
       <c r="M13" t="n">
-        <v>58.75</v>
+        <v>52.98</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
@@ -1221,46 +1221,46 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>AMZN</t>
+          <t>TSM</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Tecnología</t>
+          <t>Chips</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>268.05</v>
+        <v>406.54</v>
       </c>
       <c r="D14" t="n">
         <v>84</v>
       </c>
       <c r="E14" t="n">
-        <v>-1.15</v>
+        <v>-1.25</v>
       </c>
       <c r="F14" t="n">
-        <v>0.45</v>
+        <v>0.61</v>
       </c>
       <c r="G14" t="n">
-        <v>6.98</v>
+        <v>15.44</v>
       </c>
       <c r="H14" t="n">
-        <v>2.6</v>
+        <v>3.8</v>
       </c>
       <c r="I14" t="n">
-        <v>265.26</v>
+        <v>400.36</v>
       </c>
       <c r="J14" t="n">
-        <v>269.79</v>
+        <v>410.4</v>
       </c>
       <c r="K14" t="n">
-        <v>257.58</v>
+        <v>383.38</v>
       </c>
       <c r="L14" t="n">
-        <v>285.5</v>
+        <v>445.14</v>
       </c>
       <c r="M14" t="n">
-        <v>55.32</v>
+        <v>50.72</v>
       </c>
       <c r="N14" t="inlineStr">
         <is>
@@ -1281,46 +1281,46 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>SMCI</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Servidores IA</t>
+          <t>IA / Chips</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>32.75</v>
+        <v>430.61</v>
       </c>
       <c r="D15" t="n">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="E15" t="n">
-        <v>-2.59</v>
+        <v>-5.4</v>
       </c>
       <c r="F15" t="n">
-        <v>0.72</v>
+        <v>0.42</v>
       </c>
       <c r="G15" t="n">
-        <v>2.26</v>
+        <v>27.56</v>
       </c>
       <c r="H15" t="n">
-        <v>6.91</v>
+        <v>6.4</v>
       </c>
       <c r="I15" t="n">
-        <v>31.85</v>
+        <v>419.59</v>
       </c>
       <c r="J15" t="n">
-        <v>33.32</v>
+        <v>437.5</v>
       </c>
       <c r="K15" t="n">
-        <v>29.36</v>
+        <v>389.27</v>
       </c>
       <c r="L15" t="n">
-        <v>38.41</v>
+        <v>499.51</v>
       </c>
       <c r="M15" t="n">
-        <v>59.76</v>
+        <v>69.39</v>
       </c>
       <c r="N15" t="inlineStr">
         <is>
@@ -1337,458 +1337,446 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>CVX</t>
+          <t>MU</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Energía</t>
+          <t>Memoria / Chips</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>186.5</v>
+        <v>735.9299999999999</v>
       </c>
       <c r="D16" t="n">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="E16" t="n">
-        <v>2.19</v>
+        <v>-1.46</v>
       </c>
       <c r="F16" t="n">
-        <v>0.35</v>
+        <v>0.8</v>
       </c>
       <c r="G16" t="n">
-        <v>4.31</v>
+        <v>53.45</v>
       </c>
       <c r="H16" t="n">
-        <v>2.31</v>
+        <v>7.26</v>
       </c>
       <c r="I16" t="n">
-        <v>184.77</v>
+        <v>714.55</v>
       </c>
       <c r="J16" t="n">
-        <v>187.57</v>
+        <v>749.29</v>
       </c>
       <c r="K16" t="n">
-        <v>180.03</v>
+        <v>655.76</v>
       </c>
       <c r="L16" t="n">
-        <v>197.28</v>
+        <v>869.54</v>
       </c>
       <c r="M16" t="n">
-        <v>52.18</v>
+        <v>71.69</v>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>BAJO</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>🔥</t>
-        </is>
-      </c>
+          <t>MEDIO</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>VIGILAR</t>
+          <t>POSIBLE COMPRA</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>ARM</t>
+          <t>TSLA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Chips</t>
+          <t>Autos / Tech</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>225.73</v>
+        <v>425.06</v>
       </c>
       <c r="D17" t="n">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="E17" t="n">
-        <v>5.82</v>
+        <v>-0.77</v>
       </c>
       <c r="F17" t="n">
-        <v>0.57</v>
+        <v>0.67</v>
       </c>
       <c r="G17" t="n">
-        <v>16.35</v>
+        <v>17.19</v>
       </c>
       <c r="H17" t="n">
-        <v>7.24</v>
+        <v>4.04</v>
       </c>
       <c r="I17" t="n">
-        <v>219.19</v>
+        <v>418.19</v>
       </c>
       <c r="J17" t="n">
-        <v>229.82</v>
+        <v>429.36</v>
       </c>
       <c r="K17" t="n">
-        <v>201.2</v>
+        <v>399.28</v>
       </c>
       <c r="L17" t="n">
-        <v>266.61</v>
+        <v>468.03</v>
       </c>
       <c r="M17" t="n">
-        <v>46.71</v>
+        <v>68.13</v>
       </c>
       <c r="N17" t="inlineStr">
         <is>
           <t>MEDIO</t>
         </is>
       </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>🔥</t>
-        </is>
-      </c>
+      <c r="O17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>VIGILAR</t>
+          <t>POSIBLE COMPRA</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>HOOD</t>
+          <t>AMZN</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Trading</t>
+          <t>Tecnología</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>81.04000000000001</v>
+        <v>263.11</v>
       </c>
       <c r="D18" t="n">
-        <v>62</v>
+        <v>76</v>
       </c>
       <c r="E18" t="n">
-        <v>6.24</v>
+        <v>-3.51</v>
       </c>
       <c r="F18" t="n">
-        <v>0.77</v>
+        <v>0.65</v>
       </c>
       <c r="G18" t="n">
-        <v>4.32</v>
+        <v>7.19</v>
       </c>
       <c r="H18" t="n">
-        <v>5.33</v>
+        <v>2.73</v>
       </c>
       <c r="I18" t="n">
-        <v>79.31</v>
+        <v>260.23</v>
       </c>
       <c r="J18" t="n">
-        <v>82.12</v>
+        <v>264.91</v>
       </c>
       <c r="K18" t="n">
-        <v>74.56</v>
+        <v>252.33</v>
       </c>
       <c r="L18" t="n">
-        <v>91.84999999999999</v>
+        <v>281.08</v>
       </c>
       <c r="M18" t="n">
-        <v>45.03</v>
+        <v>52.47</v>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>MEDIO</t>
-        </is>
-      </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>🔥</t>
-        </is>
-      </c>
+          <t>BAJO</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>VIGILAR</t>
+          <t>POSIBLE COMPRA</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>OXY</t>
+          <t>SMCI</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Energía</t>
+          <t>Servidores IA</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>56.9</v>
+        <v>31.09</v>
       </c>
       <c r="D19" t="n">
-        <v>62</v>
+        <v>76</v>
       </c>
       <c r="E19" t="n">
-        <v>5.5</v>
+        <v>-12.09</v>
       </c>
       <c r="F19" t="n">
-        <v>0.5</v>
+        <v>0.52</v>
       </c>
       <c r="G19" t="n">
-        <v>1.87</v>
+        <v>2.29</v>
       </c>
       <c r="H19" t="n">
-        <v>3.28</v>
+        <v>7.36</v>
       </c>
       <c r="I19" t="n">
-        <v>56.16</v>
+        <v>30.18</v>
       </c>
       <c r="J19" t="n">
-        <v>57.37</v>
+        <v>31.67</v>
       </c>
       <c r="K19" t="n">
-        <v>54.11</v>
+        <v>27.66</v>
       </c>
       <c r="L19" t="n">
-        <v>61.57</v>
+        <v>36.81</v>
       </c>
       <c r="M19" t="n">
-        <v>49.42</v>
+        <v>58.2</v>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>BAJO</t>
-        </is>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>🔥</t>
-        </is>
-      </c>
+          <t>MEDIO</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>VIGILAR</t>
+          <t>POSIBLE COMPRA</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>AI</t>
+          <t>UPST</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>IA</t>
+          <t>Fintech IA</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>8.970000000000001</v>
+        <v>29.88</v>
       </c>
       <c r="D20" t="n">
-        <v>66</v>
+        <v>46</v>
       </c>
       <c r="E20" t="n">
-        <v>-6.4</v>
+        <v>3.18</v>
       </c>
       <c r="F20" t="n">
-        <v>0.93</v>
+        <v>0.95</v>
       </c>
       <c r="G20" t="n">
-        <v>0.45</v>
+        <v>1.9</v>
       </c>
       <c r="H20" t="n">
-        <v>4.97</v>
+        <v>6.34</v>
       </c>
       <c r="I20" t="n">
-        <v>8.789999999999999</v>
+        <v>29.12</v>
       </c>
       <c r="J20" t="n">
-        <v>9.08</v>
+        <v>30.35</v>
       </c>
       <c r="K20" t="n">
-        <v>8.300000000000001</v>
+        <v>27.04</v>
       </c>
       <c r="L20" t="n">
-        <v>10.08</v>
+        <v>34.62</v>
       </c>
       <c r="M20" t="n">
-        <v>55.29</v>
+        <v>38.57</v>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>BAJO</t>
-        </is>
-      </c>
-      <c r="O20" t="inlineStr"/>
+          <t>MEDIO</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>🔥</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>VIGILAR</t>
+          <t>NO COMPRAR</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>SOUN</t>
+          <t>KLAC</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>IA</t>
+          <t>Equipos chips</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>8.359999999999999</v>
+        <v>1824.25</v>
       </c>
       <c r="D21" t="n">
-        <v>58</v>
+        <v>72</v>
       </c>
       <c r="E21" t="n">
-        <v>-13.19</v>
+        <v>-2.4</v>
       </c>
       <c r="F21" t="n">
-        <v>0.41</v>
+        <v>0.51</v>
       </c>
       <c r="G21" t="n">
-        <v>0.64</v>
+        <v>87.39</v>
       </c>
       <c r="H21" t="n">
-        <v>7.66</v>
+        <v>4.79</v>
       </c>
       <c r="I21" t="n">
-        <v>8.1</v>
+        <v>1789.29</v>
       </c>
       <c r="J21" t="n">
-        <v>8.52</v>
+        <v>1846.1</v>
       </c>
       <c r="K21" t="n">
-        <v>7.4</v>
+        <v>1693.17</v>
       </c>
       <c r="L21" t="n">
-        <v>9.960000000000001</v>
+        <v>2042.72</v>
       </c>
       <c r="M21" t="n">
-        <v>51.63</v>
+        <v>44.36</v>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>MEDIO</t>
+          <t>BAJO</t>
         </is>
       </c>
       <c r="O21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>NO COMPRAR</t>
+          <t>VIGILAR</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>META</t>
+          <t>ARM</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Tecnología</t>
+          <t>Chips</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>617.3</v>
+        <v>209.91</v>
       </c>
       <c r="D22" t="n">
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="E22" t="n">
-        <v>0.08</v>
+        <v>-1.57</v>
       </c>
       <c r="F22" t="n">
-        <v>0.51</v>
+        <v>0.67</v>
       </c>
       <c r="G22" t="n">
-        <v>17.26</v>
+        <v>16.2</v>
       </c>
       <c r="H22" t="n">
-        <v>2.8</v>
+        <v>7.72</v>
       </c>
       <c r="I22" t="n">
-        <v>610.4</v>
+        <v>203.43</v>
       </c>
       <c r="J22" t="n">
-        <v>621.62</v>
+        <v>213.97</v>
       </c>
       <c r="K22" t="n">
-        <v>591.42</v>
+        <v>185.61</v>
       </c>
       <c r="L22" t="n">
-        <v>660.45</v>
+        <v>250.43</v>
       </c>
       <c r="M22" t="n">
-        <v>27.59</v>
+        <v>47.87</v>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>BAJO</t>
+          <t>MEDIO</t>
         </is>
       </c>
       <c r="O22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>NO COMPRAR</t>
+          <t>VIGILAR</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>SOUN</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Tecnología</t>
+          <t>IA</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>409.6</v>
+        <v>8.5</v>
       </c>
       <c r="D23" t="n">
-        <v>46</v>
+        <v>58</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.66</v>
+        <v>-4.28</v>
       </c>
       <c r="F23" t="n">
-        <v>0.54</v>
+        <v>0.44</v>
       </c>
       <c r="G23" t="n">
-        <v>10.79</v>
+        <v>0.66</v>
       </c>
       <c r="H23" t="n">
-        <v>2.63</v>
+        <v>7.77</v>
       </c>
       <c r="I23" t="n">
-        <v>405.28</v>
+        <v>8.24</v>
       </c>
       <c r="J23" t="n">
-        <v>412.29</v>
+        <v>8.67</v>
       </c>
       <c r="K23" t="n">
-        <v>393.41</v>
+        <v>7.51</v>
       </c>
       <c r="L23" t="n">
-        <v>436.57</v>
+        <v>10.15</v>
       </c>
       <c r="M23" t="n">
-        <v>38.47</v>
+        <v>53.23</v>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>BAJO</t>
+          <t>MEDIO</t>
         </is>
       </c>
       <c r="O23" t="inlineStr"/>
@@ -1801,50 +1789,50 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>PYPL</t>
+          <t>COIN</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Pagos</t>
+          <t>Cripto / Trading</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>45.13</v>
+        <v>196.29</v>
       </c>
       <c r="D24" t="n">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.35</v>
+        <v>-2.42</v>
       </c>
       <c r="F24" t="n">
-        <v>0.43</v>
+        <v>1.1</v>
       </c>
       <c r="G24" t="n">
-        <v>1.55</v>
+        <v>14.49</v>
       </c>
       <c r="H24" t="n">
-        <v>3.44</v>
+        <v>7.38</v>
       </c>
       <c r="I24" t="n">
-        <v>44.51</v>
+        <v>190.49</v>
       </c>
       <c r="J24" t="n">
-        <v>45.52</v>
+        <v>199.91</v>
       </c>
       <c r="K24" t="n">
-        <v>42.8</v>
+        <v>174.56</v>
       </c>
       <c r="L24" t="n">
-        <v>49.02</v>
+        <v>232.5</v>
       </c>
       <c r="M24" t="n">
-        <v>21.22</v>
+        <v>49.82</v>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>BAJO</t>
+          <t>MEDIO</t>
         </is>
       </c>
       <c r="O24" t="inlineStr"/>
@@ -1857,50 +1845,50 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>UPST</t>
+          <t>META</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Fintech IA</t>
+          <t>Tecnología</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>29.23</v>
+        <v>616.74</v>
       </c>
       <c r="D25" t="n">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="E25" t="n">
-        <v>0.79</v>
+        <v>1.17</v>
       </c>
       <c r="F25" t="n">
-        <v>0.71</v>
+        <v>0.54</v>
       </c>
       <c r="G25" t="n">
-        <v>1.78</v>
+        <v>17.27</v>
       </c>
       <c r="H25" t="n">
-        <v>6.09</v>
+        <v>2.8</v>
       </c>
       <c r="I25" t="n">
-        <v>28.52</v>
+        <v>609.83</v>
       </c>
       <c r="J25" t="n">
-        <v>29.67</v>
+        <v>621.0599999999999</v>
       </c>
       <c r="K25" t="n">
-        <v>26.56</v>
+        <v>590.83</v>
       </c>
       <c r="L25" t="n">
-        <v>33.68</v>
+        <v>659.92</v>
       </c>
       <c r="M25" t="n">
-        <v>34.63</v>
+        <v>25.84</v>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>MEDIO</t>
+          <t>BAJO</t>
         </is>
       </c>
       <c r="O25" t="inlineStr"/>
@@ -1913,46 +1901,46 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>SOFI</t>
+          <t>HOOD</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Fintech</t>
+          <t>Trading</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>15.88</v>
+        <v>77.34999999999999</v>
       </c>
       <c r="D26" t="n">
-        <v>38</v>
+        <v>54</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.78</v>
+        <v>0.42</v>
       </c>
       <c r="F26" t="n">
-        <v>0.75</v>
+        <v>0.54</v>
       </c>
       <c r="G26" t="n">
-        <v>0.83</v>
+        <v>4.44</v>
       </c>
       <c r="H26" t="n">
-        <v>5.21</v>
+        <v>5.75</v>
       </c>
       <c r="I26" t="n">
-        <v>15.54</v>
+        <v>75.56999999999999</v>
       </c>
       <c r="J26" t="n">
-        <v>16.08</v>
+        <v>78.45999999999999</v>
       </c>
       <c r="K26" t="n">
-        <v>14.64</v>
+        <v>70.68000000000001</v>
       </c>
       <c r="L26" t="n">
-        <v>17.94</v>
+        <v>88.45999999999999</v>
       </c>
       <c r="M26" t="n">
-        <v>33.4</v>
+        <v>41.58</v>
       </c>
       <c r="N26" t="inlineStr">
         <is>
@@ -1969,46 +1957,46 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>PLTR</t>
+          <t>PYPL</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>IA / Software</t>
+          <t>Pagos</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>133.52</v>
+        <v>44.62</v>
       </c>
       <c r="D27" t="n">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="E27" t="n">
-        <v>-2.58</v>
+        <v>-1.65</v>
       </c>
       <c r="F27" t="n">
-        <v>0.67</v>
+        <v>0.66</v>
       </c>
       <c r="G27" t="n">
-        <v>5.77</v>
+        <v>1.52</v>
       </c>
       <c r="H27" t="n">
-        <v>4.32</v>
+        <v>3.4</v>
       </c>
       <c r="I27" t="n">
-        <v>131.21</v>
+        <v>44.01</v>
       </c>
       <c r="J27" t="n">
-        <v>134.96</v>
+        <v>45</v>
       </c>
       <c r="K27" t="n">
-        <v>124.86</v>
+        <v>42.34</v>
       </c>
       <c r="L27" t="n">
-        <v>147.95</v>
+        <v>48.42</v>
       </c>
       <c r="M27" t="n">
-        <v>38.23</v>
+        <v>21.67</v>
       </c>
       <c r="N27" t="inlineStr">
         <is>
@@ -2025,226 +2013,214 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>COIN</t>
+          <t>AI</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Cripto / Trading</t>
+          <t>IA</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>216.42</v>
+        <v>8.67</v>
       </c>
       <c r="D28" t="n">
-        <v>85</v>
+        <v>46</v>
       </c>
       <c r="E28" t="n">
-        <v>12.16</v>
+        <v>-12.16</v>
       </c>
       <c r="F28" t="n">
-        <v>1.34</v>
+        <v>0.8</v>
       </c>
       <c r="G28" t="n">
-        <v>13.74</v>
+        <v>0.45</v>
       </c>
       <c r="H28" t="n">
-        <v>6.35</v>
+        <v>5.21</v>
       </c>
       <c r="I28" t="n">
-        <v>210.92</v>
+        <v>8.49</v>
       </c>
       <c r="J28" t="n">
-        <v>219.85</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="K28" t="n">
-        <v>195.81</v>
+        <v>7.99</v>
       </c>
       <c r="L28" t="n">
-        <v>250.77</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="M28" t="n">
-        <v>58.1</v>
+        <v>48.21</v>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>ALTO</t>
-        </is>
-      </c>
-      <c r="O28" t="inlineStr">
-        <is>
-          <t>🔥🔥</t>
-        </is>
-      </c>
+          <t>MEDIO</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>VIGILAR</t>
+          <t>NO COMPRAR</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>PLTR</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Tecnología</t>
+          <t>IA / Software</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>298.99</v>
+        <v>134.47</v>
       </c>
       <c r="D29" t="n">
-        <v>86</v>
+        <v>36</v>
       </c>
       <c r="E29" t="n">
-        <v>4.12</v>
+        <v>-2.42</v>
       </c>
       <c r="F29" t="n">
-        <v>0.49</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="G29" t="n">
-        <v>6.61</v>
+        <v>5.72</v>
       </c>
       <c r="H29" t="n">
-        <v>2.21</v>
+        <v>4.25</v>
       </c>
       <c r="I29" t="n">
-        <v>296.35</v>
+        <v>132.18</v>
       </c>
       <c r="J29" t="n">
-        <v>300.65</v>
+        <v>135.9</v>
       </c>
       <c r="K29" t="n">
-        <v>289.09</v>
+        <v>125.89</v>
       </c>
       <c r="L29" t="n">
-        <v>315.51</v>
+        <v>148.77</v>
       </c>
       <c r="M29" t="n">
-        <v>82.28</v>
+        <v>39.63</v>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>ALTO</t>
-        </is>
-      </c>
-      <c r="O29" t="inlineStr">
-        <is>
-          <t>🔥</t>
-        </is>
-      </c>
+          <t>BAJO</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>VIGILAR</t>
+          <t>NO COMPRAR</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>SPY</t>
+          <t>SOFI</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>ETF Mercado</t>
+          <t>Fintech</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>748.45</v>
+        <v>15.7</v>
       </c>
       <c r="D30" t="n">
-        <v>82</v>
+        <v>28</v>
       </c>
       <c r="E30" t="n">
-        <v>2.31</v>
+        <v>-0.29</v>
       </c>
       <c r="F30" t="n">
-        <v>0.64</v>
+        <v>0.59</v>
       </c>
       <c r="G30" t="n">
-        <v>6.71</v>
+        <v>0.82</v>
       </c>
       <c r="H30" t="n">
-        <v>0.9</v>
+        <v>5.2</v>
       </c>
       <c r="I30" t="n">
-        <v>745.77</v>
+        <v>15.38</v>
       </c>
       <c r="J30" t="n">
-        <v>750.13</v>
+        <v>15.91</v>
       </c>
       <c r="K30" t="n">
-        <v>738.38</v>
+        <v>14.48</v>
       </c>
       <c r="L30" t="n">
-        <v>765.23</v>
+        <v>17.75</v>
       </c>
       <c r="M30" t="n">
-        <v>82.13</v>
+        <v>30.58</v>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>ALTO</t>
-        </is>
-      </c>
-      <c r="O30" t="inlineStr">
-        <is>
-          <t>🔥</t>
-        </is>
-      </c>
+          <t>MEDIO</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>VIGILAR</t>
+          <t>NO COMPRAR</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>QQQ</t>
+          <t>AAPL</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>ETF Nasdaq</t>
+          <t>Tecnología</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>720.47</v>
+        <v>301.28</v>
       </c>
       <c r="D31" t="n">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="E31" t="n">
-        <v>3.67</v>
+        <v>2.81</v>
       </c>
       <c r="F31" t="n">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="G31" t="n">
-        <v>9.9</v>
+        <v>6.66</v>
       </c>
       <c r="H31" t="n">
-        <v>1.37</v>
+        <v>2.21</v>
       </c>
       <c r="I31" t="n">
-        <v>716.51</v>
+        <v>298.61</v>
       </c>
       <c r="J31" t="n">
-        <v>722.95</v>
+        <v>302.94</v>
       </c>
       <c r="K31" t="n">
-        <v>705.62</v>
+        <v>291.28</v>
       </c>
       <c r="L31" t="n">
-        <v>745.22</v>
+        <v>317.93</v>
       </c>
       <c r="M31" t="n">
-        <v>82.81</v>
+        <v>88.70999999999999</v>
       </c>
       <c r="N31" t="inlineStr">
         <is>
@@ -2265,53 +2241,57 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>GOOGL</t>
+          <t>RKLB</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Tecnología</t>
+          <t>Espacial</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>401.02</v>
+        <v>126.83</v>
       </c>
       <c r="D32" t="n">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="E32" t="n">
-        <v>0.76</v>
+        <v>20.26</v>
       </c>
       <c r="F32" t="n">
-        <v>0.59</v>
+        <v>0.66</v>
       </c>
       <c r="G32" t="n">
-        <v>11.26</v>
+        <v>9.65</v>
       </c>
       <c r="H32" t="n">
-        <v>2.81</v>
+        <v>7.61</v>
       </c>
       <c r="I32" t="n">
-        <v>396.52</v>
+        <v>122.97</v>
       </c>
       <c r="J32" t="n">
-        <v>403.83</v>
+        <v>129.24</v>
       </c>
       <c r="K32" t="n">
-        <v>384.14</v>
+        <v>112.36</v>
       </c>
       <c r="L32" t="n">
-        <v>429.16</v>
+        <v>150.95</v>
       </c>
       <c r="M32" t="n">
-        <v>80.5</v>
+        <v>74.98</v>
       </c>
       <c r="N32" t="inlineStr">
         <is>
           <t>ALTO</t>
         </is>
       </c>
-      <c r="O32" t="inlineStr"/>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>🔥</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>VIGILAR</t>
@@ -2321,53 +2301,57 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>TSLA</t>
+          <t>IONQ</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Autos / Tech</t>
+          <t>Computación cuántica</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>444.58</v>
+        <v>52.5</v>
       </c>
       <c r="D33" t="n">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="E33" t="n">
-        <v>7.96</v>
+        <v>6.62</v>
       </c>
       <c r="F33" t="n">
-        <v>0.64</v>
+        <v>0.63</v>
       </c>
       <c r="G33" t="n">
-        <v>16.96</v>
+        <v>4.72</v>
       </c>
       <c r="H33" t="n">
-        <v>3.82</v>
+        <v>8.98</v>
       </c>
       <c r="I33" t="n">
-        <v>437.79</v>
+        <v>50.61</v>
       </c>
       <c r="J33" t="n">
-        <v>448.82</v>
+        <v>53.68</v>
       </c>
       <c r="K33" t="n">
-        <v>419.13</v>
+        <v>45.42</v>
       </c>
       <c r="L33" t="n">
-        <v>486.99</v>
+        <v>64.29000000000001</v>
       </c>
       <c r="M33" t="n">
-        <v>80.81999999999999</v>
+        <v>62.03</v>
       </c>
       <c r="N33" t="inlineStr">
         <is>
           <t>ALTO</t>
         </is>
       </c>
-      <c r="O33" t="inlineStr"/>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>🔥</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>VIGILAR</t>
@@ -2377,7 +2361,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>QCOM</t>
+          <t>INTC</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2386,37 +2370,37 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>201.46</v>
+        <v>109.21</v>
       </c>
       <c r="D34" t="n">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.54</v>
+        <v>-12.58</v>
       </c>
       <c r="F34" t="n">
-        <v>0.67</v>
+        <v>0.66</v>
       </c>
       <c r="G34" t="n">
-        <v>19.09</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="H34" t="n">
-        <v>9.470000000000001</v>
+        <v>8.35</v>
       </c>
       <c r="I34" t="n">
-        <v>193.82</v>
+        <v>105.56</v>
       </c>
       <c r="J34" t="n">
-        <v>206.23</v>
+        <v>111.49</v>
       </c>
       <c r="K34" t="n">
-        <v>172.82</v>
+        <v>95.52</v>
       </c>
       <c r="L34" t="n">
-        <v>249.17</v>
+        <v>132.01</v>
       </c>
       <c r="M34" t="n">
-        <v>67.15000000000001</v>
+        <v>65.02</v>
       </c>
       <c r="N34" t="inlineStr">
         <is>
@@ -2433,46 +2417,46 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>RKLB</t>
+          <t>QQQ</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Espacial</t>
+          <t>ETF Nasdaq</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>131.71</v>
+        <v>711.38</v>
       </c>
       <c r="D35" t="n">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="E35" t="n">
-        <v>67.61</v>
+        <v>0.02</v>
       </c>
       <c r="F35" t="n">
-        <v>0.79</v>
+        <v>1</v>
       </c>
       <c r="G35" t="n">
-        <v>9.27</v>
+        <v>10.65</v>
       </c>
       <c r="H35" t="n">
-        <v>7.04</v>
+        <v>1.5</v>
       </c>
       <c r="I35" t="n">
-        <v>128</v>
+        <v>707.12</v>
       </c>
       <c r="J35" t="n">
-        <v>134.03</v>
+        <v>714.05</v>
       </c>
       <c r="K35" t="n">
-        <v>117.81</v>
+        <v>695.41</v>
       </c>
       <c r="L35" t="n">
-        <v>154.88</v>
+        <v>738.01</v>
       </c>
       <c r="M35" t="n">
-        <v>80.53</v>
+        <v>75.18000000000001</v>
       </c>
       <c r="N35" t="inlineStr">
         <is>
@@ -2489,46 +2473,46 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>IONQ</t>
+          <t>GOOGL</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Computación cuántica</t>
+          <t>Tecnología</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>57.48</v>
+        <v>396.25</v>
       </c>
       <c r="D36" t="n">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="E36" t="n">
-        <v>20.55</v>
+        <v>-1.14</v>
       </c>
       <c r="F36" t="n">
-        <v>0.6</v>
+        <v>0.46</v>
       </c>
       <c r="G36" t="n">
-        <v>4.49</v>
+        <v>11.07</v>
       </c>
       <c r="H36" t="n">
-        <v>7.81</v>
+        <v>2.79</v>
       </c>
       <c r="I36" t="n">
-        <v>55.69</v>
+        <v>391.82</v>
       </c>
       <c r="J36" t="n">
-        <v>58.6</v>
+        <v>399.02</v>
       </c>
       <c r="K36" t="n">
-        <v>50.75</v>
+        <v>379.64</v>
       </c>
       <c r="L36" t="n">
-        <v>68.7</v>
+        <v>423.93</v>
       </c>
       <c r="M36" t="n">
-        <v>72.97</v>
+        <v>75.05</v>
       </c>
       <c r="N36" t="inlineStr">
         <is>
@@ -2545,46 +2529,46 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>MU</t>
+          <t>QCOM</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Memoria / Chips</t>
+          <t>Chips</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>791.45</v>
+        <v>204.47</v>
       </c>
       <c r="D37" t="n">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="E37" t="n">
-        <v>22.4</v>
+        <v>-6.67</v>
       </c>
       <c r="F37" t="n">
-        <v>0.76</v>
+        <v>0.58</v>
       </c>
       <c r="G37" t="n">
-        <v>51.82</v>
+        <v>18.68</v>
       </c>
       <c r="H37" t="n">
-        <v>6.55</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="I37" t="n">
-        <v>770.72</v>
+        <v>197</v>
       </c>
       <c r="J37" t="n">
-        <v>804.4</v>
+        <v>209.14</v>
       </c>
       <c r="K37" t="n">
-        <v>713.72</v>
+        <v>176.45</v>
       </c>
       <c r="L37" t="n">
-        <v>921</v>
+        <v>251.17</v>
       </c>
       <c r="M37" t="n">
-        <v>82.06</v>
+        <v>67.18000000000001</v>
       </c>
       <c r="N37" t="inlineStr">
         <is>

--- a/analisis_acciones.xlsx
+++ b/analisis_acciones.xlsx
@@ -501,46 +501,46 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>NVDA</t>
+          <t>CVX</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>IA / Chips</t>
+          <t>Energía</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>228.06</v>
+        <v>195.49</v>
       </c>
       <c r="D2" t="n">
         <v>95</v>
       </c>
       <c r="E2" t="n">
-        <v>5.98</v>
+        <v>5.82</v>
       </c>
       <c r="F2" t="n">
-        <v>0.83</v>
+        <v>0.7</v>
       </c>
       <c r="G2" t="n">
-        <v>8.210000000000001</v>
+        <v>4.46</v>
       </c>
       <c r="H2" t="n">
-        <v>3.6</v>
+        <v>2.28</v>
       </c>
       <c r="I2" t="n">
-        <v>224.78</v>
+        <v>193.71</v>
       </c>
       <c r="J2" t="n">
-        <v>230.11</v>
+        <v>196.6</v>
       </c>
       <c r="K2" t="n">
-        <v>215.74</v>
+        <v>188.8</v>
       </c>
       <c r="L2" t="n">
-        <v>248.59</v>
+        <v>206.63</v>
       </c>
       <c r="M2" t="n">
-        <v>58.53</v>
+        <v>60.32</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -561,46 +561,46 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AMAT</t>
+          <t>SLB</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Equipos chips</t>
+          <t>Energía</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>441.09</v>
+        <v>56.9</v>
       </c>
       <c r="D3" t="n">
         <v>95</v>
       </c>
       <c r="E3" t="n">
-        <v>1.3</v>
+        <v>3.58</v>
       </c>
       <c r="F3" t="n">
-        <v>1.26</v>
+        <v>0.6</v>
       </c>
       <c r="G3" t="n">
-        <v>18.71</v>
+        <v>1.5</v>
       </c>
       <c r="H3" t="n">
-        <v>4.24</v>
+        <v>2.64</v>
       </c>
       <c r="I3" t="n">
-        <v>433.61</v>
+        <v>56.29</v>
       </c>
       <c r="J3" t="n">
-        <v>445.77</v>
+        <v>57.27</v>
       </c>
       <c r="K3" t="n">
-        <v>413.03</v>
+        <v>54.64</v>
       </c>
       <c r="L3" t="n">
-        <v>487.86</v>
+        <v>60.65</v>
       </c>
       <c r="M3" t="n">
-        <v>61.66</v>
+        <v>55.62</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -621,7 +621,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CVX</t>
+          <t>XOM</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -630,41 +630,41 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>190.26</v>
+        <v>160.68</v>
       </c>
       <c r="D4" t="n">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E4" t="n">
-        <v>4.76</v>
+        <v>8.08</v>
       </c>
       <c r="F4" t="n">
-        <v>0.58</v>
+        <v>0.84</v>
       </c>
       <c r="G4" t="n">
-        <v>4.25</v>
+        <v>4.22</v>
       </c>
       <c r="H4" t="n">
-        <v>2.23</v>
+        <v>2.63</v>
       </c>
       <c r="I4" t="n">
-        <v>188.56</v>
+        <v>158.99</v>
       </c>
       <c r="J4" t="n">
-        <v>191.32</v>
+        <v>161.73</v>
       </c>
       <c r="K4" t="n">
-        <v>183.89</v>
+        <v>154.35</v>
       </c>
       <c r="L4" t="n">
-        <v>200.88</v>
+        <v>171.23</v>
       </c>
       <c r="M4" t="n">
-        <v>58.33</v>
+        <v>65.70999999999999</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>BAJO</t>
+          <t>MEDIO</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -681,7 +681,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>XOM</t>
+          <t>OXY</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -690,37 +690,37 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>157.05</v>
+        <v>59.92</v>
       </c>
       <c r="D5" t="n">
         <v>94</v>
       </c>
       <c r="E5" t="n">
-        <v>8.630000000000001</v>
+        <v>8.67</v>
       </c>
       <c r="F5" t="n">
-        <v>0.86</v>
+        <v>0.75</v>
       </c>
       <c r="G5" t="n">
-        <v>3.94</v>
+        <v>2.01</v>
       </c>
       <c r="H5" t="n">
-        <v>2.51</v>
+        <v>3.35</v>
       </c>
       <c r="I5" t="n">
-        <v>155.47</v>
+        <v>59.12</v>
       </c>
       <c r="J5" t="n">
-        <v>158.04</v>
+        <v>60.42</v>
       </c>
       <c r="K5" t="n">
-        <v>151.14</v>
+        <v>56.91</v>
       </c>
       <c r="L5" t="n">
-        <v>166.9</v>
+        <v>64.94</v>
       </c>
       <c r="M5" t="n">
-        <v>63.3</v>
+        <v>53.26</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
@@ -741,46 +741,46 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SLB</t>
+          <t>NVDA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Energía</t>
+          <t>IA / Chips</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>55.49</v>
+        <v>220.53</v>
       </c>
       <c r="D6" t="n">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="E6" t="n">
-        <v>4.18</v>
+        <v>0.5</v>
       </c>
       <c r="F6" t="n">
-        <v>0.45</v>
+        <v>0.76</v>
       </c>
       <c r="G6" t="n">
-        <v>1.44</v>
+        <v>8.44</v>
       </c>
       <c r="H6" t="n">
-        <v>2.59</v>
+        <v>3.83</v>
       </c>
       <c r="I6" t="n">
-        <v>54.92</v>
+        <v>217.15</v>
       </c>
       <c r="J6" t="n">
-        <v>55.85</v>
+        <v>222.64</v>
       </c>
       <c r="K6" t="n">
-        <v>53.34</v>
+        <v>207.87</v>
       </c>
       <c r="L6" t="n">
-        <v>59.08</v>
+        <v>241.63</v>
       </c>
       <c r="M6" t="n">
-        <v>51.34</v>
+        <v>55.17</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -801,46 +801,46 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>TSLA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Tecnología</t>
+          <t>Autos / Tech</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>425.05</v>
+        <v>409.2</v>
       </c>
       <c r="D7" t="n">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="E7" t="n">
-        <v>2.39</v>
+        <v>-8.039999999999999</v>
       </c>
       <c r="F7" t="n">
-        <v>1.03</v>
+        <v>0.73</v>
       </c>
       <c r="G7" t="n">
-        <v>11.41</v>
+        <v>17.8</v>
       </c>
       <c r="H7" t="n">
-        <v>2.68</v>
+        <v>4.35</v>
       </c>
       <c r="I7" t="n">
-        <v>420.49</v>
+        <v>402.08</v>
       </c>
       <c r="J7" t="n">
-        <v>427.9</v>
+        <v>413.65</v>
       </c>
       <c r="K7" t="n">
-        <v>407.94</v>
+        <v>382.5</v>
       </c>
       <c r="L7" t="n">
-        <v>453.57</v>
+        <v>453.7</v>
       </c>
       <c r="M7" t="n">
-        <v>50.14</v>
+        <v>61.75</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -849,7 +849,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -861,55 +861,55 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>OXY</t>
+          <t>SOXX</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Energía</t>
+          <t>ETF Chips</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>59.08</v>
+        <v>490.83</v>
       </c>
       <c r="D8" t="n">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E8" t="n">
-        <v>11.41</v>
+        <v>-7.87</v>
       </c>
       <c r="F8" t="n">
-        <v>0.93</v>
+        <v>1.07</v>
       </c>
       <c r="G8" t="n">
-        <v>1.97</v>
+        <v>19.84</v>
       </c>
       <c r="H8" t="n">
-        <v>3.33</v>
+        <v>4.04</v>
       </c>
       <c r="I8" t="n">
-        <v>58.29</v>
+        <v>482.89</v>
       </c>
       <c r="J8" t="n">
-        <v>59.57</v>
+        <v>495.79</v>
       </c>
       <c r="K8" t="n">
-        <v>56.13</v>
+        <v>461.06</v>
       </c>
       <c r="L8" t="n">
-        <v>64</v>
+        <v>540.4299999999999</v>
       </c>
       <c r="M8" t="n">
-        <v>54.4</v>
+        <v>63</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>MEDIO</t>
+          <t>BAJO</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -921,46 +921,46 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SPY</t>
+          <t>QQQ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ETF Mercado</t>
+          <t>ETF Nasdaq</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>740.63</v>
+        <v>702.1</v>
       </c>
       <c r="D9" t="n">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="E9" t="n">
-        <v>0.41</v>
+        <v>-1.57</v>
       </c>
       <c r="F9" t="n">
-        <v>0.77</v>
+        <v>1.04</v>
       </c>
       <c r="G9" t="n">
-        <v>7.2</v>
+        <v>10.85</v>
       </c>
       <c r="H9" t="n">
-        <v>0.97</v>
+        <v>1.55</v>
       </c>
       <c r="I9" t="n">
-        <v>737.75</v>
+        <v>697.76</v>
       </c>
       <c r="J9" t="n">
-        <v>742.4299999999999</v>
+        <v>704.8099999999999</v>
       </c>
       <c r="K9" t="n">
-        <v>729.83</v>
+        <v>685.8200000000001</v>
       </c>
       <c r="L9" t="n">
-        <v>758.64</v>
+        <v>729.22</v>
       </c>
       <c r="M9" t="n">
-        <v>71.31</v>
+        <v>73.15000000000001</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
@@ -981,50 +981,50 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ASML</t>
+          <t>SPY</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Chips</t>
+          <t>ETF Mercado</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1513.92</v>
+        <v>736.03</v>
       </c>
       <c r="D10" t="n">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="E10" t="n">
-        <v>-4.91</v>
+        <v>-0.44</v>
       </c>
       <c r="F10" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="G10" t="n">
-        <v>65.62</v>
+        <v>7.35</v>
       </c>
       <c r="H10" t="n">
-        <v>4.33</v>
+        <v>1</v>
       </c>
       <c r="I10" t="n">
-        <v>1487.67</v>
+        <v>733.09</v>
       </c>
       <c r="J10" t="n">
-        <v>1530.32</v>
+        <v>737.87</v>
       </c>
       <c r="K10" t="n">
-        <v>1415.5</v>
+        <v>725.01</v>
       </c>
       <c r="L10" t="n">
-        <v>1677.96</v>
+        <v>754.42</v>
       </c>
       <c r="M10" t="n">
-        <v>56.55</v>
+        <v>70</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>BAJO</t>
+          <t>MEDIO</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1041,57 +1041,53 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>LRCX</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Equipos chips</t>
+          <t>IA / Chips</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>286.91</v>
+        <v>416.29</v>
       </c>
       <c r="D11" t="n">
-        <v>94</v>
+        <v>79</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.43</v>
+        <v>-9.26</v>
       </c>
       <c r="F11" t="n">
-        <v>0.66</v>
+        <v>0.5</v>
       </c>
       <c r="G11" t="n">
-        <v>13.74</v>
+        <v>28.01</v>
       </c>
       <c r="H11" t="n">
-        <v>4.79</v>
+        <v>6.73</v>
       </c>
       <c r="I11" t="n">
-        <v>281.42</v>
+        <v>405.09</v>
       </c>
       <c r="J11" t="n">
-        <v>290.34</v>
+        <v>423.29</v>
       </c>
       <c r="K11" t="n">
-        <v>266.31</v>
+        <v>374.28</v>
       </c>
       <c r="L11" t="n">
-        <v>321.25</v>
+        <v>486.31</v>
       </c>
       <c r="M11" t="n">
-        <v>62.41</v>
+        <v>68.59</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>BAJO</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>🔥</t>
-        </is>
-      </c>
+          <t>MEDIO</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>POSIBLE COMPRA</t>
@@ -1101,57 +1097,53 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SOXX</t>
+          <t>AVGO</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>ETF Chips</t>
+          <t>IA / Chips</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>513.9</v>
+        <v>418.55</v>
       </c>
       <c r="D12" t="n">
-        <v>94</v>
+        <v>76</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.23</v>
+        <v>-2.31</v>
       </c>
       <c r="F12" t="n">
-        <v>0.93</v>
+        <v>0.58</v>
       </c>
       <c r="G12" t="n">
-        <v>19.17</v>
+        <v>16.3</v>
       </c>
       <c r="H12" t="n">
-        <v>3.73</v>
+        <v>3.89</v>
       </c>
       <c r="I12" t="n">
-        <v>506.23</v>
+        <v>412.02</v>
       </c>
       <c r="J12" t="n">
-        <v>518.6900000000001</v>
+        <v>422.62</v>
       </c>
       <c r="K12" t="n">
-        <v>485.14</v>
+        <v>394.09</v>
       </c>
       <c r="L12" t="n">
-        <v>561.83</v>
+        <v>459.3</v>
       </c>
       <c r="M12" t="n">
-        <v>65.06999999999999</v>
+        <v>57.38</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
           <t>BAJO</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>🔥</t>
-        </is>
-      </c>
+      <c r="O12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>POSIBLE COMPRA</t>
@@ -1161,57 +1153,53 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>AVGO</t>
+          <t>AMZN</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>IA / Chips</t>
+          <t>Tecnología</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>426.39</v>
+        <v>264.16</v>
       </c>
       <c r="D13" t="n">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.84</v>
+        <v>-1.8</v>
       </c>
       <c r="F13" t="n">
         <v>0.58</v>
       </c>
       <c r="G13" t="n">
-        <v>17.05</v>
+        <v>7.32</v>
       </c>
       <c r="H13" t="n">
-        <v>4</v>
+        <v>2.77</v>
       </c>
       <c r="I13" t="n">
-        <v>419.56</v>
+        <v>261.23</v>
       </c>
       <c r="J13" t="n">
-        <v>430.65</v>
+        <v>265.99</v>
       </c>
       <c r="K13" t="n">
-        <v>400.8</v>
+        <v>253.18</v>
       </c>
       <c r="L13" t="n">
-        <v>469.02</v>
+        <v>282.46</v>
       </c>
       <c r="M13" t="n">
-        <v>52.98</v>
+        <v>55.9</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
           <t>BAJO</t>
         </is>
       </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>🔥</t>
-        </is>
-      </c>
+      <c r="O13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>POSIBLE COMPRA</t>
@@ -1221,57 +1209,53 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>SMCI</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Chips</t>
+          <t>Servidores IA</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>406.54</v>
+        <v>30.45</v>
       </c>
       <c r="D14" t="n">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="E14" t="n">
-        <v>-1.25</v>
+        <v>-9.140000000000001</v>
       </c>
       <c r="F14" t="n">
-        <v>0.61</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="G14" t="n">
-        <v>15.44</v>
+        <v>2.32</v>
       </c>
       <c r="H14" t="n">
-        <v>3.8</v>
+        <v>7.62</v>
       </c>
       <c r="I14" t="n">
-        <v>400.36</v>
+        <v>29.53</v>
       </c>
       <c r="J14" t="n">
-        <v>410.4</v>
+        <v>31.03</v>
       </c>
       <c r="K14" t="n">
-        <v>383.38</v>
+        <v>26.98</v>
       </c>
       <c r="L14" t="n">
-        <v>445.14</v>
+        <v>36.25</v>
       </c>
       <c r="M14" t="n">
-        <v>50.72</v>
+        <v>58.08</v>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>BAJO</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>🔥</t>
-        </is>
-      </c>
+          <t>MEDIO</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>POSIBLE COMPRA</t>
@@ -1281,50 +1265,50 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>TSM</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>IA / Chips</t>
+          <t>Chips</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>430.61</v>
+        <v>393.54</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="E15" t="n">
-        <v>-5.4</v>
+        <v>-2.72</v>
       </c>
       <c r="F15" t="n">
-        <v>0.42</v>
+        <v>0.68</v>
       </c>
       <c r="G15" t="n">
-        <v>27.56</v>
+        <v>15.28</v>
       </c>
       <c r="H15" t="n">
-        <v>6.4</v>
+        <v>3.88</v>
       </c>
       <c r="I15" t="n">
-        <v>419.59</v>
+        <v>387.43</v>
       </c>
       <c r="J15" t="n">
-        <v>437.5</v>
+        <v>397.36</v>
       </c>
       <c r="K15" t="n">
-        <v>389.27</v>
+        <v>370.62</v>
       </c>
       <c r="L15" t="n">
-        <v>499.51</v>
+        <v>431.74</v>
       </c>
       <c r="M15" t="n">
-        <v>69.39</v>
+        <v>50.55</v>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>MEDIO</t>
+          <t>BAJO</t>
         </is>
       </c>
       <c r="O15" t="inlineStr"/>
@@ -1337,50 +1321,50 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>MU</t>
+          <t>ASML</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Memoria / Chips</t>
+          <t>Chips</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>735.9299999999999</v>
+        <v>1465.23</v>
       </c>
       <c r="D16" t="n">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="E16" t="n">
-        <v>-1.46</v>
+        <v>-6.42</v>
       </c>
       <c r="F16" t="n">
-        <v>0.8</v>
+        <v>0.76</v>
       </c>
       <c r="G16" t="n">
-        <v>53.45</v>
+        <v>65.73</v>
       </c>
       <c r="H16" t="n">
-        <v>7.26</v>
+        <v>4.49</v>
       </c>
       <c r="I16" t="n">
-        <v>714.55</v>
+        <v>1438.94</v>
       </c>
       <c r="J16" t="n">
-        <v>749.29</v>
+        <v>1481.67</v>
       </c>
       <c r="K16" t="n">
-        <v>655.76</v>
+        <v>1366.65</v>
       </c>
       <c r="L16" t="n">
-        <v>869.54</v>
+        <v>1629.55</v>
       </c>
       <c r="M16" t="n">
-        <v>71.69</v>
+        <v>56.47</v>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>MEDIO</t>
+          <t>BAJO</t>
         </is>
       </c>
       <c r="O16" t="inlineStr"/>
@@ -1393,50 +1377,50 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>TSLA</t>
+          <t>AMAT</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Autos / Tech</t>
+          <t>Equipos chips</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>425.06</v>
+        <v>411.61</v>
       </c>
       <c r="D17" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.77</v>
+        <v>-7.22</v>
       </c>
       <c r="F17" t="n">
-        <v>0.67</v>
+        <v>0.76</v>
       </c>
       <c r="G17" t="n">
-        <v>17.19</v>
+        <v>19.42</v>
       </c>
       <c r="H17" t="n">
-        <v>4.04</v>
+        <v>4.72</v>
       </c>
       <c r="I17" t="n">
-        <v>418.19</v>
+        <v>403.84</v>
       </c>
       <c r="J17" t="n">
-        <v>429.36</v>
+        <v>416.47</v>
       </c>
       <c r="K17" t="n">
-        <v>399.28</v>
+        <v>382.47</v>
       </c>
       <c r="L17" t="n">
-        <v>468.03</v>
+        <v>460.17</v>
       </c>
       <c r="M17" t="n">
-        <v>68.13</v>
+        <v>59.53</v>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>MEDIO</t>
+          <t>BAJO</t>
         </is>
       </c>
       <c r="O17" t="inlineStr"/>
@@ -1449,50 +1433,50 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>AMZN</t>
+          <t>LRCX</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Tecnología</t>
+          <t>Equipos chips</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>263.11</v>
+        <v>275.67</v>
       </c>
       <c r="D18" t="n">
         <v>76</v>
       </c>
       <c r="E18" t="n">
-        <v>-3.51</v>
+        <v>-6.89</v>
       </c>
       <c r="F18" t="n">
-        <v>0.65</v>
+        <v>0.5</v>
       </c>
       <c r="G18" t="n">
-        <v>7.19</v>
+        <v>14.34</v>
       </c>
       <c r="H18" t="n">
-        <v>2.73</v>
+        <v>5.2</v>
       </c>
       <c r="I18" t="n">
-        <v>260.23</v>
+        <v>269.93</v>
       </c>
       <c r="J18" t="n">
-        <v>264.91</v>
+        <v>279.25</v>
       </c>
       <c r="K18" t="n">
-        <v>252.33</v>
+        <v>254.16</v>
       </c>
       <c r="L18" t="n">
-        <v>281.08</v>
+        <v>311.5</v>
       </c>
       <c r="M18" t="n">
-        <v>52.47</v>
+        <v>60.76</v>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>BAJO</t>
+          <t>MEDIO</t>
         </is>
       </c>
       <c r="O18" t="inlineStr"/>
@@ -1505,106 +1489,110 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>SMCI</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Servidores IA</t>
+          <t>Tecnología</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>31.09</v>
+        <v>422.55</v>
       </c>
       <c r="D19" t="n">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="E19" t="n">
-        <v>-12.09</v>
+        <v>2.4</v>
       </c>
       <c r="F19" t="n">
-        <v>0.52</v>
+        <v>0.65</v>
       </c>
       <c r="G19" t="n">
-        <v>2.29</v>
+        <v>11.52</v>
       </c>
       <c r="H19" t="n">
-        <v>7.36</v>
+        <v>2.73</v>
       </c>
       <c r="I19" t="n">
-        <v>30.18</v>
+        <v>417.94</v>
       </c>
       <c r="J19" t="n">
-        <v>31.67</v>
+        <v>425.43</v>
       </c>
       <c r="K19" t="n">
-        <v>27.66</v>
+        <v>405.28</v>
       </c>
       <c r="L19" t="n">
-        <v>36.81</v>
+        <v>451.34</v>
       </c>
       <c r="M19" t="n">
-        <v>58.2</v>
+        <v>45.44</v>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>MEDIO</t>
-        </is>
-      </c>
-      <c r="O19" t="inlineStr"/>
+          <t>BAJO</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>🔥</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>POSIBLE COMPRA</t>
+          <t>VIGILAR</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>UPST</t>
+          <t>META</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Fintech IA</t>
+          <t>Tecnología</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>29.88</v>
+        <v>612.3200000000001</v>
       </c>
       <c r="D20" t="n">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="E20" t="n">
-        <v>3.18</v>
+        <v>2.25</v>
       </c>
       <c r="F20" t="n">
-        <v>0.95</v>
+        <v>0.65</v>
       </c>
       <c r="G20" t="n">
-        <v>1.9</v>
+        <v>17.2</v>
       </c>
       <c r="H20" t="n">
-        <v>6.34</v>
+        <v>2.81</v>
       </c>
       <c r="I20" t="n">
-        <v>29.12</v>
+        <v>605.4400000000001</v>
       </c>
       <c r="J20" t="n">
-        <v>30.35</v>
+        <v>616.62</v>
       </c>
       <c r="K20" t="n">
-        <v>27.04</v>
+        <v>586.53</v>
       </c>
       <c r="L20" t="n">
-        <v>34.62</v>
+        <v>655.3099999999999</v>
       </c>
       <c r="M20" t="n">
-        <v>38.57</v>
+        <v>26.43</v>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>MEDIO</t>
+          <t>BAJO</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
@@ -1621,50 +1609,50 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>KLAC</t>
+          <t>ARM</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Equipos chips</t>
+          <t>Chips</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>1824.25</v>
+        <v>209.83</v>
       </c>
       <c r="D21" t="n">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.4</v>
+        <v>-1.33</v>
       </c>
       <c r="F21" t="n">
-        <v>0.51</v>
+        <v>0.53</v>
       </c>
       <c r="G21" t="n">
-        <v>87.39</v>
+        <v>15.38</v>
       </c>
       <c r="H21" t="n">
-        <v>4.79</v>
+        <v>7.33</v>
       </c>
       <c r="I21" t="n">
-        <v>1789.29</v>
+        <v>203.68</v>
       </c>
       <c r="J21" t="n">
-        <v>1846.1</v>
+        <v>213.68</v>
       </c>
       <c r="K21" t="n">
-        <v>1693.17</v>
+        <v>186.75</v>
       </c>
       <c r="L21" t="n">
-        <v>2042.72</v>
+        <v>248.29</v>
       </c>
       <c r="M21" t="n">
-        <v>44.36</v>
+        <v>54.49</v>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>BAJO</t>
+          <t>MEDIO</t>
         </is>
       </c>
       <c r="O21" t="inlineStr"/>
@@ -1677,50 +1665,50 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>ARM</t>
+          <t>KLAC</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Chips</t>
+          <t>Equipos chips</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>209.91</v>
+        <v>1744.06</v>
       </c>
       <c r="D22" t="n">
         <v>64</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.57</v>
+        <v>-5.48</v>
       </c>
       <c r="F22" t="n">
-        <v>0.67</v>
+        <v>0.5</v>
       </c>
       <c r="G22" t="n">
-        <v>16.2</v>
+        <v>85.22</v>
       </c>
       <c r="H22" t="n">
-        <v>7.72</v>
+        <v>4.89</v>
       </c>
       <c r="I22" t="n">
-        <v>203.43</v>
+        <v>1709.97</v>
       </c>
       <c r="J22" t="n">
-        <v>213.97</v>
+        <v>1765.37</v>
       </c>
       <c r="K22" t="n">
-        <v>185.61</v>
+        <v>1616.22</v>
       </c>
       <c r="L22" t="n">
-        <v>250.43</v>
+        <v>1957.12</v>
       </c>
       <c r="M22" t="n">
-        <v>47.87</v>
+        <v>45.09</v>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>MEDIO</t>
+          <t>BAJO</t>
         </is>
       </c>
       <c r="O22" t="inlineStr"/>
@@ -1742,37 +1730,37 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>8.5</v>
+        <v>8.34</v>
       </c>
       <c r="D23" t="n">
         <v>58</v>
       </c>
       <c r="E23" t="n">
-        <v>-4.28</v>
+        <v>-1.36</v>
       </c>
       <c r="F23" t="n">
-        <v>0.44</v>
+        <v>0.46</v>
       </c>
       <c r="G23" t="n">
         <v>0.66</v>
       </c>
       <c r="H23" t="n">
-        <v>7.77</v>
+        <v>7.97</v>
       </c>
       <c r="I23" t="n">
-        <v>8.24</v>
+        <v>8.07</v>
       </c>
       <c r="J23" t="n">
-        <v>8.67</v>
+        <v>8.5</v>
       </c>
       <c r="K23" t="n">
-        <v>7.51</v>
+        <v>7.34</v>
       </c>
       <c r="L23" t="n">
-        <v>10.15</v>
+        <v>9.99</v>
       </c>
       <c r="M23" t="n">
-        <v>53.23</v>
+        <v>52.58</v>
       </c>
       <c r="N23" t="inlineStr">
         <is>
@@ -1798,37 +1786,37 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>196.29</v>
+        <v>187</v>
       </c>
       <c r="D24" t="n">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.42</v>
+        <v>-13.67</v>
       </c>
       <c r="F24" t="n">
-        <v>1.1</v>
+        <v>0.75</v>
       </c>
       <c r="G24" t="n">
-        <v>14.49</v>
+        <v>14.73</v>
       </c>
       <c r="H24" t="n">
-        <v>7.38</v>
+        <v>7.87</v>
       </c>
       <c r="I24" t="n">
-        <v>190.49</v>
+        <v>181.11</v>
       </c>
       <c r="J24" t="n">
-        <v>199.91</v>
+        <v>190.68</v>
       </c>
       <c r="K24" t="n">
-        <v>174.56</v>
+        <v>164.91</v>
       </c>
       <c r="L24" t="n">
-        <v>232.5</v>
+        <v>223.81</v>
       </c>
       <c r="M24" t="n">
-        <v>49.82</v>
+        <v>46.98</v>
       </c>
       <c r="N24" t="inlineStr">
         <is>
@@ -1845,50 +1833,50 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>META</t>
+          <t>HOOD</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Tecnología</t>
+          <t>Trading</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>616.74</v>
+        <v>76.36</v>
       </c>
       <c r="D25" t="n">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="E25" t="n">
-        <v>1.17</v>
+        <v>-5.47</v>
       </c>
       <c r="F25" t="n">
-        <v>0.54</v>
+        <v>0.58</v>
       </c>
       <c r="G25" t="n">
-        <v>17.27</v>
+        <v>4.54</v>
       </c>
       <c r="H25" t="n">
-        <v>2.8</v>
+        <v>5.94</v>
       </c>
       <c r="I25" t="n">
-        <v>609.83</v>
+        <v>74.54000000000001</v>
       </c>
       <c r="J25" t="n">
-        <v>621.0599999999999</v>
+        <v>77.48999999999999</v>
       </c>
       <c r="K25" t="n">
-        <v>590.83</v>
+        <v>69.55</v>
       </c>
       <c r="L25" t="n">
-        <v>659.92</v>
+        <v>87.70999999999999</v>
       </c>
       <c r="M25" t="n">
-        <v>25.84</v>
+        <v>42.55</v>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>BAJO</t>
+          <t>MEDIO</t>
         </is>
       </c>
       <c r="O25" t="inlineStr"/>
@@ -1901,50 +1889,50 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>HOOD</t>
+          <t>PYPL</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Trading</t>
+          <t>Pagos</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>77.34999999999999</v>
+        <v>44.31</v>
       </c>
       <c r="D26" t="n">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="E26" t="n">
-        <v>0.42</v>
+        <v>-1.68</v>
       </c>
       <c r="F26" t="n">
-        <v>0.54</v>
+        <v>0.43</v>
       </c>
       <c r="G26" t="n">
-        <v>4.44</v>
+        <v>1.53</v>
       </c>
       <c r="H26" t="n">
-        <v>5.75</v>
+        <v>3.45</v>
       </c>
       <c r="I26" t="n">
-        <v>75.56999999999999</v>
+        <v>43.7</v>
       </c>
       <c r="J26" t="n">
-        <v>78.45999999999999</v>
+        <v>44.7</v>
       </c>
       <c r="K26" t="n">
-        <v>70.68000000000001</v>
+        <v>42.02</v>
       </c>
       <c r="L26" t="n">
-        <v>88.45999999999999</v>
+        <v>48.14</v>
       </c>
       <c r="M26" t="n">
-        <v>41.58</v>
+        <v>21.26</v>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>MEDIO</t>
+          <t>BAJO</t>
         </is>
       </c>
       <c r="O26" t="inlineStr"/>
@@ -1957,50 +1945,50 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>PYPL</t>
+          <t>AI</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Pagos</t>
+          <t>IA</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>44.62</v>
+        <v>8.74</v>
       </c>
       <c r="D27" t="n">
         <v>46</v>
       </c>
       <c r="E27" t="n">
-        <v>-1.65</v>
+        <v>-7.75</v>
       </c>
       <c r="F27" t="n">
-        <v>0.66</v>
+        <v>0.77</v>
       </c>
       <c r="G27" t="n">
-        <v>1.52</v>
+        <v>0.46</v>
       </c>
       <c r="H27" t="n">
-        <v>3.4</v>
+        <v>5.24</v>
       </c>
       <c r="I27" t="n">
-        <v>44.01</v>
+        <v>8.56</v>
       </c>
       <c r="J27" t="n">
-        <v>45</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="K27" t="n">
-        <v>42.34</v>
+        <v>8.06</v>
       </c>
       <c r="L27" t="n">
-        <v>48.42</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="M27" t="n">
-        <v>21.67</v>
+        <v>46.59</v>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>BAJO</t>
+          <t>MEDIO</t>
         </is>
       </c>
       <c r="O27" t="inlineStr"/>
@@ -2013,50 +2001,50 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>AI</t>
+          <t>PLTR</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>IA</t>
+          <t>IA / Software</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>8.67</v>
+        <v>133.76</v>
       </c>
       <c r="D28" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E28" t="n">
-        <v>-12.16</v>
+        <v>-2.29</v>
       </c>
       <c r="F28" t="n">
-        <v>0.8</v>
+        <v>0.57</v>
       </c>
       <c r="G28" t="n">
-        <v>0.45</v>
+        <v>5.8</v>
       </c>
       <c r="H28" t="n">
-        <v>5.21</v>
+        <v>4.34</v>
       </c>
       <c r="I28" t="n">
-        <v>8.49</v>
+        <v>131.43</v>
       </c>
       <c r="J28" t="n">
-        <v>8.779999999999999</v>
+        <v>135.21</v>
       </c>
       <c r="K28" t="n">
-        <v>7.99</v>
+        <v>125.05</v>
       </c>
       <c r="L28" t="n">
-        <v>9.800000000000001</v>
+        <v>148.27</v>
       </c>
       <c r="M28" t="n">
-        <v>48.21</v>
+        <v>40.59</v>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>MEDIO</t>
+          <t>BAJO</t>
         </is>
       </c>
       <c r="O28" t="inlineStr"/>
@@ -2069,50 +2057,50 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>PLTR</t>
+          <t>UPST</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>IA / Software</t>
+          <t>Fintech IA</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>134.47</v>
+        <v>27.69</v>
       </c>
       <c r="D29" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E29" t="n">
-        <v>-2.42</v>
+        <v>-3.47</v>
       </c>
       <c r="F29" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.88</v>
       </c>
       <c r="G29" t="n">
-        <v>5.72</v>
+        <v>1.95</v>
       </c>
       <c r="H29" t="n">
-        <v>4.25</v>
+        <v>7.06</v>
       </c>
       <c r="I29" t="n">
-        <v>132.18</v>
+        <v>26.91</v>
       </c>
       <c r="J29" t="n">
-        <v>135.9</v>
+        <v>28.18</v>
       </c>
       <c r="K29" t="n">
-        <v>125.89</v>
+        <v>24.76</v>
       </c>
       <c r="L29" t="n">
-        <v>148.77</v>
+        <v>32.58</v>
       </c>
       <c r="M29" t="n">
-        <v>39.63</v>
+        <v>33.58</v>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>BAJO</t>
+          <t>MEDIO</t>
         </is>
       </c>
       <c r="O29" t="inlineStr"/>
@@ -2134,37 +2122,37 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>15.7</v>
+        <v>15.51</v>
       </c>
       <c r="D30" t="n">
         <v>28</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.29</v>
+        <v>-4.61</v>
       </c>
       <c r="F30" t="n">
-        <v>0.59</v>
+        <v>0.84</v>
       </c>
       <c r="G30" t="n">
-        <v>0.82</v>
+        <v>0.84</v>
       </c>
       <c r="H30" t="n">
-        <v>5.2</v>
+        <v>5.44</v>
       </c>
       <c r="I30" t="n">
-        <v>15.38</v>
+        <v>15.17</v>
       </c>
       <c r="J30" t="n">
-        <v>15.91</v>
+        <v>15.72</v>
       </c>
       <c r="K30" t="n">
-        <v>14.48</v>
+        <v>14.24</v>
       </c>
       <c r="L30" t="n">
-        <v>17.75</v>
+        <v>17.62</v>
       </c>
       <c r="M30" t="n">
-        <v>30.58</v>
+        <v>31.4</v>
       </c>
       <c r="N30" t="inlineStr">
         <is>
@@ -2181,57 +2169,53 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>MU</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Tecnología</t>
+          <t>Memoria / Chips</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>301.28</v>
+        <v>670.1900000000001</v>
       </c>
       <c r="D31" t="n">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="E31" t="n">
-        <v>2.81</v>
+        <v>-15.73</v>
       </c>
       <c r="F31" t="n">
-        <v>0.73</v>
+        <v>0.99</v>
       </c>
       <c r="G31" t="n">
-        <v>6.66</v>
+        <v>57.55</v>
       </c>
       <c r="H31" t="n">
-        <v>2.21</v>
+        <v>8.59</v>
       </c>
       <c r="I31" t="n">
-        <v>298.61</v>
+        <v>647.17</v>
       </c>
       <c r="J31" t="n">
-        <v>302.94</v>
+        <v>684.58</v>
       </c>
       <c r="K31" t="n">
-        <v>291.28</v>
+        <v>583.87</v>
       </c>
       <c r="L31" t="n">
-        <v>317.93</v>
+        <v>814.0599999999999</v>
       </c>
       <c r="M31" t="n">
-        <v>88.70999999999999</v>
+        <v>65.56999999999999</v>
       </c>
       <c r="N31" t="inlineStr">
         <is>
           <t>ALTO</t>
         </is>
       </c>
-      <c r="O31" t="inlineStr">
-        <is>
-          <t>🔥</t>
-        </is>
-      </c>
+      <c r="O31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>VIGILAR</t>
@@ -2241,57 +2225,53 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>RKLB</t>
+          <t>AAPL</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Espacial</t>
+          <t>Tecnología</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>126.83</v>
+        <v>296.72</v>
       </c>
       <c r="D32" t="n">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="E32" t="n">
-        <v>20.26</v>
+        <v>1.38</v>
       </c>
       <c r="F32" t="n">
-        <v>0.66</v>
+        <v>0.5</v>
       </c>
       <c r="G32" t="n">
-        <v>9.65</v>
+        <v>6.67</v>
       </c>
       <c r="H32" t="n">
-        <v>7.61</v>
+        <v>2.25</v>
       </c>
       <c r="I32" t="n">
-        <v>122.97</v>
+        <v>294.05</v>
       </c>
       <c r="J32" t="n">
-        <v>129.24</v>
+        <v>298.39</v>
       </c>
       <c r="K32" t="n">
-        <v>112.36</v>
+        <v>286.71</v>
       </c>
       <c r="L32" t="n">
-        <v>150.95</v>
+        <v>313.4</v>
       </c>
       <c r="M32" t="n">
-        <v>74.98</v>
+        <v>80.41</v>
       </c>
       <c r="N32" t="inlineStr">
         <is>
           <t>ALTO</t>
         </is>
       </c>
-      <c r="O32" t="inlineStr">
-        <is>
-          <t>🔥</t>
-        </is>
-      </c>
+      <c r="O32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>VIGILAR</t>
@@ -2301,57 +2281,53 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>IONQ</t>
+          <t>QCOM</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Computación cuántica</t>
+          <t>Chips</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>52.5</v>
+        <v>201.04</v>
       </c>
       <c r="D33" t="n">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="E33" t="n">
-        <v>6.62</v>
+        <v>-15.36</v>
       </c>
       <c r="F33" t="n">
-        <v>0.63</v>
+        <v>0.46</v>
       </c>
       <c r="G33" t="n">
-        <v>4.72</v>
+        <v>19.37</v>
       </c>
       <c r="H33" t="n">
-        <v>8.98</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="I33" t="n">
-        <v>50.61</v>
+        <v>193.29</v>
       </c>
       <c r="J33" t="n">
-        <v>53.68</v>
+        <v>205.88</v>
       </c>
       <c r="K33" t="n">
-        <v>45.42</v>
+        <v>171.99</v>
       </c>
       <c r="L33" t="n">
-        <v>64.29000000000001</v>
+        <v>249.45</v>
       </c>
       <c r="M33" t="n">
-        <v>62.03</v>
+        <v>66.47</v>
       </c>
       <c r="N33" t="inlineStr">
         <is>
           <t>ALTO</t>
         </is>
       </c>
-      <c r="O33" t="inlineStr">
-        <is>
-          <t>🔥</t>
-        </is>
-      </c>
+      <c r="O33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>VIGILAR</t>
@@ -2370,37 +2346,37 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>109.21</v>
+        <v>107.14</v>
       </c>
       <c r="D34" t="n">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="E34" t="n">
-        <v>-12.58</v>
+        <v>-17.23</v>
       </c>
       <c r="F34" t="n">
-        <v>0.66</v>
+        <v>0.75</v>
       </c>
       <c r="G34" t="n">
-        <v>9.119999999999999</v>
+        <v>9.73</v>
       </c>
       <c r="H34" t="n">
-        <v>8.35</v>
+        <v>9.08</v>
       </c>
       <c r="I34" t="n">
-        <v>105.56</v>
+        <v>103.25</v>
       </c>
       <c r="J34" t="n">
-        <v>111.49</v>
+        <v>109.57</v>
       </c>
       <c r="K34" t="n">
-        <v>95.52</v>
+        <v>92.55</v>
       </c>
       <c r="L34" t="n">
-        <v>132.01</v>
+        <v>131.46</v>
       </c>
       <c r="M34" t="n">
-        <v>65.02</v>
+        <v>63.76</v>
       </c>
       <c r="N34" t="inlineStr">
         <is>
@@ -2417,46 +2393,46 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>QQQ</t>
+          <t>GOOGL</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>ETF Nasdaq</t>
+          <t>Tecnología</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>711.38</v>
+        <v>398.14</v>
       </c>
       <c r="D35" t="n">
-        <v>82</v>
+        <v>68</v>
       </c>
       <c r="E35" t="n">
-        <v>0.02</v>
+        <v>2.45</v>
       </c>
       <c r="F35" t="n">
-        <v>1</v>
+        <v>0.72</v>
       </c>
       <c r="G35" t="n">
-        <v>10.65</v>
+        <v>11.63</v>
       </c>
       <c r="H35" t="n">
-        <v>1.5</v>
+        <v>2.92</v>
       </c>
       <c r="I35" t="n">
-        <v>707.12</v>
+        <v>393.49</v>
       </c>
       <c r="J35" t="n">
-        <v>714.05</v>
+        <v>401.05</v>
       </c>
       <c r="K35" t="n">
-        <v>695.41</v>
+        <v>380.7</v>
       </c>
       <c r="L35" t="n">
-        <v>738.01</v>
+        <v>427.21</v>
       </c>
       <c r="M35" t="n">
-        <v>75.18000000000001</v>
+        <v>76.31</v>
       </c>
       <c r="N35" t="inlineStr">
         <is>
@@ -2473,46 +2449,46 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>GOOGL</t>
+          <t>RKLB</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Tecnología</t>
+          <t>Espacial</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>396.25</v>
+        <v>129.78</v>
       </c>
       <c r="D36" t="n">
-        <v>78</v>
+        <v>64</v>
       </c>
       <c r="E36" t="n">
-        <v>-1.14</v>
+        <v>10.59</v>
       </c>
       <c r="F36" t="n">
-        <v>0.46</v>
+        <v>1.01</v>
       </c>
       <c r="G36" t="n">
-        <v>11.07</v>
+        <v>10.28</v>
       </c>
       <c r="H36" t="n">
-        <v>2.79</v>
+        <v>7.92</v>
       </c>
       <c r="I36" t="n">
-        <v>391.82</v>
+        <v>125.66</v>
       </c>
       <c r="J36" t="n">
-        <v>399.02</v>
+        <v>132.35</v>
       </c>
       <c r="K36" t="n">
-        <v>379.64</v>
+        <v>114.35</v>
       </c>
       <c r="L36" t="n">
-        <v>423.93</v>
+        <v>155.49</v>
       </c>
       <c r="M36" t="n">
-        <v>75.05</v>
+        <v>77.66</v>
       </c>
       <c r="N36" t="inlineStr">
         <is>
@@ -2529,46 +2505,46 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>QCOM</t>
+          <t>IONQ</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Chips</t>
+          <t>Computación cuántica</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>204.47</v>
+        <v>48.69</v>
       </c>
       <c r="D37" t="n">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="E37" t="n">
-        <v>-6.67</v>
+        <v>-14.4</v>
       </c>
       <c r="F37" t="n">
-        <v>0.58</v>
+        <v>0.55</v>
       </c>
       <c r="G37" t="n">
-        <v>18.68</v>
+        <v>4.91</v>
       </c>
       <c r="H37" t="n">
-        <v>9.140000000000001</v>
+        <v>10.08</v>
       </c>
       <c r="I37" t="n">
-        <v>197</v>
+        <v>46.73</v>
       </c>
       <c r="J37" t="n">
-        <v>209.14</v>
+        <v>49.92</v>
       </c>
       <c r="K37" t="n">
-        <v>176.45</v>
+        <v>41.33</v>
       </c>
       <c r="L37" t="n">
-        <v>251.17</v>
+        <v>60.97</v>
       </c>
       <c r="M37" t="n">
-        <v>67.18000000000001</v>
+        <v>57.19</v>
       </c>
       <c r="N37" t="inlineStr">
         <is>

--- a/analisis_acciones.xlsx
+++ b/analisis_acciones.xlsx
@@ -510,41 +510,41 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>195.49</v>
+        <v>197.33</v>
       </c>
       <c r="D2" t="n">
         <v>95</v>
       </c>
       <c r="E2" t="n">
-        <v>5.82</v>
+        <v>6.12</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7</v>
+        <v>0.93</v>
       </c>
       <c r="G2" t="n">
-        <v>4.46</v>
+        <v>4.55</v>
       </c>
       <c r="H2" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="I2" t="n">
-        <v>193.71</v>
+        <v>195.51</v>
       </c>
       <c r="J2" t="n">
-        <v>196.6</v>
+        <v>198.47</v>
       </c>
       <c r="K2" t="n">
-        <v>188.8</v>
+        <v>190.51</v>
       </c>
       <c r="L2" t="n">
-        <v>206.63</v>
+        <v>208.7</v>
       </c>
       <c r="M2" t="n">
-        <v>60.32</v>
+        <v>57.86</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>BAJO</t>
+          <t>MEDIO</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -570,37 +570,37 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>56.9</v>
+        <v>56.78</v>
       </c>
       <c r="D3" t="n">
         <v>95</v>
       </c>
       <c r="E3" t="n">
-        <v>3.58</v>
+        <v>2.05</v>
       </c>
       <c r="F3" t="n">
-        <v>0.6</v>
+        <v>0.53</v>
       </c>
       <c r="G3" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="H3" t="n">
-        <v>2.64</v>
+        <v>2.57</v>
       </c>
       <c r="I3" t="n">
-        <v>56.29</v>
+        <v>56.2</v>
       </c>
       <c r="J3" t="n">
-        <v>57.27</v>
+        <v>57.14</v>
       </c>
       <c r="K3" t="n">
-        <v>54.64</v>
+        <v>54.59</v>
       </c>
       <c r="L3" t="n">
-        <v>60.65</v>
+        <v>60.43</v>
       </c>
       <c r="M3" t="n">
-        <v>55.62</v>
+        <v>54.63</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -630,37 +630,37 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>160.68</v>
+        <v>162.63</v>
       </c>
       <c r="D4" t="n">
         <v>94</v>
       </c>
       <c r="E4" t="n">
-        <v>8.08</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="F4" t="n">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="G4" t="n">
-        <v>4.22</v>
+        <v>4.17</v>
       </c>
       <c r="H4" t="n">
-        <v>2.63</v>
+        <v>2.57</v>
       </c>
       <c r="I4" t="n">
-        <v>158.99</v>
+        <v>160.96</v>
       </c>
       <c r="J4" t="n">
-        <v>161.73</v>
+        <v>163.67</v>
       </c>
       <c r="K4" t="n">
-        <v>154.35</v>
+        <v>156.37</v>
       </c>
       <c r="L4" t="n">
-        <v>171.23</v>
+        <v>173.06</v>
       </c>
       <c r="M4" t="n">
-        <v>65.70999999999999</v>
+        <v>63.52</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -681,50 +681,50 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>OXY</t>
+          <t>SOXX</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Energía</t>
+          <t>ETF Chips</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>59.92</v>
+        <v>496.74</v>
       </c>
       <c r="D5" t="n">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="E5" t="n">
-        <v>8.67</v>
+        <v>-3.73</v>
       </c>
       <c r="F5" t="n">
-        <v>0.75</v>
+        <v>1.44</v>
       </c>
       <c r="G5" t="n">
-        <v>2.01</v>
+        <v>21.02</v>
       </c>
       <c r="H5" t="n">
-        <v>3.35</v>
+        <v>4.23</v>
       </c>
       <c r="I5" t="n">
-        <v>59.12</v>
+        <v>488.33</v>
       </c>
       <c r="J5" t="n">
-        <v>60.42</v>
+        <v>501.99</v>
       </c>
       <c r="K5" t="n">
-        <v>56.91</v>
+        <v>465.22</v>
       </c>
       <c r="L5" t="n">
-        <v>64.94</v>
+        <v>549.28</v>
       </c>
       <c r="M5" t="n">
-        <v>53.26</v>
+        <v>62.63</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>MEDIO</t>
+          <t>BAJO</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -741,55 +741,55 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>NVDA</t>
+          <t>OXY</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>IA / Chips</t>
+          <t>Energía</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>220.53</v>
+        <v>60.72</v>
       </c>
       <c r="D6" t="n">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="E6" t="n">
-        <v>0.5</v>
+        <v>7.91</v>
       </c>
       <c r="F6" t="n">
-        <v>0.76</v>
+        <v>0.95</v>
       </c>
       <c r="G6" t="n">
-        <v>8.44</v>
+        <v>1.94</v>
       </c>
       <c r="H6" t="n">
-        <v>3.83</v>
+        <v>3.2</v>
       </c>
       <c r="I6" t="n">
-        <v>217.15</v>
+        <v>59.94</v>
       </c>
       <c r="J6" t="n">
-        <v>222.64</v>
+        <v>61.21</v>
       </c>
       <c r="K6" t="n">
-        <v>207.87</v>
+        <v>57.8</v>
       </c>
       <c r="L6" t="n">
-        <v>241.63</v>
+        <v>65.58</v>
       </c>
       <c r="M6" t="n">
-        <v>55.17</v>
+        <v>49.89</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>BAJO</t>
+          <t>MEDIO</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -801,55 +801,55 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>TSLA</t>
+          <t>ARM</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Autos / Tech</t>
+          <t>Chips</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>409.2</v>
+        <v>223.15</v>
       </c>
       <c r="D7" t="n">
         <v>84</v>
       </c>
       <c r="E7" t="n">
-        <v>-8.039999999999999</v>
+        <v>7.32</v>
       </c>
       <c r="F7" t="n">
-        <v>0.73</v>
+        <v>0.92</v>
       </c>
       <c r="G7" t="n">
-        <v>17.8</v>
+        <v>16.39</v>
       </c>
       <c r="H7" t="n">
-        <v>4.35</v>
+        <v>7.34</v>
       </c>
       <c r="I7" t="n">
-        <v>402.08</v>
+        <v>216.59</v>
       </c>
       <c r="J7" t="n">
-        <v>413.65</v>
+        <v>227.25</v>
       </c>
       <c r="K7" t="n">
-        <v>382.5</v>
+        <v>198.57</v>
       </c>
       <c r="L7" t="n">
-        <v>453.7</v>
+        <v>264.12</v>
       </c>
       <c r="M7" t="n">
-        <v>61.75</v>
+        <v>57.96</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>BAJO</t>
+          <t>MEDIO</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -861,46 +861,46 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SOXX</t>
+          <t>NVDA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>ETF Chips</t>
+          <t>IA / Chips</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>490.83</v>
+        <v>220.61</v>
       </c>
       <c r="D8" t="n">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="E8" t="n">
-        <v>-7.87</v>
+        <v>-0.08</v>
       </c>
       <c r="F8" t="n">
-        <v>1.07</v>
+        <v>0.83</v>
       </c>
       <c r="G8" t="n">
-        <v>19.84</v>
+        <v>8.51</v>
       </c>
       <c r="H8" t="n">
-        <v>4.04</v>
+        <v>3.86</v>
       </c>
       <c r="I8" t="n">
-        <v>482.89</v>
+        <v>217.21</v>
       </c>
       <c r="J8" t="n">
-        <v>495.79</v>
+        <v>222.74</v>
       </c>
       <c r="K8" t="n">
-        <v>461.06</v>
+        <v>207.84</v>
       </c>
       <c r="L8" t="n">
-        <v>540.4299999999999</v>
+        <v>241.89</v>
       </c>
       <c r="M8" t="n">
-        <v>63</v>
+        <v>58.45</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
@@ -921,46 +921,46 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>QQQ</t>
+          <t>GOOGL</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ETF Nasdaq</t>
+          <t>Tecnología</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>702.1</v>
+        <v>387.66</v>
       </c>
       <c r="D9" t="n">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.57</v>
+        <v>0.08</v>
       </c>
       <c r="F9" t="n">
-        <v>1.04</v>
+        <v>1.13</v>
       </c>
       <c r="G9" t="n">
-        <v>10.85</v>
+        <v>11.59</v>
       </c>
       <c r="H9" t="n">
-        <v>1.55</v>
+        <v>2.99</v>
       </c>
       <c r="I9" t="n">
-        <v>697.76</v>
+        <v>383.02</v>
       </c>
       <c r="J9" t="n">
-        <v>704.8099999999999</v>
+        <v>390.56</v>
       </c>
       <c r="K9" t="n">
-        <v>685.8200000000001</v>
+        <v>370.28</v>
       </c>
       <c r="L9" t="n">
-        <v>729.22</v>
+        <v>416.63</v>
       </c>
       <c r="M9" t="n">
-        <v>73.15000000000001</v>
+        <v>68.89</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
@@ -981,50 +981,50 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SPY</t>
+          <t>TSLA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ETF Mercado</t>
+          <t>Autos / Tech</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>736.03</v>
+        <v>404.11</v>
       </c>
       <c r="D10" t="n">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.44</v>
+        <v>-6.77</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7</v>
+        <v>0.76</v>
       </c>
       <c r="G10" t="n">
-        <v>7.35</v>
+        <v>18.51</v>
       </c>
       <c r="H10" t="n">
-        <v>1</v>
+        <v>4.58</v>
       </c>
       <c r="I10" t="n">
-        <v>733.09</v>
+        <v>396.7</v>
       </c>
       <c r="J10" t="n">
-        <v>737.87</v>
+        <v>408.74</v>
       </c>
       <c r="K10" t="n">
-        <v>725.01</v>
+        <v>376.34</v>
       </c>
       <c r="L10" t="n">
-        <v>754.42</v>
+        <v>450.4</v>
       </c>
       <c r="M10" t="n">
-        <v>70</v>
+        <v>60.95</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>MEDIO</t>
+          <t>BAJO</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1041,53 +1041,57 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>SPY</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>IA / Chips</t>
+          <t>ETF Mercado</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>416.29</v>
+        <v>733.78</v>
       </c>
       <c r="D11" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E11" t="n">
-        <v>-9.26</v>
+        <v>-0.6</v>
       </c>
       <c r="F11" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="G11" t="n">
-        <v>28.01</v>
+        <v>7.59</v>
       </c>
       <c r="H11" t="n">
-        <v>6.73</v>
+        <v>1.03</v>
       </c>
       <c r="I11" t="n">
-        <v>405.09</v>
+        <v>730.74</v>
       </c>
       <c r="J11" t="n">
-        <v>423.29</v>
+        <v>735.6799999999999</v>
       </c>
       <c r="K11" t="n">
-        <v>374.28</v>
+        <v>722.4</v>
       </c>
       <c r="L11" t="n">
-        <v>486.31</v>
+        <v>752.75</v>
       </c>
       <c r="M11" t="n">
-        <v>68.59</v>
+        <v>67.62</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>MEDIO</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr"/>
+          <t>BAJO</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>🔥</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>POSIBLE COMPRA</t>
@@ -1097,7 +1101,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>AVGO</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1106,41 +1110,41 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>418.55</v>
+        <v>414.05</v>
       </c>
       <c r="D12" t="n">
         <v>76</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.31</v>
+        <v>-7.64</v>
       </c>
       <c r="F12" t="n">
-        <v>0.58</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="G12" t="n">
-        <v>16.3</v>
+        <v>29.02</v>
       </c>
       <c r="H12" t="n">
-        <v>3.89</v>
+        <v>7.01</v>
       </c>
       <c r="I12" t="n">
-        <v>412.02</v>
+        <v>402.44</v>
       </c>
       <c r="J12" t="n">
-        <v>422.62</v>
+        <v>421.3</v>
       </c>
       <c r="K12" t="n">
-        <v>394.09</v>
+        <v>370.53</v>
       </c>
       <c r="L12" t="n">
-        <v>459.3</v>
+        <v>486.59</v>
       </c>
       <c r="M12" t="n">
-        <v>57.38</v>
+        <v>66.12</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>BAJO</t>
+          <t>MEDIO</t>
         </is>
       </c>
       <c r="O12" t="inlineStr"/>
@@ -1153,46 +1157,46 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>AMZN</t>
+          <t>AVGO</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Tecnología</t>
+          <t>IA / Chips</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>264.16</v>
+        <v>411.07</v>
       </c>
       <c r="D13" t="n">
         <v>76</v>
       </c>
       <c r="E13" t="n">
-        <v>-1.8</v>
+        <v>-1.96</v>
       </c>
       <c r="F13" t="n">
-        <v>0.58</v>
+        <v>1.01</v>
       </c>
       <c r="G13" t="n">
-        <v>7.32</v>
+        <v>16.73</v>
       </c>
       <c r="H13" t="n">
-        <v>2.77</v>
+        <v>4.07</v>
       </c>
       <c r="I13" t="n">
-        <v>261.23</v>
+        <v>404.38</v>
       </c>
       <c r="J13" t="n">
-        <v>265.99</v>
+        <v>415.25</v>
       </c>
       <c r="K13" t="n">
-        <v>253.18</v>
+        <v>385.98</v>
       </c>
       <c r="L13" t="n">
-        <v>282.46</v>
+        <v>452.89</v>
       </c>
       <c r="M13" t="n">
-        <v>55.9</v>
+        <v>52.18</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
@@ -1209,50 +1213,50 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>SMCI</t>
+          <t>ASML</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Servidores IA</t>
+          <t>Chips</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>30.45</v>
+        <v>1459.44</v>
       </c>
       <c r="D14" t="n">
         <v>76</v>
       </c>
       <c r="E14" t="n">
-        <v>-9.140000000000001</v>
+        <v>-4.04</v>
       </c>
       <c r="F14" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.79</v>
       </c>
       <c r="G14" t="n">
-        <v>2.32</v>
+        <v>67.13</v>
       </c>
       <c r="H14" t="n">
-        <v>7.62</v>
+        <v>4.6</v>
       </c>
       <c r="I14" t="n">
-        <v>29.53</v>
+        <v>1432.59</v>
       </c>
       <c r="J14" t="n">
-        <v>31.03</v>
+        <v>1476.22</v>
       </c>
       <c r="K14" t="n">
-        <v>26.98</v>
+        <v>1358.74</v>
       </c>
       <c r="L14" t="n">
-        <v>36.25</v>
+        <v>1627.27</v>
       </c>
       <c r="M14" t="n">
-        <v>58.08</v>
+        <v>55.28</v>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>MEDIO</t>
+          <t>BAJO</t>
         </is>
       </c>
       <c r="O14" t="inlineStr"/>
@@ -1265,46 +1269,46 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>AMAT</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Chips</t>
+          <t>Equipos chips</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>393.54</v>
+        <v>406.91</v>
       </c>
       <c r="D15" t="n">
         <v>76</v>
       </c>
       <c r="E15" t="n">
-        <v>-2.72</v>
+        <v>-5.63</v>
       </c>
       <c r="F15" t="n">
-        <v>0.68</v>
+        <v>1</v>
       </c>
       <c r="G15" t="n">
-        <v>15.28</v>
+        <v>20.08</v>
       </c>
       <c r="H15" t="n">
-        <v>3.88</v>
+        <v>4.93</v>
       </c>
       <c r="I15" t="n">
-        <v>387.43</v>
+        <v>398.88</v>
       </c>
       <c r="J15" t="n">
-        <v>397.36</v>
+        <v>411.93</v>
       </c>
       <c r="K15" t="n">
-        <v>370.62</v>
+        <v>376.79</v>
       </c>
       <c r="L15" t="n">
-        <v>431.74</v>
+        <v>457.11</v>
       </c>
       <c r="M15" t="n">
-        <v>50.55</v>
+        <v>57.45</v>
       </c>
       <c r="N15" t="inlineStr">
         <is>
@@ -1321,158 +1325,166 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>ASML</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Chips</t>
+          <t>Tecnología</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1465.23</v>
+        <v>417.42</v>
       </c>
       <c r="D16" t="n">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="E16" t="n">
-        <v>-6.42</v>
+        <v>2.37</v>
       </c>
       <c r="F16" t="n">
-        <v>0.76</v>
+        <v>0.85</v>
       </c>
       <c r="G16" t="n">
-        <v>65.73</v>
+        <v>12.03</v>
       </c>
       <c r="H16" t="n">
-        <v>4.49</v>
+        <v>2.88</v>
       </c>
       <c r="I16" t="n">
-        <v>1438.94</v>
+        <v>412.61</v>
       </c>
       <c r="J16" t="n">
-        <v>1481.67</v>
+        <v>420.43</v>
       </c>
       <c r="K16" t="n">
-        <v>1366.65</v>
+        <v>399.37</v>
       </c>
       <c r="L16" t="n">
-        <v>1629.55</v>
+        <v>447.5</v>
       </c>
       <c r="M16" t="n">
-        <v>56.47</v>
+        <v>45.36</v>
       </c>
       <c r="N16" t="inlineStr">
         <is>
           <t>BAJO</t>
         </is>
       </c>
-      <c r="O16" t="inlineStr"/>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>🔥</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>POSIBLE COMPRA</t>
+          <t>VIGILAR</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>AMAT</t>
+          <t>SOUN</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Equipos chips</t>
+          <t>IA</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>411.61</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="D17" t="n">
-        <v>76</v>
+        <v>66</v>
       </c>
       <c r="E17" t="n">
-        <v>-7.22</v>
+        <v>4.84</v>
       </c>
       <c r="F17" t="n">
-        <v>0.76</v>
+        <v>0.63</v>
       </c>
       <c r="G17" t="n">
-        <v>19.42</v>
+        <v>0.66</v>
       </c>
       <c r="H17" t="n">
-        <v>4.72</v>
+        <v>7.81</v>
       </c>
       <c r="I17" t="n">
-        <v>403.84</v>
+        <v>8.19</v>
       </c>
       <c r="J17" t="n">
-        <v>416.47</v>
+        <v>8.609999999999999</v>
       </c>
       <c r="K17" t="n">
-        <v>382.47</v>
+        <v>7.46</v>
       </c>
       <c r="L17" t="n">
-        <v>460.17</v>
+        <v>10.1</v>
       </c>
       <c r="M17" t="n">
-        <v>59.53</v>
+        <v>57.31</v>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>BAJO</t>
-        </is>
-      </c>
-      <c r="O17" t="inlineStr"/>
+          <t>MEDIO</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>🔥</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>POSIBLE COMPRA</t>
+          <t>VIGILAR</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>LRCX</t>
+          <t>QQQ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Equipos chips</t>
+          <t>ETF Nasdaq</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>275.67</v>
+        <v>701.53</v>
       </c>
       <c r="D18" t="n">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="E18" t="n">
-        <v>-6.89</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="F18" t="n">
-        <v>0.5</v>
+        <v>1.11</v>
       </c>
       <c r="G18" t="n">
-        <v>14.34</v>
+        <v>11.29</v>
       </c>
       <c r="H18" t="n">
-        <v>5.2</v>
+        <v>1.61</v>
       </c>
       <c r="I18" t="n">
-        <v>269.93</v>
+        <v>697.02</v>
       </c>
       <c r="J18" t="n">
-        <v>279.25</v>
+        <v>704.35</v>
       </c>
       <c r="K18" t="n">
-        <v>254.16</v>
+        <v>684.6</v>
       </c>
       <c r="L18" t="n">
-        <v>311.5</v>
+        <v>729.75</v>
       </c>
       <c r="M18" t="n">
-        <v>60.76</v>
+        <v>71.53</v>
       </c>
       <c r="N18" t="inlineStr">
         <is>
@@ -1482,64 +1494,60 @@
       <c r="O18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>POSIBLE COMPRA</t>
+          <t>VIGILAR</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>LRCX</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Tecnología</t>
+          <t>Equipos chips</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>422.55</v>
+        <v>273.38</v>
       </c>
       <c r="D19" t="n">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E19" t="n">
-        <v>2.4</v>
+        <v>-5.48</v>
       </c>
       <c r="F19" t="n">
-        <v>0.65</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="G19" t="n">
-        <v>11.52</v>
+        <v>14.53</v>
       </c>
       <c r="H19" t="n">
-        <v>2.73</v>
+        <v>5.31</v>
       </c>
       <c r="I19" t="n">
-        <v>417.94</v>
+        <v>267.57</v>
       </c>
       <c r="J19" t="n">
-        <v>425.43</v>
+        <v>277.01</v>
       </c>
       <c r="K19" t="n">
-        <v>405.28</v>
+        <v>251.59</v>
       </c>
       <c r="L19" t="n">
-        <v>451.34</v>
+        <v>309.69</v>
       </c>
       <c r="M19" t="n">
-        <v>45.44</v>
+        <v>60.86</v>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>BAJO</t>
-        </is>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>🔥</t>
-        </is>
-      </c>
+          <t>MEDIO</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>VIGILAR</t>
@@ -1549,110 +1557,106 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>META</t>
+          <t>SMCI</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Tecnología</t>
+          <t>Servidores IA</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>612.3200000000001</v>
+        <v>30.56</v>
       </c>
       <c r="D20" t="n">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="E20" t="n">
-        <v>2.25</v>
+        <v>-6.8</v>
       </c>
       <c r="F20" t="n">
-        <v>0.65</v>
+        <v>0.58</v>
       </c>
       <c r="G20" t="n">
-        <v>17.2</v>
+        <v>2.33</v>
       </c>
       <c r="H20" t="n">
-        <v>2.81</v>
+        <v>7.61</v>
       </c>
       <c r="I20" t="n">
-        <v>605.4400000000001</v>
+        <v>29.63</v>
       </c>
       <c r="J20" t="n">
-        <v>616.62</v>
+        <v>31.14</v>
       </c>
       <c r="K20" t="n">
-        <v>586.53</v>
+        <v>27.07</v>
       </c>
       <c r="L20" t="n">
-        <v>655.3099999999999</v>
+        <v>36.37</v>
       </c>
       <c r="M20" t="n">
-        <v>26.43</v>
+        <v>61.28</v>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>BAJO</t>
-        </is>
-      </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>🔥</t>
-        </is>
-      </c>
+          <t>MEDIO</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>NO COMPRAR</t>
+          <t>VIGILAR</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>ARM</t>
+          <t>AMZN</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Chips</t>
+          <t>Tecnología</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>209.83</v>
+        <v>259.34</v>
       </c>
       <c r="D21" t="n">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.33</v>
+        <v>-2.44</v>
       </c>
       <c r="F21" t="n">
-        <v>0.53</v>
+        <v>0.86</v>
       </c>
       <c r="G21" t="n">
-        <v>15.38</v>
+        <v>7.42</v>
       </c>
       <c r="H21" t="n">
-        <v>7.33</v>
+        <v>2.86</v>
       </c>
       <c r="I21" t="n">
-        <v>203.68</v>
+        <v>256.37</v>
       </c>
       <c r="J21" t="n">
-        <v>213.68</v>
+        <v>261.2</v>
       </c>
       <c r="K21" t="n">
-        <v>186.75</v>
+        <v>248.2</v>
       </c>
       <c r="L21" t="n">
-        <v>248.29</v>
+        <v>277.9</v>
       </c>
       <c r="M21" t="n">
-        <v>54.49</v>
+        <v>45.45</v>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>MEDIO</t>
+          <t>BAJO</t>
         </is>
       </c>
       <c r="O21" t="inlineStr"/>
@@ -1665,46 +1669,46 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>KLAC</t>
+          <t>TSM</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Equipos chips</t>
+          <t>Chips</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>1744.06</v>
+        <v>392.63</v>
       </c>
       <c r="D22" t="n">
         <v>64</v>
       </c>
       <c r="E22" t="n">
-        <v>-5.48</v>
+        <v>-1.17</v>
       </c>
       <c r="F22" t="n">
-        <v>0.5</v>
+        <v>0.85</v>
       </c>
       <c r="G22" t="n">
-        <v>85.22</v>
+        <v>15.72</v>
       </c>
       <c r="H22" t="n">
-        <v>4.89</v>
+        <v>4</v>
       </c>
       <c r="I22" t="n">
-        <v>1709.97</v>
+        <v>386.34</v>
       </c>
       <c r="J22" t="n">
-        <v>1765.37</v>
+        <v>396.56</v>
       </c>
       <c r="K22" t="n">
-        <v>1616.22</v>
+        <v>369.05</v>
       </c>
       <c r="L22" t="n">
-        <v>1957.12</v>
+        <v>431.93</v>
       </c>
       <c r="M22" t="n">
-        <v>45.09</v>
+        <v>49.44</v>
       </c>
       <c r="N22" t="inlineStr">
         <is>
@@ -1721,56 +1725,56 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>SOUN</t>
+          <t>KLAC</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>IA</t>
+          <t>Equipos chips</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>8.34</v>
+        <v>1740.58</v>
       </c>
       <c r="D23" t="n">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.36</v>
+        <v>-3.78</v>
       </c>
       <c r="F23" t="n">
-        <v>0.46</v>
+        <v>0.89</v>
       </c>
       <c r="G23" t="n">
-        <v>0.66</v>
+        <v>86.64</v>
       </c>
       <c r="H23" t="n">
-        <v>7.97</v>
+        <v>4.98</v>
       </c>
       <c r="I23" t="n">
-        <v>8.07</v>
+        <v>1705.93</v>
       </c>
       <c r="J23" t="n">
-        <v>8.5</v>
+        <v>1762.24</v>
       </c>
       <c r="K23" t="n">
-        <v>7.34</v>
+        <v>1610.62</v>
       </c>
       <c r="L23" t="n">
-        <v>9.99</v>
+        <v>1957.17</v>
       </c>
       <c r="M23" t="n">
-        <v>52.58</v>
+        <v>44.39</v>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>MEDIO</t>
+          <t>BAJO</t>
         </is>
       </c>
       <c r="O23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>NO COMPRAR</t>
+          <t>VIGILAR</t>
         </is>
       </c>
     </row>
@@ -1786,37 +1790,37 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>187</v>
+        <v>193.45</v>
       </c>
       <c r="D24" t="n">
-        <v>46</v>
+        <v>58</v>
       </c>
       <c r="E24" t="n">
-        <v>-13.67</v>
+        <v>-6.83</v>
       </c>
       <c r="F24" t="n">
-        <v>0.75</v>
+        <v>0.7</v>
       </c>
       <c r="G24" t="n">
-        <v>14.73</v>
+        <v>14.26</v>
       </c>
       <c r="H24" t="n">
-        <v>7.87</v>
+        <v>7.37</v>
       </c>
       <c r="I24" t="n">
-        <v>181.11</v>
+        <v>187.74</v>
       </c>
       <c r="J24" t="n">
-        <v>190.68</v>
+        <v>197.02</v>
       </c>
       <c r="K24" t="n">
-        <v>164.91</v>
+        <v>172.06</v>
       </c>
       <c r="L24" t="n">
-        <v>223.81</v>
+        <v>229.11</v>
       </c>
       <c r="M24" t="n">
-        <v>46.98</v>
+        <v>55.48</v>
       </c>
       <c r="N24" t="inlineStr">
         <is>
@@ -1842,37 +1846,37 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>76.36</v>
+        <v>74.16</v>
       </c>
       <c r="D25" t="n">
-        <v>46</v>
+        <v>58</v>
       </c>
       <c r="E25" t="n">
-        <v>-5.47</v>
+        <v>-5.25</v>
       </c>
       <c r="F25" t="n">
-        <v>0.58</v>
+        <v>0.71</v>
       </c>
       <c r="G25" t="n">
-        <v>4.54</v>
+        <v>3.96</v>
       </c>
       <c r="H25" t="n">
-        <v>5.94</v>
+        <v>5.33</v>
       </c>
       <c r="I25" t="n">
-        <v>74.54000000000001</v>
+        <v>72.58</v>
       </c>
       <c r="J25" t="n">
-        <v>77.48999999999999</v>
+        <v>75.15000000000001</v>
       </c>
       <c r="K25" t="n">
-        <v>69.55</v>
+        <v>68.23</v>
       </c>
       <c r="L25" t="n">
-        <v>87.70999999999999</v>
+        <v>84.05</v>
       </c>
       <c r="M25" t="n">
-        <v>42.55</v>
+        <v>54.99</v>
       </c>
       <c r="N25" t="inlineStr">
         <is>
@@ -1889,50 +1893,50 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>PYPL</t>
+          <t>AI</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Pagos</t>
+          <t>IA</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>44.31</v>
+        <v>8.82</v>
       </c>
       <c r="D26" t="n">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="E26" t="n">
-        <v>-1.68</v>
+        <v>0.4</v>
       </c>
       <c r="F26" t="n">
-        <v>0.43</v>
+        <v>0.78</v>
       </c>
       <c r="G26" t="n">
-        <v>1.53</v>
+        <v>0.46</v>
       </c>
       <c r="H26" t="n">
-        <v>3.45</v>
+        <v>5.16</v>
       </c>
       <c r="I26" t="n">
-        <v>43.7</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="J26" t="n">
-        <v>44.7</v>
+        <v>8.94</v>
       </c>
       <c r="K26" t="n">
-        <v>42.02</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="L26" t="n">
-        <v>48.14</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="M26" t="n">
-        <v>21.26</v>
+        <v>49.46</v>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>BAJO</t>
+          <t>MEDIO</t>
         </is>
       </c>
       <c r="O26" t="inlineStr"/>
@@ -1945,46 +1949,46 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>AI</t>
+          <t>UPST</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>IA</t>
+          <t>Fintech IA</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>8.74</v>
+        <v>28.08</v>
       </c>
       <c r="D27" t="n">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="E27" t="n">
-        <v>-7.75</v>
+        <v>0.86</v>
       </c>
       <c r="F27" t="n">
-        <v>0.77</v>
+        <v>1.13</v>
       </c>
       <c r="G27" t="n">
-        <v>0.46</v>
+        <v>1.87</v>
       </c>
       <c r="H27" t="n">
-        <v>5.24</v>
+        <v>6.64</v>
       </c>
       <c r="I27" t="n">
-        <v>8.56</v>
+        <v>27.33</v>
       </c>
       <c r="J27" t="n">
-        <v>8.859999999999999</v>
+        <v>28.55</v>
       </c>
       <c r="K27" t="n">
-        <v>8.06</v>
+        <v>25.28</v>
       </c>
       <c r="L27" t="n">
-        <v>9.890000000000001</v>
+        <v>32.74</v>
       </c>
       <c r="M27" t="n">
-        <v>46.59</v>
+        <v>40.94</v>
       </c>
       <c r="N27" t="inlineStr">
         <is>
@@ -2001,46 +2005,46 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>PLTR</t>
+          <t>META</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>IA / Software</t>
+          <t>Tecnología</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>133.76</v>
+        <v>602.61</v>
       </c>
       <c r="D28" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="E28" t="n">
-        <v>-2.29</v>
+        <v>-0.06</v>
       </c>
       <c r="F28" t="n">
-        <v>0.57</v>
+        <v>0.67</v>
       </c>
       <c r="G28" t="n">
-        <v>5.8</v>
+        <v>17.4</v>
       </c>
       <c r="H28" t="n">
-        <v>4.34</v>
+        <v>2.89</v>
       </c>
       <c r="I28" t="n">
-        <v>131.43</v>
+        <v>595.65</v>
       </c>
       <c r="J28" t="n">
-        <v>135.21</v>
+        <v>606.96</v>
       </c>
       <c r="K28" t="n">
-        <v>125.05</v>
+        <v>576.5</v>
       </c>
       <c r="L28" t="n">
-        <v>148.27</v>
+        <v>646.12</v>
       </c>
       <c r="M28" t="n">
-        <v>40.59</v>
+        <v>24.93</v>
       </c>
       <c r="N28" t="inlineStr">
         <is>
@@ -2057,50 +2061,50 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>UPST</t>
+          <t>PYPL</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Fintech IA</t>
+          <t>Pagos</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>27.69</v>
+        <v>43.83</v>
       </c>
       <c r="D29" t="n">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="E29" t="n">
-        <v>-3.47</v>
+        <v>-3.54</v>
       </c>
       <c r="F29" t="n">
-        <v>0.88</v>
+        <v>0.91</v>
       </c>
       <c r="G29" t="n">
-        <v>1.95</v>
+        <v>1.43</v>
       </c>
       <c r="H29" t="n">
-        <v>7.06</v>
+        <v>3.26</v>
       </c>
       <c r="I29" t="n">
-        <v>26.91</v>
+        <v>43.26</v>
       </c>
       <c r="J29" t="n">
-        <v>28.18</v>
+        <v>44.19</v>
       </c>
       <c r="K29" t="n">
-        <v>24.76</v>
+        <v>41.69</v>
       </c>
       <c r="L29" t="n">
-        <v>32.58</v>
+        <v>47.4</v>
       </c>
       <c r="M29" t="n">
-        <v>33.58</v>
+        <v>7.93</v>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>MEDIO</t>
+          <t>BAJO</t>
         </is>
       </c>
       <c r="O29" t="inlineStr"/>
@@ -2113,50 +2117,50 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>SOFI</t>
+          <t>PLTR</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Fintech</t>
+          <t>IA / Software</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>15.51</v>
+        <v>135.26</v>
       </c>
       <c r="D30" t="n">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="E30" t="n">
-        <v>-4.61</v>
+        <v>-0.54</v>
       </c>
       <c r="F30" t="n">
-        <v>0.84</v>
+        <v>0.67</v>
       </c>
       <c r="G30" t="n">
-        <v>0.84</v>
+        <v>5.62</v>
       </c>
       <c r="H30" t="n">
-        <v>5.44</v>
+        <v>4.15</v>
       </c>
       <c r="I30" t="n">
-        <v>15.17</v>
+        <v>133.01</v>
       </c>
       <c r="J30" t="n">
-        <v>15.72</v>
+        <v>136.66</v>
       </c>
       <c r="K30" t="n">
-        <v>14.24</v>
+        <v>126.84</v>
       </c>
       <c r="L30" t="n">
-        <v>17.62</v>
+        <v>149.3</v>
       </c>
       <c r="M30" t="n">
-        <v>31.4</v>
+        <v>46.36</v>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>MEDIO</t>
+          <t>BAJO</t>
         </is>
       </c>
       <c r="O30" t="inlineStr"/>
@@ -2169,56 +2173,56 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>MU</t>
+          <t>SOFI</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Memoria / Chips</t>
+          <t>Fintech</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>670.1900000000001</v>
+        <v>15.23</v>
       </c>
       <c r="D31" t="n">
-        <v>82</v>
+        <v>44</v>
       </c>
       <c r="E31" t="n">
-        <v>-15.73</v>
+        <v>-4.21</v>
       </c>
       <c r="F31" t="n">
-        <v>0.99</v>
+        <v>0.91</v>
       </c>
       <c r="G31" t="n">
-        <v>57.55</v>
+        <v>0.7</v>
       </c>
       <c r="H31" t="n">
-        <v>8.59</v>
+        <v>4.57</v>
       </c>
       <c r="I31" t="n">
-        <v>647.17</v>
+        <v>14.95</v>
       </c>
       <c r="J31" t="n">
-        <v>684.58</v>
+        <v>15.4</v>
       </c>
       <c r="K31" t="n">
-        <v>583.87</v>
+        <v>14.19</v>
       </c>
       <c r="L31" t="n">
-        <v>814.0599999999999</v>
+        <v>16.97</v>
       </c>
       <c r="M31" t="n">
-        <v>65.56999999999999</v>
+        <v>47.22</v>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>ALTO</t>
+          <t>BAJO</t>
         </is>
       </c>
       <c r="O31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>VIGILAR</t>
+          <t>NO COMPRAR</t>
         </is>
       </c>
     </row>
@@ -2234,37 +2238,37 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>296.72</v>
+        <v>298.97</v>
       </c>
       <c r="D32" t="n">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="E32" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="F32" t="n">
-        <v>0.5</v>
+        <v>0.73</v>
       </c>
       <c r="G32" t="n">
-        <v>6.67</v>
+        <v>6.68</v>
       </c>
       <c r="H32" t="n">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="I32" t="n">
-        <v>294.05</v>
+        <v>296.3</v>
       </c>
       <c r="J32" t="n">
-        <v>298.39</v>
+        <v>300.64</v>
       </c>
       <c r="K32" t="n">
-        <v>286.71</v>
+        <v>288.94</v>
       </c>
       <c r="L32" t="n">
-        <v>313.4</v>
+        <v>315.68</v>
       </c>
       <c r="M32" t="n">
-        <v>80.41</v>
+        <v>84.06</v>
       </c>
       <c r="N32" t="inlineStr">
         <is>
@@ -2281,46 +2285,46 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>QCOM</t>
+          <t>MU</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Chips</t>
+          <t>Memoria / Chips</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>201.04</v>
+        <v>698.74</v>
       </c>
       <c r="D33" t="n">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="E33" t="n">
-        <v>-15.36</v>
+        <v>-8.85</v>
       </c>
       <c r="F33" t="n">
-        <v>0.46</v>
+        <v>1.19</v>
       </c>
       <c r="G33" t="n">
-        <v>19.37</v>
+        <v>60.9</v>
       </c>
       <c r="H33" t="n">
-        <v>9.630000000000001</v>
+        <v>8.720000000000001</v>
       </c>
       <c r="I33" t="n">
-        <v>193.29</v>
+        <v>674.38</v>
       </c>
       <c r="J33" t="n">
-        <v>205.88</v>
+        <v>713.97</v>
       </c>
       <c r="K33" t="n">
-        <v>171.99</v>
+        <v>607.38</v>
       </c>
       <c r="L33" t="n">
-        <v>249.45</v>
+        <v>851</v>
       </c>
       <c r="M33" t="n">
-        <v>66.47</v>
+        <v>67.19</v>
       </c>
       <c r="N33" t="inlineStr">
         <is>
@@ -2346,37 +2350,37 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>107.14</v>
+        <v>110.8</v>
       </c>
       <c r="D34" t="n">
         <v>72</v>
       </c>
       <c r="E34" t="n">
-        <v>-17.23</v>
+        <v>-8.130000000000001</v>
       </c>
       <c r="F34" t="n">
-        <v>0.75</v>
+        <v>0.9</v>
       </c>
       <c r="G34" t="n">
-        <v>9.73</v>
+        <v>9.74</v>
       </c>
       <c r="H34" t="n">
-        <v>9.08</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I34" t="n">
-        <v>103.25</v>
+        <v>106.9</v>
       </c>
       <c r="J34" t="n">
-        <v>109.57</v>
+        <v>113.24</v>
       </c>
       <c r="K34" t="n">
-        <v>92.55</v>
+        <v>96.18000000000001</v>
       </c>
       <c r="L34" t="n">
-        <v>131.46</v>
+        <v>135.16</v>
       </c>
       <c r="M34" t="n">
-        <v>63.76</v>
+        <v>60.91</v>
       </c>
       <c r="N34" t="inlineStr">
         <is>
@@ -2393,46 +2397,46 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>GOOGL</t>
+          <t>QCOM</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Tecnología</t>
+          <t>Chips</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>398.14</v>
+        <v>195.61</v>
       </c>
       <c r="D35" t="n">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="E35" t="n">
-        <v>2.45</v>
+        <v>-6.99</v>
       </c>
       <c r="F35" t="n">
-        <v>0.72</v>
+        <v>0.6</v>
       </c>
       <c r="G35" t="n">
-        <v>11.63</v>
+        <v>19.75</v>
       </c>
       <c r="H35" t="n">
-        <v>2.92</v>
+        <v>10.1</v>
       </c>
       <c r="I35" t="n">
-        <v>393.49</v>
+        <v>187.71</v>
       </c>
       <c r="J35" t="n">
-        <v>401.05</v>
+        <v>200.55</v>
       </c>
       <c r="K35" t="n">
-        <v>380.7</v>
+        <v>165.98</v>
       </c>
       <c r="L35" t="n">
-        <v>427.21</v>
+        <v>245</v>
       </c>
       <c r="M35" t="n">
-        <v>76.31</v>
+        <v>62.48</v>
       </c>
       <c r="N35" t="inlineStr">
         <is>
@@ -2458,37 +2462,37 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>129.78</v>
+        <v>127.31</v>
       </c>
       <c r="D36" t="n">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="E36" t="n">
-        <v>10.59</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="F36" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="G36" t="n">
-        <v>10.28</v>
+        <v>11.09</v>
       </c>
       <c r="H36" t="n">
-        <v>7.92</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="I36" t="n">
-        <v>125.66</v>
+        <v>122.87</v>
       </c>
       <c r="J36" t="n">
-        <v>132.35</v>
+        <v>130.08</v>
       </c>
       <c r="K36" t="n">
-        <v>114.35</v>
+        <v>110.67</v>
       </c>
       <c r="L36" t="n">
-        <v>155.49</v>
+        <v>155.04</v>
       </c>
       <c r="M36" t="n">
-        <v>77.66</v>
+        <v>76.14</v>
       </c>
       <c r="N36" t="inlineStr">
         <is>
@@ -2514,37 +2518,37 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>48.69</v>
+        <v>48.44</v>
       </c>
       <c r="D37" t="n">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="E37" t="n">
-        <v>-14.4</v>
+        <v>-13.3</v>
       </c>
       <c r="F37" t="n">
-        <v>0.55</v>
+        <v>0.59</v>
       </c>
       <c r="G37" t="n">
-        <v>4.91</v>
+        <v>4.95</v>
       </c>
       <c r="H37" t="n">
-        <v>10.08</v>
+        <v>10.23</v>
       </c>
       <c r="I37" t="n">
-        <v>46.73</v>
+        <v>46.46</v>
       </c>
       <c r="J37" t="n">
-        <v>49.92</v>
+        <v>49.68</v>
       </c>
       <c r="K37" t="n">
-        <v>41.33</v>
+        <v>41.01</v>
       </c>
       <c r="L37" t="n">
-        <v>60.97</v>
+        <v>60.82</v>
       </c>
       <c r="M37" t="n">
-        <v>57.19</v>
+        <v>58.26</v>
       </c>
       <c r="N37" t="inlineStr">
         <is>
@@ -2554,7 +2558,7 @@
       <c r="O37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>VIGILAR</t>
+          <t>NO COMPRAR</t>
         </is>
       </c>
     </row>

--- a/analisis_acciones.xlsx
+++ b/analisis_acciones.xlsx
@@ -510,46 +510,46 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>197.33</v>
+        <v>191.33</v>
       </c>
       <c r="D2" t="n">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="E2" t="n">
-        <v>6.12</v>
+        <v>3.81</v>
       </c>
       <c r="F2" t="n">
-        <v>0.93</v>
+        <v>1.44</v>
       </c>
       <c r="G2" t="n">
-        <v>4.55</v>
+        <v>4.6</v>
       </c>
       <c r="H2" t="n">
-        <v>2.3</v>
+        <v>2.41</v>
       </c>
       <c r="I2" t="n">
-        <v>195.51</v>
+        <v>189.49</v>
       </c>
       <c r="J2" t="n">
-        <v>198.47</v>
+        <v>192.48</v>
       </c>
       <c r="K2" t="n">
-        <v>190.51</v>
+        <v>184.42</v>
       </c>
       <c r="L2" t="n">
-        <v>208.7</v>
+        <v>202.84</v>
       </c>
       <c r="M2" t="n">
-        <v>57.86</v>
+        <v>49.71</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>MEDIO</t>
+          <t>BAJO</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>🔥🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -570,37 +570,37 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>56.78</v>
+        <v>57.28</v>
       </c>
       <c r="D3" t="n">
         <v>95</v>
       </c>
       <c r="E3" t="n">
-        <v>2.05</v>
+        <v>3.43</v>
       </c>
       <c r="F3" t="n">
-        <v>0.53</v>
+        <v>0.88</v>
       </c>
       <c r="G3" t="n">
-        <v>1.46</v>
+        <v>1.41</v>
       </c>
       <c r="H3" t="n">
-        <v>2.57</v>
+        <v>2.46</v>
       </c>
       <c r="I3" t="n">
-        <v>56.2</v>
+        <v>56.72</v>
       </c>
       <c r="J3" t="n">
-        <v>57.14</v>
+        <v>57.63</v>
       </c>
       <c r="K3" t="n">
-        <v>54.59</v>
+        <v>55.17</v>
       </c>
       <c r="L3" t="n">
-        <v>60.43</v>
+        <v>60.8</v>
       </c>
       <c r="M3" t="n">
-        <v>54.63</v>
+        <v>51.82</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -630,41 +630,41 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>162.63</v>
+        <v>156.28</v>
       </c>
       <c r="D4" t="n">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E4" t="n">
-        <v>8.699999999999999</v>
+        <v>3.81</v>
       </c>
       <c r="F4" t="n">
         <v>0.85</v>
       </c>
       <c r="G4" t="n">
-        <v>4.17</v>
+        <v>4.39</v>
       </c>
       <c r="H4" t="n">
-        <v>2.57</v>
+        <v>2.81</v>
       </c>
       <c r="I4" t="n">
-        <v>160.96</v>
+        <v>154.52</v>
       </c>
       <c r="J4" t="n">
-        <v>163.67</v>
+        <v>157.38</v>
       </c>
       <c r="K4" t="n">
-        <v>156.37</v>
+        <v>149.69</v>
       </c>
       <c r="L4" t="n">
-        <v>173.06</v>
+        <v>167.26</v>
       </c>
       <c r="M4" t="n">
-        <v>63.52</v>
+        <v>53.82</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>MEDIO</t>
+          <t>BAJO</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -681,46 +681,46 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SOXX</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ETF Chips</t>
+          <t>Tecnología</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>496.74</v>
+        <v>421.06</v>
       </c>
       <c r="D5" t="n">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="E5" t="n">
-        <v>-3.73</v>
+        <v>3.91</v>
       </c>
       <c r="F5" t="n">
-        <v>1.44</v>
+        <v>0.8</v>
       </c>
       <c r="G5" t="n">
-        <v>21.02</v>
+        <v>10.91</v>
       </c>
       <c r="H5" t="n">
-        <v>4.23</v>
+        <v>2.59</v>
       </c>
       <c r="I5" t="n">
-        <v>488.33</v>
+        <v>416.69</v>
       </c>
       <c r="J5" t="n">
-        <v>501.99</v>
+        <v>423.79</v>
       </c>
       <c r="K5" t="n">
-        <v>465.22</v>
+        <v>404.69</v>
       </c>
       <c r="L5" t="n">
-        <v>549.28</v>
+        <v>448.35</v>
       </c>
       <c r="M5" t="n">
-        <v>62.63</v>
+        <v>60.58</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
@@ -750,41 +750,41 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>60.72</v>
+        <v>58.87</v>
       </c>
       <c r="D6" t="n">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="E6" t="n">
-        <v>7.91</v>
+        <v>4.79</v>
       </c>
       <c r="F6" t="n">
-        <v>0.95</v>
+        <v>0.93</v>
       </c>
       <c r="G6" t="n">
-        <v>1.94</v>
+        <v>1.98</v>
       </c>
       <c r="H6" t="n">
-        <v>3.2</v>
+        <v>3.37</v>
       </c>
       <c r="I6" t="n">
-        <v>59.94</v>
+        <v>58.08</v>
       </c>
       <c r="J6" t="n">
-        <v>61.21</v>
+        <v>59.37</v>
       </c>
       <c r="K6" t="n">
-        <v>57.8</v>
+        <v>55.89</v>
       </c>
       <c r="L6" t="n">
-        <v>65.58</v>
+        <v>63.83</v>
       </c>
       <c r="M6" t="n">
-        <v>49.89</v>
+        <v>45.8</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>MEDIO</t>
+          <t>BAJO</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -801,7 +801,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ARM</t>
+          <t>TSM</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -810,46 +810,46 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>223.15</v>
+        <v>401.62</v>
       </c>
       <c r="D7" t="n">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="E7" t="n">
-        <v>7.32</v>
+        <v>0.46</v>
       </c>
       <c r="F7" t="n">
-        <v>0.92</v>
+        <v>0.7</v>
       </c>
       <c r="G7" t="n">
-        <v>16.39</v>
+        <v>15.59</v>
       </c>
       <c r="H7" t="n">
-        <v>7.34</v>
+        <v>3.88</v>
       </c>
       <c r="I7" t="n">
-        <v>216.59</v>
+        <v>395.38</v>
       </c>
       <c r="J7" t="n">
-        <v>227.25</v>
+        <v>405.52</v>
       </c>
       <c r="K7" t="n">
-        <v>198.57</v>
+        <v>378.24</v>
       </c>
       <c r="L7" t="n">
-        <v>264.12</v>
+        <v>440.59</v>
       </c>
       <c r="M7" t="n">
-        <v>57.96</v>
+        <v>52.43</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>MEDIO</t>
+          <t>BAJO</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -861,46 +861,46 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>NVDA</t>
+          <t>SPY</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>IA / Chips</t>
+          <t>ETF Mercado</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>220.61</v>
+        <v>741.25</v>
       </c>
       <c r="D8" t="n">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.08</v>
+        <v>-0.14</v>
       </c>
       <c r="F8" t="n">
-        <v>0.83</v>
+        <v>0.93</v>
       </c>
       <c r="G8" t="n">
-        <v>8.51</v>
+        <v>7.5</v>
       </c>
       <c r="H8" t="n">
-        <v>3.86</v>
+        <v>1.01</v>
       </c>
       <c r="I8" t="n">
-        <v>217.21</v>
+        <v>738.25</v>
       </c>
       <c r="J8" t="n">
-        <v>222.74</v>
+        <v>743.13</v>
       </c>
       <c r="K8" t="n">
-        <v>207.84</v>
+        <v>730</v>
       </c>
       <c r="L8" t="n">
-        <v>241.89</v>
+        <v>760.01</v>
       </c>
       <c r="M8" t="n">
-        <v>58.45</v>
+        <v>67.79000000000001</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
@@ -921,46 +921,46 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>GOOGL</t>
+          <t>NVDA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Tecnología</t>
+          <t>IA / Chips</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>387.66</v>
+        <v>223.47</v>
       </c>
       <c r="D9" t="n">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="E9" t="n">
-        <v>0.08</v>
+        <v>-1.05</v>
       </c>
       <c r="F9" t="n">
-        <v>1.13</v>
+        <v>1.07</v>
       </c>
       <c r="G9" t="n">
-        <v>11.59</v>
+        <v>8.09</v>
       </c>
       <c r="H9" t="n">
-        <v>2.99</v>
+        <v>3.62</v>
       </c>
       <c r="I9" t="n">
-        <v>383.02</v>
+        <v>220.24</v>
       </c>
       <c r="J9" t="n">
-        <v>390.56</v>
+        <v>225.49</v>
       </c>
       <c r="K9" t="n">
-        <v>370.28</v>
+        <v>211.34</v>
       </c>
       <c r="L9" t="n">
-        <v>416.63</v>
+        <v>243.68</v>
       </c>
       <c r="M9" t="n">
-        <v>68.89</v>
+        <v>69.8</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
@@ -981,46 +981,46 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>TSLA</t>
+          <t>AVGO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Autos / Tech</t>
+          <t>IA / Chips</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>404.11</v>
+        <v>417.76</v>
       </c>
       <c r="D10" t="n">
         <v>84</v>
       </c>
       <c r="E10" t="n">
-        <v>-6.77</v>
+        <v>0.23</v>
       </c>
       <c r="F10" t="n">
-        <v>0.76</v>
+        <v>0.85</v>
       </c>
       <c r="G10" t="n">
-        <v>18.51</v>
+        <v>16.66</v>
       </c>
       <c r="H10" t="n">
-        <v>4.58</v>
+        <v>3.99</v>
       </c>
       <c r="I10" t="n">
-        <v>396.7</v>
+        <v>411.1</v>
       </c>
       <c r="J10" t="n">
-        <v>408.74</v>
+        <v>421.92</v>
       </c>
       <c r="K10" t="n">
-        <v>376.34</v>
+        <v>392.78</v>
       </c>
       <c r="L10" t="n">
-        <v>450.4</v>
+        <v>459.4</v>
       </c>
       <c r="M10" t="n">
-        <v>60.95</v>
+        <v>50.13</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
@@ -1041,46 +1041,46 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SPY</t>
+          <t>GOOGL</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>ETF Mercado</t>
+          <t>Tecnología</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>733.78</v>
+        <v>388.91</v>
       </c>
       <c r="D11" t="n">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.6</v>
+        <v>-3.41</v>
       </c>
       <c r="F11" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="G11" t="n">
-        <v>7.59</v>
+        <v>9.81</v>
       </c>
       <c r="H11" t="n">
-        <v>1.03</v>
+        <v>2.52</v>
       </c>
       <c r="I11" t="n">
-        <v>730.74</v>
+        <v>384.99</v>
       </c>
       <c r="J11" t="n">
-        <v>735.6799999999999</v>
+        <v>391.36</v>
       </c>
       <c r="K11" t="n">
-        <v>722.4</v>
+        <v>374.2</v>
       </c>
       <c r="L11" t="n">
-        <v>752.75</v>
+        <v>413.43</v>
       </c>
       <c r="M11" t="n">
-        <v>67.62</v>
+        <v>53.1</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
@@ -1101,53 +1101,57 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>ASML</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>IA / Chips</t>
+          <t>Chips</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>414.05</v>
+        <v>1550.13</v>
       </c>
       <c r="D12" t="n">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="E12" t="n">
-        <v>-7.64</v>
+        <v>-1.99</v>
       </c>
       <c r="F12" t="n">
-        <v>0.8100000000000001</v>
+        <v>1.03</v>
       </c>
       <c r="G12" t="n">
-        <v>29.02</v>
+        <v>70.26000000000001</v>
       </c>
       <c r="H12" t="n">
-        <v>7.01</v>
+        <v>4.53</v>
       </c>
       <c r="I12" t="n">
-        <v>402.44</v>
+        <v>1522.03</v>
       </c>
       <c r="J12" t="n">
-        <v>421.3</v>
+        <v>1567.7</v>
       </c>
       <c r="K12" t="n">
-        <v>370.53</v>
+        <v>1444.74</v>
       </c>
       <c r="L12" t="n">
-        <v>486.59</v>
+        <v>1725.78</v>
       </c>
       <c r="M12" t="n">
-        <v>66.12</v>
+        <v>58.35</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>MEDIO</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr"/>
+          <t>BAJO</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>🔥</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>POSIBLE COMPRA</t>
@@ -1157,53 +1161,57 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>AVGO</t>
+          <t>AMAT</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>IA / Chips</t>
+          <t>Equipos chips</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>411.07</v>
+        <v>426.85</v>
       </c>
       <c r="D13" t="n">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="E13" t="n">
-        <v>-1.96</v>
+        <v>-2.24</v>
       </c>
       <c r="F13" t="n">
-        <v>1.01</v>
+        <v>0.85</v>
       </c>
       <c r="G13" t="n">
-        <v>16.73</v>
+        <v>20.59</v>
       </c>
       <c r="H13" t="n">
-        <v>4.07</v>
+        <v>4.82</v>
       </c>
       <c r="I13" t="n">
-        <v>404.38</v>
+        <v>418.61</v>
       </c>
       <c r="J13" t="n">
-        <v>415.25</v>
+        <v>432</v>
       </c>
       <c r="K13" t="n">
-        <v>385.98</v>
+        <v>395.97</v>
       </c>
       <c r="L13" t="n">
-        <v>452.89</v>
+        <v>478.33</v>
       </c>
       <c r="M13" t="n">
-        <v>52.18</v>
+        <v>59.45</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
           <t>BAJO</t>
         </is>
       </c>
-      <c r="O13" t="inlineStr"/>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>🔥</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>POSIBLE COMPRA</t>
@@ -1213,53 +1221,57 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>ASML</t>
+          <t>KLAC</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Chips</t>
+          <t>Equipos chips</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1459.44</v>
+        <v>1829.47</v>
       </c>
       <c r="D14" t="n">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="E14" t="n">
-        <v>-4.04</v>
+        <v>-0.97</v>
       </c>
       <c r="F14" t="n">
-        <v>0.79</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="G14" t="n">
-        <v>67.13</v>
+        <v>81.3</v>
       </c>
       <c r="H14" t="n">
-        <v>4.6</v>
+        <v>4.44</v>
       </c>
       <c r="I14" t="n">
-        <v>1432.59</v>
+        <v>1796.95</v>
       </c>
       <c r="J14" t="n">
-        <v>1476.22</v>
+        <v>1849.8</v>
       </c>
       <c r="K14" t="n">
-        <v>1358.74</v>
+        <v>1707.52</v>
       </c>
       <c r="L14" t="n">
-        <v>1627.27</v>
+        <v>2032.72</v>
       </c>
       <c r="M14" t="n">
-        <v>55.28</v>
+        <v>56.01</v>
       </c>
       <c r="N14" t="inlineStr">
         <is>
           <t>BAJO</t>
         </is>
       </c>
-      <c r="O14" t="inlineStr"/>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>🔥</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>POSIBLE COMPRA</t>
@@ -1269,53 +1281,57 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>AMAT</t>
+          <t>SOXX</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Equipos chips</t>
+          <t>ETF Chips</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>406.91</v>
+        <v>520.3099999999999</v>
       </c>
       <c r="D15" t="n">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="E15" t="n">
-        <v>-5.63</v>
+        <v>-1.51</v>
       </c>
       <c r="F15" t="n">
-        <v>1</v>
+        <v>1.09</v>
       </c>
       <c r="G15" t="n">
-        <v>20.08</v>
+        <v>21.8</v>
       </c>
       <c r="H15" t="n">
-        <v>4.93</v>
+        <v>4.19</v>
       </c>
       <c r="I15" t="n">
-        <v>398.88</v>
+        <v>511.59</v>
       </c>
       <c r="J15" t="n">
-        <v>411.93</v>
+        <v>525.76</v>
       </c>
       <c r="K15" t="n">
-        <v>376.79</v>
+        <v>487.61</v>
       </c>
       <c r="L15" t="n">
-        <v>457.11</v>
+        <v>574.8200000000001</v>
       </c>
       <c r="M15" t="n">
-        <v>57.45</v>
+        <v>64.93000000000001</v>
       </c>
       <c r="N15" t="inlineStr">
         <is>
           <t>BAJO</t>
         </is>
       </c>
-      <c r="O15" t="inlineStr"/>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>🔥</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>POSIBLE COMPRA</t>
@@ -1325,50 +1341,50 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>QQQ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Tecnología</t>
+          <t>ETF Nasdaq</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>417.42</v>
+        <v>713.15</v>
       </c>
       <c r="D16" t="n">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="E16" t="n">
-        <v>2.37</v>
+        <v>-0.22</v>
       </c>
       <c r="F16" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="G16" t="n">
-        <v>12.03</v>
+        <v>11.31</v>
       </c>
       <c r="H16" t="n">
-        <v>2.88</v>
+        <v>1.59</v>
       </c>
       <c r="I16" t="n">
-        <v>412.61</v>
+        <v>708.63</v>
       </c>
       <c r="J16" t="n">
-        <v>420.43</v>
+        <v>715.98</v>
       </c>
       <c r="K16" t="n">
-        <v>399.37</v>
+        <v>696.1900000000001</v>
       </c>
       <c r="L16" t="n">
-        <v>447.5</v>
+        <v>741.42</v>
       </c>
       <c r="M16" t="n">
-        <v>45.36</v>
+        <v>73.11</v>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>BAJO</t>
+          <t>MEDIO</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
@@ -1378,113 +1394,109 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>VIGILAR</t>
+          <t>POSIBLE COMPRA</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>SOUN</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>IA</t>
+          <t>IA / Chips</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>8.449999999999999</v>
+        <v>447.58</v>
       </c>
       <c r="D17" t="n">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="E17" t="n">
-        <v>4.84</v>
+        <v>0.47</v>
       </c>
       <c r="F17" t="n">
-        <v>0.63</v>
+        <v>0.78</v>
       </c>
       <c r="G17" t="n">
-        <v>0.66</v>
+        <v>29.94</v>
       </c>
       <c r="H17" t="n">
-        <v>7.81</v>
+        <v>6.69</v>
       </c>
       <c r="I17" t="n">
-        <v>8.19</v>
+        <v>435.6</v>
       </c>
       <c r="J17" t="n">
-        <v>8.609999999999999</v>
+        <v>455.07</v>
       </c>
       <c r="K17" t="n">
-        <v>7.46</v>
+        <v>402.67</v>
       </c>
       <c r="L17" t="n">
-        <v>10.1</v>
+        <v>522.4400000000001</v>
       </c>
       <c r="M17" t="n">
-        <v>57.31</v>
+        <v>68.27</v>
       </c>
       <c r="N17" t="inlineStr">
         <is>
           <t>MEDIO</t>
         </is>
       </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>🔥</t>
-        </is>
-      </c>
+      <c r="O17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>VIGILAR</t>
+          <t>POSIBLE COMPRA</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>QQQ</t>
+          <t>LRCX</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>ETF Nasdaq</t>
+          <t>Equipos chips</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>701.53</v>
+        <v>292.09</v>
       </c>
       <c r="D18" t="n">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.8100000000000001</v>
+        <v>-1.13</v>
       </c>
       <c r="F18" t="n">
-        <v>1.11</v>
+        <v>0.89</v>
       </c>
       <c r="G18" t="n">
-        <v>11.29</v>
+        <v>15.26</v>
       </c>
       <c r="H18" t="n">
-        <v>1.61</v>
+        <v>5.23</v>
       </c>
       <c r="I18" t="n">
-        <v>697.02</v>
+        <v>285.98</v>
       </c>
       <c r="J18" t="n">
-        <v>704.35</v>
+        <v>295.91</v>
       </c>
       <c r="K18" t="n">
-        <v>684.6</v>
+        <v>269.19</v>
       </c>
       <c r="L18" t="n">
-        <v>729.75</v>
+        <v>330.25</v>
       </c>
       <c r="M18" t="n">
-        <v>71.53</v>
+        <v>63.92</v>
       </c>
       <c r="N18" t="inlineStr">
         <is>
@@ -1494,60 +1506,64 @@
       <c r="O18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>VIGILAR</t>
+          <t>POSIBLE COMPRA</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>LRCX</t>
+          <t>SMCI</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Equipos chips</t>
+          <t>Servidores IA</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>273.38</v>
+        <v>33.46</v>
       </c>
       <c r="D19" t="n">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="E19" t="n">
-        <v>-5.48</v>
+        <v>4.56</v>
       </c>
       <c r="F19" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.95</v>
       </c>
       <c r="G19" t="n">
-        <v>14.53</v>
+        <v>2.48</v>
       </c>
       <c r="H19" t="n">
-        <v>5.31</v>
+        <v>7.42</v>
       </c>
       <c r="I19" t="n">
-        <v>267.57</v>
+        <v>32.47</v>
       </c>
       <c r="J19" t="n">
-        <v>277.01</v>
+        <v>34.08</v>
       </c>
       <c r="K19" t="n">
-        <v>251.59</v>
+        <v>29.74</v>
       </c>
       <c r="L19" t="n">
-        <v>309.69</v>
+        <v>39.67</v>
       </c>
       <c r="M19" t="n">
-        <v>60.86</v>
+        <v>64.69</v>
       </c>
       <c r="N19" t="inlineStr">
         <is>
           <t>MEDIO</t>
         </is>
       </c>
-      <c r="O19" t="inlineStr"/>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>🔥</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>VIGILAR</t>
@@ -1557,53 +1573,57 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>SMCI</t>
+          <t>AI</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Servidores IA</t>
+          <t>IA</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>30.56</v>
+        <v>9.279999999999999</v>
       </c>
       <c r="D20" t="n">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="E20" t="n">
-        <v>-6.8</v>
+        <v>7.28</v>
       </c>
       <c r="F20" t="n">
-        <v>0.58</v>
+        <v>1.11</v>
       </c>
       <c r="G20" t="n">
-        <v>2.33</v>
+        <v>0.48</v>
       </c>
       <c r="H20" t="n">
-        <v>7.61</v>
+        <v>5.22</v>
       </c>
       <c r="I20" t="n">
-        <v>29.63</v>
+        <v>9.09</v>
       </c>
       <c r="J20" t="n">
-        <v>31.14</v>
+        <v>9.4</v>
       </c>
       <c r="K20" t="n">
-        <v>27.07</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="L20" t="n">
-        <v>36.37</v>
+        <v>10.49</v>
       </c>
       <c r="M20" t="n">
-        <v>61.28</v>
+        <v>56.1</v>
       </c>
       <c r="N20" t="inlineStr">
         <is>
           <t>MEDIO</t>
         </is>
       </c>
-      <c r="O20" t="inlineStr"/>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>🔥</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>VIGILAR</t>
@@ -1613,53 +1633,57 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>AMZN</t>
+          <t>PLTR</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Tecnología</t>
+          <t>IA / Software</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>259.34</v>
+        <v>137.15</v>
       </c>
       <c r="D21" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.44</v>
+        <v>5.46</v>
       </c>
       <c r="F21" t="n">
-        <v>0.86</v>
+        <v>0.7</v>
       </c>
       <c r="G21" t="n">
-        <v>7.42</v>
+        <v>5.71</v>
       </c>
       <c r="H21" t="n">
-        <v>2.86</v>
+        <v>4.16</v>
       </c>
       <c r="I21" t="n">
-        <v>256.37</v>
+        <v>134.87</v>
       </c>
       <c r="J21" t="n">
-        <v>261.2</v>
+        <v>138.58</v>
       </c>
       <c r="K21" t="n">
-        <v>248.2</v>
+        <v>128.59</v>
       </c>
       <c r="L21" t="n">
-        <v>277.9</v>
+        <v>151.42</v>
       </c>
       <c r="M21" t="n">
-        <v>45.45</v>
+        <v>47.42</v>
       </c>
       <c r="N21" t="inlineStr">
         <is>
           <t>BAJO</t>
         </is>
       </c>
-      <c r="O21" t="inlineStr"/>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>🔥</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>VIGILAR</t>
@@ -1669,214 +1693,222 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>SOFI</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Chips</t>
+          <t>Fintech</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>392.63</v>
+        <v>15.69</v>
       </c>
       <c r="D22" t="n">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.17</v>
+        <v>2.48</v>
       </c>
       <c r="F22" t="n">
-        <v>0.85</v>
+        <v>0.64</v>
       </c>
       <c r="G22" t="n">
-        <v>15.72</v>
+        <v>0.68</v>
       </c>
       <c r="H22" t="n">
-        <v>4</v>
+        <v>4.36</v>
       </c>
       <c r="I22" t="n">
-        <v>386.34</v>
+        <v>15.42</v>
       </c>
       <c r="J22" t="n">
-        <v>396.56</v>
+        <v>15.86</v>
       </c>
       <c r="K22" t="n">
-        <v>369.05</v>
+        <v>14.66</v>
       </c>
       <c r="L22" t="n">
-        <v>431.93</v>
+        <v>17.4</v>
       </c>
       <c r="M22" t="n">
-        <v>49.44</v>
+        <v>46.05</v>
       </c>
       <c r="N22" t="inlineStr">
         <is>
           <t>BAJO</t>
         </is>
       </c>
-      <c r="O22" t="inlineStr"/>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>🔥</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>VIGILAR</t>
+          <t>NO COMPRAR</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>KLAC</t>
+          <t>UPST</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Equipos chips</t>
+          <t>Fintech IA</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>1740.58</v>
+        <v>28.84</v>
       </c>
       <c r="D23" t="n">
-        <v>64</v>
+        <v>46</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.78</v>
+        <v>6.85</v>
       </c>
       <c r="F23" t="n">
-        <v>0.89</v>
+        <v>0.91</v>
       </c>
       <c r="G23" t="n">
-        <v>86.64</v>
+        <v>1.92</v>
       </c>
       <c r="H23" t="n">
-        <v>4.98</v>
+        <v>6.65</v>
       </c>
       <c r="I23" t="n">
-        <v>1705.93</v>
+        <v>28.07</v>
       </c>
       <c r="J23" t="n">
-        <v>1762.24</v>
+        <v>29.32</v>
       </c>
       <c r="K23" t="n">
-        <v>1610.62</v>
+        <v>25.96</v>
       </c>
       <c r="L23" t="n">
-        <v>1957.17</v>
+        <v>33.64</v>
       </c>
       <c r="M23" t="n">
-        <v>44.39</v>
+        <v>39.38</v>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>BAJO</t>
-        </is>
-      </c>
-      <c r="O23" t="inlineStr"/>
+          <t>MEDIO</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>🔥</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>VIGILAR</t>
+          <t>NO COMPRAR</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>COIN</t>
+          <t>TSLA</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Cripto / Trading</t>
+          <t>Autos / Tech</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>193.45</v>
+        <v>417.26</v>
       </c>
       <c r="D24" t="n">
-        <v>58</v>
+        <v>74</v>
       </c>
       <c r="E24" t="n">
-        <v>-6.83</v>
+        <v>-6.29</v>
       </c>
       <c r="F24" t="n">
-        <v>0.7</v>
+        <v>0.77</v>
       </c>
       <c r="G24" t="n">
-        <v>14.26</v>
+        <v>18.28</v>
       </c>
       <c r="H24" t="n">
-        <v>7.37</v>
+        <v>4.38</v>
       </c>
       <c r="I24" t="n">
-        <v>187.74</v>
+        <v>409.95</v>
       </c>
       <c r="J24" t="n">
-        <v>197.02</v>
+        <v>421.83</v>
       </c>
       <c r="K24" t="n">
-        <v>172.06</v>
+        <v>389.83</v>
       </c>
       <c r="L24" t="n">
-        <v>229.11</v>
+        <v>462.97</v>
       </c>
       <c r="M24" t="n">
-        <v>55.48</v>
+        <v>62.09</v>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>MEDIO</t>
+          <t>BAJO</t>
         </is>
       </c>
       <c r="O24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>NO COMPRAR</t>
+          <t>VIGILAR</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>HOOD</t>
+          <t>SOUN</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Trading</t>
+          <t>IA</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>74.16</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="D25" t="n">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="E25" t="n">
-        <v>-5.25</v>
+        <v>0.36</v>
       </c>
       <c r="F25" t="n">
-        <v>0.71</v>
+        <v>0.62</v>
       </c>
       <c r="G25" t="n">
-        <v>3.96</v>
+        <v>0.65</v>
       </c>
       <c r="H25" t="n">
-        <v>5.33</v>
+        <v>7.74</v>
       </c>
       <c r="I25" t="n">
-        <v>72.58</v>
+        <v>8.19</v>
       </c>
       <c r="J25" t="n">
-        <v>75.15000000000001</v>
+        <v>8.609999999999999</v>
       </c>
       <c r="K25" t="n">
-        <v>68.23</v>
+        <v>7.47</v>
       </c>
       <c r="L25" t="n">
-        <v>84.05</v>
+        <v>10.09</v>
       </c>
       <c r="M25" t="n">
-        <v>54.99</v>
+        <v>55.09</v>
       </c>
       <c r="N25" t="inlineStr">
         <is>
@@ -1886,109 +1918,109 @@
       <c r="O25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>NO COMPRAR</t>
+          <t>VIGILAR</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>AI</t>
+          <t>AMZN</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>IA</t>
+          <t>Tecnología</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>8.82</v>
+        <v>265.01</v>
       </c>
       <c r="D26" t="n">
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="E26" t="n">
-        <v>0.4</v>
+        <v>-1.9</v>
       </c>
       <c r="F26" t="n">
-        <v>0.78</v>
+        <v>0.76</v>
       </c>
       <c r="G26" t="n">
-        <v>0.46</v>
+        <v>6.6</v>
       </c>
       <c r="H26" t="n">
-        <v>5.16</v>
+        <v>2.49</v>
       </c>
       <c r="I26" t="n">
-        <v>8.640000000000001</v>
+        <v>262.37</v>
       </c>
       <c r="J26" t="n">
-        <v>8.94</v>
+        <v>266.66</v>
       </c>
       <c r="K26" t="n">
-        <v>8.140000000000001</v>
+        <v>255.1</v>
       </c>
       <c r="L26" t="n">
-        <v>9.960000000000001</v>
+        <v>281.52</v>
       </c>
       <c r="M26" t="n">
-        <v>49.46</v>
+        <v>49.94</v>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>MEDIO</t>
+          <t>BAJO</t>
         </is>
       </c>
       <c r="O26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>NO COMPRAR</t>
+          <t>VIGILAR</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>UPST</t>
+          <t>COIN</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Fintech IA</t>
+          <t>Cripto / Trading</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>28.08</v>
+        <v>191.29</v>
       </c>
       <c r="D27" t="n">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="E27" t="n">
-        <v>0.86</v>
+        <v>-5.21</v>
       </c>
       <c r="F27" t="n">
-        <v>1.13</v>
+        <v>0.72</v>
       </c>
       <c r="G27" t="n">
-        <v>1.87</v>
+        <v>14.06</v>
       </c>
       <c r="H27" t="n">
-        <v>6.64</v>
+        <v>7.35</v>
       </c>
       <c r="I27" t="n">
-        <v>27.33</v>
+        <v>185.66</v>
       </c>
       <c r="J27" t="n">
-        <v>28.55</v>
+        <v>194.81</v>
       </c>
       <c r="K27" t="n">
-        <v>25.28</v>
+        <v>170.19</v>
       </c>
       <c r="L27" t="n">
-        <v>32.74</v>
+        <v>226.45</v>
       </c>
       <c r="M27" t="n">
-        <v>40.94</v>
+        <v>51.71</v>
       </c>
       <c r="N27" t="inlineStr">
         <is>
@@ -2005,50 +2037,50 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>META</t>
+          <t>HOOD</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Tecnología</t>
+          <t>Trading</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>602.61</v>
+        <v>75.76000000000001</v>
       </c>
       <c r="D28" t="n">
-        <v>46</v>
+        <v>58</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.06</v>
+        <v>-1.29</v>
       </c>
       <c r="F28" t="n">
-        <v>0.67</v>
+        <v>0.65</v>
       </c>
       <c r="G28" t="n">
-        <v>17.4</v>
+        <v>3.92</v>
       </c>
       <c r="H28" t="n">
-        <v>2.89</v>
+        <v>5.17</v>
       </c>
       <c r="I28" t="n">
-        <v>595.65</v>
+        <v>74.19</v>
       </c>
       <c r="J28" t="n">
-        <v>606.96</v>
+        <v>76.73999999999999</v>
       </c>
       <c r="K28" t="n">
-        <v>576.5</v>
+        <v>69.88</v>
       </c>
       <c r="L28" t="n">
-        <v>646.12</v>
+        <v>85.56</v>
       </c>
       <c r="M28" t="n">
-        <v>24.93</v>
+        <v>54.85</v>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>BAJO</t>
+          <t>MEDIO</t>
         </is>
       </c>
       <c r="O28" t="inlineStr"/>
@@ -2061,46 +2093,46 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>PYPL</t>
+          <t>META</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Pagos</t>
+          <t>Tecnología</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>43.83</v>
+        <v>605.0599999999999</v>
       </c>
       <c r="D29" t="n">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="E29" t="n">
-        <v>-3.54</v>
+        <v>-1.88</v>
       </c>
       <c r="F29" t="n">
-        <v>0.91</v>
+        <v>0.7</v>
       </c>
       <c r="G29" t="n">
-        <v>1.43</v>
+        <v>13.2</v>
       </c>
       <c r="H29" t="n">
-        <v>3.26</v>
+        <v>2.18</v>
       </c>
       <c r="I29" t="n">
-        <v>43.26</v>
+        <v>599.78</v>
       </c>
       <c r="J29" t="n">
-        <v>44.19</v>
+        <v>608.36</v>
       </c>
       <c r="K29" t="n">
-        <v>41.69</v>
+        <v>585.27</v>
       </c>
       <c r="L29" t="n">
-        <v>47.4</v>
+        <v>638.05</v>
       </c>
       <c r="M29" t="n">
-        <v>7.93</v>
+        <v>45.6</v>
       </c>
       <c r="N29" t="inlineStr">
         <is>
@@ -2117,46 +2149,46 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>PLTR</t>
+          <t>PYPL</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>IA / Software</t>
+          <t>Pagos</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>135.26</v>
+        <v>44.38</v>
       </c>
       <c r="D30" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.54</v>
+        <v>-1.89</v>
       </c>
       <c r="F30" t="n">
-        <v>0.67</v>
+        <v>0.7</v>
       </c>
       <c r="G30" t="n">
-        <v>5.62</v>
+        <v>1.43</v>
       </c>
       <c r="H30" t="n">
-        <v>4.15</v>
+        <v>3.21</v>
       </c>
       <c r="I30" t="n">
-        <v>133.01</v>
+        <v>43.8</v>
       </c>
       <c r="J30" t="n">
-        <v>136.66</v>
+        <v>44.73</v>
       </c>
       <c r="K30" t="n">
-        <v>126.84</v>
+        <v>42.24</v>
       </c>
       <c r="L30" t="n">
-        <v>149.3</v>
+        <v>47.94</v>
       </c>
       <c r="M30" t="n">
-        <v>46.36</v>
+        <v>14.83</v>
       </c>
       <c r="N30" t="inlineStr">
         <is>
@@ -2173,56 +2205,60 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>SOFI</t>
+          <t>ARM</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Fintech</t>
+          <t>Chips</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>15.23</v>
+        <v>256.73</v>
       </c>
       <c r="D31" t="n">
-        <v>44</v>
+        <v>95</v>
       </c>
       <c r="E31" t="n">
-        <v>-4.21</v>
+        <v>16.06</v>
       </c>
       <c r="F31" t="n">
-        <v>0.91</v>
+        <v>1.47</v>
       </c>
       <c r="G31" t="n">
-        <v>0.7</v>
+        <v>17.9</v>
       </c>
       <c r="H31" t="n">
-        <v>4.57</v>
+        <v>6.97</v>
       </c>
       <c r="I31" t="n">
-        <v>14.95</v>
+        <v>249.57</v>
       </c>
       <c r="J31" t="n">
-        <v>15.4</v>
+        <v>261.2</v>
       </c>
       <c r="K31" t="n">
-        <v>14.19</v>
+        <v>229.88</v>
       </c>
       <c r="L31" t="n">
-        <v>16.97</v>
+        <v>301.48</v>
       </c>
       <c r="M31" t="n">
-        <v>47.22</v>
+        <v>64.53</v>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>BAJO</t>
-        </is>
-      </c>
-      <c r="O31" t="inlineStr"/>
+          <t>ALTO</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>🔥🔥</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>NO COMPRAR</t>
+          <t>VIGILAR</t>
         </is>
       </c>
     </row>
@@ -2238,37 +2274,37 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>298.97</v>
+        <v>302.25</v>
       </c>
       <c r="D32" t="n">
         <v>86</v>
       </c>
       <c r="E32" t="n">
-        <v>1.41</v>
+        <v>1.13</v>
       </c>
       <c r="F32" t="n">
-        <v>0.73</v>
+        <v>0.78</v>
       </c>
       <c r="G32" t="n">
-        <v>6.68</v>
+        <v>6.46</v>
       </c>
       <c r="H32" t="n">
-        <v>2.24</v>
+        <v>2.14</v>
       </c>
       <c r="I32" t="n">
-        <v>296.3</v>
+        <v>299.67</v>
       </c>
       <c r="J32" t="n">
-        <v>300.64</v>
+        <v>303.87</v>
       </c>
       <c r="K32" t="n">
-        <v>288.94</v>
+        <v>292.56</v>
       </c>
       <c r="L32" t="n">
-        <v>315.68</v>
+        <v>318.4</v>
       </c>
       <c r="M32" t="n">
-        <v>84.06</v>
+        <v>84.81</v>
       </c>
       <c r="N32" t="inlineStr">
         <is>
@@ -2285,46 +2321,46 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>MU</t>
+          <t>INTC</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Memoria / Chips</t>
+          <t>Chips</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>698.74</v>
+        <v>118.96</v>
       </c>
       <c r="D33" t="n">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="E33" t="n">
-        <v>-8.85</v>
+        <v>-1.11</v>
       </c>
       <c r="F33" t="n">
-        <v>1.19</v>
+        <v>0.97</v>
       </c>
       <c r="G33" t="n">
-        <v>60.9</v>
+        <v>10.24</v>
       </c>
       <c r="H33" t="n">
-        <v>8.720000000000001</v>
+        <v>8.609999999999999</v>
       </c>
       <c r="I33" t="n">
-        <v>674.38</v>
+        <v>114.86</v>
       </c>
       <c r="J33" t="n">
-        <v>713.97</v>
+        <v>121.52</v>
       </c>
       <c r="K33" t="n">
-        <v>607.38</v>
+        <v>103.6</v>
       </c>
       <c r="L33" t="n">
-        <v>851</v>
+        <v>144.56</v>
       </c>
       <c r="M33" t="n">
-        <v>67.19</v>
+        <v>65.02</v>
       </c>
       <c r="N33" t="inlineStr">
         <is>
@@ -2341,46 +2377,46 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>INTC</t>
+          <t>MU</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Chips</t>
+          <t>Memoria / Chips</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>110.8</v>
+        <v>731.99</v>
       </c>
       <c r="D34" t="n">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="E34" t="n">
-        <v>-8.130000000000001</v>
+        <v>-8.91</v>
       </c>
       <c r="F34" t="n">
-        <v>0.9</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="G34" t="n">
-        <v>9.74</v>
+        <v>61.19</v>
       </c>
       <c r="H34" t="n">
-        <v>8.800000000000001</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="I34" t="n">
-        <v>106.9</v>
+        <v>707.51</v>
       </c>
       <c r="J34" t="n">
-        <v>113.24</v>
+        <v>747.29</v>
       </c>
       <c r="K34" t="n">
-        <v>96.18000000000001</v>
+        <v>640.2</v>
       </c>
       <c r="L34" t="n">
-        <v>135.16</v>
+        <v>884.97</v>
       </c>
       <c r="M34" t="n">
-        <v>60.91</v>
+        <v>69.3</v>
       </c>
       <c r="N34" t="inlineStr">
         <is>
@@ -2406,37 +2442,37 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>195.61</v>
+        <v>202.51</v>
       </c>
       <c r="D35" t="n">
         <v>62</v>
       </c>
       <c r="E35" t="n">
-        <v>-6.99</v>
+        <v>-5</v>
       </c>
       <c r="F35" t="n">
         <v>0.6</v>
       </c>
       <c r="G35" t="n">
-        <v>19.75</v>
+        <v>18.23</v>
       </c>
       <c r="H35" t="n">
-        <v>10.1</v>
+        <v>9</v>
       </c>
       <c r="I35" t="n">
-        <v>187.71</v>
+        <v>195.22</v>
       </c>
       <c r="J35" t="n">
-        <v>200.55</v>
+        <v>207.07</v>
       </c>
       <c r="K35" t="n">
-        <v>165.98</v>
+        <v>175.16</v>
       </c>
       <c r="L35" t="n">
-        <v>245</v>
+        <v>248.09</v>
       </c>
       <c r="M35" t="n">
-        <v>62.48</v>
+        <v>58.07</v>
       </c>
       <c r="N35" t="inlineStr">
         <is>
@@ -2453,46 +2489,46 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>RKLB</t>
+          <t>IONQ</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Espacial</t>
+          <t>Computación cuántica</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>127.31</v>
+        <v>52.47</v>
       </c>
       <c r="D36" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="E36" t="n">
-        <v>8.289999999999999</v>
+        <v>-5.05</v>
       </c>
       <c r="F36" t="n">
-        <v>1.11</v>
+        <v>0.63</v>
       </c>
       <c r="G36" t="n">
-        <v>11.09</v>
+        <v>4.98</v>
       </c>
       <c r="H36" t="n">
-        <v>8.710000000000001</v>
+        <v>9.5</v>
       </c>
       <c r="I36" t="n">
-        <v>122.87</v>
+        <v>50.48</v>
       </c>
       <c r="J36" t="n">
-        <v>130.08</v>
+        <v>53.72</v>
       </c>
       <c r="K36" t="n">
-        <v>110.67</v>
+        <v>45</v>
       </c>
       <c r="L36" t="n">
-        <v>155.04</v>
+        <v>64.93000000000001</v>
       </c>
       <c r="M36" t="n">
-        <v>76.14</v>
+        <v>59.34</v>
       </c>
       <c r="N36" t="inlineStr">
         <is>
@@ -2509,46 +2545,46 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>IONQ</t>
+          <t>RKLB</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Computación cuántica</t>
+          <t>Espacial</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>48.44</v>
+        <v>134.28</v>
       </c>
       <c r="D37" t="n">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="E37" t="n">
-        <v>-13.3</v>
+        <v>8.16</v>
       </c>
       <c r="F37" t="n">
-        <v>0.59</v>
+        <v>0.83</v>
       </c>
       <c r="G37" t="n">
-        <v>4.95</v>
+        <v>11.42</v>
       </c>
       <c r="H37" t="n">
-        <v>10.23</v>
+        <v>8.5</v>
       </c>
       <c r="I37" t="n">
-        <v>46.46</v>
+        <v>129.71</v>
       </c>
       <c r="J37" t="n">
-        <v>49.68</v>
+        <v>137.13</v>
       </c>
       <c r="K37" t="n">
-        <v>41.01</v>
+        <v>117.16</v>
       </c>
       <c r="L37" t="n">
-        <v>60.82</v>
+        <v>162.82</v>
       </c>
       <c r="M37" t="n">
-        <v>58.26</v>
+        <v>76.5</v>
       </c>
       <c r="N37" t="inlineStr">
         <is>
@@ -2558,7 +2594,7 @@
       <c r="O37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>NO COMPRAR</t>
+          <t>VIGILAR</t>
         </is>
       </c>
     </row>

--- a/analisis_acciones.xlsx
+++ b/analisis_acciones.xlsx
@@ -501,7 +501,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>CVX</t>
+          <t>SLB</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -510,37 +510,37 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>191.33</v>
+        <v>57.25</v>
       </c>
       <c r="D2" t="n">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="E2" t="n">
-        <v>3.81</v>
+        <v>2.69</v>
       </c>
       <c r="F2" t="n">
-        <v>1.44</v>
+        <v>0.63</v>
       </c>
       <c r="G2" t="n">
-        <v>4.6</v>
+        <v>1.4</v>
       </c>
       <c r="H2" t="n">
-        <v>2.41</v>
+        <v>2.45</v>
       </c>
       <c r="I2" t="n">
-        <v>189.49</v>
+        <v>56.69</v>
       </c>
       <c r="J2" t="n">
-        <v>192.48</v>
+        <v>57.6</v>
       </c>
       <c r="K2" t="n">
-        <v>184.42</v>
+        <v>55.15</v>
       </c>
       <c r="L2" t="n">
-        <v>202.84</v>
+        <v>60.75</v>
       </c>
       <c r="M2" t="n">
-        <v>49.71</v>
+        <v>51.5</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -549,7 +549,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥🔥</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -561,7 +561,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SLB</t>
+          <t>XOM</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -570,37 +570,37 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>57.28</v>
+        <v>155.29</v>
       </c>
       <c r="D3" t="n">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="E3" t="n">
-        <v>3.43</v>
+        <v>2.33</v>
       </c>
       <c r="F3" t="n">
-        <v>0.88</v>
+        <v>0.84</v>
       </c>
       <c r="G3" t="n">
-        <v>1.41</v>
+        <v>4.54</v>
       </c>
       <c r="H3" t="n">
-        <v>2.46</v>
+        <v>2.92</v>
       </c>
       <c r="I3" t="n">
-        <v>56.72</v>
+        <v>153.47</v>
       </c>
       <c r="J3" t="n">
-        <v>57.63</v>
+        <v>156.43</v>
       </c>
       <c r="K3" t="n">
-        <v>55.17</v>
+        <v>148.48</v>
       </c>
       <c r="L3" t="n">
-        <v>60.8</v>
+        <v>166.64</v>
       </c>
       <c r="M3" t="n">
-        <v>51.82</v>
+        <v>54.63</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -621,7 +621,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>XOM</t>
+          <t>CVX</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -630,37 +630,37 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>156.28</v>
+        <v>191.01</v>
       </c>
       <c r="D4" t="n">
         <v>92</v>
       </c>
       <c r="E4" t="n">
-        <v>3.81</v>
+        <v>3.28</v>
       </c>
       <c r="F4" t="n">
-        <v>0.85</v>
+        <v>0.89</v>
       </c>
       <c r="G4" t="n">
-        <v>4.39</v>
+        <v>4.66</v>
       </c>
       <c r="H4" t="n">
-        <v>2.81</v>
+        <v>2.44</v>
       </c>
       <c r="I4" t="n">
-        <v>154.52</v>
+        <v>189.15</v>
       </c>
       <c r="J4" t="n">
-        <v>157.38</v>
+        <v>192.18</v>
       </c>
       <c r="K4" t="n">
-        <v>149.69</v>
+        <v>184.02</v>
       </c>
       <c r="L4" t="n">
-        <v>167.26</v>
+        <v>202.66</v>
       </c>
       <c r="M4" t="n">
-        <v>53.82</v>
+        <v>52.9</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -681,46 +681,46 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>OXY</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Tecnología</t>
+          <t>Energía</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>421.06</v>
+        <v>58.83</v>
       </c>
       <c r="D5" t="n">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="E5" t="n">
-        <v>3.91</v>
+        <v>3.5</v>
       </c>
       <c r="F5" t="n">
-        <v>0.8</v>
+        <v>1.02</v>
       </c>
       <c r="G5" t="n">
-        <v>10.91</v>
+        <v>2</v>
       </c>
       <c r="H5" t="n">
-        <v>2.59</v>
+        <v>3.39</v>
       </c>
       <c r="I5" t="n">
-        <v>416.69</v>
+        <v>58.03</v>
       </c>
       <c r="J5" t="n">
-        <v>423.79</v>
+        <v>59.33</v>
       </c>
       <c r="K5" t="n">
-        <v>404.69</v>
+        <v>55.84</v>
       </c>
       <c r="L5" t="n">
-        <v>448.35</v>
+        <v>63.82</v>
       </c>
       <c r="M5" t="n">
-        <v>60.58</v>
+        <v>50.32</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
@@ -741,46 +741,46 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>OXY</t>
+          <t>NVDA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Energía</t>
+          <t>IA / Chips</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>58.87</v>
+        <v>219.51</v>
       </c>
       <c r="D6" t="n">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="E6" t="n">
-        <v>4.79</v>
+        <v>-6.88</v>
       </c>
       <c r="F6" t="n">
-        <v>0.93</v>
+        <v>1.22</v>
       </c>
       <c r="G6" t="n">
-        <v>1.98</v>
+        <v>8.34</v>
       </c>
       <c r="H6" t="n">
-        <v>3.37</v>
+        <v>3.8</v>
       </c>
       <c r="I6" t="n">
-        <v>58.08</v>
+        <v>216.17</v>
       </c>
       <c r="J6" t="n">
-        <v>59.37</v>
+        <v>221.6</v>
       </c>
       <c r="K6" t="n">
-        <v>55.89</v>
+        <v>207</v>
       </c>
       <c r="L6" t="n">
-        <v>63.83</v>
+        <v>240.36</v>
       </c>
       <c r="M6" t="n">
-        <v>45.8</v>
+        <v>66.66</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
@@ -801,46 +801,46 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Chips</t>
+          <t>Tecnología</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>401.62</v>
+        <v>419.09</v>
       </c>
       <c r="D7" t="n">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="E7" t="n">
-        <v>0.46</v>
+        <v>2.36</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="G7" t="n">
-        <v>15.59</v>
+        <v>11.01</v>
       </c>
       <c r="H7" t="n">
-        <v>3.88</v>
+        <v>2.63</v>
       </c>
       <c r="I7" t="n">
-        <v>395.38</v>
+        <v>414.69</v>
       </c>
       <c r="J7" t="n">
-        <v>405.52</v>
+        <v>421.84</v>
       </c>
       <c r="K7" t="n">
-        <v>378.24</v>
+        <v>402.58</v>
       </c>
       <c r="L7" t="n">
-        <v>440.59</v>
+        <v>446.61</v>
       </c>
       <c r="M7" t="n">
-        <v>52.43</v>
+        <v>54</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -849,7 +849,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -861,46 +861,46 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SPY</t>
+          <t>ASML</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>ETF Mercado</t>
+          <t>Chips</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>741.25</v>
+        <v>1592</v>
       </c>
       <c r="D8" t="n">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.14</v>
+        <v>0.47</v>
       </c>
       <c r="F8" t="n">
-        <v>0.93</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="G8" t="n">
-        <v>7.5</v>
+        <v>72.08</v>
       </c>
       <c r="H8" t="n">
-        <v>1.01</v>
+        <v>4.53</v>
       </c>
       <c r="I8" t="n">
-        <v>738.25</v>
+        <v>1563.17</v>
       </c>
       <c r="J8" t="n">
-        <v>743.13</v>
+        <v>1610.02</v>
       </c>
       <c r="K8" t="n">
-        <v>730</v>
+        <v>1483.88</v>
       </c>
       <c r="L8" t="n">
-        <v>760.01</v>
+        <v>1772.19</v>
       </c>
       <c r="M8" t="n">
-        <v>67.79000000000001</v>
+        <v>61.87</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
@@ -921,50 +921,50 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>NVDA</t>
+          <t>AMZN</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>IA / Chips</t>
+          <t>Tecnología</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>223.47</v>
+        <v>268.46</v>
       </c>
       <c r="D9" t="n">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.05</v>
+        <v>0.46</v>
       </c>
       <c r="F9" t="n">
-        <v>1.07</v>
+        <v>0.79</v>
       </c>
       <c r="G9" t="n">
-        <v>8.09</v>
+        <v>6.43</v>
       </c>
       <c r="H9" t="n">
-        <v>3.62</v>
+        <v>2.39</v>
       </c>
       <c r="I9" t="n">
-        <v>220.24</v>
+        <v>265.89</v>
       </c>
       <c r="J9" t="n">
-        <v>225.49</v>
+        <v>270.07</v>
       </c>
       <c r="K9" t="n">
-        <v>211.34</v>
+        <v>258.82</v>
       </c>
       <c r="L9" t="n">
-        <v>243.68</v>
+        <v>284.53</v>
       </c>
       <c r="M9" t="n">
-        <v>69.8</v>
+        <v>50.22</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>MEDIO</t>
+          <t>BAJO</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -981,50 +981,50 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>AVGO</t>
+          <t>LRCX</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>IA / Chips</t>
+          <t>Equipos chips</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>417.76</v>
+        <v>302.24</v>
       </c>
       <c r="D10" t="n">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="E10" t="n">
-        <v>0.23</v>
+        <v>1.03</v>
       </c>
       <c r="F10" t="n">
-        <v>0.85</v>
+        <v>0.96</v>
       </c>
       <c r="G10" t="n">
-        <v>16.66</v>
+        <v>15.34</v>
       </c>
       <c r="H10" t="n">
-        <v>3.99</v>
+        <v>5.08</v>
       </c>
       <c r="I10" t="n">
-        <v>411.1</v>
+        <v>296.1</v>
       </c>
       <c r="J10" t="n">
-        <v>421.92</v>
+        <v>306.07</v>
       </c>
       <c r="K10" t="n">
-        <v>392.78</v>
+        <v>279.23</v>
       </c>
       <c r="L10" t="n">
-        <v>459.4</v>
+        <v>340.59</v>
       </c>
       <c r="M10" t="n">
-        <v>50.13</v>
+        <v>67.25</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>BAJO</t>
+          <t>MEDIO</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1041,46 +1041,46 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>GOOGL</t>
+          <t>SOXX</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Tecnología</t>
+          <t>ETF Chips</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>388.91</v>
+        <v>524.71</v>
       </c>
       <c r="D11" t="n">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.41</v>
+        <v>-1</v>
       </c>
       <c r="F11" t="n">
-        <v>1.03</v>
+        <v>0.77</v>
       </c>
       <c r="G11" t="n">
-        <v>9.81</v>
+        <v>21.8</v>
       </c>
       <c r="H11" t="n">
-        <v>2.52</v>
+        <v>4.15</v>
       </c>
       <c r="I11" t="n">
-        <v>384.99</v>
+        <v>515.99</v>
       </c>
       <c r="J11" t="n">
-        <v>391.36</v>
+        <v>530.16</v>
       </c>
       <c r="K11" t="n">
-        <v>374.2</v>
+        <v>492.01</v>
       </c>
       <c r="L11" t="n">
-        <v>413.43</v>
+        <v>579.2</v>
       </c>
       <c r="M11" t="n">
-        <v>53.1</v>
+        <v>64.95</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
@@ -1101,46 +1101,46 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ASML</t>
+          <t>SPY</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Chips</t>
+          <t>ETF Mercado</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1550.13</v>
+        <v>742.77</v>
       </c>
       <c r="D12" t="n">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.99</v>
+        <v>-0.72</v>
       </c>
       <c r="F12" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="G12" t="n">
+        <v>7.62</v>
+      </c>
+      <c r="H12" t="n">
         <v>1.03</v>
       </c>
-      <c r="G12" t="n">
-        <v>70.26000000000001</v>
-      </c>
-      <c r="H12" t="n">
-        <v>4.53</v>
-      </c>
       <c r="I12" t="n">
-        <v>1522.03</v>
+        <v>739.72</v>
       </c>
       <c r="J12" t="n">
-        <v>1567.7</v>
+        <v>744.67</v>
       </c>
       <c r="K12" t="n">
-        <v>1444.74</v>
+        <v>731.34</v>
       </c>
       <c r="L12" t="n">
-        <v>1725.78</v>
+        <v>761.8200000000001</v>
       </c>
       <c r="M12" t="n">
-        <v>58.35</v>
+        <v>67.55</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
@@ -1161,46 +1161,46 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>AMAT</t>
+          <t>GOOGL</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Equipos chips</t>
+          <t>Tecnología</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>426.85</v>
+        <v>387.66</v>
       </c>
       <c r="D13" t="n">
         <v>84</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.24</v>
+        <v>-3.34</v>
       </c>
       <c r="F13" t="n">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="G13" t="n">
-        <v>20.59</v>
+        <v>9.93</v>
       </c>
       <c r="H13" t="n">
-        <v>4.82</v>
+        <v>2.56</v>
       </c>
       <c r="I13" t="n">
-        <v>418.61</v>
+        <v>383.69</v>
       </c>
       <c r="J13" t="n">
-        <v>432</v>
+        <v>390.14</v>
       </c>
       <c r="K13" t="n">
-        <v>395.97</v>
+        <v>372.76</v>
       </c>
       <c r="L13" t="n">
-        <v>478.33</v>
+        <v>412.5</v>
       </c>
       <c r="M13" t="n">
-        <v>59.45</v>
+        <v>51.48</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
@@ -1221,50 +1221,50 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>KLAC</t>
+          <t>SMCI</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Equipos chips</t>
+          <t>Servidores IA</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1829.47</v>
+        <v>33.46</v>
       </c>
       <c r="D14" t="n">
         <v>84</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.97</v>
+        <v>1.3</v>
       </c>
       <c r="F14" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.71</v>
       </c>
       <c r="G14" t="n">
-        <v>81.3</v>
+        <v>2.49</v>
       </c>
       <c r="H14" t="n">
-        <v>4.44</v>
+        <v>7.44</v>
       </c>
       <c r="I14" t="n">
-        <v>1796.95</v>
+        <v>32.46</v>
       </c>
       <c r="J14" t="n">
-        <v>1849.8</v>
+        <v>34.08</v>
       </c>
       <c r="K14" t="n">
-        <v>1707.52</v>
+        <v>29.72</v>
       </c>
       <c r="L14" t="n">
-        <v>2032.72</v>
+        <v>39.69</v>
       </c>
       <c r="M14" t="n">
-        <v>56.01</v>
+        <v>65.68000000000001</v>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>BAJO</t>
+          <t>MEDIO</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
@@ -1281,46 +1281,46 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>SOXX</t>
+          <t>TSM</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>ETF Chips</t>
+          <t>Chips</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>520.3099999999999</v>
+        <v>407.15</v>
       </c>
       <c r="D15" t="n">
         <v>84</v>
       </c>
       <c r="E15" t="n">
-        <v>-1.51</v>
+        <v>-2.53</v>
       </c>
       <c r="F15" t="n">
-        <v>1.09</v>
+        <v>0.63</v>
       </c>
       <c r="G15" t="n">
-        <v>21.8</v>
+        <v>15.6</v>
       </c>
       <c r="H15" t="n">
-        <v>4.19</v>
+        <v>3.83</v>
       </c>
       <c r="I15" t="n">
-        <v>511.59</v>
+        <v>400.91</v>
       </c>
       <c r="J15" t="n">
-        <v>525.76</v>
+        <v>411.05</v>
       </c>
       <c r="K15" t="n">
-        <v>487.61</v>
+        <v>383.75</v>
       </c>
       <c r="L15" t="n">
-        <v>574.8200000000001</v>
+        <v>446.15</v>
       </c>
       <c r="M15" t="n">
-        <v>64.93000000000001</v>
+        <v>54</v>
       </c>
       <c r="N15" t="inlineStr">
         <is>
@@ -1341,50 +1341,50 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>QQQ</t>
+          <t>AMAT</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>ETF Nasdaq</t>
+          <t>Equipos chips</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>713.15</v>
+        <v>427.36</v>
       </c>
       <c r="D16" t="n">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.22</v>
+        <v>-3</v>
       </c>
       <c r="F16" t="n">
-        <v>0.9</v>
+        <v>0.72</v>
       </c>
       <c r="G16" t="n">
-        <v>11.31</v>
+        <v>20.37</v>
       </c>
       <c r="H16" t="n">
-        <v>1.59</v>
+        <v>4.77</v>
       </c>
       <c r="I16" t="n">
-        <v>708.63</v>
+        <v>419.21</v>
       </c>
       <c r="J16" t="n">
-        <v>715.98</v>
+        <v>432.45</v>
       </c>
       <c r="K16" t="n">
-        <v>696.1900000000001</v>
+        <v>396.8</v>
       </c>
       <c r="L16" t="n">
-        <v>741.42</v>
+        <v>478.29</v>
       </c>
       <c r="M16" t="n">
-        <v>73.11</v>
+        <v>61.5</v>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>MEDIO</t>
+          <t>BAJO</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
@@ -1401,53 +1401,57 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>KLAC</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>IA / Chips</t>
+          <t>Equipos chips</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>447.58</v>
+        <v>1842.18</v>
       </c>
       <c r="D17" t="n">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="E17" t="n">
-        <v>0.47</v>
+        <v>-2.56</v>
       </c>
       <c r="F17" t="n">
-        <v>0.78</v>
+        <v>0.73</v>
       </c>
       <c r="G17" t="n">
-        <v>29.94</v>
+        <v>81.05</v>
       </c>
       <c r="H17" t="n">
-        <v>6.69</v>
+        <v>4.4</v>
       </c>
       <c r="I17" t="n">
-        <v>435.6</v>
+        <v>1809.76</v>
       </c>
       <c r="J17" t="n">
-        <v>455.07</v>
+        <v>1862.44</v>
       </c>
       <c r="K17" t="n">
-        <v>402.67</v>
+        <v>1720.61</v>
       </c>
       <c r="L17" t="n">
-        <v>522.4400000000001</v>
+        <v>2044.79</v>
       </c>
       <c r="M17" t="n">
-        <v>68.27</v>
+        <v>58.88</v>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>MEDIO</t>
-        </is>
-      </c>
-      <c r="O17" t="inlineStr"/>
+          <t>BAJO</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>🔥</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>POSIBLE COMPRA</t>
@@ -1457,53 +1461,57 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>LRCX</t>
+          <t>QQQ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Equipos chips</t>
+          <t>ETF Nasdaq</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>292.09</v>
+        <v>714.51</v>
       </c>
       <c r="D18" t="n">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.13</v>
+        <v>-0.73</v>
       </c>
       <c r="F18" t="n">
-        <v>0.89</v>
+        <v>0.87</v>
       </c>
       <c r="G18" t="n">
-        <v>15.26</v>
+        <v>11.46</v>
       </c>
       <c r="H18" t="n">
-        <v>5.23</v>
+        <v>1.6</v>
       </c>
       <c r="I18" t="n">
-        <v>285.98</v>
+        <v>709.9299999999999</v>
       </c>
       <c r="J18" t="n">
-        <v>295.91</v>
+        <v>717.37</v>
       </c>
       <c r="K18" t="n">
-        <v>269.19</v>
+        <v>697.3200000000001</v>
       </c>
       <c r="L18" t="n">
-        <v>330.25</v>
+        <v>743.16</v>
       </c>
       <c r="M18" t="n">
-        <v>63.92</v>
+        <v>71.66</v>
       </c>
       <c r="N18" t="inlineStr">
         <is>
           <t>MEDIO</t>
         </is>
       </c>
-      <c r="O18" t="inlineStr"/>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>🔥</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>POSIBLE COMPRA</t>
@@ -1513,60 +1521,56 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>SMCI</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Servidores IA</t>
+          <t>IA / Chips</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>33.46</v>
+        <v>449.59</v>
       </c>
       <c r="D19" t="n">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="E19" t="n">
-        <v>4.56</v>
+        <v>-0.02</v>
       </c>
       <c r="F19" t="n">
-        <v>0.95</v>
+        <v>0.6</v>
       </c>
       <c r="G19" t="n">
-        <v>2.48</v>
+        <v>30.37</v>
       </c>
       <c r="H19" t="n">
-        <v>7.42</v>
+        <v>6.75</v>
       </c>
       <c r="I19" t="n">
-        <v>32.47</v>
+        <v>437.44</v>
       </c>
       <c r="J19" t="n">
-        <v>34.08</v>
+        <v>457.18</v>
       </c>
       <c r="K19" t="n">
-        <v>29.74</v>
+        <v>404.04</v>
       </c>
       <c r="L19" t="n">
-        <v>39.67</v>
+        <v>525.51</v>
       </c>
       <c r="M19" t="n">
-        <v>64.69</v>
+        <v>67.75</v>
       </c>
       <c r="N19" t="inlineStr">
         <is>
           <t>MEDIO</t>
         </is>
       </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>🔥</t>
-        </is>
-      </c>
+      <c r="O19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>VIGILAR</t>
+          <t>POSIBLE COMPRA</t>
         </is>
       </c>
     </row>
@@ -1582,37 +1586,37 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>9.279999999999999</v>
+        <v>9.33</v>
       </c>
       <c r="D20" t="n">
         <v>74</v>
       </c>
       <c r="E20" t="n">
-        <v>7.28</v>
+        <v>3.32</v>
       </c>
       <c r="F20" t="n">
-        <v>1.11</v>
+        <v>0.74</v>
       </c>
       <c r="G20" t="n">
-        <v>0.48</v>
+        <v>0.47</v>
       </c>
       <c r="H20" t="n">
-        <v>5.22</v>
+        <v>5.03</v>
       </c>
       <c r="I20" t="n">
-        <v>9.09</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="J20" t="n">
-        <v>9.4</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="K20" t="n">
-        <v>8.550000000000001</v>
+        <v>8.630000000000001</v>
       </c>
       <c r="L20" t="n">
-        <v>10.49</v>
+        <v>10.5</v>
       </c>
       <c r="M20" t="n">
-        <v>56.1</v>
+        <v>52.49</v>
       </c>
       <c r="N20" t="inlineStr">
         <is>
@@ -1642,37 +1646,37 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>137.15</v>
+        <v>137.41</v>
       </c>
       <c r="D21" t="n">
         <v>62</v>
       </c>
       <c r="E21" t="n">
-        <v>5.46</v>
+        <v>2.76</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7</v>
+        <v>0.57</v>
       </c>
       <c r="G21" t="n">
-        <v>5.71</v>
+        <v>5.41</v>
       </c>
       <c r="H21" t="n">
-        <v>4.16</v>
+        <v>3.93</v>
       </c>
       <c r="I21" t="n">
-        <v>134.87</v>
+        <v>135.25</v>
       </c>
       <c r="J21" t="n">
-        <v>138.58</v>
+        <v>138.77</v>
       </c>
       <c r="K21" t="n">
-        <v>128.59</v>
+        <v>129.3</v>
       </c>
       <c r="L21" t="n">
-        <v>151.42</v>
+        <v>150.93</v>
       </c>
       <c r="M21" t="n">
-        <v>47.42</v>
+        <v>40.01</v>
       </c>
       <c r="N21" t="inlineStr">
         <is>
@@ -1693,222 +1697,214 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>SOFI</t>
+          <t>TSLA</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Fintech</t>
+          <t>Autos / Tech</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>15.69</v>
+        <v>417.85</v>
       </c>
       <c r="D22" t="n">
-        <v>52</v>
+        <v>74</v>
       </c>
       <c r="E22" t="n">
-        <v>2.48</v>
+        <v>-5.74</v>
       </c>
       <c r="F22" t="n">
-        <v>0.64</v>
+        <v>0.75</v>
       </c>
       <c r="G22" t="n">
-        <v>0.68</v>
+        <v>17.93</v>
       </c>
       <c r="H22" t="n">
-        <v>4.36</v>
+        <v>4.29</v>
       </c>
       <c r="I22" t="n">
-        <v>15.42</v>
+        <v>410.68</v>
       </c>
       <c r="J22" t="n">
-        <v>15.86</v>
+        <v>422.33</v>
       </c>
       <c r="K22" t="n">
-        <v>14.66</v>
+        <v>390.96</v>
       </c>
       <c r="L22" t="n">
-        <v>17.4</v>
+        <v>462.67</v>
       </c>
       <c r="M22" t="n">
-        <v>46.05</v>
+        <v>59.74</v>
       </c>
       <c r="N22" t="inlineStr">
         <is>
           <t>BAJO</t>
         </is>
       </c>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t>🔥</t>
-        </is>
-      </c>
+      <c r="O22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>NO COMPRAR</t>
+          <t>VIGILAR</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>UPST</t>
+          <t>AVGO</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Fintech IA</t>
+          <t>IA / Chips</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>28.84</v>
+        <v>414.57</v>
       </c>
       <c r="D23" t="n">
-        <v>46</v>
+        <v>64</v>
       </c>
       <c r="E23" t="n">
-        <v>6.85</v>
+        <v>-5.73</v>
       </c>
       <c r="F23" t="n">
-        <v>0.91</v>
+        <v>0.86</v>
       </c>
       <c r="G23" t="n">
-        <v>1.92</v>
+        <v>16.79</v>
       </c>
       <c r="H23" t="n">
-        <v>6.65</v>
+        <v>4.05</v>
       </c>
       <c r="I23" t="n">
-        <v>28.07</v>
+        <v>407.86</v>
       </c>
       <c r="J23" t="n">
-        <v>29.32</v>
+        <v>418.77</v>
       </c>
       <c r="K23" t="n">
-        <v>25.96</v>
+        <v>389.39</v>
       </c>
       <c r="L23" t="n">
-        <v>33.64</v>
+        <v>456.54</v>
       </c>
       <c r="M23" t="n">
-        <v>39.38</v>
+        <v>47.27</v>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>MEDIO</t>
-        </is>
-      </c>
-      <c r="O23" t="inlineStr">
-        <is>
-          <t>🔥</t>
-        </is>
-      </c>
+          <t>BAJO</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>NO COMPRAR</t>
+          <t>VIGILAR</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>TSLA</t>
+          <t>COIN</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Autos / Tech</t>
+          <t>Cripto / Trading</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>417.26</v>
+        <v>193.56</v>
       </c>
       <c r="D24" t="n">
-        <v>74</v>
+        <v>58</v>
       </c>
       <c r="E24" t="n">
-        <v>-6.29</v>
+        <v>-8.699999999999999</v>
       </c>
       <c r="F24" t="n">
-        <v>0.77</v>
+        <v>0.58</v>
       </c>
       <c r="G24" t="n">
-        <v>18.28</v>
+        <v>14.16</v>
       </c>
       <c r="H24" t="n">
-        <v>4.38</v>
+        <v>7.31</v>
       </c>
       <c r="I24" t="n">
-        <v>409.95</v>
+        <v>187.9</v>
       </c>
       <c r="J24" t="n">
-        <v>421.83</v>
+        <v>197.1</v>
       </c>
       <c r="K24" t="n">
-        <v>389.83</v>
+        <v>172.33</v>
       </c>
       <c r="L24" t="n">
-        <v>462.97</v>
+        <v>228.95</v>
       </c>
       <c r="M24" t="n">
-        <v>62.09</v>
+        <v>51.13</v>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>BAJO</t>
+          <t>MEDIO</t>
         </is>
       </c>
       <c r="O24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>VIGILAR</t>
+          <t>NO COMPRAR</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>SOUN</t>
+          <t>HOOD</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>IA</t>
+          <t>Trading</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>8.449999999999999</v>
+        <v>75.92</v>
       </c>
       <c r="D25" t="n">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="E25" t="n">
-        <v>0.36</v>
+        <v>-5.92</v>
       </c>
       <c r="F25" t="n">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="G25" t="n">
-        <v>0.65</v>
+        <v>3.9</v>
       </c>
       <c r="H25" t="n">
-        <v>7.74</v>
+        <v>5.14</v>
       </c>
       <c r="I25" t="n">
-        <v>8.19</v>
+        <v>74.36</v>
       </c>
       <c r="J25" t="n">
-        <v>8.609999999999999</v>
+        <v>76.89</v>
       </c>
       <c r="K25" t="n">
-        <v>7.47</v>
+        <v>70.06999999999999</v>
       </c>
       <c r="L25" t="n">
-        <v>10.09</v>
+        <v>85.67</v>
       </c>
       <c r="M25" t="n">
-        <v>55.09</v>
+        <v>53.9</v>
       </c>
       <c r="N25" t="inlineStr">
         <is>
@@ -1918,14 +1914,14 @@
       <c r="O25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>VIGILAR</t>
+          <t>NO COMPRAR</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>AMZN</t>
+          <t>META</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1934,37 +1930,37 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>265.01</v>
+        <v>607.38</v>
       </c>
       <c r="D26" t="n">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="E26" t="n">
-        <v>-1.9</v>
+        <v>-1.79</v>
       </c>
       <c r="F26" t="n">
         <v>0.76</v>
       </c>
       <c r="G26" t="n">
-        <v>6.6</v>
+        <v>13.34</v>
       </c>
       <c r="H26" t="n">
-        <v>2.49</v>
+        <v>2.2</v>
       </c>
       <c r="I26" t="n">
-        <v>262.37</v>
+        <v>602.04</v>
       </c>
       <c r="J26" t="n">
-        <v>266.66</v>
+        <v>610.72</v>
       </c>
       <c r="K26" t="n">
-        <v>255.1</v>
+        <v>587.37</v>
       </c>
       <c r="L26" t="n">
-        <v>281.52</v>
+        <v>640.73</v>
       </c>
       <c r="M26" t="n">
-        <v>49.94</v>
+        <v>49.11</v>
       </c>
       <c r="N26" t="inlineStr">
         <is>
@@ -1974,57 +1970,57 @@
       <c r="O26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>VIGILAR</t>
+          <t>NO COMPRAR</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>COIN</t>
+          <t>PYPL</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Cripto / Trading</t>
+          <t>Pagos</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>191.29</v>
+        <v>44.3</v>
       </c>
       <c r="D27" t="n">
-        <v>58</v>
+        <v>46</v>
       </c>
       <c r="E27" t="n">
-        <v>-5.21</v>
+        <v>-1.64</v>
       </c>
       <c r="F27" t="n">
         <v>0.72</v>
       </c>
       <c r="G27" t="n">
-        <v>14.06</v>
+        <v>1.43</v>
       </c>
       <c r="H27" t="n">
-        <v>7.35</v>
+        <v>3.23</v>
       </c>
       <c r="I27" t="n">
-        <v>185.66</v>
+        <v>43.73</v>
       </c>
       <c r="J27" t="n">
-        <v>194.81</v>
+        <v>44.66</v>
       </c>
       <c r="K27" t="n">
-        <v>170.19</v>
+        <v>42.15</v>
       </c>
       <c r="L27" t="n">
-        <v>226.45</v>
+        <v>47.88</v>
       </c>
       <c r="M27" t="n">
-        <v>51.71</v>
+        <v>11.48</v>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>MEDIO</t>
+          <t>BAJO</t>
         </is>
       </c>
       <c r="O27" t="inlineStr"/>
@@ -2037,50 +2033,50 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>HOOD</t>
+          <t>SOFI</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Trading</t>
+          <t>Fintech</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>75.76000000000001</v>
+        <v>15.65</v>
       </c>
       <c r="D28" t="n">
-        <v>58</v>
+        <v>44</v>
       </c>
       <c r="E28" t="n">
-        <v>-1.29</v>
+        <v>-2.31</v>
       </c>
       <c r="F28" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G28" t="n">
         <v>0.65</v>
       </c>
-      <c r="G28" t="n">
-        <v>3.92</v>
-      </c>
       <c r="H28" t="n">
-        <v>5.17</v>
+        <v>4.15</v>
       </c>
       <c r="I28" t="n">
-        <v>74.19</v>
+        <v>15.39</v>
       </c>
       <c r="J28" t="n">
-        <v>76.73999999999999</v>
+        <v>15.81</v>
       </c>
       <c r="K28" t="n">
-        <v>69.88</v>
+        <v>14.67</v>
       </c>
       <c r="L28" t="n">
-        <v>85.56</v>
+        <v>17.27</v>
       </c>
       <c r="M28" t="n">
-        <v>54.85</v>
+        <v>42.04</v>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>MEDIO</t>
+          <t>BAJO</t>
         </is>
       </c>
       <c r="O28" t="inlineStr"/>
@@ -2093,50 +2089,50 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>META</t>
+          <t>SOUN</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Tecnología</t>
+          <t>IA</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>605.0599999999999</v>
+        <v>8.32</v>
       </c>
       <c r="D29" t="n">
-        <v>54</v>
+        <v>38</v>
       </c>
       <c r="E29" t="n">
-        <v>-1.88</v>
+        <v>-2.35</v>
       </c>
       <c r="F29" t="n">
-        <v>0.7</v>
+        <v>0.74</v>
       </c>
       <c r="G29" t="n">
-        <v>13.2</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H29" t="n">
-        <v>2.18</v>
+        <v>6.7</v>
       </c>
       <c r="I29" t="n">
-        <v>599.78</v>
+        <v>8.1</v>
       </c>
       <c r="J29" t="n">
-        <v>608.36</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="K29" t="n">
-        <v>585.27</v>
+        <v>7.48</v>
       </c>
       <c r="L29" t="n">
-        <v>638.05</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="M29" t="n">
-        <v>45.6</v>
+        <v>31.44</v>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>BAJO</t>
+          <t>MEDIO</t>
         </is>
       </c>
       <c r="O29" t="inlineStr"/>
@@ -2149,50 +2145,50 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>PYPL</t>
+          <t>UPST</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Pagos</t>
+          <t>Fintech IA</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>44.38</v>
+        <v>28.85</v>
       </c>
       <c r="D30" t="n">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="E30" t="n">
-        <v>-1.89</v>
+        <v>-2.89</v>
       </c>
       <c r="F30" t="n">
-        <v>0.7</v>
+        <v>0.76</v>
       </c>
       <c r="G30" t="n">
-        <v>1.43</v>
+        <v>1.89</v>
       </c>
       <c r="H30" t="n">
-        <v>3.21</v>
+        <v>6.55</v>
       </c>
       <c r="I30" t="n">
-        <v>43.8</v>
+        <v>28.09</v>
       </c>
       <c r="J30" t="n">
-        <v>44.73</v>
+        <v>29.32</v>
       </c>
       <c r="K30" t="n">
-        <v>42.24</v>
+        <v>26.02</v>
       </c>
       <c r="L30" t="n">
-        <v>47.94</v>
+        <v>33.57</v>
       </c>
       <c r="M30" t="n">
-        <v>14.83</v>
+        <v>33.45</v>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>BAJO</t>
+          <t>MEDIO</t>
         </is>
       </c>
       <c r="O30" t="inlineStr"/>
@@ -2214,37 +2210,37 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>256.73</v>
+        <v>298.23</v>
       </c>
       <c r="D31" t="n">
         <v>95</v>
       </c>
       <c r="E31" t="n">
-        <v>16.06</v>
+        <v>30.52</v>
       </c>
       <c r="F31" t="n">
-        <v>1.47</v>
+        <v>1.73</v>
       </c>
       <c r="G31" t="n">
-        <v>17.9</v>
+        <v>20.24</v>
       </c>
       <c r="H31" t="n">
-        <v>6.97</v>
+        <v>6.79</v>
       </c>
       <c r="I31" t="n">
-        <v>249.57</v>
+        <v>290.13</v>
       </c>
       <c r="J31" t="n">
-        <v>261.2</v>
+        <v>303.29</v>
       </c>
       <c r="K31" t="n">
-        <v>229.88</v>
+        <v>267.87</v>
       </c>
       <c r="L31" t="n">
-        <v>301.48</v>
+        <v>348.83</v>
       </c>
       <c r="M31" t="n">
-        <v>64.53</v>
+        <v>71.73</v>
       </c>
       <c r="N31" t="inlineStr">
         <is>
@@ -2265,53 +2261,57 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>IONQ</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Tecnología</t>
+          <t>Computación cuántica</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>302.25</v>
+        <v>58.89</v>
       </c>
       <c r="D32" t="n">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="E32" t="n">
-        <v>1.13</v>
+        <v>2.47</v>
       </c>
       <c r="F32" t="n">
-        <v>0.78</v>
+        <v>1.79</v>
       </c>
       <c r="G32" t="n">
-        <v>6.46</v>
+        <v>5.42</v>
       </c>
       <c r="H32" t="n">
-        <v>2.14</v>
+        <v>9.210000000000001</v>
       </c>
       <c r="I32" t="n">
-        <v>299.67</v>
+        <v>56.72</v>
       </c>
       <c r="J32" t="n">
-        <v>303.87</v>
+        <v>60.25</v>
       </c>
       <c r="K32" t="n">
-        <v>292.56</v>
+        <v>50.76</v>
       </c>
       <c r="L32" t="n">
-        <v>318.4</v>
+        <v>72.44</v>
       </c>
       <c r="M32" t="n">
-        <v>84.81</v>
+        <v>64.2</v>
       </c>
       <c r="N32" t="inlineStr">
         <is>
           <t>ALTO</t>
         </is>
       </c>
-      <c r="O32" t="inlineStr"/>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>🔥🔥</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>VIGILAR</t>
@@ -2321,53 +2321,57 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>INTC</t>
+          <t>AAPL</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Chips</t>
+          <t>Tecnología</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>118.96</v>
+        <v>304.99</v>
       </c>
       <c r="D33" t="n">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="E33" t="n">
-        <v>-1.11</v>
+        <v>2.27</v>
       </c>
       <c r="F33" t="n">
-        <v>0.97</v>
+        <v>0.89</v>
       </c>
       <c r="G33" t="n">
-        <v>10.24</v>
+        <v>5.7</v>
       </c>
       <c r="H33" t="n">
-        <v>8.609999999999999</v>
+        <v>1.87</v>
       </c>
       <c r="I33" t="n">
-        <v>114.86</v>
+        <v>302.71</v>
       </c>
       <c r="J33" t="n">
-        <v>121.52</v>
+        <v>306.41</v>
       </c>
       <c r="K33" t="n">
-        <v>103.6</v>
+        <v>296.45</v>
       </c>
       <c r="L33" t="n">
-        <v>144.56</v>
+        <v>319.23</v>
       </c>
       <c r="M33" t="n">
-        <v>65.02</v>
+        <v>82.44</v>
       </c>
       <c r="N33" t="inlineStr">
         <is>
           <t>ALTO</t>
         </is>
       </c>
-      <c r="O33" t="inlineStr"/>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>🔥</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>VIGILAR</t>
@@ -2377,53 +2381,57 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>MU</t>
+          <t>INTC</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Memoria / Chips</t>
+          <t>Chips</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>731.99</v>
+        <v>118.5</v>
       </c>
       <c r="D34" t="n">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="E34" t="n">
-        <v>-8.91</v>
+        <v>2.22</v>
       </c>
       <c r="F34" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.62</v>
       </c>
       <c r="G34" t="n">
-        <v>61.19</v>
+        <v>10.13</v>
       </c>
       <c r="H34" t="n">
-        <v>8.359999999999999</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="I34" t="n">
-        <v>707.51</v>
+        <v>114.45</v>
       </c>
       <c r="J34" t="n">
-        <v>747.29</v>
+        <v>121.03</v>
       </c>
       <c r="K34" t="n">
-        <v>640.2</v>
+        <v>103.31</v>
       </c>
       <c r="L34" t="n">
-        <v>884.97</v>
+        <v>143.82</v>
       </c>
       <c r="M34" t="n">
-        <v>69.3</v>
+        <v>62.29</v>
       </c>
       <c r="N34" t="inlineStr">
         <is>
           <t>ALTO</t>
         </is>
       </c>
-      <c r="O34" t="inlineStr"/>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>🔥</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>VIGILAR</t>
@@ -2433,46 +2441,46 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>QCOM</t>
+          <t>RKLB</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Chips</t>
+          <t>Espacial</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>202.51</v>
+        <v>125.45</v>
       </c>
       <c r="D35" t="n">
-        <v>62</v>
+        <v>75</v>
       </c>
       <c r="E35" t="n">
-        <v>-5</v>
+        <v>-5.36</v>
       </c>
       <c r="F35" t="n">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
       <c r="G35" t="n">
-        <v>18.23</v>
+        <v>11.78</v>
       </c>
       <c r="H35" t="n">
-        <v>9</v>
+        <v>9.390000000000001</v>
       </c>
       <c r="I35" t="n">
-        <v>195.22</v>
+        <v>120.74</v>
       </c>
       <c r="J35" t="n">
-        <v>207.07</v>
+        <v>128.4</v>
       </c>
       <c r="K35" t="n">
-        <v>175.16</v>
+        <v>107.77</v>
       </c>
       <c r="L35" t="n">
-        <v>248.09</v>
+        <v>154.91</v>
       </c>
       <c r="M35" t="n">
-        <v>58.07</v>
+        <v>72.68000000000001</v>
       </c>
       <c r="N35" t="inlineStr">
         <is>
@@ -2489,46 +2497,46 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>IONQ</t>
+          <t>QCOM</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Computación cuántica</t>
+          <t>Chips</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>52.47</v>
+        <v>213.41</v>
       </c>
       <c r="D36" t="n">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="E36" t="n">
-        <v>-5.05</v>
+        <v>6.66</v>
       </c>
       <c r="F36" t="n">
-        <v>0.63</v>
+        <v>0.85</v>
       </c>
       <c r="G36" t="n">
-        <v>4.98</v>
+        <v>18.77</v>
       </c>
       <c r="H36" t="n">
-        <v>9.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I36" t="n">
-        <v>50.48</v>
+        <v>205.9</v>
       </c>
       <c r="J36" t="n">
-        <v>53.72</v>
+        <v>218.1</v>
       </c>
       <c r="K36" t="n">
-        <v>45</v>
+        <v>185.25</v>
       </c>
       <c r="L36" t="n">
-        <v>64.93000000000001</v>
+        <v>260.34</v>
       </c>
       <c r="M36" t="n">
-        <v>59.34</v>
+        <v>62.11</v>
       </c>
       <c r="N36" t="inlineStr">
         <is>
@@ -2545,46 +2553,46 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>RKLB</t>
+          <t>MU</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Espacial</t>
+          <t>Memoria / Chips</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>134.28</v>
+        <v>762.1</v>
       </c>
       <c r="D37" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="E37" t="n">
-        <v>8.16</v>
+        <v>-1.79</v>
       </c>
       <c r="F37" t="n">
         <v>0.83</v>
       </c>
       <c r="G37" t="n">
-        <v>11.42</v>
+        <v>60.99</v>
       </c>
       <c r="H37" t="n">
-        <v>8.5</v>
+        <v>8</v>
       </c>
       <c r="I37" t="n">
-        <v>129.71</v>
+        <v>737.7</v>
       </c>
       <c r="J37" t="n">
-        <v>137.13</v>
+        <v>777.35</v>
       </c>
       <c r="K37" t="n">
-        <v>117.16</v>
+        <v>670.61</v>
       </c>
       <c r="L37" t="n">
-        <v>162.82</v>
+        <v>914.58</v>
       </c>
       <c r="M37" t="n">
-        <v>76.5</v>
+        <v>69.58</v>
       </c>
       <c r="N37" t="inlineStr">
         <is>

--- a/analisis_acciones.xlsx
+++ b/analisis_acciones.xlsx
@@ -501,50 +501,50 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>SLB</t>
+          <t>ASML</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Energía</t>
+          <t>Chips</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>57.25</v>
+        <v>1635.5</v>
       </c>
       <c r="D2" t="n">
         <v>95</v>
       </c>
       <c r="E2" t="n">
-        <v>2.69</v>
+        <v>8.9</v>
       </c>
       <c r="F2" t="n">
-        <v>0.63</v>
+        <v>0.79</v>
       </c>
       <c r="G2" t="n">
-        <v>1.4</v>
+        <v>72.19</v>
       </c>
       <c r="H2" t="n">
-        <v>2.45</v>
+        <v>4.41</v>
       </c>
       <c r="I2" t="n">
-        <v>56.69</v>
+        <v>1606.62</v>
       </c>
       <c r="J2" t="n">
-        <v>57.6</v>
+        <v>1653.55</v>
       </c>
       <c r="K2" t="n">
-        <v>55.15</v>
+        <v>1527.22</v>
       </c>
       <c r="L2" t="n">
-        <v>60.75</v>
+        <v>1815.97</v>
       </c>
       <c r="M2" t="n">
-        <v>51.5</v>
+        <v>67.86</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>BAJO</t>
+          <t>MEDIO</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -561,50 +561,50 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>XOM</t>
+          <t>LRCX</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Energía</t>
+          <t>Equipos chips</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>155.29</v>
+        <v>305.77</v>
       </c>
       <c r="D3" t="n">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="E3" t="n">
-        <v>2.33</v>
+        <v>7.39</v>
       </c>
       <c r="F3" t="n">
-        <v>0.84</v>
+        <v>0.44</v>
       </c>
       <c r="G3" t="n">
-        <v>4.54</v>
+        <v>15.31</v>
       </c>
       <c r="H3" t="n">
-        <v>2.92</v>
+        <v>5.01</v>
       </c>
       <c r="I3" t="n">
-        <v>153.47</v>
+        <v>299.65</v>
       </c>
       <c r="J3" t="n">
-        <v>156.43</v>
+        <v>309.6</v>
       </c>
       <c r="K3" t="n">
-        <v>148.48</v>
+        <v>282.81</v>
       </c>
       <c r="L3" t="n">
-        <v>166.64</v>
+        <v>344.05</v>
       </c>
       <c r="M3" t="n">
-        <v>54.63</v>
+        <v>67.66</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>BAJO</t>
+          <t>MEDIO</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -621,46 +621,46 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CVX</t>
+          <t>KLAC</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Energía</t>
+          <t>Equipos chips</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>191.01</v>
+        <v>1892.04</v>
       </c>
       <c r="D4" t="n">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="E4" t="n">
-        <v>3.28</v>
+        <v>5</v>
       </c>
       <c r="F4" t="n">
-        <v>0.89</v>
+        <v>0.38</v>
       </c>
       <c r="G4" t="n">
-        <v>4.66</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="H4" t="n">
-        <v>2.44</v>
+        <v>4.26</v>
       </c>
       <c r="I4" t="n">
-        <v>189.15</v>
+        <v>1859.8</v>
       </c>
       <c r="J4" t="n">
-        <v>192.18</v>
+        <v>1912.19</v>
       </c>
       <c r="K4" t="n">
-        <v>184.02</v>
+        <v>1771.14</v>
       </c>
       <c r="L4" t="n">
-        <v>202.66</v>
+        <v>2093.53</v>
       </c>
       <c r="M4" t="n">
-        <v>52.9</v>
+        <v>62.88</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -681,7 +681,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>OXY</t>
+          <t>SLB</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -690,37 +690,37 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>58.83</v>
+        <v>57.82</v>
       </c>
       <c r="D5" t="n">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="E5" t="n">
-        <v>3.5</v>
+        <v>4.41</v>
       </c>
       <c r="F5" t="n">
-        <v>1.02</v>
+        <v>0.45</v>
       </c>
       <c r="G5" t="n">
-        <v>2</v>
+        <v>1.41</v>
       </c>
       <c r="H5" t="n">
-        <v>3.39</v>
+        <v>2.44</v>
       </c>
       <c r="I5" t="n">
-        <v>58.03</v>
+        <v>57.26</v>
       </c>
       <c r="J5" t="n">
-        <v>59.33</v>
+        <v>58.17</v>
       </c>
       <c r="K5" t="n">
-        <v>55.84</v>
+        <v>55.7</v>
       </c>
       <c r="L5" t="n">
-        <v>63.82</v>
+        <v>61.35</v>
       </c>
       <c r="M5" t="n">
-        <v>50.32</v>
+        <v>60.66</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
@@ -741,50 +741,50 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>NVDA</t>
+          <t>SOXX</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>IA / Chips</t>
+          <t>ETF Chips</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>219.51</v>
+        <v>537.24</v>
       </c>
       <c r="D6" t="n">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E6" t="n">
-        <v>-6.88</v>
+        <v>5.65</v>
       </c>
       <c r="F6" t="n">
-        <v>1.22</v>
+        <v>0.74</v>
       </c>
       <c r="G6" t="n">
-        <v>8.34</v>
+        <v>22.18</v>
       </c>
       <c r="H6" t="n">
-        <v>3.8</v>
+        <v>4.13</v>
       </c>
       <c r="I6" t="n">
-        <v>216.17</v>
+        <v>528.37</v>
       </c>
       <c r="J6" t="n">
-        <v>221.6</v>
+        <v>542.79</v>
       </c>
       <c r="K6" t="n">
-        <v>207</v>
+        <v>503.97</v>
       </c>
       <c r="L6" t="n">
-        <v>240.36</v>
+        <v>592.7</v>
       </c>
       <c r="M6" t="n">
-        <v>66.66</v>
+        <v>68.23999999999999</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>BAJO</t>
+          <t>MEDIO</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -801,50 +801,50 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>MU</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Tecnología</t>
+          <t>Memoria / Chips</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>419.09</v>
+        <v>763</v>
       </c>
       <c r="D7" t="n">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="E7" t="n">
-        <v>2.36</v>
+        <v>5.29</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9</v>
+        <v>0.55</v>
       </c>
       <c r="G7" t="n">
-        <v>11.01</v>
+        <v>59.73</v>
       </c>
       <c r="H7" t="n">
-        <v>2.63</v>
+        <v>7.83</v>
       </c>
       <c r="I7" t="n">
-        <v>414.69</v>
+        <v>739.11</v>
       </c>
       <c r="J7" t="n">
-        <v>421.84</v>
+        <v>777.9299999999999</v>
       </c>
       <c r="K7" t="n">
-        <v>402.58</v>
+        <v>673.4</v>
       </c>
       <c r="L7" t="n">
-        <v>446.61</v>
+        <v>912.33</v>
       </c>
       <c r="M7" t="n">
-        <v>54</v>
+        <v>67.66</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>BAJO</t>
+          <t>MEDIO</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -861,55 +861,55 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ASML</t>
+          <t>AI</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Chips</t>
+          <t>IA</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1592</v>
+        <v>9.34</v>
       </c>
       <c r="D8" t="n">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="E8" t="n">
-        <v>0.47</v>
+        <v>7.92</v>
       </c>
       <c r="F8" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.73</v>
       </c>
       <c r="G8" t="n">
-        <v>72.08</v>
+        <v>0.48</v>
       </c>
       <c r="H8" t="n">
-        <v>4.53</v>
+        <v>5.14</v>
       </c>
       <c r="I8" t="n">
-        <v>1563.17</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="J8" t="n">
-        <v>1610.02</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="K8" t="n">
-        <v>1483.88</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="L8" t="n">
-        <v>1772.19</v>
+        <v>10.53</v>
       </c>
       <c r="M8" t="n">
-        <v>61.87</v>
+        <v>51.71</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>BAJO</t>
+          <t>MEDIO</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -921,46 +921,46 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>AMZN</t>
+          <t>CVX</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Tecnología</t>
+          <t>Energía</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>268.46</v>
+        <v>191.59</v>
       </c>
       <c r="D9" t="n">
         <v>92</v>
       </c>
       <c r="E9" t="n">
-        <v>0.46</v>
+        <v>1.17</v>
       </c>
       <c r="F9" t="n">
-        <v>0.79</v>
+        <v>0.41</v>
       </c>
       <c r="G9" t="n">
-        <v>6.43</v>
+        <v>4.39</v>
       </c>
       <c r="H9" t="n">
-        <v>2.39</v>
+        <v>2.29</v>
       </c>
       <c r="I9" t="n">
-        <v>265.89</v>
+        <v>189.83</v>
       </c>
       <c r="J9" t="n">
-        <v>270.07</v>
+        <v>192.69</v>
       </c>
       <c r="K9" t="n">
-        <v>258.82</v>
+        <v>185.01</v>
       </c>
       <c r="L9" t="n">
-        <v>284.53</v>
+        <v>202.56</v>
       </c>
       <c r="M9" t="n">
-        <v>50.22</v>
+        <v>51.49</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
@@ -981,46 +981,46 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>LRCX</t>
+          <t>SPY</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Equipos chips</t>
+          <t>ETF Mercado</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>302.24</v>
+        <v>746.25</v>
       </c>
       <c r="D10" t="n">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="E10" t="n">
-        <v>1.03</v>
+        <v>0.96</v>
       </c>
       <c r="F10" t="n">
-        <v>0.96</v>
+        <v>0.49</v>
       </c>
       <c r="G10" t="n">
-        <v>15.34</v>
+        <v>7.55</v>
       </c>
       <c r="H10" t="n">
-        <v>5.08</v>
+        <v>1.01</v>
       </c>
       <c r="I10" t="n">
-        <v>296.1</v>
+        <v>743.23</v>
       </c>
       <c r="J10" t="n">
-        <v>306.07</v>
+        <v>748.14</v>
       </c>
       <c r="K10" t="n">
-        <v>279.23</v>
+        <v>734.92</v>
       </c>
       <c r="L10" t="n">
-        <v>340.59</v>
+        <v>765.14</v>
       </c>
       <c r="M10" t="n">
-        <v>67.25</v>
+        <v>72.11</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
@@ -1041,50 +1041,50 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SOXX</t>
+          <t>QQQ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>ETF Chips</t>
+          <t>ETF Nasdaq</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>524.71</v>
+        <v>718.27</v>
       </c>
       <c r="D11" t="n">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="E11" t="n">
-        <v>-1</v>
+        <v>1.32</v>
       </c>
       <c r="F11" t="n">
-        <v>0.77</v>
+        <v>0.63</v>
       </c>
       <c r="G11" t="n">
-        <v>21.8</v>
+        <v>11.44</v>
       </c>
       <c r="H11" t="n">
-        <v>4.15</v>
+        <v>1.59</v>
       </c>
       <c r="I11" t="n">
-        <v>515.99</v>
+        <v>713.6900000000001</v>
       </c>
       <c r="J11" t="n">
-        <v>530.16</v>
+        <v>721.13</v>
       </c>
       <c r="K11" t="n">
-        <v>492.01</v>
+        <v>701.1</v>
       </c>
       <c r="L11" t="n">
-        <v>579.2</v>
+        <v>746.88</v>
       </c>
       <c r="M11" t="n">
-        <v>64.95</v>
+        <v>73.72</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>BAJO</t>
+          <t>MEDIO</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1101,46 +1101,46 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SPY</t>
+          <t>NVDA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>ETF Mercado</t>
+          <t>IA / Chips</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>742.77</v>
+        <v>215.04</v>
       </c>
       <c r="D12" t="n">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.72</v>
+        <v>-4.56</v>
       </c>
       <c r="F12" t="n">
-        <v>0.87</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="G12" t="n">
-        <v>7.62</v>
+        <v>8.279999999999999</v>
       </c>
       <c r="H12" t="n">
-        <v>1.03</v>
+        <v>3.85</v>
       </c>
       <c r="I12" t="n">
-        <v>739.72</v>
+        <v>211.73</v>
       </c>
       <c r="J12" t="n">
-        <v>744.67</v>
+        <v>217.11</v>
       </c>
       <c r="K12" t="n">
-        <v>731.34</v>
+        <v>202.62</v>
       </c>
       <c r="L12" t="n">
-        <v>761.8200000000001</v>
+        <v>235.74</v>
       </c>
       <c r="M12" t="n">
-        <v>67.55</v>
+        <v>62.24</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
@@ -1161,46 +1161,46 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>GOOGL</t>
+          <t>TSM</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Tecnología</t>
+          <t>Chips</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>387.66</v>
+        <v>404.02</v>
       </c>
       <c r="D13" t="n">
         <v>84</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.34</v>
+        <v>-0.08</v>
       </c>
       <c r="F13" t="n">
-        <v>0.79</v>
+        <v>0.37</v>
       </c>
       <c r="G13" t="n">
-        <v>9.93</v>
+        <v>15.2</v>
       </c>
       <c r="H13" t="n">
-        <v>2.56</v>
+        <v>3.76</v>
       </c>
       <c r="I13" t="n">
-        <v>383.69</v>
+        <v>397.95</v>
       </c>
       <c r="J13" t="n">
-        <v>390.14</v>
+        <v>407.82</v>
       </c>
       <c r="K13" t="n">
-        <v>372.76</v>
+        <v>381.23</v>
       </c>
       <c r="L13" t="n">
-        <v>412.5</v>
+        <v>442.01</v>
       </c>
       <c r="M13" t="n">
-        <v>51.48</v>
+        <v>51.03</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
@@ -1221,50 +1221,50 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>SMCI</t>
+          <t>AMAT</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Servidores IA</t>
+          <t>Equipos chips</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>33.46</v>
+        <v>432.83</v>
       </c>
       <c r="D14" t="n">
         <v>84</v>
       </c>
       <c r="E14" t="n">
-        <v>1.3</v>
+        <v>-0.74</v>
       </c>
       <c r="F14" t="n">
-        <v>0.71</v>
+        <v>0.39</v>
       </c>
       <c r="G14" t="n">
-        <v>2.49</v>
+        <v>20.02</v>
       </c>
       <c r="H14" t="n">
-        <v>7.44</v>
+        <v>4.63</v>
       </c>
       <c r="I14" t="n">
-        <v>32.46</v>
+        <v>424.82</v>
       </c>
       <c r="J14" t="n">
-        <v>34.08</v>
+        <v>437.84</v>
       </c>
       <c r="K14" t="n">
-        <v>29.72</v>
+        <v>402.8</v>
       </c>
       <c r="L14" t="n">
-        <v>39.69</v>
+        <v>482.88</v>
       </c>
       <c r="M14" t="n">
-        <v>65.68000000000001</v>
+        <v>62.34</v>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>MEDIO</t>
+          <t>BAJO</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
@@ -1281,46 +1281,46 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>XOM</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Chips</t>
+          <t>Energía</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>407.15</v>
+        <v>155.05</v>
       </c>
       <c r="D15" t="n">
         <v>84</v>
       </c>
       <c r="E15" t="n">
-        <v>-2.53</v>
+        <v>-1.82</v>
       </c>
       <c r="F15" t="n">
-        <v>0.63</v>
+        <v>0.43</v>
       </c>
       <c r="G15" t="n">
-        <v>15.6</v>
+        <v>4.36</v>
       </c>
       <c r="H15" t="n">
-        <v>3.83</v>
+        <v>2.81</v>
       </c>
       <c r="I15" t="n">
-        <v>400.91</v>
+        <v>153.31</v>
       </c>
       <c r="J15" t="n">
-        <v>411.05</v>
+        <v>156.14</v>
       </c>
       <c r="K15" t="n">
-        <v>383.75</v>
+        <v>148.51</v>
       </c>
       <c r="L15" t="n">
-        <v>446.15</v>
+        <v>165.95</v>
       </c>
       <c r="M15" t="n">
-        <v>54</v>
+        <v>53.16</v>
       </c>
       <c r="N15" t="inlineStr">
         <is>
@@ -1341,46 +1341,46 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>AMAT</t>
+          <t>TSLA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Equipos chips</t>
+          <t>Autos / Tech</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>427.36</v>
+        <v>427.41</v>
       </c>
       <c r="D16" t="n">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="E16" t="n">
-        <v>-3</v>
+        <v>1.22</v>
       </c>
       <c r="F16" t="n">
-        <v>0.72</v>
+        <v>0.71</v>
       </c>
       <c r="G16" t="n">
-        <v>20.37</v>
+        <v>18.2</v>
       </c>
       <c r="H16" t="n">
-        <v>4.77</v>
+        <v>4.26</v>
       </c>
       <c r="I16" t="n">
-        <v>419.21</v>
+        <v>420.13</v>
       </c>
       <c r="J16" t="n">
-        <v>432.45</v>
+        <v>431.96</v>
       </c>
       <c r="K16" t="n">
-        <v>396.8</v>
+        <v>400.11</v>
       </c>
       <c r="L16" t="n">
-        <v>478.29</v>
+        <v>472.92</v>
       </c>
       <c r="M16" t="n">
-        <v>61.5</v>
+        <v>61.9</v>
       </c>
       <c r="N16" t="inlineStr">
         <is>
@@ -1401,57 +1401,53 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>KLAC</t>
+          <t>GOOGL</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Equipos chips</t>
+          <t>Tecnología</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1842.18</v>
+        <v>383.45</v>
       </c>
       <c r="D17" t="n">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="E17" t="n">
-        <v>-2.56</v>
+        <v>-3.36</v>
       </c>
       <c r="F17" t="n">
-        <v>0.73</v>
+        <v>0.43</v>
       </c>
       <c r="G17" t="n">
-        <v>81.05</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="H17" t="n">
-        <v>4.4</v>
+        <v>2.56</v>
       </c>
       <c r="I17" t="n">
-        <v>1809.76</v>
+        <v>379.53</v>
       </c>
       <c r="J17" t="n">
-        <v>1862.44</v>
+        <v>385.9</v>
       </c>
       <c r="K17" t="n">
-        <v>1720.61</v>
+        <v>368.75</v>
       </c>
       <c r="L17" t="n">
-        <v>2044.79</v>
+        <v>407.96</v>
       </c>
       <c r="M17" t="n">
-        <v>58.88</v>
+        <v>50.15</v>
       </c>
       <c r="N17" t="inlineStr">
         <is>
           <t>BAJO</t>
         </is>
       </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>🔥</t>
-        </is>
-      </c>
+      <c r="O17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>POSIBLE COMPRA</t>
@@ -1461,50 +1457,50 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>QQQ</t>
+          <t>PLTR</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>ETF Nasdaq</t>
+          <t>IA / Software</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>714.51</v>
+        <v>137.09</v>
       </c>
       <c r="D18" t="n">
-        <v>81</v>
+        <v>54</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.73</v>
+        <v>2.31</v>
       </c>
       <c r="F18" t="n">
-        <v>0.87</v>
+        <v>0.53</v>
       </c>
       <c r="G18" t="n">
-        <v>11.46</v>
+        <v>5.35</v>
       </c>
       <c r="H18" t="n">
-        <v>1.6</v>
+        <v>3.9</v>
       </c>
       <c r="I18" t="n">
-        <v>709.9299999999999</v>
+        <v>134.95</v>
       </c>
       <c r="J18" t="n">
-        <v>717.37</v>
+        <v>138.42</v>
       </c>
       <c r="K18" t="n">
-        <v>697.3200000000001</v>
+        <v>129.06</v>
       </c>
       <c r="L18" t="n">
-        <v>743.16</v>
+        <v>150.45</v>
       </c>
       <c r="M18" t="n">
-        <v>71.66</v>
+        <v>35.89</v>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>MEDIO</t>
+          <t>BAJO</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
@@ -1514,120 +1510,116 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>POSIBLE COMPRA</t>
+          <t>NO COMPRAR</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>IA / Chips</t>
+          <t>Tecnología</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>449.59</v>
+        <v>418.8</v>
       </c>
       <c r="D19" t="n">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.02</v>
+        <v>-0.52</v>
       </c>
       <c r="F19" t="n">
-        <v>0.6</v>
+        <v>0.46</v>
       </c>
       <c r="G19" t="n">
-        <v>30.37</v>
+        <v>10.85</v>
       </c>
       <c r="H19" t="n">
-        <v>6.75</v>
+        <v>2.59</v>
       </c>
       <c r="I19" t="n">
-        <v>437.44</v>
+        <v>414.46</v>
       </c>
       <c r="J19" t="n">
-        <v>457.18</v>
+        <v>421.51</v>
       </c>
       <c r="K19" t="n">
-        <v>404.04</v>
+        <v>402.52</v>
       </c>
       <c r="L19" t="n">
-        <v>525.51</v>
+        <v>445.93</v>
       </c>
       <c r="M19" t="n">
-        <v>67.75</v>
+        <v>55.37</v>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>MEDIO</t>
+          <t>BAJO</t>
         </is>
       </c>
       <c r="O19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>POSIBLE COMPRA</t>
+          <t>VIGILAR</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>AI</t>
+          <t>AMZN</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>IA</t>
+          <t>Tecnología</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>9.33</v>
+        <v>266.87</v>
       </c>
       <c r="D20" t="n">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="E20" t="n">
-        <v>3.32</v>
+        <v>1.03</v>
       </c>
       <c r="F20" t="n">
-        <v>0.74</v>
+        <v>0.43</v>
       </c>
       <c r="G20" t="n">
-        <v>0.47</v>
+        <v>6.08</v>
       </c>
       <c r="H20" t="n">
-        <v>5.03</v>
+        <v>2.28</v>
       </c>
       <c r="I20" t="n">
-        <v>9.140000000000001</v>
+        <v>264.44</v>
       </c>
       <c r="J20" t="n">
-        <v>9.449999999999999</v>
+        <v>268.39</v>
       </c>
       <c r="K20" t="n">
-        <v>8.630000000000001</v>
+        <v>257.76</v>
       </c>
       <c r="L20" t="n">
-        <v>10.5</v>
+        <v>282.06</v>
       </c>
       <c r="M20" t="n">
-        <v>52.49</v>
+        <v>43.89</v>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>MEDIO</t>
-        </is>
-      </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>🔥</t>
-        </is>
-      </c>
+          <t>BAJO</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>VIGILAR</t>
@@ -1637,57 +1629,53 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>PLTR</t>
+          <t>OXY</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>IA / Software</t>
+          <t>Energía</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>137.41</v>
+        <v>58.9</v>
       </c>
       <c r="D21" t="n">
-        <v>62</v>
+        <v>72</v>
       </c>
       <c r="E21" t="n">
-        <v>2.76</v>
+        <v>-1.21</v>
       </c>
       <c r="F21" t="n">
-        <v>0.57</v>
+        <v>0.4</v>
       </c>
       <c r="G21" t="n">
-        <v>5.41</v>
+        <v>1.95</v>
       </c>
       <c r="H21" t="n">
-        <v>3.93</v>
+        <v>3.32</v>
       </c>
       <c r="I21" t="n">
-        <v>135.25</v>
+        <v>58.12</v>
       </c>
       <c r="J21" t="n">
-        <v>138.77</v>
+        <v>59.39</v>
       </c>
       <c r="K21" t="n">
-        <v>129.3</v>
+        <v>55.97</v>
       </c>
       <c r="L21" t="n">
-        <v>150.93</v>
+        <v>63.78</v>
       </c>
       <c r="M21" t="n">
-        <v>40.01</v>
+        <v>45.98</v>
       </c>
       <c r="N21" t="inlineStr">
         <is>
           <t>BAJO</t>
         </is>
       </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>🔥</t>
-        </is>
-      </c>
+      <c r="O21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>VIGILAR</t>
@@ -1697,46 +1685,46 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>TSLA</t>
+          <t>AVGO</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Autos / Tech</t>
+          <t>IA / Chips</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>417.85</v>
+        <v>411.84</v>
       </c>
       <c r="D22" t="n">
-        <v>74</v>
+        <v>64</v>
       </c>
       <c r="E22" t="n">
-        <v>-5.74</v>
+        <v>-3.14</v>
       </c>
       <c r="F22" t="n">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="G22" t="n">
-        <v>17.93</v>
+        <v>16.46</v>
       </c>
       <c r="H22" t="n">
-        <v>4.29</v>
+        <v>4</v>
       </c>
       <c r="I22" t="n">
-        <v>410.68</v>
+        <v>405.26</v>
       </c>
       <c r="J22" t="n">
-        <v>422.33</v>
+        <v>415.95</v>
       </c>
       <c r="K22" t="n">
-        <v>390.96</v>
+        <v>387.15</v>
       </c>
       <c r="L22" t="n">
-        <v>462.67</v>
+        <v>452.99</v>
       </c>
       <c r="M22" t="n">
-        <v>59.74</v>
+        <v>48.07</v>
       </c>
       <c r="N22" t="inlineStr">
         <is>
@@ -1753,46 +1741,46 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>AVGO</t>
+          <t>META</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>IA / Chips</t>
+          <t>Tecnología</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>414.57</v>
+        <v>609.83</v>
       </c>
       <c r="D23" t="n">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="E23" t="n">
-        <v>-5.73</v>
+        <v>-0.72</v>
       </c>
       <c r="F23" t="n">
-        <v>0.86</v>
+        <v>0.5</v>
       </c>
       <c r="G23" t="n">
-        <v>16.79</v>
+        <v>13.1</v>
       </c>
       <c r="H23" t="n">
-        <v>4.05</v>
+        <v>2.15</v>
       </c>
       <c r="I23" t="n">
-        <v>407.86</v>
+        <v>604.59</v>
       </c>
       <c r="J23" t="n">
-        <v>418.77</v>
+        <v>613.1</v>
       </c>
       <c r="K23" t="n">
-        <v>389.39</v>
+        <v>590.1799999999999</v>
       </c>
       <c r="L23" t="n">
-        <v>456.54</v>
+        <v>642.5700000000001</v>
       </c>
       <c r="M23" t="n">
-        <v>47.27</v>
+        <v>49.63</v>
       </c>
       <c r="N23" t="inlineStr">
         <is>
@@ -1802,57 +1790,57 @@
       <c r="O23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>VIGILAR</t>
+          <t>NO COMPRAR</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>COIN</t>
+          <t>SOFI</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Cripto / Trading</t>
+          <t>Fintech</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>193.56</v>
+        <v>15.65</v>
       </c>
       <c r="D24" t="n">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="E24" t="n">
-        <v>-8.699999999999999</v>
+        <v>0.26</v>
       </c>
       <c r="F24" t="n">
-        <v>0.58</v>
+        <v>0.74</v>
       </c>
       <c r="G24" t="n">
-        <v>14.16</v>
+        <v>0.64</v>
       </c>
       <c r="H24" t="n">
-        <v>7.31</v>
+        <v>4.12</v>
       </c>
       <c r="I24" t="n">
-        <v>187.9</v>
+        <v>15.39</v>
       </c>
       <c r="J24" t="n">
-        <v>197.1</v>
+        <v>15.81</v>
       </c>
       <c r="K24" t="n">
-        <v>172.33</v>
+        <v>14.68</v>
       </c>
       <c r="L24" t="n">
-        <v>228.95</v>
+        <v>17.26</v>
       </c>
       <c r="M24" t="n">
-        <v>51.13</v>
+        <v>44.11</v>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>MEDIO</t>
+          <t>BAJO</t>
         </is>
       </c>
       <c r="O24" t="inlineStr"/>
@@ -1865,46 +1853,46 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>HOOD</t>
+          <t>COIN</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Trading</t>
+          <t>Cripto / Trading</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>75.92</v>
+        <v>186.02</v>
       </c>
       <c r="D25" t="n">
-        <v>58</v>
+        <v>46</v>
       </c>
       <c r="E25" t="n">
-        <v>-5.92</v>
+        <v>-4.82</v>
       </c>
       <c r="F25" t="n">
-        <v>0.64</v>
+        <v>0.61</v>
       </c>
       <c r="G25" t="n">
-        <v>3.9</v>
+        <v>13.76</v>
       </c>
       <c r="H25" t="n">
-        <v>5.14</v>
+        <v>7.4</v>
       </c>
       <c r="I25" t="n">
-        <v>74.36</v>
+        <v>180.51</v>
       </c>
       <c r="J25" t="n">
-        <v>76.89</v>
+        <v>189.46</v>
       </c>
       <c r="K25" t="n">
-        <v>70.06999999999999</v>
+        <v>165.37</v>
       </c>
       <c r="L25" t="n">
-        <v>85.67</v>
+        <v>220.43</v>
       </c>
       <c r="M25" t="n">
-        <v>53.9</v>
+        <v>41.31</v>
       </c>
       <c r="N25" t="inlineStr">
         <is>
@@ -1921,50 +1909,50 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>META</t>
+          <t>HOOD</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Tecnología</t>
+          <t>Trading</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>607.38</v>
+        <v>73.43000000000001</v>
       </c>
       <c r="D26" t="n">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="E26" t="n">
-        <v>-1.79</v>
+        <v>-4.81</v>
       </c>
       <c r="F26" t="n">
-        <v>0.76</v>
+        <v>0.63</v>
       </c>
       <c r="G26" t="n">
-        <v>13.34</v>
+        <v>3.84</v>
       </c>
       <c r="H26" t="n">
-        <v>2.2</v>
+        <v>5.22</v>
       </c>
       <c r="I26" t="n">
-        <v>602.04</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="J26" t="n">
-        <v>610.72</v>
+        <v>74.39</v>
       </c>
       <c r="K26" t="n">
-        <v>587.37</v>
+        <v>67.68000000000001</v>
       </c>
       <c r="L26" t="n">
-        <v>640.73</v>
+        <v>83.02</v>
       </c>
       <c r="M26" t="n">
-        <v>49.11</v>
+        <v>44.54</v>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>BAJO</t>
+          <t>MEDIO</t>
         </is>
       </c>
       <c r="O26" t="inlineStr"/>
@@ -1977,50 +1965,50 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>PYPL</t>
+          <t>SOUN</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Pagos</t>
+          <t>IA</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>44.3</v>
+        <v>8.18</v>
       </c>
       <c r="D27" t="n">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="E27" t="n">
-        <v>-1.64</v>
+        <v>-2.79</v>
       </c>
       <c r="F27" t="n">
-        <v>0.72</v>
+        <v>0.93</v>
       </c>
       <c r="G27" t="n">
-        <v>1.43</v>
+        <v>0.55</v>
       </c>
       <c r="H27" t="n">
-        <v>3.23</v>
+        <v>6.78</v>
       </c>
       <c r="I27" t="n">
-        <v>43.73</v>
+        <v>7.95</v>
       </c>
       <c r="J27" t="n">
-        <v>44.66</v>
+        <v>8.31</v>
       </c>
       <c r="K27" t="n">
-        <v>42.15</v>
+        <v>7.34</v>
       </c>
       <c r="L27" t="n">
-        <v>47.88</v>
+        <v>9.56</v>
       </c>
       <c r="M27" t="n">
-        <v>11.48</v>
+        <v>30.93</v>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>BAJO</t>
+          <t>MEDIO</t>
         </is>
       </c>
       <c r="O27" t="inlineStr"/>
@@ -2033,50 +2021,50 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>SOFI</t>
+          <t>UPST</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Fintech</t>
+          <t>Fintech IA</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>15.65</v>
+        <v>28.63</v>
       </c>
       <c r="D28" t="n">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="E28" t="n">
-        <v>-2.31</v>
+        <v>-2.98</v>
       </c>
       <c r="F28" t="n">
-        <v>0.7</v>
+        <v>0.46</v>
       </c>
       <c r="G28" t="n">
-        <v>0.65</v>
+        <v>1.84</v>
       </c>
       <c r="H28" t="n">
-        <v>4.15</v>
+        <v>6.43</v>
       </c>
       <c r="I28" t="n">
-        <v>15.39</v>
+        <v>27.89</v>
       </c>
       <c r="J28" t="n">
-        <v>15.81</v>
+        <v>29.09</v>
       </c>
       <c r="K28" t="n">
-        <v>14.67</v>
+        <v>25.87</v>
       </c>
       <c r="L28" t="n">
-        <v>17.27</v>
+        <v>33.23</v>
       </c>
       <c r="M28" t="n">
-        <v>42.04</v>
+        <v>34.75</v>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>BAJO</t>
+          <t>MEDIO</t>
         </is>
       </c>
       <c r="O28" t="inlineStr"/>
@@ -2089,50 +2077,50 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>SOUN</t>
+          <t>PYPL</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>IA</t>
+          <t>Pagos</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>8.32</v>
+        <v>44.16</v>
       </c>
       <c r="D29" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E29" t="n">
-        <v>-2.35</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="F29" t="n">
-        <v>0.74</v>
+        <v>0.36</v>
       </c>
       <c r="G29" t="n">
-        <v>0.5600000000000001</v>
+        <v>1.42</v>
       </c>
       <c r="H29" t="n">
-        <v>6.7</v>
+        <v>3.21</v>
       </c>
       <c r="I29" t="n">
-        <v>8.1</v>
+        <v>43.59</v>
       </c>
       <c r="J29" t="n">
-        <v>8.460000000000001</v>
+        <v>44.51</v>
       </c>
       <c r="K29" t="n">
-        <v>7.48</v>
+        <v>42.04</v>
       </c>
       <c r="L29" t="n">
-        <v>9.710000000000001</v>
+        <v>47.7</v>
       </c>
       <c r="M29" t="n">
-        <v>31.44</v>
+        <v>11.35</v>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>MEDIO</t>
+          <t>BAJO</t>
         </is>
       </c>
       <c r="O29" t="inlineStr"/>
@@ -2145,102 +2133,106 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>UPST</t>
+          <t>IONQ</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Fintech IA</t>
+          <t>Computación cuántica</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>28.85</v>
+        <v>62.98</v>
       </c>
       <c r="D30" t="n">
-        <v>38</v>
+        <v>81</v>
       </c>
       <c r="E30" t="n">
-        <v>-2.89</v>
+        <v>21.23</v>
       </c>
       <c r="F30" t="n">
-        <v>0.76</v>
+        <v>1.32</v>
       </c>
       <c r="G30" t="n">
-        <v>1.89</v>
+        <v>5.69</v>
       </c>
       <c r="H30" t="n">
-        <v>6.55</v>
+        <v>9.039999999999999</v>
       </c>
       <c r="I30" t="n">
-        <v>28.09</v>
+        <v>60.7</v>
       </c>
       <c r="J30" t="n">
-        <v>29.32</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="K30" t="n">
-        <v>26.02</v>
+        <v>54.44</v>
       </c>
       <c r="L30" t="n">
-        <v>33.57</v>
+        <v>77.20999999999999</v>
       </c>
       <c r="M30" t="n">
-        <v>33.45</v>
+        <v>67.83</v>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>MEDIO</t>
-        </is>
-      </c>
-      <c r="O30" t="inlineStr"/>
+          <t>ALTO</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>🔥🔥</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>NO COMPRAR</t>
+          <t>VIGILAR</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>ARM</t>
+          <t>AAPL</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Chips</t>
+          <t>Tecnología</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>298.23</v>
+        <v>309.16</v>
       </c>
       <c r="D31" t="n">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="E31" t="n">
-        <v>30.52</v>
+        <v>2.97</v>
       </c>
       <c r="F31" t="n">
-        <v>1.73</v>
+        <v>0.63</v>
       </c>
       <c r="G31" t="n">
-        <v>20.24</v>
+        <v>5.74</v>
       </c>
       <c r="H31" t="n">
-        <v>6.79</v>
+        <v>1.86</v>
       </c>
       <c r="I31" t="n">
-        <v>290.13</v>
+        <v>306.86</v>
       </c>
       <c r="J31" t="n">
-        <v>303.29</v>
+        <v>310.6</v>
       </c>
       <c r="K31" t="n">
-        <v>267.87</v>
+        <v>300.55</v>
       </c>
       <c r="L31" t="n">
-        <v>348.83</v>
+        <v>323.51</v>
       </c>
       <c r="M31" t="n">
-        <v>71.73</v>
+        <v>91.18000000000001</v>
       </c>
       <c r="N31" t="inlineStr">
         <is>
@@ -2249,7 +2241,7 @@
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -2261,57 +2253,53 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>IONQ</t>
+          <t>SMCI</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Computación cuántica</t>
+          <t>Servidores IA</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>58.89</v>
+        <v>35.49</v>
       </c>
       <c r="D32" t="n">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="E32" t="n">
-        <v>2.47</v>
+        <v>14.34</v>
       </c>
       <c r="F32" t="n">
-        <v>1.79</v>
+        <v>0.83</v>
       </c>
       <c r="G32" t="n">
-        <v>5.42</v>
+        <v>2.57</v>
       </c>
       <c r="H32" t="n">
-        <v>9.210000000000001</v>
+        <v>7.23</v>
       </c>
       <c r="I32" t="n">
-        <v>56.72</v>
+        <v>34.46</v>
       </c>
       <c r="J32" t="n">
-        <v>60.25</v>
+        <v>36.13</v>
       </c>
       <c r="K32" t="n">
-        <v>50.76</v>
+        <v>31.64</v>
       </c>
       <c r="L32" t="n">
-        <v>72.44</v>
+        <v>41.91</v>
       </c>
       <c r="M32" t="n">
-        <v>64.2</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="N32" t="inlineStr">
         <is>
           <t>ALTO</t>
         </is>
       </c>
-      <c r="O32" t="inlineStr">
-        <is>
-          <t>🔥🔥</t>
-        </is>
-      </c>
+      <c r="O32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>VIGILAR</t>
@@ -2321,57 +2309,53 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>RKLB</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Tecnología</t>
+          <t>Espacial</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>304.99</v>
+        <v>135.86</v>
       </c>
       <c r="D33" t="n">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="E33" t="n">
-        <v>2.27</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="F33" t="n">
-        <v>0.89</v>
+        <v>1.02</v>
       </c>
       <c r="G33" t="n">
-        <v>5.7</v>
+        <v>12.41</v>
       </c>
       <c r="H33" t="n">
-        <v>1.87</v>
+        <v>9.130000000000001</v>
       </c>
       <c r="I33" t="n">
-        <v>302.71</v>
+        <v>130.9</v>
       </c>
       <c r="J33" t="n">
-        <v>306.41</v>
+        <v>138.96</v>
       </c>
       <c r="K33" t="n">
-        <v>296.45</v>
+        <v>117.25</v>
       </c>
       <c r="L33" t="n">
-        <v>319.23</v>
+        <v>166.88</v>
       </c>
       <c r="M33" t="n">
-        <v>82.44</v>
+        <v>74.86</v>
       </c>
       <c r="N33" t="inlineStr">
         <is>
           <t>ALTO</t>
         </is>
       </c>
-      <c r="O33" t="inlineStr">
-        <is>
-          <t>🔥</t>
-        </is>
-      </c>
+      <c r="O33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>VIGILAR</t>
@@ -2390,48 +2374,44 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>118.5</v>
+        <v>119.78</v>
       </c>
       <c r="D34" t="n">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="E34" t="n">
-        <v>2.22</v>
+        <v>10.12</v>
       </c>
       <c r="F34" t="n">
-        <v>0.62</v>
+        <v>0.45</v>
       </c>
       <c r="G34" t="n">
-        <v>10.13</v>
+        <v>10.16</v>
       </c>
       <c r="H34" t="n">
-        <v>8.550000000000001</v>
+        <v>8.48</v>
       </c>
       <c r="I34" t="n">
-        <v>114.45</v>
+        <v>115.72</v>
       </c>
       <c r="J34" t="n">
-        <v>121.03</v>
+        <v>122.32</v>
       </c>
       <c r="K34" t="n">
-        <v>103.31</v>
+        <v>104.54</v>
       </c>
       <c r="L34" t="n">
-        <v>143.82</v>
+        <v>145.18</v>
       </c>
       <c r="M34" t="n">
-        <v>62.29</v>
+        <v>66.16</v>
       </c>
       <c r="N34" t="inlineStr">
         <is>
           <t>ALTO</t>
         </is>
       </c>
-      <c r="O34" t="inlineStr">
-        <is>
-          <t>🔥</t>
-        </is>
-      </c>
+      <c r="O34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>VIGILAR</t>
@@ -2441,46 +2421,46 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>RKLB</t>
+          <t>QCOM</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Espacial</t>
+          <t>Chips</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>125.45</v>
+        <v>237.86</v>
       </c>
       <c r="D35" t="n">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="E35" t="n">
-        <v>-5.36</v>
+        <v>18.05</v>
       </c>
       <c r="F35" t="n">
-        <v>1.1</v>
+        <v>0.78</v>
       </c>
       <c r="G35" t="n">
-        <v>11.78</v>
+        <v>19.91</v>
       </c>
       <c r="H35" t="n">
-        <v>9.390000000000001</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="I35" t="n">
-        <v>120.74</v>
+        <v>229.9</v>
       </c>
       <c r="J35" t="n">
-        <v>128.4</v>
+        <v>242.84</v>
       </c>
       <c r="K35" t="n">
-        <v>107.77</v>
+        <v>207.99</v>
       </c>
       <c r="L35" t="n">
-        <v>154.91</v>
+        <v>287.64</v>
       </c>
       <c r="M35" t="n">
-        <v>72.68000000000001</v>
+        <v>70.91</v>
       </c>
       <c r="N35" t="inlineStr">
         <is>
@@ -2497,7 +2477,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>QCOM</t>
+          <t>ARM</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2506,37 +2486,37 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>213.41</v>
+        <v>304.56</v>
       </c>
       <c r="D36" t="n">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="E36" t="n">
-        <v>6.66</v>
+        <v>45.61</v>
       </c>
       <c r="F36" t="n">
-        <v>0.85</v>
+        <v>1.02</v>
       </c>
       <c r="G36" t="n">
-        <v>18.77</v>
+        <v>20.93</v>
       </c>
       <c r="H36" t="n">
-        <v>8.800000000000001</v>
+        <v>6.87</v>
       </c>
       <c r="I36" t="n">
-        <v>205.9</v>
+        <v>296.19</v>
       </c>
       <c r="J36" t="n">
-        <v>218.1</v>
+        <v>309.79</v>
       </c>
       <c r="K36" t="n">
-        <v>185.25</v>
+        <v>273.16</v>
       </c>
       <c r="L36" t="n">
-        <v>260.34</v>
+        <v>356.89</v>
       </c>
       <c r="M36" t="n">
-        <v>62.11</v>
+        <v>75.48999999999999</v>
       </c>
       <c r="N36" t="inlineStr">
         <is>
@@ -2553,46 +2533,46 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>MU</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Memoria / Chips</t>
+          <t>IA / Chips</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>762.1</v>
+        <v>467.55</v>
       </c>
       <c r="D37" t="n">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="E37" t="n">
-        <v>-1.79</v>
+        <v>10.25</v>
       </c>
       <c r="F37" t="n">
-        <v>0.83</v>
+        <v>0.7</v>
       </c>
       <c r="G37" t="n">
-        <v>60.99</v>
+        <v>30.99</v>
       </c>
       <c r="H37" t="n">
-        <v>8</v>
+        <v>6.63</v>
       </c>
       <c r="I37" t="n">
-        <v>737.7</v>
+        <v>455.15</v>
       </c>
       <c r="J37" t="n">
-        <v>777.35</v>
+        <v>475.3</v>
       </c>
       <c r="K37" t="n">
-        <v>670.61</v>
+        <v>421.06</v>
       </c>
       <c r="L37" t="n">
-        <v>914.58</v>
+        <v>545.03</v>
       </c>
       <c r="M37" t="n">
-        <v>69.58</v>
+        <v>75.23</v>
       </c>
       <c r="N37" t="inlineStr">
         <is>
@@ -2602,7 +2582,7 @@
       <c r="O37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>VIGILAR</t>
+          <t>NO COMPRAR</t>
         </is>
       </c>
     </row>

--- a/analisis_acciones.xlsx
+++ b/analisis_acciones.xlsx
@@ -510,37 +510,37 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1635.5</v>
+        <v>1632.9</v>
       </c>
       <c r="D2" t="n">
         <v>95</v>
       </c>
       <c r="E2" t="n">
-        <v>8.9</v>
+        <v>8.73</v>
       </c>
       <c r="F2" t="n">
-        <v>0.79</v>
+        <v>1.01</v>
       </c>
       <c r="G2" t="n">
         <v>72.19</v>
       </c>
       <c r="H2" t="n">
-        <v>4.41</v>
+        <v>4.42</v>
       </c>
       <c r="I2" t="n">
-        <v>1606.62</v>
+        <v>1604.02</v>
       </c>
       <c r="J2" t="n">
-        <v>1653.55</v>
+        <v>1650.95</v>
       </c>
       <c r="K2" t="n">
-        <v>1527.22</v>
+        <v>1524.62</v>
       </c>
       <c r="L2" t="n">
-        <v>1815.97</v>
+        <v>1813.37</v>
       </c>
       <c r="M2" t="n">
-        <v>67.86</v>
+        <v>67.73999999999999</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -570,16 +570,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>305.77</v>
+        <v>305.35</v>
       </c>
       <c r="D3" t="n">
         <v>95</v>
       </c>
       <c r="E3" t="n">
-        <v>7.39</v>
+        <v>7.25</v>
       </c>
       <c r="F3" t="n">
-        <v>0.44</v>
+        <v>0.85</v>
       </c>
       <c r="G3" t="n">
         <v>15.31</v>
@@ -588,19 +588,19 @@
         <v>5.01</v>
       </c>
       <c r="I3" t="n">
-        <v>299.65</v>
+        <v>299.23</v>
       </c>
       <c r="J3" t="n">
-        <v>309.6</v>
+        <v>309.18</v>
       </c>
       <c r="K3" t="n">
-        <v>282.81</v>
+        <v>282.38</v>
       </c>
       <c r="L3" t="n">
-        <v>344.05</v>
+        <v>343.63</v>
       </c>
       <c r="M3" t="n">
-        <v>67.66</v>
+        <v>67.55</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -630,37 +630,37 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1892.04</v>
+        <v>1888.38</v>
       </c>
       <c r="D4" t="n">
         <v>95</v>
       </c>
       <c r="E4" t="n">
-        <v>5</v>
+        <v>4.79</v>
       </c>
       <c r="F4" t="n">
-        <v>0.38</v>
+        <v>0.67</v>
       </c>
       <c r="G4" t="n">
         <v>80.59999999999999</v>
       </c>
       <c r="H4" t="n">
-        <v>4.26</v>
+        <v>4.27</v>
       </c>
       <c r="I4" t="n">
-        <v>1859.8</v>
+        <v>1856.14</v>
       </c>
       <c r="J4" t="n">
-        <v>1912.19</v>
+        <v>1908.53</v>
       </c>
       <c r="K4" t="n">
-        <v>1771.14</v>
+        <v>1767.47</v>
       </c>
       <c r="L4" t="n">
-        <v>2093.53</v>
+        <v>2089.89</v>
       </c>
       <c r="M4" t="n">
-        <v>62.88</v>
+        <v>62.69</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -690,37 +690,37 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>57.82</v>
+        <v>57.28</v>
       </c>
       <c r="D5" t="n">
         <v>95</v>
       </c>
       <c r="E5" t="n">
-        <v>4.41</v>
+        <v>3.43</v>
       </c>
       <c r="F5" t="n">
-        <v>0.45</v>
+        <v>0.86</v>
       </c>
       <c r="G5" t="n">
         <v>1.41</v>
       </c>
       <c r="H5" t="n">
-        <v>2.44</v>
+        <v>2.47</v>
       </c>
       <c r="I5" t="n">
-        <v>57.26</v>
+        <v>56.71</v>
       </c>
       <c r="J5" t="n">
-        <v>58.17</v>
+        <v>57.63</v>
       </c>
       <c r="K5" t="n">
-        <v>55.7</v>
+        <v>55.16</v>
       </c>
       <c r="L5" t="n">
-        <v>61.35</v>
+        <v>60.81</v>
       </c>
       <c r="M5" t="n">
-        <v>60.66</v>
+        <v>58.48</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
@@ -750,16 +750,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>537.24</v>
+        <v>537.33</v>
       </c>
       <c r="D6" t="n">
         <v>93</v>
       </c>
       <c r="E6" t="n">
-        <v>5.65</v>
+        <v>5.67</v>
       </c>
       <c r="F6" t="n">
-        <v>0.74</v>
+        <v>0.92</v>
       </c>
       <c r="G6" t="n">
         <v>22.18</v>
@@ -768,19 +768,19 @@
         <v>4.13</v>
       </c>
       <c r="I6" t="n">
-        <v>528.37</v>
+        <v>528.46</v>
       </c>
       <c r="J6" t="n">
-        <v>542.79</v>
+        <v>542.88</v>
       </c>
       <c r="K6" t="n">
-        <v>503.97</v>
+        <v>504.06</v>
       </c>
       <c r="L6" t="n">
-        <v>592.7</v>
+        <v>592.79</v>
       </c>
       <c r="M6" t="n">
-        <v>68.23999999999999</v>
+        <v>68.26000000000001</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
@@ -810,37 +810,37 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>763</v>
+        <v>751</v>
       </c>
       <c r="D7" t="n">
         <v>84</v>
       </c>
       <c r="E7" t="n">
-        <v>5.29</v>
+        <v>3.63</v>
       </c>
       <c r="F7" t="n">
-        <v>0.55</v>
+        <v>0.7</v>
       </c>
       <c r="G7" t="n">
-        <v>59.73</v>
+        <v>59.74</v>
       </c>
       <c r="H7" t="n">
-        <v>7.83</v>
+        <v>7.95</v>
       </c>
       <c r="I7" t="n">
-        <v>739.11</v>
+        <v>727.11</v>
       </c>
       <c r="J7" t="n">
-        <v>777.9299999999999</v>
+        <v>765.9299999999999</v>
       </c>
       <c r="K7" t="n">
-        <v>673.4</v>
+        <v>661.4</v>
       </c>
       <c r="L7" t="n">
-        <v>912.33</v>
+        <v>900.34</v>
       </c>
       <c r="M7" t="n">
-        <v>67.66</v>
+        <v>66.20999999999999</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -870,37 +870,37 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>9.34</v>
+        <v>9.289999999999999</v>
       </c>
       <c r="D8" t="n">
         <v>84</v>
       </c>
       <c r="E8" t="n">
-        <v>7.92</v>
+        <v>7.4</v>
       </c>
       <c r="F8" t="n">
-        <v>0.73</v>
+        <v>1.03</v>
       </c>
       <c r="G8" t="n">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="H8" t="n">
-        <v>5.14</v>
+        <v>5.26</v>
       </c>
       <c r="I8" t="n">
-        <v>9.140000000000001</v>
+        <v>9.09</v>
       </c>
       <c r="J8" t="n">
-        <v>9.449999999999999</v>
+        <v>9.41</v>
       </c>
       <c r="K8" t="n">
-        <v>8.619999999999999</v>
+        <v>8.56</v>
       </c>
       <c r="L8" t="n">
-        <v>10.53</v>
+        <v>10.51</v>
       </c>
       <c r="M8" t="n">
-        <v>51.71</v>
+        <v>51.03</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
@@ -921,46 +921,46 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CVX</t>
+          <t>TSM</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Energía</t>
+          <t>Chips</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>191.59</v>
+        <v>404.52</v>
       </c>
       <c r="D9" t="n">
         <v>92</v>
       </c>
       <c r="E9" t="n">
-        <v>1.17</v>
+        <v>0.04</v>
       </c>
       <c r="F9" t="n">
-        <v>0.41</v>
+        <v>0.53</v>
       </c>
       <c r="G9" t="n">
-        <v>4.39</v>
+        <v>15.26</v>
       </c>
       <c r="H9" t="n">
-        <v>2.29</v>
+        <v>3.77</v>
       </c>
       <c r="I9" t="n">
-        <v>189.83</v>
+        <v>398.41</v>
       </c>
       <c r="J9" t="n">
-        <v>192.69</v>
+        <v>408.34</v>
       </c>
       <c r="K9" t="n">
-        <v>185.01</v>
+        <v>381.62</v>
       </c>
       <c r="L9" t="n">
-        <v>202.56</v>
+        <v>442.68</v>
       </c>
       <c r="M9" t="n">
-        <v>51.49</v>
+        <v>51.24</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
@@ -981,50 +981,50 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SPY</t>
+          <t>CVX</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ETF Mercado</t>
+          <t>Energía</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>746.25</v>
+        <v>191.43</v>
       </c>
       <c r="D10" t="n">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="E10" t="n">
-        <v>0.96</v>
+        <v>1.09</v>
       </c>
       <c r="F10" t="n">
-        <v>0.49</v>
+        <v>0.72</v>
       </c>
       <c r="G10" t="n">
-        <v>7.55</v>
+        <v>4.42</v>
       </c>
       <c r="H10" t="n">
-        <v>1.01</v>
+        <v>2.31</v>
       </c>
       <c r="I10" t="n">
-        <v>743.23</v>
+        <v>189.66</v>
       </c>
       <c r="J10" t="n">
-        <v>748.14</v>
+        <v>192.53</v>
       </c>
       <c r="K10" t="n">
-        <v>734.92</v>
+        <v>184.8</v>
       </c>
       <c r="L10" t="n">
-        <v>765.14</v>
+        <v>202.47</v>
       </c>
       <c r="M10" t="n">
-        <v>72.11</v>
+        <v>51.27</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>MEDIO</t>
+          <t>BAJO</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1041,46 +1041,46 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>QQQ</t>
+          <t>SPY</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>ETF Nasdaq</t>
+          <t>ETF Mercado</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>718.27</v>
+        <v>745.64</v>
       </c>
       <c r="D11" t="n">
         <v>89</v>
       </c>
       <c r="E11" t="n">
-        <v>1.32</v>
+        <v>0.88</v>
       </c>
       <c r="F11" t="n">
-        <v>0.63</v>
+        <v>0.88</v>
       </c>
       <c r="G11" t="n">
-        <v>11.44</v>
+        <v>7.55</v>
       </c>
       <c r="H11" t="n">
-        <v>1.59</v>
+        <v>1.01</v>
       </c>
       <c r="I11" t="n">
-        <v>713.6900000000001</v>
+        <v>742.62</v>
       </c>
       <c r="J11" t="n">
-        <v>721.13</v>
+        <v>747.53</v>
       </c>
       <c r="K11" t="n">
-        <v>701.1</v>
+        <v>734.3099999999999</v>
       </c>
       <c r="L11" t="n">
-        <v>746.88</v>
+        <v>764.53</v>
       </c>
       <c r="M11" t="n">
-        <v>73.72</v>
+        <v>71.84</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
@@ -1101,50 +1101,50 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>NVDA</t>
+          <t>QQQ</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>IA / Chips</t>
+          <t>ETF Nasdaq</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>215.04</v>
+        <v>717.54</v>
       </c>
       <c r="D12" t="n">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.56</v>
+        <v>1.21</v>
       </c>
       <c r="F12" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.84</v>
       </c>
       <c r="G12" t="n">
-        <v>8.279999999999999</v>
+        <v>11.44</v>
       </c>
       <c r="H12" t="n">
-        <v>3.85</v>
+        <v>1.59</v>
       </c>
       <c r="I12" t="n">
-        <v>211.73</v>
+        <v>712.96</v>
       </c>
       <c r="J12" t="n">
-        <v>217.11</v>
+        <v>720.4</v>
       </c>
       <c r="K12" t="n">
-        <v>202.62</v>
+        <v>700.37</v>
       </c>
       <c r="L12" t="n">
-        <v>235.74</v>
+        <v>746.15</v>
       </c>
       <c r="M12" t="n">
-        <v>62.24</v>
+        <v>73.52</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>BAJO</t>
+          <t>MEDIO</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -1161,46 +1161,46 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>NVDA</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Chips</t>
+          <t>IA / Chips</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>404.02</v>
+        <v>215.33</v>
       </c>
       <c r="D13" t="n">
         <v>84</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.08</v>
+        <v>-4.43</v>
       </c>
       <c r="F13" t="n">
-        <v>0.37</v>
+        <v>1.04</v>
       </c>
       <c r="G13" t="n">
-        <v>15.2</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="H13" t="n">
-        <v>3.76</v>
+        <v>3.85</v>
       </c>
       <c r="I13" t="n">
-        <v>397.95</v>
+        <v>212.02</v>
       </c>
       <c r="J13" t="n">
-        <v>407.82</v>
+        <v>217.4</v>
       </c>
       <c r="K13" t="n">
-        <v>381.23</v>
+        <v>202.9</v>
       </c>
       <c r="L13" t="n">
-        <v>442.01</v>
+        <v>236.04</v>
       </c>
       <c r="M13" t="n">
-        <v>51.03</v>
+        <v>62.51</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
@@ -1230,16 +1230,16 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>432.83</v>
+        <v>432.16</v>
       </c>
       <c r="D14" t="n">
         <v>84</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.74</v>
+        <v>-0.9</v>
       </c>
       <c r="F14" t="n">
-        <v>0.39</v>
+        <v>0.63</v>
       </c>
       <c r="G14" t="n">
         <v>20.02</v>
@@ -1248,19 +1248,19 @@
         <v>4.63</v>
       </c>
       <c r="I14" t="n">
-        <v>424.82</v>
+        <v>424.15</v>
       </c>
       <c r="J14" t="n">
-        <v>437.84</v>
+        <v>437.17</v>
       </c>
       <c r="K14" t="n">
-        <v>402.8</v>
+        <v>402.13</v>
       </c>
       <c r="L14" t="n">
-        <v>482.88</v>
+        <v>482.21</v>
       </c>
       <c r="M14" t="n">
-        <v>62.34</v>
+        <v>62.19</v>
       </c>
       <c r="N14" t="inlineStr">
         <is>
@@ -1290,16 +1290,16 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>155.05</v>
+        <v>154.92</v>
       </c>
       <c r="D15" t="n">
         <v>84</v>
       </c>
       <c r="E15" t="n">
-        <v>-1.82</v>
+        <v>-1.9</v>
       </c>
       <c r="F15" t="n">
-        <v>0.43</v>
+        <v>0.74</v>
       </c>
       <c r="G15" t="n">
         <v>4.36</v>
@@ -1308,19 +1308,19 @@
         <v>2.81</v>
       </c>
       <c r="I15" t="n">
-        <v>153.31</v>
+        <v>153.18</v>
       </c>
       <c r="J15" t="n">
-        <v>156.14</v>
+        <v>156.01</v>
       </c>
       <c r="K15" t="n">
-        <v>148.51</v>
+        <v>148.38</v>
       </c>
       <c r="L15" t="n">
-        <v>165.95</v>
+        <v>165.82</v>
       </c>
       <c r="M15" t="n">
-        <v>53.16</v>
+        <v>52.98</v>
       </c>
       <c r="N15" t="inlineStr">
         <is>
@@ -1350,37 +1350,37 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>427.41</v>
+        <v>426.01</v>
       </c>
       <c r="D16" t="n">
         <v>82</v>
       </c>
       <c r="E16" t="n">
-        <v>1.22</v>
+        <v>0.89</v>
       </c>
       <c r="F16" t="n">
-        <v>0.71</v>
+        <v>0.84</v>
       </c>
       <c r="G16" t="n">
         <v>18.2</v>
       </c>
       <c r="H16" t="n">
-        <v>4.26</v>
+        <v>4.27</v>
       </c>
       <c r="I16" t="n">
-        <v>420.13</v>
+        <v>418.73</v>
       </c>
       <c r="J16" t="n">
-        <v>431.96</v>
+        <v>430.56</v>
       </c>
       <c r="K16" t="n">
-        <v>400.11</v>
+        <v>398.71</v>
       </c>
       <c r="L16" t="n">
-        <v>472.92</v>
+        <v>471.52</v>
       </c>
       <c r="M16" t="n">
-        <v>61.9</v>
+        <v>61.54</v>
       </c>
       <c r="N16" t="inlineStr">
         <is>
@@ -1401,123 +1401,123 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>GOOGL</t>
+          <t>PLTR</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Tecnología</t>
+          <t>IA / Software</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>383.45</v>
+        <v>136.88</v>
       </c>
       <c r="D17" t="n">
-        <v>76</v>
+        <v>54</v>
       </c>
       <c r="E17" t="n">
-        <v>-3.36</v>
+        <v>2.16</v>
       </c>
       <c r="F17" t="n">
-        <v>0.43</v>
+        <v>0.68</v>
       </c>
       <c r="G17" t="n">
-        <v>9.800000000000001</v>
+        <v>5.35</v>
       </c>
       <c r="H17" t="n">
-        <v>2.56</v>
+        <v>3.91</v>
       </c>
       <c r="I17" t="n">
-        <v>379.53</v>
+        <v>134.74</v>
       </c>
       <c r="J17" t="n">
-        <v>385.9</v>
+        <v>138.22</v>
       </c>
       <c r="K17" t="n">
-        <v>368.75</v>
+        <v>128.86</v>
       </c>
       <c r="L17" t="n">
-        <v>407.96</v>
+        <v>150.25</v>
       </c>
       <c r="M17" t="n">
-        <v>50.15</v>
+        <v>35.66</v>
       </c>
       <c r="N17" t="inlineStr">
         <is>
           <t>BAJO</t>
         </is>
       </c>
-      <c r="O17" t="inlineStr"/>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>🔥</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>POSIBLE COMPRA</t>
+          <t>NO COMPRAR</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>PLTR</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>IA / Software</t>
+          <t>Tecnología</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>137.09</v>
+        <v>418.57</v>
       </c>
       <c r="D18" t="n">
-        <v>54</v>
+        <v>74</v>
       </c>
       <c r="E18" t="n">
-        <v>2.31</v>
+        <v>-0.58</v>
       </c>
       <c r="F18" t="n">
-        <v>0.53</v>
+        <v>0.65</v>
       </c>
       <c r="G18" t="n">
-        <v>5.35</v>
+        <v>10.85</v>
       </c>
       <c r="H18" t="n">
-        <v>3.9</v>
+        <v>2.59</v>
       </c>
       <c r="I18" t="n">
-        <v>134.95</v>
+        <v>414.23</v>
       </c>
       <c r="J18" t="n">
-        <v>138.42</v>
+        <v>421.28</v>
       </c>
       <c r="K18" t="n">
-        <v>129.06</v>
+        <v>402.29</v>
       </c>
       <c r="L18" t="n">
-        <v>150.45</v>
+        <v>445.7</v>
       </c>
       <c r="M18" t="n">
-        <v>35.89</v>
+        <v>55.15</v>
       </c>
       <c r="N18" t="inlineStr">
         <is>
           <t>BAJO</t>
         </is>
       </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>🔥</t>
-        </is>
-      </c>
+      <c r="O18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>NO COMPRAR</t>
+          <t>VIGILAR</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>AMZN</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1526,37 +1526,37 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>418.8</v>
+        <v>266.32</v>
       </c>
       <c r="D19" t="n">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.52</v>
+        <v>0.83</v>
       </c>
       <c r="F19" t="n">
-        <v>0.46</v>
+        <v>0.63</v>
       </c>
       <c r="G19" t="n">
-        <v>10.85</v>
+        <v>6.12</v>
       </c>
       <c r="H19" t="n">
-        <v>2.59</v>
+        <v>2.3</v>
       </c>
       <c r="I19" t="n">
-        <v>414.46</v>
+        <v>263.87</v>
       </c>
       <c r="J19" t="n">
-        <v>421.51</v>
+        <v>267.85</v>
       </c>
       <c r="K19" t="n">
-        <v>402.52</v>
+        <v>257.14</v>
       </c>
       <c r="L19" t="n">
-        <v>445.93</v>
+        <v>281.62</v>
       </c>
       <c r="M19" t="n">
-        <v>55.37</v>
+        <v>43.33</v>
       </c>
       <c r="N19" t="inlineStr">
         <is>
@@ -1573,46 +1573,46 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>AMZN</t>
+          <t>OXY</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Tecnología</t>
+          <t>Energía</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>266.87</v>
+        <v>58.81</v>
       </c>
       <c r="D20" t="n">
         <v>72</v>
       </c>
       <c r="E20" t="n">
-        <v>1.03</v>
+        <v>-1.36</v>
       </c>
       <c r="F20" t="n">
-        <v>0.43</v>
+        <v>0.64</v>
       </c>
       <c r="G20" t="n">
-        <v>6.08</v>
+        <v>1.95</v>
       </c>
       <c r="H20" t="n">
-        <v>2.28</v>
+        <v>3.32</v>
       </c>
       <c r="I20" t="n">
-        <v>264.44</v>
+        <v>58.03</v>
       </c>
       <c r="J20" t="n">
-        <v>268.39</v>
+        <v>59.3</v>
       </c>
       <c r="K20" t="n">
-        <v>257.76</v>
+        <v>55.88</v>
       </c>
       <c r="L20" t="n">
-        <v>282.06</v>
+        <v>63.7</v>
       </c>
       <c r="M20" t="n">
-        <v>43.89</v>
+        <v>45.7</v>
       </c>
       <c r="N20" t="inlineStr">
         <is>
@@ -1629,46 +1629,46 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>OXY</t>
+          <t>AVGO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Energía</t>
+          <t>IA / Chips</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>58.9</v>
+        <v>414.14</v>
       </c>
       <c r="D21" t="n">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.21</v>
+        <v>-2.6</v>
       </c>
       <c r="F21" t="n">
-        <v>0.4</v>
+        <v>0.76</v>
       </c>
       <c r="G21" t="n">
-        <v>1.95</v>
+        <v>16.47</v>
       </c>
       <c r="H21" t="n">
-        <v>3.32</v>
+        <v>3.98</v>
       </c>
       <c r="I21" t="n">
-        <v>58.12</v>
+        <v>407.55</v>
       </c>
       <c r="J21" t="n">
-        <v>59.39</v>
+        <v>418.26</v>
       </c>
       <c r="K21" t="n">
-        <v>55.97</v>
+        <v>389.44</v>
       </c>
       <c r="L21" t="n">
-        <v>63.78</v>
+        <v>455.3</v>
       </c>
       <c r="M21" t="n">
-        <v>45.98</v>
+        <v>49</v>
       </c>
       <c r="N21" t="inlineStr">
         <is>
@@ -1685,46 +1685,46 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>AVGO</t>
+          <t>GOOGL</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>IA / Chips</t>
+          <t>Tecnología</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>411.84</v>
+        <v>382.97</v>
       </c>
       <c r="D22" t="n">
         <v>64</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.14</v>
+        <v>-3.48</v>
       </c>
       <c r="F22" t="n">
-        <v>0.5</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="G22" t="n">
-        <v>16.46</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="H22" t="n">
-        <v>4</v>
+        <v>2.58</v>
       </c>
       <c r="I22" t="n">
-        <v>405.26</v>
+        <v>379.01</v>
       </c>
       <c r="J22" t="n">
-        <v>415.95</v>
+        <v>385.44</v>
       </c>
       <c r="K22" t="n">
-        <v>387.15</v>
+        <v>368.13</v>
       </c>
       <c r="L22" t="n">
-        <v>452.99</v>
+        <v>407.7</v>
       </c>
       <c r="M22" t="n">
-        <v>48.07</v>
+        <v>49.8</v>
       </c>
       <c r="N22" t="inlineStr">
         <is>
@@ -1750,16 +1750,16 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>609.83</v>
+        <v>610.26</v>
       </c>
       <c r="D23" t="n">
         <v>54</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.72</v>
+        <v>-0.65</v>
       </c>
       <c r="F23" t="n">
-        <v>0.5</v>
+        <v>0.72</v>
       </c>
       <c r="G23" t="n">
         <v>13.1</v>
@@ -1768,19 +1768,19 @@
         <v>2.15</v>
       </c>
       <c r="I23" t="n">
-        <v>604.59</v>
+        <v>605.02</v>
       </c>
       <c r="J23" t="n">
-        <v>613.1</v>
+        <v>613.53</v>
       </c>
       <c r="K23" t="n">
-        <v>590.1799999999999</v>
+        <v>590.61</v>
       </c>
       <c r="L23" t="n">
-        <v>642.5700000000001</v>
+        <v>643</v>
       </c>
       <c r="M23" t="n">
-        <v>49.63</v>
+        <v>49.9</v>
       </c>
       <c r="N23" t="inlineStr">
         <is>
@@ -1806,16 +1806,16 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>15.65</v>
+        <v>15.62</v>
       </c>
       <c r="D24" t="n">
         <v>52</v>
       </c>
       <c r="E24" t="n">
-        <v>0.26</v>
+        <v>0.06</v>
       </c>
       <c r="F24" t="n">
-        <v>0.74</v>
+        <v>0.84</v>
       </c>
       <c r="G24" t="n">
         <v>0.64</v>
@@ -1824,19 +1824,19 @@
         <v>4.12</v>
       </c>
       <c r="I24" t="n">
-        <v>15.39</v>
+        <v>15.36</v>
       </c>
       <c r="J24" t="n">
-        <v>15.81</v>
+        <v>15.78</v>
       </c>
       <c r="K24" t="n">
-        <v>14.68</v>
+        <v>14.65</v>
       </c>
       <c r="L24" t="n">
-        <v>17.26</v>
+        <v>17.23</v>
       </c>
       <c r="M24" t="n">
-        <v>44.11</v>
+        <v>43.83</v>
       </c>
       <c r="N24" t="inlineStr">
         <is>
@@ -1862,37 +1862,37 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>186.02</v>
+        <v>184.99</v>
       </c>
       <c r="D25" t="n">
         <v>46</v>
       </c>
       <c r="E25" t="n">
-        <v>-4.82</v>
+        <v>-5.34</v>
       </c>
       <c r="F25" t="n">
-        <v>0.61</v>
+        <v>0.82</v>
       </c>
       <c r="G25" t="n">
-        <v>13.76</v>
+        <v>13.84</v>
       </c>
       <c r="H25" t="n">
-        <v>7.4</v>
+        <v>7.48</v>
       </c>
       <c r="I25" t="n">
-        <v>180.51</v>
+        <v>179.46</v>
       </c>
       <c r="J25" t="n">
-        <v>189.46</v>
+        <v>188.45</v>
       </c>
       <c r="K25" t="n">
-        <v>165.37</v>
+        <v>164.23</v>
       </c>
       <c r="L25" t="n">
-        <v>220.43</v>
+        <v>219.58</v>
       </c>
       <c r="M25" t="n">
-        <v>41.31</v>
+        <v>40.88</v>
       </c>
       <c r="N25" t="inlineStr">
         <is>
@@ -1918,16 +1918,16 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>73.43000000000001</v>
+        <v>73.64</v>
       </c>
       <c r="D26" t="n">
         <v>46</v>
       </c>
       <c r="E26" t="n">
-        <v>-4.81</v>
+        <v>-4.54</v>
       </c>
       <c r="F26" t="n">
-        <v>0.63</v>
+        <v>0.82</v>
       </c>
       <c r="G26" t="n">
         <v>3.84</v>
@@ -1936,19 +1936,19 @@
         <v>5.22</v>
       </c>
       <c r="I26" t="n">
-        <v>71.90000000000001</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="J26" t="n">
-        <v>74.39</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="K26" t="n">
-        <v>67.68000000000001</v>
+        <v>67.88</v>
       </c>
       <c r="L26" t="n">
-        <v>83.02</v>
+        <v>83.25</v>
       </c>
       <c r="M26" t="n">
-        <v>44.54</v>
+        <v>44.87</v>
       </c>
       <c r="N26" t="inlineStr">
         <is>
@@ -1974,22 +1974,22 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>8.18</v>
+        <v>8.17</v>
       </c>
       <c r="D27" t="n">
         <v>38</v>
       </c>
       <c r="E27" t="n">
-        <v>-2.79</v>
+        <v>-2.85</v>
       </c>
       <c r="F27" t="n">
-        <v>0.93</v>
+        <v>1.08</v>
       </c>
       <c r="G27" t="n">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H27" t="n">
-        <v>6.78</v>
+        <v>6.84</v>
       </c>
       <c r="I27" t="n">
         <v>7.95</v>
@@ -1998,13 +1998,13 @@
         <v>8.31</v>
       </c>
       <c r="K27" t="n">
-        <v>7.34</v>
+        <v>7.33</v>
       </c>
       <c r="L27" t="n">
-        <v>9.56</v>
+        <v>9.57</v>
       </c>
       <c r="M27" t="n">
-        <v>30.93</v>
+        <v>30.88</v>
       </c>
       <c r="N27" t="inlineStr">
         <is>
@@ -2030,37 +2030,37 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>28.63</v>
+        <v>28.56</v>
       </c>
       <c r="D28" t="n">
         <v>38</v>
       </c>
       <c r="E28" t="n">
-        <v>-2.98</v>
+        <v>-3.22</v>
       </c>
       <c r="F28" t="n">
-        <v>0.46</v>
+        <v>0.67</v>
       </c>
       <c r="G28" t="n">
         <v>1.84</v>
       </c>
       <c r="H28" t="n">
-        <v>6.43</v>
+        <v>6.45</v>
       </c>
       <c r="I28" t="n">
-        <v>27.89</v>
+        <v>27.82</v>
       </c>
       <c r="J28" t="n">
-        <v>29.09</v>
+        <v>29.02</v>
       </c>
       <c r="K28" t="n">
-        <v>25.87</v>
+        <v>25.8</v>
       </c>
       <c r="L28" t="n">
-        <v>33.23</v>
+        <v>33.17</v>
       </c>
       <c r="M28" t="n">
-        <v>34.75</v>
+        <v>34.53</v>
       </c>
       <c r="N28" t="inlineStr">
         <is>
@@ -2086,37 +2086,37 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>44.16</v>
+        <v>44.23</v>
       </c>
       <c r="D29" t="n">
         <v>36</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-0.41</v>
       </c>
       <c r="F29" t="n">
-        <v>0.36</v>
+        <v>0.71</v>
       </c>
       <c r="G29" t="n">
         <v>1.42</v>
       </c>
       <c r="H29" t="n">
-        <v>3.21</v>
+        <v>3.22</v>
       </c>
       <c r="I29" t="n">
-        <v>43.59</v>
+        <v>43.66</v>
       </c>
       <c r="J29" t="n">
-        <v>44.51</v>
+        <v>44.59</v>
       </c>
       <c r="K29" t="n">
-        <v>42.04</v>
+        <v>42.1</v>
       </c>
       <c r="L29" t="n">
-        <v>47.7</v>
+        <v>47.79</v>
       </c>
       <c r="M29" t="n">
-        <v>11.35</v>
+        <v>11.45</v>
       </c>
       <c r="N29" t="inlineStr">
         <is>
@@ -2133,46 +2133,46 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>IONQ</t>
+          <t>AAPL</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Computación cuántica</t>
+          <t>Tecnología</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>62.98</v>
+        <v>308.82</v>
       </c>
       <c r="D30" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E30" t="n">
-        <v>21.23</v>
+        <v>2.86</v>
       </c>
       <c r="F30" t="n">
-        <v>1.32</v>
+        <v>0.9</v>
       </c>
       <c r="G30" t="n">
-        <v>5.69</v>
+        <v>5.74</v>
       </c>
       <c r="H30" t="n">
-        <v>9.039999999999999</v>
+        <v>1.86</v>
       </c>
       <c r="I30" t="n">
-        <v>60.7</v>
+        <v>306.52</v>
       </c>
       <c r="J30" t="n">
-        <v>64.40000000000001</v>
+        <v>310.26</v>
       </c>
       <c r="K30" t="n">
-        <v>54.44</v>
+        <v>300.21</v>
       </c>
       <c r="L30" t="n">
-        <v>77.20999999999999</v>
+        <v>323.17</v>
       </c>
       <c r="M30" t="n">
-        <v>67.83</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="N30" t="inlineStr">
         <is>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -2193,46 +2193,46 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>IONQ</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Tecnología</t>
+          <t>Computación cuántica</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>309.16</v>
+        <v>63.64</v>
       </c>
       <c r="D31" t="n">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="E31" t="n">
-        <v>2.97</v>
+        <v>22.5</v>
       </c>
       <c r="F31" t="n">
-        <v>0.63</v>
+        <v>1.54</v>
       </c>
       <c r="G31" t="n">
-        <v>5.74</v>
+        <v>5.71</v>
       </c>
       <c r="H31" t="n">
-        <v>1.86</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="I31" t="n">
-        <v>306.86</v>
+        <v>61.36</v>
       </c>
       <c r="J31" t="n">
-        <v>310.6</v>
+        <v>65.06999999999999</v>
       </c>
       <c r="K31" t="n">
-        <v>300.55</v>
+        <v>55.08</v>
       </c>
       <c r="L31" t="n">
-        <v>323.51</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="M31" t="n">
-        <v>91.18000000000001</v>
+        <v>68.26000000000001</v>
       </c>
       <c r="N31" t="inlineStr">
         <is>
@@ -2262,37 +2262,37 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>35.49</v>
+        <v>35.58</v>
       </c>
       <c r="D32" t="n">
         <v>78</v>
       </c>
       <c r="E32" t="n">
-        <v>14.34</v>
+        <v>14.63</v>
       </c>
       <c r="F32" t="n">
-        <v>0.83</v>
+        <v>1.03</v>
       </c>
       <c r="G32" t="n">
         <v>2.57</v>
       </c>
       <c r="H32" t="n">
-        <v>7.23</v>
+        <v>7.22</v>
       </c>
       <c r="I32" t="n">
-        <v>34.46</v>
+        <v>34.55</v>
       </c>
       <c r="J32" t="n">
-        <v>36.13</v>
+        <v>36.22</v>
       </c>
       <c r="K32" t="n">
-        <v>31.64</v>
+        <v>31.73</v>
       </c>
       <c r="L32" t="n">
-        <v>41.91</v>
+        <v>42</v>
       </c>
       <c r="M32" t="n">
-        <v>67.59999999999999</v>
+        <v>67.73</v>
       </c>
       <c r="N32" t="inlineStr">
         <is>
@@ -2318,37 +2318,37 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>135.86</v>
+        <v>135.76</v>
       </c>
       <c r="D33" t="n">
         <v>77</v>
       </c>
       <c r="E33" t="n">
-        <v>8.890000000000001</v>
+        <v>8.81</v>
       </c>
       <c r="F33" t="n">
-        <v>1.02</v>
+        <v>1.18</v>
       </c>
       <c r="G33" t="n">
         <v>12.41</v>
       </c>
       <c r="H33" t="n">
-        <v>9.130000000000001</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="I33" t="n">
-        <v>130.9</v>
+        <v>130.8</v>
       </c>
       <c r="J33" t="n">
-        <v>138.96</v>
+        <v>138.86</v>
       </c>
       <c r="K33" t="n">
-        <v>117.25</v>
+        <v>117.15</v>
       </c>
       <c r="L33" t="n">
-        <v>166.88</v>
+        <v>166.78</v>
       </c>
       <c r="M33" t="n">
-        <v>74.86</v>
+        <v>74.84</v>
       </c>
       <c r="N33" t="inlineStr">
         <is>
@@ -2374,16 +2374,16 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>119.78</v>
+        <v>119.84</v>
       </c>
       <c r="D34" t="n">
         <v>74</v>
       </c>
       <c r="E34" t="n">
-        <v>10.12</v>
+        <v>10.18</v>
       </c>
       <c r="F34" t="n">
-        <v>0.45</v>
+        <v>0.54</v>
       </c>
       <c r="G34" t="n">
         <v>10.16</v>
@@ -2392,19 +2392,19 @@
         <v>8.48</v>
       </c>
       <c r="I34" t="n">
-        <v>115.72</v>
+        <v>115.78</v>
       </c>
       <c r="J34" t="n">
-        <v>122.32</v>
+        <v>122.38</v>
       </c>
       <c r="K34" t="n">
-        <v>104.54</v>
+        <v>104.6</v>
       </c>
       <c r="L34" t="n">
-        <v>145.18</v>
+        <v>145.24</v>
       </c>
       <c r="M34" t="n">
-        <v>66.16</v>
+        <v>66.19</v>
       </c>
       <c r="N34" t="inlineStr">
         <is>
@@ -2430,37 +2430,37 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>237.86</v>
+        <v>238.16</v>
       </c>
       <c r="D35" t="n">
         <v>67</v>
       </c>
       <c r="E35" t="n">
-        <v>18.05</v>
+        <v>18.2</v>
       </c>
       <c r="F35" t="n">
-        <v>0.78</v>
+        <v>0.95</v>
       </c>
       <c r="G35" t="n">
         <v>19.91</v>
       </c>
       <c r="H35" t="n">
-        <v>8.369999999999999</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="I35" t="n">
-        <v>229.9</v>
+        <v>230.2</v>
       </c>
       <c r="J35" t="n">
-        <v>242.84</v>
+        <v>243.14</v>
       </c>
       <c r="K35" t="n">
-        <v>207.99</v>
+        <v>208.29</v>
       </c>
       <c r="L35" t="n">
-        <v>287.64</v>
+        <v>287.94</v>
       </c>
       <c r="M35" t="n">
-        <v>70.91</v>
+        <v>70.95999999999999</v>
       </c>
       <c r="N35" t="inlineStr">
         <is>
@@ -2486,37 +2486,37 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>304.56</v>
+        <v>306.51</v>
       </c>
       <c r="D36" t="n">
         <v>64</v>
       </c>
       <c r="E36" t="n">
-        <v>45.61</v>
+        <v>46.54</v>
       </c>
       <c r="F36" t="n">
-        <v>1.02</v>
+        <v>1.16</v>
       </c>
       <c r="G36" t="n">
         <v>20.93</v>
       </c>
       <c r="H36" t="n">
-        <v>6.87</v>
+        <v>6.83</v>
       </c>
       <c r="I36" t="n">
-        <v>296.19</v>
+        <v>298.14</v>
       </c>
       <c r="J36" t="n">
-        <v>309.79</v>
+        <v>311.74</v>
       </c>
       <c r="K36" t="n">
-        <v>273.16</v>
+        <v>275.11</v>
       </c>
       <c r="L36" t="n">
-        <v>356.89</v>
+        <v>358.84</v>
       </c>
       <c r="M36" t="n">
-        <v>75.48999999999999</v>
+        <v>75.72</v>
       </c>
       <c r="N36" t="inlineStr">
         <is>
@@ -2542,16 +2542,16 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>467.55</v>
+        <v>467.51</v>
       </c>
       <c r="D37" t="n">
         <v>54</v>
       </c>
       <c r="E37" t="n">
-        <v>10.25</v>
+        <v>10.24</v>
       </c>
       <c r="F37" t="n">
-        <v>0.7</v>
+        <v>0.82</v>
       </c>
       <c r="G37" t="n">
         <v>30.99</v>
@@ -2560,19 +2560,19 @@
         <v>6.63</v>
       </c>
       <c r="I37" t="n">
-        <v>455.15</v>
+        <v>455.11</v>
       </c>
       <c r="J37" t="n">
-        <v>475.3</v>
+        <v>475.26</v>
       </c>
       <c r="K37" t="n">
-        <v>421.06</v>
+        <v>421.02</v>
       </c>
       <c r="L37" t="n">
-        <v>545.03</v>
+        <v>545</v>
       </c>
       <c r="M37" t="n">
-        <v>75.23</v>
+        <v>75.22</v>
       </c>
       <c r="N37" t="inlineStr">
         <is>

--- a/analisis_acciones.xlsx
+++ b/analisis_acciones.xlsx
@@ -501,46 +501,46 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ASML</t>
+          <t>AI</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Chips</t>
+          <t>IA</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1632.9</v>
+        <v>9.59</v>
       </c>
       <c r="D2" t="n">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="E2" t="n">
-        <v>8.73</v>
+        <v>9.6</v>
       </c>
       <c r="F2" t="n">
-        <v>1.01</v>
+        <v>1.43</v>
       </c>
       <c r="G2" t="n">
-        <v>72.19</v>
+        <v>0.51</v>
       </c>
       <c r="H2" t="n">
-        <v>4.42</v>
+        <v>5.28</v>
       </c>
       <c r="I2" t="n">
-        <v>1604.02</v>
+        <v>9.390000000000001</v>
       </c>
       <c r="J2" t="n">
-        <v>1650.95</v>
+        <v>9.720000000000001</v>
       </c>
       <c r="K2" t="n">
-        <v>1524.62</v>
+        <v>8.83</v>
       </c>
       <c r="L2" t="n">
-        <v>1813.37</v>
+        <v>10.86</v>
       </c>
       <c r="M2" t="n">
-        <v>67.73999999999999</v>
+        <v>52.57</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -549,7 +549,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>🔥🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -561,46 +561,46 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>LRCX</t>
+          <t>ASML</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Equipos chips</t>
+          <t>Chips</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>305.35</v>
+        <v>1632.03</v>
       </c>
       <c r="D3" t="n">
         <v>95</v>
       </c>
       <c r="E3" t="n">
-        <v>7.25</v>
+        <v>10.84</v>
       </c>
       <c r="F3" t="n">
-        <v>0.85</v>
+        <v>0.88</v>
       </c>
       <c r="G3" t="n">
-        <v>15.31</v>
+        <v>70.42</v>
       </c>
       <c r="H3" t="n">
-        <v>5.01</v>
+        <v>4.31</v>
       </c>
       <c r="I3" t="n">
-        <v>299.23</v>
+        <v>1603.86</v>
       </c>
       <c r="J3" t="n">
-        <v>309.18</v>
+        <v>1649.63</v>
       </c>
       <c r="K3" t="n">
-        <v>282.38</v>
+        <v>1526.41</v>
       </c>
       <c r="L3" t="n">
-        <v>343.63</v>
+        <v>1808.07</v>
       </c>
       <c r="M3" t="n">
-        <v>67.55</v>
+        <v>64.79000000000001</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -621,7 +621,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>KLAC</t>
+          <t>AMAT</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -630,41 +630,41 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1888.38</v>
+        <v>454.89</v>
       </c>
       <c r="D4" t="n">
         <v>95</v>
       </c>
       <c r="E4" t="n">
-        <v>4.79</v>
+        <v>10.13</v>
       </c>
       <c r="F4" t="n">
-        <v>0.67</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="G4" t="n">
-        <v>80.59999999999999</v>
+        <v>20.13</v>
       </c>
       <c r="H4" t="n">
-        <v>4.27</v>
+        <v>4.43</v>
       </c>
       <c r="I4" t="n">
-        <v>1856.14</v>
+        <v>446.84</v>
       </c>
       <c r="J4" t="n">
-        <v>1908.53</v>
+        <v>459.92</v>
       </c>
       <c r="K4" t="n">
-        <v>1767.47</v>
+        <v>424.7</v>
       </c>
       <c r="L4" t="n">
-        <v>2089.89</v>
+        <v>505.21</v>
       </c>
       <c r="M4" t="n">
-        <v>62.69</v>
+        <v>62.92</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>BAJO</t>
+          <t>MEDIO</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -681,46 +681,46 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SLB</t>
+          <t>TSM</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Energía</t>
+          <t>Chips</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>57.28</v>
+        <v>412.32</v>
       </c>
       <c r="D5" t="n">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="E5" t="n">
-        <v>3.43</v>
+        <v>4.13</v>
       </c>
       <c r="F5" t="n">
-        <v>0.86</v>
+        <v>0.77</v>
       </c>
       <c r="G5" t="n">
-        <v>1.41</v>
+        <v>15.15</v>
       </c>
       <c r="H5" t="n">
-        <v>2.47</v>
+        <v>3.67</v>
       </c>
       <c r="I5" t="n">
-        <v>56.71</v>
+        <v>406.26</v>
       </c>
       <c r="J5" t="n">
-        <v>57.63</v>
+        <v>416.11</v>
       </c>
       <c r="K5" t="n">
-        <v>55.16</v>
+        <v>389.59</v>
       </c>
       <c r="L5" t="n">
-        <v>60.81</v>
+        <v>450.2</v>
       </c>
       <c r="M5" t="n">
-        <v>58.48</v>
+        <v>57.6</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
@@ -741,46 +741,46 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SOXX</t>
+          <t>QQQ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>ETF Chips</t>
+          <t>ETF Nasdaq</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>537.33</v>
+        <v>730.28</v>
       </c>
       <c r="D6" t="n">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="E6" t="n">
-        <v>5.67</v>
+        <v>3.46</v>
       </c>
       <c r="F6" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="G6" t="n">
-        <v>22.18</v>
+        <v>11.71</v>
       </c>
       <c r="H6" t="n">
-        <v>4.13</v>
+        <v>1.6</v>
       </c>
       <c r="I6" t="n">
-        <v>528.46</v>
+        <v>725.6</v>
       </c>
       <c r="J6" t="n">
-        <v>542.88</v>
+        <v>733.21</v>
       </c>
       <c r="K6" t="n">
-        <v>504.06</v>
+        <v>712.71</v>
       </c>
       <c r="L6" t="n">
-        <v>592.79</v>
+        <v>759.5599999999999</v>
       </c>
       <c r="M6" t="n">
-        <v>68.26000000000001</v>
+        <v>74.59</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
@@ -801,50 +801,50 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>MU</t>
+          <t>TSLA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Memoria / Chips</t>
+          <t>Autos / Tech</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>751</v>
+        <v>433.59</v>
       </c>
       <c r="D7" t="n">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="E7" t="n">
-        <v>3.63</v>
+        <v>5.76</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7</v>
+        <v>0.83</v>
       </c>
       <c r="G7" t="n">
-        <v>59.74</v>
+        <v>17.92</v>
       </c>
       <c r="H7" t="n">
-        <v>7.95</v>
+        <v>4.13</v>
       </c>
       <c r="I7" t="n">
-        <v>727.11</v>
+        <v>426.42</v>
       </c>
       <c r="J7" t="n">
-        <v>765.9299999999999</v>
+        <v>438.07</v>
       </c>
       <c r="K7" t="n">
-        <v>661.4</v>
+        <v>406.71</v>
       </c>
       <c r="L7" t="n">
-        <v>900.34</v>
+        <v>478.39</v>
       </c>
       <c r="M7" t="n">
-        <v>66.20999999999999</v>
+        <v>64.78</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>MEDIO</t>
+          <t>BAJO</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -861,55 +861,55 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>AI</t>
+          <t>SLB</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>IA</t>
+          <t>Energía</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>9.289999999999999</v>
+        <v>57.98</v>
       </c>
       <c r="D8" t="n">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="E8" t="n">
-        <v>7.4</v>
+        <v>1.45</v>
       </c>
       <c r="F8" t="n">
-        <v>1.03</v>
+        <v>1.13</v>
       </c>
       <c r="G8" t="n">
-        <v>0.49</v>
+        <v>1.47</v>
       </c>
       <c r="H8" t="n">
-        <v>5.26</v>
+        <v>2.54</v>
       </c>
       <c r="I8" t="n">
-        <v>9.09</v>
+        <v>57.39</v>
       </c>
       <c r="J8" t="n">
-        <v>9.41</v>
+        <v>58.35</v>
       </c>
       <c r="K8" t="n">
-        <v>8.56</v>
+        <v>55.77</v>
       </c>
       <c r="L8" t="n">
-        <v>10.51</v>
+        <v>61.66</v>
       </c>
       <c r="M8" t="n">
-        <v>51.03</v>
+        <v>59.84</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>MEDIO</t>
+          <t>BAJO</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -921,50 +921,50 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>SPY</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Chips</t>
+          <t>ETF Mercado</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>404.52</v>
+        <v>750.59</v>
       </c>
       <c r="D9" t="n">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="E9" t="n">
-        <v>0.04</v>
+        <v>1.62</v>
       </c>
       <c r="F9" t="n">
-        <v>0.53</v>
+        <v>0.75</v>
       </c>
       <c r="G9" t="n">
-        <v>15.26</v>
+        <v>7.52</v>
       </c>
       <c r="H9" t="n">
-        <v>3.77</v>
+        <v>1</v>
       </c>
       <c r="I9" t="n">
-        <v>398.41</v>
+        <v>747.58</v>
       </c>
       <c r="J9" t="n">
-        <v>408.34</v>
+        <v>752.47</v>
       </c>
       <c r="K9" t="n">
-        <v>381.62</v>
+        <v>739.3200000000001</v>
       </c>
       <c r="L9" t="n">
-        <v>442.68</v>
+        <v>769.38</v>
       </c>
       <c r="M9" t="n">
-        <v>51.24</v>
+        <v>71.48</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>BAJO</t>
+          <t>MEDIO</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -981,46 +981,46 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CVX</t>
+          <t>NVDA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Energía</t>
+          <t>IA / Chips</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>191.43</v>
+        <v>214.86</v>
       </c>
       <c r="D10" t="n">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="E10" t="n">
-        <v>1.09</v>
+        <v>-3.36</v>
       </c>
       <c r="F10" t="n">
-        <v>0.72</v>
+        <v>1.12</v>
       </c>
       <c r="G10" t="n">
-        <v>4.42</v>
+        <v>8.43</v>
       </c>
       <c r="H10" t="n">
-        <v>2.31</v>
+        <v>3.92</v>
       </c>
       <c r="I10" t="n">
-        <v>189.66</v>
+        <v>211.49</v>
       </c>
       <c r="J10" t="n">
-        <v>192.53</v>
+        <v>216.97</v>
       </c>
       <c r="K10" t="n">
-        <v>184.8</v>
+        <v>202.22</v>
       </c>
       <c r="L10" t="n">
-        <v>202.47</v>
+        <v>235.93</v>
       </c>
       <c r="M10" t="n">
-        <v>51.27</v>
+        <v>63.94</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
@@ -1041,50 +1041,50 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SPY</t>
+          <t>GOOGL</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>ETF Mercado</t>
+          <t>Tecnología</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>745.64</v>
+        <v>388.88</v>
       </c>
       <c r="D11" t="n">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="E11" t="n">
-        <v>0.88</v>
+        <v>-2.03</v>
       </c>
       <c r="F11" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="G11" t="n">
-        <v>7.55</v>
+        <v>9.68</v>
       </c>
       <c r="H11" t="n">
-        <v>1.01</v>
+        <v>2.49</v>
       </c>
       <c r="I11" t="n">
-        <v>742.62</v>
+        <v>385.01</v>
       </c>
       <c r="J11" t="n">
-        <v>747.53</v>
+        <v>391.3</v>
       </c>
       <c r="K11" t="n">
-        <v>734.3099999999999</v>
+        <v>374.36</v>
       </c>
       <c r="L11" t="n">
-        <v>764.53</v>
+        <v>413.09</v>
       </c>
       <c r="M11" t="n">
-        <v>71.84</v>
+        <v>50.32</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>MEDIO</t>
+          <t>BAJO</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1101,50 +1101,50 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>QQQ</t>
+          <t>AVGO</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>ETF Nasdaq</t>
+          <t>IA / Chips</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>717.54</v>
+        <v>422.01</v>
       </c>
       <c r="D12" t="n">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="E12" t="n">
-        <v>1.21</v>
+        <v>0.31</v>
       </c>
       <c r="F12" t="n">
-        <v>0.84</v>
+        <v>1.09</v>
       </c>
       <c r="G12" t="n">
-        <v>11.44</v>
+        <v>16.77</v>
       </c>
       <c r="H12" t="n">
-        <v>1.59</v>
+        <v>3.97</v>
       </c>
       <c r="I12" t="n">
-        <v>712.96</v>
+        <v>415.3</v>
       </c>
       <c r="J12" t="n">
-        <v>720.4</v>
+        <v>426.2</v>
       </c>
       <c r="K12" t="n">
-        <v>700.37</v>
+        <v>396.85</v>
       </c>
       <c r="L12" t="n">
-        <v>746.15</v>
+        <v>463.94</v>
       </c>
       <c r="M12" t="n">
-        <v>73.52</v>
+        <v>47.68</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>MEDIO</t>
+          <t>BAJO</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -1161,46 +1161,46 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>NVDA</t>
+          <t>CVX</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>IA / Chips</t>
+          <t>Energía</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>215.33</v>
+        <v>184.71</v>
       </c>
       <c r="D13" t="n">
-        <v>84</v>
+        <v>71</v>
       </c>
       <c r="E13" t="n">
-        <v>-4.43</v>
+        <v>-4.96</v>
       </c>
       <c r="F13" t="n">
-        <v>1.04</v>
+        <v>1.27</v>
       </c>
       <c r="G13" t="n">
-        <v>8.289999999999999</v>
+        <v>4.73</v>
       </c>
       <c r="H13" t="n">
-        <v>3.85</v>
+        <v>2.56</v>
       </c>
       <c r="I13" t="n">
-        <v>212.02</v>
+        <v>182.82</v>
       </c>
       <c r="J13" t="n">
-        <v>217.4</v>
+        <v>185.89</v>
       </c>
       <c r="K13" t="n">
-        <v>202.9</v>
+        <v>177.62</v>
       </c>
       <c r="L13" t="n">
-        <v>236.04</v>
+        <v>196.53</v>
       </c>
       <c r="M13" t="n">
-        <v>62.51</v>
+        <v>42.57</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
@@ -1214,57 +1214,57 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>POSIBLE COMPRA</t>
+          <t>VIGILAR</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>AMAT</t>
+          <t>UPST</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Equipos chips</t>
+          <t>Fintech IA</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>432.16</v>
+        <v>30.62</v>
       </c>
       <c r="D14" t="n">
-        <v>84</v>
+        <v>66</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.9</v>
+        <v>9.59</v>
       </c>
       <c r="F14" t="n">
-        <v>0.63</v>
+        <v>1.15</v>
       </c>
       <c r="G14" t="n">
-        <v>20.02</v>
+        <v>1.94</v>
       </c>
       <c r="H14" t="n">
-        <v>4.63</v>
+        <v>6.32</v>
       </c>
       <c r="I14" t="n">
-        <v>424.15</v>
+        <v>29.85</v>
       </c>
       <c r="J14" t="n">
-        <v>437.17</v>
+        <v>31.1</v>
       </c>
       <c r="K14" t="n">
-        <v>402.13</v>
+        <v>27.72</v>
       </c>
       <c r="L14" t="n">
-        <v>482.21</v>
+        <v>35.46</v>
       </c>
       <c r="M14" t="n">
-        <v>62.19</v>
+        <v>47.81</v>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>BAJO</t>
+          <t>MEDIO</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
@@ -1274,194 +1274,182 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>POSIBLE COMPRA</t>
+          <t>VIGILAR</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>XOM</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Energía</t>
+          <t>Tecnología</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>154.92</v>
+        <v>416.03</v>
       </c>
       <c r="D15" t="n">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="E15" t="n">
-        <v>-1.9</v>
+        <v>-1.56</v>
       </c>
       <c r="F15" t="n">
-        <v>0.74</v>
+        <v>0.86</v>
       </c>
       <c r="G15" t="n">
-        <v>4.36</v>
+        <v>10.77</v>
       </c>
       <c r="H15" t="n">
-        <v>2.81</v>
+        <v>2.59</v>
       </c>
       <c r="I15" t="n">
-        <v>153.18</v>
+        <v>411.72</v>
       </c>
       <c r="J15" t="n">
-        <v>156.01</v>
+        <v>418.72</v>
       </c>
       <c r="K15" t="n">
-        <v>148.38</v>
+        <v>399.88</v>
       </c>
       <c r="L15" t="n">
-        <v>165.82</v>
+        <v>442.94</v>
       </c>
       <c r="M15" t="n">
-        <v>52.98</v>
+        <v>54.85</v>
       </c>
       <c r="N15" t="inlineStr">
         <is>
           <t>BAJO</t>
         </is>
       </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>🔥</t>
-        </is>
-      </c>
+      <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>POSIBLE COMPRA</t>
+          <t>VIGILAR</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>TSLA</t>
+          <t>PLTR</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Autos / Tech</t>
+          <t>IA / Software</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>426.01</v>
+        <v>136.6</v>
       </c>
       <c r="D16" t="n">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="E16" t="n">
-        <v>0.89</v>
+        <v>1.08</v>
       </c>
       <c r="F16" t="n">
-        <v>0.84</v>
+        <v>0.76</v>
       </c>
       <c r="G16" t="n">
-        <v>18.2</v>
+        <v>4.92</v>
       </c>
       <c r="H16" t="n">
-        <v>4.27</v>
+        <v>3.6</v>
       </c>
       <c r="I16" t="n">
-        <v>418.73</v>
+        <v>134.63</v>
       </c>
       <c r="J16" t="n">
-        <v>430.56</v>
+        <v>137.83</v>
       </c>
       <c r="K16" t="n">
-        <v>398.71</v>
+        <v>129.22</v>
       </c>
       <c r="L16" t="n">
-        <v>471.52</v>
+        <v>148.91</v>
       </c>
       <c r="M16" t="n">
-        <v>61.54</v>
+        <v>51.56</v>
       </c>
       <c r="N16" t="inlineStr">
         <is>
           <t>BAJO</t>
         </is>
       </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>🔥</t>
-        </is>
-      </c>
+      <c r="O16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>POSIBLE COMPRA</t>
+          <t>VIGILAR</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>PLTR</t>
+          <t>AMZN</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>IA / Software</t>
+          <t>Tecnología</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>136.88</v>
+        <v>265.29</v>
       </c>
       <c r="D17" t="n">
-        <v>54</v>
+        <v>72</v>
       </c>
       <c r="E17" t="n">
-        <v>2.16</v>
+        <v>0.16</v>
       </c>
       <c r="F17" t="n">
-        <v>0.68</v>
+        <v>0.87</v>
       </c>
       <c r="G17" t="n">
-        <v>5.35</v>
+        <v>6.17</v>
       </c>
       <c r="H17" t="n">
-        <v>3.91</v>
+        <v>2.33</v>
       </c>
       <c r="I17" t="n">
-        <v>134.74</v>
+        <v>262.82</v>
       </c>
       <c r="J17" t="n">
-        <v>138.22</v>
+        <v>266.83</v>
       </c>
       <c r="K17" t="n">
-        <v>128.86</v>
+        <v>256.03</v>
       </c>
       <c r="L17" t="n">
-        <v>150.25</v>
+        <v>280.72</v>
       </c>
       <c r="M17" t="n">
-        <v>35.66</v>
+        <v>40.27</v>
       </c>
       <c r="N17" t="inlineStr">
         <is>
           <t>BAJO</t>
         </is>
       </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>🔥</t>
-        </is>
-      </c>
+      <c r="O17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>NO COMPRAR</t>
+          <t>VIGILAR</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>META</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1470,37 +1458,37 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>418.57</v>
+        <v>612.34</v>
       </c>
       <c r="D18" t="n">
-        <v>74</v>
+        <v>64</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.58</v>
+        <v>0.18</v>
       </c>
       <c r="F18" t="n">
-        <v>0.65</v>
+        <v>0.68</v>
       </c>
       <c r="G18" t="n">
-        <v>10.85</v>
+        <v>12.75</v>
       </c>
       <c r="H18" t="n">
-        <v>2.59</v>
+        <v>2.08</v>
       </c>
       <c r="I18" t="n">
-        <v>414.23</v>
+        <v>607.24</v>
       </c>
       <c r="J18" t="n">
-        <v>421.28</v>
+        <v>615.53</v>
       </c>
       <c r="K18" t="n">
-        <v>402.29</v>
+        <v>593.21</v>
       </c>
       <c r="L18" t="n">
-        <v>445.7</v>
+        <v>644.22</v>
       </c>
       <c r="M18" t="n">
-        <v>55.15</v>
+        <v>54.93</v>
       </c>
       <c r="N18" t="inlineStr">
         <is>
@@ -1517,46 +1505,46 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>AMZN</t>
+          <t>XOM</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Tecnología</t>
+          <t>Energía</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>266.32</v>
+        <v>149.81</v>
       </c>
       <c r="D19" t="n">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="E19" t="n">
-        <v>0.83</v>
+        <v>-6.65</v>
       </c>
       <c r="F19" t="n">
-        <v>0.63</v>
+        <v>0.59</v>
       </c>
       <c r="G19" t="n">
-        <v>6.12</v>
+        <v>4.54</v>
       </c>
       <c r="H19" t="n">
-        <v>2.3</v>
+        <v>3.03</v>
       </c>
       <c r="I19" t="n">
-        <v>263.87</v>
+        <v>147.99</v>
       </c>
       <c r="J19" t="n">
-        <v>267.85</v>
+        <v>150.95</v>
       </c>
       <c r="K19" t="n">
-        <v>257.14</v>
+        <v>142.99</v>
       </c>
       <c r="L19" t="n">
-        <v>281.62</v>
+        <v>161.17</v>
       </c>
       <c r="M19" t="n">
-        <v>43.33</v>
+        <v>45.2</v>
       </c>
       <c r="N19" t="inlineStr">
         <is>
@@ -1582,37 +1570,37 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>58.81</v>
+        <v>57.46</v>
       </c>
       <c r="D20" t="n">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.36</v>
+        <v>-3.75</v>
       </c>
       <c r="F20" t="n">
-        <v>0.64</v>
+        <v>0.73</v>
       </c>
       <c r="G20" t="n">
-        <v>1.95</v>
+        <v>1.99</v>
       </c>
       <c r="H20" t="n">
-        <v>3.32</v>
+        <v>3.47</v>
       </c>
       <c r="I20" t="n">
-        <v>58.03</v>
+        <v>56.66</v>
       </c>
       <c r="J20" t="n">
-        <v>59.3</v>
+        <v>57.96</v>
       </c>
       <c r="K20" t="n">
-        <v>55.88</v>
+        <v>54.47</v>
       </c>
       <c r="L20" t="n">
-        <v>63.7</v>
+        <v>62.44</v>
       </c>
       <c r="M20" t="n">
-        <v>45.7</v>
+        <v>44.6</v>
       </c>
       <c r="N20" t="inlineStr">
         <is>
@@ -1629,46 +1617,46 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>AVGO</t>
+          <t>SOFI</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>IA / Chips</t>
+          <t>Fintech</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>414.14</v>
+        <v>15.98</v>
       </c>
       <c r="D21" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.6</v>
+        <v>1.72</v>
       </c>
       <c r="F21" t="n">
-        <v>0.76</v>
+        <v>1.13</v>
       </c>
       <c r="G21" t="n">
-        <v>16.47</v>
+        <v>0.71</v>
       </c>
       <c r="H21" t="n">
-        <v>3.98</v>
+        <v>4.46</v>
       </c>
       <c r="I21" t="n">
-        <v>407.55</v>
+        <v>15.69</v>
       </c>
       <c r="J21" t="n">
-        <v>418.26</v>
+        <v>16.16</v>
       </c>
       <c r="K21" t="n">
-        <v>389.44</v>
+        <v>14.91</v>
       </c>
       <c r="L21" t="n">
-        <v>455.3</v>
+        <v>17.76</v>
       </c>
       <c r="M21" t="n">
-        <v>49</v>
+        <v>49.59</v>
       </c>
       <c r="N21" t="inlineStr">
         <is>
@@ -1685,106 +1673,106 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>GOOGL</t>
+          <t>COIN</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Tecnología</t>
+          <t>Cripto / Trading</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>382.97</v>
+        <v>180.01</v>
       </c>
       <c r="D22" t="n">
-        <v>64</v>
+        <v>46</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.48</v>
+        <v>-4.98</v>
       </c>
       <c r="F22" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.79</v>
       </c>
       <c r="G22" t="n">
-        <v>9.890000000000001</v>
+        <v>13.42</v>
       </c>
       <c r="H22" t="n">
-        <v>2.58</v>
+        <v>7.46</v>
       </c>
       <c r="I22" t="n">
-        <v>379.01</v>
+        <v>174.64</v>
       </c>
       <c r="J22" t="n">
-        <v>385.44</v>
+        <v>183.37</v>
       </c>
       <c r="K22" t="n">
-        <v>368.13</v>
+        <v>159.87</v>
       </c>
       <c r="L22" t="n">
-        <v>407.7</v>
+        <v>213.57</v>
       </c>
       <c r="M22" t="n">
-        <v>49.8</v>
+        <v>40.99</v>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>BAJO</t>
+          <t>MEDIO</t>
         </is>
       </c>
       <c r="O22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>VIGILAR</t>
+          <t>NO COMPRAR</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>META</t>
+          <t>HOOD</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Tecnología</t>
+          <t>Trading</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>610.26</v>
+        <v>74.09</v>
       </c>
       <c r="D23" t="n">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.65</v>
+        <v>-3.97</v>
       </c>
       <c r="F23" t="n">
-        <v>0.72</v>
+        <v>0.79</v>
       </c>
       <c r="G23" t="n">
-        <v>13.1</v>
+        <v>3.87</v>
       </c>
       <c r="H23" t="n">
-        <v>2.15</v>
+        <v>5.22</v>
       </c>
       <c r="I23" t="n">
-        <v>605.02</v>
+        <v>72.54000000000001</v>
       </c>
       <c r="J23" t="n">
-        <v>613.53</v>
+        <v>75.06</v>
       </c>
       <c r="K23" t="n">
-        <v>590.61</v>
+        <v>68.29000000000001</v>
       </c>
       <c r="L23" t="n">
-        <v>643</v>
+        <v>83.75</v>
       </c>
       <c r="M23" t="n">
-        <v>49.9</v>
+        <v>44.81</v>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>BAJO</t>
+          <t>MEDIO</t>
         </is>
       </c>
       <c r="O23" t="inlineStr"/>
@@ -1797,50 +1785,50 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>SOFI</t>
+          <t>SOUN</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Fintech</t>
+          <t>IA</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>15.62</v>
+        <v>8.130000000000001</v>
       </c>
       <c r="D24" t="n">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="E24" t="n">
-        <v>0.06</v>
+        <v>-2.63</v>
       </c>
       <c r="F24" t="n">
-        <v>0.84</v>
+        <v>0.74</v>
       </c>
       <c r="G24" t="n">
-        <v>0.64</v>
+        <v>0.53</v>
       </c>
       <c r="H24" t="n">
-        <v>4.12</v>
+        <v>6.56</v>
       </c>
       <c r="I24" t="n">
-        <v>15.36</v>
+        <v>7.92</v>
       </c>
       <c r="J24" t="n">
-        <v>15.78</v>
+        <v>8.26</v>
       </c>
       <c r="K24" t="n">
-        <v>14.65</v>
+        <v>7.33</v>
       </c>
       <c r="L24" t="n">
-        <v>17.23</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="M24" t="n">
-        <v>43.83</v>
+        <v>33.76</v>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>BAJO</t>
+          <t>MEDIO</t>
         </is>
       </c>
       <c r="O24" t="inlineStr"/>
@@ -1853,50 +1841,50 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>COIN</t>
+          <t>PYPL</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Cripto / Trading</t>
+          <t>Pagos</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>184.99</v>
+        <v>44.16</v>
       </c>
       <c r="D25" t="n">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="E25" t="n">
-        <v>-5.34</v>
+        <v>-0.51</v>
       </c>
       <c r="F25" t="n">
-        <v>0.82</v>
+        <v>0.78</v>
       </c>
       <c r="G25" t="n">
-        <v>13.84</v>
+        <v>1.04</v>
       </c>
       <c r="H25" t="n">
-        <v>7.48</v>
+        <v>2.36</v>
       </c>
       <c r="I25" t="n">
-        <v>179.46</v>
+        <v>43.74</v>
       </c>
       <c r="J25" t="n">
-        <v>188.45</v>
+        <v>44.42</v>
       </c>
       <c r="K25" t="n">
-        <v>164.23</v>
+        <v>42.59</v>
       </c>
       <c r="L25" t="n">
-        <v>219.58</v>
+        <v>46.77</v>
       </c>
       <c r="M25" t="n">
-        <v>40.88</v>
+        <v>22</v>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>MEDIO</t>
+          <t>BAJO</t>
         </is>
       </c>
       <c r="O25" t="inlineStr"/>
@@ -1909,224 +1897,240 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>HOOD</t>
+          <t>MU</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Trading</t>
+          <t>Memoria / Chips</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>73.64</v>
+        <v>895.88</v>
       </c>
       <c r="D26" t="n">
-        <v>46</v>
+        <v>88</v>
       </c>
       <c r="E26" t="n">
-        <v>-4.54</v>
+        <v>31.45</v>
       </c>
       <c r="F26" t="n">
-        <v>0.82</v>
+        <v>1.41</v>
       </c>
       <c r="G26" t="n">
-        <v>3.84</v>
+        <v>66.2</v>
       </c>
       <c r="H26" t="n">
-        <v>5.22</v>
+        <v>7.39</v>
       </c>
       <c r="I26" t="n">
-        <v>72.09999999999999</v>
+        <v>869.4</v>
       </c>
       <c r="J26" t="n">
-        <v>74.59999999999999</v>
+        <v>912.4299999999999</v>
       </c>
       <c r="K26" t="n">
-        <v>67.88</v>
+        <v>796.58</v>
       </c>
       <c r="L26" t="n">
-        <v>83.25</v>
+        <v>1061.38</v>
       </c>
       <c r="M26" t="n">
-        <v>44.87</v>
+        <v>70.64</v>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>MEDIO</t>
-        </is>
-      </c>
-      <c r="O26" t="inlineStr"/>
+          <t>ALTO</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>🔥🔥</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>NO COMPRAR</t>
+          <t>VIGILAR</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>SOUN</t>
+          <t>LRCX</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>IA</t>
+          <t>Equipos chips</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>8.17</v>
+        <v>322.68</v>
       </c>
       <c r="D27" t="n">
-        <v>38</v>
+        <v>95</v>
       </c>
       <c r="E27" t="n">
-        <v>-2.85</v>
+        <v>16.09</v>
       </c>
       <c r="F27" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="G27" t="n">
-        <v>0.5600000000000001</v>
+        <v>15.11</v>
       </c>
       <c r="H27" t="n">
-        <v>6.84</v>
+        <v>4.68</v>
       </c>
       <c r="I27" t="n">
-        <v>7.95</v>
+        <v>316.64</v>
       </c>
       <c r="J27" t="n">
-        <v>8.31</v>
+        <v>326.46</v>
       </c>
       <c r="K27" t="n">
-        <v>7.33</v>
+        <v>300.01</v>
       </c>
       <c r="L27" t="n">
-        <v>9.57</v>
+        <v>360.46</v>
       </c>
       <c r="M27" t="n">
-        <v>30.88</v>
+        <v>67.58</v>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>MEDIO</t>
-        </is>
-      </c>
-      <c r="O27" t="inlineStr"/>
+          <t>ALTO</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>🔥</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>NO COMPRAR</t>
+          <t>VIGILAR</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>UPST</t>
+          <t>KLAC</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Fintech IA</t>
+          <t>Equipos chips</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>28.56</v>
+        <v>2011.39</v>
       </c>
       <c r="D28" t="n">
-        <v>38</v>
+        <v>95</v>
       </c>
       <c r="E28" t="n">
-        <v>-3.22</v>
+        <v>14.51</v>
       </c>
       <c r="F28" t="n">
-        <v>0.67</v>
+        <v>1.06</v>
       </c>
       <c r="G28" t="n">
-        <v>1.84</v>
+        <v>86.36</v>
       </c>
       <c r="H28" t="n">
-        <v>6.45</v>
+        <v>4.29</v>
       </c>
       <c r="I28" t="n">
-        <v>27.82</v>
+        <v>1976.84</v>
       </c>
       <c r="J28" t="n">
-        <v>29.02</v>
+        <v>2032.98</v>
       </c>
       <c r="K28" t="n">
-        <v>25.8</v>
+        <v>1881.85</v>
       </c>
       <c r="L28" t="n">
-        <v>33.17</v>
+        <v>2227.3</v>
       </c>
       <c r="M28" t="n">
-        <v>34.53</v>
+        <v>67.5</v>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>MEDIO</t>
-        </is>
-      </c>
-      <c r="O28" t="inlineStr"/>
+          <t>ALTO</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>🔥</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>NO COMPRAR</t>
+          <t>VIGILAR</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>PYPL</t>
+          <t>SOXX</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Pagos</t>
+          <t>ETF Chips</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>44.23</v>
+        <v>570.09</v>
       </c>
       <c r="D29" t="n">
-        <v>36</v>
+        <v>95</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.41</v>
+        <v>14.97</v>
       </c>
       <c r="F29" t="n">
-        <v>0.71</v>
+        <v>1.03</v>
       </c>
       <c r="G29" t="n">
-        <v>1.42</v>
+        <v>23</v>
       </c>
       <c r="H29" t="n">
-        <v>3.22</v>
+        <v>4.04</v>
       </c>
       <c r="I29" t="n">
-        <v>43.66</v>
+        <v>560.89</v>
       </c>
       <c r="J29" t="n">
-        <v>44.59</v>
+        <v>575.84</v>
       </c>
       <c r="K29" t="n">
-        <v>42.1</v>
+        <v>535.58</v>
       </c>
       <c r="L29" t="n">
-        <v>47.79</v>
+        <v>627.6</v>
       </c>
       <c r="M29" t="n">
-        <v>11.45</v>
+        <v>70.01000000000001</v>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>BAJO</t>
-        </is>
-      </c>
-      <c r="O29" t="inlineStr"/>
+          <t>ALTO</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>🔥</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>NO COMPRAR</t>
+          <t>VIGILAR</t>
         </is>
       </c>
     </row>
@@ -2142,37 +2146,37 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>308.82</v>
+        <v>308.33</v>
       </c>
       <c r="D30" t="n">
         <v>82</v>
       </c>
       <c r="E30" t="n">
-        <v>2.86</v>
+        <v>3.52</v>
       </c>
       <c r="F30" t="n">
-        <v>0.9</v>
+        <v>0.86</v>
       </c>
       <c r="G30" t="n">
-        <v>5.74</v>
+        <v>5.46</v>
       </c>
       <c r="H30" t="n">
-        <v>1.86</v>
+        <v>1.77</v>
       </c>
       <c r="I30" t="n">
-        <v>306.52</v>
+        <v>306.15</v>
       </c>
       <c r="J30" t="n">
-        <v>310.26</v>
+        <v>309.7</v>
       </c>
       <c r="K30" t="n">
-        <v>300.21</v>
+        <v>300.14</v>
       </c>
       <c r="L30" t="n">
-        <v>323.17</v>
+        <v>321.99</v>
       </c>
       <c r="M30" t="n">
-        <v>91.09999999999999</v>
+        <v>87.70999999999999</v>
       </c>
       <c r="N30" t="inlineStr">
         <is>
@@ -2193,57 +2197,53 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>IONQ</t>
+          <t>INTC</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Computación cuántica</t>
+          <t>Chips</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>63.64</v>
+        <v>123.52</v>
       </c>
       <c r="D31" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E31" t="n">
-        <v>22.5</v>
+        <v>14.19</v>
       </c>
       <c r="F31" t="n">
-        <v>1.54</v>
+        <v>0.64</v>
       </c>
       <c r="G31" t="n">
-        <v>5.71</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="H31" t="n">
-        <v>8.960000000000001</v>
+        <v>7.85</v>
       </c>
       <c r="I31" t="n">
-        <v>61.36</v>
+        <v>119.64</v>
       </c>
       <c r="J31" t="n">
-        <v>65.06999999999999</v>
+        <v>125.95</v>
       </c>
       <c r="K31" t="n">
-        <v>55.08</v>
+        <v>108.97</v>
       </c>
       <c r="L31" t="n">
-        <v>77.90000000000001</v>
+        <v>147.77</v>
       </c>
       <c r="M31" t="n">
-        <v>68.26000000000001</v>
+        <v>61.71</v>
       </c>
       <c r="N31" t="inlineStr">
         <is>
           <t>ALTO</t>
         </is>
       </c>
-      <c r="O31" t="inlineStr">
-        <is>
-          <t>🔥</t>
-        </is>
-      </c>
+      <c r="O31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>VIGILAR</t>
@@ -2253,46 +2253,46 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>SMCI</t>
+          <t>IONQ</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Servidores IA</t>
+          <t>Computación cuántica</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>35.58</v>
+        <v>63.62</v>
       </c>
       <c r="D32" t="n">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="E32" t="n">
-        <v>14.63</v>
+        <v>29.02</v>
       </c>
       <c r="F32" t="n">
-        <v>1.03</v>
+        <v>0.87</v>
       </c>
       <c r="G32" t="n">
-        <v>2.57</v>
+        <v>5.77</v>
       </c>
       <c r="H32" t="n">
-        <v>7.22</v>
+        <v>9.07</v>
       </c>
       <c r="I32" t="n">
-        <v>34.55</v>
+        <v>61.31</v>
       </c>
       <c r="J32" t="n">
-        <v>36.22</v>
+        <v>65.06</v>
       </c>
       <c r="K32" t="n">
-        <v>31.73</v>
+        <v>54.96</v>
       </c>
       <c r="L32" t="n">
-        <v>42</v>
+        <v>78.05</v>
       </c>
       <c r="M32" t="n">
-        <v>67.73</v>
+        <v>66.7</v>
       </c>
       <c r="N32" t="inlineStr">
         <is>
@@ -2309,46 +2309,46 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>RKLB</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Espacial</t>
+          <t>IA / Chips</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>135.76</v>
+        <v>503.89</v>
       </c>
       <c r="D33" t="n">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="E33" t="n">
-        <v>8.81</v>
+        <v>19.69</v>
       </c>
       <c r="F33" t="n">
-        <v>1.18</v>
+        <v>0.89</v>
       </c>
       <c r="G33" t="n">
-        <v>12.41</v>
+        <v>32.52</v>
       </c>
       <c r="H33" t="n">
-        <v>9.140000000000001</v>
+        <v>6.45</v>
       </c>
       <c r="I33" t="n">
-        <v>130.8</v>
+        <v>490.88</v>
       </c>
       <c r="J33" t="n">
-        <v>138.86</v>
+        <v>512.02</v>
       </c>
       <c r="K33" t="n">
-        <v>117.15</v>
+        <v>455.1</v>
       </c>
       <c r="L33" t="n">
-        <v>166.78</v>
+        <v>585.2</v>
       </c>
       <c r="M33" t="n">
-        <v>74.84</v>
+        <v>77.28</v>
       </c>
       <c r="N33" t="inlineStr">
         <is>
@@ -2365,7 +2365,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>INTC</t>
+          <t>ARM</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2374,37 +2374,37 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>119.84</v>
+        <v>321.22</v>
       </c>
       <c r="D34" t="n">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="E34" t="n">
-        <v>10.18</v>
+        <v>49.32</v>
       </c>
       <c r="F34" t="n">
-        <v>0.54</v>
+        <v>0.9</v>
       </c>
       <c r="G34" t="n">
-        <v>10.16</v>
+        <v>21.92</v>
       </c>
       <c r="H34" t="n">
-        <v>8.48</v>
+        <v>6.82</v>
       </c>
       <c r="I34" t="n">
-        <v>115.78</v>
+        <v>312.45</v>
       </c>
       <c r="J34" t="n">
-        <v>122.38</v>
+        <v>326.7</v>
       </c>
       <c r="K34" t="n">
-        <v>104.6</v>
+        <v>288.34</v>
       </c>
       <c r="L34" t="n">
-        <v>145.24</v>
+        <v>376.03</v>
       </c>
       <c r="M34" t="n">
-        <v>66.19</v>
+        <v>76.78</v>
       </c>
       <c r="N34" t="inlineStr">
         <is>
@@ -2421,46 +2421,46 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>QCOM</t>
+          <t>SMCI</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Chips</t>
+          <t>Servidores IA</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>238.16</v>
+        <v>37.1</v>
       </c>
       <c r="D35" t="n">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="E35" t="n">
-        <v>18.2</v>
+        <v>20.26</v>
       </c>
       <c r="F35" t="n">
-        <v>0.95</v>
+        <v>1.08</v>
       </c>
       <c r="G35" t="n">
-        <v>19.91</v>
+        <v>2.68</v>
       </c>
       <c r="H35" t="n">
-        <v>8.359999999999999</v>
+        <v>7.23</v>
       </c>
       <c r="I35" t="n">
-        <v>230.2</v>
+        <v>36.03</v>
       </c>
       <c r="J35" t="n">
-        <v>243.14</v>
+        <v>37.77</v>
       </c>
       <c r="K35" t="n">
-        <v>208.29</v>
+        <v>33.08</v>
       </c>
       <c r="L35" t="n">
-        <v>287.94</v>
+        <v>43.81</v>
       </c>
       <c r="M35" t="n">
-        <v>70.95999999999999</v>
+        <v>70.13</v>
       </c>
       <c r="N35" t="inlineStr">
         <is>
@@ -2477,7 +2477,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>ARM</t>
+          <t>QCOM</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2486,37 +2486,37 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>306.51</v>
+        <v>248.82</v>
       </c>
       <c r="D36" t="n">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="E36" t="n">
-        <v>46.54</v>
+        <v>22.19</v>
       </c>
       <c r="F36" t="n">
-        <v>1.16</v>
+        <v>0.97</v>
       </c>
       <c r="G36" t="n">
-        <v>20.93</v>
+        <v>19.89</v>
       </c>
       <c r="H36" t="n">
-        <v>6.83</v>
+        <v>8</v>
       </c>
       <c r="I36" t="n">
-        <v>298.14</v>
+        <v>240.86</v>
       </c>
       <c r="J36" t="n">
-        <v>311.74</v>
+        <v>253.79</v>
       </c>
       <c r="K36" t="n">
-        <v>275.11</v>
+        <v>218.98</v>
       </c>
       <c r="L36" t="n">
-        <v>358.84</v>
+        <v>298.56</v>
       </c>
       <c r="M36" t="n">
-        <v>75.72</v>
+        <v>69.59</v>
       </c>
       <c r="N36" t="inlineStr">
         <is>
@@ -2533,46 +2533,46 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>RKLB</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>IA / Chips</t>
+          <t>Espacial</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>467.51</v>
+        <v>143.2</v>
       </c>
       <c r="D37" t="n">
-        <v>54</v>
+        <v>68</v>
       </c>
       <c r="E37" t="n">
-        <v>10.24</v>
+        <v>9.18</v>
       </c>
       <c r="F37" t="n">
-        <v>0.82</v>
+        <v>1.11</v>
       </c>
       <c r="G37" t="n">
-        <v>30.99</v>
+        <v>12.68</v>
       </c>
       <c r="H37" t="n">
-        <v>6.63</v>
+        <v>8.85</v>
       </c>
       <c r="I37" t="n">
-        <v>455.11</v>
+        <v>138.13</v>
       </c>
       <c r="J37" t="n">
-        <v>475.26</v>
+        <v>146.37</v>
       </c>
       <c r="K37" t="n">
-        <v>421.02</v>
+        <v>124.18</v>
       </c>
       <c r="L37" t="n">
-        <v>545</v>
+        <v>174.9</v>
       </c>
       <c r="M37" t="n">
-        <v>75.22</v>
+        <v>77.42</v>
       </c>
       <c r="N37" t="inlineStr">
         <is>
@@ -2582,7 +2582,7 @@
       <c r="O37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>NO COMPRAR</t>
+          <t>VIGILAR</t>
         </is>
       </c>
     </row>

--- a/analisis_acciones.xlsx
+++ b/analisis_acciones.xlsx
@@ -501,50 +501,50 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AI</t>
+          <t>META</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>IA</t>
+          <t>Tecnología</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>9.59</v>
+        <v>635.26</v>
       </c>
       <c r="D2" t="n">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="E2" t="n">
-        <v>9.6</v>
+        <v>5.42</v>
       </c>
       <c r="F2" t="n">
-        <v>1.43</v>
+        <v>1.35</v>
       </c>
       <c r="G2" t="n">
-        <v>0.51</v>
+        <v>13.3</v>
       </c>
       <c r="H2" t="n">
-        <v>5.28</v>
+        <v>2.09</v>
       </c>
       <c r="I2" t="n">
-        <v>9.390000000000001</v>
+        <v>629.9400000000001</v>
       </c>
       <c r="J2" t="n">
-        <v>9.720000000000001</v>
+        <v>638.58</v>
       </c>
       <c r="K2" t="n">
-        <v>8.83</v>
+        <v>615.3099999999999</v>
       </c>
       <c r="L2" t="n">
-        <v>10.86</v>
+        <v>668.5</v>
       </c>
       <c r="M2" t="n">
-        <v>52.57</v>
+        <v>62.44</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>MEDIO</t>
+          <t>BAJO</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -561,7 +561,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ASML</t>
+          <t>TSM</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -570,37 +570,37 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1632.03</v>
+        <v>422.73</v>
       </c>
       <c r="D3" t="n">
         <v>95</v>
       </c>
       <c r="E3" t="n">
-        <v>10.84</v>
+        <v>7.67</v>
       </c>
       <c r="F3" t="n">
-        <v>0.88</v>
+        <v>1.05</v>
       </c>
       <c r="G3" t="n">
-        <v>70.42</v>
+        <v>14.65</v>
       </c>
       <c r="H3" t="n">
-        <v>4.31</v>
+        <v>3.47</v>
       </c>
       <c r="I3" t="n">
-        <v>1603.86</v>
+        <v>416.87</v>
       </c>
       <c r="J3" t="n">
-        <v>1649.63</v>
+        <v>426.39</v>
       </c>
       <c r="K3" t="n">
-        <v>1526.41</v>
+        <v>400.76</v>
       </c>
       <c r="L3" t="n">
-        <v>1808.07</v>
+        <v>459.35</v>
       </c>
       <c r="M3" t="n">
-        <v>64.79000000000001</v>
+        <v>51.57</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -621,46 +621,46 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AMAT</t>
+          <t>ASML</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Equipos chips</t>
+          <t>Chips</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>454.89</v>
+        <v>1597.87</v>
       </c>
       <c r="D4" t="n">
         <v>95</v>
       </c>
       <c r="E4" t="n">
-        <v>10.13</v>
+        <v>9.49</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.77</v>
       </c>
       <c r="G4" t="n">
-        <v>20.13</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="H4" t="n">
-        <v>4.43</v>
+        <v>4.2</v>
       </c>
       <c r="I4" t="n">
-        <v>446.84</v>
+        <v>1571.03</v>
       </c>
       <c r="J4" t="n">
-        <v>459.92</v>
+        <v>1614.64</v>
       </c>
       <c r="K4" t="n">
-        <v>424.7</v>
+        <v>1497.23</v>
       </c>
       <c r="L4" t="n">
-        <v>505.21</v>
+        <v>1765.61</v>
       </c>
       <c r="M4" t="n">
-        <v>62.92</v>
+        <v>54.65</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -681,50 +681,50 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>AMAT</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Chips</t>
+          <t>Equipos chips</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>412.32</v>
+        <v>448.25</v>
       </c>
       <c r="D5" t="n">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="E5" t="n">
-        <v>4.13</v>
+        <v>10.3</v>
       </c>
       <c r="F5" t="n">
-        <v>0.77</v>
+        <v>0.66</v>
       </c>
       <c r="G5" t="n">
-        <v>15.15</v>
+        <v>20.08</v>
       </c>
       <c r="H5" t="n">
-        <v>3.67</v>
+        <v>4.48</v>
       </c>
       <c r="I5" t="n">
-        <v>406.26</v>
+        <v>440.22</v>
       </c>
       <c r="J5" t="n">
-        <v>416.11</v>
+        <v>453.27</v>
       </c>
       <c r="K5" t="n">
-        <v>389.59</v>
+        <v>418.13</v>
       </c>
       <c r="L5" t="n">
-        <v>450.2</v>
+        <v>498.45</v>
       </c>
       <c r="M5" t="n">
-        <v>57.6</v>
+        <v>56.25</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>BAJO</t>
+          <t>MEDIO</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -741,50 +741,50 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>QQQ</t>
+          <t>SPY</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>ETF Nasdaq</t>
+          <t>ETF Mercado</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>730.28</v>
+        <v>750.46</v>
       </c>
       <c r="D6" t="n">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="E6" t="n">
-        <v>3.46</v>
+        <v>2.28</v>
       </c>
       <c r="F6" t="n">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="G6" t="n">
-        <v>11.71</v>
+        <v>6.97</v>
       </c>
       <c r="H6" t="n">
-        <v>1.6</v>
+        <v>0.93</v>
       </c>
       <c r="I6" t="n">
-        <v>725.6</v>
+        <v>747.67</v>
       </c>
       <c r="J6" t="n">
-        <v>733.21</v>
+        <v>752.2</v>
       </c>
       <c r="K6" t="n">
-        <v>712.71</v>
+        <v>740.01</v>
       </c>
       <c r="L6" t="n">
-        <v>759.5599999999999</v>
+        <v>767.88</v>
       </c>
       <c r="M6" t="n">
-        <v>74.59</v>
+        <v>65.84</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>MEDIO</t>
+          <t>BAJO</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -801,46 +801,46 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>TSLA</t>
+          <t>SLB</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Autos / Tech</t>
+          <t>Energía</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>433.59</v>
+        <v>56.5</v>
       </c>
       <c r="D7" t="n">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="E7" t="n">
-        <v>5.76</v>
+        <v>-0.48</v>
       </c>
       <c r="F7" t="n">
-        <v>0.83</v>
+        <v>1.38</v>
       </c>
       <c r="G7" t="n">
-        <v>17.92</v>
+        <v>1.5</v>
       </c>
       <c r="H7" t="n">
-        <v>4.13</v>
+        <v>2.65</v>
       </c>
       <c r="I7" t="n">
-        <v>426.42</v>
+        <v>55.9</v>
       </c>
       <c r="J7" t="n">
-        <v>438.07</v>
+        <v>56.87</v>
       </c>
       <c r="K7" t="n">
-        <v>406.71</v>
+        <v>54.25</v>
       </c>
       <c r="L7" t="n">
-        <v>478.39</v>
+        <v>60.25</v>
       </c>
       <c r="M7" t="n">
-        <v>64.78</v>
+        <v>56.26</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -861,55 +861,55 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SLB</t>
+          <t>QQQ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Energía</t>
+          <t>ETF Nasdaq</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>57.98</v>
+        <v>729.45</v>
       </c>
       <c r="D8" t="n">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="E8" t="n">
-        <v>1.45</v>
+        <v>3.98</v>
       </c>
       <c r="F8" t="n">
-        <v>1.13</v>
+        <v>0.85</v>
       </c>
       <c r="G8" t="n">
-        <v>1.47</v>
+        <v>11.25</v>
       </c>
       <c r="H8" t="n">
-        <v>2.54</v>
+        <v>1.54</v>
       </c>
       <c r="I8" t="n">
-        <v>57.39</v>
+        <v>724.95</v>
       </c>
       <c r="J8" t="n">
-        <v>58.35</v>
+        <v>732.26</v>
       </c>
       <c r="K8" t="n">
-        <v>55.77</v>
+        <v>712.5700000000001</v>
       </c>
       <c r="L8" t="n">
-        <v>61.66</v>
+        <v>757.58</v>
       </c>
       <c r="M8" t="n">
-        <v>59.84</v>
+        <v>69.67</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>BAJO</t>
+          <t>MEDIO</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -921,46 +921,46 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SPY</t>
+          <t>TSLA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ETF Mercado</t>
+          <t>Autos / Tech</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>750.59</v>
+        <v>440.36</v>
       </c>
       <c r="D9" t="n">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="E9" t="n">
-        <v>1.62</v>
+        <v>8.970000000000001</v>
       </c>
       <c r="F9" t="n">
-        <v>0.75</v>
+        <v>0.83</v>
       </c>
       <c r="G9" t="n">
-        <v>7.52</v>
+        <v>17.52</v>
       </c>
       <c r="H9" t="n">
-        <v>1</v>
+        <v>3.98</v>
       </c>
       <c r="I9" t="n">
-        <v>747.58</v>
+        <v>433.35</v>
       </c>
       <c r="J9" t="n">
-        <v>752.47</v>
+        <v>444.74</v>
       </c>
       <c r="K9" t="n">
-        <v>739.3200000000001</v>
+        <v>414.08</v>
       </c>
       <c r="L9" t="n">
-        <v>769.38</v>
+        <v>484.15</v>
       </c>
       <c r="M9" t="n">
-        <v>71.48</v>
+        <v>64.16</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -981,7 +981,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>NVDA</t>
+          <t>AVGO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -990,37 +990,37 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>214.86</v>
+        <v>421.86</v>
       </c>
       <c r="D10" t="n">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.36</v>
+        <v>2.62</v>
       </c>
       <c r="F10" t="n">
-        <v>1.12</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="G10" t="n">
-        <v>8.43</v>
+        <v>16.51</v>
       </c>
       <c r="H10" t="n">
-        <v>3.92</v>
+        <v>3.91</v>
       </c>
       <c r="I10" t="n">
-        <v>211.49</v>
+        <v>415.25</v>
       </c>
       <c r="J10" t="n">
-        <v>216.97</v>
+        <v>425.99</v>
       </c>
       <c r="K10" t="n">
-        <v>202.22</v>
+        <v>397.09</v>
       </c>
       <c r="L10" t="n">
-        <v>235.93</v>
+        <v>463.14</v>
       </c>
       <c r="M10" t="n">
-        <v>63.94</v>
+        <v>48.42</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1041,7 +1041,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>GOOGL</t>
+          <t>AMZN</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1050,37 +1050,37 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>388.88</v>
+        <v>271.85</v>
       </c>
       <c r="D11" t="n">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.03</v>
+        <v>4.82</v>
       </c>
       <c r="F11" t="n">
-        <v>0.89</v>
+        <v>0.91</v>
       </c>
       <c r="G11" t="n">
-        <v>9.68</v>
+        <v>6.28</v>
       </c>
       <c r="H11" t="n">
-        <v>2.49</v>
+        <v>2.31</v>
       </c>
       <c r="I11" t="n">
-        <v>385.01</v>
+        <v>269.34</v>
       </c>
       <c r="J11" t="n">
-        <v>391.3</v>
+        <v>273.42</v>
       </c>
       <c r="K11" t="n">
-        <v>374.36</v>
+        <v>262.43</v>
       </c>
       <c r="L11" t="n">
-        <v>413.09</v>
+        <v>287.56</v>
       </c>
       <c r="M11" t="n">
-        <v>50.32</v>
+        <v>46.7</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
@@ -1089,7 +1089,7 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1101,50 +1101,50 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>AVGO</t>
+          <t>UPST</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>IA / Chips</t>
+          <t>Fintech IA</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>422.01</v>
+        <v>30.72</v>
       </c>
       <c r="D12" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="E12" t="n">
-        <v>0.31</v>
+        <v>9.4</v>
       </c>
       <c r="F12" t="n">
-        <v>1.09</v>
+        <v>0.78</v>
       </c>
       <c r="G12" t="n">
-        <v>16.77</v>
+        <v>1.79</v>
       </c>
       <c r="H12" t="n">
-        <v>3.97</v>
+        <v>5.82</v>
       </c>
       <c r="I12" t="n">
-        <v>415.3</v>
+        <v>30.01</v>
       </c>
       <c r="J12" t="n">
-        <v>426.2</v>
+        <v>31.17</v>
       </c>
       <c r="K12" t="n">
-        <v>396.85</v>
+        <v>28.04</v>
       </c>
       <c r="L12" t="n">
-        <v>463.94</v>
+        <v>35.19</v>
       </c>
       <c r="M12" t="n">
-        <v>47.68</v>
+        <v>59.94</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>BAJO</t>
+          <t>MEDIO</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -1161,173 +1161,169 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>CVX</t>
+          <t>NVDA</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Energía</t>
+          <t>IA / Chips</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>184.71</v>
+        <v>212.6</v>
       </c>
       <c r="D13" t="n">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="E13" t="n">
-        <v>-4.96</v>
+        <v>-3.63</v>
       </c>
       <c r="F13" t="n">
-        <v>1.27</v>
+        <v>1</v>
       </c>
       <c r="G13" t="n">
-        <v>4.73</v>
+        <v>8.02</v>
       </c>
       <c r="H13" t="n">
-        <v>2.56</v>
+        <v>3.77</v>
       </c>
       <c r="I13" t="n">
-        <v>182.82</v>
+        <v>209.39</v>
       </c>
       <c r="J13" t="n">
-        <v>185.89</v>
+        <v>214.61</v>
       </c>
       <c r="K13" t="n">
-        <v>177.62</v>
+        <v>200.57</v>
       </c>
       <c r="L13" t="n">
-        <v>196.53</v>
+        <v>232.65</v>
       </c>
       <c r="M13" t="n">
-        <v>42.57</v>
+        <v>54.2</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
           <t>BAJO</t>
         </is>
       </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>🔥</t>
-        </is>
-      </c>
+      <c r="O13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>VIGILAR</t>
+          <t>POSIBLE COMPRA</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>UPST</t>
+          <t>OXY</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Fintech IA</t>
+          <t>Energía</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>30.62</v>
+        <v>56.89</v>
       </c>
       <c r="D14" t="n">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="E14" t="n">
-        <v>9.59</v>
+        <v>-6.28</v>
       </c>
       <c r="F14" t="n">
-        <v>1.15</v>
+        <v>0.9</v>
       </c>
       <c r="G14" t="n">
-        <v>1.94</v>
+        <v>1.82</v>
       </c>
       <c r="H14" t="n">
-        <v>6.32</v>
+        <v>3.2</v>
       </c>
       <c r="I14" t="n">
-        <v>29.85</v>
+        <v>56.16</v>
       </c>
       <c r="J14" t="n">
-        <v>31.1</v>
+        <v>57.35</v>
       </c>
       <c r="K14" t="n">
-        <v>27.72</v>
+        <v>54.16</v>
       </c>
       <c r="L14" t="n">
-        <v>35.46</v>
+        <v>61.45</v>
       </c>
       <c r="M14" t="n">
-        <v>47.81</v>
+        <v>56.44</v>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>MEDIO</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>🔥</t>
-        </is>
-      </c>
+          <t>BAJO</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>VIGILAR</t>
+          <t>POSIBLE COMPRA</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>SOFI</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Tecnología</t>
+          <t>Fintech</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>416.03</v>
+        <v>16.17</v>
       </c>
       <c r="D15" t="n">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="E15" t="n">
-        <v>-1.56</v>
+        <v>6.17</v>
       </c>
       <c r="F15" t="n">
-        <v>0.86</v>
+        <v>0.93</v>
       </c>
       <c r="G15" t="n">
-        <v>10.77</v>
+        <v>0.73</v>
       </c>
       <c r="H15" t="n">
-        <v>2.59</v>
+        <v>4.49</v>
       </c>
       <c r="I15" t="n">
-        <v>411.72</v>
+        <v>15.88</v>
       </c>
       <c r="J15" t="n">
-        <v>418.72</v>
+        <v>16.35</v>
       </c>
       <c r="K15" t="n">
-        <v>399.88</v>
+        <v>15.08</v>
       </c>
       <c r="L15" t="n">
-        <v>442.94</v>
+        <v>17.99</v>
       </c>
       <c r="M15" t="n">
-        <v>54.85</v>
+        <v>48.64</v>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>BAJO</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr"/>
+          <t>MEDIO</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>🔥</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>VIGILAR</t>
@@ -1337,53 +1333,57 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>PLTR</t>
+          <t>AI</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>IA / Software</t>
+          <t>IA</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>136.6</v>
+        <v>9.59</v>
       </c>
       <c r="D16" t="n">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="E16" t="n">
-        <v>1.08</v>
+        <v>8.609999999999999</v>
       </c>
       <c r="F16" t="n">
-        <v>0.76</v>
+        <v>0.86</v>
       </c>
       <c r="G16" t="n">
-        <v>4.92</v>
+        <v>0.49</v>
       </c>
       <c r="H16" t="n">
-        <v>3.6</v>
+        <v>5.09</v>
       </c>
       <c r="I16" t="n">
-        <v>134.63</v>
+        <v>9.390000000000001</v>
       </c>
       <c r="J16" t="n">
-        <v>137.83</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="K16" t="n">
-        <v>129.22</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="L16" t="n">
-        <v>148.91</v>
+        <v>10.81</v>
       </c>
       <c r="M16" t="n">
-        <v>51.56</v>
+        <v>49.85</v>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>BAJO</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr"/>
+          <t>MEDIO</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>🔥</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>VIGILAR</t>
@@ -1393,63 +1393,67 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>AMZN</t>
+          <t>HOOD</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Tecnología</t>
+          <t>Trading</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>265.29</v>
+        <v>76.23</v>
       </c>
       <c r="D17" t="n">
-        <v>72</v>
+        <v>52</v>
       </c>
       <c r="E17" t="n">
-        <v>0.16</v>
+        <v>2.79</v>
       </c>
       <c r="F17" t="n">
-        <v>0.87</v>
+        <v>1</v>
       </c>
       <c r="G17" t="n">
-        <v>6.17</v>
+        <v>3.86</v>
       </c>
       <c r="H17" t="n">
-        <v>2.33</v>
+        <v>5.06</v>
       </c>
       <c r="I17" t="n">
-        <v>262.82</v>
+        <v>74.69</v>
       </c>
       <c r="J17" t="n">
-        <v>266.83</v>
+        <v>77.19</v>
       </c>
       <c r="K17" t="n">
-        <v>256.03</v>
+        <v>70.44</v>
       </c>
       <c r="L17" t="n">
-        <v>280.72</v>
+        <v>85.88</v>
       </c>
       <c r="M17" t="n">
-        <v>40.27</v>
+        <v>45.04</v>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>BAJO</t>
-        </is>
-      </c>
-      <c r="O17" t="inlineStr"/>
+          <t>MEDIO</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>🔥</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>VIGILAR</t>
+          <t>NO COMPRAR</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>META</t>
+          <t>GOOGL</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1458,37 +1462,37 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>612.34</v>
+        <v>388.83</v>
       </c>
       <c r="D18" t="n">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="E18" t="n">
-        <v>0.18</v>
+        <v>0.3</v>
       </c>
       <c r="F18" t="n">
-        <v>0.68</v>
+        <v>0.76</v>
       </c>
       <c r="G18" t="n">
-        <v>12.75</v>
+        <v>9.44</v>
       </c>
       <c r="H18" t="n">
-        <v>2.08</v>
+        <v>2.43</v>
       </c>
       <c r="I18" t="n">
-        <v>607.24</v>
+        <v>385.06</v>
       </c>
       <c r="J18" t="n">
-        <v>615.53</v>
+        <v>391.19</v>
       </c>
       <c r="K18" t="n">
-        <v>593.21</v>
+        <v>374.68</v>
       </c>
       <c r="L18" t="n">
-        <v>644.22</v>
+        <v>412.42</v>
       </c>
       <c r="M18" t="n">
-        <v>54.93</v>
+        <v>42.33</v>
       </c>
       <c r="N18" t="inlineStr">
         <is>
@@ -1514,37 +1518,37 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>149.81</v>
+        <v>147.9</v>
       </c>
       <c r="D19" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="E19" t="n">
-        <v>-6.65</v>
+        <v>-9.01</v>
       </c>
       <c r="F19" t="n">
-        <v>0.59</v>
+        <v>0.93</v>
       </c>
       <c r="G19" t="n">
-        <v>4.54</v>
+        <v>4.28</v>
       </c>
       <c r="H19" t="n">
-        <v>3.03</v>
+        <v>2.89</v>
       </c>
       <c r="I19" t="n">
-        <v>147.99</v>
+        <v>146.19</v>
       </c>
       <c r="J19" t="n">
-        <v>150.95</v>
+        <v>148.97</v>
       </c>
       <c r="K19" t="n">
-        <v>142.99</v>
+        <v>141.48</v>
       </c>
       <c r="L19" t="n">
-        <v>161.17</v>
+        <v>158.6</v>
       </c>
       <c r="M19" t="n">
-        <v>45.2</v>
+        <v>50.28</v>
       </c>
       <c r="N19" t="inlineStr">
         <is>
@@ -1561,46 +1565,46 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>OXY</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Energía</t>
+          <t>Tecnología</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>57.46</v>
+        <v>412.67</v>
       </c>
       <c r="D20" t="n">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="E20" t="n">
-        <v>-3.75</v>
+        <v>-0.92</v>
       </c>
       <c r="F20" t="n">
-        <v>0.73</v>
+        <v>0.8</v>
       </c>
       <c r="G20" t="n">
-        <v>1.99</v>
+        <v>10.28</v>
       </c>
       <c r="H20" t="n">
-        <v>3.47</v>
+        <v>2.49</v>
       </c>
       <c r="I20" t="n">
-        <v>56.66</v>
+        <v>408.56</v>
       </c>
       <c r="J20" t="n">
-        <v>57.96</v>
+        <v>415.24</v>
       </c>
       <c r="K20" t="n">
-        <v>54.47</v>
+        <v>397.25</v>
       </c>
       <c r="L20" t="n">
-        <v>62.44</v>
+        <v>438.36</v>
       </c>
       <c r="M20" t="n">
-        <v>44.6</v>
+        <v>49.66</v>
       </c>
       <c r="N20" t="inlineStr">
         <is>
@@ -1610,53 +1614,53 @@
       <c r="O20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>VIGILAR</t>
+          <t>NO COMPRAR</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>SOFI</t>
+          <t>PLTR</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Fintech</t>
+          <t>IA / Software</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>15.98</v>
+        <v>132.51</v>
       </c>
       <c r="D21" t="n">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="E21" t="n">
-        <v>1.72</v>
+        <v>-2.03</v>
       </c>
       <c r="F21" t="n">
-        <v>1.13</v>
+        <v>0.77</v>
       </c>
       <c r="G21" t="n">
-        <v>0.71</v>
+        <v>4.94</v>
       </c>
       <c r="H21" t="n">
-        <v>4.46</v>
+        <v>3.73</v>
       </c>
       <c r="I21" t="n">
-        <v>15.69</v>
+        <v>130.53</v>
       </c>
       <c r="J21" t="n">
-        <v>16.16</v>
+        <v>133.74</v>
       </c>
       <c r="K21" t="n">
-        <v>14.91</v>
+        <v>125.1</v>
       </c>
       <c r="L21" t="n">
-        <v>17.76</v>
+        <v>144.86</v>
       </c>
       <c r="M21" t="n">
-        <v>49.59</v>
+        <v>47.34</v>
       </c>
       <c r="N21" t="inlineStr">
         <is>
@@ -1666,57 +1670,57 @@
       <c r="O21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>VIGILAR</t>
+          <t>NO COMPRAR</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>COIN</t>
+          <t>CVX</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Cripto / Trading</t>
+          <t>Energía</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>180.01</v>
+        <v>182.4</v>
       </c>
       <c r="D22" t="n">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="E22" t="n">
-        <v>-4.98</v>
+        <v>-7.53</v>
       </c>
       <c r="F22" t="n">
-        <v>0.79</v>
+        <v>0.89</v>
       </c>
       <c r="G22" t="n">
-        <v>13.42</v>
+        <v>4.34</v>
       </c>
       <c r="H22" t="n">
-        <v>7.46</v>
+        <v>2.38</v>
       </c>
       <c r="I22" t="n">
-        <v>174.64</v>
+        <v>180.66</v>
       </c>
       <c r="J22" t="n">
-        <v>183.37</v>
+        <v>183.49</v>
       </c>
       <c r="K22" t="n">
-        <v>159.87</v>
+        <v>175.88</v>
       </c>
       <c r="L22" t="n">
-        <v>213.57</v>
+        <v>193.26</v>
       </c>
       <c r="M22" t="n">
-        <v>40.99</v>
+        <v>48.52</v>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>MEDIO</t>
+          <t>BAJO</t>
         </is>
       </c>
       <c r="O22" t="inlineStr"/>
@@ -1729,46 +1733,46 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>HOOD</t>
+          <t>COIN</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Trading</t>
+          <t>Cripto / Trading</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>74.09</v>
+        <v>173.78</v>
       </c>
       <c r="D23" t="n">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.97</v>
+        <v>-10.17</v>
       </c>
       <c r="F23" t="n">
-        <v>0.79</v>
+        <v>0.83</v>
       </c>
       <c r="G23" t="n">
-        <v>3.87</v>
+        <v>13.5</v>
       </c>
       <c r="H23" t="n">
-        <v>5.22</v>
+        <v>7.77</v>
       </c>
       <c r="I23" t="n">
-        <v>72.54000000000001</v>
+        <v>168.38</v>
       </c>
       <c r="J23" t="n">
-        <v>75.06</v>
+        <v>177.15</v>
       </c>
       <c r="K23" t="n">
-        <v>68.29000000000001</v>
+        <v>153.53</v>
       </c>
       <c r="L23" t="n">
-        <v>83.75</v>
+        <v>207.53</v>
       </c>
       <c r="M23" t="n">
-        <v>44.81</v>
+        <v>38.42</v>
       </c>
       <c r="N23" t="inlineStr">
         <is>
@@ -1794,37 +1798,37 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>8.130000000000001</v>
+        <v>8.08</v>
       </c>
       <c r="D24" t="n">
         <v>38</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.63</v>
+        <v>-4.38</v>
       </c>
       <c r="F24" t="n">
-        <v>0.74</v>
+        <v>0.57</v>
       </c>
       <c r="G24" t="n">
-        <v>0.53</v>
+        <v>0.52</v>
       </c>
       <c r="H24" t="n">
-        <v>6.56</v>
+        <v>6.48</v>
       </c>
       <c r="I24" t="n">
-        <v>7.92</v>
+        <v>7.87</v>
       </c>
       <c r="J24" t="n">
-        <v>8.26</v>
+        <v>8.210000000000001</v>
       </c>
       <c r="K24" t="n">
-        <v>7.33</v>
+        <v>7.3</v>
       </c>
       <c r="L24" t="n">
-        <v>9.460000000000001</v>
+        <v>9.390000000000001</v>
       </c>
       <c r="M24" t="n">
-        <v>33.76</v>
+        <v>27.99</v>
       </c>
       <c r="N24" t="inlineStr">
         <is>
@@ -1850,37 +1854,37 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>44.16</v>
+        <v>43.76</v>
       </c>
       <c r="D25" t="n">
         <v>36</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.51</v>
+        <v>-0.16</v>
       </c>
       <c r="F25" t="n">
-        <v>0.78</v>
+        <v>0.9</v>
       </c>
       <c r="G25" t="n">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="H25" t="n">
-        <v>2.36</v>
+        <v>2.29</v>
       </c>
       <c r="I25" t="n">
-        <v>43.74</v>
+        <v>43.36</v>
       </c>
       <c r="J25" t="n">
-        <v>44.42</v>
+        <v>44.01</v>
       </c>
       <c r="K25" t="n">
-        <v>42.59</v>
+        <v>42.26</v>
       </c>
       <c r="L25" t="n">
-        <v>46.77</v>
+        <v>46.26</v>
       </c>
       <c r="M25" t="n">
-        <v>22</v>
+        <v>21.08</v>
       </c>
       <c r="N25" t="inlineStr">
         <is>
@@ -1897,46 +1901,46 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>MU</t>
+          <t>SOXX</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Memoria / Chips</t>
+          <t>ETF Chips</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>895.88</v>
+        <v>563.98</v>
       </c>
       <c r="D26" t="n">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="E26" t="n">
-        <v>31.45</v>
+        <v>13.54</v>
       </c>
       <c r="F26" t="n">
-        <v>1.41</v>
+        <v>1.37</v>
       </c>
       <c r="G26" t="n">
-        <v>66.2</v>
+        <v>23.6</v>
       </c>
       <c r="H26" t="n">
-        <v>7.39</v>
+        <v>4.19</v>
       </c>
       <c r="I26" t="n">
-        <v>869.4</v>
+        <v>554.54</v>
       </c>
       <c r="J26" t="n">
-        <v>912.4299999999999</v>
+        <v>569.88</v>
       </c>
       <c r="K26" t="n">
-        <v>796.58</v>
+        <v>528.5700000000001</v>
       </c>
       <c r="L26" t="n">
-        <v>1061.38</v>
+        <v>622.99</v>
       </c>
       <c r="M26" t="n">
-        <v>70.64</v>
+        <v>64.26000000000001</v>
       </c>
       <c r="N26" t="inlineStr">
         <is>
@@ -1957,46 +1961,46 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>LRCX</t>
+          <t>MU</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Equipos chips</t>
+          <t>Memoria / Chips</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>322.68</v>
+        <v>928.41</v>
       </c>
       <c r="D27" t="n">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="E27" t="n">
-        <v>16.09</v>
+        <v>32.87</v>
       </c>
       <c r="F27" t="n">
-        <v>1.04</v>
+        <v>1.32</v>
       </c>
       <c r="G27" t="n">
-        <v>15.11</v>
+        <v>68.2</v>
       </c>
       <c r="H27" t="n">
-        <v>4.68</v>
+        <v>7.35</v>
       </c>
       <c r="I27" t="n">
-        <v>316.64</v>
+        <v>901.13</v>
       </c>
       <c r="J27" t="n">
-        <v>326.46</v>
+        <v>945.46</v>
       </c>
       <c r="K27" t="n">
-        <v>300.01</v>
+        <v>826.12</v>
       </c>
       <c r="L27" t="n">
-        <v>360.46</v>
+        <v>1098.9</v>
       </c>
       <c r="M27" t="n">
-        <v>67.58</v>
+        <v>70.92</v>
       </c>
       <c r="N27" t="inlineStr">
         <is>
@@ -2005,7 +2009,7 @@
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -2017,7 +2021,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>KLAC</t>
+          <t>LRCX</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2026,37 +2030,37 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>2011.39</v>
+        <v>318.93</v>
       </c>
       <c r="D28" t="n">
         <v>95</v>
       </c>
       <c r="E28" t="n">
-        <v>14.51</v>
+        <v>16.66</v>
       </c>
       <c r="F28" t="n">
-        <v>1.06</v>
+        <v>0.96</v>
       </c>
       <c r="G28" t="n">
-        <v>86.36</v>
+        <v>14.9</v>
       </c>
       <c r="H28" t="n">
-        <v>4.29</v>
+        <v>4.67</v>
       </c>
       <c r="I28" t="n">
-        <v>1976.84</v>
+        <v>312.97</v>
       </c>
       <c r="J28" t="n">
-        <v>2032.98</v>
+        <v>322.65</v>
       </c>
       <c r="K28" t="n">
-        <v>1881.85</v>
+        <v>296.59</v>
       </c>
       <c r="L28" t="n">
-        <v>2227.3</v>
+        <v>356.17</v>
       </c>
       <c r="M28" t="n">
-        <v>67.5</v>
+        <v>59.4</v>
       </c>
       <c r="N28" t="inlineStr">
         <is>
@@ -2077,46 +2081,46 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>SOXX</t>
+          <t>KLAC</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>ETF Chips</t>
+          <t>Equipos chips</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>570.09</v>
+        <v>1957.19</v>
       </c>
       <c r="D29" t="n">
         <v>95</v>
       </c>
       <c r="E29" t="n">
-        <v>14.97</v>
+        <v>12.44</v>
       </c>
       <c r="F29" t="n">
-        <v>1.03</v>
+        <v>0.9</v>
       </c>
       <c r="G29" t="n">
-        <v>23</v>
+        <v>88.03</v>
       </c>
       <c r="H29" t="n">
-        <v>4.04</v>
+        <v>4.5</v>
       </c>
       <c r="I29" t="n">
-        <v>560.89</v>
+        <v>1921.98</v>
       </c>
       <c r="J29" t="n">
-        <v>575.84</v>
+        <v>1979.2</v>
       </c>
       <c r="K29" t="n">
-        <v>535.58</v>
+        <v>1825.15</v>
       </c>
       <c r="L29" t="n">
-        <v>627.6</v>
+        <v>2177.26</v>
       </c>
       <c r="M29" t="n">
-        <v>70.01000000000001</v>
+        <v>59.26</v>
       </c>
       <c r="N29" t="inlineStr">
         <is>
@@ -2137,46 +2141,46 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Tecnología</t>
+          <t>IA / Chips</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>308.33</v>
+        <v>495.54</v>
       </c>
       <c r="D30" t="n">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="E30" t="n">
-        <v>3.52</v>
+        <v>19.68</v>
       </c>
       <c r="F30" t="n">
-        <v>0.86</v>
+        <v>0.66</v>
       </c>
       <c r="G30" t="n">
-        <v>5.46</v>
+        <v>28.82</v>
       </c>
       <c r="H30" t="n">
-        <v>1.77</v>
+        <v>5.82</v>
       </c>
       <c r="I30" t="n">
-        <v>306.15</v>
+        <v>484.01</v>
       </c>
       <c r="J30" t="n">
-        <v>309.7</v>
+        <v>502.75</v>
       </c>
       <c r="K30" t="n">
-        <v>300.14</v>
+        <v>452.3</v>
       </c>
       <c r="L30" t="n">
-        <v>321.99</v>
+        <v>567.6</v>
       </c>
       <c r="M30" t="n">
-        <v>87.70999999999999</v>
+        <v>67.28</v>
       </c>
       <c r="N30" t="inlineStr">
         <is>
@@ -2197,7 +2201,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>INTC</t>
+          <t>ARM</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2206,44 +2210,48 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>123.52</v>
+        <v>302.71</v>
       </c>
       <c r="D31" t="n">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="E31" t="n">
-        <v>14.19</v>
+        <v>35.65</v>
       </c>
       <c r="F31" t="n">
-        <v>0.64</v>
+        <v>0.79</v>
       </c>
       <c r="G31" t="n">
-        <v>9.699999999999999</v>
+        <v>21.36</v>
       </c>
       <c r="H31" t="n">
-        <v>7.85</v>
+        <v>7.06</v>
       </c>
       <c r="I31" t="n">
-        <v>119.64</v>
+        <v>294.17</v>
       </c>
       <c r="J31" t="n">
-        <v>125.95</v>
+        <v>308.05</v>
       </c>
       <c r="K31" t="n">
-        <v>108.97</v>
+        <v>270.67</v>
       </c>
       <c r="L31" t="n">
-        <v>147.77</v>
+        <v>356.11</v>
       </c>
       <c r="M31" t="n">
-        <v>61.71</v>
+        <v>66.36</v>
       </c>
       <c r="N31" t="inlineStr">
         <is>
           <t>ALTO</t>
         </is>
       </c>
-      <c r="O31" t="inlineStr"/>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>🔥</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>VIGILAR</t>
@@ -2253,53 +2261,57 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>IONQ</t>
+          <t>SMCI</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Computación cuántica</t>
+          <t>Servidores IA</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>63.62</v>
+        <v>38.19</v>
       </c>
       <c r="D32" t="n">
-        <v>74</v>
+        <v>86</v>
       </c>
       <c r="E32" t="n">
-        <v>29.02</v>
+        <v>24.97</v>
       </c>
       <c r="F32" t="n">
-        <v>0.87</v>
+        <v>0.9</v>
       </c>
       <c r="G32" t="n">
-        <v>5.77</v>
+        <v>2.34</v>
       </c>
       <c r="H32" t="n">
-        <v>9.07</v>
+        <v>6.12</v>
       </c>
       <c r="I32" t="n">
-        <v>61.31</v>
+        <v>37.25</v>
       </c>
       <c r="J32" t="n">
-        <v>65.06</v>
+        <v>38.77</v>
       </c>
       <c r="K32" t="n">
-        <v>54.96</v>
+        <v>34.68</v>
       </c>
       <c r="L32" t="n">
-        <v>78.05</v>
+        <v>44.04</v>
       </c>
       <c r="M32" t="n">
-        <v>66.7</v>
+        <v>60.21</v>
       </c>
       <c r="N32" t="inlineStr">
         <is>
           <t>ALTO</t>
         </is>
       </c>
-      <c r="O32" t="inlineStr"/>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>🔥</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>VIGILAR</t>
@@ -2309,53 +2321,57 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>QCOM</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>IA / Chips</t>
+          <t>Chips</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>503.89</v>
+        <v>233.4</v>
       </c>
       <c r="D33" t="n">
-        <v>72</v>
+        <v>84</v>
       </c>
       <c r="E33" t="n">
-        <v>19.69</v>
+        <v>19.32</v>
       </c>
       <c r="F33" t="n">
-        <v>0.89</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="G33" t="n">
-        <v>32.52</v>
+        <v>20.87</v>
       </c>
       <c r="H33" t="n">
-        <v>6.45</v>
+        <v>8.94</v>
       </c>
       <c r="I33" t="n">
-        <v>490.88</v>
+        <v>225.05</v>
       </c>
       <c r="J33" t="n">
-        <v>512.02</v>
+        <v>238.62</v>
       </c>
       <c r="K33" t="n">
-        <v>455.1</v>
+        <v>202.09</v>
       </c>
       <c r="L33" t="n">
-        <v>585.2</v>
+        <v>285.58</v>
       </c>
       <c r="M33" t="n">
-        <v>77.28</v>
+        <v>62.13</v>
       </c>
       <c r="N33" t="inlineStr">
         <is>
           <t>ALTO</t>
         </is>
       </c>
-      <c r="O33" t="inlineStr"/>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>🔥</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>VIGILAR</t>
@@ -2365,53 +2381,57 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>ARM</t>
+          <t>AAPL</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Chips</t>
+          <t>Tecnología</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>321.22</v>
+        <v>310.85</v>
       </c>
       <c r="D34" t="n">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="E34" t="n">
-        <v>49.32</v>
+        <v>3.97</v>
       </c>
       <c r="F34" t="n">
-        <v>0.9</v>
+        <v>1.02</v>
       </c>
       <c r="G34" t="n">
-        <v>21.92</v>
+        <v>5.32</v>
       </c>
       <c r="H34" t="n">
-        <v>6.82</v>
+        <v>1.71</v>
       </c>
       <c r="I34" t="n">
-        <v>312.45</v>
+        <v>308.72</v>
       </c>
       <c r="J34" t="n">
-        <v>326.7</v>
+        <v>312.18</v>
       </c>
       <c r="K34" t="n">
-        <v>288.34</v>
+        <v>302.87</v>
       </c>
       <c r="L34" t="n">
-        <v>376.03</v>
+        <v>324.15</v>
       </c>
       <c r="M34" t="n">
-        <v>76.78</v>
+        <v>87.39</v>
       </c>
       <c r="N34" t="inlineStr">
         <is>
           <t>ALTO</t>
         </is>
       </c>
-      <c r="O34" t="inlineStr"/>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>🔥</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>VIGILAR</t>
@@ -2421,46 +2441,46 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>SMCI</t>
+          <t>INTC</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Servidores IA</t>
+          <t>Chips</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>37.1</v>
+        <v>121.77</v>
       </c>
       <c r="D35" t="n">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="E35" t="n">
-        <v>20.26</v>
+        <v>9.9</v>
       </c>
       <c r="F35" t="n">
-        <v>1.08</v>
+        <v>0.62</v>
       </c>
       <c r="G35" t="n">
-        <v>2.68</v>
+        <v>9.789999999999999</v>
       </c>
       <c r="H35" t="n">
-        <v>7.23</v>
+        <v>8.039999999999999</v>
       </c>
       <c r="I35" t="n">
-        <v>36.03</v>
+        <v>117.85</v>
       </c>
       <c r="J35" t="n">
-        <v>37.77</v>
+        <v>124.22</v>
       </c>
       <c r="K35" t="n">
-        <v>33.08</v>
+        <v>107.08</v>
       </c>
       <c r="L35" t="n">
-        <v>43.81</v>
+        <v>146.25</v>
       </c>
       <c r="M35" t="n">
-        <v>70.13</v>
+        <v>57.01</v>
       </c>
       <c r="N35" t="inlineStr">
         <is>
@@ -2477,46 +2497,46 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>QCOM</t>
+          <t>IONQ</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Chips</t>
+          <t>Computación cuántica</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>248.82</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="D36" t="n">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="E36" t="n">
-        <v>22.19</v>
+        <v>35.01</v>
       </c>
       <c r="F36" t="n">
-        <v>0.97</v>
+        <v>0.84</v>
       </c>
       <c r="G36" t="n">
-        <v>19.89</v>
+        <v>5.92</v>
       </c>
       <c r="H36" t="n">
-        <v>8</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="I36" t="n">
-        <v>240.86</v>
+        <v>63.03</v>
       </c>
       <c r="J36" t="n">
-        <v>253.79</v>
+        <v>66.88</v>
       </c>
       <c r="K36" t="n">
-        <v>218.98</v>
+        <v>56.52</v>
       </c>
       <c r="L36" t="n">
-        <v>298.56</v>
+        <v>80.19</v>
       </c>
       <c r="M36" t="n">
-        <v>69.59</v>
+        <v>64.59</v>
       </c>
       <c r="N36" t="inlineStr">
         <is>
@@ -2542,37 +2562,37 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>143.2</v>
+        <v>150.23</v>
       </c>
       <c r="D37" t="n">
         <v>68</v>
       </c>
       <c r="E37" t="n">
-        <v>9.18</v>
+        <v>18</v>
       </c>
       <c r="F37" t="n">
-        <v>1.11</v>
+        <v>0.99</v>
       </c>
       <c r="G37" t="n">
-        <v>12.68</v>
+        <v>13.19</v>
       </c>
       <c r="H37" t="n">
-        <v>8.85</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="I37" t="n">
-        <v>138.13</v>
+        <v>144.95</v>
       </c>
       <c r="J37" t="n">
-        <v>146.37</v>
+        <v>153.53</v>
       </c>
       <c r="K37" t="n">
-        <v>124.18</v>
+        <v>130.44</v>
       </c>
       <c r="L37" t="n">
-        <v>174.9</v>
+        <v>183.21</v>
       </c>
       <c r="M37" t="n">
-        <v>77.42</v>
+        <v>77.64</v>
       </c>
       <c r="N37" t="inlineStr">
         <is>

--- a/analisis_acciones.xlsx
+++ b/analisis_acciones.xlsx
@@ -501,50 +501,50 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>META</t>
+          <t>HOOD</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Tecnología</t>
+          <t>Trading</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>635.26</v>
+        <v>84.84</v>
       </c>
       <c r="D2" t="n">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="E2" t="n">
-        <v>5.42</v>
+        <v>11.99</v>
       </c>
       <c r="F2" t="n">
-        <v>1.35</v>
+        <v>1.87</v>
       </c>
       <c r="G2" t="n">
-        <v>13.3</v>
+        <v>4.4</v>
       </c>
       <c r="H2" t="n">
-        <v>2.09</v>
+        <v>5.19</v>
       </c>
       <c r="I2" t="n">
-        <v>629.9400000000001</v>
+        <v>83.08</v>
       </c>
       <c r="J2" t="n">
-        <v>638.58</v>
+        <v>85.94</v>
       </c>
       <c r="K2" t="n">
-        <v>615.3099999999999</v>
+        <v>78.23999999999999</v>
       </c>
       <c r="L2" t="n">
-        <v>668.5</v>
+        <v>95.84999999999999</v>
       </c>
       <c r="M2" t="n">
-        <v>62.44</v>
+        <v>62.49</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>BAJO</t>
+          <t>MEDIO</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -561,46 +561,46 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>AI</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Chips</t>
+          <t>IA</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>422.73</v>
+        <v>10.22</v>
       </c>
       <c r="D3" t="n">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="E3" t="n">
-        <v>7.67</v>
+        <v>10.13</v>
       </c>
       <c r="F3" t="n">
-        <v>1.05</v>
+        <v>1.38</v>
       </c>
       <c r="G3" t="n">
-        <v>14.65</v>
+        <v>0.52</v>
       </c>
       <c r="H3" t="n">
-        <v>3.47</v>
+        <v>5.11</v>
       </c>
       <c r="I3" t="n">
-        <v>416.87</v>
+        <v>10.01</v>
       </c>
       <c r="J3" t="n">
-        <v>426.39</v>
+        <v>10.35</v>
       </c>
       <c r="K3" t="n">
-        <v>400.76</v>
+        <v>9.44</v>
       </c>
       <c r="L3" t="n">
-        <v>459.35</v>
+        <v>11.53</v>
       </c>
       <c r="M3" t="n">
-        <v>51.57</v>
+        <v>58.16</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -609,7 +609,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>🔥🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -621,50 +621,50 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ASML</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Chips</t>
+          <t>Tecnología</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1597.87</v>
+        <v>426.99</v>
       </c>
       <c r="D4" t="n">
         <v>95</v>
       </c>
       <c r="E4" t="n">
-        <v>9.49</v>
+        <v>1.63</v>
       </c>
       <c r="F4" t="n">
-        <v>0.77</v>
+        <v>1.36</v>
       </c>
       <c r="G4" t="n">
-        <v>67.09999999999999</v>
+        <v>10.48</v>
       </c>
       <c r="H4" t="n">
-        <v>4.2</v>
+        <v>2.45</v>
       </c>
       <c r="I4" t="n">
-        <v>1571.03</v>
+        <v>422.8</v>
       </c>
       <c r="J4" t="n">
-        <v>1614.64</v>
+        <v>429.61</v>
       </c>
       <c r="K4" t="n">
-        <v>1497.23</v>
+        <v>411.27</v>
       </c>
       <c r="L4" t="n">
-        <v>1765.61</v>
+        <v>453.19</v>
       </c>
       <c r="M4" t="n">
-        <v>54.65</v>
+        <v>55.45</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>MEDIO</t>
+          <t>BAJO</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -681,50 +681,50 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AMAT</t>
+          <t>AMZN</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Equipos chips</t>
+          <t>Tecnología</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>448.25</v>
+        <v>274</v>
       </c>
       <c r="D5" t="n">
         <v>95</v>
       </c>
       <c r="E5" t="n">
-        <v>10.3</v>
+        <v>3.39</v>
       </c>
       <c r="F5" t="n">
-        <v>0.66</v>
+        <v>0.93</v>
       </c>
       <c r="G5" t="n">
-        <v>20.08</v>
+        <v>6.34</v>
       </c>
       <c r="H5" t="n">
-        <v>4.48</v>
+        <v>2.32</v>
       </c>
       <c r="I5" t="n">
-        <v>440.22</v>
+        <v>271.46</v>
       </c>
       <c r="J5" t="n">
-        <v>453.27</v>
+        <v>275.59</v>
       </c>
       <c r="K5" t="n">
-        <v>418.13</v>
+        <v>264.48</v>
       </c>
       <c r="L5" t="n">
-        <v>498.45</v>
+        <v>289.86</v>
       </c>
       <c r="M5" t="n">
-        <v>56.25</v>
+        <v>53.08</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>MEDIO</t>
+          <t>BAJO</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -741,46 +741,46 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SPY</t>
+          <t>TSM</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>ETF Mercado</t>
+          <t>Chips</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>750.46</v>
+        <v>424.86</v>
       </c>
       <c r="D6" t="n">
         <v>95</v>
       </c>
       <c r="E6" t="n">
-        <v>2.28</v>
+        <v>5.79</v>
       </c>
       <c r="F6" t="n">
-        <v>0.86</v>
+        <v>0.68</v>
       </c>
       <c r="G6" t="n">
-        <v>6.97</v>
+        <v>14.71</v>
       </c>
       <c r="H6" t="n">
-        <v>0.93</v>
+        <v>3.46</v>
       </c>
       <c r="I6" t="n">
-        <v>747.67</v>
+        <v>418.97</v>
       </c>
       <c r="J6" t="n">
-        <v>752.2</v>
+        <v>428.54</v>
       </c>
       <c r="K6" t="n">
-        <v>740.01</v>
+        <v>402.79</v>
       </c>
       <c r="L6" t="n">
-        <v>767.88</v>
+        <v>461.64</v>
       </c>
       <c r="M6" t="n">
-        <v>65.84</v>
+        <v>55.36</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
@@ -801,46 +801,46 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SLB</t>
+          <t>ASML</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Energía</t>
+          <t>Chips</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>56.5</v>
+        <v>1605.77</v>
       </c>
       <c r="D7" t="n">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.48</v>
+        <v>3.59</v>
       </c>
       <c r="F7" t="n">
-        <v>1.38</v>
+        <v>0.59</v>
       </c>
       <c r="G7" t="n">
-        <v>1.5</v>
+        <v>66.76000000000001</v>
       </c>
       <c r="H7" t="n">
-        <v>2.65</v>
+        <v>4.16</v>
       </c>
       <c r="I7" t="n">
-        <v>55.9</v>
+        <v>1579.06</v>
       </c>
       <c r="J7" t="n">
-        <v>56.87</v>
+        <v>1622.46</v>
       </c>
       <c r="K7" t="n">
-        <v>54.25</v>
+        <v>1505.63</v>
       </c>
       <c r="L7" t="n">
-        <v>60.25</v>
+        <v>1772.68</v>
       </c>
       <c r="M7" t="n">
-        <v>56.26</v>
+        <v>58.08</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -861,50 +861,50 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>QQQ</t>
+          <t>AMAT</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>ETF Nasdaq</t>
+          <t>Equipos chips</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>729.45</v>
+        <v>449.68</v>
       </c>
       <c r="D8" t="n">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="E8" t="n">
-        <v>3.98</v>
+        <v>5.48</v>
       </c>
       <c r="F8" t="n">
-        <v>0.85</v>
+        <v>0.74</v>
       </c>
       <c r="G8" t="n">
-        <v>11.25</v>
+        <v>19.85</v>
       </c>
       <c r="H8" t="n">
-        <v>1.54</v>
+        <v>4.41</v>
       </c>
       <c r="I8" t="n">
-        <v>724.95</v>
+        <v>441.74</v>
       </c>
       <c r="J8" t="n">
-        <v>732.26</v>
+        <v>454.64</v>
       </c>
       <c r="K8" t="n">
-        <v>712.5700000000001</v>
+        <v>419.9</v>
       </c>
       <c r="L8" t="n">
-        <v>757.58</v>
+        <v>499.31</v>
       </c>
       <c r="M8" t="n">
-        <v>69.67</v>
+        <v>63.65</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>MEDIO</t>
+          <t>BAJO</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -921,46 +921,46 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>TSLA</t>
+          <t>LRCX</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Autos / Tech</t>
+          <t>Equipos chips</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>440.36</v>
+        <v>318</v>
       </c>
       <c r="D9" t="n">
-        <v>86</v>
+        <v>95</v>
       </c>
       <c r="E9" t="n">
-        <v>8.970000000000001</v>
+        <v>8.869999999999999</v>
       </c>
       <c r="F9" t="n">
-        <v>0.83</v>
+        <v>0.91</v>
       </c>
       <c r="G9" t="n">
-        <v>17.52</v>
+        <v>14.83</v>
       </c>
       <c r="H9" t="n">
-        <v>3.98</v>
+        <v>4.66</v>
       </c>
       <c r="I9" t="n">
-        <v>433.35</v>
+        <v>312.07</v>
       </c>
       <c r="J9" t="n">
-        <v>444.74</v>
+        <v>321.71</v>
       </c>
       <c r="K9" t="n">
-        <v>414.08</v>
+        <v>295.76</v>
       </c>
       <c r="L9" t="n">
-        <v>484.15</v>
+        <v>355.07</v>
       </c>
       <c r="M9" t="n">
-        <v>64.16</v>
+        <v>64.84999999999999</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
@@ -981,46 +981,46 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>AVGO</t>
+          <t>KLAC</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>IA / Chips</t>
+          <t>Equipos chips</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>421.86</v>
+        <v>1927.63</v>
       </c>
       <c r="D10" t="n">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="E10" t="n">
-        <v>2.62</v>
+        <v>5.37</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.83</v>
       </c>
       <c r="G10" t="n">
-        <v>16.51</v>
+        <v>87.69</v>
       </c>
       <c r="H10" t="n">
-        <v>3.91</v>
+        <v>4.55</v>
       </c>
       <c r="I10" t="n">
-        <v>415.25</v>
+        <v>1892.55</v>
       </c>
       <c r="J10" t="n">
-        <v>425.99</v>
+        <v>1949.55</v>
       </c>
       <c r="K10" t="n">
-        <v>397.09</v>
+        <v>1796.1</v>
       </c>
       <c r="L10" t="n">
-        <v>463.14</v>
+        <v>2146.85</v>
       </c>
       <c r="M10" t="n">
-        <v>48.42</v>
+        <v>61.11</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
@@ -1041,46 +1041,46 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>AMZN</t>
+          <t>AVGO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Tecnología</t>
+          <t>IA / Chips</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>271.85</v>
+        <v>426.58</v>
       </c>
       <c r="D11" t="n">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="E11" t="n">
-        <v>4.82</v>
+        <v>2.11</v>
       </c>
       <c r="F11" t="n">
-        <v>0.91</v>
+        <v>0.95</v>
       </c>
       <c r="G11" t="n">
-        <v>6.28</v>
+        <v>16.19</v>
       </c>
       <c r="H11" t="n">
-        <v>2.31</v>
+        <v>3.8</v>
       </c>
       <c r="I11" t="n">
-        <v>269.34</v>
+        <v>420.1</v>
       </c>
       <c r="J11" t="n">
-        <v>273.42</v>
+        <v>430.63</v>
       </c>
       <c r="K11" t="n">
-        <v>262.43</v>
+        <v>402.29</v>
       </c>
       <c r="L11" t="n">
-        <v>287.56</v>
+        <v>467.06</v>
       </c>
       <c r="M11" t="n">
-        <v>46.7</v>
+        <v>56.65</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
@@ -1101,55 +1101,55 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>UPST</t>
+          <t>TSLA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Fintech IA</t>
+          <t>Autos / Tech</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>30.72</v>
+        <v>442.1</v>
       </c>
       <c r="D12" t="n">
-        <v>78</v>
+        <v>92</v>
       </c>
       <c r="E12" t="n">
-        <v>9.4</v>
+        <v>5.95</v>
       </c>
       <c r="F12" t="n">
-        <v>0.78</v>
+        <v>0.61</v>
       </c>
       <c r="G12" t="n">
-        <v>1.79</v>
+        <v>16.84</v>
       </c>
       <c r="H12" t="n">
-        <v>5.82</v>
+        <v>3.81</v>
       </c>
       <c r="I12" t="n">
-        <v>30.01</v>
+        <v>435.36</v>
       </c>
       <c r="J12" t="n">
-        <v>31.17</v>
+        <v>446.31</v>
       </c>
       <c r="K12" t="n">
-        <v>28.04</v>
+        <v>416.83</v>
       </c>
       <c r="L12" t="n">
-        <v>35.19</v>
+        <v>484.21</v>
       </c>
       <c r="M12" t="n">
-        <v>59.94</v>
+        <v>61.17</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>MEDIO</t>
+          <t>BAJO</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1161,53 +1161,57 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>NVDA</t>
+          <t>META</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>IA / Chips</t>
+          <t>Tecnología</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>212.6</v>
+        <v>635.29</v>
       </c>
       <c r="D13" t="n">
-        <v>76</v>
+        <v>90</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.63</v>
+        <v>5</v>
       </c>
       <c r="F13" t="n">
-        <v>1</v>
+        <v>0.99</v>
       </c>
       <c r="G13" t="n">
-        <v>8.02</v>
+        <v>13.41</v>
       </c>
       <c r="H13" t="n">
-        <v>3.77</v>
+        <v>2.11</v>
       </c>
       <c r="I13" t="n">
-        <v>209.39</v>
+        <v>629.92</v>
       </c>
       <c r="J13" t="n">
-        <v>214.61</v>
+        <v>638.64</v>
       </c>
       <c r="K13" t="n">
-        <v>200.57</v>
+        <v>615.17</v>
       </c>
       <c r="L13" t="n">
-        <v>232.65</v>
+        <v>668.8200000000001</v>
       </c>
       <c r="M13" t="n">
-        <v>54.2</v>
+        <v>60.74</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
           <t>BAJO</t>
         </is>
       </c>
-      <c r="O13" t="inlineStr"/>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>🔥🔥</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>POSIBLE COMPRA</t>
@@ -1217,53 +1221,57 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>OXY</t>
+          <t>QQQ</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Energía</t>
+          <t>ETF Nasdaq</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>56.89</v>
+        <v>735.6</v>
       </c>
       <c r="D14" t="n">
-        <v>76</v>
+        <v>89</v>
       </c>
       <c r="E14" t="n">
-        <v>-6.28</v>
+        <v>3.15</v>
       </c>
       <c r="F14" t="n">
-        <v>0.9</v>
+        <v>0.79</v>
       </c>
       <c r="G14" t="n">
-        <v>1.82</v>
+        <v>11.3</v>
       </c>
       <c r="H14" t="n">
-        <v>3.2</v>
+        <v>1.54</v>
       </c>
       <c r="I14" t="n">
-        <v>56.16</v>
+        <v>731.08</v>
       </c>
       <c r="J14" t="n">
-        <v>57.35</v>
+        <v>738.4299999999999</v>
       </c>
       <c r="K14" t="n">
-        <v>54.16</v>
+        <v>718.65</v>
       </c>
       <c r="L14" t="n">
-        <v>61.45</v>
+        <v>763.86</v>
       </c>
       <c r="M14" t="n">
-        <v>56.44</v>
+        <v>72.36</v>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>BAJO</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr"/>
+          <t>MEDIO</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>🔥🔥</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>POSIBLE COMPRA</t>
@@ -1273,46 +1281,46 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>SOFI</t>
+          <t>SOXX</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Fintech</t>
+          <t>ETF Chips</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>16.17</v>
+        <v>569.47</v>
       </c>
       <c r="D15" t="n">
-        <v>70</v>
+        <v>89</v>
       </c>
       <c r="E15" t="n">
-        <v>6.17</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="F15" t="n">
-        <v>0.93</v>
+        <v>0.79</v>
       </c>
       <c r="G15" t="n">
-        <v>0.73</v>
+        <v>23.76</v>
       </c>
       <c r="H15" t="n">
-        <v>4.49</v>
+        <v>4.17</v>
       </c>
       <c r="I15" t="n">
-        <v>15.88</v>
+        <v>559.96</v>
       </c>
       <c r="J15" t="n">
-        <v>16.35</v>
+        <v>575.41</v>
       </c>
       <c r="K15" t="n">
-        <v>15.08</v>
+        <v>533.83</v>
       </c>
       <c r="L15" t="n">
-        <v>17.99</v>
+        <v>628.88</v>
       </c>
       <c r="M15" t="n">
-        <v>48.64</v>
+        <v>70.17</v>
       </c>
       <c r="N15" t="inlineStr">
         <is>
@@ -1321,58 +1329,58 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>VIGILAR</t>
+          <t>POSIBLE COMPRA</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>AI</t>
+          <t>SOFI</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>IA</t>
+          <t>Fintech</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>9.59</v>
+        <v>16.97</v>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>84</v>
       </c>
       <c r="E16" t="n">
-        <v>8.609999999999999</v>
+        <v>8.16</v>
       </c>
       <c r="F16" t="n">
-        <v>0.86</v>
+        <v>1.07</v>
       </c>
       <c r="G16" t="n">
-        <v>0.49</v>
+        <v>0.77</v>
       </c>
       <c r="H16" t="n">
-        <v>5.09</v>
+        <v>4.55</v>
       </c>
       <c r="I16" t="n">
-        <v>9.390000000000001</v>
+        <v>16.66</v>
       </c>
       <c r="J16" t="n">
-        <v>9.710000000000001</v>
+        <v>17.16</v>
       </c>
       <c r="K16" t="n">
-        <v>8.859999999999999</v>
+        <v>15.81</v>
       </c>
       <c r="L16" t="n">
-        <v>10.81</v>
+        <v>18.9</v>
       </c>
       <c r="M16" t="n">
-        <v>49.85</v>
+        <v>59.17</v>
       </c>
       <c r="N16" t="inlineStr">
         <is>
@@ -1381,174 +1389,178 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>VIGILAR</t>
+          <t>POSIBLE COMPRA</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>HOOD</t>
+          <t>PLTR</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Trading</t>
+          <t>IA / Software</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>76.23</v>
+        <v>143.34</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>82</v>
       </c>
       <c r="E17" t="n">
-        <v>2.79</v>
+        <v>4.51</v>
       </c>
       <c r="F17" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="G17" t="n">
-        <v>3.86</v>
+        <v>5.21</v>
       </c>
       <c r="H17" t="n">
-        <v>5.06</v>
+        <v>3.63</v>
       </c>
       <c r="I17" t="n">
-        <v>74.69</v>
+        <v>141.26</v>
       </c>
       <c r="J17" t="n">
-        <v>77.19</v>
+        <v>144.64</v>
       </c>
       <c r="K17" t="n">
-        <v>70.44</v>
+        <v>135.53</v>
       </c>
       <c r="L17" t="n">
-        <v>85.88</v>
+        <v>156.35</v>
       </c>
       <c r="M17" t="n">
-        <v>45.04</v>
+        <v>59.95</v>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>MEDIO</t>
+          <t>BAJO</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>NO COMPRAR</t>
+          <t>POSIBLE COMPRA</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>GOOGL</t>
+          <t>SPY</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Tecnología</t>
+          <t>ETF Mercado</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>388.83</v>
+        <v>754.6</v>
       </c>
       <c r="D18" t="n">
-        <v>72</v>
+        <v>89</v>
       </c>
       <c r="E18" t="n">
-        <v>0.3</v>
+        <v>1.8</v>
       </c>
       <c r="F18" t="n">
-        <v>0.76</v>
+        <v>0.74</v>
       </c>
       <c r="G18" t="n">
-        <v>9.44</v>
+        <v>6.94</v>
       </c>
       <c r="H18" t="n">
-        <v>2.43</v>
+        <v>0.92</v>
       </c>
       <c r="I18" t="n">
-        <v>385.06</v>
+        <v>751.83</v>
       </c>
       <c r="J18" t="n">
-        <v>391.19</v>
+        <v>756.33</v>
       </c>
       <c r="K18" t="n">
-        <v>374.68</v>
+        <v>744.2</v>
       </c>
       <c r="L18" t="n">
-        <v>412.42</v>
+        <v>771.9400000000001</v>
       </c>
       <c r="M18" t="n">
-        <v>42.33</v>
+        <v>71.16</v>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>BAJO</t>
-        </is>
-      </c>
-      <c r="O18" t="inlineStr"/>
+          <t>MEDIO</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>🔥</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>VIGILAR</t>
+          <t>POSIBLE COMPRA</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>XOM</t>
+          <t>NVDA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Energía</t>
+          <t>IA / Chips</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>147.9</v>
+        <v>214.25</v>
       </c>
       <c r="D19" t="n">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="E19" t="n">
-        <v>-9.01</v>
+        <v>-4.13</v>
       </c>
       <c r="F19" t="n">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="G19" t="n">
-        <v>4.28</v>
+        <v>7.78</v>
       </c>
       <c r="H19" t="n">
-        <v>2.89</v>
+        <v>3.63</v>
       </c>
       <c r="I19" t="n">
-        <v>146.19</v>
+        <v>211.14</v>
       </c>
       <c r="J19" t="n">
-        <v>148.97</v>
+        <v>216.19</v>
       </c>
       <c r="K19" t="n">
-        <v>141.48</v>
+        <v>202.58</v>
       </c>
       <c r="L19" t="n">
-        <v>158.6</v>
+        <v>233.69</v>
       </c>
       <c r="M19" t="n">
-        <v>50.28</v>
+        <v>52.51</v>
       </c>
       <c r="N19" t="inlineStr">
         <is>
@@ -1558,53 +1570,53 @@
       <c r="O19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>VIGILAR</t>
+          <t>POSIBLE COMPRA</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>SLB</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Tecnología</t>
+          <t>Energía</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>412.67</v>
+        <v>55.12</v>
       </c>
       <c r="D20" t="n">
-        <v>54</v>
+        <v>76</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.92</v>
+        <v>-3.77</v>
       </c>
       <c r="F20" t="n">
-        <v>0.8</v>
+        <v>1.15</v>
       </c>
       <c r="G20" t="n">
-        <v>10.28</v>
+        <v>1.49</v>
       </c>
       <c r="H20" t="n">
-        <v>2.49</v>
+        <v>2.7</v>
       </c>
       <c r="I20" t="n">
-        <v>408.56</v>
+        <v>54.53</v>
       </c>
       <c r="J20" t="n">
-        <v>415.24</v>
+        <v>55.49</v>
       </c>
       <c r="K20" t="n">
-        <v>397.25</v>
+        <v>52.89</v>
       </c>
       <c r="L20" t="n">
-        <v>438.36</v>
+        <v>58.84</v>
       </c>
       <c r="M20" t="n">
-        <v>49.66</v>
+        <v>60.69</v>
       </c>
       <c r="N20" t="inlineStr">
         <is>
@@ -1614,53 +1626,53 @@
       <c r="O20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>NO COMPRAR</t>
+          <t>POSIBLE COMPRA</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>PLTR</t>
+          <t>GOOGL</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>IA / Software</t>
+          <t>Tecnología</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>132.51</v>
+        <v>390.13</v>
       </c>
       <c r="D21" t="n">
-        <v>54</v>
+        <v>72</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.03</v>
+        <v>0.31</v>
       </c>
       <c r="F21" t="n">
-        <v>0.77</v>
+        <v>0.73</v>
       </c>
       <c r="G21" t="n">
-        <v>4.94</v>
+        <v>9.390000000000001</v>
       </c>
       <c r="H21" t="n">
-        <v>3.73</v>
+        <v>2.41</v>
       </c>
       <c r="I21" t="n">
-        <v>130.53</v>
+        <v>386.38</v>
       </c>
       <c r="J21" t="n">
-        <v>133.74</v>
+        <v>392.48</v>
       </c>
       <c r="K21" t="n">
-        <v>125.1</v>
+        <v>376.05</v>
       </c>
       <c r="L21" t="n">
-        <v>144.86</v>
+        <v>413.59</v>
       </c>
       <c r="M21" t="n">
-        <v>47.34</v>
+        <v>43.58</v>
       </c>
       <c r="N21" t="inlineStr">
         <is>
@@ -1670,14 +1682,14 @@
       <c r="O21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>NO COMPRAR</t>
+          <t>VIGILAR</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>CVX</t>
+          <t>XOM</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1686,37 +1698,37 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>182.4</v>
+        <v>146.96</v>
       </c>
       <c r="D22" t="n">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="E22" t="n">
-        <v>-7.53</v>
+        <v>-5.96</v>
       </c>
       <c r="F22" t="n">
-        <v>0.89</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="G22" t="n">
-        <v>4.34</v>
+        <v>4.2</v>
       </c>
       <c r="H22" t="n">
-        <v>2.38</v>
+        <v>2.86</v>
       </c>
       <c r="I22" t="n">
-        <v>180.66</v>
+        <v>145.28</v>
       </c>
       <c r="J22" t="n">
-        <v>183.49</v>
+        <v>148.01</v>
       </c>
       <c r="K22" t="n">
-        <v>175.88</v>
+        <v>140.66</v>
       </c>
       <c r="L22" t="n">
-        <v>193.26</v>
+        <v>157.46</v>
       </c>
       <c r="M22" t="n">
-        <v>48.52</v>
+        <v>51.87</v>
       </c>
       <c r="N22" t="inlineStr">
         <is>
@@ -1726,169 +1738,169 @@
       <c r="O22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>NO COMPRAR</t>
+          <t>VIGILAR</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>COIN</t>
+          <t>CVX</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Cripto / Trading</t>
+          <t>Energía</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>173.78</v>
+        <v>183.03</v>
       </c>
       <c r="D23" t="n">
-        <v>38</v>
+        <v>66</v>
       </c>
       <c r="E23" t="n">
-        <v>-10.17</v>
+        <v>-4.34</v>
       </c>
       <c r="F23" t="n">
-        <v>0.83</v>
+        <v>0.86</v>
       </c>
       <c r="G23" t="n">
-        <v>13.5</v>
+        <v>4.17</v>
       </c>
       <c r="H23" t="n">
-        <v>7.77</v>
+        <v>2.28</v>
       </c>
       <c r="I23" t="n">
-        <v>168.38</v>
+        <v>181.36</v>
       </c>
       <c r="J23" t="n">
-        <v>177.15</v>
+        <v>184.07</v>
       </c>
       <c r="K23" t="n">
-        <v>153.53</v>
+        <v>176.77</v>
       </c>
       <c r="L23" t="n">
-        <v>207.53</v>
+        <v>193.46</v>
       </c>
       <c r="M23" t="n">
-        <v>38.42</v>
+        <v>53.17</v>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>MEDIO</t>
+          <t>BAJO</t>
         </is>
       </c>
       <c r="O23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>NO COMPRAR</t>
+          <t>VIGILAR</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>SOUN</t>
+          <t>OXY</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>IA</t>
+          <t>Energía</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>8.08</v>
+        <v>57.32</v>
       </c>
       <c r="D24" t="n">
-        <v>38</v>
+        <v>66</v>
       </c>
       <c r="E24" t="n">
-        <v>-4.38</v>
+        <v>-2.63</v>
       </c>
       <c r="F24" t="n">
-        <v>0.57</v>
+        <v>0.88</v>
       </c>
       <c r="G24" t="n">
-        <v>0.52</v>
+        <v>1.78</v>
       </c>
       <c r="H24" t="n">
-        <v>6.48</v>
+        <v>3.1</v>
       </c>
       <c r="I24" t="n">
-        <v>7.87</v>
+        <v>56.61</v>
       </c>
       <c r="J24" t="n">
-        <v>8.210000000000001</v>
+        <v>57.76</v>
       </c>
       <c r="K24" t="n">
-        <v>7.3</v>
+        <v>54.65</v>
       </c>
       <c r="L24" t="n">
-        <v>9.390000000000001</v>
+        <v>61.76</v>
       </c>
       <c r="M24" t="n">
-        <v>27.99</v>
+        <v>63</v>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>MEDIO</t>
+          <t>BAJO</t>
         </is>
       </c>
       <c r="O24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>NO COMPRAR</t>
+          <t>VIGILAR</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>PYPL</t>
+          <t>COIN</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Pagos</t>
+          <t>Cripto / Trading</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>43.76</v>
+        <v>182.25</v>
       </c>
       <c r="D25" t="n">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.16</v>
+        <v>-4.73</v>
       </c>
       <c r="F25" t="n">
-        <v>0.9</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="G25" t="n">
-        <v>1</v>
+        <v>13.9</v>
       </c>
       <c r="H25" t="n">
-        <v>2.29</v>
+        <v>7.63</v>
       </c>
       <c r="I25" t="n">
-        <v>43.36</v>
+        <v>176.69</v>
       </c>
       <c r="J25" t="n">
-        <v>44.01</v>
+        <v>185.73</v>
       </c>
       <c r="K25" t="n">
-        <v>42.26</v>
+        <v>161.4</v>
       </c>
       <c r="L25" t="n">
-        <v>46.26</v>
+        <v>217.01</v>
       </c>
       <c r="M25" t="n">
-        <v>21.08</v>
+        <v>45.04</v>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>BAJO</t>
+          <t>MEDIO</t>
         </is>
       </c>
       <c r="O25" t="inlineStr"/>
@@ -1901,166 +1913,158 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>SOXX</t>
+          <t>SOUN</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>ETF Chips</t>
+          <t>IA</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>563.98</v>
+        <v>8.56</v>
       </c>
       <c r="D26" t="n">
-        <v>95</v>
+        <v>46</v>
       </c>
       <c r="E26" t="n">
-        <v>13.54</v>
+        <v>1.3</v>
       </c>
       <c r="F26" t="n">
-        <v>1.37</v>
+        <v>0.9</v>
       </c>
       <c r="G26" t="n">
-        <v>23.6</v>
+        <v>0.54</v>
       </c>
       <c r="H26" t="n">
-        <v>4.19</v>
+        <v>6.3</v>
       </c>
       <c r="I26" t="n">
-        <v>554.54</v>
+        <v>8.34</v>
       </c>
       <c r="J26" t="n">
-        <v>569.88</v>
+        <v>8.69</v>
       </c>
       <c r="K26" t="n">
-        <v>528.5700000000001</v>
+        <v>7.75</v>
       </c>
       <c r="L26" t="n">
-        <v>622.99</v>
+        <v>9.91</v>
       </c>
       <c r="M26" t="n">
-        <v>64.26000000000001</v>
+        <v>33.02</v>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>ALTO</t>
-        </is>
-      </c>
-      <c r="O26" t="inlineStr">
-        <is>
-          <t>🔥🔥</t>
-        </is>
-      </c>
+          <t>MEDIO</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>VIGILAR</t>
+          <t>NO COMPRAR</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>MU</t>
+          <t>PYPL</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Memoria / Chips</t>
+          <t>Pagos</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>928.41</v>
+        <v>44.46</v>
       </c>
       <c r="D27" t="n">
-        <v>88</v>
+        <v>44</v>
       </c>
       <c r="E27" t="n">
-        <v>32.87</v>
+        <v>0.19</v>
       </c>
       <c r="F27" t="n">
-        <v>1.32</v>
+        <v>1</v>
       </c>
       <c r="G27" t="n">
-        <v>68.2</v>
+        <v>1.02</v>
       </c>
       <c r="H27" t="n">
-        <v>7.35</v>
+        <v>2.29</v>
       </c>
       <c r="I27" t="n">
-        <v>901.13</v>
+        <v>44.05</v>
       </c>
       <c r="J27" t="n">
-        <v>945.46</v>
+        <v>44.71</v>
       </c>
       <c r="K27" t="n">
-        <v>826.12</v>
+        <v>42.93</v>
       </c>
       <c r="L27" t="n">
-        <v>1098.9</v>
+        <v>47.01</v>
       </c>
       <c r="M27" t="n">
-        <v>70.92</v>
+        <v>32.36</v>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>ALTO</t>
-        </is>
-      </c>
-      <c r="O27" t="inlineStr">
-        <is>
-          <t>🔥🔥</t>
-        </is>
-      </c>
+          <t>BAJO</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>VIGILAR</t>
+          <t>NO COMPRAR</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>LRCX</t>
+          <t>SMCI</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Equipos chips</t>
+          <t>Servidores IA</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>318.93</v>
+        <v>41.3</v>
       </c>
       <c r="D28" t="n">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="E28" t="n">
-        <v>16.66</v>
+        <v>23.43</v>
       </c>
       <c r="F28" t="n">
-        <v>0.96</v>
+        <v>1.67</v>
       </c>
       <c r="G28" t="n">
-        <v>14.9</v>
+        <v>2.57</v>
       </c>
       <c r="H28" t="n">
-        <v>4.67</v>
+        <v>6.23</v>
       </c>
       <c r="I28" t="n">
-        <v>312.97</v>
+        <v>40.27</v>
       </c>
       <c r="J28" t="n">
-        <v>322.65</v>
+        <v>41.94</v>
       </c>
       <c r="K28" t="n">
-        <v>296.59</v>
+        <v>37.44</v>
       </c>
       <c r="L28" t="n">
-        <v>356.17</v>
+        <v>47.73</v>
       </c>
       <c r="M28" t="n">
-        <v>59.4</v>
+        <v>69.83</v>
       </c>
       <c r="N28" t="inlineStr">
         <is>
@@ -2069,7 +2073,7 @@
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -2081,46 +2085,46 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>KLAC</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Equipos chips</t>
+          <t>IA / Chips</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>1957.19</v>
+        <v>518.09</v>
       </c>
       <c r="D29" t="n">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="E29" t="n">
-        <v>12.44</v>
+        <v>15.75</v>
       </c>
       <c r="F29" t="n">
-        <v>0.9</v>
+        <v>0.76</v>
       </c>
       <c r="G29" t="n">
-        <v>88.03</v>
+        <v>29.76</v>
       </c>
       <c r="H29" t="n">
-        <v>4.5</v>
+        <v>5.74</v>
       </c>
       <c r="I29" t="n">
-        <v>1921.98</v>
+        <v>506.19</v>
       </c>
       <c r="J29" t="n">
-        <v>1979.2</v>
+        <v>525.53</v>
       </c>
       <c r="K29" t="n">
-        <v>1825.15</v>
+        <v>473.45</v>
       </c>
       <c r="L29" t="n">
-        <v>2177.26</v>
+        <v>592.48</v>
       </c>
       <c r="M29" t="n">
-        <v>59.26</v>
+        <v>74.45</v>
       </c>
       <c r="N29" t="inlineStr">
         <is>
@@ -2141,46 +2145,46 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>UPST</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>IA / Chips</t>
+          <t>Fintech IA</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>495.54</v>
+        <v>32.69</v>
       </c>
       <c r="D30" t="n">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E30" t="n">
-        <v>19.68</v>
+        <v>13.35</v>
       </c>
       <c r="F30" t="n">
-        <v>0.66</v>
+        <v>1.05</v>
       </c>
       <c r="G30" t="n">
-        <v>28.82</v>
+        <v>1.87</v>
       </c>
       <c r="H30" t="n">
-        <v>5.82</v>
+        <v>5.72</v>
       </c>
       <c r="I30" t="n">
-        <v>484.01</v>
+        <v>31.94</v>
       </c>
       <c r="J30" t="n">
-        <v>502.75</v>
+        <v>33.16</v>
       </c>
       <c r="K30" t="n">
-        <v>452.3</v>
+        <v>29.89</v>
       </c>
       <c r="L30" t="n">
-        <v>567.6</v>
+        <v>37.36</v>
       </c>
       <c r="M30" t="n">
-        <v>67.28</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="N30" t="inlineStr">
         <is>
@@ -2201,7 +2205,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>ARM</t>
+          <t>QCOM</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2210,37 +2214,37 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>302.71</v>
+        <v>243.29</v>
       </c>
       <c r="D31" t="n">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="E31" t="n">
-        <v>35.65</v>
+        <v>20.14</v>
       </c>
       <c r="F31" t="n">
-        <v>0.79</v>
+        <v>0.55</v>
       </c>
       <c r="G31" t="n">
-        <v>21.36</v>
+        <v>19.58</v>
       </c>
       <c r="H31" t="n">
-        <v>7.06</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="I31" t="n">
-        <v>294.17</v>
+        <v>235.46</v>
       </c>
       <c r="J31" t="n">
-        <v>308.05</v>
+        <v>248.19</v>
       </c>
       <c r="K31" t="n">
-        <v>270.67</v>
+        <v>213.92</v>
       </c>
       <c r="L31" t="n">
-        <v>356.11</v>
+        <v>292.24</v>
       </c>
       <c r="M31" t="n">
-        <v>66.36</v>
+        <v>62.11</v>
       </c>
       <c r="N31" t="inlineStr">
         <is>
@@ -2261,46 +2265,46 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>SMCI</t>
+          <t>AAPL</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Servidores IA</t>
+          <t>Tecnología</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>38.19</v>
+        <v>312.51</v>
       </c>
       <c r="D32" t="n">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="E32" t="n">
-        <v>24.97</v>
+        <v>3.39</v>
       </c>
       <c r="F32" t="n">
-        <v>0.9</v>
+        <v>0.89</v>
       </c>
       <c r="G32" t="n">
-        <v>2.34</v>
+        <v>5.09</v>
       </c>
       <c r="H32" t="n">
-        <v>6.12</v>
+        <v>1.63</v>
       </c>
       <c r="I32" t="n">
-        <v>37.25</v>
+        <v>310.47</v>
       </c>
       <c r="J32" t="n">
-        <v>38.77</v>
+        <v>313.78</v>
       </c>
       <c r="K32" t="n">
-        <v>34.68</v>
+        <v>304.87</v>
       </c>
       <c r="L32" t="n">
-        <v>44.04</v>
+        <v>325.25</v>
       </c>
       <c r="M32" t="n">
-        <v>60.21</v>
+        <v>88.20999999999999</v>
       </c>
       <c r="N32" t="inlineStr">
         <is>
@@ -2321,46 +2325,46 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>QCOM</t>
+          <t>MU</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Chips</t>
+          <t>Memoria / Chips</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>233.4</v>
+        <v>923.52</v>
       </c>
       <c r="D33" t="n">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="E33" t="n">
-        <v>19.32</v>
+        <v>26.17</v>
       </c>
       <c r="F33" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.89</v>
       </c>
       <c r="G33" t="n">
-        <v>20.87</v>
+        <v>67.98</v>
       </c>
       <c r="H33" t="n">
-        <v>8.94</v>
+        <v>7.36</v>
       </c>
       <c r="I33" t="n">
-        <v>225.05</v>
+        <v>896.33</v>
       </c>
       <c r="J33" t="n">
-        <v>238.62</v>
+        <v>940.52</v>
       </c>
       <c r="K33" t="n">
-        <v>202.09</v>
+        <v>821.54</v>
       </c>
       <c r="L33" t="n">
-        <v>285.58</v>
+        <v>1093.48</v>
       </c>
       <c r="M33" t="n">
-        <v>62.13</v>
+        <v>72.68000000000001</v>
       </c>
       <c r="N33" t="inlineStr">
         <is>
@@ -2381,57 +2385,53 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>INTC</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Tecnología</t>
+          <t>Chips</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>310.85</v>
+        <v>120.89</v>
       </c>
       <c r="D34" t="n">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="E34" t="n">
-        <v>3.97</v>
+        <v>1.62</v>
       </c>
       <c r="F34" t="n">
-        <v>1.02</v>
+        <v>0.67</v>
       </c>
       <c r="G34" t="n">
-        <v>5.32</v>
+        <v>9.9</v>
       </c>
       <c r="H34" t="n">
-        <v>1.71</v>
+        <v>8.19</v>
       </c>
       <c r="I34" t="n">
-        <v>308.72</v>
+        <v>116.93</v>
       </c>
       <c r="J34" t="n">
-        <v>312.18</v>
+        <v>123.36</v>
       </c>
       <c r="K34" t="n">
-        <v>302.87</v>
+        <v>106.04</v>
       </c>
       <c r="L34" t="n">
-        <v>324.15</v>
+        <v>145.63</v>
       </c>
       <c r="M34" t="n">
-        <v>87.39</v>
+        <v>59.39</v>
       </c>
       <c r="N34" t="inlineStr">
         <is>
           <t>ALTO</t>
         </is>
       </c>
-      <c r="O34" t="inlineStr">
-        <is>
-          <t>🔥</t>
-        </is>
-      </c>
+      <c r="O34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>VIGILAR</t>
@@ -2441,46 +2441,46 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>INTC</t>
+          <t>RKLB</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Chips</t>
+          <t>Espacial</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>121.77</v>
+        <v>148.03</v>
       </c>
       <c r="D35" t="n">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="E35" t="n">
-        <v>9.9</v>
+        <v>10.24</v>
       </c>
       <c r="F35" t="n">
-        <v>0.62</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="G35" t="n">
-        <v>9.789999999999999</v>
+        <v>13.31</v>
       </c>
       <c r="H35" t="n">
-        <v>8.039999999999999</v>
+        <v>8.99</v>
       </c>
       <c r="I35" t="n">
-        <v>117.85</v>
+        <v>142.71</v>
       </c>
       <c r="J35" t="n">
-        <v>124.22</v>
+        <v>151.36</v>
       </c>
       <c r="K35" t="n">
-        <v>107.08</v>
+        <v>128.07</v>
       </c>
       <c r="L35" t="n">
-        <v>146.25</v>
+        <v>181.29</v>
       </c>
       <c r="M35" t="n">
-        <v>57.01</v>
+        <v>80.26000000000001</v>
       </c>
       <c r="N35" t="inlineStr">
         <is>
@@ -2497,46 +2497,46 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>IONQ</t>
+          <t>ARM</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Computación cuántica</t>
+          <t>Chips</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>65.40000000000001</v>
+        <v>335.27</v>
       </c>
       <c r="D36" t="n">
-        <v>74</v>
+        <v>64</v>
       </c>
       <c r="E36" t="n">
-        <v>35.01</v>
+        <v>30.59</v>
       </c>
       <c r="F36" t="n">
-        <v>0.84</v>
+        <v>1.18</v>
       </c>
       <c r="G36" t="n">
-        <v>5.92</v>
+        <v>22.77</v>
       </c>
       <c r="H36" t="n">
-        <v>9.050000000000001</v>
+        <v>6.79</v>
       </c>
       <c r="I36" t="n">
-        <v>63.03</v>
+        <v>326.16</v>
       </c>
       <c r="J36" t="n">
-        <v>66.88</v>
+        <v>340.96</v>
       </c>
       <c r="K36" t="n">
-        <v>56.52</v>
+        <v>301.11</v>
       </c>
       <c r="L36" t="n">
-        <v>80.19</v>
+        <v>392.2</v>
       </c>
       <c r="M36" t="n">
-        <v>64.59</v>
+        <v>79.26000000000001</v>
       </c>
       <c r="N36" t="inlineStr">
         <is>
@@ -2553,46 +2553,46 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>RKLB</t>
+          <t>IONQ</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Espacial</t>
+          <t>Computación cuántica</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>150.23</v>
+        <v>70.14</v>
       </c>
       <c r="D37" t="n">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="E37" t="n">
-        <v>18</v>
+        <v>33.68</v>
       </c>
       <c r="F37" t="n">
-        <v>0.99</v>
+        <v>0.83</v>
       </c>
       <c r="G37" t="n">
-        <v>13.19</v>
+        <v>5.93</v>
       </c>
       <c r="H37" t="n">
-        <v>8.779999999999999</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="I37" t="n">
-        <v>144.95</v>
+        <v>67.77</v>
       </c>
       <c r="J37" t="n">
-        <v>153.53</v>
+        <v>71.62</v>
       </c>
       <c r="K37" t="n">
-        <v>130.44</v>
+        <v>61.24</v>
       </c>
       <c r="L37" t="n">
-        <v>183.21</v>
+        <v>84.97</v>
       </c>
       <c r="M37" t="n">
-        <v>77.64</v>
+        <v>75.63</v>
       </c>
       <c r="N37" t="inlineStr">
         <is>
@@ -2602,7 +2602,7 @@
       <c r="O37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>VIGILAR</t>
+          <t>NO COMPRAR</t>
         </is>
       </c>
     </row>

--- a/analisis_acciones.xlsx
+++ b/analisis_acciones.xlsx
@@ -501,46 +501,46 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>HOOD</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Trading</t>
+          <t>Tecnología</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>84.84</v>
+        <v>450.24</v>
       </c>
       <c r="D2" t="n">
         <v>95</v>
       </c>
       <c r="E2" t="n">
-        <v>11.99</v>
+        <v>7.43</v>
       </c>
       <c r="F2" t="n">
-        <v>1.87</v>
+        <v>2.22</v>
       </c>
       <c r="G2" t="n">
-        <v>4.4</v>
+        <v>11.66</v>
       </c>
       <c r="H2" t="n">
-        <v>5.19</v>
+        <v>2.59</v>
       </c>
       <c r="I2" t="n">
-        <v>83.08</v>
+        <v>445.57</v>
       </c>
       <c r="J2" t="n">
-        <v>85.94</v>
+        <v>453.16</v>
       </c>
       <c r="K2" t="n">
-        <v>78.23999999999999</v>
+        <v>432.74</v>
       </c>
       <c r="L2" t="n">
-        <v>95.84999999999999</v>
+        <v>479.4</v>
       </c>
       <c r="M2" t="n">
-        <v>62.49</v>
+        <v>71.70999999999999</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -561,46 +561,46 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AI</t>
+          <t>AVGO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>IA</t>
+          <t>IA / Chips</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>10.22</v>
+        <v>446.77</v>
       </c>
       <c r="D3" t="n">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="E3" t="n">
-        <v>10.13</v>
+        <v>7.77</v>
       </c>
       <c r="F3" t="n">
-        <v>1.38</v>
+        <v>2.13</v>
       </c>
       <c r="G3" t="n">
-        <v>0.52</v>
+        <v>16.18</v>
       </c>
       <c r="H3" t="n">
-        <v>5.11</v>
+        <v>3.62</v>
       </c>
       <c r="I3" t="n">
-        <v>10.01</v>
+        <v>440.3</v>
       </c>
       <c r="J3" t="n">
-        <v>10.35</v>
+        <v>450.82</v>
       </c>
       <c r="K3" t="n">
-        <v>9.44</v>
+        <v>422.5</v>
       </c>
       <c r="L3" t="n">
-        <v>11.53</v>
+        <v>487.22</v>
       </c>
       <c r="M3" t="n">
-        <v>58.16</v>
+        <v>57.75</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -621,7 +621,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>META</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -630,37 +630,37 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>426.99</v>
+        <v>632.51</v>
       </c>
       <c r="D4" t="n">
         <v>95</v>
       </c>
       <c r="E4" t="n">
-        <v>1.63</v>
+        <v>4.14</v>
       </c>
       <c r="F4" t="n">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="G4" t="n">
-        <v>10.48</v>
+        <v>13.5</v>
       </c>
       <c r="H4" t="n">
-        <v>2.45</v>
+        <v>2.13</v>
       </c>
       <c r="I4" t="n">
-        <v>422.8</v>
+        <v>627.11</v>
       </c>
       <c r="J4" t="n">
-        <v>429.61</v>
+        <v>635.88</v>
       </c>
       <c r="K4" t="n">
-        <v>411.27</v>
+        <v>612.26</v>
       </c>
       <c r="L4" t="n">
-        <v>453.19</v>
+        <v>666.26</v>
       </c>
       <c r="M4" t="n">
-        <v>55.45</v>
+        <v>64.02</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -669,7 +669,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>🔥🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -681,46 +681,46 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AMZN</t>
+          <t>TSM</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Tecnología</t>
+          <t>Chips</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>274</v>
+        <v>418.45</v>
       </c>
       <c r="D5" t="n">
         <v>95</v>
       </c>
       <c r="E5" t="n">
-        <v>3.39</v>
+        <v>2.78</v>
       </c>
       <c r="F5" t="n">
-        <v>0.93</v>
+        <v>0.75</v>
       </c>
       <c r="G5" t="n">
-        <v>6.34</v>
+        <v>14.5</v>
       </c>
       <c r="H5" t="n">
-        <v>2.32</v>
+        <v>3.47</v>
       </c>
       <c r="I5" t="n">
-        <v>271.46</v>
+        <v>412.65</v>
       </c>
       <c r="J5" t="n">
-        <v>275.59</v>
+        <v>422.08</v>
       </c>
       <c r="K5" t="n">
-        <v>264.48</v>
+        <v>396.69</v>
       </c>
       <c r="L5" t="n">
-        <v>289.86</v>
+        <v>454.71</v>
       </c>
       <c r="M5" t="n">
-        <v>53.08</v>
+        <v>53.26</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
@@ -741,46 +741,46 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>AMAT</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Chips</t>
+          <t>Equipos chips</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>424.86</v>
+        <v>450.06</v>
       </c>
       <c r="D6" t="n">
         <v>95</v>
       </c>
       <c r="E6" t="n">
-        <v>5.79</v>
+        <v>5.31</v>
       </c>
       <c r="F6" t="n">
-        <v>0.68</v>
+        <v>0.82</v>
       </c>
       <c r="G6" t="n">
-        <v>14.71</v>
+        <v>18.96</v>
       </c>
       <c r="H6" t="n">
-        <v>3.46</v>
+        <v>4.21</v>
       </c>
       <c r="I6" t="n">
-        <v>418.97</v>
+        <v>442.48</v>
       </c>
       <c r="J6" t="n">
-        <v>428.54</v>
+        <v>454.8</v>
       </c>
       <c r="K6" t="n">
-        <v>402.79</v>
+        <v>421.63</v>
       </c>
       <c r="L6" t="n">
-        <v>461.64</v>
+        <v>497.45</v>
       </c>
       <c r="M6" t="n">
-        <v>55.36</v>
+        <v>56.29</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
@@ -801,46 +801,46 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ASML</t>
+          <t>LRCX</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Chips</t>
+          <t>Equipos chips</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1605.77</v>
+        <v>318.18</v>
       </c>
       <c r="D7" t="n">
         <v>95</v>
       </c>
       <c r="E7" t="n">
-        <v>3.59</v>
+        <v>5.27</v>
       </c>
       <c r="F7" t="n">
-        <v>0.59</v>
+        <v>1.13</v>
       </c>
       <c r="G7" t="n">
-        <v>66.76000000000001</v>
+        <v>14.58</v>
       </c>
       <c r="H7" t="n">
-        <v>4.16</v>
+        <v>4.58</v>
       </c>
       <c r="I7" t="n">
-        <v>1579.06</v>
+        <v>312.35</v>
       </c>
       <c r="J7" t="n">
-        <v>1622.46</v>
+        <v>321.82</v>
       </c>
       <c r="K7" t="n">
-        <v>1505.63</v>
+        <v>296.32</v>
       </c>
       <c r="L7" t="n">
-        <v>1772.68</v>
+        <v>354.62</v>
       </c>
       <c r="M7" t="n">
-        <v>58.08</v>
+        <v>62.23</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -861,7 +861,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>AMAT</t>
+          <t>KLAC</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -870,37 +870,37 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>449.68</v>
+        <v>1921.71</v>
       </c>
       <c r="D8" t="n">
         <v>95</v>
       </c>
       <c r="E8" t="n">
-        <v>5.48</v>
+        <v>4.32</v>
       </c>
       <c r="F8" t="n">
-        <v>0.74</v>
+        <v>1.13</v>
       </c>
       <c r="G8" t="n">
-        <v>19.85</v>
+        <v>83.25</v>
       </c>
       <c r="H8" t="n">
-        <v>4.41</v>
+        <v>4.33</v>
       </c>
       <c r="I8" t="n">
-        <v>441.74</v>
+        <v>1888.41</v>
       </c>
       <c r="J8" t="n">
-        <v>454.64</v>
+        <v>1942.52</v>
       </c>
       <c r="K8" t="n">
-        <v>419.9</v>
+        <v>1796.83</v>
       </c>
       <c r="L8" t="n">
-        <v>499.31</v>
+        <v>2129.84</v>
       </c>
       <c r="M8" t="n">
-        <v>63.65</v>
+        <v>54.23</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
@@ -921,50 +921,50 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>LRCX</t>
+          <t>QQQ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Equipos chips</t>
+          <t>ETF Nasdaq</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>318</v>
+        <v>738.3099999999999</v>
       </c>
       <c r="D9" t="n">
         <v>95</v>
       </c>
       <c r="E9" t="n">
-        <v>8.869999999999999</v>
+        <v>3.33</v>
       </c>
       <c r="F9" t="n">
-        <v>0.91</v>
+        <v>0.98</v>
       </c>
       <c r="G9" t="n">
-        <v>14.83</v>
+        <v>10.59</v>
       </c>
       <c r="H9" t="n">
-        <v>4.66</v>
+        <v>1.43</v>
       </c>
       <c r="I9" t="n">
-        <v>312.07</v>
+        <v>734.0700000000001</v>
       </c>
       <c r="J9" t="n">
-        <v>321.71</v>
+        <v>740.96</v>
       </c>
       <c r="K9" t="n">
-        <v>295.76</v>
+        <v>722.42</v>
       </c>
       <c r="L9" t="n">
-        <v>355.07</v>
+        <v>764.79</v>
       </c>
       <c r="M9" t="n">
-        <v>64.84999999999999</v>
+        <v>67.5</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>MEDIO</t>
+          <t>BAJO</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -981,50 +981,50 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>KLAC</t>
+          <t>SOXX</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Equipos chips</t>
+          <t>ETF Chips</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1927.63</v>
+        <v>569.08</v>
       </c>
       <c r="D10" t="n">
         <v>95</v>
       </c>
       <c r="E10" t="n">
-        <v>5.37</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="F10" t="n">
-        <v>0.83</v>
+        <v>0.87</v>
       </c>
       <c r="G10" t="n">
-        <v>87.69</v>
+        <v>23.01</v>
       </c>
       <c r="H10" t="n">
-        <v>4.55</v>
+        <v>4.04</v>
       </c>
       <c r="I10" t="n">
-        <v>1892.55</v>
+        <v>559.87</v>
       </c>
       <c r="J10" t="n">
-        <v>1949.55</v>
+        <v>574.83</v>
       </c>
       <c r="K10" t="n">
-        <v>1796.1</v>
+        <v>534.5599999999999</v>
       </c>
       <c r="L10" t="n">
-        <v>2146.85</v>
+        <v>626.62</v>
       </c>
       <c r="M10" t="n">
-        <v>61.11</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>BAJO</t>
+          <t>MEDIO</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1041,46 +1041,46 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>AVGO</t>
+          <t>TSLA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>IA / Chips</t>
+          <t>Autos / Tech</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>426.58</v>
+        <v>435.79</v>
       </c>
       <c r="D11" t="n">
         <v>92</v>
       </c>
       <c r="E11" t="n">
-        <v>2.11</v>
+        <v>4.29</v>
       </c>
       <c r="F11" t="n">
-        <v>0.95</v>
+        <v>0.86</v>
       </c>
       <c r="G11" t="n">
-        <v>16.19</v>
+        <v>16.45</v>
       </c>
       <c r="H11" t="n">
-        <v>3.8</v>
+        <v>3.77</v>
       </c>
       <c r="I11" t="n">
-        <v>420.1</v>
+        <v>429.21</v>
       </c>
       <c r="J11" t="n">
-        <v>430.63</v>
+        <v>439.9</v>
       </c>
       <c r="K11" t="n">
-        <v>402.29</v>
+        <v>411.12</v>
       </c>
       <c r="L11" t="n">
-        <v>467.06</v>
+        <v>476.92</v>
       </c>
       <c r="M11" t="n">
-        <v>56.65</v>
+        <v>52.96</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
@@ -1101,46 +1101,46 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>TSLA</t>
+          <t>SLB</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Autos / Tech</t>
+          <t>Energía</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>442.1</v>
+        <v>54.55</v>
       </c>
       <c r="D12" t="n">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="E12" t="n">
-        <v>5.95</v>
+        <v>-4.72</v>
       </c>
       <c r="F12" t="n">
-        <v>0.61</v>
+        <v>2.4</v>
       </c>
       <c r="G12" t="n">
-        <v>16.84</v>
+        <v>1.46</v>
       </c>
       <c r="H12" t="n">
-        <v>3.81</v>
+        <v>2.68</v>
       </c>
       <c r="I12" t="n">
-        <v>435.36</v>
+        <v>53.97</v>
       </c>
       <c r="J12" t="n">
-        <v>446.31</v>
+        <v>54.92</v>
       </c>
       <c r="K12" t="n">
-        <v>416.83</v>
+        <v>52.36</v>
       </c>
       <c r="L12" t="n">
-        <v>484.21</v>
+        <v>58.2</v>
       </c>
       <c r="M12" t="n">
-        <v>61.17</v>
+        <v>56.26</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
@@ -1161,7 +1161,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>META</t>
+          <t>AMZN</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1170,37 +1170,37 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>635.29</v>
+        <v>270.64</v>
       </c>
       <c r="D13" t="n">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="E13" t="n">
-        <v>5</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="F13" t="n">
-        <v>0.99</v>
+        <v>1.38</v>
       </c>
       <c r="G13" t="n">
-        <v>13.41</v>
+        <v>6.42</v>
       </c>
       <c r="H13" t="n">
-        <v>2.11</v>
+        <v>2.37</v>
       </c>
       <c r="I13" t="n">
-        <v>629.92</v>
+        <v>268.07</v>
       </c>
       <c r="J13" t="n">
-        <v>638.64</v>
+        <v>272.25</v>
       </c>
       <c r="K13" t="n">
-        <v>615.17</v>
+        <v>261</v>
       </c>
       <c r="L13" t="n">
-        <v>668.8200000000001</v>
+        <v>286.7</v>
       </c>
       <c r="M13" t="n">
-        <v>60.74</v>
+        <v>47.86</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
@@ -1221,46 +1221,46 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>QQQ</t>
+          <t>SOUN</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>ETF Nasdaq</t>
+          <t>IA</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>735.6</v>
+        <v>9</v>
       </c>
       <c r="D14" t="n">
-        <v>89</v>
+        <v>75</v>
       </c>
       <c r="E14" t="n">
-        <v>3.15</v>
+        <v>8.17</v>
       </c>
       <c r="F14" t="n">
-        <v>0.79</v>
+        <v>1.28</v>
       </c>
       <c r="G14" t="n">
-        <v>11.3</v>
+        <v>0.49</v>
       </c>
       <c r="H14" t="n">
-        <v>1.54</v>
+        <v>5.5</v>
       </c>
       <c r="I14" t="n">
-        <v>731.08</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J14" t="n">
-        <v>738.4299999999999</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="K14" t="n">
-        <v>718.65</v>
+        <v>8.26</v>
       </c>
       <c r="L14" t="n">
-        <v>763.86</v>
+        <v>10.24</v>
       </c>
       <c r="M14" t="n">
-        <v>72.36</v>
+        <v>52.11</v>
       </c>
       <c r="N14" t="inlineStr">
         <is>
@@ -1281,55 +1281,55 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>SOXX</t>
+          <t>ASML</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>ETF Chips</t>
+          <t>Chips</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>569.47</v>
+        <v>1612.76</v>
       </c>
       <c r="D15" t="n">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="E15" t="n">
-        <v>9.449999999999999</v>
+        <v>1.3</v>
       </c>
       <c r="F15" t="n">
-        <v>0.79</v>
+        <v>0.66</v>
       </c>
       <c r="G15" t="n">
-        <v>23.76</v>
+        <v>64.67</v>
       </c>
       <c r="H15" t="n">
-        <v>4.17</v>
+        <v>4.01</v>
       </c>
       <c r="I15" t="n">
-        <v>559.96</v>
+        <v>1586.89</v>
       </c>
       <c r="J15" t="n">
-        <v>575.41</v>
+        <v>1628.93</v>
       </c>
       <c r="K15" t="n">
-        <v>533.83</v>
+        <v>1515.76</v>
       </c>
       <c r="L15" t="n">
-        <v>628.88</v>
+        <v>1774.42</v>
       </c>
       <c r="M15" t="n">
-        <v>70.17</v>
+        <v>52.15</v>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>MEDIO</t>
+          <t>BAJO</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -1341,46 +1341,46 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>SOFI</t>
+          <t>SPY</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Fintech</t>
+          <t>ETF Mercado</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>16.97</v>
+        <v>756.48</v>
       </c>
       <c r="D16" t="n">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="E16" t="n">
-        <v>8.16</v>
+        <v>1.85</v>
       </c>
       <c r="F16" t="n">
-        <v>1.07</v>
+        <v>1.15</v>
       </c>
       <c r="G16" t="n">
-        <v>0.77</v>
+        <v>6.72</v>
       </c>
       <c r="H16" t="n">
-        <v>4.55</v>
+        <v>0.89</v>
       </c>
       <c r="I16" t="n">
-        <v>16.66</v>
+        <v>753.79</v>
       </c>
       <c r="J16" t="n">
-        <v>17.16</v>
+        <v>758.16</v>
       </c>
       <c r="K16" t="n">
-        <v>15.81</v>
+        <v>746.4</v>
       </c>
       <c r="L16" t="n">
-        <v>18.9</v>
+        <v>773.28</v>
       </c>
       <c r="M16" t="n">
-        <v>59.17</v>
+        <v>68.77</v>
       </c>
       <c r="N16" t="inlineStr">
         <is>
@@ -1389,7 +1389,7 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -1401,46 +1401,46 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>PLTR</t>
+          <t>CVX</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>IA / Software</t>
+          <t>Energía</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>143.34</v>
+        <v>182.46</v>
       </c>
       <c r="D17" t="n">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="E17" t="n">
-        <v>4.51</v>
+        <v>-4.48</v>
       </c>
       <c r="F17" t="n">
-        <v>1.2</v>
+        <v>1.35</v>
       </c>
       <c r="G17" t="n">
-        <v>5.21</v>
+        <v>4.22</v>
       </c>
       <c r="H17" t="n">
-        <v>3.63</v>
+        <v>2.31</v>
       </c>
       <c r="I17" t="n">
-        <v>141.26</v>
+        <v>180.77</v>
       </c>
       <c r="J17" t="n">
-        <v>144.64</v>
+        <v>183.51</v>
       </c>
       <c r="K17" t="n">
-        <v>135.53</v>
+        <v>176.13</v>
       </c>
       <c r="L17" t="n">
-        <v>156.35</v>
+        <v>193.01</v>
       </c>
       <c r="M17" t="n">
-        <v>59.95</v>
+        <v>53.64</v>
       </c>
       <c r="N17" t="inlineStr">
         <is>
@@ -1449,62 +1449,62 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>POSIBLE COMPRA</t>
+          <t>VIGILAR</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>SPY</t>
+          <t>NVDA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>ETF Mercado</t>
+          <t>IA / Chips</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>754.6</v>
+        <v>211.14</v>
       </c>
       <c r="D18" t="n">
-        <v>89</v>
+        <v>71</v>
       </c>
       <c r="E18" t="n">
-        <v>1.8</v>
+        <v>-3.81</v>
       </c>
       <c r="F18" t="n">
-        <v>0.74</v>
+        <v>1.41</v>
       </c>
       <c r="G18" t="n">
-        <v>6.94</v>
+        <v>7.81</v>
       </c>
       <c r="H18" t="n">
-        <v>0.92</v>
+        <v>3.7</v>
       </c>
       <c r="I18" t="n">
-        <v>751.83</v>
+        <v>208.02</v>
       </c>
       <c r="J18" t="n">
-        <v>756.33</v>
+        <v>213.09</v>
       </c>
       <c r="K18" t="n">
-        <v>744.2</v>
+        <v>199.43</v>
       </c>
       <c r="L18" t="n">
-        <v>771.9400000000001</v>
+        <v>230.66</v>
       </c>
       <c r="M18" t="n">
-        <v>71.16</v>
+        <v>46.25</v>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>MEDIO</t>
+          <t>BAJO</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
@@ -1514,70 +1514,74 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>POSIBLE COMPRA</t>
+          <t>VIGILAR</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>NVDA</t>
+          <t>GOOGL</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>IA / Chips</t>
+          <t>Tecnología</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>214.25</v>
+        <v>380.34</v>
       </c>
       <c r="D19" t="n">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="E19" t="n">
-        <v>-4.13</v>
+        <v>-1.89</v>
       </c>
       <c r="F19" t="n">
-        <v>0.87</v>
+        <v>1.62</v>
       </c>
       <c r="G19" t="n">
-        <v>7.78</v>
+        <v>9.82</v>
       </c>
       <c r="H19" t="n">
-        <v>3.63</v>
+        <v>2.58</v>
       </c>
       <c r="I19" t="n">
-        <v>211.14</v>
+        <v>376.41</v>
       </c>
       <c r="J19" t="n">
-        <v>216.19</v>
+        <v>382.79</v>
       </c>
       <c r="K19" t="n">
-        <v>202.58</v>
+        <v>365.62</v>
       </c>
       <c r="L19" t="n">
-        <v>233.69</v>
+        <v>404.88</v>
       </c>
       <c r="M19" t="n">
-        <v>52.51</v>
+        <v>35.01</v>
       </c>
       <c r="N19" t="inlineStr">
         <is>
           <t>BAJO</t>
         </is>
       </c>
-      <c r="O19" t="inlineStr"/>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>🔥</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>POSIBLE COMPRA</t>
+          <t>VIGILAR</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>SLB</t>
+          <t>XOM</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1586,37 +1590,37 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>55.12</v>
+        <v>145.26</v>
       </c>
       <c r="D20" t="n">
-        <v>76</v>
+        <v>66</v>
       </c>
       <c r="E20" t="n">
-        <v>-3.77</v>
+        <v>-6.46</v>
       </c>
       <c r="F20" t="n">
-        <v>1.15</v>
+        <v>0.67</v>
       </c>
       <c r="G20" t="n">
-        <v>1.49</v>
+        <v>4.17</v>
       </c>
       <c r="H20" t="n">
-        <v>2.7</v>
+        <v>2.87</v>
       </c>
       <c r="I20" t="n">
-        <v>54.53</v>
+        <v>143.59</v>
       </c>
       <c r="J20" t="n">
-        <v>55.49</v>
+        <v>146.3</v>
       </c>
       <c r="K20" t="n">
-        <v>52.89</v>
+        <v>139</v>
       </c>
       <c r="L20" t="n">
-        <v>58.84</v>
+        <v>155.69</v>
       </c>
       <c r="M20" t="n">
-        <v>60.69</v>
+        <v>52.3</v>
       </c>
       <c r="N20" t="inlineStr">
         <is>
@@ -1626,53 +1630,53 @@
       <c r="O20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>POSIBLE COMPRA</t>
+          <t>VIGILAR</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>GOOGL</t>
+          <t>OXY</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Tecnología</t>
+          <t>Energía</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>390.13</v>
+        <v>56.63</v>
       </c>
       <c r="D21" t="n">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="E21" t="n">
-        <v>0.31</v>
+        <v>-3.74</v>
       </c>
       <c r="F21" t="n">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="G21" t="n">
-        <v>9.390000000000001</v>
+        <v>1.78</v>
       </c>
       <c r="H21" t="n">
-        <v>2.41</v>
+        <v>3.14</v>
       </c>
       <c r="I21" t="n">
-        <v>386.38</v>
+        <v>55.92</v>
       </c>
       <c r="J21" t="n">
-        <v>392.48</v>
+        <v>57.08</v>
       </c>
       <c r="K21" t="n">
-        <v>376.05</v>
+        <v>53.96</v>
       </c>
       <c r="L21" t="n">
-        <v>413.59</v>
+        <v>61.08</v>
       </c>
       <c r="M21" t="n">
-        <v>43.58</v>
+        <v>64.08</v>
       </c>
       <c r="N21" t="inlineStr">
         <is>
@@ -1689,46 +1693,46 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>XOM</t>
+          <t>PYPL</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Energía</t>
+          <t>Pagos</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>146.96</v>
+        <v>44.75</v>
       </c>
       <c r="D22" t="n">
-        <v>66</v>
+        <v>52</v>
       </c>
       <c r="E22" t="n">
-        <v>-5.96</v>
+        <v>1.02</v>
       </c>
       <c r="F22" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.97</v>
       </c>
       <c r="G22" t="n">
-        <v>4.2</v>
+        <v>1</v>
       </c>
       <c r="H22" t="n">
-        <v>2.86</v>
+        <v>2.24</v>
       </c>
       <c r="I22" t="n">
-        <v>145.28</v>
+        <v>44.35</v>
       </c>
       <c r="J22" t="n">
-        <v>148.01</v>
+        <v>45</v>
       </c>
       <c r="K22" t="n">
-        <v>140.66</v>
+        <v>43.25</v>
       </c>
       <c r="L22" t="n">
-        <v>157.46</v>
+        <v>47.25</v>
       </c>
       <c r="M22" t="n">
-        <v>51.87</v>
+        <v>43</v>
       </c>
       <c r="N22" t="inlineStr">
         <is>
@@ -1738,116 +1742,120 @@
       <c r="O22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>VIGILAR</t>
+          <t>NO COMPRAR</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>CVX</t>
+          <t>COIN</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Energía</t>
+          <t>Cripto / Trading</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>183.03</v>
+        <v>189.03</v>
       </c>
       <c r="D23" t="n">
-        <v>66</v>
+        <v>46</v>
       </c>
       <c r="E23" t="n">
-        <v>-4.34</v>
+        <v>-2.34</v>
       </c>
       <c r="F23" t="n">
-        <v>0.86</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="G23" t="n">
-        <v>4.17</v>
+        <v>13.5</v>
       </c>
       <c r="H23" t="n">
-        <v>2.28</v>
+        <v>7.14</v>
       </c>
       <c r="I23" t="n">
-        <v>181.36</v>
+        <v>183.63</v>
       </c>
       <c r="J23" t="n">
-        <v>184.07</v>
+        <v>192.41</v>
       </c>
       <c r="K23" t="n">
-        <v>176.77</v>
+        <v>168.78</v>
       </c>
       <c r="L23" t="n">
-        <v>193.46</v>
+        <v>222.78</v>
       </c>
       <c r="M23" t="n">
-        <v>53.17</v>
+        <v>44.3</v>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>BAJO</t>
+          <t>MEDIO</t>
         </is>
       </c>
       <c r="O23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>VIGILAR</t>
+          <t>NO COMPRAR</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>OXY</t>
+          <t>AI</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Energía</t>
+          <t>IA</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>57.32</v>
+        <v>10.77</v>
       </c>
       <c r="D24" t="n">
-        <v>66</v>
+        <v>95</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.63</v>
+        <v>15.43</v>
       </c>
       <c r="F24" t="n">
-        <v>0.88</v>
+        <v>2.15</v>
       </c>
       <c r="G24" t="n">
-        <v>1.78</v>
+        <v>0.54</v>
       </c>
       <c r="H24" t="n">
-        <v>3.1</v>
+        <v>5</v>
       </c>
       <c r="I24" t="n">
-        <v>56.61</v>
+        <v>10.55</v>
       </c>
       <c r="J24" t="n">
-        <v>57.76</v>
+        <v>10.9</v>
       </c>
       <c r="K24" t="n">
-        <v>54.65</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="L24" t="n">
-        <v>61.76</v>
+        <v>12.12</v>
       </c>
       <c r="M24" t="n">
-        <v>63</v>
+        <v>60.77</v>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>BAJO</t>
-        </is>
-      </c>
-      <c r="O24" t="inlineStr"/>
+          <t>ALTO</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>🔥🔥</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>VIGILAR</t>
@@ -1857,168 +1865,180 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>COIN</t>
+          <t>HOOD</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Cripto / Trading</t>
+          <t>Trading</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>182.25</v>
+        <v>94.3</v>
       </c>
       <c r="D25" t="n">
-        <v>46</v>
+        <v>91</v>
       </c>
       <c r="E25" t="n">
-        <v>-4.73</v>
+        <v>24.21</v>
       </c>
       <c r="F25" t="n">
-        <v>0.9399999999999999</v>
+        <v>2.55</v>
       </c>
       <c r="G25" t="n">
-        <v>13.9</v>
+        <v>4.93</v>
       </c>
       <c r="H25" t="n">
-        <v>7.63</v>
+        <v>5.23</v>
       </c>
       <c r="I25" t="n">
-        <v>176.69</v>
+        <v>92.33</v>
       </c>
       <c r="J25" t="n">
-        <v>185.73</v>
+        <v>95.53</v>
       </c>
       <c r="K25" t="n">
-        <v>161.4</v>
+        <v>86.91</v>
       </c>
       <c r="L25" t="n">
-        <v>217.01</v>
+        <v>106.62</v>
       </c>
       <c r="M25" t="n">
-        <v>45.04</v>
+        <v>70.09</v>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>MEDIO</t>
-        </is>
-      </c>
-      <c r="O25" t="inlineStr"/>
+          <t>ALTO</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>🔥🔥</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>NO COMPRAR</t>
+          <t>VIGILAR</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>SOUN</t>
+          <t>PLTR</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>IA</t>
+          <t>IA / Software</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>8.56</v>
+        <v>156.54</v>
       </c>
       <c r="D26" t="n">
-        <v>46</v>
+        <v>89</v>
       </c>
       <c r="E26" t="n">
-        <v>1.3</v>
+        <v>13.92</v>
       </c>
       <c r="F26" t="n">
-        <v>0.9</v>
+        <v>2.03</v>
       </c>
       <c r="G26" t="n">
-        <v>0.54</v>
+        <v>6</v>
       </c>
       <c r="H26" t="n">
-        <v>6.3</v>
+        <v>3.83</v>
       </c>
       <c r="I26" t="n">
-        <v>8.34</v>
+        <v>154.14</v>
       </c>
       <c r="J26" t="n">
-        <v>8.69</v>
+        <v>158.04</v>
       </c>
       <c r="K26" t="n">
-        <v>7.75</v>
+        <v>147.54</v>
       </c>
       <c r="L26" t="n">
-        <v>9.91</v>
+        <v>171.55</v>
       </c>
       <c r="M26" t="n">
-        <v>33.02</v>
+        <v>71.27</v>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>MEDIO</t>
-        </is>
-      </c>
-      <c r="O26" t="inlineStr"/>
+          <t>ALTO</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>🔥🔥</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>NO COMPRAR</t>
+          <t>VIGILAR</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>PYPL</t>
+          <t>SOFI</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Pagos</t>
+          <t>Fintech</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>44.46</v>
+        <v>18.22</v>
       </c>
       <c r="D27" t="n">
-        <v>44</v>
+        <v>89</v>
       </c>
       <c r="E27" t="n">
-        <v>0.19</v>
+        <v>16.42</v>
       </c>
       <c r="F27" t="n">
-        <v>1</v>
+        <v>2.25</v>
       </c>
       <c r="G27" t="n">
-        <v>1.02</v>
+        <v>0.85</v>
       </c>
       <c r="H27" t="n">
-        <v>2.29</v>
+        <v>4.66</v>
       </c>
       <c r="I27" t="n">
-        <v>44.05</v>
+        <v>17.88</v>
       </c>
       <c r="J27" t="n">
-        <v>44.71</v>
+        <v>18.43</v>
       </c>
       <c r="K27" t="n">
-        <v>42.93</v>
+        <v>16.95</v>
       </c>
       <c r="L27" t="n">
-        <v>47.01</v>
+        <v>20.34</v>
       </c>
       <c r="M27" t="n">
-        <v>32.36</v>
+        <v>69.63</v>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>BAJO</t>
-        </is>
-      </c>
-      <c r="O27" t="inlineStr"/>
+          <t>ALTO</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>🔥🔥</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>NO COMPRAR</t>
+          <t>VIGILAR</t>
         </is>
       </c>
     </row>
@@ -2034,37 +2054,37 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>41.3</v>
+        <v>46.09</v>
       </c>
       <c r="D28" t="n">
         <v>83</v>
       </c>
       <c r="E28" t="n">
-        <v>23.43</v>
+        <v>37.75</v>
       </c>
       <c r="F28" t="n">
-        <v>1.67</v>
+        <v>2.04</v>
       </c>
       <c r="G28" t="n">
-        <v>2.57</v>
+        <v>2.84</v>
       </c>
       <c r="H28" t="n">
-        <v>6.23</v>
+        <v>6.16</v>
       </c>
       <c r="I28" t="n">
-        <v>40.27</v>
+        <v>44.96</v>
       </c>
       <c r="J28" t="n">
-        <v>41.94</v>
+        <v>46.8</v>
       </c>
       <c r="K28" t="n">
-        <v>37.44</v>
+        <v>41.83</v>
       </c>
       <c r="L28" t="n">
-        <v>47.73</v>
+        <v>53.18</v>
       </c>
       <c r="M28" t="n">
-        <v>69.83</v>
+        <v>73.93000000000001</v>
       </c>
       <c r="N28" t="inlineStr">
         <is>
@@ -2085,46 +2105,46 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>MU</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>IA / Chips</t>
+          <t>Memoria / Chips</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>518.09</v>
+        <v>971</v>
       </c>
       <c r="D29" t="n">
         <v>89</v>
       </c>
       <c r="E29" t="n">
-        <v>15.75</v>
+        <v>27.41</v>
       </c>
       <c r="F29" t="n">
-        <v>0.76</v>
+        <v>1.08</v>
       </c>
       <c r="G29" t="n">
-        <v>29.76</v>
+        <v>64.91</v>
       </c>
       <c r="H29" t="n">
-        <v>5.74</v>
+        <v>6.68</v>
       </c>
       <c r="I29" t="n">
-        <v>506.19</v>
+        <v>945.04</v>
       </c>
       <c r="J29" t="n">
-        <v>525.53</v>
+        <v>987.23</v>
       </c>
       <c r="K29" t="n">
-        <v>473.45</v>
+        <v>873.64</v>
       </c>
       <c r="L29" t="n">
-        <v>592.48</v>
+        <v>1133.26</v>
       </c>
       <c r="M29" t="n">
-        <v>74.45</v>
+        <v>70.09</v>
       </c>
       <c r="N29" t="inlineStr">
         <is>
@@ -2145,46 +2165,46 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>UPST</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Fintech IA</t>
+          <t>IA / Chips</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>32.69</v>
+        <v>516.1</v>
       </c>
       <c r="D30" t="n">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="E30" t="n">
-        <v>13.35</v>
+        <v>14.79</v>
       </c>
       <c r="F30" t="n">
-        <v>1.05</v>
+        <v>0.55</v>
       </c>
       <c r="G30" t="n">
-        <v>1.87</v>
+        <v>27.67</v>
       </c>
       <c r="H30" t="n">
-        <v>5.72</v>
+        <v>5.36</v>
       </c>
       <c r="I30" t="n">
-        <v>31.94</v>
+        <v>505.03</v>
       </c>
       <c r="J30" t="n">
-        <v>33.16</v>
+        <v>523.02</v>
       </c>
       <c r="K30" t="n">
-        <v>29.89</v>
+        <v>474.6</v>
       </c>
       <c r="L30" t="n">
-        <v>37.36</v>
+        <v>585.27</v>
       </c>
       <c r="M30" t="n">
-        <v>65.59999999999999</v>
+        <v>66.97</v>
       </c>
       <c r="N30" t="inlineStr">
         <is>
@@ -2214,37 +2234,37 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>243.29</v>
+        <v>251.02</v>
       </c>
       <c r="D31" t="n">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="E31" t="n">
-        <v>20.14</v>
+        <v>17.62</v>
       </c>
       <c r="F31" t="n">
-        <v>0.55</v>
+        <v>0.99</v>
       </c>
       <c r="G31" t="n">
-        <v>19.58</v>
+        <v>18.95</v>
       </c>
       <c r="H31" t="n">
-        <v>8.050000000000001</v>
+        <v>7.55</v>
       </c>
       <c r="I31" t="n">
-        <v>235.46</v>
+        <v>243.44</v>
       </c>
       <c r="J31" t="n">
-        <v>248.19</v>
+        <v>255.76</v>
       </c>
       <c r="K31" t="n">
-        <v>213.92</v>
+        <v>222.6</v>
       </c>
       <c r="L31" t="n">
-        <v>292.24</v>
+        <v>298.39</v>
       </c>
       <c r="M31" t="n">
-        <v>62.11</v>
+        <v>60.01</v>
       </c>
       <c r="N31" t="inlineStr">
         <is>
@@ -2274,37 +2294,37 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>312.51</v>
+        <v>312.06</v>
       </c>
       <c r="D32" t="n">
         <v>82</v>
       </c>
       <c r="E32" t="n">
-        <v>3.39</v>
+        <v>2.32</v>
       </c>
       <c r="F32" t="n">
-        <v>0.89</v>
+        <v>1.17</v>
       </c>
       <c r="G32" t="n">
-        <v>5.09</v>
+        <v>4.97</v>
       </c>
       <c r="H32" t="n">
-        <v>1.63</v>
+        <v>1.59</v>
       </c>
       <c r="I32" t="n">
-        <v>310.47</v>
+        <v>310.07</v>
       </c>
       <c r="J32" t="n">
-        <v>313.78</v>
+        <v>313.3</v>
       </c>
       <c r="K32" t="n">
-        <v>304.87</v>
+        <v>304.61</v>
       </c>
       <c r="L32" t="n">
-        <v>325.25</v>
+        <v>324.47</v>
       </c>
       <c r="M32" t="n">
-        <v>88.20999999999999</v>
+        <v>84.28</v>
       </c>
       <c r="N32" t="inlineStr">
         <is>
@@ -2325,57 +2345,53 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>MU</t>
+          <t>RKLB</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Memoria / Chips</t>
+          <t>Espacial</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>923.52</v>
+        <v>143.48</v>
       </c>
       <c r="D33" t="n">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="E33" t="n">
-        <v>26.17</v>
+        <v>14.37</v>
       </c>
       <c r="F33" t="n">
-        <v>0.89</v>
+        <v>1.15</v>
       </c>
       <c r="G33" t="n">
-        <v>67.98</v>
+        <v>12.37</v>
       </c>
       <c r="H33" t="n">
-        <v>7.36</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="I33" t="n">
-        <v>896.33</v>
+        <v>138.53</v>
       </c>
       <c r="J33" t="n">
-        <v>940.52</v>
+        <v>146.57</v>
       </c>
       <c r="K33" t="n">
-        <v>821.54</v>
+        <v>124.92</v>
       </c>
       <c r="L33" t="n">
-        <v>1093.48</v>
+        <v>174.41</v>
       </c>
       <c r="M33" t="n">
-        <v>72.68000000000001</v>
+        <v>70.56</v>
       </c>
       <c r="N33" t="inlineStr">
         <is>
           <t>ALTO</t>
         </is>
       </c>
-      <c r="O33" t="inlineStr">
-        <is>
-          <t>🔥</t>
-        </is>
-      </c>
+      <c r="O33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>VIGILAR</t>
@@ -2385,7 +2401,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>INTC</t>
+          <t>ARM</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2394,37 +2410,37 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>120.89</v>
+        <v>353.29</v>
       </c>
       <c r="D34" t="n">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="E34" t="n">
-        <v>1.62</v>
+        <v>18.46</v>
       </c>
       <c r="F34" t="n">
-        <v>0.67</v>
+        <v>0.85</v>
       </c>
       <c r="G34" t="n">
-        <v>9.9</v>
+        <v>23.5</v>
       </c>
       <c r="H34" t="n">
-        <v>8.19</v>
+        <v>6.65</v>
       </c>
       <c r="I34" t="n">
-        <v>116.93</v>
+        <v>343.89</v>
       </c>
       <c r="J34" t="n">
-        <v>123.36</v>
+        <v>359.16</v>
       </c>
       <c r="K34" t="n">
-        <v>106.04</v>
+        <v>318.04</v>
       </c>
       <c r="L34" t="n">
-        <v>145.63</v>
+        <v>412.04</v>
       </c>
       <c r="M34" t="n">
-        <v>59.39</v>
+        <v>80.92</v>
       </c>
       <c r="N34" t="inlineStr">
         <is>
@@ -2441,46 +2457,46 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>RKLB</t>
+          <t>UPST</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Espacial</t>
+          <t>Fintech IA</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>148.03</v>
+        <v>33.79</v>
       </c>
       <c r="D35" t="n">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="E35" t="n">
-        <v>10.24</v>
+        <v>17.12</v>
       </c>
       <c r="F35" t="n">
-        <v>0.6899999999999999</v>
+        <v>1.13</v>
       </c>
       <c r="G35" t="n">
-        <v>13.31</v>
+        <v>1.9</v>
       </c>
       <c r="H35" t="n">
-        <v>8.99</v>
+        <v>5.61</v>
       </c>
       <c r="I35" t="n">
-        <v>142.71</v>
+        <v>33.03</v>
       </c>
       <c r="J35" t="n">
-        <v>151.36</v>
+        <v>34.26</v>
       </c>
       <c r="K35" t="n">
-        <v>128.07</v>
+        <v>30.95</v>
       </c>
       <c r="L35" t="n">
-        <v>181.29</v>
+        <v>38.53</v>
       </c>
       <c r="M35" t="n">
-        <v>80.26000000000001</v>
+        <v>68.73999999999999</v>
       </c>
       <c r="N35" t="inlineStr">
         <is>
@@ -2497,46 +2513,46 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>ARM</t>
+          <t>IONQ</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Chips</t>
+          <t>Computación cuántica</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>335.27</v>
+        <v>72.06999999999999</v>
       </c>
       <c r="D36" t="n">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="E36" t="n">
-        <v>30.59</v>
+        <v>22.38</v>
       </c>
       <c r="F36" t="n">
-        <v>1.18</v>
+        <v>0.79</v>
       </c>
       <c r="G36" t="n">
-        <v>22.77</v>
+        <v>6.07</v>
       </c>
       <c r="H36" t="n">
-        <v>6.79</v>
+        <v>8.42</v>
       </c>
       <c r="I36" t="n">
-        <v>326.16</v>
+        <v>69.64</v>
       </c>
       <c r="J36" t="n">
-        <v>340.96</v>
+        <v>73.59</v>
       </c>
       <c r="K36" t="n">
-        <v>301.11</v>
+        <v>62.97</v>
       </c>
       <c r="L36" t="n">
-        <v>392.2</v>
+        <v>87.23999999999999</v>
       </c>
       <c r="M36" t="n">
-        <v>79.26000000000001</v>
+        <v>75.83</v>
       </c>
       <c r="N36" t="inlineStr">
         <is>
@@ -2546,53 +2562,53 @@
       <c r="O36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>VIGILAR</t>
+          <t>NO COMPRAR</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>IONQ</t>
+          <t>INTC</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Computación cuántica</t>
+          <t>Chips</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>70.14</v>
+        <v>114.68</v>
       </c>
       <c r="D37" t="n">
-        <v>58</v>
+        <v>44</v>
       </c>
       <c r="E37" t="n">
-        <v>33.68</v>
+        <v>-3.22</v>
       </c>
       <c r="F37" t="n">
-        <v>0.83</v>
+        <v>1.1</v>
       </c>
       <c r="G37" t="n">
-        <v>5.93</v>
+        <v>9.34</v>
       </c>
       <c r="H37" t="n">
-        <v>8.460000000000001</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="I37" t="n">
-        <v>67.77</v>
+        <v>110.94</v>
       </c>
       <c r="J37" t="n">
-        <v>71.62</v>
+        <v>117.01</v>
       </c>
       <c r="K37" t="n">
-        <v>61.24</v>
+        <v>100.67</v>
       </c>
       <c r="L37" t="n">
-        <v>84.97</v>
+        <v>138.02</v>
       </c>
       <c r="M37" t="n">
-        <v>75.63</v>
+        <v>39.94</v>
       </c>
       <c r="N37" t="inlineStr">
         <is>

--- a/analisis_acciones.xlsx
+++ b/analisis_acciones.xlsx
@@ -501,46 +501,46 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>AVGO</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Tecnología</t>
+          <t>IA / Chips</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>450.24</v>
+        <v>459.97</v>
       </c>
       <c r="D2" t="n">
         <v>95</v>
       </c>
       <c r="E2" t="n">
-        <v>7.43</v>
+        <v>11.07</v>
       </c>
       <c r="F2" t="n">
-        <v>2.22</v>
+        <v>1.43</v>
       </c>
       <c r="G2" t="n">
-        <v>11.66</v>
+        <v>17.26</v>
       </c>
       <c r="H2" t="n">
-        <v>2.59</v>
+        <v>3.75</v>
       </c>
       <c r="I2" t="n">
-        <v>445.57</v>
+        <v>453.06</v>
       </c>
       <c r="J2" t="n">
-        <v>453.16</v>
+        <v>464.29</v>
       </c>
       <c r="K2" t="n">
-        <v>432.74</v>
+        <v>434.07</v>
       </c>
       <c r="L2" t="n">
-        <v>479.4</v>
+        <v>503.13</v>
       </c>
       <c r="M2" t="n">
-        <v>71.70999999999999</v>
+        <v>63.16</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -561,46 +561,46 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AVGO</t>
+          <t>TSM</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>IA / Chips</t>
+          <t>Chips</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>446.77</v>
+        <v>435.63</v>
       </c>
       <c r="D3" t="n">
         <v>95</v>
       </c>
       <c r="E3" t="n">
-        <v>7.77</v>
+        <v>7.69</v>
       </c>
       <c r="F3" t="n">
-        <v>2.13</v>
+        <v>1.35</v>
       </c>
       <c r="G3" t="n">
-        <v>16.18</v>
+        <v>15.76</v>
       </c>
       <c r="H3" t="n">
         <v>3.62</v>
       </c>
       <c r="I3" t="n">
-        <v>440.3</v>
+        <v>429.33</v>
       </c>
       <c r="J3" t="n">
-        <v>450.82</v>
+        <v>439.57</v>
       </c>
       <c r="K3" t="n">
-        <v>422.5</v>
+        <v>412</v>
       </c>
       <c r="L3" t="n">
-        <v>487.22</v>
+        <v>475.02</v>
       </c>
       <c r="M3" t="n">
-        <v>57.75</v>
+        <v>63.65</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -621,55 +621,55 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>META</t>
+          <t>AMAT</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Tecnología</t>
+          <t>Equipos chips</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>632.51</v>
+        <v>458.17</v>
       </c>
       <c r="D4" t="n">
         <v>95</v>
       </c>
       <c r="E4" t="n">
-        <v>4.14</v>
+        <v>6.02</v>
       </c>
       <c r="F4" t="n">
-        <v>1.31</v>
+        <v>0.78</v>
       </c>
       <c r="G4" t="n">
-        <v>13.5</v>
+        <v>19.86</v>
       </c>
       <c r="H4" t="n">
-        <v>2.13</v>
+        <v>4.33</v>
       </c>
       <c r="I4" t="n">
-        <v>627.11</v>
+        <v>450.23</v>
       </c>
       <c r="J4" t="n">
-        <v>635.88</v>
+        <v>463.14</v>
       </c>
       <c r="K4" t="n">
-        <v>612.26</v>
+        <v>428.38</v>
       </c>
       <c r="L4" t="n">
-        <v>666.26</v>
+        <v>507.82</v>
       </c>
       <c r="M4" t="n">
-        <v>64.02</v>
+        <v>56.27</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>BAJO</t>
+          <t>MEDIO</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥🔥</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -681,46 +681,46 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>LRCX</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Chips</t>
+          <t>Equipos chips</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>418.45</v>
+        <v>317.12</v>
       </c>
       <c r="D5" t="n">
         <v>95</v>
       </c>
       <c r="E5" t="n">
-        <v>2.78</v>
+        <v>3.85</v>
       </c>
       <c r="F5" t="n">
-        <v>0.75</v>
+        <v>0.87</v>
       </c>
       <c r="G5" t="n">
-        <v>14.5</v>
+        <v>15.03</v>
       </c>
       <c r="H5" t="n">
-        <v>3.47</v>
+        <v>4.74</v>
       </c>
       <c r="I5" t="n">
-        <v>412.65</v>
+        <v>311.11</v>
       </c>
       <c r="J5" t="n">
-        <v>422.08</v>
+        <v>320.88</v>
       </c>
       <c r="K5" t="n">
-        <v>396.69</v>
+        <v>294.57</v>
       </c>
       <c r="L5" t="n">
-        <v>454.71</v>
+        <v>354.7</v>
       </c>
       <c r="M5" t="n">
-        <v>53.26</v>
+        <v>60.78</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
@@ -741,7 +741,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AMAT</t>
+          <t>KLAC</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -750,37 +750,37 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>450.06</v>
+        <v>1940.04</v>
       </c>
       <c r="D6" t="n">
         <v>95</v>
       </c>
       <c r="E6" t="n">
-        <v>5.31</v>
+        <v>2.74</v>
       </c>
       <c r="F6" t="n">
-        <v>0.82</v>
+        <v>0.73</v>
       </c>
       <c r="G6" t="n">
-        <v>18.96</v>
+        <v>83.84</v>
       </c>
       <c r="H6" t="n">
-        <v>4.21</v>
+        <v>4.32</v>
       </c>
       <c r="I6" t="n">
-        <v>442.48</v>
+        <v>1906.5</v>
       </c>
       <c r="J6" t="n">
-        <v>454.8</v>
+        <v>1961</v>
       </c>
       <c r="K6" t="n">
-        <v>421.63</v>
+        <v>1814.28</v>
       </c>
       <c r="L6" t="n">
-        <v>497.45</v>
+        <v>2149.64</v>
       </c>
       <c r="M6" t="n">
-        <v>56.29</v>
+        <v>57.55</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
@@ -801,50 +801,50 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>LRCX</t>
+          <t>QQQ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Equipos chips</t>
+          <t>ETF Nasdaq</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>318.18</v>
+        <v>742.74</v>
       </c>
       <c r="D7" t="n">
         <v>95</v>
       </c>
       <c r="E7" t="n">
-        <v>5.27</v>
+        <v>3.51</v>
       </c>
       <c r="F7" t="n">
-        <v>1.13</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="G7" t="n">
-        <v>14.58</v>
+        <v>10.88</v>
       </c>
       <c r="H7" t="n">
-        <v>4.58</v>
+        <v>1.46</v>
       </c>
       <c r="I7" t="n">
-        <v>312.35</v>
+        <v>738.39</v>
       </c>
       <c r="J7" t="n">
-        <v>321.82</v>
+        <v>745.46</v>
       </c>
       <c r="K7" t="n">
-        <v>296.32</v>
+        <v>726.42</v>
       </c>
       <c r="L7" t="n">
-        <v>354.62</v>
+        <v>769.9299999999999</v>
       </c>
       <c r="M7" t="n">
-        <v>62.23</v>
+        <v>68.47</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>BAJO</t>
+          <t>MEDIO</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -861,50 +861,50 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>KLAC</t>
+          <t>SOXX</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Equipos chips</t>
+          <t>ETF Chips</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1921.71</v>
+        <v>571.9299999999999</v>
       </c>
       <c r="D8" t="n">
         <v>95</v>
       </c>
       <c r="E8" t="n">
-        <v>4.32</v>
+        <v>6.44</v>
       </c>
       <c r="F8" t="n">
-        <v>1.13</v>
+        <v>0.8</v>
       </c>
       <c r="G8" t="n">
-        <v>83.25</v>
+        <v>23.53</v>
       </c>
       <c r="H8" t="n">
-        <v>4.33</v>
+        <v>4.11</v>
       </c>
       <c r="I8" t="n">
-        <v>1888.41</v>
+        <v>562.52</v>
       </c>
       <c r="J8" t="n">
-        <v>1942.52</v>
+        <v>577.8099999999999</v>
       </c>
       <c r="K8" t="n">
-        <v>1796.83</v>
+        <v>536.64</v>
       </c>
       <c r="L8" t="n">
-        <v>2129.84</v>
+        <v>630.75</v>
       </c>
       <c r="M8" t="n">
-        <v>54.23</v>
+        <v>62.72</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>BAJO</t>
+          <t>MEDIO</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -921,46 +921,46 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>QQQ</t>
+          <t>NVDA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ETF Nasdaq</t>
+          <t>IA / Chips</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>738.3099999999999</v>
+        <v>224.36</v>
       </c>
       <c r="D9" t="n">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="E9" t="n">
-        <v>3.33</v>
+        <v>4.19</v>
       </c>
       <c r="F9" t="n">
-        <v>0.98</v>
+        <v>1.16</v>
       </c>
       <c r="G9" t="n">
-        <v>10.59</v>
+        <v>8.19</v>
       </c>
       <c r="H9" t="n">
-        <v>1.43</v>
+        <v>3.65</v>
       </c>
       <c r="I9" t="n">
-        <v>734.0700000000001</v>
+        <v>221.08</v>
       </c>
       <c r="J9" t="n">
-        <v>740.96</v>
+        <v>226.41</v>
       </c>
       <c r="K9" t="n">
-        <v>722.42</v>
+        <v>212.08</v>
       </c>
       <c r="L9" t="n">
-        <v>764.79</v>
+        <v>244.83</v>
       </c>
       <c r="M9" t="n">
-        <v>67.5</v>
+        <v>53.9</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
@@ -981,46 +981,46 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SOXX</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ETF Chips</t>
+          <t>IA / Chips</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>569.08</v>
+        <v>510.13</v>
       </c>
       <c r="D10" t="n">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="E10" t="n">
-        <v>8.460000000000001</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="F10" t="n">
-        <v>0.87</v>
+        <v>0.83</v>
       </c>
       <c r="G10" t="n">
-        <v>23.01</v>
+        <v>28.55</v>
       </c>
       <c r="H10" t="n">
-        <v>4.04</v>
+        <v>5.6</v>
       </c>
       <c r="I10" t="n">
-        <v>559.87</v>
+        <v>498.71</v>
       </c>
       <c r="J10" t="n">
-        <v>574.83</v>
+        <v>517.27</v>
       </c>
       <c r="K10" t="n">
-        <v>534.5599999999999</v>
+        <v>467.3</v>
       </c>
       <c r="L10" t="n">
-        <v>626.62</v>
+        <v>581.51</v>
       </c>
       <c r="M10" t="n">
-        <v>64.90000000000001</v>
+        <v>64.12</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
@@ -1041,46 +1041,46 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>TSLA</t>
+          <t>PYPL</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Autos / Tech</t>
+          <t>Pagos</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>435.79</v>
+        <v>45.19</v>
       </c>
       <c r="D11" t="n">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="E11" t="n">
-        <v>4.29</v>
+        <v>2.17</v>
       </c>
       <c r="F11" t="n">
-        <v>0.86</v>
+        <v>1</v>
       </c>
       <c r="G11" t="n">
-        <v>16.45</v>
+        <v>1.09</v>
       </c>
       <c r="H11" t="n">
-        <v>3.77</v>
+        <v>2.42</v>
       </c>
       <c r="I11" t="n">
-        <v>429.21</v>
+        <v>44.75</v>
       </c>
       <c r="J11" t="n">
-        <v>439.9</v>
+        <v>45.46</v>
       </c>
       <c r="K11" t="n">
-        <v>411.12</v>
+        <v>43.55</v>
       </c>
       <c r="L11" t="n">
-        <v>476.92</v>
+        <v>47.92</v>
       </c>
       <c r="M11" t="n">
-        <v>52.96</v>
+        <v>51.31</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
@@ -1101,46 +1101,46 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SLB</t>
+          <t>ASML</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Energía</t>
+          <t>Chips</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>54.55</v>
+        <v>1628.57</v>
       </c>
       <c r="D12" t="n">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.72</v>
+        <v>-0.27</v>
       </c>
       <c r="F12" t="n">
-        <v>2.4</v>
+        <v>0.65</v>
       </c>
       <c r="G12" t="n">
-        <v>1.46</v>
+        <v>63.97</v>
       </c>
       <c r="H12" t="n">
-        <v>2.68</v>
+        <v>3.93</v>
       </c>
       <c r="I12" t="n">
-        <v>53.97</v>
+        <v>1602.98</v>
       </c>
       <c r="J12" t="n">
-        <v>54.92</v>
+        <v>1644.56</v>
       </c>
       <c r="K12" t="n">
-        <v>52.36</v>
+        <v>1532.62</v>
       </c>
       <c r="L12" t="n">
-        <v>58.2</v>
+        <v>1788.49</v>
       </c>
       <c r="M12" t="n">
-        <v>56.26</v>
+        <v>56.64</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
@@ -1149,7 +1149,7 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1161,46 +1161,46 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>AMZN</t>
+          <t>OXY</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Tecnología</t>
+          <t>Energía</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>270.64</v>
+        <v>58.92</v>
       </c>
       <c r="D13" t="n">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="E13" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.19</v>
       </c>
       <c r="F13" t="n">
-        <v>1.38</v>
+        <v>0.99</v>
       </c>
       <c r="G13" t="n">
-        <v>6.42</v>
+        <v>1.84</v>
       </c>
       <c r="H13" t="n">
-        <v>2.37</v>
+        <v>3.12</v>
       </c>
       <c r="I13" t="n">
-        <v>268.07</v>
+        <v>58.18</v>
       </c>
       <c r="J13" t="n">
-        <v>272.25</v>
+        <v>59.38</v>
       </c>
       <c r="K13" t="n">
-        <v>261</v>
+        <v>56.16</v>
       </c>
       <c r="L13" t="n">
-        <v>286.7</v>
+        <v>63.52</v>
       </c>
       <c r="M13" t="n">
-        <v>47.86</v>
+        <v>64.58</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
@@ -1209,7 +1209,7 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1221,46 +1221,46 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>SOUN</t>
+          <t>SPY</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>IA</t>
+          <t>ETF Mercado</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>9</v>
+        <v>758.54</v>
       </c>
       <c r="D14" t="n">
-        <v>75</v>
+        <v>89</v>
       </c>
       <c r="E14" t="n">
-        <v>8.17</v>
+        <v>1.73</v>
       </c>
       <c r="F14" t="n">
-        <v>1.28</v>
+        <v>0.82</v>
       </c>
       <c r="G14" t="n">
-        <v>0.49</v>
+        <v>6.81</v>
       </c>
       <c r="H14" t="n">
-        <v>5.5</v>
+        <v>0.9</v>
       </c>
       <c r="I14" t="n">
-        <v>8.800000000000001</v>
+        <v>755.8200000000001</v>
       </c>
       <c r="J14" t="n">
-        <v>9.119999999999999</v>
+        <v>760.24</v>
       </c>
       <c r="K14" t="n">
-        <v>8.26</v>
+        <v>748.33</v>
       </c>
       <c r="L14" t="n">
-        <v>10.24</v>
+        <v>775.5599999999999</v>
       </c>
       <c r="M14" t="n">
-        <v>52.11</v>
+        <v>69</v>
       </c>
       <c r="N14" t="inlineStr">
         <is>
@@ -1269,7 +1269,7 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -1281,50 +1281,50 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ASML</t>
+          <t>AAPL</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Chips</t>
+          <t>Tecnología</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1612.76</v>
+        <v>306.31</v>
       </c>
       <c r="D15" t="n">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="E15" t="n">
-        <v>1.3</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="F15" t="n">
-        <v>0.66</v>
+        <v>0.93</v>
       </c>
       <c r="G15" t="n">
-        <v>64.67</v>
+        <v>5.21</v>
       </c>
       <c r="H15" t="n">
-        <v>4.01</v>
+        <v>1.7</v>
       </c>
       <c r="I15" t="n">
-        <v>1586.89</v>
+        <v>304.23</v>
       </c>
       <c r="J15" t="n">
-        <v>1628.93</v>
+        <v>307.61</v>
       </c>
       <c r="K15" t="n">
-        <v>1515.76</v>
+        <v>298.5</v>
       </c>
       <c r="L15" t="n">
-        <v>1774.42</v>
+        <v>319.33</v>
       </c>
       <c r="M15" t="n">
-        <v>52.15</v>
+        <v>70.58</v>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>BAJO</t>
+          <t>MEDIO</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
@@ -1341,50 +1341,50 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>SPY</t>
+          <t>META</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>ETF Mercado</t>
+          <t>Tecnología</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>756.48</v>
+        <v>600.47</v>
       </c>
       <c r="D16" t="n">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="E16" t="n">
-        <v>1.85</v>
+        <v>-1.6</v>
       </c>
       <c r="F16" t="n">
-        <v>1.15</v>
+        <v>1.8</v>
       </c>
       <c r="G16" t="n">
-        <v>6.72</v>
+        <v>15.26</v>
       </c>
       <c r="H16" t="n">
-        <v>0.89</v>
+        <v>2.54</v>
       </c>
       <c r="I16" t="n">
-        <v>753.79</v>
+        <v>594.37</v>
       </c>
       <c r="J16" t="n">
-        <v>758.16</v>
+        <v>604.29</v>
       </c>
       <c r="K16" t="n">
-        <v>746.4</v>
+        <v>577.58</v>
       </c>
       <c r="L16" t="n">
-        <v>773.28</v>
+        <v>638.62</v>
       </c>
       <c r="M16" t="n">
-        <v>68.77</v>
+        <v>50.78</v>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>MEDIO</t>
+          <t>BAJO</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
@@ -1401,46 +1401,46 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>CVX</t>
+          <t>AMZN</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Energía</t>
+          <t>Tecnología</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>182.46</v>
+        <v>261.26</v>
       </c>
       <c r="D17" t="n">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E17" t="n">
-        <v>-4.48</v>
+        <v>-1.9</v>
       </c>
       <c r="F17" t="n">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="G17" t="n">
-        <v>4.22</v>
+        <v>6.77</v>
       </c>
       <c r="H17" t="n">
-        <v>2.31</v>
+        <v>2.59</v>
       </c>
       <c r="I17" t="n">
-        <v>180.77</v>
+        <v>258.55</v>
       </c>
       <c r="J17" t="n">
-        <v>183.51</v>
+        <v>262.95</v>
       </c>
       <c r="K17" t="n">
-        <v>176.13</v>
+        <v>251.11</v>
       </c>
       <c r="L17" t="n">
-        <v>193.01</v>
+        <v>278.17</v>
       </c>
       <c r="M17" t="n">
-        <v>53.64</v>
+        <v>42.77</v>
       </c>
       <c r="N17" t="inlineStr">
         <is>
@@ -1461,57 +1461,53 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>NVDA</t>
+          <t>XOM</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>IA / Chips</t>
+          <t>Energía</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>211.14</v>
+        <v>149.38</v>
       </c>
       <c r="D18" t="n">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="E18" t="n">
-        <v>-3.81</v>
+        <v>-3.58</v>
       </c>
       <c r="F18" t="n">
-        <v>1.41</v>
+        <v>0.93</v>
       </c>
       <c r="G18" t="n">
-        <v>7.81</v>
+        <v>4.12</v>
       </c>
       <c r="H18" t="n">
-        <v>3.7</v>
+        <v>2.76</v>
       </c>
       <c r="I18" t="n">
-        <v>208.02</v>
+        <v>147.73</v>
       </c>
       <c r="J18" t="n">
-        <v>213.09</v>
+        <v>150.41</v>
       </c>
       <c r="K18" t="n">
-        <v>199.43</v>
+        <v>143.2</v>
       </c>
       <c r="L18" t="n">
-        <v>230.66</v>
+        <v>159.67</v>
       </c>
       <c r="M18" t="n">
-        <v>46.25</v>
+        <v>51</v>
       </c>
       <c r="N18" t="inlineStr">
         <is>
           <t>BAJO</t>
         </is>
       </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>🔥</t>
-        </is>
-      </c>
+      <c r="O18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>VIGILAR</t>
@@ -1521,57 +1517,53 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>GOOGL</t>
+          <t>CVX</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Tecnología</t>
+          <t>Energía</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>380.34</v>
+        <v>185.83</v>
       </c>
       <c r="D19" t="n">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.89</v>
+        <v>-2.93</v>
       </c>
       <c r="F19" t="n">
-        <v>1.62</v>
+        <v>0.85</v>
       </c>
       <c r="G19" t="n">
-        <v>9.82</v>
+        <v>4.36</v>
       </c>
       <c r="H19" t="n">
-        <v>2.58</v>
+        <v>2.34</v>
       </c>
       <c r="I19" t="n">
-        <v>376.41</v>
+        <v>184.09</v>
       </c>
       <c r="J19" t="n">
-        <v>382.79</v>
+        <v>186.92</v>
       </c>
       <c r="K19" t="n">
-        <v>365.62</v>
+        <v>179.3</v>
       </c>
       <c r="L19" t="n">
-        <v>404.88</v>
+        <v>196.72</v>
       </c>
       <c r="M19" t="n">
-        <v>35.01</v>
+        <v>54.02</v>
       </c>
       <c r="N19" t="inlineStr">
         <is>
           <t>BAJO</t>
         </is>
       </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>🔥</t>
-        </is>
-      </c>
+      <c r="O19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>VIGILAR</t>
@@ -1581,7 +1573,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>XOM</t>
+          <t>SLB</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1590,37 +1582,37 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>145.26</v>
+        <v>54.75</v>
       </c>
       <c r="D20" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="E20" t="n">
-        <v>-6.46</v>
+        <v>-4.42</v>
       </c>
       <c r="F20" t="n">
-        <v>0.67</v>
+        <v>1</v>
       </c>
       <c r="G20" t="n">
-        <v>4.17</v>
+        <v>1.42</v>
       </c>
       <c r="H20" t="n">
-        <v>2.87</v>
+        <v>2.6</v>
       </c>
       <c r="I20" t="n">
-        <v>143.59</v>
+        <v>54.18</v>
       </c>
       <c r="J20" t="n">
-        <v>146.3</v>
+        <v>55.11</v>
       </c>
       <c r="K20" t="n">
-        <v>139</v>
+        <v>52.62</v>
       </c>
       <c r="L20" t="n">
-        <v>155.69</v>
+        <v>58.3</v>
       </c>
       <c r="M20" t="n">
-        <v>52.3</v>
+        <v>48.97</v>
       </c>
       <c r="N20" t="inlineStr">
         <is>
@@ -1637,46 +1629,46 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>OXY</t>
+          <t>GOOGL</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Energía</t>
+          <t>Tecnología</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>56.63</v>
+        <v>376.37</v>
       </c>
       <c r="D21" t="n">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.74</v>
+        <v>-1.72</v>
       </c>
       <c r="F21" t="n">
-        <v>0.74</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="G21" t="n">
-        <v>1.78</v>
+        <v>9.42</v>
       </c>
       <c r="H21" t="n">
-        <v>3.14</v>
+        <v>2.5</v>
       </c>
       <c r="I21" t="n">
-        <v>55.92</v>
+        <v>372.6</v>
       </c>
       <c r="J21" t="n">
-        <v>57.08</v>
+        <v>378.73</v>
       </c>
       <c r="K21" t="n">
-        <v>53.96</v>
+        <v>362.24</v>
       </c>
       <c r="L21" t="n">
-        <v>61.08</v>
+        <v>399.93</v>
       </c>
       <c r="M21" t="n">
-        <v>64.08</v>
+        <v>39.78</v>
       </c>
       <c r="N21" t="inlineStr">
         <is>
@@ -1686,53 +1678,53 @@
       <c r="O21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>VIGILAR</t>
+          <t>NO COMPRAR</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>PYPL</t>
+          <t>TSLA</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Pagos</t>
+          <t>Autos / Tech</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>44.75</v>
+        <v>415.88</v>
       </c>
       <c r="D22" t="n">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="E22" t="n">
-        <v>1.02</v>
+        <v>-2.38</v>
       </c>
       <c r="F22" t="n">
-        <v>0.97</v>
+        <v>0.83</v>
       </c>
       <c r="G22" t="n">
-        <v>1</v>
+        <v>15.6</v>
       </c>
       <c r="H22" t="n">
-        <v>2.24</v>
+        <v>3.75</v>
       </c>
       <c r="I22" t="n">
-        <v>44.35</v>
+        <v>409.64</v>
       </c>
       <c r="J22" t="n">
-        <v>45</v>
+        <v>419.78</v>
       </c>
       <c r="K22" t="n">
-        <v>43.25</v>
+        <v>392.48</v>
       </c>
       <c r="L22" t="n">
-        <v>47.25</v>
+        <v>454.87</v>
       </c>
       <c r="M22" t="n">
-        <v>43</v>
+        <v>38.69</v>
       </c>
       <c r="N22" t="inlineStr">
         <is>
@@ -1758,37 +1750,37 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>189.03</v>
+        <v>182.61</v>
       </c>
       <c r="D23" t="n">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.34</v>
+        <v>-1.29</v>
       </c>
       <c r="F23" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.92</v>
       </c>
       <c r="G23" t="n">
-        <v>13.5</v>
+        <v>12.63</v>
       </c>
       <c r="H23" t="n">
-        <v>7.14</v>
+        <v>6.92</v>
       </c>
       <c r="I23" t="n">
-        <v>183.63</v>
+        <v>177.56</v>
       </c>
       <c r="J23" t="n">
-        <v>192.41</v>
+        <v>185.77</v>
       </c>
       <c r="K23" t="n">
-        <v>168.78</v>
+        <v>163.66</v>
       </c>
       <c r="L23" t="n">
-        <v>222.78</v>
+        <v>214.19</v>
       </c>
       <c r="M23" t="n">
-        <v>44.3</v>
+        <v>32.56</v>
       </c>
       <c r="N23" t="inlineStr">
         <is>
@@ -1814,37 +1806,37 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>10.77</v>
+        <v>11.75</v>
       </c>
       <c r="D24" t="n">
         <v>95</v>
       </c>
       <c r="E24" t="n">
-        <v>15.43</v>
+        <v>26.48</v>
       </c>
       <c r="F24" t="n">
-        <v>2.15</v>
+        <v>2.12</v>
       </c>
       <c r="G24" t="n">
-        <v>0.54</v>
+        <v>0.58</v>
       </c>
       <c r="H24" t="n">
-        <v>5</v>
+        <v>4.96</v>
       </c>
       <c r="I24" t="n">
-        <v>10.55</v>
+        <v>11.52</v>
       </c>
       <c r="J24" t="n">
-        <v>10.9</v>
+        <v>11.9</v>
       </c>
       <c r="K24" t="n">
-        <v>9.960000000000001</v>
+        <v>10.88</v>
       </c>
       <c r="L24" t="n">
-        <v>12.12</v>
+        <v>13.21</v>
       </c>
       <c r="M24" t="n">
-        <v>60.77</v>
+        <v>73.79000000000001</v>
       </c>
       <c r="N24" t="inlineStr">
         <is>
@@ -1874,37 +1866,37 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>94.3</v>
+        <v>90.73</v>
       </c>
       <c r="D25" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E25" t="n">
-        <v>24.21</v>
+        <v>23.21</v>
       </c>
       <c r="F25" t="n">
-        <v>2.55</v>
+        <v>1.63</v>
       </c>
       <c r="G25" t="n">
-        <v>4.93</v>
+        <v>5.1</v>
       </c>
       <c r="H25" t="n">
-        <v>5.23</v>
+        <v>5.62</v>
       </c>
       <c r="I25" t="n">
-        <v>92.33</v>
+        <v>88.69</v>
       </c>
       <c r="J25" t="n">
-        <v>95.53</v>
+        <v>92</v>
       </c>
       <c r="K25" t="n">
-        <v>86.91</v>
+        <v>83.08</v>
       </c>
       <c r="L25" t="n">
-        <v>106.62</v>
+        <v>103.48</v>
       </c>
       <c r="M25" t="n">
-        <v>70.09</v>
+        <v>61.62</v>
       </c>
       <c r="N25" t="inlineStr">
         <is>
@@ -1925,46 +1917,46 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>PLTR</t>
+          <t>SOFI</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>IA / Software</t>
+          <t>Fintech</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>156.54</v>
+        <v>18.58</v>
       </c>
       <c r="D26" t="n">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="E26" t="n">
-        <v>13.92</v>
+        <v>18.95</v>
       </c>
       <c r="F26" t="n">
-        <v>2.03</v>
+        <v>1.41</v>
       </c>
       <c r="G26" t="n">
-        <v>6</v>
+        <v>0.89</v>
       </c>
       <c r="H26" t="n">
-        <v>3.83</v>
+        <v>4.78</v>
       </c>
       <c r="I26" t="n">
-        <v>154.14</v>
+        <v>18.22</v>
       </c>
       <c r="J26" t="n">
-        <v>158.04</v>
+        <v>18.8</v>
       </c>
       <c r="K26" t="n">
-        <v>147.54</v>
+        <v>17.25</v>
       </c>
       <c r="L26" t="n">
-        <v>171.55</v>
+        <v>20.8</v>
       </c>
       <c r="M26" t="n">
-        <v>71.27</v>
+        <v>68.89</v>
       </c>
       <c r="N26" t="inlineStr">
         <is>
@@ -1985,46 +1977,46 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>SOFI</t>
+          <t>MU</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Fintech</t>
+          <t>Memoria / Chips</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>18.22</v>
+        <v>1035.5</v>
       </c>
       <c r="D27" t="n">
         <v>89</v>
       </c>
       <c r="E27" t="n">
-        <v>16.42</v>
+        <v>37.88</v>
       </c>
       <c r="F27" t="n">
-        <v>2.25</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="G27" t="n">
-        <v>0.85</v>
+        <v>65.2</v>
       </c>
       <c r="H27" t="n">
-        <v>4.66</v>
+        <v>6.3</v>
       </c>
       <c r="I27" t="n">
-        <v>17.88</v>
+        <v>1009.42</v>
       </c>
       <c r="J27" t="n">
-        <v>18.43</v>
+        <v>1051.8</v>
       </c>
       <c r="K27" t="n">
-        <v>16.95</v>
+        <v>937.7</v>
       </c>
       <c r="L27" t="n">
-        <v>20.34</v>
+        <v>1198.5</v>
       </c>
       <c r="M27" t="n">
-        <v>69.63</v>
+        <v>70.93000000000001</v>
       </c>
       <c r="N27" t="inlineStr">
         <is>
@@ -2033,7 +2025,7 @@
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -2045,46 +2037,46 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>SMCI</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Servidores IA</t>
+          <t>Tecnología</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>46.09</v>
+        <v>460.52</v>
       </c>
       <c r="D28" t="n">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="E28" t="n">
-        <v>37.75</v>
+        <v>10.02</v>
       </c>
       <c r="F28" t="n">
-        <v>2.04</v>
+        <v>1.45</v>
       </c>
       <c r="G28" t="n">
-        <v>2.84</v>
+        <v>12.13</v>
       </c>
       <c r="H28" t="n">
-        <v>6.16</v>
+        <v>2.63</v>
       </c>
       <c r="I28" t="n">
-        <v>44.96</v>
+        <v>455.67</v>
       </c>
       <c r="J28" t="n">
-        <v>46.8</v>
+        <v>463.55</v>
       </c>
       <c r="K28" t="n">
-        <v>41.83</v>
+        <v>442.33</v>
       </c>
       <c r="L28" t="n">
-        <v>53.18</v>
+        <v>490.84</v>
       </c>
       <c r="M28" t="n">
-        <v>73.93000000000001</v>
+        <v>76.84999999999999</v>
       </c>
       <c r="N28" t="inlineStr">
         <is>
@@ -2093,7 +2085,7 @@
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -2105,46 +2097,46 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>MU</t>
+          <t>ARM</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Memoria / Chips</t>
+          <t>Chips</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>971</v>
+        <v>408.85</v>
       </c>
       <c r="D29" t="n">
-        <v>89</v>
+        <v>76</v>
       </c>
       <c r="E29" t="n">
-        <v>27.41</v>
+        <v>33.39</v>
       </c>
       <c r="F29" t="n">
-        <v>1.08</v>
+        <v>1.57</v>
       </c>
       <c r="G29" t="n">
-        <v>64.91</v>
+        <v>27.71</v>
       </c>
       <c r="H29" t="n">
-        <v>6.68</v>
+        <v>6.78</v>
       </c>
       <c r="I29" t="n">
-        <v>945.04</v>
+        <v>397.77</v>
       </c>
       <c r="J29" t="n">
-        <v>987.23</v>
+        <v>415.78</v>
       </c>
       <c r="K29" t="n">
-        <v>873.64</v>
+        <v>367.28</v>
       </c>
       <c r="L29" t="n">
-        <v>1133.26</v>
+        <v>478.13</v>
       </c>
       <c r="M29" t="n">
-        <v>70.09</v>
+        <v>84.87</v>
       </c>
       <c r="N29" t="inlineStr">
         <is>
@@ -2165,46 +2157,46 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>PLTR</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>IA / Chips</t>
+          <t>IA / Software</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>516.1</v>
+        <v>160.65</v>
       </c>
       <c r="D30" t="n">
-        <v>88</v>
+        <v>67</v>
       </c>
       <c r="E30" t="n">
-        <v>14.79</v>
+        <v>17.37</v>
       </c>
       <c r="F30" t="n">
-        <v>0.55</v>
+        <v>1.22</v>
       </c>
       <c r="G30" t="n">
-        <v>27.67</v>
+        <v>6.2</v>
       </c>
       <c r="H30" t="n">
-        <v>5.36</v>
+        <v>3.86</v>
       </c>
       <c r="I30" t="n">
-        <v>505.03</v>
+        <v>158.17</v>
       </c>
       <c r="J30" t="n">
-        <v>523.02</v>
+        <v>162.2</v>
       </c>
       <c r="K30" t="n">
-        <v>474.6</v>
+        <v>151.35</v>
       </c>
       <c r="L30" t="n">
-        <v>585.27</v>
+        <v>176.15</v>
       </c>
       <c r="M30" t="n">
-        <v>66.97</v>
+        <v>75.14</v>
       </c>
       <c r="N30" t="inlineStr">
         <is>
@@ -2225,57 +2217,53 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>QCOM</t>
+          <t>SOUN</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Chips</t>
+          <t>IA</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>251.02</v>
+        <v>9.25</v>
       </c>
       <c r="D31" t="n">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="E31" t="n">
-        <v>17.62</v>
+        <v>13.22</v>
       </c>
       <c r="F31" t="n">
-        <v>0.99</v>
+        <v>1.12</v>
       </c>
       <c r="G31" t="n">
-        <v>18.95</v>
+        <v>0.51</v>
       </c>
       <c r="H31" t="n">
-        <v>7.55</v>
+        <v>5.49</v>
       </c>
       <c r="I31" t="n">
-        <v>243.44</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="J31" t="n">
-        <v>255.76</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="K31" t="n">
-        <v>222.6</v>
+        <v>8.49</v>
       </c>
       <c r="L31" t="n">
-        <v>298.39</v>
+        <v>10.52</v>
       </c>
       <c r="M31" t="n">
-        <v>60.01</v>
+        <v>65.04000000000001</v>
       </c>
       <c r="N31" t="inlineStr">
         <is>
           <t>ALTO</t>
         </is>
       </c>
-      <c r="O31" t="inlineStr">
-        <is>
-          <t>🔥</t>
-        </is>
-      </c>
+      <c r="O31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>VIGILAR</t>
@@ -2285,57 +2273,53 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>IONQ</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Tecnología</t>
+          <t>Computación cuántica</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>312.06</v>
+        <v>69.28</v>
       </c>
       <c r="D32" t="n">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="E32" t="n">
-        <v>2.32</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="F32" t="n">
-        <v>1.17</v>
+        <v>0.78</v>
       </c>
       <c r="G32" t="n">
-        <v>4.97</v>
+        <v>5.7</v>
       </c>
       <c r="H32" t="n">
-        <v>1.59</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="I32" t="n">
-        <v>310.07</v>
+        <v>67</v>
       </c>
       <c r="J32" t="n">
-        <v>313.3</v>
+        <v>70.7</v>
       </c>
       <c r="K32" t="n">
-        <v>304.61</v>
+        <v>60.74</v>
       </c>
       <c r="L32" t="n">
-        <v>324.47</v>
+        <v>83.52</v>
       </c>
       <c r="M32" t="n">
-        <v>84.28</v>
+        <v>65.75</v>
       </c>
       <c r="N32" t="inlineStr">
         <is>
           <t>ALTO</t>
         </is>
       </c>
-      <c r="O32" t="inlineStr">
-        <is>
-          <t>🔥</t>
-        </is>
-      </c>
+      <c r="O32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>VIGILAR</t>
@@ -2354,37 +2338,37 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>143.48</v>
+        <v>122.39</v>
       </c>
       <c r="D33" t="n">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="E33" t="n">
-        <v>14.37</v>
+        <v>-9.85</v>
       </c>
       <c r="F33" t="n">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="G33" t="n">
-        <v>12.37</v>
+        <v>12.5</v>
       </c>
       <c r="H33" t="n">
-        <v>8.619999999999999</v>
+        <v>10.21</v>
       </c>
       <c r="I33" t="n">
-        <v>138.53</v>
+        <v>117.39</v>
       </c>
       <c r="J33" t="n">
-        <v>146.57</v>
+        <v>125.52</v>
       </c>
       <c r="K33" t="n">
-        <v>124.92</v>
+        <v>103.64</v>
       </c>
       <c r="L33" t="n">
-        <v>174.41</v>
+        <v>153.64</v>
       </c>
       <c r="M33" t="n">
-        <v>70.56</v>
+        <v>52.48</v>
       </c>
       <c r="N33" t="inlineStr">
         <is>
@@ -2401,46 +2385,46 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>ARM</t>
+          <t>UPST</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Chips</t>
+          <t>Fintech IA</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>353.29</v>
+        <v>33.61</v>
       </c>
       <c r="D34" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E34" t="n">
-        <v>18.46</v>
+        <v>17.68</v>
       </c>
       <c r="F34" t="n">
-        <v>0.85</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="G34" t="n">
-        <v>23.5</v>
+        <v>1.94</v>
       </c>
       <c r="H34" t="n">
-        <v>6.65</v>
+        <v>5.78</v>
       </c>
       <c r="I34" t="n">
-        <v>343.89</v>
+        <v>32.83</v>
       </c>
       <c r="J34" t="n">
-        <v>359.16</v>
+        <v>34.1</v>
       </c>
       <c r="K34" t="n">
-        <v>318.04</v>
+        <v>30.7</v>
       </c>
       <c r="L34" t="n">
-        <v>412.04</v>
+        <v>38.46</v>
       </c>
       <c r="M34" t="n">
-        <v>80.92</v>
+        <v>69.22</v>
       </c>
       <c r="N34" t="inlineStr">
         <is>
@@ -2457,46 +2441,46 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>UPST</t>
+          <t>QCOM</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Fintech IA</t>
+          <t>Chips</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>33.79</v>
+        <v>228.99</v>
       </c>
       <c r="D35" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E35" t="n">
-        <v>17.12</v>
+        <v>-3.85</v>
       </c>
       <c r="F35" t="n">
-        <v>1.13</v>
+        <v>0.72</v>
       </c>
       <c r="G35" t="n">
-        <v>1.9</v>
+        <v>18.62</v>
       </c>
       <c r="H35" t="n">
-        <v>5.61</v>
+        <v>8.130000000000001</v>
       </c>
       <c r="I35" t="n">
-        <v>33.03</v>
+        <v>221.54</v>
       </c>
       <c r="J35" t="n">
-        <v>34.26</v>
+        <v>233.64</v>
       </c>
       <c r="K35" t="n">
-        <v>30.95</v>
+        <v>201.06</v>
       </c>
       <c r="L35" t="n">
-        <v>38.53</v>
+        <v>275.54</v>
       </c>
       <c r="M35" t="n">
-        <v>68.73999999999999</v>
+        <v>47.38</v>
       </c>
       <c r="N35" t="inlineStr">
         <is>
@@ -2513,46 +2497,46 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>IONQ</t>
+          <t>SMCI</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Computación cuántica</t>
+          <t>Servidores IA</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>72.06999999999999</v>
+        <v>46.88</v>
       </c>
       <c r="D36" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="E36" t="n">
-        <v>22.38</v>
+        <v>31.76</v>
       </c>
       <c r="F36" t="n">
-        <v>0.79</v>
+        <v>1.02</v>
       </c>
       <c r="G36" t="n">
-        <v>6.07</v>
+        <v>2.8</v>
       </c>
       <c r="H36" t="n">
-        <v>8.42</v>
+        <v>5.97</v>
       </c>
       <c r="I36" t="n">
-        <v>69.64</v>
+        <v>45.76</v>
       </c>
       <c r="J36" t="n">
-        <v>73.59</v>
+        <v>47.58</v>
       </c>
       <c r="K36" t="n">
-        <v>62.97</v>
+        <v>42.68</v>
       </c>
       <c r="L36" t="n">
-        <v>87.23999999999999</v>
+        <v>53.88</v>
       </c>
       <c r="M36" t="n">
-        <v>75.83</v>
+        <v>81.3</v>
       </c>
       <c r="N36" t="inlineStr">
         <is>
@@ -2578,37 +2562,37 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>114.68</v>
+        <v>109.33</v>
       </c>
       <c r="D37" t="n">
         <v>44</v>
       </c>
       <c r="E37" t="n">
-        <v>-3.22</v>
+        <v>-8.77</v>
       </c>
       <c r="F37" t="n">
-        <v>1.1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="G37" t="n">
-        <v>9.34</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="H37" t="n">
-        <v>8.140000000000001</v>
+        <v>8.51</v>
       </c>
       <c r="I37" t="n">
-        <v>110.94</v>
+        <v>105.61</v>
       </c>
       <c r="J37" t="n">
-        <v>117.01</v>
+        <v>111.66</v>
       </c>
       <c r="K37" t="n">
-        <v>100.67</v>
+        <v>95.37</v>
       </c>
       <c r="L37" t="n">
-        <v>138.02</v>
+        <v>132.59</v>
       </c>
       <c r="M37" t="n">
-        <v>39.94</v>
+        <v>30.56</v>
       </c>
       <c r="N37" t="inlineStr">
         <is>

--- a/analisis_acciones.xlsx
+++ b/analisis_acciones.xlsx
@@ -501,7 +501,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AVGO</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -510,37 +510,37 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>459.97</v>
+        <v>521.54</v>
       </c>
       <c r="D2" t="n">
         <v>95</v>
       </c>
       <c r="E2" t="n">
-        <v>11.07</v>
+        <v>3.5</v>
       </c>
       <c r="F2" t="n">
-        <v>1.43</v>
+        <v>0.59</v>
       </c>
       <c r="G2" t="n">
-        <v>17.26</v>
+        <v>27.73</v>
       </c>
       <c r="H2" t="n">
-        <v>3.75</v>
+        <v>5.32</v>
       </c>
       <c r="I2" t="n">
-        <v>453.06</v>
+        <v>510.45</v>
       </c>
       <c r="J2" t="n">
-        <v>464.29</v>
+        <v>528.47</v>
       </c>
       <c r="K2" t="n">
-        <v>434.07</v>
+        <v>479.94</v>
       </c>
       <c r="L2" t="n">
-        <v>503.13</v>
+        <v>590.88</v>
       </c>
       <c r="M2" t="n">
-        <v>63.16</v>
+        <v>70.04000000000001</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -549,7 +549,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥🔥</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -570,37 +570,37 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>435.63</v>
+        <v>446.69</v>
       </c>
       <c r="D3" t="n">
         <v>95</v>
       </c>
       <c r="E3" t="n">
-        <v>7.69</v>
+        <v>8.34</v>
       </c>
       <c r="F3" t="n">
-        <v>1.35</v>
+        <v>0.76</v>
       </c>
       <c r="G3" t="n">
-        <v>15.76</v>
+        <v>15.35</v>
       </c>
       <c r="H3" t="n">
-        <v>3.62</v>
+        <v>3.44</v>
       </c>
       <c r="I3" t="n">
-        <v>429.33</v>
+        <v>440.55</v>
       </c>
       <c r="J3" t="n">
-        <v>439.57</v>
+        <v>450.53</v>
       </c>
       <c r="K3" t="n">
-        <v>412</v>
+        <v>423.66</v>
       </c>
       <c r="L3" t="n">
-        <v>475.02</v>
+        <v>485.07</v>
       </c>
       <c r="M3" t="n">
-        <v>63.65</v>
+        <v>70.98999999999999</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -609,7 +609,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥🔥</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -621,46 +621,46 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AMAT</t>
+          <t>ASML</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Equipos chips</t>
+          <t>Chips</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>458.17</v>
+        <v>1705.37</v>
       </c>
       <c r="D4" t="n">
         <v>95</v>
       </c>
       <c r="E4" t="n">
-        <v>6.02</v>
+        <v>4.49</v>
       </c>
       <c r="F4" t="n">
-        <v>0.78</v>
+        <v>0.91</v>
       </c>
       <c r="G4" t="n">
-        <v>19.86</v>
+        <v>63.18</v>
       </c>
       <c r="H4" t="n">
-        <v>4.33</v>
+        <v>3.7</v>
       </c>
       <c r="I4" t="n">
-        <v>450.23</v>
+        <v>1680.1</v>
       </c>
       <c r="J4" t="n">
-        <v>463.14</v>
+        <v>1721.16</v>
       </c>
       <c r="K4" t="n">
-        <v>428.38</v>
+        <v>1610.6</v>
       </c>
       <c r="L4" t="n">
-        <v>507.82</v>
+        <v>1863.32</v>
       </c>
       <c r="M4" t="n">
-        <v>56.27</v>
+        <v>68.27</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -681,7 +681,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>LRCX</t>
+          <t>AMAT</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -690,41 +690,41 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>317.12</v>
+        <v>490.05</v>
       </c>
       <c r="D5" t="n">
         <v>95</v>
       </c>
       <c r="E5" t="n">
-        <v>3.85</v>
+        <v>7.73</v>
       </c>
       <c r="F5" t="n">
-        <v>0.87</v>
+        <v>1.16</v>
       </c>
       <c r="G5" t="n">
-        <v>15.03</v>
+        <v>20.31</v>
       </c>
       <c r="H5" t="n">
-        <v>4.74</v>
+        <v>4.14</v>
       </c>
       <c r="I5" t="n">
-        <v>311.11</v>
+        <v>481.93</v>
       </c>
       <c r="J5" t="n">
-        <v>320.88</v>
+        <v>495.13</v>
       </c>
       <c r="K5" t="n">
-        <v>294.57</v>
+        <v>459.58</v>
       </c>
       <c r="L5" t="n">
-        <v>354.7</v>
+        <v>540.83</v>
       </c>
       <c r="M5" t="n">
-        <v>60.78</v>
+        <v>71.23</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>BAJO</t>
+          <t>MEDIO</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -741,7 +741,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>KLAC</t>
+          <t>LRCX</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -750,41 +750,41 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1940.04</v>
+        <v>334.41</v>
       </c>
       <c r="D6" t="n">
         <v>95</v>
       </c>
       <c r="E6" t="n">
-        <v>2.74</v>
+        <v>3.64</v>
       </c>
       <c r="F6" t="n">
-        <v>0.73</v>
+        <v>0.87</v>
       </c>
       <c r="G6" t="n">
-        <v>83.84</v>
+        <v>15.04</v>
       </c>
       <c r="H6" t="n">
-        <v>4.32</v>
+        <v>4.5</v>
       </c>
       <c r="I6" t="n">
-        <v>1906.5</v>
+        <v>328.39</v>
       </c>
       <c r="J6" t="n">
-        <v>1961</v>
+        <v>338.17</v>
       </c>
       <c r="K6" t="n">
-        <v>1814.28</v>
+        <v>311.85</v>
       </c>
       <c r="L6" t="n">
-        <v>2149.64</v>
+        <v>372.01</v>
       </c>
       <c r="M6" t="n">
-        <v>57.55</v>
+        <v>70.88</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>BAJO</t>
+          <t>MEDIO</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -801,50 +801,50 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>QQQ</t>
+          <t>NVDA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ETF Nasdaq</t>
+          <t>IA / Chips</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>742.74</v>
+        <v>222.82</v>
       </c>
       <c r="D7" t="n">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="E7" t="n">
-        <v>3.51</v>
+        <v>3.7</v>
       </c>
       <c r="F7" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.96</v>
       </c>
       <c r="G7" t="n">
-        <v>10.88</v>
+        <v>8.34</v>
       </c>
       <c r="H7" t="n">
-        <v>1.46</v>
+        <v>3.74</v>
       </c>
       <c r="I7" t="n">
-        <v>738.39</v>
+        <v>219.48</v>
       </c>
       <c r="J7" t="n">
-        <v>745.46</v>
+        <v>224.9</v>
       </c>
       <c r="K7" t="n">
-        <v>726.42</v>
+        <v>210.31</v>
       </c>
       <c r="L7" t="n">
-        <v>769.9299999999999</v>
+        <v>243.66</v>
       </c>
       <c r="M7" t="n">
-        <v>68.47</v>
+        <v>51.61</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>MEDIO</t>
+          <t>BAJO</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -861,46 +861,46 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SOXX</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>ETF Chips</t>
+          <t>Tecnología</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>571.9299999999999</v>
+        <v>441.31</v>
       </c>
       <c r="D8" t="n">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="E8" t="n">
-        <v>6.44</v>
+        <v>6.08</v>
       </c>
       <c r="F8" t="n">
-        <v>0.8</v>
+        <v>1.01</v>
       </c>
       <c r="G8" t="n">
-        <v>23.53</v>
+        <v>12.93</v>
       </c>
       <c r="H8" t="n">
-        <v>4.11</v>
+        <v>2.93</v>
       </c>
       <c r="I8" t="n">
-        <v>562.52</v>
+        <v>436.14</v>
       </c>
       <c r="J8" t="n">
-        <v>577.8099999999999</v>
+        <v>444.54</v>
       </c>
       <c r="K8" t="n">
-        <v>536.64</v>
+        <v>421.91</v>
       </c>
       <c r="L8" t="n">
-        <v>630.75</v>
+        <v>473.64</v>
       </c>
       <c r="M8" t="n">
-        <v>62.72</v>
+        <v>66.37</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
@@ -921,46 +921,46 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>NVDA</t>
+          <t>OXY</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>IA / Chips</t>
+          <t>Energía</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>224.36</v>
+        <v>59.09</v>
       </c>
       <c r="D9" t="n">
         <v>92</v>
       </c>
       <c r="E9" t="n">
-        <v>4.19</v>
+        <v>2.84</v>
       </c>
       <c r="F9" t="n">
-        <v>1.16</v>
+        <v>0.78</v>
       </c>
       <c r="G9" t="n">
-        <v>8.19</v>
+        <v>1.85</v>
       </c>
       <c r="H9" t="n">
-        <v>3.65</v>
+        <v>3.13</v>
       </c>
       <c r="I9" t="n">
-        <v>221.08</v>
+        <v>58.35</v>
       </c>
       <c r="J9" t="n">
-        <v>226.41</v>
+        <v>59.55</v>
       </c>
       <c r="K9" t="n">
-        <v>212.08</v>
+        <v>56.32</v>
       </c>
       <c r="L9" t="n">
-        <v>244.83</v>
+        <v>63.71</v>
       </c>
       <c r="M9" t="n">
-        <v>53.9</v>
+        <v>61.75</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
@@ -981,46 +981,46 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>UPST</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>IA / Chips</t>
+          <t>Fintech IA</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>510.13</v>
+        <v>32.39</v>
       </c>
       <c r="D10" t="n">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="E10" t="n">
-        <v>9.119999999999999</v>
+        <v>5.78</v>
       </c>
       <c r="F10" t="n">
-        <v>0.83</v>
+        <v>0.91</v>
       </c>
       <c r="G10" t="n">
-        <v>28.55</v>
+        <v>1.98</v>
       </c>
       <c r="H10" t="n">
-        <v>5.6</v>
+        <v>6.1</v>
       </c>
       <c r="I10" t="n">
-        <v>498.71</v>
+        <v>31.6</v>
       </c>
       <c r="J10" t="n">
-        <v>517.27</v>
+        <v>32.88</v>
       </c>
       <c r="K10" t="n">
-        <v>467.3</v>
+        <v>29.43</v>
       </c>
       <c r="L10" t="n">
-        <v>581.51</v>
+        <v>37.33</v>
       </c>
       <c r="M10" t="n">
-        <v>64.12</v>
+        <v>67.27</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
@@ -1041,46 +1041,46 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>PYPL</t>
+          <t>KLAC</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Pagos</t>
+          <t>Equipos chips</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>45.19</v>
+        <v>2045.2</v>
       </c>
       <c r="D11" t="n">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="E11" t="n">
-        <v>2.17</v>
+        <v>1.68</v>
       </c>
       <c r="F11" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="G11" t="n">
-        <v>1.09</v>
+        <v>84.23</v>
       </c>
       <c r="H11" t="n">
-        <v>2.42</v>
+        <v>4.12</v>
       </c>
       <c r="I11" t="n">
-        <v>44.75</v>
+        <v>2011.51</v>
       </c>
       <c r="J11" t="n">
-        <v>45.46</v>
+        <v>2066.26</v>
       </c>
       <c r="K11" t="n">
-        <v>43.55</v>
+        <v>1918.86</v>
       </c>
       <c r="L11" t="n">
-        <v>47.92</v>
+        <v>2255.76</v>
       </c>
       <c r="M11" t="n">
-        <v>51.31</v>
+        <v>66.51000000000001</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
@@ -1089,7 +1089,7 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1101,50 +1101,50 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ASML</t>
+          <t>SPY</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Chips</t>
+          <t>ETF Mercado</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1628.57</v>
+        <v>759.5700000000001</v>
       </c>
       <c r="D12" t="n">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.27</v>
+        <v>1.2</v>
       </c>
       <c r="F12" t="n">
-        <v>0.65</v>
+        <v>0.59</v>
       </c>
       <c r="G12" t="n">
-        <v>63.97</v>
+        <v>6.54</v>
       </c>
       <c r="H12" t="n">
-        <v>3.93</v>
+        <v>0.86</v>
       </c>
       <c r="I12" t="n">
-        <v>1602.98</v>
+        <v>756.96</v>
       </c>
       <c r="J12" t="n">
-        <v>1644.56</v>
+        <v>761.2</v>
       </c>
       <c r="K12" t="n">
-        <v>1532.62</v>
+        <v>749.77</v>
       </c>
       <c r="L12" t="n">
-        <v>1788.49</v>
+        <v>775.91</v>
       </c>
       <c r="M12" t="n">
-        <v>56.64</v>
+        <v>71.17</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>BAJO</t>
+          <t>MEDIO</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -1161,50 +1161,50 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>OXY</t>
+          <t>QCOM</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Energía</t>
+          <t>Chips</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>58.92</v>
+        <v>240.84</v>
       </c>
       <c r="D13" t="n">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="E13" t="n">
-        <v>0.19</v>
+        <v>-3.21</v>
       </c>
       <c r="F13" t="n">
-        <v>0.99</v>
+        <v>0.63</v>
       </c>
       <c r="G13" t="n">
-        <v>1.84</v>
+        <v>17.45</v>
       </c>
       <c r="H13" t="n">
-        <v>3.12</v>
+        <v>7.24</v>
       </c>
       <c r="I13" t="n">
-        <v>58.18</v>
+        <v>233.86</v>
       </c>
       <c r="J13" t="n">
-        <v>59.38</v>
+        <v>245.2</v>
       </c>
       <c r="K13" t="n">
-        <v>56.16</v>
+        <v>214.67</v>
       </c>
       <c r="L13" t="n">
-        <v>63.52</v>
+        <v>284.46</v>
       </c>
       <c r="M13" t="n">
-        <v>64.58</v>
+        <v>60.34</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>BAJO</t>
+          <t>MEDIO</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -1221,50 +1221,50 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>SPY</t>
+          <t>SLB</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>ETF Mercado</t>
+          <t>Energía</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>758.54</v>
+        <v>56.56</v>
       </c>
       <c r="D14" t="n">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="E14" t="n">
-        <v>1.73</v>
+        <v>-2.45</v>
       </c>
       <c r="F14" t="n">
-        <v>0.82</v>
+        <v>0.74</v>
       </c>
       <c r="G14" t="n">
-        <v>6.81</v>
+        <v>1.46</v>
       </c>
       <c r="H14" t="n">
-        <v>0.9</v>
+        <v>2.59</v>
       </c>
       <c r="I14" t="n">
-        <v>755.8200000000001</v>
+        <v>55.97</v>
       </c>
       <c r="J14" t="n">
-        <v>760.24</v>
+        <v>56.93</v>
       </c>
       <c r="K14" t="n">
-        <v>748.33</v>
+        <v>54.36</v>
       </c>
       <c r="L14" t="n">
-        <v>775.5599999999999</v>
+        <v>60.22</v>
       </c>
       <c r="M14" t="n">
-        <v>69</v>
+        <v>54.67</v>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>MEDIO</t>
+          <t>BAJO</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
@@ -1281,50 +1281,50 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>CVX</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Tecnología</t>
+          <t>Energía</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>306.31</v>
+        <v>187.55</v>
       </c>
       <c r="D15" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.8100000000000001</v>
+        <v>1.54</v>
       </c>
       <c r="F15" t="n">
-        <v>0.93</v>
+        <v>0.58</v>
       </c>
       <c r="G15" t="n">
-        <v>5.21</v>
+        <v>4.44</v>
       </c>
       <c r="H15" t="n">
-        <v>1.7</v>
+        <v>2.37</v>
       </c>
       <c r="I15" t="n">
-        <v>304.23</v>
+        <v>185.77</v>
       </c>
       <c r="J15" t="n">
-        <v>307.61</v>
+        <v>188.66</v>
       </c>
       <c r="K15" t="n">
-        <v>298.5</v>
+        <v>180.89</v>
       </c>
       <c r="L15" t="n">
-        <v>319.33</v>
+        <v>198.66</v>
       </c>
       <c r="M15" t="n">
-        <v>70.58</v>
+        <v>54.7</v>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>MEDIO</t>
+          <t>BAJO</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
@@ -1341,50 +1341,50 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>META</t>
+          <t>SOUN</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Tecnología</t>
+          <t>IA</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>600.47</v>
+        <v>8.82</v>
       </c>
       <c r="D16" t="n">
         <v>78</v>
       </c>
       <c r="E16" t="n">
-        <v>-1.6</v>
+        <v>8.49</v>
       </c>
       <c r="F16" t="n">
-        <v>1.8</v>
+        <v>1.01</v>
       </c>
       <c r="G16" t="n">
-        <v>15.26</v>
+        <v>0.5</v>
       </c>
       <c r="H16" t="n">
-        <v>2.54</v>
+        <v>5.67</v>
       </c>
       <c r="I16" t="n">
-        <v>594.37</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="J16" t="n">
-        <v>604.29</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="K16" t="n">
-        <v>577.58</v>
+        <v>8.07</v>
       </c>
       <c r="L16" t="n">
-        <v>638.62</v>
+        <v>10.07</v>
       </c>
       <c r="M16" t="n">
-        <v>50.78</v>
+        <v>64.06999999999999</v>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>BAJO</t>
+          <t>MEDIO</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
@@ -1401,50 +1401,50 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>AMZN</t>
+          <t>PLTR</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Tecnología</t>
+          <t>IA / Software</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>261.26</v>
+        <v>152.17</v>
       </c>
       <c r="D17" t="n">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.9</v>
+        <v>11.4</v>
       </c>
       <c r="F17" t="n">
-        <v>1.31</v>
+        <v>0.95</v>
       </c>
       <c r="G17" t="n">
-        <v>6.77</v>
+        <v>6.69</v>
       </c>
       <c r="H17" t="n">
-        <v>2.59</v>
+        <v>4.4</v>
       </c>
       <c r="I17" t="n">
-        <v>258.55</v>
+        <v>149.49</v>
       </c>
       <c r="J17" t="n">
-        <v>262.95</v>
+        <v>153.84</v>
       </c>
       <c r="K17" t="n">
-        <v>251.11</v>
+        <v>142.13</v>
       </c>
       <c r="L17" t="n">
-        <v>278.17</v>
+        <v>168.9</v>
       </c>
       <c r="M17" t="n">
-        <v>42.77</v>
+        <v>64.73999999999999</v>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>BAJO</t>
+          <t>MEDIO</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
@@ -1454,60 +1454,64 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>VIGILAR</t>
+          <t>POSIBLE COMPRA</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>XOM</t>
+          <t>GOOGL</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Energía</t>
+          <t>Tecnología</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>149.38</v>
+        <v>361.85</v>
       </c>
       <c r="D18" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="E18" t="n">
-        <v>-3.58</v>
+        <v>-6.95</v>
       </c>
       <c r="F18" t="n">
-        <v>0.93</v>
+        <v>1.67</v>
       </c>
       <c r="G18" t="n">
-        <v>4.12</v>
+        <v>10.28</v>
       </c>
       <c r="H18" t="n">
-        <v>2.76</v>
+        <v>2.84</v>
       </c>
       <c r="I18" t="n">
-        <v>147.73</v>
+        <v>357.74</v>
       </c>
       <c r="J18" t="n">
-        <v>150.41</v>
+        <v>364.42</v>
       </c>
       <c r="K18" t="n">
-        <v>143.2</v>
+        <v>346.42</v>
       </c>
       <c r="L18" t="n">
-        <v>159.67</v>
+        <v>387.56</v>
       </c>
       <c r="M18" t="n">
-        <v>51</v>
+        <v>32.6</v>
       </c>
       <c r="N18" t="inlineStr">
         <is>
           <t>BAJO</t>
         </is>
       </c>
-      <c r="O18" t="inlineStr"/>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>🔥</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>VIGILAR</t>
@@ -1517,53 +1521,57 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>CVX</t>
+          <t>SOFI</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Energía</t>
+          <t>Fintech</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>185.83</v>
+        <v>17.74</v>
       </c>
       <c r="D19" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.93</v>
+        <v>11.01</v>
       </c>
       <c r="F19" t="n">
-        <v>0.85</v>
+        <v>1.08</v>
       </c>
       <c r="G19" t="n">
-        <v>4.36</v>
+        <v>0.91</v>
       </c>
       <c r="H19" t="n">
-        <v>2.34</v>
+        <v>5.14</v>
       </c>
       <c r="I19" t="n">
-        <v>184.09</v>
+        <v>17.38</v>
       </c>
       <c r="J19" t="n">
-        <v>186.92</v>
+        <v>17.97</v>
       </c>
       <c r="K19" t="n">
-        <v>179.3</v>
+        <v>16.37</v>
       </c>
       <c r="L19" t="n">
-        <v>196.72</v>
+        <v>20.02</v>
       </c>
       <c r="M19" t="n">
-        <v>54.02</v>
+        <v>63.9</v>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>BAJO</t>
-        </is>
-      </c>
-      <c r="O19" t="inlineStr"/>
+          <t>MEDIO</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>🔥</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>VIGILAR</t>
@@ -1573,46 +1581,46 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>SLB</t>
+          <t>AMZN</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Energía</t>
+          <t>Tecnología</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>54.75</v>
+        <v>256.52</v>
       </c>
       <c r="D20" t="n">
         <v>64</v>
       </c>
       <c r="E20" t="n">
-        <v>-4.42</v>
+        <v>-3.31</v>
       </c>
       <c r="F20" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="G20" t="n">
-        <v>1.42</v>
+        <v>6.8</v>
       </c>
       <c r="H20" t="n">
-        <v>2.6</v>
+        <v>2.65</v>
       </c>
       <c r="I20" t="n">
-        <v>54.18</v>
+        <v>253.8</v>
       </c>
       <c r="J20" t="n">
-        <v>55.11</v>
+        <v>258.22</v>
       </c>
       <c r="K20" t="n">
-        <v>52.62</v>
+        <v>246.31</v>
       </c>
       <c r="L20" t="n">
-        <v>58.3</v>
+        <v>273.53</v>
       </c>
       <c r="M20" t="n">
-        <v>48.97</v>
+        <v>41.55</v>
       </c>
       <c r="N20" t="inlineStr">
         <is>
@@ -1629,46 +1637,46 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>GOOGL</t>
+          <t>PYPL</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Tecnología</t>
+          <t>Pagos</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>376.37</v>
+        <v>44.53</v>
       </c>
       <c r="D21" t="n">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.72</v>
+        <v>0.84</v>
       </c>
       <c r="F21" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="G21" t="n">
-        <v>9.42</v>
+        <v>1.05</v>
       </c>
       <c r="H21" t="n">
-        <v>2.5</v>
+        <v>2.37</v>
       </c>
       <c r="I21" t="n">
-        <v>372.6</v>
+        <v>44.11</v>
       </c>
       <c r="J21" t="n">
-        <v>378.73</v>
+        <v>44.79</v>
       </c>
       <c r="K21" t="n">
-        <v>362.24</v>
+        <v>42.95</v>
       </c>
       <c r="L21" t="n">
-        <v>399.93</v>
+        <v>47.16</v>
       </c>
       <c r="M21" t="n">
-        <v>39.78</v>
+        <v>40.64</v>
       </c>
       <c r="N21" t="inlineStr">
         <is>
@@ -1678,7 +1686,7 @@
       <c r="O21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>NO COMPRAR</t>
+          <t>VIGILAR</t>
         </is>
       </c>
     </row>
@@ -1694,37 +1702,37 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>415.88</v>
+        <v>423.74</v>
       </c>
       <c r="D22" t="n">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.38</v>
+        <v>-2.27</v>
       </c>
       <c r="F22" t="n">
-        <v>0.83</v>
+        <v>0.71</v>
       </c>
       <c r="G22" t="n">
-        <v>15.6</v>
+        <v>14.52</v>
       </c>
       <c r="H22" t="n">
-        <v>3.75</v>
+        <v>3.43</v>
       </c>
       <c r="I22" t="n">
-        <v>409.64</v>
+        <v>417.93</v>
       </c>
       <c r="J22" t="n">
-        <v>419.78</v>
+        <v>427.37</v>
       </c>
       <c r="K22" t="n">
-        <v>392.48</v>
+        <v>401.96</v>
       </c>
       <c r="L22" t="n">
-        <v>454.87</v>
+        <v>460.05</v>
       </c>
       <c r="M22" t="n">
-        <v>38.69</v>
+        <v>46.12</v>
       </c>
       <c r="N22" t="inlineStr">
         <is>
@@ -1741,50 +1749,50 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>COIN</t>
+          <t>XOM</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Cripto / Trading</t>
+          <t>Energía</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>182.61</v>
+        <v>149.56</v>
       </c>
       <c r="D23" t="n">
-        <v>38</v>
+        <v>54</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.29</v>
+        <v>-0.17</v>
       </c>
       <c r="F23" t="n">
-        <v>0.92</v>
+        <v>0.6</v>
       </c>
       <c r="G23" t="n">
-        <v>12.63</v>
+        <v>4.14</v>
       </c>
       <c r="H23" t="n">
-        <v>6.92</v>
+        <v>2.77</v>
       </c>
       <c r="I23" t="n">
-        <v>177.56</v>
+        <v>147.91</v>
       </c>
       <c r="J23" t="n">
-        <v>185.77</v>
+        <v>150.59</v>
       </c>
       <c r="K23" t="n">
-        <v>163.66</v>
+        <v>143.36</v>
       </c>
       <c r="L23" t="n">
-        <v>214.19</v>
+        <v>159.9</v>
       </c>
       <c r="M23" t="n">
-        <v>32.56</v>
+        <v>49.92</v>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>MEDIO</t>
+          <t>BAJO</t>
         </is>
       </c>
       <c r="O23" t="inlineStr"/>
@@ -1797,166 +1805,158 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>AI</t>
+          <t>META</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>IA</t>
+          <t>Tecnología</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>11.75</v>
+        <v>597.63</v>
       </c>
       <c r="D24" t="n">
-        <v>95</v>
+        <v>44</v>
       </c>
       <c r="E24" t="n">
-        <v>26.48</v>
+        <v>-2.4</v>
       </c>
       <c r="F24" t="n">
-        <v>2.12</v>
+        <v>1.15</v>
       </c>
       <c r="G24" t="n">
-        <v>0.58</v>
+        <v>15.34</v>
       </c>
       <c r="H24" t="n">
-        <v>4.96</v>
+        <v>2.57</v>
       </c>
       <c r="I24" t="n">
-        <v>11.52</v>
+        <v>591.5</v>
       </c>
       <c r="J24" t="n">
-        <v>11.9</v>
+        <v>601.46</v>
       </c>
       <c r="K24" t="n">
-        <v>10.88</v>
+        <v>574.63</v>
       </c>
       <c r="L24" t="n">
-        <v>13.21</v>
+        <v>635.97</v>
       </c>
       <c r="M24" t="n">
-        <v>73.79000000000001</v>
+        <v>47.36</v>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>ALTO</t>
-        </is>
-      </c>
-      <c r="O24" t="inlineStr">
-        <is>
-          <t>🔥🔥</t>
-        </is>
-      </c>
+          <t>BAJO</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>VIGILAR</t>
+          <t>NO COMPRAR</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>HOOD</t>
+          <t>COIN</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Trading</t>
+          <t>Cripto / Trading</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>90.73</v>
+        <v>173.99</v>
       </c>
       <c r="D25" t="n">
-        <v>90</v>
+        <v>38</v>
       </c>
       <c r="E25" t="n">
-        <v>23.21</v>
+        <v>-3.34</v>
       </c>
       <c r="F25" t="n">
-        <v>1.63</v>
+        <v>0.86</v>
       </c>
       <c r="G25" t="n">
-        <v>5.1</v>
+        <v>12.11</v>
       </c>
       <c r="H25" t="n">
-        <v>5.62</v>
+        <v>6.96</v>
       </c>
       <c r="I25" t="n">
-        <v>88.69</v>
+        <v>169.15</v>
       </c>
       <c r="J25" t="n">
-        <v>92</v>
+        <v>177.02</v>
       </c>
       <c r="K25" t="n">
-        <v>83.08</v>
+        <v>155.83</v>
       </c>
       <c r="L25" t="n">
-        <v>103.48</v>
+        <v>204.26</v>
       </c>
       <c r="M25" t="n">
-        <v>61.62</v>
+        <v>32.68</v>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>ALTO</t>
-        </is>
-      </c>
-      <c r="O25" t="inlineStr">
-        <is>
-          <t>🔥🔥</t>
-        </is>
-      </c>
+          <t>MEDIO</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>VIGILAR</t>
+          <t>NO COMPRAR</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>SOFI</t>
+          <t>AVGO</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Fintech</t>
+          <t>IA / Chips</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>18.58</v>
+        <v>481.57</v>
       </c>
       <c r="D26" t="n">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="E26" t="n">
-        <v>18.95</v>
+        <v>14.11</v>
       </c>
       <c r="F26" t="n">
-        <v>1.41</v>
+        <v>1.62</v>
       </c>
       <c r="G26" t="n">
-        <v>0.89</v>
+        <v>17.84</v>
       </c>
       <c r="H26" t="n">
-        <v>4.78</v>
+        <v>3.7</v>
       </c>
       <c r="I26" t="n">
-        <v>18.22</v>
+        <v>474.44</v>
       </c>
       <c r="J26" t="n">
-        <v>18.8</v>
+        <v>486.03</v>
       </c>
       <c r="K26" t="n">
-        <v>17.25</v>
+        <v>454.82</v>
       </c>
       <c r="L26" t="n">
-        <v>20.8</v>
+        <v>526.16</v>
       </c>
       <c r="M26" t="n">
-        <v>68.89</v>
+        <v>73.54000000000001</v>
       </c>
       <c r="N26" t="inlineStr">
         <is>
@@ -1977,46 +1977,46 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>MU</t>
+          <t>SOXX</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Memoria / Chips</t>
+          <t>ETF Chips</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>1035.5</v>
+        <v>605.02</v>
       </c>
       <c r="D27" t="n">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="E27" t="n">
-        <v>37.88</v>
+        <v>6.13</v>
       </c>
       <c r="F27" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.84</v>
       </c>
       <c r="G27" t="n">
-        <v>65.2</v>
+        <v>23.27</v>
       </c>
       <c r="H27" t="n">
-        <v>6.3</v>
+        <v>3.85</v>
       </c>
       <c r="I27" t="n">
-        <v>1009.42</v>
+        <v>595.71</v>
       </c>
       <c r="J27" t="n">
-        <v>1051.8</v>
+        <v>610.84</v>
       </c>
       <c r="K27" t="n">
-        <v>937.7</v>
+        <v>570.11</v>
       </c>
       <c r="L27" t="n">
-        <v>1198.5</v>
+        <v>663.21</v>
       </c>
       <c r="M27" t="n">
-        <v>70.93000000000001</v>
+        <v>76.13</v>
       </c>
       <c r="N27" t="inlineStr">
         <is>
@@ -2037,7 +2037,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>AAPL</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2046,37 +2046,37 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>460.52</v>
+        <v>315.2</v>
       </c>
       <c r="D28" t="n">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="E28" t="n">
-        <v>10.02</v>
+        <v>2.23</v>
       </c>
       <c r="F28" t="n">
-        <v>1.45</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="G28" t="n">
-        <v>12.13</v>
+        <v>5.67</v>
       </c>
       <c r="H28" t="n">
-        <v>2.63</v>
+        <v>1.8</v>
       </c>
       <c r="I28" t="n">
-        <v>455.67</v>
+        <v>312.93</v>
       </c>
       <c r="J28" t="n">
-        <v>463.55</v>
+        <v>316.62</v>
       </c>
       <c r="K28" t="n">
-        <v>442.33</v>
+        <v>306.7</v>
       </c>
       <c r="L28" t="n">
-        <v>490.84</v>
+        <v>329.37</v>
       </c>
       <c r="M28" t="n">
-        <v>76.84999999999999</v>
+        <v>75.58</v>
       </c>
       <c r="N28" t="inlineStr">
         <is>
@@ -2097,46 +2097,46 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>ARM</t>
+          <t>QQQ</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Chips</t>
+          <t>ETF Nasdaq</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>408.85</v>
+        <v>746.16</v>
       </c>
       <c r="D29" t="n">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="E29" t="n">
-        <v>33.39</v>
+        <v>2.17</v>
       </c>
       <c r="F29" t="n">
-        <v>1.57</v>
+        <v>0.73</v>
       </c>
       <c r="G29" t="n">
-        <v>27.71</v>
+        <v>10.2</v>
       </c>
       <c r="H29" t="n">
-        <v>6.78</v>
+        <v>1.37</v>
       </c>
       <c r="I29" t="n">
-        <v>397.77</v>
+        <v>742.08</v>
       </c>
       <c r="J29" t="n">
-        <v>415.78</v>
+        <v>748.71</v>
       </c>
       <c r="K29" t="n">
-        <v>367.28</v>
+        <v>730.85</v>
       </c>
       <c r="L29" t="n">
-        <v>478.13</v>
+        <v>771.67</v>
       </c>
       <c r="M29" t="n">
-        <v>84.87</v>
+        <v>75.23999999999999</v>
       </c>
       <c r="N29" t="inlineStr">
         <is>
@@ -2157,46 +2157,46 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>PLTR</t>
+          <t>AI</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>IA / Software</t>
+          <t>IA</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>160.65</v>
+        <v>11.18</v>
       </c>
       <c r="D30" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E30" t="n">
-        <v>17.37</v>
+        <v>16.58</v>
       </c>
       <c r="F30" t="n">
-        <v>1.22</v>
+        <v>1.76</v>
       </c>
       <c r="G30" t="n">
-        <v>6.2</v>
+        <v>0.58</v>
       </c>
       <c r="H30" t="n">
-        <v>3.86</v>
+        <v>5.2</v>
       </c>
       <c r="I30" t="n">
-        <v>158.17</v>
+        <v>10.95</v>
       </c>
       <c r="J30" t="n">
-        <v>162.2</v>
+        <v>11.33</v>
       </c>
       <c r="K30" t="n">
-        <v>151.35</v>
+        <v>10.31</v>
       </c>
       <c r="L30" t="n">
-        <v>176.15</v>
+        <v>12.63</v>
       </c>
       <c r="M30" t="n">
-        <v>75.14</v>
+        <v>75.7</v>
       </c>
       <c r="N30" t="inlineStr">
         <is>
@@ -2217,46 +2217,46 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>SOUN</t>
+          <t>IONQ</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>IA</t>
+          <t>Computación cuántica</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>9.25</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="D31" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E31" t="n">
-        <v>13.22</v>
+        <v>12.23</v>
       </c>
       <c r="F31" t="n">
-        <v>1.12</v>
+        <v>0.76</v>
       </c>
       <c r="G31" t="n">
-        <v>0.51</v>
+        <v>5.45</v>
       </c>
       <c r="H31" t="n">
-        <v>5.49</v>
+        <v>7.63</v>
       </c>
       <c r="I31" t="n">
-        <v>9.050000000000001</v>
+        <v>69.22</v>
       </c>
       <c r="J31" t="n">
-        <v>9.380000000000001</v>
+        <v>72.76000000000001</v>
       </c>
       <c r="K31" t="n">
-        <v>8.49</v>
+        <v>63.22</v>
       </c>
       <c r="L31" t="n">
-        <v>10.52</v>
+        <v>85.03</v>
       </c>
       <c r="M31" t="n">
-        <v>65.04000000000001</v>
+        <v>69.20999999999999</v>
       </c>
       <c r="N31" t="inlineStr">
         <is>
@@ -2273,46 +2273,46 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>IONQ</t>
+          <t>HOOD</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Computación cuántica</t>
+          <t>Trading</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>69.28</v>
+        <v>88.16</v>
       </c>
       <c r="D32" t="n">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="E32" t="n">
-        <v>8.859999999999999</v>
+        <v>18.99</v>
       </c>
       <c r="F32" t="n">
-        <v>0.78</v>
+        <v>1.02</v>
       </c>
       <c r="G32" t="n">
-        <v>5.7</v>
+        <v>5.12</v>
       </c>
       <c r="H32" t="n">
-        <v>8.220000000000001</v>
+        <v>5.81</v>
       </c>
       <c r="I32" t="n">
-        <v>67</v>
+        <v>86.11</v>
       </c>
       <c r="J32" t="n">
-        <v>70.7</v>
+        <v>89.44</v>
       </c>
       <c r="K32" t="n">
-        <v>60.74</v>
+        <v>80.48</v>
       </c>
       <c r="L32" t="n">
-        <v>83.52</v>
+        <v>100.96</v>
       </c>
       <c r="M32" t="n">
-        <v>65.75</v>
+        <v>61.53</v>
       </c>
       <c r="N32" t="inlineStr">
         <is>
@@ -2329,46 +2329,46 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>RKLB</t>
+          <t>MU</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Espacial</t>
+          <t>Memoria / Chips</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>122.39</v>
+        <v>1064.1</v>
       </c>
       <c r="D33" t="n">
         <v>72</v>
       </c>
       <c r="E33" t="n">
-        <v>-9.85</v>
+        <v>18.78</v>
       </c>
       <c r="F33" t="n">
-        <v>1.18</v>
+        <v>0.82</v>
       </c>
       <c r="G33" t="n">
-        <v>12.5</v>
+        <v>63.09</v>
       </c>
       <c r="H33" t="n">
-        <v>10.21</v>
+        <v>5.93</v>
       </c>
       <c r="I33" t="n">
-        <v>117.39</v>
+        <v>1038.86</v>
       </c>
       <c r="J33" t="n">
-        <v>125.52</v>
+        <v>1079.87</v>
       </c>
       <c r="K33" t="n">
-        <v>103.64</v>
+        <v>969.46</v>
       </c>
       <c r="L33" t="n">
-        <v>153.64</v>
+        <v>1221.83</v>
       </c>
       <c r="M33" t="n">
-        <v>52.48</v>
+        <v>75.93000000000001</v>
       </c>
       <c r="N33" t="inlineStr">
         <is>
@@ -2385,46 +2385,46 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>UPST</t>
+          <t>RKLB</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Fintech IA</t>
+          <t>Espacial</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>33.61</v>
+        <v>123.32</v>
       </c>
       <c r="D34" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E34" t="n">
-        <v>17.68</v>
+        <v>-13.88</v>
       </c>
       <c r="F34" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.61</v>
       </c>
       <c r="G34" t="n">
-        <v>1.94</v>
+        <v>12.33</v>
       </c>
       <c r="H34" t="n">
-        <v>5.78</v>
+        <v>10</v>
       </c>
       <c r="I34" t="n">
-        <v>32.83</v>
+        <v>118.39</v>
       </c>
       <c r="J34" t="n">
-        <v>34.1</v>
+        <v>126.4</v>
       </c>
       <c r="K34" t="n">
-        <v>30.7</v>
+        <v>104.83</v>
       </c>
       <c r="L34" t="n">
-        <v>38.46</v>
+        <v>154.14</v>
       </c>
       <c r="M34" t="n">
-        <v>69.22</v>
+        <v>52.81</v>
       </c>
       <c r="N34" t="inlineStr">
         <is>
@@ -2441,7 +2441,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>QCOM</t>
+          <t>ARM</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2450,37 +2450,37 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>228.99</v>
+        <v>402.71</v>
       </c>
       <c r="D35" t="n">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="E35" t="n">
-        <v>-3.85</v>
+        <v>25.37</v>
       </c>
       <c r="F35" t="n">
-        <v>0.72</v>
+        <v>1.11</v>
       </c>
       <c r="G35" t="n">
-        <v>18.62</v>
+        <v>29.46</v>
       </c>
       <c r="H35" t="n">
-        <v>8.130000000000001</v>
+        <v>7.32</v>
       </c>
       <c r="I35" t="n">
-        <v>221.54</v>
+        <v>390.93</v>
       </c>
       <c r="J35" t="n">
-        <v>233.64</v>
+        <v>410.07</v>
       </c>
       <c r="K35" t="n">
-        <v>201.06</v>
+        <v>358.52</v>
       </c>
       <c r="L35" t="n">
-        <v>275.54</v>
+        <v>476.36</v>
       </c>
       <c r="M35" t="n">
-        <v>47.38</v>
+        <v>84.44</v>
       </c>
       <c r="N35" t="inlineStr">
         <is>
@@ -2506,37 +2506,37 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>46.88</v>
+        <v>50.17</v>
       </c>
       <c r="D36" t="n">
         <v>54</v>
       </c>
       <c r="E36" t="n">
-        <v>31.76</v>
+        <v>35.23</v>
       </c>
       <c r="F36" t="n">
-        <v>1.02</v>
+        <v>1.13</v>
       </c>
       <c r="G36" t="n">
-        <v>2.8</v>
+        <v>2.96</v>
       </c>
       <c r="H36" t="n">
-        <v>5.97</v>
+        <v>5.9</v>
       </c>
       <c r="I36" t="n">
-        <v>45.76</v>
+        <v>48.99</v>
       </c>
       <c r="J36" t="n">
-        <v>47.58</v>
+        <v>50.91</v>
       </c>
       <c r="K36" t="n">
-        <v>42.68</v>
+        <v>45.73</v>
       </c>
       <c r="L36" t="n">
-        <v>53.88</v>
+        <v>57.57</v>
       </c>
       <c r="M36" t="n">
-        <v>81.3</v>
+        <v>86.36</v>
       </c>
       <c r="N36" t="inlineStr">
         <is>
@@ -2562,37 +2562,37 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>109.33</v>
+        <v>107.93</v>
       </c>
       <c r="D37" t="n">
         <v>44</v>
       </c>
       <c r="E37" t="n">
-        <v>-8.77</v>
+        <v>-12.62</v>
       </c>
       <c r="F37" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.75</v>
       </c>
       <c r="G37" t="n">
-        <v>9.300000000000001</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="H37" t="n">
-        <v>8.51</v>
+        <v>8.01</v>
       </c>
       <c r="I37" t="n">
-        <v>105.61</v>
+        <v>104.47</v>
       </c>
       <c r="J37" t="n">
-        <v>111.66</v>
+        <v>110.09</v>
       </c>
       <c r="K37" t="n">
-        <v>95.37</v>
+        <v>94.97</v>
       </c>
       <c r="L37" t="n">
-        <v>132.59</v>
+        <v>129.53</v>
       </c>
       <c r="M37" t="n">
-        <v>30.56</v>
+        <v>35.69</v>
       </c>
       <c r="N37" t="inlineStr">
         <is>

--- a/analisis_acciones.xlsx
+++ b/analisis_acciones.xlsx
@@ -501,46 +501,46 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>AI</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>IA / Chips</t>
+          <t>IA</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>521.54</v>
+        <v>10.71</v>
       </c>
       <c r="D2" t="n">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="E2" t="n">
-        <v>3.5</v>
+        <v>11.68</v>
       </c>
       <c r="F2" t="n">
-        <v>0.59</v>
+        <v>2.88</v>
       </c>
       <c r="G2" t="n">
-        <v>27.73</v>
+        <v>0.62</v>
       </c>
       <c r="H2" t="n">
-        <v>5.32</v>
+        <v>5.78</v>
       </c>
       <c r="I2" t="n">
-        <v>510.45</v>
+        <v>10.46</v>
       </c>
       <c r="J2" t="n">
-        <v>528.47</v>
+        <v>10.86</v>
       </c>
       <c r="K2" t="n">
-        <v>479.94</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="L2" t="n">
-        <v>590.88</v>
+        <v>12.26</v>
       </c>
       <c r="M2" t="n">
-        <v>70.04000000000001</v>
+        <v>70.68000000000001</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -549,7 +549,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>🔥🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -570,41 +570,41 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>446.69</v>
+        <v>436.69</v>
       </c>
       <c r="D3" t="n">
         <v>95</v>
       </c>
       <c r="E3" t="n">
-        <v>8.34</v>
+        <v>3.3</v>
       </c>
       <c r="F3" t="n">
-        <v>0.76</v>
+        <v>0.7</v>
       </c>
       <c r="G3" t="n">
-        <v>15.35</v>
+        <v>15.52</v>
       </c>
       <c r="H3" t="n">
-        <v>3.44</v>
+        <v>3.56</v>
       </c>
       <c r="I3" t="n">
-        <v>440.55</v>
+        <v>430.48</v>
       </c>
       <c r="J3" t="n">
-        <v>450.53</v>
+        <v>440.57</v>
       </c>
       <c r="K3" t="n">
-        <v>423.66</v>
+        <v>413.4</v>
       </c>
       <c r="L3" t="n">
-        <v>485.07</v>
+        <v>475.5</v>
       </c>
       <c r="M3" t="n">
-        <v>70.98999999999999</v>
+        <v>64.73</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>MEDIO</t>
+          <t>BAJO</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -630,37 +630,37 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1705.37</v>
+        <v>1726.36</v>
       </c>
       <c r="D4" t="n">
         <v>95</v>
       </c>
       <c r="E4" t="n">
-        <v>4.49</v>
+        <v>8.039999999999999</v>
       </c>
       <c r="F4" t="n">
-        <v>0.91</v>
+        <v>1.11</v>
       </c>
       <c r="G4" t="n">
-        <v>63.18</v>
+        <v>61.15</v>
       </c>
       <c r="H4" t="n">
-        <v>3.7</v>
+        <v>3.54</v>
       </c>
       <c r="I4" t="n">
-        <v>1680.1</v>
+        <v>1701.9</v>
       </c>
       <c r="J4" t="n">
-        <v>1721.16</v>
+        <v>1741.65</v>
       </c>
       <c r="K4" t="n">
-        <v>1610.6</v>
+        <v>1634.63</v>
       </c>
       <c r="L4" t="n">
-        <v>1863.32</v>
+        <v>1879.24</v>
       </c>
       <c r="M4" t="n">
-        <v>68.27</v>
+        <v>65.56999999999999</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -690,37 +690,37 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>490.05</v>
+        <v>500.77</v>
       </c>
       <c r="D5" t="n">
         <v>95</v>
       </c>
       <c r="E5" t="n">
-        <v>7.73</v>
+        <v>11.72</v>
       </c>
       <c r="F5" t="n">
-        <v>1.16</v>
+        <v>1.01</v>
       </c>
       <c r="G5" t="n">
-        <v>20.31</v>
+        <v>20.5</v>
       </c>
       <c r="H5" t="n">
-        <v>4.14</v>
+        <v>4.09</v>
       </c>
       <c r="I5" t="n">
-        <v>481.93</v>
+        <v>492.57</v>
       </c>
       <c r="J5" t="n">
-        <v>495.13</v>
+        <v>505.9</v>
       </c>
       <c r="K5" t="n">
-        <v>459.58</v>
+        <v>470.02</v>
       </c>
       <c r="L5" t="n">
-        <v>540.83</v>
+        <v>552.02</v>
       </c>
       <c r="M5" t="n">
-        <v>71.23</v>
+        <v>72.28</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
@@ -750,37 +750,37 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>334.41</v>
+        <v>343.71</v>
       </c>
       <c r="D6" t="n">
         <v>95</v>
       </c>
       <c r="E6" t="n">
-        <v>3.64</v>
+        <v>7.77</v>
       </c>
       <c r="F6" t="n">
-        <v>0.87</v>
+        <v>0.93</v>
       </c>
       <c r="G6" t="n">
-        <v>15.04</v>
+        <v>15.2</v>
       </c>
       <c r="H6" t="n">
-        <v>4.5</v>
+        <v>4.42</v>
       </c>
       <c r="I6" t="n">
-        <v>328.39</v>
+        <v>337.63</v>
       </c>
       <c r="J6" t="n">
-        <v>338.17</v>
+        <v>347.51</v>
       </c>
       <c r="K6" t="n">
-        <v>311.85</v>
+        <v>320.91</v>
       </c>
       <c r="L6" t="n">
-        <v>372.01</v>
+        <v>381.71</v>
       </c>
       <c r="M6" t="n">
-        <v>70.88</v>
+        <v>71.69</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
@@ -801,50 +801,50 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>NVDA</t>
+          <t>KLAC</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>IA / Chips</t>
+          <t>Equipos chips</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>222.82</v>
+        <v>2125.11</v>
       </c>
       <c r="D7" t="n">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="E7" t="n">
-        <v>3.7</v>
+        <v>8.58</v>
       </c>
       <c r="F7" t="n">
-        <v>0.96</v>
+        <v>0.99</v>
       </c>
       <c r="G7" t="n">
-        <v>8.34</v>
+        <v>88.22</v>
       </c>
       <c r="H7" t="n">
-        <v>3.74</v>
+        <v>4.15</v>
       </c>
       <c r="I7" t="n">
-        <v>219.48</v>
+        <v>2089.82</v>
       </c>
       <c r="J7" t="n">
-        <v>224.9</v>
+        <v>2147.17</v>
       </c>
       <c r="K7" t="n">
-        <v>210.31</v>
+        <v>1992.78</v>
       </c>
       <c r="L7" t="n">
-        <v>243.66</v>
+        <v>2345.66</v>
       </c>
       <c r="M7" t="n">
-        <v>51.61</v>
+        <v>68.34999999999999</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>BAJO</t>
+          <t>MEDIO</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -861,46 +861,46 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>QQQ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Tecnología</t>
+          <t>ETF Nasdaq</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>441.31</v>
+        <v>744.21</v>
       </c>
       <c r="D8" t="n">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="E8" t="n">
-        <v>6.08</v>
+        <v>2.02</v>
       </c>
       <c r="F8" t="n">
-        <v>1.01</v>
+        <v>0.97</v>
       </c>
       <c r="G8" t="n">
-        <v>12.93</v>
+        <v>9.9</v>
       </c>
       <c r="H8" t="n">
-        <v>2.93</v>
+        <v>1.33</v>
       </c>
       <c r="I8" t="n">
-        <v>436.14</v>
+        <v>740.25</v>
       </c>
       <c r="J8" t="n">
-        <v>444.54</v>
+        <v>746.6900000000001</v>
       </c>
       <c r="K8" t="n">
-        <v>421.91</v>
+        <v>729.35</v>
       </c>
       <c r="L8" t="n">
-        <v>473.64</v>
+        <v>768.97</v>
       </c>
       <c r="M8" t="n">
-        <v>66.37</v>
+        <v>70.61</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
@@ -921,50 +921,50 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>OXY</t>
+          <t>QCOM</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Energía</t>
+          <t>Chips</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>59.09</v>
+        <v>250.01</v>
       </c>
       <c r="D9" t="n">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="E9" t="n">
-        <v>2.84</v>
+        <v>7.12</v>
       </c>
       <c r="F9" t="n">
-        <v>0.78</v>
+        <v>0.68</v>
       </c>
       <c r="G9" t="n">
-        <v>1.85</v>
+        <v>18.14</v>
       </c>
       <c r="H9" t="n">
-        <v>3.13</v>
+        <v>7.26</v>
       </c>
       <c r="I9" t="n">
-        <v>58.35</v>
+        <v>242.75</v>
       </c>
       <c r="J9" t="n">
-        <v>59.55</v>
+        <v>254.55</v>
       </c>
       <c r="K9" t="n">
-        <v>56.32</v>
+        <v>222.79</v>
       </c>
       <c r="L9" t="n">
-        <v>63.71</v>
+        <v>295.37</v>
       </c>
       <c r="M9" t="n">
-        <v>61.75</v>
+        <v>61.96</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>BAJO</t>
+          <t>MEDIO</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -981,50 +981,50 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>UPST</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Fintech IA</t>
+          <t>Tecnología</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>32.39</v>
+        <v>427.34</v>
       </c>
       <c r="D10" t="n">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="E10" t="n">
-        <v>5.78</v>
+        <v>3.55</v>
       </c>
       <c r="F10" t="n">
-        <v>0.91</v>
+        <v>0.97</v>
       </c>
       <c r="G10" t="n">
-        <v>1.98</v>
+        <v>13.67</v>
       </c>
       <c r="H10" t="n">
-        <v>6.1</v>
+        <v>3.2</v>
       </c>
       <c r="I10" t="n">
-        <v>31.6</v>
+        <v>421.87</v>
       </c>
       <c r="J10" t="n">
-        <v>32.88</v>
+        <v>430.76</v>
       </c>
       <c r="K10" t="n">
-        <v>29.43</v>
+        <v>406.84</v>
       </c>
       <c r="L10" t="n">
-        <v>37.33</v>
+        <v>461.51</v>
       </c>
       <c r="M10" t="n">
-        <v>67.27</v>
+        <v>59.87</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>MEDIO</t>
+          <t>BAJO</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1041,46 +1041,46 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>KLAC</t>
+          <t>CVX</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Equipos chips</t>
+          <t>Energía</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>2045.2</v>
+        <v>189.71</v>
       </c>
       <c r="D11" t="n">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="E11" t="n">
-        <v>1.68</v>
+        <v>4.01</v>
       </c>
       <c r="F11" t="n">
-        <v>1.03</v>
+        <v>0.71</v>
       </c>
       <c r="G11" t="n">
-        <v>84.23</v>
+        <v>4.59</v>
       </c>
       <c r="H11" t="n">
-        <v>4.12</v>
+        <v>2.42</v>
       </c>
       <c r="I11" t="n">
-        <v>2011.51</v>
+        <v>187.87</v>
       </c>
       <c r="J11" t="n">
-        <v>2066.26</v>
+        <v>190.86</v>
       </c>
       <c r="K11" t="n">
-        <v>1918.86</v>
+        <v>182.83</v>
       </c>
       <c r="L11" t="n">
-        <v>2255.76</v>
+        <v>201.18</v>
       </c>
       <c r="M11" t="n">
-        <v>66.51000000000001</v>
+        <v>57.28</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
@@ -1089,7 +1089,7 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1101,55 +1101,55 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SPY</t>
+          <t>OXY</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>ETF Mercado</t>
+          <t>Energía</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>759.5700000000001</v>
+        <v>59.64</v>
       </c>
       <c r="D12" t="n">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="E12" t="n">
-        <v>1.2</v>
+        <v>4.83</v>
       </c>
       <c r="F12" t="n">
-        <v>0.59</v>
+        <v>0.7</v>
       </c>
       <c r="G12" t="n">
-        <v>6.54</v>
+        <v>1.9</v>
       </c>
       <c r="H12" t="n">
-        <v>0.86</v>
+        <v>3.18</v>
       </c>
       <c r="I12" t="n">
-        <v>756.96</v>
+        <v>58.88</v>
       </c>
       <c r="J12" t="n">
-        <v>761.2</v>
+        <v>60.11</v>
       </c>
       <c r="K12" t="n">
-        <v>749.77</v>
+        <v>56.79</v>
       </c>
       <c r="L12" t="n">
-        <v>775.91</v>
+        <v>64.38</v>
       </c>
       <c r="M12" t="n">
-        <v>71.17</v>
+        <v>63.88</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>MEDIO</t>
+          <t>BAJO</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1161,46 +1161,46 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>QCOM</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Chips</t>
+          <t>IA / Chips</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>240.84</v>
+        <v>542.52</v>
       </c>
       <c r="D13" t="n">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.21</v>
+        <v>9.48</v>
       </c>
       <c r="F13" t="n">
-        <v>0.63</v>
+        <v>0.77</v>
       </c>
       <c r="G13" t="n">
-        <v>17.45</v>
+        <v>27.6</v>
       </c>
       <c r="H13" t="n">
-        <v>7.24</v>
+        <v>5.09</v>
       </c>
       <c r="I13" t="n">
-        <v>233.86</v>
+        <v>531.48</v>
       </c>
       <c r="J13" t="n">
-        <v>245.2</v>
+        <v>549.42</v>
       </c>
       <c r="K13" t="n">
-        <v>214.67</v>
+        <v>501.13</v>
       </c>
       <c r="L13" t="n">
-        <v>284.46</v>
+        <v>611.51</v>
       </c>
       <c r="M13" t="n">
-        <v>60.34</v>
+        <v>74.14</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
@@ -1209,7 +1209,7 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1221,55 +1221,55 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>SLB</t>
+          <t>PLTR</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Energía</t>
+          <t>IA / Software</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>56.56</v>
+        <v>142.2</v>
       </c>
       <c r="D14" t="n">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="E14" t="n">
-        <v>-2.45</v>
+        <v>7.31</v>
       </c>
       <c r="F14" t="n">
-        <v>0.74</v>
+        <v>0.96</v>
       </c>
       <c r="G14" t="n">
-        <v>1.46</v>
+        <v>6.89</v>
       </c>
       <c r="H14" t="n">
-        <v>2.59</v>
+        <v>4.84</v>
       </c>
       <c r="I14" t="n">
-        <v>55.97</v>
+        <v>139.45</v>
       </c>
       <c r="J14" t="n">
-        <v>56.93</v>
+        <v>143.92</v>
       </c>
       <c r="K14" t="n">
-        <v>54.36</v>
+        <v>131.87</v>
       </c>
       <c r="L14" t="n">
-        <v>60.22</v>
+        <v>159.41</v>
       </c>
       <c r="M14" t="n">
-        <v>54.67</v>
+        <v>60.32</v>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>BAJO</t>
+          <t>MEDIO</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -1281,7 +1281,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>CVX</t>
+          <t>XOM</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1290,37 +1290,37 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>187.55</v>
+        <v>152.53</v>
       </c>
       <c r="D15" t="n">
         <v>82</v>
       </c>
       <c r="E15" t="n">
-        <v>1.54</v>
+        <v>3.13</v>
       </c>
       <c r="F15" t="n">
-        <v>0.58</v>
+        <v>0.82</v>
       </c>
       <c r="G15" t="n">
-        <v>4.44</v>
+        <v>4.37</v>
       </c>
       <c r="H15" t="n">
-        <v>2.37</v>
+        <v>2.86</v>
       </c>
       <c r="I15" t="n">
-        <v>185.77</v>
+        <v>150.78</v>
       </c>
       <c r="J15" t="n">
-        <v>188.66</v>
+        <v>153.62</v>
       </c>
       <c r="K15" t="n">
-        <v>180.89</v>
+        <v>145.98</v>
       </c>
       <c r="L15" t="n">
-        <v>198.66</v>
+        <v>163.45</v>
       </c>
       <c r="M15" t="n">
-        <v>54.7</v>
+        <v>52.71</v>
       </c>
       <c r="N15" t="inlineStr">
         <is>
@@ -1329,7 +1329,7 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -1341,55 +1341,55 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>SOUN</t>
+          <t>META</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>IA</t>
+          <t>Tecnología</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>8.82</v>
+        <v>622.98</v>
       </c>
       <c r="D16" t="n">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="E16" t="n">
-        <v>8.49</v>
+        <v>-1.93</v>
       </c>
       <c r="F16" t="n">
-        <v>1.01</v>
+        <v>1.3</v>
       </c>
       <c r="G16" t="n">
-        <v>0.5</v>
+        <v>15.57</v>
       </c>
       <c r="H16" t="n">
-        <v>5.67</v>
+        <v>2.5</v>
       </c>
       <c r="I16" t="n">
-        <v>8.619999999999999</v>
+        <v>616.75</v>
       </c>
       <c r="J16" t="n">
-        <v>8.949999999999999</v>
+        <v>626.87</v>
       </c>
       <c r="K16" t="n">
-        <v>8.07</v>
+        <v>599.63</v>
       </c>
       <c r="L16" t="n">
-        <v>10.07</v>
+        <v>661.9</v>
       </c>
       <c r="M16" t="n">
-        <v>64.06999999999999</v>
+        <v>52.8</v>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>MEDIO</t>
+          <t>BAJO</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -1401,50 +1401,50 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>PLTR</t>
+          <t>SPY</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>IA / Software</t>
+          <t>ETF Mercado</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>152.17</v>
+        <v>754.24</v>
       </c>
       <c r="D17" t="n">
-        <v>76</v>
+        <v>95</v>
       </c>
       <c r="E17" t="n">
-        <v>11.4</v>
+        <v>0.5</v>
       </c>
       <c r="F17" t="n">
-        <v>0.95</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="G17" t="n">
-        <v>6.69</v>
+        <v>6.36</v>
       </c>
       <c r="H17" t="n">
-        <v>4.4</v>
+        <v>0.84</v>
       </c>
       <c r="I17" t="n">
-        <v>149.49</v>
+        <v>751.7</v>
       </c>
       <c r="J17" t="n">
-        <v>153.84</v>
+        <v>755.83</v>
       </c>
       <c r="K17" t="n">
-        <v>142.13</v>
+        <v>744.7</v>
       </c>
       <c r="L17" t="n">
-        <v>168.9</v>
+        <v>770.15</v>
       </c>
       <c r="M17" t="n">
-        <v>64.73999999999999</v>
+        <v>61.53</v>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>MEDIO</t>
+          <t>BAJO</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
@@ -1461,46 +1461,46 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>GOOGL</t>
+          <t>SLB</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Tecnología</t>
+          <t>Energía</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>361.85</v>
+        <v>56.85</v>
       </c>
       <c r="D18" t="n">
-        <v>68</v>
+        <v>92</v>
       </c>
       <c r="E18" t="n">
-        <v>-6.95</v>
+        <v>0.62</v>
       </c>
       <c r="F18" t="n">
-        <v>1.67</v>
+        <v>0.87</v>
       </c>
       <c r="G18" t="n">
-        <v>10.28</v>
+        <v>1.49</v>
       </c>
       <c r="H18" t="n">
-        <v>2.84</v>
+        <v>2.63</v>
       </c>
       <c r="I18" t="n">
-        <v>357.74</v>
+        <v>56.25</v>
       </c>
       <c r="J18" t="n">
-        <v>364.42</v>
+        <v>57.22</v>
       </c>
       <c r="K18" t="n">
-        <v>346.42</v>
+        <v>54.61</v>
       </c>
       <c r="L18" t="n">
-        <v>387.56</v>
+        <v>60.59</v>
       </c>
       <c r="M18" t="n">
-        <v>32.6</v>
+        <v>57.43</v>
       </c>
       <c r="N18" t="inlineStr">
         <is>
@@ -1514,57 +1514,57 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>VIGILAR</t>
+          <t>POSIBLE COMPRA</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>SOFI</t>
+          <t>AAPL</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Fintech</t>
+          <t>Tecnología</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>17.74</v>
+        <v>310.26</v>
       </c>
       <c r="D19" t="n">
-        <v>68</v>
+        <v>80</v>
       </c>
       <c r="E19" t="n">
-        <v>11.01</v>
+        <v>-0.19</v>
       </c>
       <c r="F19" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="G19" t="n">
-        <v>0.91</v>
+        <v>5.72</v>
       </c>
       <c r="H19" t="n">
-        <v>5.14</v>
+        <v>1.84</v>
       </c>
       <c r="I19" t="n">
-        <v>17.38</v>
+        <v>307.97</v>
       </c>
       <c r="J19" t="n">
-        <v>17.97</v>
+        <v>311.69</v>
       </c>
       <c r="K19" t="n">
-        <v>16.37</v>
+        <v>301.69</v>
       </c>
       <c r="L19" t="n">
-        <v>20.02</v>
+        <v>324.55</v>
       </c>
       <c r="M19" t="n">
-        <v>63.9</v>
+        <v>63.98</v>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>MEDIO</t>
+          <t>BAJO</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
@@ -1574,238 +1574,250 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>VIGILAR</t>
+          <t>POSIBLE COMPRA</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>AMZN</t>
+          <t>HOOD</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Tecnología</t>
+          <t>Trading</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>256.52</v>
+        <v>82.84999999999999</v>
       </c>
       <c r="D20" t="n">
-        <v>64</v>
+        <v>78</v>
       </c>
       <c r="E20" t="n">
-        <v>-3.31</v>
+        <v>8.68</v>
       </c>
       <c r="F20" t="n">
-        <v>1.05</v>
+        <v>0.93</v>
       </c>
       <c r="G20" t="n">
-        <v>6.8</v>
+        <v>5.32</v>
       </c>
       <c r="H20" t="n">
-        <v>2.65</v>
+        <v>6.42</v>
       </c>
       <c r="I20" t="n">
-        <v>253.8</v>
+        <v>80.72</v>
       </c>
       <c r="J20" t="n">
-        <v>258.22</v>
+        <v>84.18000000000001</v>
       </c>
       <c r="K20" t="n">
-        <v>246.31</v>
+        <v>74.87</v>
       </c>
       <c r="L20" t="n">
-        <v>273.53</v>
+        <v>96.15000000000001</v>
       </c>
       <c r="M20" t="n">
-        <v>41.55</v>
+        <v>56.54</v>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>BAJO</t>
-        </is>
-      </c>
-      <c r="O20" t="inlineStr"/>
+          <t>MEDIO</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>🔥</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>VIGILAR</t>
+          <t>POSIBLE COMPRA</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>PYPL</t>
+          <t>UPST</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Pagos</t>
+          <t>Fintech IA</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>44.53</v>
+        <v>30.29</v>
       </c>
       <c r="D21" t="n">
-        <v>62</v>
+        <v>76</v>
       </c>
       <c r="E21" t="n">
-        <v>0.84</v>
+        <v>-1.4</v>
       </c>
       <c r="F21" t="n">
-        <v>0.6899999999999999</v>
+        <v>1.04</v>
       </c>
       <c r="G21" t="n">
-        <v>1.05</v>
+        <v>2.06</v>
       </c>
       <c r="H21" t="n">
-        <v>2.37</v>
+        <v>6.8</v>
       </c>
       <c r="I21" t="n">
-        <v>44.11</v>
+        <v>29.47</v>
       </c>
       <c r="J21" t="n">
-        <v>44.79</v>
+        <v>30.8</v>
       </c>
       <c r="K21" t="n">
-        <v>42.95</v>
+        <v>27.2</v>
       </c>
       <c r="L21" t="n">
-        <v>47.16</v>
+        <v>35.44</v>
       </c>
       <c r="M21" t="n">
-        <v>40.64</v>
+        <v>61.44</v>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>BAJO</t>
+          <t>MEDIO</t>
         </is>
       </c>
       <c r="O21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>VIGILAR</t>
+          <t>POSIBLE COMPRA</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>TSLA</t>
+          <t>SOFI</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Autos / Tech</t>
+          <t>Fintech</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>423.74</v>
+        <v>16.68</v>
       </c>
       <c r="D22" t="n">
-        <v>54</v>
+        <v>74</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.27</v>
+        <v>3.15</v>
       </c>
       <c r="F22" t="n">
-        <v>0.71</v>
+        <v>1.04</v>
       </c>
       <c r="G22" t="n">
-        <v>14.52</v>
+        <v>0.95</v>
       </c>
       <c r="H22" t="n">
-        <v>3.43</v>
+        <v>5.67</v>
       </c>
       <c r="I22" t="n">
-        <v>417.93</v>
+        <v>16.3</v>
       </c>
       <c r="J22" t="n">
-        <v>427.37</v>
+        <v>16.92</v>
       </c>
       <c r="K22" t="n">
-        <v>401.96</v>
+        <v>15.26</v>
       </c>
       <c r="L22" t="n">
-        <v>460.05</v>
+        <v>19.05</v>
       </c>
       <c r="M22" t="n">
-        <v>46.12</v>
+        <v>59.66</v>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>BAJO</t>
-        </is>
-      </c>
-      <c r="O22" t="inlineStr"/>
+          <t>MEDIO</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>🔥</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>NO COMPRAR</t>
+          <t>VIGILAR</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>XOM</t>
+          <t>GOOGL</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Energía</t>
+          <t>Tecnología</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>149.56</v>
+        <v>358.99</v>
       </c>
       <c r="D23" t="n">
-        <v>54</v>
+        <v>68</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.17</v>
+        <v>-7.67</v>
       </c>
       <c r="F23" t="n">
-        <v>0.6</v>
+        <v>1.76</v>
       </c>
       <c r="G23" t="n">
-        <v>4.14</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="H23" t="n">
-        <v>2.77</v>
+        <v>2.66</v>
       </c>
       <c r="I23" t="n">
-        <v>147.91</v>
+        <v>355.17</v>
       </c>
       <c r="J23" t="n">
-        <v>150.59</v>
+        <v>361.38</v>
       </c>
       <c r="K23" t="n">
-        <v>143.36</v>
+        <v>344.67</v>
       </c>
       <c r="L23" t="n">
-        <v>159.9</v>
+        <v>382.86</v>
       </c>
       <c r="M23" t="n">
-        <v>49.92</v>
+        <v>14.16</v>
       </c>
       <c r="N23" t="inlineStr">
         <is>
           <t>BAJO</t>
         </is>
       </c>
-      <c r="O23" t="inlineStr"/>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>🔥</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>NO COMPRAR</t>
+          <t>VIGILAR</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>META</t>
+          <t>AMZN</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1814,100 +1826,108 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>597.63</v>
+        <v>250.02</v>
       </c>
       <c r="D24" t="n">
-        <v>44</v>
+        <v>63</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.4</v>
+        <v>-8.029999999999999</v>
       </c>
       <c r="F24" t="n">
-        <v>1.15</v>
+        <v>1.28</v>
       </c>
       <c r="G24" t="n">
-        <v>15.34</v>
+        <v>6.94</v>
       </c>
       <c r="H24" t="n">
-        <v>2.57</v>
+        <v>2.77</v>
       </c>
       <c r="I24" t="n">
-        <v>591.5</v>
+        <v>247.25</v>
       </c>
       <c r="J24" t="n">
-        <v>601.46</v>
+        <v>251.75</v>
       </c>
       <c r="K24" t="n">
-        <v>574.63</v>
+        <v>239.62</v>
       </c>
       <c r="L24" t="n">
-        <v>635.97</v>
+        <v>267.36</v>
       </c>
       <c r="M24" t="n">
-        <v>47.36</v>
+        <v>32.42</v>
       </c>
       <c r="N24" t="inlineStr">
         <is>
           <t>BAJO</t>
         </is>
       </c>
-      <c r="O24" t="inlineStr"/>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>🔥</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>NO COMPRAR</t>
+          <t>VIGILAR</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>COIN</t>
+          <t>PYPL</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Cripto / Trading</t>
+          <t>Pagos</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>173.99</v>
+        <v>42.61</v>
       </c>
       <c r="D25" t="n">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="E25" t="n">
-        <v>-3.34</v>
+        <v>-2.63</v>
       </c>
       <c r="F25" t="n">
-        <v>0.86</v>
+        <v>1.28</v>
       </c>
       <c r="G25" t="n">
-        <v>12.11</v>
+        <v>1.13</v>
       </c>
       <c r="H25" t="n">
-        <v>6.96</v>
+        <v>2.65</v>
       </c>
       <c r="I25" t="n">
-        <v>169.15</v>
+        <v>42.16</v>
       </c>
       <c r="J25" t="n">
-        <v>177.02</v>
+        <v>42.89</v>
       </c>
       <c r="K25" t="n">
-        <v>155.83</v>
+        <v>40.92</v>
       </c>
       <c r="L25" t="n">
-        <v>204.26</v>
+        <v>45.43</v>
       </c>
       <c r="M25" t="n">
-        <v>32.68</v>
+        <v>30.06</v>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>MEDIO</t>
-        </is>
-      </c>
-      <c r="O25" t="inlineStr"/>
+          <t>BAJO</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>🔥</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>NO COMPRAR</t>
@@ -1917,7 +1937,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>AVGO</t>
+          <t>NVDA</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1926,48 +1946,44 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>481.57</v>
+        <v>214.75</v>
       </c>
       <c r="D26" t="n">
-        <v>95</v>
+        <v>72</v>
       </c>
       <c r="E26" t="n">
-        <v>14.11</v>
+        <v>1.01</v>
       </c>
       <c r="F26" t="n">
-        <v>1.62</v>
+        <v>0.85</v>
       </c>
       <c r="G26" t="n">
-        <v>17.84</v>
+        <v>8.43</v>
       </c>
       <c r="H26" t="n">
-        <v>3.7</v>
+        <v>3.92</v>
       </c>
       <c r="I26" t="n">
-        <v>474.44</v>
+        <v>211.38</v>
       </c>
       <c r="J26" t="n">
-        <v>486.03</v>
+        <v>216.86</v>
       </c>
       <c r="K26" t="n">
-        <v>454.82</v>
+        <v>202.11</v>
       </c>
       <c r="L26" t="n">
-        <v>526.16</v>
+        <v>235.82</v>
       </c>
       <c r="M26" t="n">
-        <v>73.54000000000001</v>
+        <v>41.65</v>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>ALTO</t>
-        </is>
-      </c>
-      <c r="O26" t="inlineStr">
-        <is>
-          <t>🔥🔥</t>
-        </is>
-      </c>
+          <t>BAJO</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>VIGILAR</t>
@@ -1977,293 +1993,281 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>SOXX</t>
+          <t>INTC</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>ETF Chips</t>
+          <t>Chips</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>605.02</v>
+        <v>112.71</v>
       </c>
       <c r="D27" t="n">
-        <v>86</v>
+        <v>56</v>
       </c>
       <c r="E27" t="n">
-        <v>6.13</v>
+        <v>-7.44</v>
       </c>
       <c r="F27" t="n">
-        <v>0.84</v>
+        <v>0.86</v>
       </c>
       <c r="G27" t="n">
-        <v>23.27</v>
+        <v>8.77</v>
       </c>
       <c r="H27" t="n">
-        <v>3.85</v>
+        <v>7.78</v>
       </c>
       <c r="I27" t="n">
-        <v>595.71</v>
+        <v>109.2</v>
       </c>
       <c r="J27" t="n">
-        <v>610.84</v>
+        <v>114.9</v>
       </c>
       <c r="K27" t="n">
-        <v>570.11</v>
+        <v>99.56</v>
       </c>
       <c r="L27" t="n">
-        <v>663.21</v>
+        <v>134.63</v>
       </c>
       <c r="M27" t="n">
-        <v>76.13</v>
+        <v>42.23</v>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>ALTO</t>
-        </is>
-      </c>
-      <c r="O27" t="inlineStr">
-        <is>
-          <t>🔥</t>
-        </is>
-      </c>
+          <t>MEDIO</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>VIGILAR</t>
+          <t>NO COMPRAR</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>TSLA</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Tecnología</t>
+          <t>Autos / Tech</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>315.2</v>
+        <v>423.7</v>
       </c>
       <c r="D28" t="n">
-        <v>82</v>
+        <v>54</v>
       </c>
       <c r="E28" t="n">
-        <v>2.23</v>
+        <v>-3.78</v>
       </c>
       <c r="F28" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.86</v>
       </c>
       <c r="G28" t="n">
-        <v>5.67</v>
+        <v>14.14</v>
       </c>
       <c r="H28" t="n">
-        <v>1.8</v>
+        <v>3.34</v>
       </c>
       <c r="I28" t="n">
-        <v>312.93</v>
+        <v>418.04</v>
       </c>
       <c r="J28" t="n">
-        <v>316.62</v>
+        <v>427.24</v>
       </c>
       <c r="K28" t="n">
-        <v>306.7</v>
+        <v>402.49</v>
       </c>
       <c r="L28" t="n">
-        <v>329.37</v>
+        <v>459.06</v>
       </c>
       <c r="M28" t="n">
-        <v>75.58</v>
+        <v>40.48</v>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>ALTO</t>
-        </is>
-      </c>
-      <c r="O28" t="inlineStr">
-        <is>
-          <t>🔥</t>
-        </is>
-      </c>
+          <t>BAJO</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>VIGILAR</t>
+          <t>NO COMPRAR</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>QQQ</t>
+          <t>SOUN</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>ETF Nasdaq</t>
+          <t>IA</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>746.16</v>
+        <v>8.08</v>
       </c>
       <c r="D29" t="n">
-        <v>82</v>
+        <v>46</v>
       </c>
       <c r="E29" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="F29" t="n">
-        <v>0.73</v>
+        <v>0.99</v>
       </c>
       <c r="G29" t="n">
-        <v>10.2</v>
+        <v>0.5</v>
       </c>
       <c r="H29" t="n">
-        <v>1.37</v>
+        <v>6.21</v>
       </c>
       <c r="I29" t="n">
-        <v>742.08</v>
+        <v>7.88</v>
       </c>
       <c r="J29" t="n">
-        <v>748.71</v>
+        <v>8.210000000000001</v>
       </c>
       <c r="K29" t="n">
-        <v>730.85</v>
+        <v>7.33</v>
       </c>
       <c r="L29" t="n">
-        <v>771.67</v>
+        <v>9.33</v>
       </c>
       <c r="M29" t="n">
-        <v>75.23999999999999</v>
+        <v>44.48</v>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>ALTO</t>
-        </is>
-      </c>
-      <c r="O29" t="inlineStr">
-        <is>
-          <t>🔥</t>
-        </is>
-      </c>
+          <t>MEDIO</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>VIGILAR</t>
+          <t>NO COMPRAR</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>AI</t>
+          <t>COIN</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>IA</t>
+          <t>Cripto / Trading</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>11.18</v>
+        <v>163.22</v>
       </c>
       <c r="D30" t="n">
-        <v>66</v>
+        <v>38</v>
       </c>
       <c r="E30" t="n">
-        <v>16.58</v>
+        <v>-6.08</v>
       </c>
       <c r="F30" t="n">
-        <v>1.76</v>
+        <v>0.96</v>
       </c>
       <c r="G30" t="n">
-        <v>0.58</v>
+        <v>12.19</v>
       </c>
       <c r="H30" t="n">
-        <v>5.2</v>
+        <v>7.47</v>
       </c>
       <c r="I30" t="n">
-        <v>10.95</v>
+        <v>158.34</v>
       </c>
       <c r="J30" t="n">
-        <v>11.33</v>
+        <v>166.27</v>
       </c>
       <c r="K30" t="n">
-        <v>10.31</v>
+        <v>144.94</v>
       </c>
       <c r="L30" t="n">
-        <v>12.63</v>
+        <v>193.69</v>
       </c>
       <c r="M30" t="n">
-        <v>75.7</v>
+        <v>31.1</v>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>ALTO</t>
-        </is>
-      </c>
-      <c r="O30" t="inlineStr">
-        <is>
-          <t>🔥</t>
-        </is>
-      </c>
+          <t>MEDIO</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>VIGILAR</t>
+          <t>NO COMPRAR</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>IONQ</t>
+          <t>AVGO</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Computación cuántica</t>
+          <t>IA / Chips</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>71.40000000000001</v>
+        <v>479.23</v>
       </c>
       <c r="D31" t="n">
-        <v>79</v>
+        <v>95</v>
       </c>
       <c r="E31" t="n">
-        <v>12.23</v>
+        <v>13.6</v>
       </c>
       <c r="F31" t="n">
-        <v>0.76</v>
+        <v>1.61</v>
       </c>
       <c r="G31" t="n">
-        <v>5.45</v>
+        <v>18.4</v>
       </c>
       <c r="H31" t="n">
-        <v>7.63</v>
+        <v>3.84</v>
       </c>
       <c r="I31" t="n">
-        <v>69.22</v>
+        <v>471.87</v>
       </c>
       <c r="J31" t="n">
-        <v>72.76000000000001</v>
+        <v>483.83</v>
       </c>
       <c r="K31" t="n">
-        <v>63.22</v>
+        <v>451.63</v>
       </c>
       <c r="L31" t="n">
-        <v>85.03</v>
+        <v>525.22</v>
       </c>
       <c r="M31" t="n">
-        <v>69.20999999999999</v>
+        <v>73.63</v>
       </c>
       <c r="N31" t="inlineStr">
         <is>
           <t>ALTO</t>
         </is>
       </c>
-      <c r="O31" t="inlineStr"/>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>🔥🔥</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>VIGILAR</t>
@@ -2273,53 +2277,57 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>HOOD</t>
+          <t>MU</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Trading</t>
+          <t>Memoria / Chips</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>88.16</v>
+        <v>1079.57</v>
       </c>
       <c r="D32" t="n">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="E32" t="n">
-        <v>18.99</v>
+        <v>16.28</v>
       </c>
       <c r="F32" t="n">
-        <v>1.02</v>
+        <v>0.71</v>
       </c>
       <c r="G32" t="n">
-        <v>5.12</v>
+        <v>63.27</v>
       </c>
       <c r="H32" t="n">
-        <v>5.81</v>
+        <v>5.86</v>
       </c>
       <c r="I32" t="n">
-        <v>86.11</v>
+        <v>1054.26</v>
       </c>
       <c r="J32" t="n">
-        <v>89.44</v>
+        <v>1095.39</v>
       </c>
       <c r="K32" t="n">
-        <v>80.48</v>
+        <v>984.66</v>
       </c>
       <c r="L32" t="n">
-        <v>100.96</v>
+        <v>1237.76</v>
       </c>
       <c r="M32" t="n">
-        <v>61.53</v>
+        <v>74.98999999999999</v>
       </c>
       <c r="N32" t="inlineStr">
         <is>
           <t>ALTO</t>
         </is>
       </c>
-      <c r="O32" t="inlineStr"/>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>🔥</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>VIGILAR</t>
@@ -2329,53 +2337,57 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>MU</t>
+          <t>SOXX</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Memoria / Chips</t>
+          <t>ETF Chips</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>1064.1</v>
+        <v>615.6799999999999</v>
       </c>
       <c r="D33" t="n">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="E33" t="n">
-        <v>18.78</v>
+        <v>9.17</v>
       </c>
       <c r="F33" t="n">
-        <v>0.82</v>
+        <v>0.95</v>
       </c>
       <c r="G33" t="n">
-        <v>63.09</v>
+        <v>23.6</v>
       </c>
       <c r="H33" t="n">
-        <v>5.93</v>
+        <v>3.83</v>
       </c>
       <c r="I33" t="n">
-        <v>1038.86</v>
+        <v>606.24</v>
       </c>
       <c r="J33" t="n">
-        <v>1079.87</v>
+        <v>621.58</v>
       </c>
       <c r="K33" t="n">
-        <v>969.46</v>
+        <v>580.28</v>
       </c>
       <c r="L33" t="n">
-        <v>1221.83</v>
+        <v>674.67</v>
       </c>
       <c r="M33" t="n">
-        <v>75.93000000000001</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="N33" t="inlineStr">
         <is>
           <t>ALTO</t>
         </is>
       </c>
-      <c r="O33" t="inlineStr"/>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>🔥</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>VIGILAR</t>
@@ -2385,53 +2397,57 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>RKLB</t>
+          <t>IONQ</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Espacial</t>
+          <t>Computación cuántica</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>123.32</v>
+        <v>68.23</v>
       </c>
       <c r="D34" t="n">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="E34" t="n">
-        <v>-13.88</v>
+        <v>4.33</v>
       </c>
       <c r="F34" t="n">
-        <v>0.61</v>
+        <v>0.84</v>
       </c>
       <c r="G34" t="n">
-        <v>12.33</v>
+        <v>5.66</v>
       </c>
       <c r="H34" t="n">
-        <v>10</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="I34" t="n">
-        <v>118.39</v>
+        <v>65.97</v>
       </c>
       <c r="J34" t="n">
-        <v>126.4</v>
+        <v>69.64</v>
       </c>
       <c r="K34" t="n">
-        <v>104.83</v>
+        <v>59.74</v>
       </c>
       <c r="L34" t="n">
-        <v>154.14</v>
+        <v>82.37</v>
       </c>
       <c r="M34" t="n">
-        <v>52.81</v>
+        <v>65.08</v>
       </c>
       <c r="N34" t="inlineStr">
         <is>
           <t>ALTO</t>
         </is>
       </c>
-      <c r="O34" t="inlineStr"/>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>🔥</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>VIGILAR</t>
@@ -2450,37 +2466,37 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>402.71</v>
+        <v>411.83</v>
       </c>
       <c r="D35" t="n">
         <v>64</v>
       </c>
       <c r="E35" t="n">
-        <v>25.37</v>
+        <v>36.05</v>
       </c>
       <c r="F35" t="n">
-        <v>1.11</v>
+        <v>0.84</v>
       </c>
       <c r="G35" t="n">
-        <v>29.46</v>
+        <v>31.53</v>
       </c>
       <c r="H35" t="n">
-        <v>7.32</v>
+        <v>7.66</v>
       </c>
       <c r="I35" t="n">
-        <v>390.93</v>
+        <v>399.22</v>
       </c>
       <c r="J35" t="n">
-        <v>410.07</v>
+        <v>419.71</v>
       </c>
       <c r="K35" t="n">
-        <v>358.52</v>
+        <v>364.53</v>
       </c>
       <c r="L35" t="n">
-        <v>476.36</v>
+        <v>490.66</v>
       </c>
       <c r="M35" t="n">
-        <v>84.44</v>
+        <v>84.20999999999999</v>
       </c>
       <c r="N35" t="inlineStr">
         <is>
@@ -2506,37 +2522,37 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>50.17</v>
+        <v>47.42</v>
       </c>
       <c r="D36" t="n">
         <v>54</v>
       </c>
       <c r="E36" t="n">
-        <v>35.23</v>
+        <v>24.17</v>
       </c>
       <c r="F36" t="n">
-        <v>1.13</v>
+        <v>1.02</v>
       </c>
       <c r="G36" t="n">
-        <v>2.96</v>
+        <v>3.2</v>
       </c>
       <c r="H36" t="n">
-        <v>5.9</v>
+        <v>6.74</v>
       </c>
       <c r="I36" t="n">
-        <v>48.99</v>
+        <v>46.14</v>
       </c>
       <c r="J36" t="n">
-        <v>50.91</v>
+        <v>48.22</v>
       </c>
       <c r="K36" t="n">
-        <v>45.73</v>
+        <v>42.63</v>
       </c>
       <c r="L36" t="n">
-        <v>57.57</v>
+        <v>55.41</v>
       </c>
       <c r="M36" t="n">
-        <v>86.36</v>
+        <v>79.81</v>
       </c>
       <c r="N36" t="inlineStr">
         <is>
@@ -2553,46 +2569,46 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>INTC</t>
+          <t>RKLB</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Chips</t>
+          <t>Espacial</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>107.93</v>
+        <v>114.7</v>
       </c>
       <c r="D37" t="n">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="E37" t="n">
-        <v>-12.62</v>
+        <v>-23.65</v>
       </c>
       <c r="F37" t="n">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="G37" t="n">
-        <v>8.640000000000001</v>
+        <v>12.29</v>
       </c>
       <c r="H37" t="n">
-        <v>8.01</v>
+        <v>10.71</v>
       </c>
       <c r="I37" t="n">
-        <v>104.47</v>
+        <v>109.79</v>
       </c>
       <c r="J37" t="n">
-        <v>110.09</v>
+        <v>117.77</v>
       </c>
       <c r="K37" t="n">
-        <v>94.97</v>
+        <v>96.27</v>
       </c>
       <c r="L37" t="n">
-        <v>129.53</v>
+        <v>145.41</v>
       </c>
       <c r="M37" t="n">
-        <v>35.69</v>
+        <v>45.47</v>
       </c>
       <c r="N37" t="inlineStr">
         <is>

--- a/analisis_acciones.xlsx
+++ b/analisis_acciones.xlsx
@@ -501,46 +501,46 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AI</t>
+          <t>ASML</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>IA</t>
+          <t>Chips</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>10.71</v>
+        <v>1757.47</v>
       </c>
       <c r="D2" t="n">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="E2" t="n">
-        <v>11.68</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="F2" t="n">
-        <v>2.88</v>
+        <v>1.38</v>
       </c>
       <c r="G2" t="n">
-        <v>0.62</v>
+        <v>65.91</v>
       </c>
       <c r="H2" t="n">
-        <v>5.78</v>
+        <v>3.75</v>
       </c>
       <c r="I2" t="n">
-        <v>10.46</v>
+        <v>1731.11</v>
       </c>
       <c r="J2" t="n">
-        <v>10.86</v>
+        <v>1773.95</v>
       </c>
       <c r="K2" t="n">
-        <v>9.779999999999999</v>
+        <v>1658.6</v>
       </c>
       <c r="L2" t="n">
-        <v>12.26</v>
+        <v>1922.25</v>
       </c>
       <c r="M2" t="n">
-        <v>70.68000000000001</v>
+        <v>67.54000000000001</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -561,55 +561,55 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>SOXX</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Chips</t>
+          <t>ETF Chips</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>436.69</v>
+        <v>602.72</v>
       </c>
       <c r="D3" t="n">
         <v>95</v>
       </c>
       <c r="E3" t="n">
-        <v>3.3</v>
+        <v>5.84</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7</v>
+        <v>1.26</v>
       </c>
       <c r="G3" t="n">
-        <v>15.52</v>
+        <v>25.54</v>
       </c>
       <c r="H3" t="n">
-        <v>3.56</v>
+        <v>4.24</v>
       </c>
       <c r="I3" t="n">
-        <v>430.48</v>
+        <v>592.5</v>
       </c>
       <c r="J3" t="n">
-        <v>440.57</v>
+        <v>609.11</v>
       </c>
       <c r="K3" t="n">
-        <v>413.4</v>
+        <v>564.41</v>
       </c>
       <c r="L3" t="n">
-        <v>475.5</v>
+        <v>666.5700000000001</v>
       </c>
       <c r="M3" t="n">
-        <v>64.73</v>
+        <v>70.2</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>BAJO</t>
+          <t>MEDIO</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>🔥🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -621,46 +621,46 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ASML</t>
+          <t>AI</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Chips</t>
+          <t>IA</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1726.36</v>
+        <v>10.58</v>
       </c>
       <c r="D4" t="n">
         <v>95</v>
       </c>
       <c r="E4" t="n">
-        <v>8.039999999999999</v>
+        <v>3.52</v>
       </c>
       <c r="F4" t="n">
-        <v>1.11</v>
+        <v>2.43</v>
       </c>
       <c r="G4" t="n">
-        <v>61.15</v>
+        <v>0.67</v>
       </c>
       <c r="H4" t="n">
-        <v>3.54</v>
+        <v>6.3</v>
       </c>
       <c r="I4" t="n">
-        <v>1701.9</v>
+        <v>10.31</v>
       </c>
       <c r="J4" t="n">
-        <v>1741.65</v>
+        <v>10.75</v>
       </c>
       <c r="K4" t="n">
-        <v>1634.63</v>
+        <v>9.58</v>
       </c>
       <c r="L4" t="n">
-        <v>1879.24</v>
+        <v>12.25</v>
       </c>
       <c r="M4" t="n">
-        <v>65.56999999999999</v>
+        <v>66.38</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -669,7 +669,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>🔥🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -681,50 +681,50 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AMAT</t>
+          <t>TSM</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Equipos chips</t>
+          <t>Chips</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>500.77</v>
+        <v>444.92</v>
       </c>
       <c r="D5" t="n">
         <v>95</v>
       </c>
       <c r="E5" t="n">
-        <v>11.72</v>
+        <v>4.72</v>
       </c>
       <c r="F5" t="n">
-        <v>1.01</v>
+        <v>0.85</v>
       </c>
       <c r="G5" t="n">
-        <v>20.5</v>
+        <v>15.42</v>
       </c>
       <c r="H5" t="n">
-        <v>4.09</v>
+        <v>3.47</v>
       </c>
       <c r="I5" t="n">
-        <v>492.57</v>
+        <v>438.75</v>
       </c>
       <c r="J5" t="n">
-        <v>505.9</v>
+        <v>448.78</v>
       </c>
       <c r="K5" t="n">
-        <v>470.02</v>
+        <v>421.79</v>
       </c>
       <c r="L5" t="n">
-        <v>552.02</v>
+        <v>483.47</v>
       </c>
       <c r="M5" t="n">
-        <v>72.28</v>
+        <v>61.77</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>MEDIO</t>
+          <t>BAJO</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -741,7 +741,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>LRCX</t>
+          <t>AMAT</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -750,34 +750,34 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>343.71</v>
+        <v>501.7</v>
       </c>
       <c r="D6" t="n">
         <v>95</v>
       </c>
       <c r="E6" t="n">
-        <v>7.77</v>
+        <v>11.57</v>
       </c>
       <c r="F6" t="n">
-        <v>0.93</v>
+        <v>0.8</v>
       </c>
       <c r="G6" t="n">
-        <v>15.2</v>
+        <v>21.85</v>
       </c>
       <c r="H6" t="n">
-        <v>4.42</v>
+        <v>4.36</v>
       </c>
       <c r="I6" t="n">
-        <v>337.63</v>
+        <v>492.96</v>
       </c>
       <c r="J6" t="n">
-        <v>347.51</v>
+        <v>507.16</v>
       </c>
       <c r="K6" t="n">
-        <v>320.91</v>
+        <v>468.93</v>
       </c>
       <c r="L6" t="n">
-        <v>381.71</v>
+        <v>556.3200000000001</v>
       </c>
       <c r="M6" t="n">
         <v>71.69</v>
@@ -801,7 +801,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>KLAC</t>
+          <t>LRCX</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -810,41 +810,41 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>2125.11</v>
+        <v>336.41</v>
       </c>
       <c r="D7" t="n">
         <v>95</v>
       </c>
       <c r="E7" t="n">
-        <v>8.58</v>
+        <v>5.79</v>
       </c>
       <c r="F7" t="n">
-        <v>0.99</v>
+        <v>0.93</v>
       </c>
       <c r="G7" t="n">
-        <v>88.22</v>
+        <v>15.92</v>
       </c>
       <c r="H7" t="n">
-        <v>4.15</v>
+        <v>4.73</v>
       </c>
       <c r="I7" t="n">
-        <v>2089.82</v>
+        <v>330.04</v>
       </c>
       <c r="J7" t="n">
-        <v>2147.17</v>
+        <v>340.39</v>
       </c>
       <c r="K7" t="n">
-        <v>1992.78</v>
+        <v>312.54</v>
       </c>
       <c r="L7" t="n">
-        <v>2345.66</v>
+        <v>376.2</v>
       </c>
       <c r="M7" t="n">
-        <v>68.34999999999999</v>
+        <v>66.22</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>MEDIO</t>
+          <t>BAJO</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -861,46 +861,46 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>QQQ</t>
+          <t>KLAC</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>ETF Nasdaq</t>
+          <t>Equipos chips</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>744.21</v>
+        <v>2131.1</v>
       </c>
       <c r="D8" t="n">
         <v>95</v>
       </c>
       <c r="E8" t="n">
-        <v>2.02</v>
+        <v>10.56</v>
       </c>
       <c r="F8" t="n">
-        <v>0.97</v>
+        <v>0.79</v>
       </c>
       <c r="G8" t="n">
-        <v>9.9</v>
+        <v>91.25</v>
       </c>
       <c r="H8" t="n">
-        <v>1.33</v>
+        <v>4.28</v>
       </c>
       <c r="I8" t="n">
-        <v>740.25</v>
+        <v>2094.6</v>
       </c>
       <c r="J8" t="n">
-        <v>746.6900000000001</v>
+        <v>2153.91</v>
       </c>
       <c r="K8" t="n">
-        <v>729.35</v>
+        <v>1994.23</v>
       </c>
       <c r="L8" t="n">
-        <v>768.97</v>
+        <v>2359.22</v>
       </c>
       <c r="M8" t="n">
-        <v>70.61</v>
+        <v>66.70999999999999</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
@@ -921,50 +921,50 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>QCOM</t>
+          <t>SLB</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Chips</t>
+          <t>Energía</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>250.01</v>
+        <v>58.01</v>
       </c>
       <c r="D9" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E9" t="n">
-        <v>7.12</v>
+        <v>5.79</v>
       </c>
       <c r="F9" t="n">
-        <v>0.68</v>
+        <v>0.63</v>
       </c>
       <c r="G9" t="n">
-        <v>18.14</v>
+        <v>1.58</v>
       </c>
       <c r="H9" t="n">
-        <v>7.26</v>
+        <v>2.73</v>
       </c>
       <c r="I9" t="n">
-        <v>242.75</v>
+        <v>57.38</v>
       </c>
       <c r="J9" t="n">
-        <v>254.55</v>
+        <v>58.41</v>
       </c>
       <c r="K9" t="n">
-        <v>222.79</v>
+        <v>55.64</v>
       </c>
       <c r="L9" t="n">
-        <v>295.37</v>
+        <v>61.96</v>
       </c>
       <c r="M9" t="n">
-        <v>61.96</v>
+        <v>61.67</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>MEDIO</t>
+          <t>BAJO</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -981,46 +981,46 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>CVX</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Tecnología</t>
+          <t>Energía</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>427.34</v>
+        <v>188.35</v>
       </c>
       <c r="D10" t="n">
         <v>92</v>
       </c>
       <c r="E10" t="n">
-        <v>3.55</v>
+        <v>2.91</v>
       </c>
       <c r="F10" t="n">
-        <v>0.97</v>
+        <v>0.39</v>
       </c>
       <c r="G10" t="n">
-        <v>13.67</v>
+        <v>4.6</v>
       </c>
       <c r="H10" t="n">
-        <v>3.2</v>
+        <v>2.44</v>
       </c>
       <c r="I10" t="n">
-        <v>421.87</v>
+        <v>186.51</v>
       </c>
       <c r="J10" t="n">
-        <v>430.76</v>
+        <v>189.5</v>
       </c>
       <c r="K10" t="n">
-        <v>406.84</v>
+        <v>181.45</v>
       </c>
       <c r="L10" t="n">
-        <v>461.51</v>
+        <v>199.84</v>
       </c>
       <c r="M10" t="n">
-        <v>59.87</v>
+        <v>54.5</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
@@ -1041,7 +1041,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>CVX</t>
+          <t>OXY</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1050,37 +1050,37 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>189.71</v>
+        <v>58.67</v>
       </c>
       <c r="D11" t="n">
         <v>92</v>
       </c>
       <c r="E11" t="n">
-        <v>4.01</v>
+        <v>2.36</v>
       </c>
       <c r="F11" t="n">
-        <v>0.71</v>
+        <v>0.64</v>
       </c>
       <c r="G11" t="n">
-        <v>4.59</v>
+        <v>1.9</v>
       </c>
       <c r="H11" t="n">
-        <v>2.42</v>
+        <v>3.24</v>
       </c>
       <c r="I11" t="n">
-        <v>187.87</v>
+        <v>57.91</v>
       </c>
       <c r="J11" t="n">
-        <v>190.86</v>
+        <v>59.15</v>
       </c>
       <c r="K11" t="n">
-        <v>182.83</v>
+        <v>55.81</v>
       </c>
       <c r="L11" t="n">
-        <v>201.18</v>
+        <v>63.43</v>
       </c>
       <c r="M11" t="n">
-        <v>57.28</v>
+        <v>57.17</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
@@ -1101,50 +1101,50 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>OXY</t>
+          <t>MU</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Energía</t>
+          <t>Memoria / Chips</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>59.64</v>
+        <v>996</v>
       </c>
       <c r="D12" t="n">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="E12" t="n">
-        <v>4.83</v>
+        <v>7.85</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7</v>
+        <v>0.95</v>
       </c>
       <c r="G12" t="n">
-        <v>1.9</v>
+        <v>68.38</v>
       </c>
       <c r="H12" t="n">
-        <v>3.18</v>
+        <v>6.87</v>
       </c>
       <c r="I12" t="n">
-        <v>58.88</v>
+        <v>968.65</v>
       </c>
       <c r="J12" t="n">
-        <v>60.11</v>
+        <v>1013.1</v>
       </c>
       <c r="K12" t="n">
-        <v>56.79</v>
+        <v>893.4299999999999</v>
       </c>
       <c r="L12" t="n">
-        <v>64.38</v>
+        <v>1166.96</v>
       </c>
       <c r="M12" t="n">
-        <v>63.88</v>
+        <v>68.09</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>BAJO</t>
+          <t>MEDIO</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -1161,46 +1161,46 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>HOOD</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>IA / Chips</t>
+          <t>Trading</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>542.52</v>
+        <v>88.33</v>
       </c>
       <c r="D13" t="n">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="E13" t="n">
-        <v>9.48</v>
+        <v>4.11</v>
       </c>
       <c r="F13" t="n">
-        <v>0.77</v>
+        <v>1.19</v>
       </c>
       <c r="G13" t="n">
-        <v>27.6</v>
+        <v>5.25</v>
       </c>
       <c r="H13" t="n">
-        <v>5.09</v>
+        <v>5.94</v>
       </c>
       <c r="I13" t="n">
-        <v>531.48</v>
+        <v>86.23</v>
       </c>
       <c r="J13" t="n">
-        <v>549.42</v>
+        <v>89.64</v>
       </c>
       <c r="K13" t="n">
-        <v>501.13</v>
+        <v>80.45</v>
       </c>
       <c r="L13" t="n">
-        <v>611.51</v>
+        <v>101.46</v>
       </c>
       <c r="M13" t="n">
-        <v>74.14</v>
+        <v>57.92</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
@@ -1221,50 +1221,50 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>PLTR</t>
+          <t>XOM</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>IA / Software</t>
+          <t>Energía</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>142.2</v>
+        <v>152.04</v>
       </c>
       <c r="D14" t="n">
         <v>82</v>
       </c>
       <c r="E14" t="n">
-        <v>7.31</v>
+        <v>3.46</v>
       </c>
       <c r="F14" t="n">
-        <v>0.96</v>
+        <v>0.53</v>
       </c>
       <c r="G14" t="n">
-        <v>6.89</v>
+        <v>4.41</v>
       </c>
       <c r="H14" t="n">
-        <v>4.84</v>
+        <v>2.9</v>
       </c>
       <c r="I14" t="n">
-        <v>139.45</v>
+        <v>150.27</v>
       </c>
       <c r="J14" t="n">
-        <v>143.92</v>
+        <v>153.14</v>
       </c>
       <c r="K14" t="n">
-        <v>131.87</v>
+        <v>145.42</v>
       </c>
       <c r="L14" t="n">
-        <v>159.41</v>
+        <v>163.08</v>
       </c>
       <c r="M14" t="n">
-        <v>60.32</v>
+        <v>50.4</v>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>MEDIO</t>
+          <t>BAJO</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
@@ -1281,46 +1281,46 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>XOM</t>
+          <t>META</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Energía</t>
+          <t>Tecnología</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>152.53</v>
+        <v>627.5700000000001</v>
       </c>
       <c r="D15" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E15" t="n">
-        <v>3.13</v>
+        <v>-1.22</v>
       </c>
       <c r="F15" t="n">
-        <v>0.82</v>
+        <v>1.27</v>
       </c>
       <c r="G15" t="n">
-        <v>4.37</v>
+        <v>16.36</v>
       </c>
       <c r="H15" t="n">
-        <v>2.86</v>
+        <v>2.61</v>
       </c>
       <c r="I15" t="n">
-        <v>150.78</v>
+        <v>621.03</v>
       </c>
       <c r="J15" t="n">
-        <v>153.62</v>
+        <v>631.66</v>
       </c>
       <c r="K15" t="n">
-        <v>145.98</v>
+        <v>603.04</v>
       </c>
       <c r="L15" t="n">
-        <v>163.45</v>
+        <v>668.46</v>
       </c>
       <c r="M15" t="n">
-        <v>52.71</v>
+        <v>53.94</v>
       </c>
       <c r="N15" t="inlineStr">
         <is>
@@ -1341,46 +1341,46 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>META</t>
+          <t>SPY</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Tecnología</t>
+          <t>ETF Mercado</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>622.98</v>
+        <v>757.09</v>
       </c>
       <c r="D16" t="n">
-        <v>81</v>
+        <v>95</v>
       </c>
       <c r="E16" t="n">
-        <v>-1.93</v>
+        <v>0.33</v>
       </c>
       <c r="F16" t="n">
-        <v>1.3</v>
+        <v>0.97</v>
       </c>
       <c r="G16" t="n">
-        <v>15.57</v>
+        <v>6.34</v>
       </c>
       <c r="H16" t="n">
-        <v>2.5</v>
+        <v>0.84</v>
       </c>
       <c r="I16" t="n">
-        <v>616.75</v>
+        <v>754.5599999999999</v>
       </c>
       <c r="J16" t="n">
-        <v>626.87</v>
+        <v>758.67</v>
       </c>
       <c r="K16" t="n">
-        <v>599.63</v>
+        <v>747.59</v>
       </c>
       <c r="L16" t="n">
-        <v>661.9</v>
+        <v>772.9299999999999</v>
       </c>
       <c r="M16" t="n">
-        <v>52.8</v>
+        <v>59.15</v>
       </c>
       <c r="N16" t="inlineStr">
         <is>
@@ -1389,7 +1389,7 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -1401,46 +1401,46 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>SPY</t>
+          <t>QQQ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>ETF Mercado</t>
+          <t>ETF Nasdaq</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>754.24</v>
+        <v>740.61</v>
       </c>
       <c r="D17" t="n">
         <v>95</v>
       </c>
       <c r="E17" t="n">
-        <v>0.5</v>
+        <v>0.68</v>
       </c>
       <c r="F17" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.95</v>
       </c>
       <c r="G17" t="n">
-        <v>6.36</v>
+        <v>10.18</v>
       </c>
       <c r="H17" t="n">
-        <v>0.84</v>
+        <v>1.37</v>
       </c>
       <c r="I17" t="n">
-        <v>751.7</v>
+        <v>736.54</v>
       </c>
       <c r="J17" t="n">
-        <v>755.83</v>
+        <v>743.15</v>
       </c>
       <c r="K17" t="n">
-        <v>744.7</v>
+        <v>725.35</v>
       </c>
       <c r="L17" t="n">
-        <v>770.15</v>
+        <v>766.05</v>
       </c>
       <c r="M17" t="n">
-        <v>61.53</v>
+        <v>64.84999999999999</v>
       </c>
       <c r="N17" t="inlineStr">
         <is>
@@ -1461,50 +1461,50 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>SLB</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Energía</t>
+          <t>IA / Chips</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>56.85</v>
+        <v>523.2</v>
       </c>
       <c r="D18" t="n">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="E18" t="n">
-        <v>0.62</v>
+        <v>0.99</v>
       </c>
       <c r="F18" t="n">
-        <v>0.87</v>
+        <v>0.83</v>
       </c>
       <c r="G18" t="n">
-        <v>1.49</v>
+        <v>29.38</v>
       </c>
       <c r="H18" t="n">
-        <v>2.63</v>
+        <v>5.62</v>
       </c>
       <c r="I18" t="n">
-        <v>56.25</v>
+        <v>511.45</v>
       </c>
       <c r="J18" t="n">
-        <v>57.22</v>
+        <v>530.55</v>
       </c>
       <c r="K18" t="n">
-        <v>54.61</v>
+        <v>479.13</v>
       </c>
       <c r="L18" t="n">
-        <v>60.59</v>
+        <v>596.66</v>
       </c>
       <c r="M18" t="n">
-        <v>57.43</v>
+        <v>67.01000000000001</v>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>BAJO</t>
+          <t>MEDIO</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
@@ -1521,7 +1521,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1530,37 +1530,37 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>310.26</v>
+        <v>428.05</v>
       </c>
       <c r="D19" t="n">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.19</v>
+        <v>0.25</v>
       </c>
       <c r="F19" t="n">
-        <v>1.06</v>
+        <v>0.71</v>
       </c>
       <c r="G19" t="n">
-        <v>5.72</v>
+        <v>13.58</v>
       </c>
       <c r="H19" t="n">
-        <v>1.84</v>
+        <v>3.17</v>
       </c>
       <c r="I19" t="n">
-        <v>307.97</v>
+        <v>422.62</v>
       </c>
       <c r="J19" t="n">
-        <v>311.69</v>
+        <v>431.45</v>
       </c>
       <c r="K19" t="n">
-        <v>301.69</v>
+        <v>407.67</v>
       </c>
       <c r="L19" t="n">
-        <v>324.55</v>
+        <v>462.01</v>
       </c>
       <c r="M19" t="n">
-        <v>63.98</v>
+        <v>58.63</v>
       </c>
       <c r="N19" t="inlineStr">
         <is>
@@ -1581,50 +1581,50 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>HOOD</t>
+          <t>AAPL</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Trading</t>
+          <t>Tecnología</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>82.84999999999999</v>
+        <v>311.23</v>
       </c>
       <c r="D20" t="n">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="E20" t="n">
-        <v>8.68</v>
+        <v>-0.41</v>
       </c>
       <c r="F20" t="n">
-        <v>0.93</v>
+        <v>0.8</v>
       </c>
       <c r="G20" t="n">
-        <v>5.32</v>
+        <v>5.63</v>
       </c>
       <c r="H20" t="n">
-        <v>6.42</v>
+        <v>1.81</v>
       </c>
       <c r="I20" t="n">
-        <v>80.72</v>
+        <v>308.98</v>
       </c>
       <c r="J20" t="n">
-        <v>84.18000000000001</v>
+        <v>312.64</v>
       </c>
       <c r="K20" t="n">
-        <v>74.87</v>
+        <v>302.78</v>
       </c>
       <c r="L20" t="n">
-        <v>96.15000000000001</v>
+        <v>325.31</v>
       </c>
       <c r="M20" t="n">
-        <v>56.54</v>
+        <v>65.84999999999999</v>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>MEDIO</t>
+          <t>BAJO</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
@@ -1641,53 +1641,57 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>UPST</t>
+          <t>AVGO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Fintech IA</t>
+          <t>IA / Chips</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>30.29</v>
+        <v>418.91</v>
       </c>
       <c r="D21" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.4</v>
+        <v>-1.8</v>
       </c>
       <c r="F21" t="n">
-        <v>1.04</v>
+        <v>3.05</v>
       </c>
       <c r="G21" t="n">
-        <v>2.06</v>
+        <v>21.93</v>
       </c>
       <c r="H21" t="n">
-        <v>6.8</v>
+        <v>5.24</v>
       </c>
       <c r="I21" t="n">
-        <v>29.47</v>
+        <v>410.14</v>
       </c>
       <c r="J21" t="n">
-        <v>30.8</v>
+        <v>424.39</v>
       </c>
       <c r="K21" t="n">
-        <v>27.2</v>
+        <v>386.02</v>
       </c>
       <c r="L21" t="n">
-        <v>35.44</v>
+        <v>473.73</v>
       </c>
       <c r="M21" t="n">
-        <v>61.44</v>
+        <v>43.84</v>
       </c>
       <c r="N21" t="inlineStr">
         <is>
           <t>MEDIO</t>
         </is>
       </c>
-      <c r="O21" t="inlineStr"/>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>🔥</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>POSIBLE COMPRA</t>
@@ -1697,166 +1701,158 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>SOFI</t>
+          <t>QCOM</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Fintech</t>
+          <t>Chips</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>16.68</v>
+        <v>242.57</v>
       </c>
       <c r="D22" t="n">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="E22" t="n">
-        <v>3.15</v>
+        <v>-0.3</v>
       </c>
       <c r="F22" t="n">
-        <v>1.04</v>
+        <v>0.51</v>
       </c>
       <c r="G22" t="n">
-        <v>0.95</v>
+        <v>18.23</v>
       </c>
       <c r="H22" t="n">
-        <v>5.67</v>
+        <v>7.51</v>
       </c>
       <c r="I22" t="n">
-        <v>16.3</v>
+        <v>235.28</v>
       </c>
       <c r="J22" t="n">
-        <v>16.92</v>
+        <v>247.13</v>
       </c>
       <c r="K22" t="n">
-        <v>15.26</v>
+        <v>215.23</v>
       </c>
       <c r="L22" t="n">
-        <v>19.05</v>
+        <v>288.14</v>
       </c>
       <c r="M22" t="n">
-        <v>59.66</v>
+        <v>64.31999999999999</v>
       </c>
       <c r="N22" t="inlineStr">
         <is>
           <t>MEDIO</t>
         </is>
       </c>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t>🔥</t>
-        </is>
-      </c>
+      <c r="O22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>VIGILAR</t>
+          <t>POSIBLE COMPRA</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>GOOGL</t>
+          <t>UPST</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Tecnología</t>
+          <t>Fintech IA</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>358.99</v>
+        <v>32.27</v>
       </c>
       <c r="D23" t="n">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="E23" t="n">
-        <v>-7.67</v>
+        <v>-1.28</v>
       </c>
       <c r="F23" t="n">
-        <v>1.76</v>
+        <v>0.86</v>
       </c>
       <c r="G23" t="n">
-        <v>9.550000000000001</v>
+        <v>2.02</v>
       </c>
       <c r="H23" t="n">
-        <v>2.66</v>
+        <v>6.26</v>
       </c>
       <c r="I23" t="n">
-        <v>355.17</v>
+        <v>31.46</v>
       </c>
       <c r="J23" t="n">
-        <v>361.38</v>
+        <v>32.77</v>
       </c>
       <c r="K23" t="n">
-        <v>344.67</v>
+        <v>29.24</v>
       </c>
       <c r="L23" t="n">
-        <v>382.86</v>
+        <v>37.32</v>
       </c>
       <c r="M23" t="n">
-        <v>14.16</v>
+        <v>59.36</v>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>BAJO</t>
-        </is>
-      </c>
-      <c r="O23" t="inlineStr">
-        <is>
-          <t>🔥</t>
-        </is>
-      </c>
+          <t>MEDIO</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>VIGILAR</t>
+          <t>POSIBLE COMPRA</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>AMZN</t>
+          <t>NVDA</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Tecnología</t>
+          <t>IA / Chips</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>250.02</v>
+        <v>218.66</v>
       </c>
       <c r="D24" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E24" t="n">
-        <v>-8.029999999999999</v>
+        <v>2.06</v>
       </c>
       <c r="F24" t="n">
-        <v>1.28</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="G24" t="n">
-        <v>6.94</v>
+        <v>8.42</v>
       </c>
       <c r="H24" t="n">
-        <v>2.77</v>
+        <v>3.85</v>
       </c>
       <c r="I24" t="n">
-        <v>247.25</v>
+        <v>215.29</v>
       </c>
       <c r="J24" t="n">
-        <v>251.75</v>
+        <v>220.77</v>
       </c>
       <c r="K24" t="n">
-        <v>239.62</v>
+        <v>206.03</v>
       </c>
       <c r="L24" t="n">
-        <v>267.36</v>
+        <v>239.71</v>
       </c>
       <c r="M24" t="n">
-        <v>32.42</v>
+        <v>35.85</v>
       </c>
       <c r="N24" t="inlineStr">
         <is>
@@ -1877,46 +1873,46 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>PYPL</t>
+          <t>GOOGL</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Pagos</t>
+          <t>Tecnología</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>42.61</v>
+        <v>372.19</v>
       </c>
       <c r="D25" t="n">
-        <v>43</v>
+        <v>63</v>
       </c>
       <c r="E25" t="n">
-        <v>-2.63</v>
+        <v>-4.6</v>
       </c>
       <c r="F25" t="n">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="G25" t="n">
-        <v>1.13</v>
+        <v>10.11</v>
       </c>
       <c r="H25" t="n">
-        <v>2.65</v>
+        <v>2.72</v>
       </c>
       <c r="I25" t="n">
-        <v>42.16</v>
+        <v>368.14</v>
       </c>
       <c r="J25" t="n">
-        <v>42.89</v>
+        <v>374.72</v>
       </c>
       <c r="K25" t="n">
-        <v>40.92</v>
+        <v>357.02</v>
       </c>
       <c r="L25" t="n">
-        <v>45.43</v>
+        <v>397.48</v>
       </c>
       <c r="M25" t="n">
-        <v>30.06</v>
+        <v>30.09</v>
       </c>
       <c r="N25" t="inlineStr">
         <is>
@@ -1930,53 +1926,53 @@
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>NO COMPRAR</t>
+          <t>VIGILAR</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>NVDA</t>
+          <t>PLTR</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>IA / Chips</t>
+          <t>IA / Software</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>214.75</v>
+        <v>141.7</v>
       </c>
       <c r="D26" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="E26" t="n">
-        <v>1.01</v>
+        <v>-1.14</v>
       </c>
       <c r="F26" t="n">
-        <v>0.85</v>
+        <v>0.97</v>
       </c>
       <c r="G26" t="n">
-        <v>8.43</v>
+        <v>6.96</v>
       </c>
       <c r="H26" t="n">
-        <v>3.92</v>
+        <v>4.91</v>
       </c>
       <c r="I26" t="n">
-        <v>211.38</v>
+        <v>138.92</v>
       </c>
       <c r="J26" t="n">
-        <v>216.86</v>
+        <v>143.44</v>
       </c>
       <c r="K26" t="n">
-        <v>202.11</v>
+        <v>131.26</v>
       </c>
       <c r="L26" t="n">
-        <v>235.82</v>
+        <v>159.1</v>
       </c>
       <c r="M26" t="n">
-        <v>41.65</v>
+        <v>57.16</v>
       </c>
       <c r="N26" t="inlineStr">
         <is>
@@ -1993,46 +1989,46 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>INTC</t>
+          <t>SOFI</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Chips</t>
+          <t>Fintech</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>112.71</v>
+        <v>17.15</v>
       </c>
       <c r="D27" t="n">
-        <v>56</v>
+        <v>74</v>
       </c>
       <c r="E27" t="n">
-        <v>-7.44</v>
+        <v>1.06</v>
       </c>
       <c r="F27" t="n">
-        <v>0.86</v>
+        <v>0.88</v>
       </c>
       <c r="G27" t="n">
-        <v>8.77</v>
+        <v>0.93</v>
       </c>
       <c r="H27" t="n">
-        <v>7.78</v>
+        <v>5.44</v>
       </c>
       <c r="I27" t="n">
-        <v>109.2</v>
+        <v>16.78</v>
       </c>
       <c r="J27" t="n">
-        <v>114.9</v>
+        <v>17.38</v>
       </c>
       <c r="K27" t="n">
-        <v>99.56</v>
+        <v>15.75</v>
       </c>
       <c r="L27" t="n">
-        <v>134.63</v>
+        <v>19.48</v>
       </c>
       <c r="M27" t="n">
-        <v>42.23</v>
+        <v>58.25</v>
       </c>
       <c r="N27" t="inlineStr">
         <is>
@@ -2042,53 +2038,53 @@
       <c r="O27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>NO COMPRAR</t>
+          <t>VIGILAR</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>TSLA</t>
+          <t>AMZN</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Autos / Tech</t>
+          <t>Tecnología</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>423.7</v>
+        <v>253.79</v>
       </c>
       <c r="D28" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="E28" t="n">
-        <v>-3.78</v>
+        <v>-7.38</v>
       </c>
       <c r="F28" t="n">
-        <v>0.86</v>
+        <v>0.9</v>
       </c>
       <c r="G28" t="n">
-        <v>14.14</v>
+        <v>7.05</v>
       </c>
       <c r="H28" t="n">
-        <v>3.34</v>
+        <v>2.78</v>
       </c>
       <c r="I28" t="n">
-        <v>418.04</v>
+        <v>250.97</v>
       </c>
       <c r="J28" t="n">
-        <v>427.24</v>
+        <v>255.55</v>
       </c>
       <c r="K28" t="n">
-        <v>402.49</v>
+        <v>243.21</v>
       </c>
       <c r="L28" t="n">
-        <v>459.06</v>
+        <v>271.43</v>
       </c>
       <c r="M28" t="n">
-        <v>40.48</v>
+        <v>38.44</v>
       </c>
       <c r="N28" t="inlineStr">
         <is>
@@ -2105,46 +2101,46 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>SOUN</t>
+          <t>INTC</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>IA</t>
+          <t>Chips</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>8.08</v>
+        <v>111.78</v>
       </c>
       <c r="D29" t="n">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="E29" t="n">
-        <v>0</v>
+        <v>-7.54</v>
       </c>
       <c r="F29" t="n">
-        <v>0.99</v>
+        <v>0.57</v>
       </c>
       <c r="G29" t="n">
-        <v>0.5</v>
+        <v>8.66</v>
       </c>
       <c r="H29" t="n">
-        <v>6.21</v>
+        <v>7.75</v>
       </c>
       <c r="I29" t="n">
-        <v>7.88</v>
+        <v>108.31</v>
       </c>
       <c r="J29" t="n">
-        <v>8.210000000000001</v>
+        <v>113.95</v>
       </c>
       <c r="K29" t="n">
-        <v>7.33</v>
+        <v>98.79000000000001</v>
       </c>
       <c r="L29" t="n">
-        <v>9.33</v>
+        <v>133.44</v>
       </c>
       <c r="M29" t="n">
-        <v>44.48</v>
+        <v>45.42</v>
       </c>
       <c r="N29" t="inlineStr">
         <is>
@@ -2161,50 +2157,50 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>COIN</t>
+          <t>TSLA</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Cripto / Trading</t>
+          <t>Autos / Tech</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>163.22</v>
+        <v>418.45</v>
       </c>
       <c r="D30" t="n">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="E30" t="n">
-        <v>-6.08</v>
+        <v>-5.35</v>
       </c>
       <c r="F30" t="n">
-        <v>0.96</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="G30" t="n">
-        <v>12.19</v>
+        <v>14.03</v>
       </c>
       <c r="H30" t="n">
-        <v>7.47</v>
+        <v>3.35</v>
       </c>
       <c r="I30" t="n">
-        <v>158.34</v>
+        <v>412.84</v>
       </c>
       <c r="J30" t="n">
-        <v>166.27</v>
+        <v>421.96</v>
       </c>
       <c r="K30" t="n">
-        <v>144.94</v>
+        <v>397.41</v>
       </c>
       <c r="L30" t="n">
-        <v>193.69</v>
+        <v>453.52</v>
       </c>
       <c r="M30" t="n">
-        <v>31.1</v>
+        <v>39.34</v>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>MEDIO</t>
+          <t>BAJO</t>
         </is>
       </c>
       <c r="O30" t="inlineStr"/>
@@ -2217,180 +2213,168 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>AVGO</t>
+          <t>SOUN</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>IA / Chips</t>
+          <t>IA</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>479.23</v>
+        <v>8.01</v>
       </c>
       <c r="D31" t="n">
-        <v>95</v>
+        <v>46</v>
       </c>
       <c r="E31" t="n">
-        <v>13.6</v>
+        <v>-6.43</v>
       </c>
       <c r="F31" t="n">
-        <v>1.61</v>
+        <v>0.62</v>
       </c>
       <c r="G31" t="n">
-        <v>18.4</v>
+        <v>0.49</v>
       </c>
       <c r="H31" t="n">
-        <v>3.84</v>
+        <v>6.16</v>
       </c>
       <c r="I31" t="n">
-        <v>471.87</v>
+        <v>7.81</v>
       </c>
       <c r="J31" t="n">
-        <v>483.83</v>
+        <v>8.130000000000001</v>
       </c>
       <c r="K31" t="n">
-        <v>451.63</v>
+        <v>7.27</v>
       </c>
       <c r="L31" t="n">
-        <v>525.22</v>
+        <v>9.24</v>
       </c>
       <c r="M31" t="n">
-        <v>73.63</v>
+        <v>41.64</v>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>ALTO</t>
-        </is>
-      </c>
-      <c r="O31" t="inlineStr">
-        <is>
-          <t>🔥🔥</t>
-        </is>
-      </c>
+          <t>MEDIO</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>VIGILAR</t>
+          <t>NO COMPRAR</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>MU</t>
+          <t>COIN</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Memoria / Chips</t>
+          <t>Cripto / Trading</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>1079.57</v>
+        <v>164.13</v>
       </c>
       <c r="D32" t="n">
-        <v>89</v>
+        <v>38</v>
       </c>
       <c r="E32" t="n">
-        <v>16.28</v>
+        <v>-9.94</v>
       </c>
       <c r="F32" t="n">
-        <v>0.71</v>
+        <v>0.86</v>
       </c>
       <c r="G32" t="n">
-        <v>63.27</v>
+        <v>10.57</v>
       </c>
       <c r="H32" t="n">
-        <v>5.86</v>
+        <v>6.44</v>
       </c>
       <c r="I32" t="n">
-        <v>1054.26</v>
+        <v>159.9</v>
       </c>
       <c r="J32" t="n">
-        <v>1095.39</v>
+        <v>166.77</v>
       </c>
       <c r="K32" t="n">
-        <v>984.66</v>
+        <v>148.28</v>
       </c>
       <c r="L32" t="n">
-        <v>1237.76</v>
+        <v>190.56</v>
       </c>
       <c r="M32" t="n">
-        <v>74.98999999999999</v>
+        <v>24.19</v>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>ALTO</t>
-        </is>
-      </c>
-      <c r="O32" t="inlineStr">
-        <is>
-          <t>🔥</t>
-        </is>
-      </c>
+          <t>MEDIO</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>VIGILAR</t>
+          <t>NO COMPRAR</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>SOXX</t>
+          <t>PYPL</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>ETF Chips</t>
+          <t>Pagos</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>615.6799999999999</v>
+        <v>42.75</v>
       </c>
       <c r="D33" t="n">
-        <v>80</v>
+        <v>36</v>
       </c>
       <c r="E33" t="n">
-        <v>9.17</v>
+        <v>-3.85</v>
       </c>
       <c r="F33" t="n">
-        <v>0.95</v>
+        <v>0.68</v>
       </c>
       <c r="G33" t="n">
-        <v>23.6</v>
+        <v>1.13</v>
       </c>
       <c r="H33" t="n">
-        <v>3.83</v>
+        <v>2.63</v>
       </c>
       <c r="I33" t="n">
-        <v>606.24</v>
+        <v>42.3</v>
       </c>
       <c r="J33" t="n">
-        <v>621.58</v>
+        <v>43.03</v>
       </c>
       <c r="K33" t="n">
-        <v>580.28</v>
+        <v>41.06</v>
       </c>
       <c r="L33" t="n">
-        <v>674.67</v>
+        <v>45.56</v>
       </c>
       <c r="M33" t="n">
-        <v>75.90000000000001</v>
+        <v>32.44</v>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>ALTO</t>
-        </is>
-      </c>
-      <c r="O33" t="inlineStr">
-        <is>
-          <t>🔥</t>
-        </is>
-      </c>
+          <t>BAJO</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>VIGILAR</t>
+          <t>NO COMPRAR</t>
         </is>
       </c>
     </row>
@@ -2406,48 +2390,44 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>68.23</v>
+        <v>65.66</v>
       </c>
       <c r="D34" t="n">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="E34" t="n">
-        <v>4.33</v>
+        <v>-6.39</v>
       </c>
       <c r="F34" t="n">
-        <v>0.84</v>
+        <v>1.09</v>
       </c>
       <c r="G34" t="n">
-        <v>5.66</v>
+        <v>5.73</v>
       </c>
       <c r="H34" t="n">
-        <v>8.289999999999999</v>
+        <v>8.73</v>
       </c>
       <c r="I34" t="n">
-        <v>65.97</v>
+        <v>63.37</v>
       </c>
       <c r="J34" t="n">
-        <v>69.64</v>
+        <v>67.09</v>
       </c>
       <c r="K34" t="n">
-        <v>59.74</v>
+        <v>57.07</v>
       </c>
       <c r="L34" t="n">
-        <v>82.37</v>
+        <v>79.98</v>
       </c>
       <c r="M34" t="n">
-        <v>65.08</v>
+        <v>59.45</v>
       </c>
       <c r="N34" t="inlineStr">
         <is>
           <t>ALTO</t>
         </is>
       </c>
-      <c r="O34" t="inlineStr">
-        <is>
-          <t>🔥</t>
-        </is>
-      </c>
+      <c r="O34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>VIGILAR</t>
@@ -2466,37 +2446,37 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>411.83</v>
+        <v>393.44</v>
       </c>
       <c r="D35" t="n">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="E35" t="n">
-        <v>36.05</v>
+        <v>17.35</v>
       </c>
       <c r="F35" t="n">
-        <v>0.84</v>
+        <v>0.83</v>
       </c>
       <c r="G35" t="n">
-        <v>31.53</v>
+        <v>33.59</v>
       </c>
       <c r="H35" t="n">
-        <v>7.66</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="I35" t="n">
-        <v>399.22</v>
+        <v>380</v>
       </c>
       <c r="J35" t="n">
-        <v>419.71</v>
+        <v>401.84</v>
       </c>
       <c r="K35" t="n">
-        <v>364.53</v>
+        <v>343.05</v>
       </c>
       <c r="L35" t="n">
-        <v>490.66</v>
+        <v>477.42</v>
       </c>
       <c r="M35" t="n">
-        <v>84.20999999999999</v>
+        <v>78.47</v>
       </c>
       <c r="N35" t="inlineStr">
         <is>
@@ -2522,37 +2502,37 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>47.42</v>
+        <v>46.9</v>
       </c>
       <c r="D36" t="n">
         <v>54</v>
       </c>
       <c r="E36" t="n">
-        <v>24.17</v>
+        <v>13.56</v>
       </c>
       <c r="F36" t="n">
-        <v>1.02</v>
+        <v>0.74</v>
       </c>
       <c r="G36" t="n">
-        <v>3.2</v>
+        <v>3.22</v>
       </c>
       <c r="H36" t="n">
-        <v>6.74</v>
+        <v>6.86</v>
       </c>
       <c r="I36" t="n">
-        <v>46.14</v>
+        <v>45.61</v>
       </c>
       <c r="J36" t="n">
-        <v>48.22</v>
+        <v>47.7</v>
       </c>
       <c r="K36" t="n">
-        <v>42.63</v>
+        <v>42.07</v>
       </c>
       <c r="L36" t="n">
-        <v>55.41</v>
+        <v>54.95</v>
       </c>
       <c r="M36" t="n">
-        <v>79.81</v>
+        <v>77.36</v>
       </c>
       <c r="N36" t="inlineStr">
         <is>
@@ -2578,37 +2558,37 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>114.7</v>
+        <v>119.95</v>
       </c>
       <c r="D37" t="n">
         <v>52</v>
       </c>
       <c r="E37" t="n">
-        <v>-23.65</v>
+        <v>-18.97</v>
       </c>
       <c r="F37" t="n">
-        <v>0.67</v>
+        <v>0.72</v>
       </c>
       <c r="G37" t="n">
-        <v>12.29</v>
+        <v>12.31</v>
       </c>
       <c r="H37" t="n">
-        <v>10.71</v>
+        <v>10.26</v>
       </c>
       <c r="I37" t="n">
-        <v>109.79</v>
+        <v>115.03</v>
       </c>
       <c r="J37" t="n">
-        <v>117.77</v>
+        <v>123.03</v>
       </c>
       <c r="K37" t="n">
-        <v>96.27</v>
+        <v>101.48</v>
       </c>
       <c r="L37" t="n">
-        <v>145.41</v>
+        <v>150.73</v>
       </c>
       <c r="M37" t="n">
-        <v>45.47</v>
+        <v>43.78</v>
       </c>
       <c r="N37" t="inlineStr">
         <is>

--- a/analisis_acciones.xlsx
+++ b/analisis_acciones.xlsx
@@ -510,46 +510,46 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1757.47</v>
+        <v>1649.77</v>
       </c>
       <c r="D2" t="n">
         <v>95</v>
       </c>
       <c r="E2" t="n">
-        <v>9.449999999999999</v>
+        <v>2.29</v>
       </c>
       <c r="F2" t="n">
-        <v>1.38</v>
+        <v>1.12</v>
       </c>
       <c r="G2" t="n">
-        <v>65.91</v>
+        <v>67.43000000000001</v>
       </c>
       <c r="H2" t="n">
-        <v>3.75</v>
+        <v>4.09</v>
       </c>
       <c r="I2" t="n">
-        <v>1731.11</v>
+        <v>1622.8</v>
       </c>
       <c r="J2" t="n">
-        <v>1773.95</v>
+        <v>1666.63</v>
       </c>
       <c r="K2" t="n">
-        <v>1658.6</v>
+        <v>1548.63</v>
       </c>
       <c r="L2" t="n">
-        <v>1922.25</v>
+        <v>1818.34</v>
       </c>
       <c r="M2" t="n">
-        <v>67.54000000000001</v>
+        <v>64.28</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>MEDIO</t>
+          <t>BAJO</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥🔥</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -561,55 +561,55 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SOXX</t>
+          <t>CVX</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ETF Chips</t>
+          <t>Energía</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>602.72</v>
+        <v>187.99</v>
       </c>
       <c r="D3" t="n">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="E3" t="n">
-        <v>5.84</v>
+        <v>3.03</v>
       </c>
       <c r="F3" t="n">
-        <v>1.26</v>
+        <v>0.44</v>
       </c>
       <c r="G3" t="n">
-        <v>25.54</v>
+        <v>4.47</v>
       </c>
       <c r="H3" t="n">
-        <v>4.24</v>
+        <v>2.38</v>
       </c>
       <c r="I3" t="n">
-        <v>592.5</v>
+        <v>186.2</v>
       </c>
       <c r="J3" t="n">
-        <v>609.11</v>
+        <v>189.1</v>
       </c>
       <c r="K3" t="n">
-        <v>564.41</v>
+        <v>181.28</v>
       </c>
       <c r="L3" t="n">
-        <v>666.5700000000001</v>
+        <v>199.16</v>
       </c>
       <c r="M3" t="n">
-        <v>70.2</v>
+        <v>47.95</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>MEDIO</t>
+          <t>BAJO</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥🔥</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -621,46 +621,46 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AI</t>
+          <t>SOXX</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>IA</t>
+          <t>ETF Chips</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>10.58</v>
+        <v>545.71</v>
       </c>
       <c r="D4" t="n">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="E4" t="n">
-        <v>3.52</v>
+        <v>-4.11</v>
       </c>
       <c r="F4" t="n">
-        <v>2.43</v>
+        <v>1.93</v>
       </c>
       <c r="G4" t="n">
-        <v>0.67</v>
+        <v>28.21</v>
       </c>
       <c r="H4" t="n">
-        <v>6.3</v>
+        <v>5.17</v>
       </c>
       <c r="I4" t="n">
-        <v>10.31</v>
+        <v>534.4299999999999</v>
       </c>
       <c r="J4" t="n">
-        <v>10.75</v>
+        <v>552.76</v>
       </c>
       <c r="K4" t="n">
-        <v>9.58</v>
+        <v>503.4</v>
       </c>
       <c r="L4" t="n">
-        <v>12.25</v>
+        <v>616.23</v>
       </c>
       <c r="M4" t="n">
-        <v>66.38</v>
+        <v>58.63</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -669,7 +669,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥🔥</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -681,55 +681,55 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>AMAT</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Chips</t>
+          <t>Equipos chips</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>444.92</v>
+        <v>457.78</v>
       </c>
       <c r="D5" t="n">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E5" t="n">
-        <v>4.72</v>
+        <v>1.72</v>
       </c>
       <c r="F5" t="n">
-        <v>0.85</v>
+        <v>0.73</v>
       </c>
       <c r="G5" t="n">
-        <v>15.42</v>
+        <v>23.49</v>
       </c>
       <c r="H5" t="n">
-        <v>3.47</v>
+        <v>5.13</v>
       </c>
       <c r="I5" t="n">
-        <v>438.75</v>
+        <v>448.38</v>
       </c>
       <c r="J5" t="n">
-        <v>448.78</v>
+        <v>463.65</v>
       </c>
       <c r="K5" t="n">
-        <v>421.79</v>
+        <v>422.54</v>
       </c>
       <c r="L5" t="n">
-        <v>483.47</v>
+        <v>516.52</v>
       </c>
       <c r="M5" t="n">
-        <v>61.77</v>
+        <v>55.96</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>BAJO</t>
+          <t>MEDIO</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -741,7 +741,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AMAT</t>
+          <t>KLAC</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -750,37 +750,37 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>501.7</v>
+        <v>1954.54</v>
       </c>
       <c r="D6" t="n">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E6" t="n">
-        <v>11.57</v>
+        <v>1.71</v>
       </c>
       <c r="F6" t="n">
-        <v>0.8</v>
+        <v>0.97</v>
       </c>
       <c r="G6" t="n">
-        <v>21.85</v>
+        <v>98.42</v>
       </c>
       <c r="H6" t="n">
-        <v>4.36</v>
+        <v>5.04</v>
       </c>
       <c r="I6" t="n">
-        <v>492.96</v>
+        <v>1915.17</v>
       </c>
       <c r="J6" t="n">
-        <v>507.16</v>
+        <v>1979.15</v>
       </c>
       <c r="K6" t="n">
-        <v>468.93</v>
+        <v>1806.9</v>
       </c>
       <c r="L6" t="n">
-        <v>556.3200000000001</v>
+        <v>2200.6</v>
       </c>
       <c r="M6" t="n">
-        <v>71.69</v>
+        <v>59.44</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -801,46 +801,46 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>LRCX</t>
+          <t>TSM</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Equipos chips</t>
+          <t>Chips</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>336.41</v>
+        <v>414.1</v>
       </c>
       <c r="D7" t="n">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="E7" t="n">
-        <v>5.79</v>
+        <v>-1.04</v>
       </c>
       <c r="F7" t="n">
-        <v>0.93</v>
+        <v>1.04</v>
       </c>
       <c r="G7" t="n">
-        <v>15.92</v>
+        <v>16.37</v>
       </c>
       <c r="H7" t="n">
-        <v>4.73</v>
+        <v>3.95</v>
       </c>
       <c r="I7" t="n">
-        <v>330.04</v>
+        <v>407.55</v>
       </c>
       <c r="J7" t="n">
-        <v>340.39</v>
+        <v>418.19</v>
       </c>
       <c r="K7" t="n">
-        <v>312.54</v>
+        <v>389.55</v>
       </c>
       <c r="L7" t="n">
-        <v>376.2</v>
+        <v>455.01</v>
       </c>
       <c r="M7" t="n">
-        <v>66.22</v>
+        <v>53.66</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -849,7 +849,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -861,55 +861,55 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>KLAC</t>
+          <t>AAPL</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Equipos chips</t>
+          <t>Tecnología</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2131.1</v>
+        <v>307.64</v>
       </c>
       <c r="D8" t="n">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="E8" t="n">
-        <v>10.56</v>
+        <v>-1.42</v>
       </c>
       <c r="F8" t="n">
-        <v>0.79</v>
+        <v>0.91</v>
       </c>
       <c r="G8" t="n">
-        <v>91.25</v>
+        <v>5.73</v>
       </c>
       <c r="H8" t="n">
-        <v>4.28</v>
+        <v>1.86</v>
       </c>
       <c r="I8" t="n">
-        <v>2094.6</v>
+        <v>305.35</v>
       </c>
       <c r="J8" t="n">
-        <v>2153.91</v>
+        <v>309.07</v>
       </c>
       <c r="K8" t="n">
-        <v>1994.23</v>
+        <v>299.05</v>
       </c>
       <c r="L8" t="n">
-        <v>2359.22</v>
+        <v>321.96</v>
       </c>
       <c r="M8" t="n">
-        <v>66.70999999999999</v>
+        <v>58.69</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>MEDIO</t>
+          <t>BAJO</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -921,57 +921,53 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SLB</t>
+          <t>LRCX</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Energía</t>
+          <t>Equipos chips</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>58.01</v>
+        <v>305.86</v>
       </c>
       <c r="D9" t="n">
-        <v>95</v>
+        <v>78</v>
       </c>
       <c r="E9" t="n">
-        <v>5.79</v>
+        <v>-3.87</v>
       </c>
       <c r="F9" t="n">
-        <v>0.63</v>
+        <v>0.74</v>
       </c>
       <c r="G9" t="n">
-        <v>1.58</v>
+        <v>16.61</v>
       </c>
       <c r="H9" t="n">
-        <v>2.73</v>
+        <v>5.43</v>
       </c>
       <c r="I9" t="n">
-        <v>57.38</v>
+        <v>299.22</v>
       </c>
       <c r="J9" t="n">
-        <v>58.41</v>
+        <v>310.01</v>
       </c>
       <c r="K9" t="n">
-        <v>55.64</v>
+        <v>280.95</v>
       </c>
       <c r="L9" t="n">
-        <v>61.96</v>
+        <v>347.38</v>
       </c>
       <c r="M9" t="n">
-        <v>61.67</v>
+        <v>58.07</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>BAJO</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>🔥🔥</t>
-        </is>
-      </c>
+          <t>MEDIO</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>POSIBLE COMPRA</t>
@@ -981,57 +977,53 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CVX</t>
+          <t>HOOD</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Energía</t>
+          <t>Trading</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>188.35</v>
+        <v>80.83</v>
       </c>
       <c r="D10" t="n">
-        <v>92</v>
+        <v>76</v>
       </c>
       <c r="E10" t="n">
-        <v>2.91</v>
+        <v>-14.29</v>
       </c>
       <c r="F10" t="n">
-        <v>0.39</v>
+        <v>1.08</v>
       </c>
       <c r="G10" t="n">
-        <v>4.6</v>
+        <v>5.58</v>
       </c>
       <c r="H10" t="n">
-        <v>2.44</v>
+        <v>6.9</v>
       </c>
       <c r="I10" t="n">
-        <v>186.51</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="J10" t="n">
-        <v>189.5</v>
+        <v>82.22</v>
       </c>
       <c r="K10" t="n">
-        <v>181.45</v>
+        <v>72.45999999999999</v>
       </c>
       <c r="L10" t="n">
-        <v>199.84</v>
+        <v>94.76000000000001</v>
       </c>
       <c r="M10" t="n">
-        <v>54.5</v>
+        <v>53.54</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>BAJO</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>🔥🔥</t>
-        </is>
-      </c>
+          <t>MEDIO</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>POSIBLE COMPRA</t>
@@ -1041,57 +1033,53 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>OXY</t>
+          <t>AI</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Energía</t>
+          <t>IA</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>58.67</v>
+        <v>10.16</v>
       </c>
       <c r="D11" t="n">
-        <v>92</v>
+        <v>76</v>
       </c>
       <c r="E11" t="n">
-        <v>2.36</v>
+        <v>-5.62</v>
       </c>
       <c r="F11" t="n">
-        <v>0.64</v>
+        <v>1.03</v>
       </c>
       <c r="G11" t="n">
-        <v>1.9</v>
+        <v>0.68</v>
       </c>
       <c r="H11" t="n">
-        <v>3.24</v>
+        <v>6.73</v>
       </c>
       <c r="I11" t="n">
-        <v>57.91</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="J11" t="n">
-        <v>59.15</v>
+        <v>10.34</v>
       </c>
       <c r="K11" t="n">
-        <v>55.81</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="L11" t="n">
-        <v>63.43</v>
+        <v>11.88</v>
       </c>
       <c r="M11" t="n">
-        <v>57.17</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>BAJO</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>🔥🔥</t>
-        </is>
-      </c>
+          <t>MEDIO</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>POSIBLE COMPRA</t>
@@ -1101,226 +1089,226 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>MU</t>
+          <t>QQQ</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Memoria / Chips</t>
+          <t>ETF Nasdaq</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>996</v>
+        <v>706.6799999999999</v>
       </c>
       <c r="D12" t="n">
-        <v>87</v>
+        <v>72</v>
       </c>
       <c r="E12" t="n">
-        <v>7.85</v>
+        <v>-4.28</v>
       </c>
       <c r="F12" t="n">
-        <v>0.95</v>
+        <v>1.77</v>
       </c>
       <c r="G12" t="n">
-        <v>68.38</v>
+        <v>11.75</v>
       </c>
       <c r="H12" t="n">
-        <v>6.87</v>
+        <v>1.66</v>
       </c>
       <c r="I12" t="n">
-        <v>968.65</v>
+        <v>701.98</v>
       </c>
       <c r="J12" t="n">
-        <v>1013.1</v>
+        <v>709.62</v>
       </c>
       <c r="K12" t="n">
-        <v>893.4299999999999</v>
+        <v>689.05</v>
       </c>
       <c r="L12" t="n">
-        <v>1166.96</v>
+        <v>736.0599999999999</v>
       </c>
       <c r="M12" t="n">
-        <v>68.09</v>
+        <v>48.79</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>MEDIO</t>
+          <t>BAJO</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>POSIBLE COMPRA</t>
+          <t>VIGILAR</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>HOOD</t>
+          <t>SPY</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Trading</t>
+          <t>ETF Mercado</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>88.33</v>
+        <v>737.0599999999999</v>
       </c>
       <c r="D13" t="n">
-        <v>84</v>
+        <v>67</v>
       </c>
       <c r="E13" t="n">
-        <v>4.11</v>
+        <v>-2.57</v>
       </c>
       <c r="F13" t="n">
-        <v>1.19</v>
+        <v>1.27</v>
       </c>
       <c r="G13" t="n">
-        <v>5.25</v>
+        <v>7.15</v>
       </c>
       <c r="H13" t="n">
-        <v>5.94</v>
+        <v>0.97</v>
       </c>
       <c r="I13" t="n">
-        <v>86.23</v>
+        <v>734.2</v>
       </c>
       <c r="J13" t="n">
-        <v>89.64</v>
+        <v>738.85</v>
       </c>
       <c r="K13" t="n">
-        <v>80.45</v>
+        <v>726.34</v>
       </c>
       <c r="L13" t="n">
-        <v>101.46</v>
+        <v>754.9299999999999</v>
       </c>
       <c r="M13" t="n">
-        <v>57.92</v>
+        <v>48.23</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>MEDIO</t>
+          <t>BAJO</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>POSIBLE COMPRA</t>
+          <t>VIGILAR</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>XOM</t>
+          <t>AVGO</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Energía</t>
+          <t>IA / Chips</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>152.04</v>
+        <v>387.41</v>
       </c>
       <c r="D14" t="n">
-        <v>82</v>
+        <v>55</v>
       </c>
       <c r="E14" t="n">
-        <v>3.46</v>
+        <v>-13.29</v>
       </c>
       <c r="F14" t="n">
-        <v>0.53</v>
+        <v>1.36</v>
       </c>
       <c r="G14" t="n">
-        <v>4.41</v>
+        <v>22.83</v>
       </c>
       <c r="H14" t="n">
-        <v>2.9</v>
+        <v>5.89</v>
       </c>
       <c r="I14" t="n">
-        <v>150.27</v>
+        <v>378.28</v>
       </c>
       <c r="J14" t="n">
-        <v>153.14</v>
+        <v>393.12</v>
       </c>
       <c r="K14" t="n">
-        <v>145.42</v>
+        <v>353.17</v>
       </c>
       <c r="L14" t="n">
-        <v>163.08</v>
+        <v>444.48</v>
       </c>
       <c r="M14" t="n">
-        <v>50.4</v>
+        <v>39.86</v>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>BAJO</t>
+          <t>MEDIO</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>POSIBLE COMPRA</t>
+          <t>NO COMPRAR</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>META</t>
+          <t>XOM</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Tecnología</t>
+          <t>Energía</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>627.5700000000001</v>
+        <v>150.37</v>
       </c>
       <c r="D15" t="n">
-        <v>81</v>
+        <v>54</v>
       </c>
       <c r="E15" t="n">
-        <v>-1.22</v>
+        <v>3.52</v>
       </c>
       <c r="F15" t="n">
-        <v>1.27</v>
+        <v>0.52</v>
       </c>
       <c r="G15" t="n">
-        <v>16.36</v>
+        <v>4.17</v>
       </c>
       <c r="H15" t="n">
-        <v>2.61</v>
+        <v>2.77</v>
       </c>
       <c r="I15" t="n">
-        <v>621.03</v>
+        <v>148.7</v>
       </c>
       <c r="J15" t="n">
-        <v>631.66</v>
+        <v>151.41</v>
       </c>
       <c r="K15" t="n">
-        <v>603.04</v>
+        <v>144.11</v>
       </c>
       <c r="L15" t="n">
-        <v>668.46</v>
+        <v>160.8</v>
       </c>
       <c r="M15" t="n">
-        <v>53.94</v>
+        <v>37.96</v>
       </c>
       <c r="N15" t="inlineStr">
         <is>
@@ -1329,58 +1317,58 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>POSIBLE COMPRA</t>
+          <t>NO COMPRAR</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>SPY</t>
+          <t>META</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>ETF Mercado</t>
+          <t>Tecnología</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>757.09</v>
+        <v>589.6900000000001</v>
       </c>
       <c r="D16" t="n">
-        <v>95</v>
+        <v>51</v>
       </c>
       <c r="E16" t="n">
-        <v>0.33</v>
+        <v>-6.77</v>
       </c>
       <c r="F16" t="n">
-        <v>0.97</v>
+        <v>1.28</v>
       </c>
       <c r="G16" t="n">
-        <v>6.34</v>
+        <v>18.82</v>
       </c>
       <c r="H16" t="n">
-        <v>0.84</v>
+        <v>3.19</v>
       </c>
       <c r="I16" t="n">
-        <v>754.5599999999999</v>
+        <v>582.16</v>
       </c>
       <c r="J16" t="n">
-        <v>758.67</v>
+        <v>594.39</v>
       </c>
       <c r="K16" t="n">
-        <v>747.59</v>
+        <v>561.46</v>
       </c>
       <c r="L16" t="n">
-        <v>772.9299999999999</v>
+        <v>636.74</v>
       </c>
       <c r="M16" t="n">
-        <v>59.15</v>
+        <v>41.81</v>
       </c>
       <c r="N16" t="inlineStr">
         <is>
@@ -1394,57 +1382,57 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>POSIBLE COMPRA</t>
+          <t>NO COMPRAR</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>QQQ</t>
+          <t>COIN</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>ETF Nasdaq</t>
+          <t>Cripto / Trading</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>740.61</v>
+        <v>150.32</v>
       </c>
       <c r="D17" t="n">
-        <v>95</v>
+        <v>45</v>
       </c>
       <c r="E17" t="n">
-        <v>0.68</v>
+        <v>-20.48</v>
       </c>
       <c r="F17" t="n">
-        <v>0.95</v>
+        <v>1.33</v>
       </c>
       <c r="G17" t="n">
-        <v>10.18</v>
+        <v>10.32</v>
       </c>
       <c r="H17" t="n">
-        <v>1.37</v>
+        <v>6.87</v>
       </c>
       <c r="I17" t="n">
-        <v>736.54</v>
+        <v>146.2</v>
       </c>
       <c r="J17" t="n">
-        <v>743.15</v>
+        <v>152.91</v>
       </c>
       <c r="K17" t="n">
-        <v>725.35</v>
+        <v>134.84</v>
       </c>
       <c r="L17" t="n">
-        <v>766.05</v>
+        <v>176.13</v>
       </c>
       <c r="M17" t="n">
-        <v>64.84999999999999</v>
+        <v>24.94</v>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>BAJO</t>
+          <t>MEDIO</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
@@ -1454,57 +1442,57 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>POSIBLE COMPRA</t>
+          <t>NO COMPRAR</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>PYPL</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>IA / Chips</t>
+          <t>Pagos</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>523.2</v>
+        <v>41.17</v>
       </c>
       <c r="D18" t="n">
-        <v>94</v>
+        <v>43</v>
       </c>
       <c r="E18" t="n">
-        <v>0.99</v>
+        <v>-7.7</v>
       </c>
       <c r="F18" t="n">
-        <v>0.83</v>
+        <v>1.26</v>
       </c>
       <c r="G18" t="n">
-        <v>29.38</v>
+        <v>1.19</v>
       </c>
       <c r="H18" t="n">
-        <v>5.62</v>
+        <v>2.88</v>
       </c>
       <c r="I18" t="n">
-        <v>511.45</v>
+        <v>40.7</v>
       </c>
       <c r="J18" t="n">
-        <v>530.55</v>
+        <v>41.47</v>
       </c>
       <c r="K18" t="n">
-        <v>479.13</v>
+        <v>39.39</v>
       </c>
       <c r="L18" t="n">
-        <v>596.66</v>
+        <v>44.14</v>
       </c>
       <c r="M18" t="n">
-        <v>67.01000000000001</v>
+        <v>29.62</v>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>MEDIO</t>
+          <t>BAJO</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
@@ -1514,233 +1502,221 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>POSIBLE COMPRA</t>
+          <t>NO COMPRAR</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>SLB</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Tecnología</t>
+          <t>Energía</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>428.05</v>
+        <v>54.76</v>
       </c>
       <c r="D19" t="n">
-        <v>92</v>
+        <v>72</v>
       </c>
       <c r="E19" t="n">
-        <v>0.25</v>
+        <v>0.92</v>
       </c>
       <c r="F19" t="n">
-        <v>0.71</v>
+        <v>0.51</v>
       </c>
       <c r="G19" t="n">
-        <v>13.58</v>
+        <v>1.77</v>
       </c>
       <c r="H19" t="n">
-        <v>3.17</v>
+        <v>3.23</v>
       </c>
       <c r="I19" t="n">
-        <v>422.62</v>
+        <v>54.06</v>
       </c>
       <c r="J19" t="n">
-        <v>431.45</v>
+        <v>55.21</v>
       </c>
       <c r="K19" t="n">
-        <v>407.67</v>
+        <v>52.11</v>
       </c>
       <c r="L19" t="n">
-        <v>462.01</v>
+        <v>59.18</v>
       </c>
       <c r="M19" t="n">
-        <v>58.63</v>
+        <v>48.82</v>
       </c>
       <c r="N19" t="inlineStr">
         <is>
           <t>BAJO</t>
         </is>
       </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>🔥</t>
-        </is>
-      </c>
+      <c r="O19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>POSIBLE COMPRA</t>
+          <t>VIGILAR</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Tecnología</t>
+          <t>IA / Chips</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>311.23</v>
+        <v>467.3</v>
       </c>
       <c r="D20" t="n">
-        <v>88</v>
+        <v>68</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.41</v>
+        <v>-9.449999999999999</v>
       </c>
       <c r="F20" t="n">
-        <v>0.8</v>
+        <v>0.99</v>
       </c>
       <c r="G20" t="n">
-        <v>5.63</v>
+        <v>31.73</v>
       </c>
       <c r="H20" t="n">
-        <v>1.81</v>
+        <v>6.79</v>
       </c>
       <c r="I20" t="n">
-        <v>308.98</v>
+        <v>454.61</v>
       </c>
       <c r="J20" t="n">
-        <v>312.64</v>
+        <v>475.24</v>
       </c>
       <c r="K20" t="n">
-        <v>302.78</v>
+        <v>419.71</v>
       </c>
       <c r="L20" t="n">
-        <v>325.31</v>
+        <v>546.63</v>
       </c>
       <c r="M20" t="n">
-        <v>65.84999999999999</v>
+        <v>58.77</v>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>BAJO</t>
-        </is>
-      </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>🔥</t>
-        </is>
-      </c>
+          <t>MEDIO</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>POSIBLE COMPRA</t>
+          <t>VIGILAR</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>AVGO</t>
+          <t>OXY</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>IA / Chips</t>
+          <t>Energía</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>418.91</v>
+        <v>57.26</v>
       </c>
       <c r="D21" t="n">
-        <v>78</v>
+        <v>64</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.8</v>
+        <v>1.11</v>
       </c>
       <c r="F21" t="n">
-        <v>3.05</v>
+        <v>0.53</v>
       </c>
       <c r="G21" t="n">
-        <v>21.93</v>
+        <v>1.83</v>
       </c>
       <c r="H21" t="n">
-        <v>5.24</v>
+        <v>3.2</v>
       </c>
       <c r="I21" t="n">
-        <v>410.14</v>
+        <v>56.53</v>
       </c>
       <c r="J21" t="n">
-        <v>424.39</v>
+        <v>57.72</v>
       </c>
       <c r="K21" t="n">
-        <v>386.02</v>
+        <v>54.51</v>
       </c>
       <c r="L21" t="n">
-        <v>473.73</v>
+        <v>61.84</v>
       </c>
       <c r="M21" t="n">
-        <v>43.84</v>
+        <v>39.65</v>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>MEDIO</t>
-        </is>
-      </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>🔥</t>
-        </is>
-      </c>
+          <t>BAJO</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>POSIBLE COMPRA</t>
+          <t>VIGILAR</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>QCOM</t>
+          <t>PLTR</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Chips</t>
+          <t>IA / Software</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>242.57</v>
+        <v>134.56</v>
       </c>
       <c r="D22" t="n">
-        <v>76</v>
+        <v>58</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.3</v>
+        <v>-14.04</v>
       </c>
       <c r="F22" t="n">
-        <v>0.51</v>
+        <v>0.63</v>
       </c>
       <c r="G22" t="n">
-        <v>18.23</v>
+        <v>7.29</v>
       </c>
       <c r="H22" t="n">
-        <v>7.51</v>
+        <v>5.42</v>
       </c>
       <c r="I22" t="n">
-        <v>235.28</v>
+        <v>131.64</v>
       </c>
       <c r="J22" t="n">
-        <v>247.13</v>
+        <v>136.38</v>
       </c>
       <c r="K22" t="n">
-        <v>215.23</v>
+        <v>123.63</v>
       </c>
       <c r="L22" t="n">
-        <v>288.14</v>
+        <v>152.78</v>
       </c>
       <c r="M22" t="n">
-        <v>64.31999999999999</v>
+        <v>50.46</v>
       </c>
       <c r="N22" t="inlineStr">
         <is>
@@ -1750,53 +1726,53 @@
       <c r="O22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>POSIBLE COMPRA</t>
+          <t>NO COMPRAR</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>UPST</t>
+          <t>SOFI</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Fintech IA</t>
+          <t>Fintech</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>32.27</v>
+        <v>15.8</v>
       </c>
       <c r="D23" t="n">
-        <v>76</v>
+        <v>58</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.28</v>
+        <v>-13.28</v>
       </c>
       <c r="F23" t="n">
-        <v>0.86</v>
+        <v>0.95</v>
       </c>
       <c r="G23" t="n">
-        <v>2.02</v>
+        <v>0.99</v>
       </c>
       <c r="H23" t="n">
-        <v>6.26</v>
+        <v>6.28</v>
       </c>
       <c r="I23" t="n">
-        <v>31.46</v>
+        <v>15.4</v>
       </c>
       <c r="J23" t="n">
-        <v>32.77</v>
+        <v>16.05</v>
       </c>
       <c r="K23" t="n">
-        <v>29.24</v>
+        <v>14.31</v>
       </c>
       <c r="L23" t="n">
-        <v>37.32</v>
+        <v>18.28</v>
       </c>
       <c r="M23" t="n">
-        <v>59.36</v>
+        <v>51.22</v>
       </c>
       <c r="N23" t="inlineStr">
         <is>
@@ -1806,7 +1782,7 @@
       <c r="O23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>POSIBLE COMPRA</t>
+          <t>NO COMPRAR</t>
         </is>
       </c>
     </row>
@@ -1822,58 +1798,54 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>218.66</v>
+        <v>205.32</v>
       </c>
       <c r="D24" t="n">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="E24" t="n">
-        <v>2.06</v>
+        <v>-2.65</v>
       </c>
       <c r="F24" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.9</v>
       </c>
       <c r="G24" t="n">
-        <v>8.42</v>
+        <v>8.609999999999999</v>
       </c>
       <c r="H24" t="n">
-        <v>3.85</v>
+        <v>4.2</v>
       </c>
       <c r="I24" t="n">
-        <v>215.29</v>
+        <v>201.87</v>
       </c>
       <c r="J24" t="n">
-        <v>220.77</v>
+        <v>207.47</v>
       </c>
       <c r="K24" t="n">
-        <v>206.03</v>
+        <v>192.39</v>
       </c>
       <c r="L24" t="n">
-        <v>239.71</v>
+        <v>226.85</v>
       </c>
       <c r="M24" t="n">
-        <v>35.85</v>
+        <v>34.45</v>
       </c>
       <c r="N24" t="inlineStr">
         <is>
           <t>BAJO</t>
         </is>
       </c>
-      <c r="O24" t="inlineStr">
-        <is>
-          <t>🔥</t>
-        </is>
-      </c>
+      <c r="O24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>VIGILAR</t>
+          <t>NO COMPRAR</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>GOOGL</t>
+          <t>AMZN</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1882,97 +1854,93 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>372.19</v>
+        <v>246.81</v>
       </c>
       <c r="D25" t="n">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="E25" t="n">
-        <v>-4.6</v>
+        <v>-8.81</v>
       </c>
       <c r="F25" t="n">
-        <v>1.36</v>
+        <v>0.92</v>
       </c>
       <c r="G25" t="n">
-        <v>10.11</v>
+        <v>7.3</v>
       </c>
       <c r="H25" t="n">
-        <v>2.72</v>
+        <v>2.96</v>
       </c>
       <c r="I25" t="n">
-        <v>368.14</v>
+        <v>243.89</v>
       </c>
       <c r="J25" t="n">
-        <v>374.72</v>
+        <v>248.63</v>
       </c>
       <c r="K25" t="n">
-        <v>357.02</v>
+        <v>235.86</v>
       </c>
       <c r="L25" t="n">
-        <v>397.48</v>
+        <v>265.06</v>
       </c>
       <c r="M25" t="n">
-        <v>30.09</v>
+        <v>36.02</v>
       </c>
       <c r="N25" t="inlineStr">
         <is>
           <t>BAJO</t>
         </is>
       </c>
-      <c r="O25" t="inlineStr">
-        <is>
-          <t>🔥</t>
-        </is>
-      </c>
+      <c r="O25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>VIGILAR</t>
+          <t>NO COMPRAR</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>PLTR</t>
+          <t>GOOGL</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>IA / Software</t>
+          <t>Tecnología</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>141.7</v>
+        <v>364.15</v>
       </c>
       <c r="D26" t="n">
-        <v>74</v>
+        <v>56</v>
       </c>
       <c r="E26" t="n">
-        <v>-1.14</v>
+        <v>-4.26</v>
       </c>
       <c r="F26" t="n">
-        <v>0.97</v>
+        <v>0.8</v>
       </c>
       <c r="G26" t="n">
-        <v>6.96</v>
+        <v>10.13</v>
       </c>
       <c r="H26" t="n">
-        <v>4.91</v>
+        <v>2.78</v>
       </c>
       <c r="I26" t="n">
-        <v>138.92</v>
+        <v>360.1</v>
       </c>
       <c r="J26" t="n">
-        <v>143.44</v>
+        <v>366.68</v>
       </c>
       <c r="K26" t="n">
-        <v>131.26</v>
+        <v>348.96</v>
       </c>
       <c r="L26" t="n">
-        <v>159.1</v>
+        <v>389.46</v>
       </c>
       <c r="M26" t="n">
-        <v>57.16</v>
+        <v>28.61</v>
       </c>
       <c r="N26" t="inlineStr">
         <is>
@@ -1982,53 +1950,53 @@
       <c r="O26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>VIGILAR</t>
+          <t>NO COMPRAR</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>SOFI</t>
+          <t>UPST</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Fintech</t>
+          <t>Fintech IA</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>17.15</v>
+        <v>29.43</v>
       </c>
       <c r="D27" t="n">
-        <v>74</v>
+        <v>56</v>
       </c>
       <c r="E27" t="n">
-        <v>1.06</v>
+        <v>-12.9</v>
       </c>
       <c r="F27" t="n">
-        <v>0.88</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="G27" t="n">
-        <v>0.93</v>
+        <v>2.08</v>
       </c>
       <c r="H27" t="n">
-        <v>5.44</v>
+        <v>7.07</v>
       </c>
       <c r="I27" t="n">
-        <v>16.78</v>
+        <v>28.6</v>
       </c>
       <c r="J27" t="n">
-        <v>17.38</v>
+        <v>29.95</v>
       </c>
       <c r="K27" t="n">
-        <v>15.75</v>
+        <v>26.31</v>
       </c>
       <c r="L27" t="n">
-        <v>19.48</v>
+        <v>34.63</v>
       </c>
       <c r="M27" t="n">
-        <v>58.25</v>
+        <v>49.75</v>
       </c>
       <c r="N27" t="inlineStr">
         <is>
@@ -2038,14 +2006,14 @@
       <c r="O27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>VIGILAR</t>
+          <t>NO COMPRAR</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>AMZN</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2054,37 +2022,37 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>253.79</v>
+        <v>415.02</v>
       </c>
       <c r="D28" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E28" t="n">
-        <v>-7.38</v>
+        <v>-7.82</v>
       </c>
       <c r="F28" t="n">
-        <v>0.9</v>
+        <v>0.61</v>
       </c>
       <c r="G28" t="n">
-        <v>7.05</v>
+        <v>13.32</v>
       </c>
       <c r="H28" t="n">
-        <v>2.78</v>
+        <v>3.21</v>
       </c>
       <c r="I28" t="n">
-        <v>250.97</v>
+        <v>409.69</v>
       </c>
       <c r="J28" t="n">
-        <v>255.55</v>
+        <v>418.35</v>
       </c>
       <c r="K28" t="n">
-        <v>243.21</v>
+        <v>395.03</v>
       </c>
       <c r="L28" t="n">
-        <v>271.43</v>
+        <v>448.33</v>
       </c>
       <c r="M28" t="n">
-        <v>38.44</v>
+        <v>47.36</v>
       </c>
       <c r="N28" t="inlineStr">
         <is>
@@ -2101,50 +2069,50 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>INTC</t>
+          <t>TSLA</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Chips</t>
+          <t>Autos / Tech</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>111.78</v>
+        <v>389.31</v>
       </c>
       <c r="D29" t="n">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="E29" t="n">
-        <v>-7.54</v>
+        <v>-10.67</v>
       </c>
       <c r="F29" t="n">
-        <v>0.57</v>
+        <v>0.99</v>
       </c>
       <c r="G29" t="n">
-        <v>8.66</v>
+        <v>15.08</v>
       </c>
       <c r="H29" t="n">
-        <v>7.75</v>
+        <v>3.87</v>
       </c>
       <c r="I29" t="n">
-        <v>108.31</v>
+        <v>383.28</v>
       </c>
       <c r="J29" t="n">
-        <v>113.95</v>
+        <v>393.08</v>
       </c>
       <c r="K29" t="n">
-        <v>98.79000000000001</v>
+        <v>366.69</v>
       </c>
       <c r="L29" t="n">
-        <v>133.44</v>
+        <v>427.02</v>
       </c>
       <c r="M29" t="n">
-        <v>45.42</v>
+        <v>36.79</v>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>MEDIO</t>
+          <t>BAJO</t>
         </is>
       </c>
       <c r="O29" t="inlineStr"/>
@@ -2157,50 +2125,50 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>TSLA</t>
+          <t>SOUN</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Autos / Tech</t>
+          <t>IA</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>418.45</v>
+        <v>7.32</v>
       </c>
       <c r="D30" t="n">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="E30" t="n">
-        <v>-5.35</v>
+        <v>-18.61</v>
       </c>
       <c r="F30" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.97</v>
       </c>
       <c r="G30" t="n">
-        <v>14.03</v>
+        <v>0.52</v>
       </c>
       <c r="H30" t="n">
-        <v>3.35</v>
+        <v>7.04</v>
       </c>
       <c r="I30" t="n">
-        <v>412.84</v>
+        <v>7.12</v>
       </c>
       <c r="J30" t="n">
-        <v>421.96</v>
+        <v>7.45</v>
       </c>
       <c r="K30" t="n">
-        <v>397.41</v>
+        <v>6.55</v>
       </c>
       <c r="L30" t="n">
-        <v>453.52</v>
+        <v>8.609999999999999</v>
       </c>
       <c r="M30" t="n">
-        <v>39.34</v>
+        <v>35.03</v>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>BAJO</t>
+          <t>MEDIO</t>
         </is>
       </c>
       <c r="O30" t="inlineStr"/>
@@ -2213,214 +2181,214 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>SOUN</t>
+          <t>MU</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>IA</t>
+          <t>Memoria / Chips</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>8.01</v>
+        <v>872.76</v>
       </c>
       <c r="D31" t="n">
-        <v>46</v>
+        <v>82</v>
       </c>
       <c r="E31" t="n">
-        <v>-6.43</v>
+        <v>-10.12</v>
       </c>
       <c r="F31" t="n">
-        <v>0.62</v>
+        <v>1.06</v>
       </c>
       <c r="G31" t="n">
-        <v>0.49</v>
+        <v>73.56</v>
       </c>
       <c r="H31" t="n">
-        <v>6.16</v>
+        <v>8.43</v>
       </c>
       <c r="I31" t="n">
-        <v>7.81</v>
+        <v>843.34</v>
       </c>
       <c r="J31" t="n">
-        <v>8.130000000000001</v>
+        <v>891.15</v>
       </c>
       <c r="K31" t="n">
-        <v>7.27</v>
+        <v>762.42</v>
       </c>
       <c r="L31" t="n">
-        <v>9.24</v>
+        <v>1056.67</v>
       </c>
       <c r="M31" t="n">
-        <v>41.64</v>
+        <v>60.89</v>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>MEDIO</t>
+          <t>ALTO</t>
         </is>
       </c>
       <c r="O31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>NO COMPRAR</t>
+          <t>VIGILAR</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>COIN</t>
+          <t>ARM</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Cripto / Trading</t>
+          <t>Chips</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>164.13</v>
+        <v>341.49</v>
       </c>
       <c r="D32" t="n">
-        <v>38</v>
+        <v>75</v>
       </c>
       <c r="E32" t="n">
-        <v>-9.94</v>
+        <v>-3.34</v>
       </c>
       <c r="F32" t="n">
-        <v>0.86</v>
+        <v>0.97</v>
       </c>
       <c r="G32" t="n">
-        <v>10.57</v>
+        <v>36.16</v>
       </c>
       <c r="H32" t="n">
-        <v>6.44</v>
+        <v>10.59</v>
       </c>
       <c r="I32" t="n">
-        <v>159.9</v>
+        <v>327.03</v>
       </c>
       <c r="J32" t="n">
-        <v>166.77</v>
+        <v>350.53</v>
       </c>
       <c r="K32" t="n">
-        <v>148.28</v>
+        <v>287.26</v>
       </c>
       <c r="L32" t="n">
-        <v>190.56</v>
+        <v>431.88</v>
       </c>
       <c r="M32" t="n">
-        <v>24.19</v>
+        <v>70.53</v>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>MEDIO</t>
+          <t>ALTO</t>
         </is>
       </c>
       <c r="O32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>NO COMPRAR</t>
+          <t>VIGILAR</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>PYPL</t>
+          <t>SMCI</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Pagos</t>
+          <t>Servidores IA</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>42.75</v>
+        <v>41.46</v>
       </c>
       <c r="D33" t="n">
-        <v>36</v>
+        <v>65</v>
       </c>
       <c r="E33" t="n">
-        <v>-3.85</v>
+        <v>-10.04</v>
       </c>
       <c r="F33" t="n">
-        <v>0.68</v>
+        <v>0.9</v>
       </c>
       <c r="G33" t="n">
-        <v>1.13</v>
+        <v>3.47</v>
       </c>
       <c r="H33" t="n">
-        <v>2.63</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="I33" t="n">
-        <v>42.3</v>
+        <v>40.08</v>
       </c>
       <c r="J33" t="n">
-        <v>43.03</v>
+        <v>42.33</v>
       </c>
       <c r="K33" t="n">
-        <v>41.06</v>
+        <v>36.26</v>
       </c>
       <c r="L33" t="n">
-        <v>45.56</v>
+        <v>50.13</v>
       </c>
       <c r="M33" t="n">
-        <v>32.44</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>BAJO</t>
+          <t>ALTO</t>
         </is>
       </c>
       <c r="O33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>NO COMPRAR</t>
+          <t>VIGILAR</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>IONQ</t>
+          <t>QCOM</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Computación cuántica</t>
+          <t>Chips</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>65.66</v>
+        <v>216.99</v>
       </c>
       <c r="D34" t="n">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="E34" t="n">
-        <v>-6.39</v>
+        <v>-13.24</v>
       </c>
       <c r="F34" t="n">
-        <v>1.09</v>
+        <v>0.53</v>
       </c>
       <c r="G34" t="n">
-        <v>5.73</v>
+        <v>19.47</v>
       </c>
       <c r="H34" t="n">
-        <v>8.73</v>
+        <v>8.970000000000001</v>
       </c>
       <c r="I34" t="n">
-        <v>63.37</v>
+        <v>209.21</v>
       </c>
       <c r="J34" t="n">
-        <v>67.09</v>
+        <v>221.86</v>
       </c>
       <c r="K34" t="n">
-        <v>57.07</v>
+        <v>187.8</v>
       </c>
       <c r="L34" t="n">
-        <v>79.98</v>
+        <v>265.66</v>
       </c>
       <c r="M34" t="n">
-        <v>59.45</v>
+        <v>54.75</v>
       </c>
       <c r="N34" t="inlineStr">
         <is>
@@ -2437,46 +2405,46 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>ARM</t>
+          <t>IONQ</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Chips</t>
+          <t>Computación cuántica</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>393.44</v>
+        <v>56.54</v>
       </c>
       <c r="D35" t="n">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="E35" t="n">
-        <v>17.35</v>
+        <v>-21.55</v>
       </c>
       <c r="F35" t="n">
-        <v>0.83</v>
+        <v>0.74</v>
       </c>
       <c r="G35" t="n">
-        <v>33.59</v>
+        <v>5.99</v>
       </c>
       <c r="H35" t="n">
-        <v>8.539999999999999</v>
+        <v>10.59</v>
       </c>
       <c r="I35" t="n">
-        <v>380</v>
+        <v>54.14</v>
       </c>
       <c r="J35" t="n">
-        <v>401.84</v>
+        <v>58.04</v>
       </c>
       <c r="K35" t="n">
-        <v>343.05</v>
+        <v>47.56</v>
       </c>
       <c r="L35" t="n">
-        <v>477.42</v>
+        <v>71.51000000000001</v>
       </c>
       <c r="M35" t="n">
-        <v>78.47</v>
+        <v>54.89</v>
       </c>
       <c r="N35" t="inlineStr">
         <is>
@@ -2486,53 +2454,53 @@
       <c r="O35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>VIGILAR</t>
+          <t>NO COMPRAR</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>SMCI</t>
+          <t>INTC</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Servidores IA</t>
+          <t>Chips</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>46.9</v>
+        <v>99.93000000000001</v>
       </c>
       <c r="D36" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E36" t="n">
-        <v>13.56</v>
+        <v>-12.86</v>
       </c>
       <c r="F36" t="n">
-        <v>0.74</v>
+        <v>0.79</v>
       </c>
       <c r="G36" t="n">
-        <v>3.22</v>
+        <v>8.77</v>
       </c>
       <c r="H36" t="n">
-        <v>6.86</v>
+        <v>8.77</v>
       </c>
       <c r="I36" t="n">
-        <v>45.61</v>
+        <v>96.42</v>
       </c>
       <c r="J36" t="n">
-        <v>47.7</v>
+        <v>102.12</v>
       </c>
       <c r="K36" t="n">
-        <v>42.07</v>
+        <v>86.78</v>
       </c>
       <c r="L36" t="n">
-        <v>54.95</v>
+        <v>121.85</v>
       </c>
       <c r="M36" t="n">
-        <v>77.36</v>
+        <v>41.16</v>
       </c>
       <c r="N36" t="inlineStr">
         <is>
@@ -2558,37 +2526,37 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>119.95</v>
+        <v>108.84</v>
       </c>
       <c r="D37" t="n">
         <v>52</v>
       </c>
       <c r="E37" t="n">
-        <v>-18.97</v>
+        <v>-24.14</v>
       </c>
       <c r="F37" t="n">
-        <v>0.72</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="G37" t="n">
-        <v>12.31</v>
+        <v>12.49</v>
       </c>
       <c r="H37" t="n">
-        <v>10.26</v>
+        <v>11.47</v>
       </c>
       <c r="I37" t="n">
-        <v>115.03</v>
+        <v>103.84</v>
       </c>
       <c r="J37" t="n">
-        <v>123.03</v>
+        <v>111.96</v>
       </c>
       <c r="K37" t="n">
-        <v>101.48</v>
+        <v>90.11</v>
       </c>
       <c r="L37" t="n">
-        <v>150.73</v>
+        <v>140.06</v>
       </c>
       <c r="M37" t="n">
-        <v>43.78</v>
+        <v>42.38</v>
       </c>
       <c r="N37" t="inlineStr">
         <is>

--- a/analisis_acciones.xlsx
+++ b/analisis_acciones.xlsx
@@ -510,46 +510,46 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1649.77</v>
+        <v>1749.04</v>
       </c>
       <c r="D2" t="n">
         <v>95</v>
       </c>
       <c r="E2" t="n">
-        <v>2.29</v>
+        <v>7.4</v>
       </c>
       <c r="F2" t="n">
-        <v>1.12</v>
+        <v>1.23</v>
       </c>
       <c r="G2" t="n">
-        <v>67.43000000000001</v>
+        <v>71.61</v>
       </c>
       <c r="H2" t="n">
         <v>4.09</v>
       </c>
       <c r="I2" t="n">
-        <v>1622.8</v>
+        <v>1720.4</v>
       </c>
       <c r="J2" t="n">
-        <v>1666.63</v>
+        <v>1766.94</v>
       </c>
       <c r="K2" t="n">
-        <v>1548.63</v>
+        <v>1641.63</v>
       </c>
       <c r="L2" t="n">
-        <v>1818.34</v>
+        <v>1928.06</v>
       </c>
       <c r="M2" t="n">
-        <v>64.28</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>BAJO</t>
+          <t>MEDIO</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>🔥🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -561,55 +561,55 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>CVX</t>
+          <t>LRCX</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Energía</t>
+          <t>Equipos chips</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>187.99</v>
+        <v>324.45</v>
       </c>
       <c r="D3" t="n">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="E3" t="n">
-        <v>3.03</v>
+        <v>2.31</v>
       </c>
       <c r="F3" t="n">
-        <v>0.44</v>
+        <v>1.26</v>
       </c>
       <c r="G3" t="n">
-        <v>4.47</v>
+        <v>17.13</v>
       </c>
       <c r="H3" t="n">
-        <v>2.38</v>
+        <v>5.28</v>
       </c>
       <c r="I3" t="n">
-        <v>186.2</v>
+        <v>317.6</v>
       </c>
       <c r="J3" t="n">
-        <v>189.1</v>
+        <v>328.73</v>
       </c>
       <c r="K3" t="n">
-        <v>181.28</v>
+        <v>298.76</v>
       </c>
       <c r="L3" t="n">
-        <v>199.16</v>
+        <v>367.26</v>
       </c>
       <c r="M3" t="n">
-        <v>47.95</v>
+        <v>65.70999999999999</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>BAJO</t>
+          <t>MEDIO</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>🔥🔥</t>
+          <t>🔥🔥🔥</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -621,46 +621,46 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SOXX</t>
+          <t>AMAT</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ETF Chips</t>
+          <t>Equipos chips</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>545.71</v>
+        <v>492.17</v>
       </c>
       <c r="D4" t="n">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="E4" t="n">
-        <v>-4.11</v>
+        <v>7.42</v>
       </c>
       <c r="F4" t="n">
-        <v>1.93</v>
+        <v>1.15</v>
       </c>
       <c r="G4" t="n">
-        <v>28.21</v>
+        <v>24.49</v>
       </c>
       <c r="H4" t="n">
-        <v>5.17</v>
+        <v>4.98</v>
       </c>
       <c r="I4" t="n">
-        <v>534.4299999999999</v>
+        <v>482.37</v>
       </c>
       <c r="J4" t="n">
-        <v>552.76</v>
+        <v>498.29</v>
       </c>
       <c r="K4" t="n">
-        <v>503.4</v>
+        <v>455.43</v>
       </c>
       <c r="L4" t="n">
-        <v>616.23</v>
+        <v>553.4</v>
       </c>
       <c r="M4" t="n">
-        <v>58.63</v>
+        <v>69.48</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -681,55 +681,55 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AMAT</t>
+          <t>AAPL</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Equipos chips</t>
+          <t>Tecnología</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>457.78</v>
+        <v>301.54</v>
       </c>
       <c r="D5" t="n">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="E5" t="n">
-        <v>1.72</v>
+        <v>-1.56</v>
       </c>
       <c r="F5" t="n">
-        <v>0.73</v>
+        <v>1.51</v>
       </c>
       <c r="G5" t="n">
-        <v>23.49</v>
+        <v>6.48</v>
       </c>
       <c r="H5" t="n">
-        <v>5.13</v>
+        <v>2.15</v>
       </c>
       <c r="I5" t="n">
-        <v>448.38</v>
+        <v>298.95</v>
       </c>
       <c r="J5" t="n">
-        <v>463.65</v>
+        <v>303.16</v>
       </c>
       <c r="K5" t="n">
-        <v>422.54</v>
+        <v>291.83</v>
       </c>
       <c r="L5" t="n">
-        <v>516.52</v>
+        <v>317.73</v>
       </c>
       <c r="M5" t="n">
-        <v>55.96</v>
+        <v>53.99</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>MEDIO</t>
+          <t>BAJO</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -741,46 +741,46 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>KLAC</t>
+          <t>SOXX</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Equipos chips</t>
+          <t>ETF Chips</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1954.54</v>
+        <v>571.45</v>
       </c>
       <c r="D6" t="n">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="E6" t="n">
-        <v>1.71</v>
+        <v>-0.08</v>
       </c>
       <c r="F6" t="n">
-        <v>0.97</v>
+        <v>1.31</v>
       </c>
       <c r="G6" t="n">
-        <v>98.42</v>
+        <v>28.97</v>
       </c>
       <c r="H6" t="n">
-        <v>5.04</v>
+        <v>5.07</v>
       </c>
       <c r="I6" t="n">
-        <v>1915.17</v>
+        <v>559.86</v>
       </c>
       <c r="J6" t="n">
-        <v>1979.15</v>
+        <v>578.6900000000001</v>
       </c>
       <c r="K6" t="n">
-        <v>1806.9</v>
+        <v>528</v>
       </c>
       <c r="L6" t="n">
-        <v>2200.6</v>
+        <v>643.87</v>
       </c>
       <c r="M6" t="n">
-        <v>59.44</v>
+        <v>65.72</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -801,55 +801,55 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>KLAC</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Chips</t>
+          <t>Equipos chips</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>414.1</v>
+        <v>2108.06</v>
       </c>
       <c r="D7" t="n">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.04</v>
+        <v>8.66</v>
       </c>
       <c r="F7" t="n">
-        <v>1.04</v>
+        <v>1.15</v>
       </c>
       <c r="G7" t="n">
-        <v>16.37</v>
+        <v>107.11</v>
       </c>
       <c r="H7" t="n">
-        <v>3.95</v>
+        <v>5.08</v>
       </c>
       <c r="I7" t="n">
-        <v>407.55</v>
+        <v>2065.22</v>
       </c>
       <c r="J7" t="n">
-        <v>418.19</v>
+        <v>2134.84</v>
       </c>
       <c r="K7" t="n">
-        <v>389.55</v>
+        <v>1947.4</v>
       </c>
       <c r="L7" t="n">
-        <v>455.01</v>
+        <v>2375.83</v>
       </c>
       <c r="M7" t="n">
-        <v>53.66</v>
+        <v>68.19</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>BAJO</t>
+          <t>MEDIO</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -861,46 +861,46 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>SLB</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Tecnología</t>
+          <t>Energía</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>307.64</v>
+        <v>56.55</v>
       </c>
       <c r="D8" t="n">
         <v>80</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.42</v>
+        <v>3.83</v>
       </c>
       <c r="F8" t="n">
-        <v>0.91</v>
+        <v>1.1</v>
       </c>
       <c r="G8" t="n">
-        <v>5.73</v>
+        <v>1.78</v>
       </c>
       <c r="H8" t="n">
-        <v>1.86</v>
+        <v>3.15</v>
       </c>
       <c r="I8" t="n">
-        <v>305.35</v>
+        <v>55.84</v>
       </c>
       <c r="J8" t="n">
-        <v>309.07</v>
+        <v>57</v>
       </c>
       <c r="K8" t="n">
-        <v>299.05</v>
+        <v>53.88</v>
       </c>
       <c r="L8" t="n">
-        <v>321.96</v>
+        <v>61</v>
       </c>
       <c r="M8" t="n">
-        <v>58.69</v>
+        <v>48.89</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
@@ -909,7 +909,7 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -921,53 +921,57 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>LRCX</t>
+          <t>TSM</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Equipos chips</t>
+          <t>Chips</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>305.86</v>
+        <v>426.8</v>
       </c>
       <c r="D9" t="n">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.87</v>
+        <v>-2.03</v>
       </c>
       <c r="F9" t="n">
-        <v>0.74</v>
+        <v>0.88</v>
       </c>
       <c r="G9" t="n">
-        <v>16.61</v>
+        <v>16.57</v>
       </c>
       <c r="H9" t="n">
-        <v>5.43</v>
+        <v>3.88</v>
       </c>
       <c r="I9" t="n">
-        <v>299.22</v>
+        <v>420.17</v>
       </c>
       <c r="J9" t="n">
-        <v>310.01</v>
+        <v>430.94</v>
       </c>
       <c r="K9" t="n">
-        <v>280.95</v>
+        <v>401.95</v>
       </c>
       <c r="L9" t="n">
-        <v>347.38</v>
+        <v>468.22</v>
       </c>
       <c r="M9" t="n">
-        <v>58.07</v>
+        <v>61.42</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>MEDIO</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr"/>
+          <t>BAJO</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>🔥</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>POSIBLE COMPRA</t>
@@ -977,53 +981,57 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>HOOD</t>
+          <t>CVX</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Trading</t>
+          <t>Energía</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>80.83</v>
+        <v>189.24</v>
       </c>
       <c r="D10" t="n">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="E10" t="n">
-        <v>-14.29</v>
+        <v>1.84</v>
       </c>
       <c r="F10" t="n">
-        <v>1.08</v>
+        <v>0.49</v>
       </c>
       <c r="G10" t="n">
-        <v>5.58</v>
+        <v>4.23</v>
       </c>
       <c r="H10" t="n">
-        <v>6.9</v>
+        <v>2.23</v>
       </c>
       <c r="I10" t="n">
-        <v>78.59999999999999</v>
+        <v>187.55</v>
       </c>
       <c r="J10" t="n">
-        <v>82.22</v>
+        <v>190.3</v>
       </c>
       <c r="K10" t="n">
-        <v>72.45999999999999</v>
+        <v>182.9</v>
       </c>
       <c r="L10" t="n">
-        <v>94.76000000000001</v>
+        <v>199.81</v>
       </c>
       <c r="M10" t="n">
-        <v>53.54</v>
+        <v>41.87</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>MEDIO</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr"/>
+          <t>BAJO</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>🔥</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>POSIBLE COMPRA</t>
@@ -1033,46 +1041,46 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>AI</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>IA</t>
+          <t>IA / Chips</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>10.16</v>
+        <v>490.33</v>
       </c>
       <c r="D11" t="n">
         <v>76</v>
       </c>
       <c r="E11" t="n">
-        <v>-5.62</v>
+        <v>-3.88</v>
       </c>
       <c r="F11" t="n">
-        <v>1.03</v>
+        <v>0.76</v>
       </c>
       <c r="G11" t="n">
-        <v>0.68</v>
+        <v>31.77</v>
       </c>
       <c r="H11" t="n">
-        <v>6.73</v>
+        <v>6.48</v>
       </c>
       <c r="I11" t="n">
-        <v>9.890000000000001</v>
+        <v>477.62</v>
       </c>
       <c r="J11" t="n">
-        <v>10.34</v>
+        <v>498.27</v>
       </c>
       <c r="K11" t="n">
-        <v>9.140000000000001</v>
+        <v>442.68</v>
       </c>
       <c r="L11" t="n">
-        <v>11.88</v>
+        <v>569.75</v>
       </c>
       <c r="M11" t="n">
-        <v>65.90000000000001</v>
+        <v>62.93</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
@@ -1089,120 +1097,112 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>QQQ</t>
+          <t>HOOD</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>ETF Nasdaq</t>
+          <t>Trading</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>706.6799999999999</v>
+        <v>85.04000000000001</v>
       </c>
       <c r="D12" t="n">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.28</v>
+        <v>-6.27</v>
       </c>
       <c r="F12" t="n">
-        <v>1.77</v>
+        <v>0.72</v>
       </c>
       <c r="G12" t="n">
-        <v>11.75</v>
+        <v>5.48</v>
       </c>
       <c r="H12" t="n">
-        <v>1.66</v>
+        <v>6.45</v>
       </c>
       <c r="I12" t="n">
-        <v>701.98</v>
+        <v>82.84999999999999</v>
       </c>
       <c r="J12" t="n">
-        <v>709.62</v>
+        <v>86.41</v>
       </c>
       <c r="K12" t="n">
-        <v>689.05</v>
+        <v>76.81999999999999</v>
       </c>
       <c r="L12" t="n">
-        <v>736.0599999999999</v>
+        <v>98.75</v>
       </c>
       <c r="M12" t="n">
-        <v>48.79</v>
+        <v>57.44</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>BAJO</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>🔥</t>
-        </is>
-      </c>
+          <t>MEDIO</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>VIGILAR</t>
+          <t>POSIBLE COMPRA</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>SPY</t>
+          <t>UPST</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>ETF Mercado</t>
+          <t>Fintech IA</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>737.0599999999999</v>
+        <v>31</v>
       </c>
       <c r="D13" t="n">
-        <v>67</v>
+        <v>76</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.57</v>
+        <v>-7.77</v>
       </c>
       <c r="F13" t="n">
-        <v>1.27</v>
+        <v>0.84</v>
       </c>
       <c r="G13" t="n">
-        <v>7.15</v>
+        <v>2.06</v>
       </c>
       <c r="H13" t="n">
-        <v>0.97</v>
+        <v>6.63</v>
       </c>
       <c r="I13" t="n">
-        <v>734.2</v>
+        <v>30.18</v>
       </c>
       <c r="J13" t="n">
-        <v>738.85</v>
+        <v>31.51</v>
       </c>
       <c r="K13" t="n">
-        <v>726.34</v>
+        <v>27.92</v>
       </c>
       <c r="L13" t="n">
-        <v>754.9299999999999</v>
+        <v>36.14</v>
       </c>
       <c r="M13" t="n">
-        <v>48.23</v>
+        <v>59.75</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>BAJO</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>🔥</t>
-        </is>
-      </c>
+          <t>MEDIO</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>VIGILAR</t>
+          <t>POSIBLE COMPRA</t>
         </is>
       </c>
     </row>
@@ -1218,37 +1218,37 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>387.41</v>
+        <v>396.6</v>
       </c>
       <c r="D14" t="n">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="E14" t="n">
-        <v>-13.29</v>
+        <v>-13.78</v>
       </c>
       <c r="F14" t="n">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="G14" t="n">
-        <v>22.83</v>
+        <v>23.33</v>
       </c>
       <c r="H14" t="n">
-        <v>5.89</v>
+        <v>5.88</v>
       </c>
       <c r="I14" t="n">
-        <v>378.28</v>
+        <v>387.27</v>
       </c>
       <c r="J14" t="n">
-        <v>393.12</v>
+        <v>402.43</v>
       </c>
       <c r="K14" t="n">
-        <v>353.17</v>
+        <v>361.6</v>
       </c>
       <c r="L14" t="n">
-        <v>444.48</v>
+        <v>454.93</v>
       </c>
       <c r="M14" t="n">
-        <v>39.86</v>
+        <v>43.8</v>
       </c>
       <c r="N14" t="inlineStr">
         <is>
@@ -1262,297 +1262,281 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>NO COMPRAR</t>
+          <t>VIGILAR</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>XOM</t>
+          <t>SPY</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Energía</t>
+          <t>ETF Mercado</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>150.37</v>
+        <v>739.22</v>
       </c>
       <c r="D15" t="n">
-        <v>54</v>
+        <v>72</v>
       </c>
       <c r="E15" t="n">
-        <v>3.52</v>
+        <v>-2.55</v>
       </c>
       <c r="F15" t="n">
-        <v>0.52</v>
+        <v>0.86</v>
       </c>
       <c r="G15" t="n">
-        <v>4.17</v>
+        <v>7.13</v>
       </c>
       <c r="H15" t="n">
-        <v>2.77</v>
+        <v>0.96</v>
       </c>
       <c r="I15" t="n">
-        <v>148.7</v>
+        <v>736.37</v>
       </c>
       <c r="J15" t="n">
-        <v>151.41</v>
+        <v>741</v>
       </c>
       <c r="K15" t="n">
-        <v>144.11</v>
+        <v>728.53</v>
       </c>
       <c r="L15" t="n">
-        <v>160.8</v>
+        <v>757.04</v>
       </c>
       <c r="M15" t="n">
-        <v>37.96</v>
+        <v>50.47</v>
       </c>
       <c r="N15" t="inlineStr">
         <is>
           <t>BAJO</t>
         </is>
       </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>🔥</t>
-        </is>
-      </c>
+      <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>NO COMPRAR</t>
+          <t>VIGILAR</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>META</t>
+          <t>QQQ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Tecnología</t>
+          <t>ETF Nasdaq</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>589.6900000000001</v>
+        <v>716.0700000000001</v>
       </c>
       <c r="D16" t="n">
-        <v>51</v>
+        <v>72</v>
       </c>
       <c r="E16" t="n">
-        <v>-6.77</v>
+        <v>-3.59</v>
       </c>
       <c r="F16" t="n">
-        <v>1.28</v>
+        <v>1.07</v>
       </c>
       <c r="G16" t="n">
-        <v>18.82</v>
+        <v>12.09</v>
       </c>
       <c r="H16" t="n">
-        <v>3.19</v>
+        <v>1.69</v>
       </c>
       <c r="I16" t="n">
-        <v>582.16</v>
+        <v>711.23</v>
       </c>
       <c r="J16" t="n">
-        <v>594.39</v>
+        <v>719.09</v>
       </c>
       <c r="K16" t="n">
-        <v>561.46</v>
+        <v>697.9400000000001</v>
       </c>
       <c r="L16" t="n">
-        <v>636.74</v>
+        <v>746.29</v>
       </c>
       <c r="M16" t="n">
-        <v>41.81</v>
+        <v>54.96</v>
       </c>
       <c r="N16" t="inlineStr">
         <is>
           <t>BAJO</t>
         </is>
       </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>🔥</t>
-        </is>
-      </c>
+      <c r="O16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>NO COMPRAR</t>
+          <t>VIGILAR</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>COIN</t>
+          <t>MU</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Cripto / Trading</t>
+          <t>Memoria / Chips</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>150.32</v>
+        <v>949.28</v>
       </c>
       <c r="D17" t="n">
-        <v>45</v>
+        <v>69</v>
       </c>
       <c r="E17" t="n">
-        <v>-20.48</v>
+        <v>-8.33</v>
       </c>
       <c r="F17" t="n">
-        <v>1.33</v>
+        <v>0.95</v>
       </c>
       <c r="G17" t="n">
-        <v>10.32</v>
+        <v>74.11</v>
       </c>
       <c r="H17" t="n">
-        <v>6.87</v>
+        <v>7.81</v>
       </c>
       <c r="I17" t="n">
-        <v>146.2</v>
+        <v>919.64</v>
       </c>
       <c r="J17" t="n">
-        <v>152.91</v>
+        <v>967.8099999999999</v>
       </c>
       <c r="K17" t="n">
-        <v>134.84</v>
+        <v>838.12</v>
       </c>
       <c r="L17" t="n">
-        <v>176.13</v>
+        <v>1134.55</v>
       </c>
       <c r="M17" t="n">
-        <v>24.94</v>
+        <v>68.31999999999999</v>
       </c>
       <c r="N17" t="inlineStr">
         <is>
           <t>MEDIO</t>
         </is>
       </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>🔥</t>
-        </is>
-      </c>
+      <c r="O17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>NO COMPRAR</t>
+          <t>VIGILAR</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>PYPL</t>
+          <t>AI</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Pagos</t>
+          <t>IA</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>41.17</v>
+        <v>10.6</v>
       </c>
       <c r="D18" t="n">
-        <v>43</v>
+        <v>69</v>
       </c>
       <c r="E18" t="n">
-        <v>-7.7</v>
+        <v>-9.789999999999999</v>
       </c>
       <c r="F18" t="n">
-        <v>1.26</v>
+        <v>0.82</v>
       </c>
       <c r="G18" t="n">
-        <v>1.19</v>
+        <v>0.71</v>
       </c>
       <c r="H18" t="n">
-        <v>2.88</v>
+        <v>6.71</v>
       </c>
       <c r="I18" t="n">
-        <v>40.7</v>
+        <v>10.32</v>
       </c>
       <c r="J18" t="n">
-        <v>41.47</v>
+        <v>10.78</v>
       </c>
       <c r="K18" t="n">
-        <v>39.39</v>
+        <v>9.529999999999999</v>
       </c>
       <c r="L18" t="n">
-        <v>44.14</v>
+        <v>12.38</v>
       </c>
       <c r="M18" t="n">
-        <v>29.62</v>
+        <v>70.23999999999999</v>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>BAJO</t>
-        </is>
-      </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>🔥</t>
-        </is>
-      </c>
+          <t>MEDIO</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>NO COMPRAR</t>
+          <t>VIGILAR</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>SLB</t>
+          <t>SOFI</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Energía</t>
+          <t>Fintech</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>54.76</v>
+        <v>16.5</v>
       </c>
       <c r="D19" t="n">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="E19" t="n">
-        <v>0.92</v>
+        <v>-11.19</v>
       </c>
       <c r="F19" t="n">
-        <v>0.51</v>
+        <v>1.08</v>
       </c>
       <c r="G19" t="n">
-        <v>1.77</v>
+        <v>0.97</v>
       </c>
       <c r="H19" t="n">
-        <v>3.23</v>
+        <v>5.89</v>
       </c>
       <c r="I19" t="n">
-        <v>54.06</v>
+        <v>16.11</v>
       </c>
       <c r="J19" t="n">
-        <v>55.21</v>
+        <v>16.74</v>
       </c>
       <c r="K19" t="n">
-        <v>52.11</v>
+        <v>15.04</v>
       </c>
       <c r="L19" t="n">
-        <v>59.18</v>
+        <v>18.93</v>
       </c>
       <c r="M19" t="n">
-        <v>48.82</v>
+        <v>54.98</v>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>BAJO</t>
+          <t>MEDIO</t>
         </is>
       </c>
       <c r="O19" t="inlineStr"/>
@@ -1565,7 +1549,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>NVDA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1574,93 +1558,93 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>467.3</v>
+        <v>208.64</v>
       </c>
       <c r="D20" t="n">
-        <v>68</v>
+        <v>56</v>
       </c>
       <c r="E20" t="n">
-        <v>-9.449999999999999</v>
+        <v>-6.9</v>
       </c>
       <c r="F20" t="n">
-        <v>0.99</v>
+        <v>0.77</v>
       </c>
       <c r="G20" t="n">
-        <v>31.73</v>
+        <v>8.17</v>
       </c>
       <c r="H20" t="n">
-        <v>6.79</v>
+        <v>3.92</v>
       </c>
       <c r="I20" t="n">
-        <v>454.61</v>
+        <v>205.37</v>
       </c>
       <c r="J20" t="n">
-        <v>475.24</v>
+        <v>210.68</v>
       </c>
       <c r="K20" t="n">
-        <v>419.71</v>
+        <v>196.39</v>
       </c>
       <c r="L20" t="n">
-        <v>546.63</v>
+        <v>229.06</v>
       </c>
       <c r="M20" t="n">
-        <v>58.77</v>
+        <v>39.55</v>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>MEDIO</t>
+          <t>BAJO</t>
         </is>
       </c>
       <c r="O20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>VIGILAR</t>
+          <t>NO COMPRAR</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>OXY</t>
+          <t>AMZN</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Energía</t>
+          <t>Tecnología</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>57.26</v>
+        <v>245.22</v>
       </c>
       <c r="D21" t="n">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="E21" t="n">
-        <v>1.11</v>
+        <v>-6.14</v>
       </c>
       <c r="F21" t="n">
-        <v>0.53</v>
+        <v>0.82</v>
       </c>
       <c r="G21" t="n">
-        <v>1.83</v>
+        <v>7.34</v>
       </c>
       <c r="H21" t="n">
-        <v>3.2</v>
+        <v>2.99</v>
       </c>
       <c r="I21" t="n">
-        <v>56.53</v>
+        <v>242.28</v>
       </c>
       <c r="J21" t="n">
-        <v>57.72</v>
+        <v>247.05</v>
       </c>
       <c r="K21" t="n">
-        <v>54.51</v>
+        <v>234.21</v>
       </c>
       <c r="L21" t="n">
-        <v>61.84</v>
+        <v>263.57</v>
       </c>
       <c r="M21" t="n">
-        <v>39.65</v>
+        <v>34.37</v>
       </c>
       <c r="N21" t="inlineStr">
         <is>
@@ -1670,57 +1654,57 @@
       <c r="O21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>VIGILAR</t>
+          <t>NO COMPRAR</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>PLTR</t>
+          <t>GOOGL</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>IA / Software</t>
+          <t>Tecnología</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>134.56</v>
+        <v>363.31</v>
       </c>
       <c r="D22" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E22" t="n">
-        <v>-14.04</v>
+        <v>-3.47</v>
       </c>
       <c r="F22" t="n">
-        <v>0.63</v>
+        <v>0.88</v>
       </c>
       <c r="G22" t="n">
-        <v>7.29</v>
+        <v>9.69</v>
       </c>
       <c r="H22" t="n">
-        <v>5.42</v>
+        <v>2.67</v>
       </c>
       <c r="I22" t="n">
-        <v>131.64</v>
+        <v>359.43</v>
       </c>
       <c r="J22" t="n">
-        <v>136.38</v>
+        <v>365.73</v>
       </c>
       <c r="K22" t="n">
-        <v>123.63</v>
+        <v>348.77</v>
       </c>
       <c r="L22" t="n">
-        <v>152.78</v>
+        <v>387.54</v>
       </c>
       <c r="M22" t="n">
-        <v>50.46</v>
+        <v>28.15</v>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>MEDIO</t>
+          <t>BAJO</t>
         </is>
       </c>
       <c r="O22" t="inlineStr"/>
@@ -1733,50 +1717,50 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>SOFI</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Fintech</t>
+          <t>Tecnología</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>15.8</v>
+        <v>411.74</v>
       </c>
       <c r="D23" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="E23" t="n">
-        <v>-13.28</v>
+        <v>-10.59</v>
       </c>
       <c r="F23" t="n">
-        <v>0.95</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="G23" t="n">
-        <v>0.99</v>
+        <v>13.26</v>
       </c>
       <c r="H23" t="n">
-        <v>6.28</v>
+        <v>3.22</v>
       </c>
       <c r="I23" t="n">
-        <v>15.4</v>
+        <v>406.44</v>
       </c>
       <c r="J23" t="n">
-        <v>16.05</v>
+        <v>415.06</v>
       </c>
       <c r="K23" t="n">
-        <v>14.31</v>
+        <v>391.85</v>
       </c>
       <c r="L23" t="n">
-        <v>18.28</v>
+        <v>444.89</v>
       </c>
       <c r="M23" t="n">
-        <v>51.22</v>
+        <v>45.28</v>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>MEDIO</t>
+          <t>BAJO</t>
         </is>
       </c>
       <c r="O23" t="inlineStr"/>
@@ -1789,46 +1773,46 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>NVDA</t>
+          <t>TSLA</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>IA / Chips</t>
+          <t>Autos / Tech</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>205.32</v>
+        <v>408.95</v>
       </c>
       <c r="D24" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.65</v>
+        <v>-1.67</v>
       </c>
       <c r="F24" t="n">
-        <v>0.9</v>
+        <v>0.98</v>
       </c>
       <c r="G24" t="n">
-        <v>8.609999999999999</v>
+        <v>15.44</v>
       </c>
       <c r="H24" t="n">
-        <v>4.2</v>
+        <v>3.78</v>
       </c>
       <c r="I24" t="n">
-        <v>201.87</v>
+        <v>402.77</v>
       </c>
       <c r="J24" t="n">
-        <v>207.47</v>
+        <v>412.81</v>
       </c>
       <c r="K24" t="n">
-        <v>192.39</v>
+        <v>385.79</v>
       </c>
       <c r="L24" t="n">
-        <v>226.85</v>
+        <v>447.56</v>
       </c>
       <c r="M24" t="n">
-        <v>34.45</v>
+        <v>49.6</v>
       </c>
       <c r="N24" t="inlineStr">
         <is>
@@ -1845,46 +1829,46 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>AMZN</t>
+          <t>XOM</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Tecnología</t>
+          <t>Energía</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>246.81</v>
+        <v>151.75</v>
       </c>
       <c r="D25" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E25" t="n">
-        <v>-8.81</v>
+        <v>1.59</v>
       </c>
       <c r="F25" t="n">
-        <v>0.92</v>
+        <v>0.83</v>
       </c>
       <c r="G25" t="n">
-        <v>7.3</v>
+        <v>3.98</v>
       </c>
       <c r="H25" t="n">
-        <v>2.96</v>
+        <v>2.63</v>
       </c>
       <c r="I25" t="n">
-        <v>243.89</v>
+        <v>150.16</v>
       </c>
       <c r="J25" t="n">
-        <v>248.63</v>
+        <v>152.75</v>
       </c>
       <c r="K25" t="n">
-        <v>235.86</v>
+        <v>145.77</v>
       </c>
       <c r="L25" t="n">
-        <v>265.06</v>
+        <v>161.71</v>
       </c>
       <c r="M25" t="n">
-        <v>36.02</v>
+        <v>35.93</v>
       </c>
       <c r="N25" t="inlineStr">
         <is>
@@ -1901,46 +1885,46 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>GOOGL</t>
+          <t>OXY</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Tecnología</t>
+          <t>Energía</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>364.15</v>
+        <v>57.48</v>
       </c>
       <c r="D26" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E26" t="n">
-        <v>-4.26</v>
+        <v>-2.44</v>
       </c>
       <c r="F26" t="n">
-        <v>0.8</v>
+        <v>0.79</v>
       </c>
       <c r="G26" t="n">
-        <v>10.13</v>
+        <v>1.79</v>
       </c>
       <c r="H26" t="n">
-        <v>2.78</v>
+        <v>3.12</v>
       </c>
       <c r="I26" t="n">
-        <v>360.1</v>
+        <v>56.76</v>
       </c>
       <c r="J26" t="n">
-        <v>366.68</v>
+        <v>57.93</v>
       </c>
       <c r="K26" t="n">
-        <v>348.96</v>
+        <v>54.79</v>
       </c>
       <c r="L26" t="n">
-        <v>389.46</v>
+        <v>61.97</v>
       </c>
       <c r="M26" t="n">
-        <v>28.61</v>
+        <v>40.9</v>
       </c>
       <c r="N26" t="inlineStr">
         <is>
@@ -1957,46 +1941,46 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>UPST</t>
+          <t>PLTR</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Fintech IA</t>
+          <t>IA / Software</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>29.43</v>
+        <v>136.47</v>
       </c>
       <c r="D27" t="n">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="E27" t="n">
-        <v>-12.9</v>
+        <v>-15.05</v>
       </c>
       <c r="F27" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.66</v>
       </c>
       <c r="G27" t="n">
-        <v>2.08</v>
+        <v>7.14</v>
       </c>
       <c r="H27" t="n">
-        <v>7.07</v>
+        <v>5.23</v>
       </c>
       <c r="I27" t="n">
-        <v>28.6</v>
+        <v>133.62</v>
       </c>
       <c r="J27" t="n">
-        <v>29.95</v>
+        <v>138.25</v>
       </c>
       <c r="K27" t="n">
-        <v>26.31</v>
+        <v>125.76</v>
       </c>
       <c r="L27" t="n">
-        <v>34.63</v>
+        <v>154.31</v>
       </c>
       <c r="M27" t="n">
-        <v>49.75</v>
+        <v>51.08</v>
       </c>
       <c r="N27" t="inlineStr">
         <is>
@@ -2013,7 +1997,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>META</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2022,37 +2006,37 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>415.02</v>
+        <v>585.39</v>
       </c>
       <c r="D28" t="n">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="E28" t="n">
-        <v>-7.82</v>
+        <v>-2.51</v>
       </c>
       <c r="F28" t="n">
-        <v>0.61</v>
+        <v>1.06</v>
       </c>
       <c r="G28" t="n">
-        <v>13.32</v>
+        <v>18.96</v>
       </c>
       <c r="H28" t="n">
-        <v>3.21</v>
+        <v>3.24</v>
       </c>
       <c r="I28" t="n">
-        <v>409.69</v>
+        <v>577.8099999999999</v>
       </c>
       <c r="J28" t="n">
-        <v>418.35</v>
+        <v>590.13</v>
       </c>
       <c r="K28" t="n">
-        <v>395.03</v>
+        <v>556.95</v>
       </c>
       <c r="L28" t="n">
-        <v>448.33</v>
+        <v>632.79</v>
       </c>
       <c r="M28" t="n">
-        <v>47.36</v>
+        <v>41.45</v>
       </c>
       <c r="N28" t="inlineStr">
         <is>
@@ -2069,50 +2053,50 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>TSLA</t>
+          <t>SOUN</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Autos / Tech</t>
+          <t>IA</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>389.31</v>
+        <v>7.49</v>
       </c>
       <c r="D29" t="n">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="E29" t="n">
-        <v>-10.67</v>
+        <v>-19.03</v>
       </c>
       <c r="F29" t="n">
-        <v>0.99</v>
+        <v>0.85</v>
       </c>
       <c r="G29" t="n">
-        <v>15.08</v>
+        <v>0.51</v>
       </c>
       <c r="H29" t="n">
-        <v>3.87</v>
+        <v>6.85</v>
       </c>
       <c r="I29" t="n">
-        <v>383.28</v>
+        <v>7.28</v>
       </c>
       <c r="J29" t="n">
-        <v>393.08</v>
+        <v>7.62</v>
       </c>
       <c r="K29" t="n">
-        <v>366.69</v>
+        <v>6.72</v>
       </c>
       <c r="L29" t="n">
-        <v>427.02</v>
+        <v>8.77</v>
       </c>
       <c r="M29" t="n">
-        <v>36.79</v>
+        <v>38.06</v>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>BAJO</t>
+          <t>MEDIO</t>
         </is>
       </c>
       <c r="O29" t="inlineStr"/>
@@ -2125,50 +2109,50 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>SOUN</t>
+          <t>PYPL</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>IA</t>
+          <t>Pagos</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>7.32</v>
+        <v>41.26</v>
       </c>
       <c r="D30" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E30" t="n">
-        <v>-18.61</v>
+        <v>-8.4</v>
       </c>
       <c r="F30" t="n">
-        <v>0.97</v>
+        <v>1.01</v>
       </c>
       <c r="G30" t="n">
-        <v>0.52</v>
+        <v>1.17</v>
       </c>
       <c r="H30" t="n">
-        <v>7.04</v>
+        <v>2.85</v>
       </c>
       <c r="I30" t="n">
-        <v>7.12</v>
+        <v>40.79</v>
       </c>
       <c r="J30" t="n">
-        <v>7.45</v>
+        <v>41.55</v>
       </c>
       <c r="K30" t="n">
-        <v>6.55</v>
+        <v>39.5</v>
       </c>
       <c r="L30" t="n">
-        <v>8.609999999999999</v>
+        <v>44.2</v>
       </c>
       <c r="M30" t="n">
-        <v>35.03</v>
+        <v>30.08</v>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>MEDIO</t>
+          <t>BAJO</t>
         </is>
       </c>
       <c r="O30" t="inlineStr"/>
@@ -2181,56 +2165,56 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>MU</t>
+          <t>COIN</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Memoria / Chips</t>
+          <t>Cripto / Trading</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>872.76</v>
+        <v>162.11</v>
       </c>
       <c r="D31" t="n">
-        <v>82</v>
+        <v>28</v>
       </c>
       <c r="E31" t="n">
-        <v>-10.12</v>
+        <v>-11.23</v>
       </c>
       <c r="F31" t="n">
-        <v>1.06</v>
+        <v>0.89</v>
       </c>
       <c r="G31" t="n">
-        <v>73.56</v>
+        <v>10.37</v>
       </c>
       <c r="H31" t="n">
-        <v>8.43</v>
+        <v>6.39</v>
       </c>
       <c r="I31" t="n">
-        <v>843.34</v>
+        <v>157.96</v>
       </c>
       <c r="J31" t="n">
-        <v>891.15</v>
+        <v>164.7</v>
       </c>
       <c r="K31" t="n">
-        <v>762.42</v>
+        <v>146.56</v>
       </c>
       <c r="L31" t="n">
-        <v>1056.67</v>
+        <v>188.03</v>
       </c>
       <c r="M31" t="n">
-        <v>60.89</v>
+        <v>35.09</v>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>ALTO</t>
+          <t>MEDIO</t>
         </is>
       </c>
       <c r="O31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>VIGILAR</t>
+          <t>NO COMPRAR</t>
         </is>
       </c>
     </row>
@@ -2246,37 +2230,37 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>341.49</v>
+        <v>346.39</v>
       </c>
       <c r="D32" t="n">
         <v>75</v>
       </c>
       <c r="E32" t="n">
-        <v>-3.34</v>
+        <v>-15.28</v>
       </c>
       <c r="F32" t="n">
-        <v>0.97</v>
+        <v>0.72</v>
       </c>
       <c r="G32" t="n">
-        <v>36.16</v>
+        <v>37.07</v>
       </c>
       <c r="H32" t="n">
-        <v>10.59</v>
+        <v>10.7</v>
       </c>
       <c r="I32" t="n">
-        <v>327.03</v>
+        <v>331.56</v>
       </c>
       <c r="J32" t="n">
-        <v>350.53</v>
+        <v>355.66</v>
       </c>
       <c r="K32" t="n">
-        <v>287.26</v>
+        <v>290.78</v>
       </c>
       <c r="L32" t="n">
-        <v>431.88</v>
+        <v>439.08</v>
       </c>
       <c r="M32" t="n">
-        <v>70.53</v>
+        <v>70.62</v>
       </c>
       <c r="N32" t="inlineStr">
         <is>
@@ -2293,46 +2277,46 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>SMCI</t>
+          <t>INTC</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Servidores IA</t>
+          <t>Chips</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>41.46</v>
+        <v>110.27</v>
       </c>
       <c r="D33" t="n">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="E33" t="n">
-        <v>-10.04</v>
+        <v>0.86</v>
       </c>
       <c r="F33" t="n">
-        <v>0.9</v>
+        <v>1.05</v>
       </c>
       <c r="G33" t="n">
-        <v>3.47</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="H33" t="n">
-        <v>8.359999999999999</v>
+        <v>8.130000000000001</v>
       </c>
       <c r="I33" t="n">
-        <v>40.08</v>
+        <v>106.68</v>
       </c>
       <c r="J33" t="n">
-        <v>42.33</v>
+        <v>112.51</v>
       </c>
       <c r="K33" t="n">
-        <v>36.26</v>
+        <v>96.81999999999999</v>
       </c>
       <c r="L33" t="n">
-        <v>50.13</v>
+        <v>132.68</v>
       </c>
       <c r="M33" t="n">
-        <v>68.09999999999999</v>
+        <v>51.71</v>
       </c>
       <c r="N33" t="inlineStr">
         <is>
@@ -2349,46 +2333,46 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>QCOM</t>
+          <t>SMCI</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Chips</t>
+          <t>Servidores IA</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>216.99</v>
+        <v>43.99</v>
       </c>
       <c r="D34" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E34" t="n">
-        <v>-13.24</v>
+        <v>-6.16</v>
       </c>
       <c r="F34" t="n">
-        <v>0.53</v>
+        <v>0.76</v>
       </c>
       <c r="G34" t="n">
-        <v>19.47</v>
+        <v>3.56</v>
       </c>
       <c r="H34" t="n">
-        <v>8.970000000000001</v>
+        <v>8.09</v>
       </c>
       <c r="I34" t="n">
-        <v>209.21</v>
+        <v>42.57</v>
       </c>
       <c r="J34" t="n">
-        <v>221.86</v>
+        <v>44.88</v>
       </c>
       <c r="K34" t="n">
-        <v>187.8</v>
+        <v>38.65</v>
       </c>
       <c r="L34" t="n">
-        <v>265.66</v>
+        <v>52.89</v>
       </c>
       <c r="M34" t="n">
-        <v>54.75</v>
+        <v>71.34999999999999</v>
       </c>
       <c r="N34" t="inlineStr">
         <is>
@@ -2405,46 +2389,46 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>IONQ</t>
+          <t>QCOM</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Computación cuántica</t>
+          <t>Chips</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>56.54</v>
+        <v>217.77</v>
       </c>
       <c r="D35" t="n">
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="E35" t="n">
-        <v>-21.55</v>
+        <v>-4.55</v>
       </c>
       <c r="F35" t="n">
-        <v>0.74</v>
+        <v>0.65</v>
       </c>
       <c r="G35" t="n">
-        <v>5.99</v>
+        <v>18.78</v>
       </c>
       <c r="H35" t="n">
-        <v>10.59</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="I35" t="n">
-        <v>54.14</v>
+        <v>210.26</v>
       </c>
       <c r="J35" t="n">
-        <v>58.04</v>
+        <v>222.46</v>
       </c>
       <c r="K35" t="n">
-        <v>47.56</v>
+        <v>189.6</v>
       </c>
       <c r="L35" t="n">
-        <v>71.51000000000001</v>
+        <v>264.71</v>
       </c>
       <c r="M35" t="n">
-        <v>54.89</v>
+        <v>54.33</v>
       </c>
       <c r="N35" t="inlineStr">
         <is>
@@ -2454,53 +2438,53 @@
       <c r="O35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>NO COMPRAR</t>
+          <t>VIGILAR</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>INTC</t>
+          <t>IONQ</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Chips</t>
+          <t>Computación cuántica</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>99.93000000000001</v>
+        <v>62.8</v>
       </c>
       <c r="D36" t="n">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="E36" t="n">
-        <v>-12.86</v>
+        <v>-9.35</v>
       </c>
       <c r="F36" t="n">
-        <v>0.79</v>
+        <v>0.82</v>
       </c>
       <c r="G36" t="n">
-        <v>8.77</v>
+        <v>6.23</v>
       </c>
       <c r="H36" t="n">
-        <v>8.77</v>
+        <v>9.92</v>
       </c>
       <c r="I36" t="n">
-        <v>96.42</v>
+        <v>60.31</v>
       </c>
       <c r="J36" t="n">
-        <v>102.12</v>
+        <v>64.36</v>
       </c>
       <c r="K36" t="n">
-        <v>86.78</v>
+        <v>53.45</v>
       </c>
       <c r="L36" t="n">
-        <v>121.85</v>
+        <v>78.38</v>
       </c>
       <c r="M36" t="n">
-        <v>41.16</v>
+        <v>63.47</v>
       </c>
       <c r="N36" t="inlineStr">
         <is>
@@ -2510,7 +2494,7 @@
       <c r="O36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>NO COMPRAR</t>
+          <t>VIGILAR</t>
         </is>
       </c>
     </row>
@@ -2526,37 +2510,37 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>108.84</v>
+        <v>113.65</v>
       </c>
       <c r="D37" t="n">
         <v>52</v>
       </c>
       <c r="E37" t="n">
-        <v>-24.14</v>
+        <v>-7.14</v>
       </c>
       <c r="F37" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.47</v>
       </c>
       <c r="G37" t="n">
-        <v>12.49</v>
+        <v>11.96</v>
       </c>
       <c r="H37" t="n">
-        <v>11.47</v>
+        <v>10.52</v>
       </c>
       <c r="I37" t="n">
-        <v>103.84</v>
+        <v>108.87</v>
       </c>
       <c r="J37" t="n">
-        <v>111.96</v>
+        <v>116.64</v>
       </c>
       <c r="K37" t="n">
-        <v>90.11</v>
+        <v>95.70999999999999</v>
       </c>
       <c r="L37" t="n">
-        <v>140.06</v>
+        <v>143.54</v>
       </c>
       <c r="M37" t="n">
-        <v>42.38</v>
+        <v>41.29</v>
       </c>
       <c r="N37" t="inlineStr">
         <is>

--- a/analisis_acciones.xlsx
+++ b/analisis_acciones.xlsx
@@ -510,37 +510,37 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1749.04</v>
+        <v>1702.85</v>
       </c>
       <c r="D2" t="n">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="E2" t="n">
-        <v>7.4</v>
+        <v>-0.15</v>
       </c>
       <c r="F2" t="n">
-        <v>1.23</v>
+        <v>1.15</v>
       </c>
       <c r="G2" t="n">
-        <v>71.61</v>
+        <v>77.78</v>
       </c>
       <c r="H2" t="n">
-        <v>4.09</v>
+        <v>4.57</v>
       </c>
       <c r="I2" t="n">
-        <v>1720.4</v>
+        <v>1671.74</v>
       </c>
       <c r="J2" t="n">
-        <v>1766.94</v>
+        <v>1722.29</v>
       </c>
       <c r="K2" t="n">
-        <v>1641.63</v>
+        <v>1586.18</v>
       </c>
       <c r="L2" t="n">
-        <v>1928.06</v>
+        <v>1897.3</v>
       </c>
       <c r="M2" t="n">
-        <v>72.90000000000001</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -549,7 +549,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -561,7 +561,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>LRCX</t>
+          <t>AMAT</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -570,37 +570,37 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>324.45</v>
+        <v>475.28</v>
       </c>
       <c r="D3" t="n">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="E3" t="n">
-        <v>2.31</v>
+        <v>-3.01</v>
       </c>
       <c r="F3" t="n">
-        <v>1.26</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="G3" t="n">
-        <v>17.13</v>
+        <v>26.88</v>
       </c>
       <c r="H3" t="n">
-        <v>5.28</v>
+        <v>5.66</v>
       </c>
       <c r="I3" t="n">
-        <v>317.6</v>
+        <v>464.53</v>
       </c>
       <c r="J3" t="n">
-        <v>328.73</v>
+        <v>482</v>
       </c>
       <c r="K3" t="n">
-        <v>298.76</v>
+        <v>434.96</v>
       </c>
       <c r="L3" t="n">
-        <v>367.26</v>
+        <v>542.48</v>
       </c>
       <c r="M3" t="n">
-        <v>65.70999999999999</v>
+        <v>66.14</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -609,7 +609,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>🔥🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -621,7 +621,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AMAT</t>
+          <t>KLAC</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -630,37 +630,37 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>492.17</v>
+        <v>2029.66</v>
       </c>
       <c r="D4" t="n">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="E4" t="n">
-        <v>7.42</v>
+        <v>-0.76</v>
       </c>
       <c r="F4" t="n">
-        <v>1.15</v>
+        <v>0.61</v>
       </c>
       <c r="G4" t="n">
-        <v>24.49</v>
+        <v>118.43</v>
       </c>
       <c r="H4" t="n">
-        <v>4.98</v>
+        <v>5.83</v>
       </c>
       <c r="I4" t="n">
-        <v>482.37</v>
+        <v>1982.28</v>
       </c>
       <c r="J4" t="n">
-        <v>498.29</v>
+        <v>2059.26</v>
       </c>
       <c r="K4" t="n">
-        <v>455.43</v>
+        <v>1852.01</v>
       </c>
       <c r="L4" t="n">
-        <v>553.4</v>
+        <v>2325.72</v>
       </c>
       <c r="M4" t="n">
-        <v>69.48</v>
+        <v>64.05</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -669,7 +669,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>🔥🔥</t>
+          <t>🔥</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -681,57 +681,53 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>TSM</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Tecnología</t>
+          <t>Chips</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>301.54</v>
+        <v>409.37</v>
       </c>
       <c r="D5" t="n">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.56</v>
+        <v>-8.35</v>
       </c>
       <c r="F5" t="n">
-        <v>1.51</v>
+        <v>0.58</v>
       </c>
       <c r="G5" t="n">
-        <v>6.48</v>
+        <v>17.68</v>
       </c>
       <c r="H5" t="n">
-        <v>2.15</v>
+        <v>4.32</v>
       </c>
       <c r="I5" t="n">
-        <v>298.95</v>
+        <v>402.3</v>
       </c>
       <c r="J5" t="n">
-        <v>303.16</v>
+        <v>413.79</v>
       </c>
       <c r="K5" t="n">
-        <v>291.83</v>
+        <v>382.86</v>
       </c>
       <c r="L5" t="n">
-        <v>317.73</v>
+        <v>453.56</v>
       </c>
       <c r="M5" t="n">
-        <v>53.99</v>
+        <v>55.62</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
           <t>BAJO</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>🔥🔥</t>
-        </is>
-      </c>
+      <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>POSIBLE COMPRA</t>
@@ -741,57 +737,53 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SOXX</t>
+          <t>LRCX</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>ETF Chips</t>
+          <t>Equipos chips</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>571.45</v>
+        <v>312.32</v>
       </c>
       <c r="D6" t="n">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.08</v>
+        <v>-6.61</v>
       </c>
       <c r="F6" t="n">
-        <v>1.31</v>
+        <v>0.64</v>
       </c>
       <c r="G6" t="n">
-        <v>28.97</v>
+        <v>18.71</v>
       </c>
       <c r="H6" t="n">
-        <v>5.07</v>
+        <v>5.99</v>
       </c>
       <c r="I6" t="n">
-        <v>559.86</v>
+        <v>304.83</v>
       </c>
       <c r="J6" t="n">
-        <v>578.6900000000001</v>
+        <v>316.99</v>
       </c>
       <c r="K6" t="n">
-        <v>528</v>
+        <v>284.25</v>
       </c>
       <c r="L6" t="n">
-        <v>643.87</v>
+        <v>359.09</v>
       </c>
       <c r="M6" t="n">
-        <v>65.72</v>
+        <v>62.52</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
           <t>MEDIO</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>🔥🔥</t>
-        </is>
-      </c>
+      <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>POSIBLE COMPRA</t>
@@ -801,57 +793,53 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>KLAC</t>
+          <t>AI</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Equipos chips</t>
+          <t>IA</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>2108.06</v>
+        <v>10.19</v>
       </c>
       <c r="D7" t="n">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="E7" t="n">
-        <v>8.66</v>
+        <v>-8.859999999999999</v>
       </c>
       <c r="F7" t="n">
-        <v>1.15</v>
+        <v>0.58</v>
       </c>
       <c r="G7" t="n">
-        <v>107.11</v>
+        <v>0.75</v>
       </c>
       <c r="H7" t="n">
-        <v>5.08</v>
+        <v>7.39</v>
       </c>
       <c r="I7" t="n">
-        <v>2065.22</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="J7" t="n">
-        <v>2134.84</v>
+        <v>10.38</v>
       </c>
       <c r="K7" t="n">
-        <v>1947.4</v>
+        <v>9.06</v>
       </c>
       <c r="L7" t="n">
-        <v>2375.83</v>
+        <v>12.07</v>
       </c>
       <c r="M7" t="n">
-        <v>68.19</v>
+        <v>63.88</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
           <t>MEDIO</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>🔥🔥</t>
-        </is>
-      </c>
+      <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>POSIBLE COMPRA</t>
@@ -861,405 +849,389 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SLB</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Energía</t>
+          <t>IA / Chips</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>56.55</v>
+        <v>447.5</v>
       </c>
       <c r="D8" t="n">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="E8" t="n">
-        <v>3.83</v>
+        <v>-14.2</v>
       </c>
       <c r="F8" t="n">
-        <v>1.1</v>
+        <v>0.54</v>
       </c>
       <c r="G8" t="n">
-        <v>1.78</v>
+        <v>33.38</v>
       </c>
       <c r="H8" t="n">
-        <v>3.15</v>
+        <v>7.46</v>
       </c>
       <c r="I8" t="n">
-        <v>55.84</v>
+        <v>434.15</v>
       </c>
       <c r="J8" t="n">
-        <v>57</v>
+        <v>455.84</v>
       </c>
       <c r="K8" t="n">
-        <v>53.88</v>
+        <v>397.44</v>
       </c>
       <c r="L8" t="n">
-        <v>61</v>
+        <v>530.9400000000001</v>
       </c>
       <c r="M8" t="n">
-        <v>48.89</v>
+        <v>55.5</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>BAJO</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>🔥🔥</t>
-        </is>
-      </c>
+          <t>MEDIO</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>POSIBLE COMPRA</t>
+          <t>VIGILAR</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>HOOD</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Chips</t>
+          <t>Trading</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>426.8</v>
+        <v>80.20999999999999</v>
       </c>
       <c r="D9" t="n">
-        <v>84</v>
+        <v>68</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.03</v>
+        <v>-9.02</v>
       </c>
       <c r="F9" t="n">
-        <v>0.88</v>
+        <v>0.58</v>
       </c>
       <c r="G9" t="n">
-        <v>16.57</v>
+        <v>5.77</v>
       </c>
       <c r="H9" t="n">
-        <v>3.88</v>
+        <v>7.19</v>
       </c>
       <c r="I9" t="n">
-        <v>420.17</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="J9" t="n">
-        <v>430.94</v>
+        <v>81.65000000000001</v>
       </c>
       <c r="K9" t="n">
-        <v>401.95</v>
+        <v>71.56</v>
       </c>
       <c r="L9" t="n">
-        <v>468.22</v>
+        <v>94.62</v>
       </c>
       <c r="M9" t="n">
-        <v>61.42</v>
+        <v>55.51</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>BAJO</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>🔥</t>
-        </is>
-      </c>
+          <t>MEDIO</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>POSIBLE COMPRA</t>
+          <t>VIGILAR</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CVX</t>
+          <t>SOXX</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Energía</t>
+          <t>ETF Chips</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>189.24</v>
+        <v>531.46</v>
       </c>
       <c r="D10" t="n">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="E10" t="n">
-        <v>1.84</v>
+        <v>-12.16</v>
       </c>
       <c r="F10" t="n">
-        <v>0.49</v>
+        <v>1.07</v>
       </c>
       <c r="G10" t="n">
-        <v>4.23</v>
+        <v>31.13</v>
       </c>
       <c r="H10" t="n">
-        <v>2.23</v>
+        <v>5.86</v>
       </c>
       <c r="I10" t="n">
-        <v>187.55</v>
+        <v>519.01</v>
       </c>
       <c r="J10" t="n">
-        <v>190.3</v>
+        <v>539.24</v>
       </c>
       <c r="K10" t="n">
-        <v>182.9</v>
+        <v>484.77</v>
       </c>
       <c r="L10" t="n">
-        <v>199.81</v>
+        <v>609.28</v>
       </c>
       <c r="M10" t="n">
-        <v>41.87</v>
+        <v>56.21</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>BAJO</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>🔥</t>
-        </is>
-      </c>
+          <t>MEDIO</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>POSIBLE COMPRA</t>
+          <t>VIGILAR</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>AAPL</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>IA / Chips</t>
+          <t>Tecnología</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>490.33</v>
+        <v>290.93</v>
       </c>
       <c r="D11" t="n">
-        <v>76</v>
+        <v>64</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.88</v>
+        <v>-7.7</v>
       </c>
       <c r="F11" t="n">
-        <v>0.76</v>
+        <v>0.64</v>
       </c>
       <c r="G11" t="n">
-        <v>31.77</v>
+        <v>6.98</v>
       </c>
       <c r="H11" t="n">
-        <v>6.48</v>
+        <v>2.4</v>
       </c>
       <c r="I11" t="n">
-        <v>477.62</v>
+        <v>288.14</v>
       </c>
       <c r="J11" t="n">
-        <v>498.27</v>
+        <v>292.68</v>
       </c>
       <c r="K11" t="n">
-        <v>442.68</v>
+        <v>280.47</v>
       </c>
       <c r="L11" t="n">
-        <v>569.75</v>
+        <v>308.38</v>
       </c>
       <c r="M11" t="n">
-        <v>62.93</v>
+        <v>42.8</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>MEDIO</t>
+          <t>BAJO</t>
         </is>
       </c>
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>POSIBLE COMPRA</t>
+          <t>VIGILAR</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>HOOD</t>
+          <t>SLB</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Trading</t>
+          <t>Energía</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>85.04000000000001</v>
+        <v>54.7</v>
       </c>
       <c r="D12" t="n">
-        <v>76</v>
+        <v>64</v>
       </c>
       <c r="E12" t="n">
-        <v>-6.27</v>
+        <v>-2.78</v>
       </c>
       <c r="F12" t="n">
-        <v>0.72</v>
+        <v>0.43</v>
       </c>
       <c r="G12" t="n">
-        <v>5.48</v>
+        <v>1.86</v>
       </c>
       <c r="H12" t="n">
-        <v>6.45</v>
+        <v>3.39</v>
       </c>
       <c r="I12" t="n">
-        <v>82.84999999999999</v>
+        <v>53.96</v>
       </c>
       <c r="J12" t="n">
-        <v>86.41</v>
+        <v>55.16</v>
       </c>
       <c r="K12" t="n">
-        <v>76.81999999999999</v>
+        <v>51.92</v>
       </c>
       <c r="L12" t="n">
-        <v>98.75</v>
+        <v>59.34</v>
       </c>
       <c r="M12" t="n">
-        <v>57.44</v>
+        <v>44.12</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>MEDIO</t>
+          <t>BAJO</t>
         </is>
       </c>
       <c r="O12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>POSIBLE COMPRA</t>
+          <t>VIGILAR</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>UPST</t>
+          <t>SPY</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Fintech IA</t>
+          <t>ETF Mercado</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>31</v>
+        <v>727.22</v>
       </c>
       <c r="D13" t="n">
-        <v>76</v>
+        <v>60</v>
       </c>
       <c r="E13" t="n">
-        <v>-7.77</v>
+        <v>-4.26</v>
       </c>
       <c r="F13" t="n">
-        <v>0.84</v>
+        <v>0.65</v>
       </c>
       <c r="G13" t="n">
-        <v>2.06</v>
+        <v>8.07</v>
       </c>
       <c r="H13" t="n">
-        <v>6.63</v>
+        <v>1.11</v>
       </c>
       <c r="I13" t="n">
-        <v>30.18</v>
+        <v>724</v>
       </c>
       <c r="J13" t="n">
-        <v>31.51</v>
+        <v>729.24</v>
       </c>
       <c r="K13" t="n">
-        <v>27.92</v>
+        <v>715.11</v>
       </c>
       <c r="L13" t="n">
-        <v>36.14</v>
+        <v>747.41</v>
       </c>
       <c r="M13" t="n">
-        <v>59.75</v>
+        <v>45.18</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>MEDIO</t>
+          <t>BAJO</t>
         </is>
       </c>
       <c r="O13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>POSIBLE COMPRA</t>
+          <t>VIGILAR</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>AVGO</t>
+          <t>QQQ</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>IA / Chips</t>
+          <t>ETF Nasdaq</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>396.6</v>
+        <v>693.48</v>
       </c>
       <c r="D14" t="n">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="E14" t="n">
-        <v>-13.78</v>
+        <v>-7.06</v>
       </c>
       <c r="F14" t="n">
-        <v>1.28</v>
+        <v>0.92</v>
       </c>
       <c r="G14" t="n">
-        <v>23.33</v>
+        <v>13.64</v>
       </c>
       <c r="H14" t="n">
-        <v>5.88</v>
+        <v>1.97</v>
       </c>
       <c r="I14" t="n">
-        <v>387.27</v>
+        <v>688.02</v>
       </c>
       <c r="J14" t="n">
-        <v>402.43</v>
+        <v>696.89</v>
       </c>
       <c r="K14" t="n">
-        <v>361.6</v>
+        <v>673.02</v>
       </c>
       <c r="L14" t="n">
-        <v>454.93</v>
+        <v>727.59</v>
       </c>
       <c r="M14" t="n">
-        <v>43.8</v>
+        <v>46.67</v>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>MEDIO</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>🔥</t>
-        </is>
-      </c>
+          <t>BAJO</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>VIGILAR</t>
@@ -1269,102 +1241,102 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>SPY</t>
+          <t>UPST</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>ETF Mercado</t>
+          <t>Fintech IA</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>739.22</v>
+        <v>29.83</v>
       </c>
       <c r="D15" t="n">
-        <v>72</v>
+        <v>58</v>
       </c>
       <c r="E15" t="n">
-        <v>-2.55</v>
+        <v>-7.9</v>
       </c>
       <c r="F15" t="n">
-        <v>0.86</v>
+        <v>0.37</v>
       </c>
       <c r="G15" t="n">
-        <v>7.13</v>
+        <v>2.12</v>
       </c>
       <c r="H15" t="n">
-        <v>0.96</v>
+        <v>7.09</v>
       </c>
       <c r="I15" t="n">
-        <v>736.37</v>
+        <v>28.98</v>
       </c>
       <c r="J15" t="n">
-        <v>741</v>
+        <v>30.36</v>
       </c>
       <c r="K15" t="n">
-        <v>728.53</v>
+        <v>26.66</v>
       </c>
       <c r="L15" t="n">
-        <v>757.04</v>
+        <v>35.12</v>
       </c>
       <c r="M15" t="n">
-        <v>50.47</v>
+        <v>55.23</v>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>BAJO</t>
+          <t>MEDIO</t>
         </is>
       </c>
       <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>VIGILAR</t>
+          <t>NO COMPRAR</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>QQQ</t>
+          <t>NVDA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>ETF Nasdaq</t>
+          <t>IA / Chips</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>716.0700000000001</v>
+        <v>200.77</v>
       </c>
       <c r="D16" t="n">
-        <v>72</v>
+        <v>56</v>
       </c>
       <c r="E16" t="n">
-        <v>-3.59</v>
+        <v>-9.789999999999999</v>
       </c>
       <c r="F16" t="n">
-        <v>1.07</v>
+        <v>0.45</v>
       </c>
       <c r="G16" t="n">
-        <v>12.09</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="H16" t="n">
-        <v>1.69</v>
+        <v>4.22</v>
       </c>
       <c r="I16" t="n">
-        <v>711.23</v>
+        <v>197.38</v>
       </c>
       <c r="J16" t="n">
-        <v>719.09</v>
+        <v>202.89</v>
       </c>
       <c r="K16" t="n">
-        <v>697.9400000000001</v>
+        <v>188.07</v>
       </c>
       <c r="L16" t="n">
-        <v>746.29</v>
+        <v>221.94</v>
       </c>
       <c r="M16" t="n">
-        <v>54.96</v>
+        <v>36.09</v>
       </c>
       <c r="N16" t="inlineStr">
         <is>
@@ -1374,53 +1346,53 @@
       <c r="O16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>VIGILAR</t>
+          <t>NO COMPRAR</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>MU</t>
+          <t>AVGO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Memoria / Chips</t>
+          <t>IA / Chips</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>949.28</v>
+        <v>373.96</v>
       </c>
       <c r="D17" t="n">
-        <v>69</v>
+        <v>56</v>
       </c>
       <c r="E17" t="n">
-        <v>-8.33</v>
+        <v>-22.35</v>
       </c>
       <c r="F17" t="n">
-        <v>0.95</v>
+        <v>0.51</v>
       </c>
       <c r="G17" t="n">
-        <v>74.11</v>
+        <v>24.73</v>
       </c>
       <c r="H17" t="n">
-        <v>7.81</v>
+        <v>6.61</v>
       </c>
       <c r="I17" t="n">
-        <v>919.64</v>
+        <v>364.07</v>
       </c>
       <c r="J17" t="n">
-        <v>967.8099999999999</v>
+        <v>380.14</v>
       </c>
       <c r="K17" t="n">
-        <v>838.12</v>
+        <v>336.86</v>
       </c>
       <c r="L17" t="n">
-        <v>1134.55</v>
+        <v>435.79</v>
       </c>
       <c r="M17" t="n">
-        <v>68.31999999999999</v>
+        <v>41.05</v>
       </c>
       <c r="N17" t="inlineStr">
         <is>
@@ -1430,165 +1402,165 @@
       <c r="O17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>VIGILAR</t>
+          <t>NO COMPRAR</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>AI</t>
+          <t>AMZN</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>IA</t>
+          <t>Tecnología</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>10.6</v>
+        <v>243.21</v>
       </c>
       <c r="D18" t="n">
-        <v>69</v>
+        <v>56</v>
       </c>
       <c r="E18" t="n">
-        <v>-9.789999999999999</v>
+        <v>-5.19</v>
       </c>
       <c r="F18" t="n">
-        <v>0.82</v>
+        <v>0.42</v>
       </c>
       <c r="G18" t="n">
-        <v>0.71</v>
+        <v>7.24</v>
       </c>
       <c r="H18" t="n">
-        <v>6.71</v>
+        <v>2.98</v>
       </c>
       <c r="I18" t="n">
-        <v>10.32</v>
+        <v>240.31</v>
       </c>
       <c r="J18" t="n">
-        <v>10.78</v>
+        <v>245.02</v>
       </c>
       <c r="K18" t="n">
-        <v>9.529999999999999</v>
+        <v>232.35</v>
       </c>
       <c r="L18" t="n">
-        <v>12.38</v>
+        <v>261.31</v>
       </c>
       <c r="M18" t="n">
-        <v>70.23999999999999</v>
+        <v>36.41</v>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>MEDIO</t>
+          <t>BAJO</t>
         </is>
       </c>
       <c r="O18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>VIGILAR</t>
+          <t>NO COMPRAR</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>SOFI</t>
+          <t>GOOGL</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Fintech</t>
+          <t>Tecnología</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>16.5</v>
+        <v>359.48</v>
       </c>
       <c r="D19" t="n">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="E19" t="n">
-        <v>-11.19</v>
+        <v>-0.6</v>
       </c>
       <c r="F19" t="n">
-        <v>1.08</v>
+        <v>0.39</v>
       </c>
       <c r="G19" t="n">
-        <v>0.97</v>
+        <v>9.81</v>
       </c>
       <c r="H19" t="n">
-        <v>5.89</v>
+        <v>2.73</v>
       </c>
       <c r="I19" t="n">
-        <v>16.11</v>
+        <v>355.55</v>
       </c>
       <c r="J19" t="n">
-        <v>16.74</v>
+        <v>361.93</v>
       </c>
       <c r="K19" t="n">
-        <v>15.04</v>
+        <v>344.76</v>
       </c>
       <c r="L19" t="n">
-        <v>18.93</v>
+        <v>384</v>
       </c>
       <c r="M19" t="n">
-        <v>54.98</v>
+        <v>30.38</v>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>MEDIO</t>
+          <t>BAJO</t>
         </is>
       </c>
       <c r="O19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>VIGILAR</t>
+          <t>NO COMPRAR</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>NVDA</t>
+          <t>CVX</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>IA / Chips</t>
+          <t>Energía</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>208.64</v>
+        <v>186.72</v>
       </c>
       <c r="D20" t="n">
         <v>56</v>
       </c>
       <c r="E20" t="n">
-        <v>-6.9</v>
+        <v>-0.44</v>
       </c>
       <c r="F20" t="n">
-        <v>0.77</v>
+        <v>0.33</v>
       </c>
       <c r="G20" t="n">
-        <v>8.17</v>
+        <v>4.12</v>
       </c>
       <c r="H20" t="n">
-        <v>3.92</v>
+        <v>2.21</v>
       </c>
       <c r="I20" t="n">
-        <v>205.37</v>
+        <v>185.07</v>
       </c>
       <c r="J20" t="n">
-        <v>210.68</v>
+        <v>187.75</v>
       </c>
       <c r="K20" t="n">
-        <v>196.39</v>
+        <v>180.54</v>
       </c>
       <c r="L20" t="n">
-        <v>229.06</v>
+        <v>197.03</v>
       </c>
       <c r="M20" t="n">
-        <v>39.55</v>
+        <v>33.01</v>
       </c>
       <c r="N20" t="inlineStr">
         <is>
@@ -1605,7 +1577,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>AMZN</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1614,37 +1586,37 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>245.22</v>
+        <v>401.46</v>
       </c>
       <c r="D21" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E21" t="n">
-        <v>-6.14</v>
+        <v>-9.029999999999999</v>
       </c>
       <c r="F21" t="n">
-        <v>0.82</v>
+        <v>0.39</v>
       </c>
       <c r="G21" t="n">
-        <v>7.34</v>
+        <v>12.88</v>
       </c>
       <c r="H21" t="n">
-        <v>2.99</v>
+        <v>3.21</v>
       </c>
       <c r="I21" t="n">
-        <v>242.28</v>
+        <v>396.31</v>
       </c>
       <c r="J21" t="n">
-        <v>247.05</v>
+        <v>404.68</v>
       </c>
       <c r="K21" t="n">
-        <v>234.21</v>
+        <v>382.15</v>
       </c>
       <c r="L21" t="n">
-        <v>263.57</v>
+        <v>433.65</v>
       </c>
       <c r="M21" t="n">
-        <v>34.37</v>
+        <v>43.7</v>
       </c>
       <c r="N21" t="inlineStr">
         <is>
@@ -1661,46 +1633,46 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>GOOGL</t>
+          <t>TSLA</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Tecnología</t>
+          <t>Autos / Tech</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>363.31</v>
+        <v>388.64</v>
       </c>
       <c r="D22" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.47</v>
+        <v>-8.279999999999999</v>
       </c>
       <c r="F22" t="n">
-        <v>0.88</v>
+        <v>0.61</v>
       </c>
       <c r="G22" t="n">
-        <v>9.69</v>
+        <v>16.45</v>
       </c>
       <c r="H22" t="n">
-        <v>2.67</v>
+        <v>4.23</v>
       </c>
       <c r="I22" t="n">
-        <v>359.43</v>
+        <v>382.06</v>
       </c>
       <c r="J22" t="n">
-        <v>365.73</v>
+        <v>392.75</v>
       </c>
       <c r="K22" t="n">
-        <v>348.77</v>
+        <v>363.97</v>
       </c>
       <c r="L22" t="n">
-        <v>387.54</v>
+        <v>429.76</v>
       </c>
       <c r="M22" t="n">
-        <v>28.15</v>
+        <v>44.59</v>
       </c>
       <c r="N22" t="inlineStr">
         <is>
@@ -1717,50 +1689,50 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>SOFI</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Tecnología</t>
+          <t>Fintech</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>411.74</v>
+        <v>15.8</v>
       </c>
       <c r="D23" t="n">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="E23" t="n">
-        <v>-10.59</v>
+        <v>-10.94</v>
       </c>
       <c r="F23" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.52</v>
       </c>
       <c r="G23" t="n">
-        <v>13.26</v>
+        <v>1.01</v>
       </c>
       <c r="H23" t="n">
-        <v>3.22</v>
+        <v>6.4</v>
       </c>
       <c r="I23" t="n">
-        <v>406.44</v>
+        <v>15.4</v>
       </c>
       <c r="J23" t="n">
-        <v>415.06</v>
+        <v>16.05</v>
       </c>
       <c r="K23" t="n">
-        <v>391.85</v>
+        <v>14.28</v>
       </c>
       <c r="L23" t="n">
-        <v>444.89</v>
+        <v>18.33</v>
       </c>
       <c r="M23" t="n">
-        <v>45.28</v>
+        <v>53.5</v>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>BAJO</t>
+          <t>MEDIO</t>
         </is>
       </c>
       <c r="O23" t="inlineStr"/>
@@ -1773,46 +1745,46 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>TSLA</t>
+          <t>XOM</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Autos / Tech</t>
+          <t>Energía</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>408.95</v>
+        <v>148.78</v>
       </c>
       <c r="D24" t="n">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.67</v>
+        <v>-0.52</v>
       </c>
       <c r="F24" t="n">
-        <v>0.98</v>
+        <v>0.3</v>
       </c>
       <c r="G24" t="n">
-        <v>15.44</v>
+        <v>4</v>
       </c>
       <c r="H24" t="n">
-        <v>3.78</v>
+        <v>2.69</v>
       </c>
       <c r="I24" t="n">
-        <v>402.77</v>
+        <v>147.18</v>
       </c>
       <c r="J24" t="n">
-        <v>412.81</v>
+        <v>149.78</v>
       </c>
       <c r="K24" t="n">
-        <v>385.79</v>
+        <v>142.77</v>
       </c>
       <c r="L24" t="n">
-        <v>447.56</v>
+        <v>158.79</v>
       </c>
       <c r="M24" t="n">
-        <v>49.6</v>
+        <v>28.46</v>
       </c>
       <c r="N24" t="inlineStr">
         <is>
@@ -1829,7 +1801,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>XOM</t>
+          <t>OXY</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1838,37 +1810,37 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>151.75</v>
+        <v>56.06</v>
       </c>
       <c r="D25" t="n">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="E25" t="n">
-        <v>1.59</v>
+        <v>-5.12</v>
       </c>
       <c r="F25" t="n">
-        <v>0.83</v>
+        <v>0.43</v>
       </c>
       <c r="G25" t="n">
-        <v>3.98</v>
+        <v>1.82</v>
       </c>
       <c r="H25" t="n">
-        <v>2.63</v>
+        <v>3.25</v>
       </c>
       <c r="I25" t="n">
-        <v>150.16</v>
+        <v>55.34</v>
       </c>
       <c r="J25" t="n">
-        <v>152.75</v>
+        <v>56.52</v>
       </c>
       <c r="K25" t="n">
-        <v>145.77</v>
+        <v>53.33</v>
       </c>
       <c r="L25" t="n">
-        <v>161.71</v>
+        <v>60.62</v>
       </c>
       <c r="M25" t="n">
-        <v>35.93</v>
+        <v>31.63</v>
       </c>
       <c r="N25" t="inlineStr">
         <is>
@@ -1885,46 +1857,46 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>OXY</t>
+          <t>META</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Energía</t>
+          <t>Tecnología</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>57.48</v>
+        <v>585.89</v>
       </c>
       <c r="D26" t="n">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="E26" t="n">
-        <v>-2.44</v>
+        <v>-1.96</v>
       </c>
       <c r="F26" t="n">
-        <v>0.79</v>
+        <v>0.35</v>
       </c>
       <c r="G26" t="n">
-        <v>1.79</v>
+        <v>18.9</v>
       </c>
       <c r="H26" t="n">
-        <v>3.12</v>
+        <v>3.23</v>
       </c>
       <c r="I26" t="n">
-        <v>56.76</v>
+        <v>578.33</v>
       </c>
       <c r="J26" t="n">
-        <v>57.93</v>
+        <v>590.61</v>
       </c>
       <c r="K26" t="n">
-        <v>54.79</v>
+        <v>557.54</v>
       </c>
       <c r="L26" t="n">
-        <v>61.97</v>
+        <v>633.13</v>
       </c>
       <c r="M26" t="n">
-        <v>40.9</v>
+        <v>44.15</v>
       </c>
       <c r="N26" t="inlineStr">
         <is>
@@ -1941,46 +1913,46 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>PLTR</t>
+          <t>SOUN</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>IA / Software</t>
+          <t>IA</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>136.47</v>
+        <v>6.86</v>
       </c>
       <c r="D27" t="n">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="E27" t="n">
-        <v>-15.05</v>
+        <v>-22.17</v>
       </c>
       <c r="F27" t="n">
-        <v>0.66</v>
+        <v>0.47</v>
       </c>
       <c r="G27" t="n">
-        <v>7.14</v>
+        <v>0.54</v>
       </c>
       <c r="H27" t="n">
-        <v>5.23</v>
+        <v>7.83</v>
       </c>
       <c r="I27" t="n">
-        <v>133.62</v>
+        <v>6.65</v>
       </c>
       <c r="J27" t="n">
-        <v>138.25</v>
+        <v>7</v>
       </c>
       <c r="K27" t="n">
-        <v>125.76</v>
+        <v>6.06</v>
       </c>
       <c r="L27" t="n">
-        <v>154.31</v>
+        <v>8.210000000000001</v>
       </c>
       <c r="M27" t="n">
-        <v>51.08</v>
+        <v>30.79</v>
       </c>
       <c r="N27" t="inlineStr">
         <is>
@@ -1997,50 +1969,50 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>META</t>
+          <t>PLTR</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Tecnología</t>
+          <t>IA / Software</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>585.39</v>
+        <v>128.88</v>
       </c>
       <c r="D28" t="n">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="E28" t="n">
-        <v>-2.51</v>
+        <v>-15.31</v>
       </c>
       <c r="F28" t="n">
-        <v>1.06</v>
+        <v>0.42</v>
       </c>
       <c r="G28" t="n">
-        <v>18.96</v>
+        <v>7.45</v>
       </c>
       <c r="H28" t="n">
-        <v>3.24</v>
+        <v>5.78</v>
       </c>
       <c r="I28" t="n">
-        <v>577.8099999999999</v>
+        <v>125.89</v>
       </c>
       <c r="J28" t="n">
-        <v>590.13</v>
+        <v>130.74</v>
       </c>
       <c r="K28" t="n">
-        <v>556.95</v>
+        <v>117.7</v>
       </c>
       <c r="L28" t="n">
-        <v>632.79</v>
+        <v>147.51</v>
       </c>
       <c r="M28" t="n">
-        <v>41.45</v>
+        <v>45.36</v>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>BAJO</t>
+          <t>MEDIO</t>
         </is>
       </c>
       <c r="O28" t="inlineStr"/>
@@ -2053,50 +2025,50 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>SOUN</t>
+          <t>PYPL</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>IA</t>
+          <t>Pagos</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>7.49</v>
+        <v>41.26</v>
       </c>
       <c r="D29" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E29" t="n">
-        <v>-19.03</v>
+        <v>-7.05</v>
       </c>
       <c r="F29" t="n">
-        <v>0.85</v>
+        <v>0.43</v>
       </c>
       <c r="G29" t="n">
-        <v>0.51</v>
+        <v>1.17</v>
       </c>
       <c r="H29" t="n">
-        <v>6.85</v>
+        <v>2.84</v>
       </c>
       <c r="I29" t="n">
-        <v>7.28</v>
+        <v>40.79</v>
       </c>
       <c r="J29" t="n">
-        <v>7.62</v>
+        <v>41.55</v>
       </c>
       <c r="K29" t="n">
-        <v>6.72</v>
+        <v>39.5</v>
       </c>
       <c r="L29" t="n">
-        <v>8.77</v>
+        <v>44.18</v>
       </c>
       <c r="M29" t="n">
-        <v>38.06</v>
+        <v>32.46</v>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>MEDIO</t>
+          <t>BAJO</t>
         </is>
       </c>
       <c r="O29" t="inlineStr"/>
@@ -2109,50 +2081,50 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>PYPL</t>
+          <t>COIN</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Pagos</t>
+          <t>Cripto / Trading</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>41.26</v>
+        <v>151.5</v>
       </c>
       <c r="D30" t="n">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="E30" t="n">
-        <v>-8.4</v>
+        <v>-12.93</v>
       </c>
       <c r="F30" t="n">
-        <v>1.01</v>
+        <v>0.45</v>
       </c>
       <c r="G30" t="n">
-        <v>1.17</v>
+        <v>10.63</v>
       </c>
       <c r="H30" t="n">
-        <v>2.85</v>
+        <v>7.02</v>
       </c>
       <c r="I30" t="n">
-        <v>40.79</v>
+        <v>147.25</v>
       </c>
       <c r="J30" t="n">
-        <v>41.55</v>
+        <v>154.16</v>
       </c>
       <c r="K30" t="n">
-        <v>39.5</v>
+        <v>135.55</v>
       </c>
       <c r="L30" t="n">
-        <v>44.2</v>
+        <v>178.08</v>
       </c>
       <c r="M30" t="n">
-        <v>30.08</v>
+        <v>28.65</v>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>BAJO</t>
+          <t>MEDIO</t>
         </is>
       </c>
       <c r="O30" t="inlineStr"/>
@@ -2165,56 +2137,56 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>COIN</t>
+          <t>MU</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Cripto / Trading</t>
+          <t>Memoria / Chips</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>162.11</v>
+        <v>871.63</v>
       </c>
       <c r="D31" t="n">
-        <v>28</v>
+        <v>72</v>
       </c>
       <c r="E31" t="n">
-        <v>-11.23</v>
+        <v>-18.09</v>
       </c>
       <c r="F31" t="n">
-        <v>0.89</v>
+        <v>0.64</v>
       </c>
       <c r="G31" t="n">
-        <v>10.37</v>
+        <v>77.42</v>
       </c>
       <c r="H31" t="n">
-        <v>6.39</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="I31" t="n">
-        <v>157.96</v>
+        <v>840.66</v>
       </c>
       <c r="J31" t="n">
-        <v>164.7</v>
+        <v>890.99</v>
       </c>
       <c r="K31" t="n">
-        <v>146.56</v>
+        <v>755.5</v>
       </c>
       <c r="L31" t="n">
-        <v>188.03</v>
+        <v>1065.18</v>
       </c>
       <c r="M31" t="n">
-        <v>35.09</v>
+        <v>60.92</v>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>MEDIO</t>
+          <t>ALTO</t>
         </is>
       </c>
       <c r="O31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>NO COMPRAR</t>
+          <t>VIGILAR</t>
         </is>
       </c>
     </row>
@@ -2230,37 +2202,37 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>346.39</v>
+        <v>305.41</v>
       </c>
       <c r="D32" t="n">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="E32" t="n">
-        <v>-15.28</v>
+        <v>-24.16</v>
       </c>
       <c r="F32" t="n">
-        <v>0.72</v>
+        <v>0.53</v>
       </c>
       <c r="G32" t="n">
-        <v>37.07</v>
+        <v>39.76</v>
       </c>
       <c r="H32" t="n">
-        <v>10.7</v>
+        <v>13.02</v>
       </c>
       <c r="I32" t="n">
-        <v>331.56</v>
+        <v>289.51</v>
       </c>
       <c r="J32" t="n">
-        <v>355.66</v>
+        <v>315.35</v>
       </c>
       <c r="K32" t="n">
-        <v>290.78</v>
+        <v>245.77</v>
       </c>
       <c r="L32" t="n">
-        <v>439.08</v>
+        <v>404.8</v>
       </c>
       <c r="M32" t="n">
-        <v>70.62</v>
+        <v>61.71</v>
       </c>
       <c r="N32" t="inlineStr">
         <is>
@@ -2277,7 +2249,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>INTC</t>
+          <t>QCOM</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2286,37 +2258,37 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>110.27</v>
+        <v>196.17</v>
       </c>
       <c r="D33" t="n">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="E33" t="n">
-        <v>0.86</v>
+        <v>-18.25</v>
       </c>
       <c r="F33" t="n">
-        <v>1.05</v>
+        <v>0.67</v>
       </c>
       <c r="G33" t="n">
-        <v>8.960000000000001</v>
+        <v>19.56</v>
       </c>
       <c r="H33" t="n">
-        <v>8.130000000000001</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="I33" t="n">
-        <v>106.68</v>
+        <v>188.35</v>
       </c>
       <c r="J33" t="n">
-        <v>112.51</v>
+        <v>201.06</v>
       </c>
       <c r="K33" t="n">
-        <v>96.81999999999999</v>
+        <v>166.83</v>
       </c>
       <c r="L33" t="n">
-        <v>132.68</v>
+        <v>245.07</v>
       </c>
       <c r="M33" t="n">
-        <v>51.71</v>
+        <v>50.35</v>
       </c>
       <c r="N33" t="inlineStr">
         <is>
@@ -2342,37 +2314,37 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>43.99</v>
+        <v>38.83</v>
       </c>
       <c r="D34" t="n">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="E34" t="n">
-        <v>-6.16</v>
+        <v>-22.6</v>
       </c>
       <c r="F34" t="n">
-        <v>0.76</v>
+        <v>0.52</v>
       </c>
       <c r="G34" t="n">
-        <v>3.56</v>
+        <v>3.86</v>
       </c>
       <c r="H34" t="n">
-        <v>8.09</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="I34" t="n">
-        <v>42.57</v>
+        <v>37.28</v>
       </c>
       <c r="J34" t="n">
-        <v>44.88</v>
+        <v>39.8</v>
       </c>
       <c r="K34" t="n">
-        <v>38.65</v>
+        <v>33.03</v>
       </c>
       <c r="L34" t="n">
-        <v>52.89</v>
+        <v>48.49</v>
       </c>
       <c r="M34" t="n">
-        <v>71.34999999999999</v>
+        <v>61.6</v>
       </c>
       <c r="N34" t="inlineStr">
         <is>
@@ -2389,46 +2361,46 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>QCOM</t>
+          <t>IONQ</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Chips</t>
+          <t>Computación cuántica</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>217.77</v>
+        <v>54.48</v>
       </c>
       <c r="D35" t="n">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="E35" t="n">
-        <v>-4.55</v>
+        <v>-23.7</v>
       </c>
       <c r="F35" t="n">
-        <v>0.65</v>
+        <v>0.57</v>
       </c>
       <c r="G35" t="n">
-        <v>18.78</v>
+        <v>6.64</v>
       </c>
       <c r="H35" t="n">
-        <v>8.619999999999999</v>
+        <v>12.19</v>
       </c>
       <c r="I35" t="n">
-        <v>210.26</v>
+        <v>51.82</v>
       </c>
       <c r="J35" t="n">
-        <v>222.46</v>
+        <v>56.14</v>
       </c>
       <c r="K35" t="n">
-        <v>189.6</v>
+        <v>44.52</v>
       </c>
       <c r="L35" t="n">
-        <v>264.71</v>
+        <v>71.08</v>
       </c>
       <c r="M35" t="n">
-        <v>54.33</v>
+        <v>55.25</v>
       </c>
       <c r="N35" t="inlineStr">
         <is>
@@ -2438,53 +2410,53 @@
       <c r="O35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>VIGILAR</t>
+          <t>NO COMPRAR</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>IONQ</t>
+          <t>INTC</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Computación cuántica</t>
+          <t>Chips</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>62.8</v>
+        <v>101.56</v>
       </c>
       <c r="D36" t="n">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="E36" t="n">
-        <v>-9.35</v>
+        <v>-5.9</v>
       </c>
       <c r="F36" t="n">
-        <v>0.82</v>
+        <v>0.57</v>
       </c>
       <c r="G36" t="n">
-        <v>6.23</v>
+        <v>9.109999999999999</v>
       </c>
       <c r="H36" t="n">
-        <v>9.92</v>
+        <v>8.970000000000001</v>
       </c>
       <c r="I36" t="n">
-        <v>60.31</v>
+        <v>97.92</v>
       </c>
       <c r="J36" t="n">
-        <v>64.36</v>
+        <v>103.84</v>
       </c>
       <c r="K36" t="n">
-        <v>53.45</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="L36" t="n">
-        <v>78.38</v>
+        <v>124.33</v>
       </c>
       <c r="M36" t="n">
-        <v>63.47</v>
+        <v>43.14</v>
       </c>
       <c r="N36" t="inlineStr">
         <is>
@@ -2494,7 +2466,7 @@
       <c r="O36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>VIGILAR</t>
+          <t>NO COMPRAR</t>
         </is>
       </c>
     </row>
@@ -2510,37 +2482,37 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>113.65</v>
+        <v>102.84</v>
       </c>
       <c r="D37" t="n">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="E37" t="n">
-        <v>-7.14</v>
+        <v>-16.61</v>
       </c>
       <c r="F37" t="n">
-        <v>0.47</v>
+        <v>0.49</v>
       </c>
       <c r="G37" t="n">
-        <v>11.96</v>
+        <v>12.05</v>
       </c>
       <c r="H37" t="n">
-        <v>10.52</v>
+        <v>11.72</v>
       </c>
       <c r="I37" t="n">
-        <v>108.87</v>
+        <v>98.02</v>
       </c>
       <c r="J37" t="n">
-        <v>116.64</v>
+        <v>105.85</v>
       </c>
       <c r="K37" t="n">
-        <v>95.70999999999999</v>
+        <v>84.77</v>
       </c>
       <c r="L37" t="n">
-        <v>143.54</v>
+        <v>132.96</v>
       </c>
       <c r="M37" t="n">
-        <v>41.29</v>
+        <v>38.62</v>
       </c>
       <c r="N37" t="inlineStr">
         <is>

--- a/analisis_acciones.xlsx
+++ b/analisis_acciones.xlsx
@@ -501,46 +501,46 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ASML</t>
+          <t>HOOD</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Chips</t>
+          <t>Trading</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1702.85</v>
+        <v>88.04000000000001</v>
       </c>
       <c r="D2" t="n">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.15</v>
+        <v>6.27</v>
       </c>
       <c r="F2" t="n">
-        <v>1.15</v>
+        <v>0.99</v>
       </c>
       <c r="G2" t="n">
-        <v>77.78</v>
+        <v>6.22</v>
       </c>
       <c r="H2" t="n">
-        <v>4.57</v>
+        <v>7.06</v>
       </c>
       <c r="I2" t="n">
-        <v>1671.74</v>
+        <v>85.56</v>
       </c>
       <c r="J2" t="n">
-        <v>1722.29</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="K2" t="n">
-        <v>1586.18</v>
+        <v>78.72</v>
       </c>
       <c r="L2" t="n">
-        <v>1897.3</v>
+        <v>103.59</v>
       </c>
       <c r="M2" t="n">
-        <v>69.09999999999999</v>
+        <v>61.37</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -549,7 +549,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -561,50 +561,50 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AMAT</t>
+          <t>ASML</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Equipos chips</t>
+          <t>Chips</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>475.28</v>
+        <v>1743.57</v>
       </c>
       <c r="D3" t="n">
-        <v>86</v>
+        <v>95</v>
       </c>
       <c r="E3" t="n">
-        <v>-3.01</v>
+        <v>1</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5600000000000001</v>
+        <v>1.05</v>
       </c>
       <c r="G3" t="n">
-        <v>26.88</v>
+        <v>78.88</v>
       </c>
       <c r="H3" t="n">
-        <v>5.66</v>
+        <v>4.52</v>
       </c>
       <c r="I3" t="n">
-        <v>464.53</v>
+        <v>1712.02</v>
       </c>
       <c r="J3" t="n">
-        <v>482</v>
+        <v>1763.29</v>
       </c>
       <c r="K3" t="n">
-        <v>434.96</v>
+        <v>1625.25</v>
       </c>
       <c r="L3" t="n">
-        <v>542.48</v>
+        <v>1940.77</v>
       </c>
       <c r="M3" t="n">
-        <v>66.14</v>
+        <v>67.17</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>MEDIO</t>
+          <t>BAJO</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -621,50 +621,50 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>KLAC</t>
+          <t>CVX</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Equipos chips</t>
+          <t>Energía</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2029.66</v>
+        <v>191.62</v>
       </c>
       <c r="D4" t="n">
-        <v>86</v>
+        <v>95</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.76</v>
+        <v>1.01</v>
       </c>
       <c r="F4" t="n">
-        <v>0.61</v>
+        <v>0.46</v>
       </c>
       <c r="G4" t="n">
-        <v>118.43</v>
+        <v>4</v>
       </c>
       <c r="H4" t="n">
-        <v>5.83</v>
+        <v>2.09</v>
       </c>
       <c r="I4" t="n">
-        <v>1982.28</v>
+        <v>190.02</v>
       </c>
       <c r="J4" t="n">
-        <v>2059.26</v>
+        <v>192.62</v>
       </c>
       <c r="K4" t="n">
-        <v>1852.01</v>
+        <v>185.62</v>
       </c>
       <c r="L4" t="n">
-        <v>2325.72</v>
+        <v>201.61</v>
       </c>
       <c r="M4" t="n">
-        <v>64.05</v>
+        <v>50.49</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>MEDIO</t>
+          <t>BAJO</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -681,53 +681,57 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>KLAC</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Chips</t>
+          <t>Equipos chips</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>409.37</v>
+        <v>2152.17</v>
       </c>
       <c r="D5" t="n">
-        <v>76</v>
+        <v>94</v>
       </c>
       <c r="E5" t="n">
-        <v>-8.35</v>
+        <v>1.27</v>
       </c>
       <c r="F5" t="n">
-        <v>0.58</v>
+        <v>0.82</v>
       </c>
       <c r="G5" t="n">
-        <v>17.68</v>
+        <v>126.82</v>
       </c>
       <c r="H5" t="n">
-        <v>4.32</v>
+        <v>5.89</v>
       </c>
       <c r="I5" t="n">
-        <v>402.3</v>
+        <v>2101.44</v>
       </c>
       <c r="J5" t="n">
-        <v>413.79</v>
+        <v>2183.87</v>
       </c>
       <c r="K5" t="n">
-        <v>382.86</v>
+        <v>1961.94</v>
       </c>
       <c r="L5" t="n">
-        <v>453.56</v>
+        <v>2469.22</v>
       </c>
       <c r="M5" t="n">
-        <v>55.62</v>
+        <v>67.81</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>BAJO</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr"/>
+          <t>MEDIO</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>🔥</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>POSIBLE COMPRA</t>
@@ -737,7 +741,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>LRCX</t>
+          <t>AMAT</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -746,44 +750,48 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>312.32</v>
+        <v>501.48</v>
       </c>
       <c r="D6" t="n">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="E6" t="n">
-        <v>-6.61</v>
+        <v>0.14</v>
       </c>
       <c r="F6" t="n">
-        <v>0.64</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="G6" t="n">
-        <v>18.71</v>
+        <v>28.8</v>
       </c>
       <c r="H6" t="n">
-        <v>5.99</v>
+        <v>5.74</v>
       </c>
       <c r="I6" t="n">
-        <v>304.83</v>
+        <v>489.96</v>
       </c>
       <c r="J6" t="n">
-        <v>316.99</v>
+        <v>508.68</v>
       </c>
       <c r="K6" t="n">
-        <v>284.25</v>
+        <v>458.29</v>
       </c>
       <c r="L6" t="n">
-        <v>359.09</v>
+        <v>573.47</v>
       </c>
       <c r="M6" t="n">
-        <v>62.52</v>
+        <v>70.22</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
           <t>MEDIO</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr"/>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>🔥</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>POSIBLE COMPRA</t>
@@ -802,44 +810,48 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>10.19</v>
+        <v>10.99</v>
       </c>
       <c r="D7" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E7" t="n">
-        <v>-8.859999999999999</v>
+        <v>2.61</v>
       </c>
       <c r="F7" t="n">
-        <v>0.58</v>
+        <v>0.47</v>
       </c>
       <c r="G7" t="n">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="H7" t="n">
-        <v>7.39</v>
+        <v>7</v>
       </c>
       <c r="I7" t="n">
-        <v>9.890000000000001</v>
+        <v>10.68</v>
       </c>
       <c r="J7" t="n">
-        <v>10.38</v>
+        <v>11.18</v>
       </c>
       <c r="K7" t="n">
-        <v>9.06</v>
+        <v>9.84</v>
       </c>
       <c r="L7" t="n">
-        <v>12.07</v>
+        <v>12.91</v>
       </c>
       <c r="M7" t="n">
-        <v>63.88</v>
+        <v>69.3</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
           <t>MEDIO</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr"/>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>🔥</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>POSIBLE COMPRA</t>
@@ -849,102 +861,102 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>TSM</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>IA / Chips</t>
+          <t>Chips</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>447.5</v>
+        <v>413.03</v>
       </c>
       <c r="D8" t="n">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="E8" t="n">
-        <v>-14.2</v>
+        <v>-5.42</v>
       </c>
       <c r="F8" t="n">
-        <v>0.54</v>
+        <v>0.59</v>
       </c>
       <c r="G8" t="n">
-        <v>33.38</v>
+        <v>18.38</v>
       </c>
       <c r="H8" t="n">
-        <v>7.46</v>
+        <v>4.45</v>
       </c>
       <c r="I8" t="n">
-        <v>434.15</v>
+        <v>405.68</v>
       </c>
       <c r="J8" t="n">
-        <v>455.84</v>
+        <v>417.62</v>
       </c>
       <c r="K8" t="n">
-        <v>397.44</v>
+        <v>385.46</v>
       </c>
       <c r="L8" t="n">
-        <v>530.9400000000001</v>
+        <v>458.98</v>
       </c>
       <c r="M8" t="n">
-        <v>55.5</v>
+        <v>54.11</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>MEDIO</t>
+          <t>BAJO</t>
         </is>
       </c>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>VIGILAR</t>
+          <t>POSIBLE COMPRA</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>HOOD</t>
+          <t>LRCX</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Trading</t>
+          <t>Equipos chips</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>80.20999999999999</v>
+        <v>325.77</v>
       </c>
       <c r="D9" t="n">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="E9" t="n">
-        <v>-9.02</v>
+        <v>-5.22</v>
       </c>
       <c r="F9" t="n">
-        <v>0.58</v>
+        <v>0.78</v>
       </c>
       <c r="G9" t="n">
-        <v>5.77</v>
+        <v>19.72</v>
       </c>
       <c r="H9" t="n">
-        <v>7.19</v>
+        <v>6.05</v>
       </c>
       <c r="I9" t="n">
-        <v>77.90000000000001</v>
+        <v>317.89</v>
       </c>
       <c r="J9" t="n">
-        <v>81.65000000000001</v>
+        <v>330.7</v>
       </c>
       <c r="K9" t="n">
-        <v>71.56</v>
+        <v>296.2</v>
       </c>
       <c r="L9" t="n">
-        <v>94.62</v>
+        <v>375.07</v>
       </c>
       <c r="M9" t="n">
-        <v>55.51</v>
+        <v>63.08</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
@@ -954,60 +966,64 @@
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>VIGILAR</t>
+          <t>POSIBLE COMPRA</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SOXX</t>
+          <t>UPST</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ETF Chips</t>
+          <t>Fintech IA</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>531.46</v>
+        <v>30.9</v>
       </c>
       <c r="D10" t="n">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="E10" t="n">
-        <v>-12.16</v>
+        <v>2.01</v>
       </c>
       <c r="F10" t="n">
-        <v>1.07</v>
+        <v>0.33</v>
       </c>
       <c r="G10" t="n">
-        <v>31.13</v>
+        <v>2.09</v>
       </c>
       <c r="H10" t="n">
-        <v>5.86</v>
+        <v>6.75</v>
       </c>
       <c r="I10" t="n">
-        <v>519.01</v>
+        <v>30.07</v>
       </c>
       <c r="J10" t="n">
-        <v>539.24</v>
+        <v>31.42</v>
       </c>
       <c r="K10" t="n">
-        <v>484.77</v>
+        <v>27.77</v>
       </c>
       <c r="L10" t="n">
-        <v>609.28</v>
+        <v>36.12</v>
       </c>
       <c r="M10" t="n">
-        <v>56.21</v>
+        <v>56.86</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
           <t>MEDIO</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr"/>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>🔥</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>VIGILAR</t>
@@ -1017,46 +1033,46 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>OXY</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Tecnología</t>
+          <t>Energía</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>290.93</v>
+        <v>58.31</v>
       </c>
       <c r="D11" t="n">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="E11" t="n">
-        <v>-7.7</v>
+        <v>-2.23</v>
       </c>
       <c r="F11" t="n">
-        <v>0.64</v>
+        <v>0.38</v>
       </c>
       <c r="G11" t="n">
-        <v>6.98</v>
+        <v>1.79</v>
       </c>
       <c r="H11" t="n">
-        <v>2.4</v>
+        <v>3.08</v>
       </c>
       <c r="I11" t="n">
-        <v>288.14</v>
+        <v>57.59</v>
       </c>
       <c r="J11" t="n">
-        <v>292.68</v>
+        <v>58.76</v>
       </c>
       <c r="K11" t="n">
-        <v>280.47</v>
+        <v>55.62</v>
       </c>
       <c r="L11" t="n">
-        <v>308.38</v>
+        <v>62.8</v>
       </c>
       <c r="M11" t="n">
-        <v>42.8</v>
+        <v>47.68</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
@@ -1082,37 +1098,37 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>54.7</v>
+        <v>56.19</v>
       </c>
       <c r="D12" t="n">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.78</v>
+        <v>-1.15</v>
       </c>
       <c r="F12" t="n">
-        <v>0.43</v>
+        <v>0.48</v>
       </c>
       <c r="G12" t="n">
-        <v>1.86</v>
+        <v>1.9</v>
       </c>
       <c r="H12" t="n">
-        <v>3.39</v>
+        <v>3.38</v>
       </c>
       <c r="I12" t="n">
-        <v>53.96</v>
+        <v>55.43</v>
       </c>
       <c r="J12" t="n">
-        <v>55.16</v>
+        <v>56.67</v>
       </c>
       <c r="K12" t="n">
-        <v>51.92</v>
+        <v>53.34</v>
       </c>
       <c r="L12" t="n">
-        <v>59.34</v>
+        <v>60.95</v>
       </c>
       <c r="M12" t="n">
-        <v>44.12</v>
+        <v>47.15</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
@@ -1129,50 +1145,50 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>SPY</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>ETF Mercado</t>
+          <t>IA / Chips</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>727.22</v>
+        <v>453.94</v>
       </c>
       <c r="D13" t="n">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="E13" t="n">
-        <v>-4.26</v>
+        <v>-16.33</v>
       </c>
       <c r="F13" t="n">
-        <v>0.65</v>
+        <v>0.46</v>
       </c>
       <c r="G13" t="n">
-        <v>8.07</v>
+        <v>33.42</v>
       </c>
       <c r="H13" t="n">
-        <v>1.11</v>
+        <v>7.36</v>
       </c>
       <c r="I13" t="n">
-        <v>724</v>
+        <v>440.57</v>
       </c>
       <c r="J13" t="n">
-        <v>729.24</v>
+        <v>462.29</v>
       </c>
       <c r="K13" t="n">
-        <v>715.11</v>
+        <v>403.81</v>
       </c>
       <c r="L13" t="n">
-        <v>747.41</v>
+        <v>537.48</v>
       </c>
       <c r="M13" t="n">
-        <v>45.18</v>
+        <v>51.2</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>BAJO</t>
+          <t>MEDIO</t>
         </is>
       </c>
       <c r="O13" t="inlineStr"/>
@@ -1185,50 +1201,50 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>QQQ</t>
+          <t>SOXX</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>ETF Nasdaq</t>
+          <t>ETF Chips</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>693.48</v>
+        <v>544.5</v>
       </c>
       <c r="D14" t="n">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="E14" t="n">
-        <v>-7.06</v>
+        <v>-11.56</v>
       </c>
       <c r="F14" t="n">
-        <v>0.92</v>
+        <v>1.14</v>
       </c>
       <c r="G14" t="n">
-        <v>13.64</v>
+        <v>32.24</v>
       </c>
       <c r="H14" t="n">
-        <v>1.97</v>
+        <v>5.92</v>
       </c>
       <c r="I14" t="n">
-        <v>688.02</v>
+        <v>531.6</v>
       </c>
       <c r="J14" t="n">
-        <v>696.89</v>
+        <v>552.5599999999999</v>
       </c>
       <c r="K14" t="n">
-        <v>673.02</v>
+        <v>496.13</v>
       </c>
       <c r="L14" t="n">
-        <v>727.59</v>
+        <v>625.11</v>
       </c>
       <c r="M14" t="n">
-        <v>46.67</v>
+        <v>54.98</v>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>BAJO</t>
+          <t>MEDIO</t>
         </is>
       </c>
       <c r="O14" t="inlineStr"/>
@@ -1241,102 +1257,102 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>UPST</t>
+          <t>AAPL</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Fintech IA</t>
+          <t>Tecnología</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>29.83</v>
+        <v>292.48</v>
       </c>
       <c r="D15" t="n">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="E15" t="n">
-        <v>-7.9</v>
+        <v>-5.73</v>
       </c>
       <c r="F15" t="n">
-        <v>0.37</v>
+        <v>0.49</v>
       </c>
       <c r="G15" t="n">
-        <v>2.12</v>
+        <v>7.22</v>
       </c>
       <c r="H15" t="n">
-        <v>7.09</v>
+        <v>2.47</v>
       </c>
       <c r="I15" t="n">
-        <v>28.98</v>
+        <v>289.59</v>
       </c>
       <c r="J15" t="n">
-        <v>30.36</v>
+        <v>294.29</v>
       </c>
       <c r="K15" t="n">
-        <v>26.66</v>
+        <v>281.64</v>
       </c>
       <c r="L15" t="n">
-        <v>35.12</v>
+        <v>310.54</v>
       </c>
       <c r="M15" t="n">
-        <v>55.23</v>
+        <v>41.09</v>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>MEDIO</t>
+          <t>BAJO</t>
         </is>
       </c>
       <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>NO COMPRAR</t>
+          <t>VIGILAR</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>NVDA</t>
+          <t>XOM</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>IA / Chips</t>
+          <t>Energía</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>200.77</v>
+        <v>151.69</v>
       </c>
       <c r="D16" t="n">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="E16" t="n">
-        <v>-9.789999999999999</v>
+        <v>-0.55</v>
       </c>
       <c r="F16" t="n">
-        <v>0.45</v>
+        <v>0.37</v>
       </c>
       <c r="G16" t="n">
-        <v>8.470000000000001</v>
+        <v>3.68</v>
       </c>
       <c r="H16" t="n">
-        <v>4.22</v>
+        <v>2.43</v>
       </c>
       <c r="I16" t="n">
-        <v>197.38</v>
+        <v>150.22</v>
       </c>
       <c r="J16" t="n">
-        <v>202.89</v>
+        <v>152.61</v>
       </c>
       <c r="K16" t="n">
-        <v>188.07</v>
+        <v>146.17</v>
       </c>
       <c r="L16" t="n">
-        <v>221.94</v>
+        <v>160.9</v>
       </c>
       <c r="M16" t="n">
-        <v>36.09</v>
+        <v>41.9</v>
       </c>
       <c r="N16" t="inlineStr">
         <is>
@@ -1346,109 +1362,109 @@
       <c r="O16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>NO COMPRAR</t>
+          <t>VIGILAR</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>AVGO</t>
+          <t>QQQ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>IA / Chips</t>
+          <t>ETF Nasdaq</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>373.96</v>
+        <v>697.3</v>
       </c>
       <c r="D17" t="n">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="E17" t="n">
-        <v>-22.35</v>
+        <v>-6.3</v>
       </c>
       <c r="F17" t="n">
-        <v>0.51</v>
+        <v>0.82</v>
       </c>
       <c r="G17" t="n">
-        <v>24.73</v>
+        <v>14.34</v>
       </c>
       <c r="H17" t="n">
-        <v>6.61</v>
+        <v>2.06</v>
       </c>
       <c r="I17" t="n">
-        <v>364.07</v>
+        <v>691.5599999999999</v>
       </c>
       <c r="J17" t="n">
-        <v>380.14</v>
+        <v>700.88</v>
       </c>
       <c r="K17" t="n">
-        <v>336.86</v>
+        <v>675.79</v>
       </c>
       <c r="L17" t="n">
-        <v>435.79</v>
+        <v>733.15</v>
       </c>
       <c r="M17" t="n">
-        <v>41.05</v>
+        <v>42.49</v>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>MEDIO</t>
+          <t>BAJO</t>
         </is>
       </c>
       <c r="O17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>NO COMPRAR</t>
+          <t>VIGILAR</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>AMZN</t>
+          <t>NVDA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Tecnología</t>
+          <t>IA / Chips</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>243.21</v>
+        <v>202.52</v>
       </c>
       <c r="D18" t="n">
         <v>56</v>
       </c>
       <c r="E18" t="n">
-        <v>-5.19</v>
+        <v>-5.58</v>
       </c>
       <c r="F18" t="n">
-        <v>0.42</v>
+        <v>0.47</v>
       </c>
       <c r="G18" t="n">
-        <v>7.24</v>
+        <v>8.630000000000001</v>
       </c>
       <c r="H18" t="n">
-        <v>2.98</v>
+        <v>4.26</v>
       </c>
       <c r="I18" t="n">
-        <v>240.31</v>
+        <v>199.07</v>
       </c>
       <c r="J18" t="n">
-        <v>245.02</v>
+        <v>204.68</v>
       </c>
       <c r="K18" t="n">
-        <v>232.35</v>
+        <v>189.58</v>
       </c>
       <c r="L18" t="n">
-        <v>261.31</v>
+        <v>224.1</v>
       </c>
       <c r="M18" t="n">
-        <v>36.41</v>
+        <v>34.28</v>
       </c>
       <c r="N18" t="inlineStr">
         <is>
@@ -1465,7 +1481,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>GOOGL</t>
+          <t>AMZN</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1474,37 +1490,37 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>359.48</v>
+        <v>238.7</v>
       </c>
       <c r="D19" t="n">
         <v>56</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.6</v>
+        <v>-4.53</v>
       </c>
       <c r="F19" t="n">
-        <v>0.39</v>
+        <v>0.45</v>
       </c>
       <c r="G19" t="n">
-        <v>9.81</v>
+        <v>7.32</v>
       </c>
       <c r="H19" t="n">
-        <v>2.73</v>
+        <v>3.07</v>
       </c>
       <c r="I19" t="n">
-        <v>355.55</v>
+        <v>235.77</v>
       </c>
       <c r="J19" t="n">
-        <v>361.93</v>
+        <v>240.53</v>
       </c>
       <c r="K19" t="n">
-        <v>344.76</v>
+        <v>227.72</v>
       </c>
       <c r="L19" t="n">
-        <v>384</v>
+        <v>257.01</v>
       </c>
       <c r="M19" t="n">
-        <v>30.38</v>
+        <v>27.39</v>
       </c>
       <c r="N19" t="inlineStr">
         <is>
@@ -1521,46 +1537,46 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>CVX</t>
+          <t>GOOGL</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Energía</t>
+          <t>Tecnología</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>186.72</v>
+        <v>357.37</v>
       </c>
       <c r="D20" t="n">
         <v>56</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.44</v>
+        <v>-0.39</v>
       </c>
       <c r="F20" t="n">
-        <v>0.33</v>
+        <v>0.47</v>
       </c>
       <c r="G20" t="n">
-        <v>4.12</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="H20" t="n">
-        <v>2.21</v>
+        <v>2.79</v>
       </c>
       <c r="I20" t="n">
-        <v>185.07</v>
+        <v>353.39</v>
       </c>
       <c r="J20" t="n">
-        <v>187.75</v>
+        <v>359.87</v>
       </c>
       <c r="K20" t="n">
-        <v>180.54</v>
+        <v>342.43</v>
       </c>
       <c r="L20" t="n">
-        <v>197.03</v>
+        <v>382.28</v>
       </c>
       <c r="M20" t="n">
-        <v>33.01</v>
+        <v>28.85</v>
       </c>
       <c r="N20" t="inlineStr">
         <is>
@@ -1586,37 +1602,37 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>401.46</v>
+        <v>402.66</v>
       </c>
       <c r="D21" t="n">
         <v>54</v>
       </c>
       <c r="E21" t="n">
-        <v>-9.029999999999999</v>
+        <v>-5.77</v>
       </c>
       <c r="F21" t="n">
         <v>0.39</v>
       </c>
       <c r="G21" t="n">
-        <v>12.88</v>
+        <v>12.84</v>
       </c>
       <c r="H21" t="n">
-        <v>3.21</v>
+        <v>3.19</v>
       </c>
       <c r="I21" t="n">
-        <v>396.31</v>
+        <v>397.53</v>
       </c>
       <c r="J21" t="n">
-        <v>404.68</v>
+        <v>405.87</v>
       </c>
       <c r="K21" t="n">
-        <v>382.15</v>
+        <v>383.4</v>
       </c>
       <c r="L21" t="n">
-        <v>433.65</v>
+        <v>434.76</v>
       </c>
       <c r="M21" t="n">
-        <v>43.7</v>
+        <v>42.37</v>
       </c>
       <c r="N21" t="inlineStr">
         <is>
@@ -1633,46 +1649,46 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>TSLA</t>
+          <t>SPY</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Autos / Tech</t>
+          <t>ETF Mercado</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>388.64</v>
+        <v>729.63</v>
       </c>
       <c r="D22" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E22" t="n">
-        <v>-8.279999999999999</v>
+        <v>-3.26</v>
       </c>
       <c r="F22" t="n">
-        <v>0.61</v>
+        <v>0.51</v>
       </c>
       <c r="G22" t="n">
-        <v>16.45</v>
+        <v>8.48</v>
       </c>
       <c r="H22" t="n">
-        <v>4.23</v>
+        <v>1.16</v>
       </c>
       <c r="I22" t="n">
-        <v>382.06</v>
+        <v>726.24</v>
       </c>
       <c r="J22" t="n">
-        <v>392.75</v>
+        <v>731.75</v>
       </c>
       <c r="K22" t="n">
-        <v>363.97</v>
+        <v>716.91</v>
       </c>
       <c r="L22" t="n">
-        <v>429.76</v>
+        <v>750.83</v>
       </c>
       <c r="M22" t="n">
-        <v>44.59</v>
+        <v>39.91</v>
       </c>
       <c r="N22" t="inlineStr">
         <is>
@@ -1689,46 +1705,46 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>SOFI</t>
+          <t>AVGO</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Fintech</t>
+          <t>IA / Chips</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>15.8</v>
+        <v>372.75</v>
       </c>
       <c r="D23" t="n">
         <v>48</v>
       </c>
       <c r="E23" t="n">
-        <v>-10.94</v>
+        <v>-22.22</v>
       </c>
       <c r="F23" t="n">
-        <v>0.52</v>
+        <v>0.7</v>
       </c>
       <c r="G23" t="n">
-        <v>1.01</v>
+        <v>25.51</v>
       </c>
       <c r="H23" t="n">
-        <v>6.4</v>
+        <v>6.84</v>
       </c>
       <c r="I23" t="n">
-        <v>15.4</v>
+        <v>362.55</v>
       </c>
       <c r="J23" t="n">
-        <v>16.05</v>
+        <v>379.13</v>
       </c>
       <c r="K23" t="n">
-        <v>14.28</v>
+        <v>334.49</v>
       </c>
       <c r="L23" t="n">
-        <v>18.33</v>
+        <v>436.51</v>
       </c>
       <c r="M23" t="n">
-        <v>53.5</v>
+        <v>38.85</v>
       </c>
       <c r="N23" t="inlineStr">
         <is>
@@ -1745,50 +1761,50 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>XOM</t>
+          <t>SOFI</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Energía</t>
+          <t>Fintech</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>148.78</v>
+        <v>16.02</v>
       </c>
       <c r="D24" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.52</v>
+        <v>-3.93</v>
       </c>
       <c r="F24" t="n">
-        <v>0.3</v>
+        <v>0.59</v>
       </c>
       <c r="G24" t="n">
-        <v>4</v>
+        <v>1.02</v>
       </c>
       <c r="H24" t="n">
-        <v>2.69</v>
+        <v>6.38</v>
       </c>
       <c r="I24" t="n">
-        <v>147.18</v>
+        <v>15.62</v>
       </c>
       <c r="J24" t="n">
-        <v>149.78</v>
+        <v>16.28</v>
       </c>
       <c r="K24" t="n">
-        <v>142.77</v>
+        <v>14.49</v>
       </c>
       <c r="L24" t="n">
-        <v>158.79</v>
+        <v>18.58</v>
       </c>
       <c r="M24" t="n">
-        <v>28.46</v>
+        <v>52.24</v>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>BAJO</t>
+          <t>MEDIO</t>
         </is>
       </c>
       <c r="O24" t="inlineStr"/>
@@ -1801,46 +1817,46 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>OXY</t>
+          <t>TSLA</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Energía</t>
+          <t>Autos / Tech</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>56.06</v>
+        <v>381.48</v>
       </c>
       <c r="D25" t="n">
         <v>46</v>
       </c>
       <c r="E25" t="n">
-        <v>-5.12</v>
+        <v>-9.960000000000001</v>
       </c>
       <c r="F25" t="n">
-        <v>0.43</v>
+        <v>0.61</v>
       </c>
       <c r="G25" t="n">
-        <v>1.82</v>
+        <v>16.88</v>
       </c>
       <c r="H25" t="n">
-        <v>3.25</v>
+        <v>4.43</v>
       </c>
       <c r="I25" t="n">
-        <v>55.34</v>
+        <v>374.73</v>
       </c>
       <c r="J25" t="n">
-        <v>56.52</v>
+        <v>385.7</v>
       </c>
       <c r="K25" t="n">
-        <v>53.33</v>
+        <v>356.16</v>
       </c>
       <c r="L25" t="n">
-        <v>60.62</v>
+        <v>423.69</v>
       </c>
       <c r="M25" t="n">
-        <v>31.63</v>
+        <v>36.95</v>
       </c>
       <c r="N25" t="inlineStr">
         <is>
@@ -1866,37 +1882,37 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>585.89</v>
+        <v>576.4299999999999</v>
       </c>
       <c r="D26" t="n">
         <v>44</v>
       </c>
       <c r="E26" t="n">
-        <v>-1.96</v>
+        <v>-7.47</v>
       </c>
       <c r="F26" t="n">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="G26" t="n">
-        <v>18.9</v>
+        <v>19.63</v>
       </c>
       <c r="H26" t="n">
-        <v>3.23</v>
+        <v>3.4</v>
       </c>
       <c r="I26" t="n">
-        <v>578.33</v>
+        <v>568.58</v>
       </c>
       <c r="J26" t="n">
-        <v>590.61</v>
+        <v>581.34</v>
       </c>
       <c r="K26" t="n">
-        <v>557.54</v>
+        <v>546.99</v>
       </c>
       <c r="L26" t="n">
-        <v>633.13</v>
+        <v>625.5</v>
       </c>
       <c r="M26" t="n">
-        <v>44.15</v>
+        <v>40.39</v>
       </c>
       <c r="N26" t="inlineStr">
         <is>
@@ -1922,37 +1938,37 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>6.86</v>
+        <v>6.94</v>
       </c>
       <c r="D27" t="n">
         <v>38</v>
       </c>
       <c r="E27" t="n">
-        <v>-22.17</v>
+        <v>-14.11</v>
       </c>
       <c r="F27" t="n">
-        <v>0.47</v>
+        <v>0.61</v>
       </c>
       <c r="G27" t="n">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="H27" t="n">
-        <v>7.83</v>
+        <v>7.94</v>
       </c>
       <c r="I27" t="n">
-        <v>6.65</v>
+        <v>6.72</v>
       </c>
       <c r="J27" t="n">
-        <v>7</v>
+        <v>7.08</v>
       </c>
       <c r="K27" t="n">
-        <v>6.06</v>
+        <v>6.11</v>
       </c>
       <c r="L27" t="n">
-        <v>8.210000000000001</v>
+        <v>8.32</v>
       </c>
       <c r="M27" t="n">
-        <v>30.79</v>
+        <v>31.36</v>
       </c>
       <c r="N27" t="inlineStr">
         <is>
@@ -1978,37 +1994,37 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>128.88</v>
+        <v>131.75</v>
       </c>
       <c r="D28" t="n">
         <v>36</v>
       </c>
       <c r="E28" t="n">
-        <v>-15.31</v>
+        <v>-7.35</v>
       </c>
       <c r="F28" t="n">
-        <v>0.42</v>
+        <v>0.39</v>
       </c>
       <c r="G28" t="n">
-        <v>7.45</v>
+        <v>7.52</v>
       </c>
       <c r="H28" t="n">
-        <v>5.78</v>
+        <v>5.71</v>
       </c>
       <c r="I28" t="n">
-        <v>125.89</v>
+        <v>128.74</v>
       </c>
       <c r="J28" t="n">
-        <v>130.74</v>
+        <v>133.63</v>
       </c>
       <c r="K28" t="n">
-        <v>117.7</v>
+        <v>120.47</v>
       </c>
       <c r="L28" t="n">
-        <v>147.51</v>
+        <v>150.55</v>
       </c>
       <c r="M28" t="n">
-        <v>45.36</v>
+        <v>45.79</v>
       </c>
       <c r="N28" t="inlineStr">
         <is>
@@ -2034,37 +2050,37 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>41.26</v>
+        <v>41.06</v>
       </c>
       <c r="D29" t="n">
         <v>36</v>
       </c>
       <c r="E29" t="n">
-        <v>-7.05</v>
+        <v>-3.33</v>
       </c>
       <c r="F29" t="n">
-        <v>0.43</v>
+        <v>0.47</v>
       </c>
       <c r="G29" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="H29" t="n">
-        <v>2.84</v>
+        <v>2.77</v>
       </c>
       <c r="I29" t="n">
-        <v>40.79</v>
+        <v>40.6</v>
       </c>
       <c r="J29" t="n">
-        <v>41.55</v>
+        <v>41.34</v>
       </c>
       <c r="K29" t="n">
-        <v>39.5</v>
+        <v>39.35</v>
       </c>
       <c r="L29" t="n">
-        <v>44.18</v>
+        <v>43.9</v>
       </c>
       <c r="M29" t="n">
-        <v>32.46</v>
+        <v>27.28</v>
       </c>
       <c r="N29" t="inlineStr">
         <is>
@@ -2090,37 +2106,37 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>151.5</v>
+        <v>156.28</v>
       </c>
       <c r="D30" t="n">
         <v>28</v>
       </c>
       <c r="E30" t="n">
-        <v>-12.93</v>
+        <v>-4.25</v>
       </c>
       <c r="F30" t="n">
-        <v>0.45</v>
+        <v>0.37</v>
       </c>
       <c r="G30" t="n">
-        <v>10.63</v>
+        <v>10.92</v>
       </c>
       <c r="H30" t="n">
-        <v>7.02</v>
+        <v>6.99</v>
       </c>
       <c r="I30" t="n">
-        <v>147.25</v>
+        <v>151.91</v>
       </c>
       <c r="J30" t="n">
-        <v>154.16</v>
+        <v>159.01</v>
       </c>
       <c r="K30" t="n">
-        <v>135.55</v>
+        <v>139.9</v>
       </c>
       <c r="L30" t="n">
-        <v>178.08</v>
+        <v>183.57</v>
       </c>
       <c r="M30" t="n">
-        <v>28.65</v>
+        <v>31.15</v>
       </c>
       <c r="N30" t="inlineStr">
         <is>
@@ -2146,37 +2162,37 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>871.63</v>
+        <v>896</v>
       </c>
       <c r="D31" t="n">
         <v>72</v>
       </c>
       <c r="E31" t="n">
-        <v>-18.09</v>
+        <v>-17</v>
       </c>
       <c r="F31" t="n">
-        <v>0.64</v>
+        <v>0.62</v>
       </c>
       <c r="G31" t="n">
-        <v>77.42</v>
+        <v>80.62</v>
       </c>
       <c r="H31" t="n">
-        <v>8.880000000000001</v>
+        <v>9</v>
       </c>
       <c r="I31" t="n">
-        <v>840.66</v>
+        <v>863.75</v>
       </c>
       <c r="J31" t="n">
-        <v>890.99</v>
+        <v>916.16</v>
       </c>
       <c r="K31" t="n">
-        <v>755.5</v>
+        <v>775.0700000000001</v>
       </c>
       <c r="L31" t="n">
-        <v>1065.18</v>
+        <v>1097.55</v>
       </c>
       <c r="M31" t="n">
-        <v>60.92</v>
+        <v>61.18</v>
       </c>
       <c r="N31" t="inlineStr">
         <is>
@@ -2202,37 +2218,37 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>305.41</v>
+        <v>307.81</v>
       </c>
       <c r="D32" t="n">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="E32" t="n">
-        <v>-24.16</v>
+        <v>-25.26</v>
       </c>
       <c r="F32" t="n">
-        <v>0.53</v>
+        <v>0.37</v>
       </c>
       <c r="G32" t="n">
-        <v>39.76</v>
+        <v>39.46</v>
       </c>
       <c r="H32" t="n">
-        <v>13.02</v>
+        <v>12.82</v>
       </c>
       <c r="I32" t="n">
-        <v>289.51</v>
+        <v>292.03</v>
       </c>
       <c r="J32" t="n">
-        <v>315.35</v>
+        <v>317.68</v>
       </c>
       <c r="K32" t="n">
-        <v>245.77</v>
+        <v>248.62</v>
       </c>
       <c r="L32" t="n">
-        <v>404.8</v>
+        <v>406.46</v>
       </c>
       <c r="M32" t="n">
-        <v>61.71</v>
+        <v>58.1</v>
       </c>
       <c r="N32" t="inlineStr">
         <is>
@@ -2249,46 +2265,46 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>QCOM</t>
+          <t>IONQ</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Chips</t>
+          <t>Computación cuántica</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>196.17</v>
+        <v>57.65</v>
       </c>
       <c r="D33" t="n">
         <v>64</v>
       </c>
       <c r="E33" t="n">
-        <v>-18.25</v>
+        <v>-15.5</v>
       </c>
       <c r="F33" t="n">
-        <v>0.67</v>
+        <v>0.49</v>
       </c>
       <c r="G33" t="n">
-        <v>19.56</v>
+        <v>6.7</v>
       </c>
       <c r="H33" t="n">
-        <v>9.970000000000001</v>
+        <v>11.63</v>
       </c>
       <c r="I33" t="n">
-        <v>188.35</v>
+        <v>54.97</v>
       </c>
       <c r="J33" t="n">
-        <v>201.06</v>
+        <v>59.33</v>
       </c>
       <c r="K33" t="n">
-        <v>166.83</v>
+        <v>47.6</v>
       </c>
       <c r="L33" t="n">
-        <v>245.07</v>
+        <v>74.42</v>
       </c>
       <c r="M33" t="n">
-        <v>50.35</v>
+        <v>54.96</v>
       </c>
       <c r="N33" t="inlineStr">
         <is>
@@ -2314,37 +2330,37 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>38.83</v>
+        <v>33.02</v>
       </c>
       <c r="D34" t="n">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="E34" t="n">
-        <v>-22.6</v>
+        <v>-30.37</v>
       </c>
       <c r="F34" t="n">
-        <v>0.52</v>
+        <v>1.57</v>
       </c>
       <c r="G34" t="n">
-        <v>3.86</v>
+        <v>4.22</v>
       </c>
       <c r="H34" t="n">
-        <v>9.949999999999999</v>
+        <v>12.79</v>
       </c>
       <c r="I34" t="n">
-        <v>37.28</v>
+        <v>31.33</v>
       </c>
       <c r="J34" t="n">
-        <v>39.8</v>
+        <v>34.08</v>
       </c>
       <c r="K34" t="n">
-        <v>33.03</v>
+        <v>26.69</v>
       </c>
       <c r="L34" t="n">
-        <v>48.49</v>
+        <v>43.58</v>
       </c>
       <c r="M34" t="n">
-        <v>61.6</v>
+        <v>49.43</v>
       </c>
       <c r="N34" t="inlineStr">
         <is>
@@ -2354,53 +2370,53 @@
       <c r="O34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>VIGILAR</t>
+          <t>NO COMPRAR</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>IONQ</t>
+          <t>QCOM</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Computación cuántica</t>
+          <t>Chips</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>54.48</v>
+        <v>191.27</v>
       </c>
       <c r="D35" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E35" t="n">
-        <v>-23.7</v>
+        <v>-23.21</v>
       </c>
       <c r="F35" t="n">
-        <v>0.57</v>
+        <v>0.42</v>
       </c>
       <c r="G35" t="n">
-        <v>6.64</v>
+        <v>20.14</v>
       </c>
       <c r="H35" t="n">
-        <v>12.19</v>
+        <v>10.53</v>
       </c>
       <c r="I35" t="n">
-        <v>51.82</v>
+        <v>183.22</v>
       </c>
       <c r="J35" t="n">
-        <v>56.14</v>
+        <v>196.31</v>
       </c>
       <c r="K35" t="n">
-        <v>44.52</v>
+        <v>161.07</v>
       </c>
       <c r="L35" t="n">
-        <v>71.08</v>
+        <v>241.62</v>
       </c>
       <c r="M35" t="n">
-        <v>55.25</v>
+        <v>47.14</v>
       </c>
       <c r="N35" t="inlineStr">
         <is>
@@ -2426,37 +2442,37 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>101.56</v>
+        <v>105.39</v>
       </c>
       <c r="D36" t="n">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="E36" t="n">
-        <v>-5.9</v>
+        <v>-6.49</v>
       </c>
       <c r="F36" t="n">
         <v>0.57</v>
       </c>
       <c r="G36" t="n">
-        <v>9.109999999999999</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="H36" t="n">
-        <v>8.970000000000001</v>
+        <v>8.43</v>
       </c>
       <c r="I36" t="n">
-        <v>97.92</v>
+        <v>101.83</v>
       </c>
       <c r="J36" t="n">
-        <v>103.84</v>
+        <v>107.61</v>
       </c>
       <c r="K36" t="n">
-        <v>87.90000000000001</v>
+        <v>92.06</v>
       </c>
       <c r="L36" t="n">
-        <v>124.33</v>
+        <v>127.61</v>
       </c>
       <c r="M36" t="n">
-        <v>43.14</v>
+        <v>37.75</v>
       </c>
       <c r="N36" t="inlineStr">
         <is>
@@ -2482,37 +2498,37 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>102.84</v>
+        <v>106.6</v>
       </c>
       <c r="D37" t="n">
         <v>44</v>
       </c>
       <c r="E37" t="n">
-        <v>-16.61</v>
+        <v>-7.06</v>
       </c>
       <c r="F37" t="n">
-        <v>0.49</v>
+        <v>0.28</v>
       </c>
       <c r="G37" t="n">
-        <v>12.05</v>
+        <v>11.81</v>
       </c>
       <c r="H37" t="n">
-        <v>11.72</v>
+        <v>11.08</v>
       </c>
       <c r="I37" t="n">
-        <v>98.02</v>
+        <v>101.87</v>
       </c>
       <c r="J37" t="n">
-        <v>105.85</v>
+        <v>109.55</v>
       </c>
       <c r="K37" t="n">
-        <v>84.77</v>
+        <v>88.88</v>
       </c>
       <c r="L37" t="n">
-        <v>132.96</v>
+        <v>136.13</v>
       </c>
       <c r="M37" t="n">
-        <v>38.62</v>
+        <v>35.69</v>
       </c>
       <c r="N37" t="inlineStr">
         <is>

--- a/analisis_acciones.xlsx
+++ b/analisis_acciones.xlsx
@@ -501,46 +501,46 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>HOOD</t>
+          <t>ASML</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Trading</t>
+          <t>Chips</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>88.04000000000001</v>
+        <v>1815.1</v>
       </c>
       <c r="D2" t="n">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="E2" t="n">
-        <v>6.27</v>
+        <v>3.28</v>
       </c>
       <c r="F2" t="n">
-        <v>0.99</v>
+        <v>0.85</v>
       </c>
       <c r="G2" t="n">
-        <v>6.22</v>
+        <v>81.86</v>
       </c>
       <c r="H2" t="n">
-        <v>7.06</v>
+        <v>4.51</v>
       </c>
       <c r="I2" t="n">
-        <v>85.56</v>
+        <v>1782.36</v>
       </c>
       <c r="J2" t="n">
-        <v>89.59999999999999</v>
+        <v>1835.57</v>
       </c>
       <c r="K2" t="n">
-        <v>78.72</v>
+        <v>1692.31</v>
       </c>
       <c r="L2" t="n">
-        <v>103.59</v>
+        <v>2019.75</v>
       </c>
       <c r="M2" t="n">
-        <v>61.37</v>
+        <v>68.23</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -561,55 +561,55 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ASML</t>
+          <t>LRCX</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Chips</t>
+          <t>Equipos chips</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1743.57</v>
+        <v>344.86</v>
       </c>
       <c r="D3" t="n">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="E3" t="n">
-        <v>1</v>
+        <v>2.51</v>
       </c>
       <c r="F3" t="n">
-        <v>1.05</v>
+        <v>0.65</v>
       </c>
       <c r="G3" t="n">
-        <v>78.88</v>
+        <v>21.03</v>
       </c>
       <c r="H3" t="n">
-        <v>4.52</v>
+        <v>6.1</v>
       </c>
       <c r="I3" t="n">
-        <v>1712.02</v>
+        <v>336.45</v>
       </c>
       <c r="J3" t="n">
-        <v>1763.29</v>
+        <v>350.12</v>
       </c>
       <c r="K3" t="n">
-        <v>1625.25</v>
+        <v>313.32</v>
       </c>
       <c r="L3" t="n">
-        <v>1940.77</v>
+        <v>397.42</v>
       </c>
       <c r="M3" t="n">
-        <v>67.17</v>
+        <v>64.63</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>BAJO</t>
+          <t>MEDIO</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -621,55 +621,55 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CVX</t>
+          <t>AMAT</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Energía</t>
+          <t>Equipos chips</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>191.62</v>
+        <v>527.29</v>
       </c>
       <c r="D4" t="n">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="E4" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="F4" t="n">
-        <v>0.46</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="G4" t="n">
-        <v>4</v>
+        <v>31.08</v>
       </c>
       <c r="H4" t="n">
-        <v>2.09</v>
+        <v>5.89</v>
       </c>
       <c r="I4" t="n">
-        <v>190.02</v>
+        <v>514.86</v>
       </c>
       <c r="J4" t="n">
-        <v>192.62</v>
+        <v>535.0599999999999</v>
       </c>
       <c r="K4" t="n">
-        <v>185.62</v>
+        <v>480.67</v>
       </c>
       <c r="L4" t="n">
-        <v>201.61</v>
+        <v>604.98</v>
       </c>
       <c r="M4" t="n">
-        <v>50.49</v>
+        <v>73.23999999999999</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>BAJO</t>
+          <t>MEDIO</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -681,50 +681,50 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>KLAC</t>
+          <t>CVX</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Equipos chips</t>
+          <t>Energía</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>2152.17</v>
+        <v>189.78</v>
       </c>
       <c r="D5" t="n">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="E5" t="n">
-        <v>1.27</v>
+        <v>0.76</v>
       </c>
       <c r="F5" t="n">
-        <v>0.82</v>
+        <v>0.26</v>
       </c>
       <c r="G5" t="n">
-        <v>126.82</v>
+        <v>3.89</v>
       </c>
       <c r="H5" t="n">
-        <v>5.89</v>
+        <v>2.05</v>
       </c>
       <c r="I5" t="n">
-        <v>2101.44</v>
+        <v>188.22</v>
       </c>
       <c r="J5" t="n">
-        <v>2183.87</v>
+        <v>190.75</v>
       </c>
       <c r="K5" t="n">
-        <v>1961.94</v>
+        <v>183.94</v>
       </c>
       <c r="L5" t="n">
-        <v>2469.22</v>
+        <v>199.51</v>
       </c>
       <c r="M5" t="n">
-        <v>67.81</v>
+        <v>47.79</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>MEDIO</t>
+          <t>BAJO</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -741,46 +741,46 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AMAT</t>
+          <t>HOOD</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Equipos chips</t>
+          <t>Trading</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>501.48</v>
+        <v>88.44</v>
       </c>
       <c r="D6" t="n">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="E6" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="F6" t="n">
         <v>0.6899999999999999</v>
       </c>
       <c r="G6" t="n">
-        <v>28.8</v>
+        <v>6.4</v>
       </c>
       <c r="H6" t="n">
-        <v>5.74</v>
+        <v>7.23</v>
       </c>
       <c r="I6" t="n">
-        <v>489.96</v>
+        <v>85.88</v>
       </c>
       <c r="J6" t="n">
-        <v>508.68</v>
+        <v>90.04000000000001</v>
       </c>
       <c r="K6" t="n">
-        <v>458.29</v>
+        <v>78.84</v>
       </c>
       <c r="L6" t="n">
-        <v>573.47</v>
+        <v>104.43</v>
       </c>
       <c r="M6" t="n">
-        <v>70.22</v>
+        <v>61.54</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
@@ -810,37 +810,37 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>10.99</v>
+        <v>10.94</v>
       </c>
       <c r="D7" t="n">
         <v>77</v>
       </c>
       <c r="E7" t="n">
-        <v>2.61</v>
+        <v>3.45</v>
       </c>
       <c r="F7" t="n">
-        <v>0.47</v>
+        <v>0.43</v>
       </c>
       <c r="G7" t="n">
-        <v>0.77</v>
+        <v>0.8</v>
       </c>
       <c r="H7" t="n">
-        <v>7</v>
+        <v>7.35</v>
       </c>
       <c r="I7" t="n">
-        <v>10.68</v>
+        <v>10.62</v>
       </c>
       <c r="J7" t="n">
-        <v>11.18</v>
+        <v>11.15</v>
       </c>
       <c r="K7" t="n">
-        <v>9.84</v>
+        <v>9.74</v>
       </c>
       <c r="L7" t="n">
-        <v>12.91</v>
+        <v>12.95</v>
       </c>
       <c r="M7" t="n">
-        <v>69.3</v>
+        <v>68.63</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -870,37 +870,37 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>413.03</v>
+        <v>410.06</v>
       </c>
       <c r="D8" t="n">
         <v>76</v>
       </c>
       <c r="E8" t="n">
-        <v>-5.42</v>
+        <v>-7.84</v>
       </c>
       <c r="F8" t="n">
-        <v>0.59</v>
+        <v>0.52</v>
       </c>
       <c r="G8" t="n">
-        <v>18.38</v>
+        <v>18.66</v>
       </c>
       <c r="H8" t="n">
-        <v>4.45</v>
+        <v>4.55</v>
       </c>
       <c r="I8" t="n">
-        <v>405.68</v>
+        <v>402.6</v>
       </c>
       <c r="J8" t="n">
-        <v>417.62</v>
+        <v>414.73</v>
       </c>
       <c r="K8" t="n">
-        <v>385.46</v>
+        <v>382.07</v>
       </c>
       <c r="L8" t="n">
-        <v>458.98</v>
+        <v>456.71</v>
       </c>
       <c r="M8" t="n">
-        <v>54.11</v>
+        <v>51.05</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
@@ -917,46 +917,46 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>LRCX</t>
+          <t>SOXX</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Equipos chips</t>
+          <t>ETF Chips</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>325.77</v>
+        <v>559.3200000000001</v>
       </c>
       <c r="D9" t="n">
         <v>76</v>
       </c>
       <c r="E9" t="n">
-        <v>-5.22</v>
+        <v>-7.2</v>
       </c>
       <c r="F9" t="n">
-        <v>0.78</v>
+        <v>0.52</v>
       </c>
       <c r="G9" t="n">
-        <v>19.72</v>
+        <v>33.71</v>
       </c>
       <c r="H9" t="n">
-        <v>6.05</v>
+        <v>6.03</v>
       </c>
       <c r="I9" t="n">
-        <v>317.89</v>
+        <v>545.84</v>
       </c>
       <c r="J9" t="n">
-        <v>330.7</v>
+        <v>567.75</v>
       </c>
       <c r="K9" t="n">
-        <v>296.2</v>
+        <v>508.76</v>
       </c>
       <c r="L9" t="n">
-        <v>375.07</v>
+        <v>643.59</v>
       </c>
       <c r="M9" t="n">
-        <v>63.08</v>
+        <v>56.67</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
@@ -973,57 +973,53 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>UPST</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Fintech IA</t>
+          <t>IA / Chips</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>30.9</v>
+        <v>462.42</v>
       </c>
       <c r="D10" t="n">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="E10" t="n">
-        <v>2.01</v>
+        <v>-11.62</v>
       </c>
       <c r="F10" t="n">
-        <v>0.33</v>
+        <v>0.44</v>
       </c>
       <c r="G10" t="n">
-        <v>2.09</v>
+        <v>34.22</v>
       </c>
       <c r="H10" t="n">
-        <v>6.75</v>
+        <v>7.4</v>
       </c>
       <c r="I10" t="n">
-        <v>30.07</v>
+        <v>448.73</v>
       </c>
       <c r="J10" t="n">
-        <v>31.42</v>
+        <v>470.97</v>
       </c>
       <c r="K10" t="n">
-        <v>27.77</v>
+        <v>411.1</v>
       </c>
       <c r="L10" t="n">
-        <v>36.12</v>
+        <v>547.96</v>
       </c>
       <c r="M10" t="n">
-        <v>56.86</v>
+        <v>52.34</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
           <t>MEDIO</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>🔥</t>
-        </is>
-      </c>
+      <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>VIGILAR</t>
@@ -1033,7 +1029,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>OXY</t>
+          <t>XOM</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1042,37 +1038,37 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>58.31</v>
+        <v>150.24</v>
       </c>
       <c r="D11" t="n">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.23</v>
+        <v>-1.18</v>
       </c>
       <c r="F11" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="G11" t="n">
-        <v>1.79</v>
+        <v>3.49</v>
       </c>
       <c r="H11" t="n">
-        <v>3.08</v>
+        <v>2.32</v>
       </c>
       <c r="I11" t="n">
-        <v>57.59</v>
+        <v>148.84</v>
       </c>
       <c r="J11" t="n">
-        <v>58.76</v>
+        <v>151.11</v>
       </c>
       <c r="K11" t="n">
-        <v>55.62</v>
+        <v>145</v>
       </c>
       <c r="L11" t="n">
-        <v>62.8</v>
+        <v>158.97</v>
       </c>
       <c r="M11" t="n">
-        <v>47.68</v>
+        <v>40.53</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
@@ -1089,7 +1085,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SLB</t>
+          <t>OXY</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1098,37 +1094,37 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>56.19</v>
+        <v>57.33</v>
       </c>
       <c r="D12" t="n">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.15</v>
+        <v>-1.82</v>
       </c>
       <c r="F12" t="n">
-        <v>0.48</v>
+        <v>0.34</v>
       </c>
       <c r="G12" t="n">
-        <v>1.9</v>
+        <v>1.69</v>
       </c>
       <c r="H12" t="n">
-        <v>3.38</v>
+        <v>2.95</v>
       </c>
       <c r="I12" t="n">
-        <v>55.43</v>
+        <v>56.66</v>
       </c>
       <c r="J12" t="n">
-        <v>56.67</v>
+        <v>57.76</v>
       </c>
       <c r="K12" t="n">
-        <v>53.34</v>
+        <v>54.8</v>
       </c>
       <c r="L12" t="n">
-        <v>60.95</v>
+        <v>61.57</v>
       </c>
       <c r="M12" t="n">
-        <v>47.15</v>
+        <v>44.56</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
@@ -1145,50 +1141,50 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>SLB</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>IA / Chips</t>
+          <t>Energía</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>453.94</v>
+        <v>55.24</v>
       </c>
       <c r="D13" t="n">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="E13" t="n">
-        <v>-16.33</v>
+        <v>-4.78</v>
       </c>
       <c r="F13" t="n">
-        <v>0.46</v>
+        <v>0.27</v>
       </c>
       <c r="G13" t="n">
-        <v>33.42</v>
+        <v>1.92</v>
       </c>
       <c r="H13" t="n">
-        <v>7.36</v>
+        <v>3.47</v>
       </c>
       <c r="I13" t="n">
-        <v>440.57</v>
+        <v>54.47</v>
       </c>
       <c r="J13" t="n">
-        <v>462.29</v>
+        <v>55.71</v>
       </c>
       <c r="K13" t="n">
-        <v>403.81</v>
+        <v>52.36</v>
       </c>
       <c r="L13" t="n">
-        <v>537.48</v>
+        <v>60.03</v>
       </c>
       <c r="M13" t="n">
-        <v>51.2</v>
+        <v>43.88</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>MEDIO</t>
+          <t>BAJO</t>
         </is>
       </c>
       <c r="O13" t="inlineStr"/>
@@ -1201,50 +1197,50 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>SOXX</t>
+          <t>QQQ</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>ETF Chips</t>
+          <t>ETF Nasdaq</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>544.5</v>
+        <v>699.36</v>
       </c>
       <c r="D14" t="n">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="E14" t="n">
-        <v>-11.56</v>
+        <v>-5.57</v>
       </c>
       <c r="F14" t="n">
-        <v>1.14</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="G14" t="n">
-        <v>32.24</v>
+        <v>14.74</v>
       </c>
       <c r="H14" t="n">
-        <v>5.92</v>
+        <v>2.11</v>
       </c>
       <c r="I14" t="n">
-        <v>531.6</v>
+        <v>693.46</v>
       </c>
       <c r="J14" t="n">
-        <v>552.5599999999999</v>
+        <v>703.04</v>
       </c>
       <c r="K14" t="n">
-        <v>496.13</v>
+        <v>677.24</v>
       </c>
       <c r="L14" t="n">
-        <v>625.11</v>
+        <v>736.21</v>
       </c>
       <c r="M14" t="n">
-        <v>54.98</v>
+        <v>43.32</v>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>MEDIO</t>
+          <t>BAJO</t>
         </is>
       </c>
       <c r="O14" t="inlineStr"/>
@@ -1257,102 +1253,102 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>UPST</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Tecnología</t>
+          <t>Fintech IA</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>292.48</v>
+        <v>29.42</v>
       </c>
       <c r="D15" t="n">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="E15" t="n">
-        <v>-5.73</v>
+        <v>-8.83</v>
       </c>
       <c r="F15" t="n">
-        <v>0.49</v>
+        <v>0.48</v>
       </c>
       <c r="G15" t="n">
-        <v>7.22</v>
+        <v>2.09</v>
       </c>
       <c r="H15" t="n">
-        <v>2.47</v>
+        <v>7.1</v>
       </c>
       <c r="I15" t="n">
-        <v>289.59</v>
+        <v>28.58</v>
       </c>
       <c r="J15" t="n">
-        <v>294.29</v>
+        <v>29.94</v>
       </c>
       <c r="K15" t="n">
-        <v>281.64</v>
+        <v>26.29</v>
       </c>
       <c r="L15" t="n">
-        <v>310.54</v>
+        <v>34.64</v>
       </c>
       <c r="M15" t="n">
-        <v>41.09</v>
+        <v>51.73</v>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>BAJO</t>
+          <t>MEDIO</t>
         </is>
       </c>
       <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>VIGILAR</t>
+          <t>NO COMPRAR</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>XOM</t>
+          <t>NVDA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Energía</t>
+          <t>IA / Chips</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>151.69</v>
+        <v>200.35</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.55</v>
+        <v>-8.369999999999999</v>
       </c>
       <c r="F16" t="n">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="G16" t="n">
-        <v>3.68</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="H16" t="n">
-        <v>2.43</v>
+        <v>4.18</v>
       </c>
       <c r="I16" t="n">
-        <v>150.22</v>
+        <v>197</v>
       </c>
       <c r="J16" t="n">
-        <v>152.61</v>
+        <v>202.44</v>
       </c>
       <c r="K16" t="n">
-        <v>146.17</v>
+        <v>187.8</v>
       </c>
       <c r="L16" t="n">
-        <v>160.9</v>
+        <v>221.27</v>
       </c>
       <c r="M16" t="n">
-        <v>41.9</v>
+        <v>35.23</v>
       </c>
       <c r="N16" t="inlineStr">
         <is>
@@ -1362,109 +1358,109 @@
       <c r="O16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>VIGILAR</t>
+          <t>NO COMPRAR</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>QQQ</t>
+          <t>AVGO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>ETF Nasdaq</t>
+          <t>IA / Chips</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>697.3</v>
+        <v>376.56</v>
       </c>
       <c r="D17" t="n">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="E17" t="n">
-        <v>-6.3</v>
+        <v>-10.11</v>
       </c>
       <c r="F17" t="n">
-        <v>0.82</v>
+        <v>0.37</v>
       </c>
       <c r="G17" t="n">
-        <v>14.34</v>
+        <v>25.42</v>
       </c>
       <c r="H17" t="n">
-        <v>2.06</v>
+        <v>6.75</v>
       </c>
       <c r="I17" t="n">
-        <v>691.5599999999999</v>
+        <v>366.39</v>
       </c>
       <c r="J17" t="n">
-        <v>700.88</v>
+        <v>382.91</v>
       </c>
       <c r="K17" t="n">
-        <v>675.79</v>
+        <v>338.43</v>
       </c>
       <c r="L17" t="n">
-        <v>733.15</v>
+        <v>440.11</v>
       </c>
       <c r="M17" t="n">
-        <v>42.49</v>
+        <v>40.68</v>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>BAJO</t>
+          <t>MEDIO</t>
         </is>
       </c>
       <c r="O17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>VIGILAR</t>
+          <t>NO COMPRAR</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>NVDA</t>
+          <t>AAPL</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>IA / Chips</t>
+          <t>Tecnología</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>202.52</v>
+        <v>293.42</v>
       </c>
       <c r="D18" t="n">
         <v>56</v>
       </c>
       <c r="E18" t="n">
-        <v>-5.58</v>
+        <v>-5.72</v>
       </c>
       <c r="F18" t="n">
-        <v>0.47</v>
+        <v>0.35</v>
       </c>
       <c r="G18" t="n">
-        <v>8.630000000000001</v>
+        <v>7.33</v>
       </c>
       <c r="H18" t="n">
-        <v>4.26</v>
+        <v>2.5</v>
       </c>
       <c r="I18" t="n">
-        <v>199.07</v>
+        <v>290.49</v>
       </c>
       <c r="J18" t="n">
-        <v>204.68</v>
+        <v>295.25</v>
       </c>
       <c r="K18" t="n">
-        <v>189.58</v>
+        <v>282.42</v>
       </c>
       <c r="L18" t="n">
-        <v>224.1</v>
+        <v>311.75</v>
       </c>
       <c r="M18" t="n">
-        <v>34.28</v>
+        <v>39.1</v>
       </c>
       <c r="N18" t="inlineStr">
         <is>
@@ -1490,37 +1486,37 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>238.7</v>
+        <v>236.07</v>
       </c>
       <c r="D19" t="n">
         <v>56</v>
       </c>
       <c r="E19" t="n">
-        <v>-4.53</v>
+        <v>-6.98</v>
       </c>
       <c r="F19" t="n">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="G19" t="n">
-        <v>7.32</v>
+        <v>7.08</v>
       </c>
       <c r="H19" t="n">
-        <v>3.07</v>
+        <v>3</v>
       </c>
       <c r="I19" t="n">
-        <v>235.77</v>
+        <v>233.24</v>
       </c>
       <c r="J19" t="n">
-        <v>240.53</v>
+        <v>237.84</v>
       </c>
       <c r="K19" t="n">
-        <v>227.72</v>
+        <v>225.45</v>
       </c>
       <c r="L19" t="n">
-        <v>257.01</v>
+        <v>253.77</v>
       </c>
       <c r="M19" t="n">
-        <v>27.39</v>
+        <v>21.76</v>
       </c>
       <c r="N19" t="inlineStr">
         <is>
@@ -1546,37 +1542,37 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>357.37</v>
+        <v>347.41</v>
       </c>
       <c r="D20" t="n">
         <v>56</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.39</v>
+        <v>-6.6</v>
       </c>
       <c r="F20" t="n">
-        <v>0.47</v>
+        <v>0.57</v>
       </c>
       <c r="G20" t="n">
-        <v>9.960000000000001</v>
+        <v>10.22</v>
       </c>
       <c r="H20" t="n">
-        <v>2.79</v>
+        <v>2.94</v>
       </c>
       <c r="I20" t="n">
-        <v>353.39</v>
+        <v>343.32</v>
       </c>
       <c r="J20" t="n">
-        <v>359.87</v>
+        <v>349.97</v>
       </c>
       <c r="K20" t="n">
-        <v>342.43</v>
+        <v>332.07</v>
       </c>
       <c r="L20" t="n">
-        <v>382.28</v>
+        <v>372.97</v>
       </c>
       <c r="M20" t="n">
-        <v>28.85</v>
+        <v>25.81</v>
       </c>
       <c r="N20" t="inlineStr">
         <is>
@@ -1593,46 +1589,46 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>SPY</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Tecnología</t>
+          <t>ETF Mercado</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>402.66</v>
+        <v>726.33</v>
       </c>
       <c r="D21" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E21" t="n">
-        <v>-5.77</v>
+        <v>-4.06</v>
       </c>
       <c r="F21" t="n">
-        <v>0.39</v>
+        <v>0.58</v>
       </c>
       <c r="G21" t="n">
-        <v>12.84</v>
+        <v>8.66</v>
       </c>
       <c r="H21" t="n">
-        <v>3.19</v>
+        <v>1.19</v>
       </c>
       <c r="I21" t="n">
-        <v>397.53</v>
+        <v>722.87</v>
       </c>
       <c r="J21" t="n">
-        <v>405.87</v>
+        <v>728.49</v>
       </c>
       <c r="K21" t="n">
-        <v>383.4</v>
+        <v>713.34</v>
       </c>
       <c r="L21" t="n">
-        <v>434.76</v>
+        <v>747.98</v>
       </c>
       <c r="M21" t="n">
-        <v>42.37</v>
+        <v>36.61</v>
       </c>
       <c r="N21" t="inlineStr">
         <is>
@@ -1649,50 +1645,50 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>SPY</t>
+          <t>SOFI</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>ETF Mercado</t>
+          <t>Fintech</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>729.63</v>
+        <v>15.87</v>
       </c>
       <c r="D22" t="n">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.26</v>
+        <v>-7.46</v>
       </c>
       <c r="F22" t="n">
-        <v>0.51</v>
+        <v>0.5</v>
       </c>
       <c r="G22" t="n">
-        <v>8.48</v>
+        <v>1.03</v>
       </c>
       <c r="H22" t="n">
-        <v>1.16</v>
+        <v>6.49</v>
       </c>
       <c r="I22" t="n">
-        <v>726.24</v>
+        <v>15.46</v>
       </c>
       <c r="J22" t="n">
-        <v>731.75</v>
+        <v>16.13</v>
       </c>
       <c r="K22" t="n">
-        <v>716.91</v>
+        <v>14.32</v>
       </c>
       <c r="L22" t="n">
-        <v>750.83</v>
+        <v>18.45</v>
       </c>
       <c r="M22" t="n">
-        <v>39.91</v>
+        <v>51.45</v>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>BAJO</t>
+          <t>MEDIO</t>
         </is>
       </c>
       <c r="O22" t="inlineStr"/>
@@ -1705,50 +1701,50 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>AVGO</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>IA / Chips</t>
+          <t>Tecnología</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>372.75</v>
+        <v>385.39</v>
       </c>
       <c r="D23" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E23" t="n">
-        <v>-22.22</v>
+        <v>-9.970000000000001</v>
       </c>
       <c r="F23" t="n">
-        <v>0.7</v>
+        <v>0.53</v>
       </c>
       <c r="G23" t="n">
-        <v>25.51</v>
+        <v>12.97</v>
       </c>
       <c r="H23" t="n">
-        <v>6.84</v>
+        <v>3.37</v>
       </c>
       <c r="I23" t="n">
-        <v>362.55</v>
+        <v>380.2</v>
       </c>
       <c r="J23" t="n">
-        <v>379.13</v>
+        <v>388.63</v>
       </c>
       <c r="K23" t="n">
-        <v>334.49</v>
+        <v>365.93</v>
       </c>
       <c r="L23" t="n">
-        <v>436.51</v>
+        <v>417.82</v>
       </c>
       <c r="M23" t="n">
-        <v>38.85</v>
+        <v>37.12</v>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>MEDIO</t>
+          <t>BAJO</t>
         </is>
       </c>
       <c r="O23" t="inlineStr"/>
@@ -1761,50 +1757,50 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>SOFI</t>
+          <t>TSLA</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Fintech</t>
+          <t>Autos / Tech</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>16.02</v>
+        <v>384.96</v>
       </c>
       <c r="D24" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.93</v>
+        <v>-8</v>
       </c>
       <c r="F24" t="n">
-        <v>0.59</v>
+        <v>0.51</v>
       </c>
       <c r="G24" t="n">
-        <v>1.02</v>
+        <v>16.66</v>
       </c>
       <c r="H24" t="n">
-        <v>6.38</v>
+        <v>4.33</v>
       </c>
       <c r="I24" t="n">
-        <v>15.62</v>
+        <v>378.29</v>
       </c>
       <c r="J24" t="n">
-        <v>16.28</v>
+        <v>389.13</v>
       </c>
       <c r="K24" t="n">
-        <v>14.49</v>
+        <v>359.96</v>
       </c>
       <c r="L24" t="n">
-        <v>18.58</v>
+        <v>426.62</v>
       </c>
       <c r="M24" t="n">
-        <v>52.24</v>
+        <v>38.23</v>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>MEDIO</t>
+          <t>BAJO</t>
         </is>
       </c>
       <c r="O24" t="inlineStr"/>
@@ -1817,46 +1813,46 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>TSLA</t>
+          <t>META</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Autos / Tech</t>
+          <t>Tecnología</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>381.48</v>
+        <v>559.8</v>
       </c>
       <c r="D25" t="n">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="E25" t="n">
-        <v>-9.960000000000001</v>
+        <v>-10.8</v>
       </c>
       <c r="F25" t="n">
-        <v>0.61</v>
+        <v>0.45</v>
       </c>
       <c r="G25" t="n">
-        <v>16.88</v>
+        <v>19.89</v>
       </c>
       <c r="H25" t="n">
-        <v>4.43</v>
+        <v>3.55</v>
       </c>
       <c r="I25" t="n">
-        <v>374.73</v>
+        <v>551.85</v>
       </c>
       <c r="J25" t="n">
-        <v>385.7</v>
+        <v>564.78</v>
       </c>
       <c r="K25" t="n">
-        <v>356.16</v>
+        <v>529.98</v>
       </c>
       <c r="L25" t="n">
-        <v>423.69</v>
+        <v>609.52</v>
       </c>
       <c r="M25" t="n">
-        <v>36.95</v>
+        <v>35.43</v>
       </c>
       <c r="N25" t="inlineStr">
         <is>
@@ -1873,50 +1869,50 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>META</t>
+          <t>PLTR</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Tecnología</t>
+          <t>IA / Software</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>576.4299999999999</v>
+        <v>129.05</v>
       </c>
       <c r="D26" t="n">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="E26" t="n">
-        <v>-7.47</v>
+        <v>-8.93</v>
       </c>
       <c r="F26" t="n">
-        <v>0.36</v>
+        <v>0.34</v>
       </c>
       <c r="G26" t="n">
-        <v>19.63</v>
+        <v>7.54</v>
       </c>
       <c r="H26" t="n">
-        <v>3.4</v>
+        <v>5.85</v>
       </c>
       <c r="I26" t="n">
-        <v>568.58</v>
+        <v>126.03</v>
       </c>
       <c r="J26" t="n">
-        <v>581.34</v>
+        <v>130.94</v>
       </c>
       <c r="K26" t="n">
-        <v>546.99</v>
+        <v>117.73</v>
       </c>
       <c r="L26" t="n">
-        <v>625.5</v>
+        <v>147.91</v>
       </c>
       <c r="M26" t="n">
-        <v>40.39</v>
+        <v>43.71</v>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>BAJO</t>
+          <t>MEDIO</t>
         </is>
       </c>
       <c r="O26" t="inlineStr"/>
@@ -1929,50 +1925,50 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>SOUN</t>
+          <t>PYPL</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>IA</t>
+          <t>Pagos</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>6.94</v>
+        <v>40.35</v>
       </c>
       <c r="D27" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E27" t="n">
-        <v>-14.11</v>
+        <v>-5.61</v>
       </c>
       <c r="F27" t="n">
-        <v>0.61</v>
+        <v>0.38</v>
       </c>
       <c r="G27" t="n">
-        <v>0.55</v>
+        <v>1.15</v>
       </c>
       <c r="H27" t="n">
-        <v>7.94</v>
+        <v>2.85</v>
       </c>
       <c r="I27" t="n">
-        <v>6.72</v>
+        <v>39.89</v>
       </c>
       <c r="J27" t="n">
-        <v>7.08</v>
+        <v>40.64</v>
       </c>
       <c r="K27" t="n">
-        <v>6.11</v>
+        <v>38.62</v>
       </c>
       <c r="L27" t="n">
-        <v>8.32</v>
+        <v>43.23</v>
       </c>
       <c r="M27" t="n">
-        <v>31.36</v>
+        <v>25.02</v>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>MEDIO</t>
+          <t>BAJO</t>
         </is>
       </c>
       <c r="O27" t="inlineStr"/>
@@ -1985,46 +1981,46 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>PLTR</t>
+          <t>COIN</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>IA / Software</t>
+          <t>Cripto / Trading</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>131.75</v>
+        <v>153.62</v>
       </c>
       <c r="D28" t="n">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="E28" t="n">
-        <v>-7.35</v>
+        <v>-6.4</v>
       </c>
       <c r="F28" t="n">
-        <v>0.39</v>
+        <v>0.29</v>
       </c>
       <c r="G28" t="n">
-        <v>7.52</v>
+        <v>10.74</v>
       </c>
       <c r="H28" t="n">
-        <v>5.71</v>
+        <v>6.99</v>
       </c>
       <c r="I28" t="n">
-        <v>128.74</v>
+        <v>149.33</v>
       </c>
       <c r="J28" t="n">
-        <v>133.63</v>
+        <v>156.3</v>
       </c>
       <c r="K28" t="n">
-        <v>120.47</v>
+        <v>137.51</v>
       </c>
       <c r="L28" t="n">
-        <v>150.55</v>
+        <v>180.46</v>
       </c>
       <c r="M28" t="n">
-        <v>45.79</v>
+        <v>28.22</v>
       </c>
       <c r="N28" t="inlineStr">
         <is>
@@ -2041,158 +2037,162 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>PYPL</t>
+          <t>KLAC</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Pagos</t>
+          <t>Equipos chips</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>41.06</v>
+        <v>2302.24</v>
       </c>
       <c r="D29" t="n">
-        <v>36</v>
+        <v>82</v>
       </c>
       <c r="E29" t="n">
-        <v>-3.33</v>
+        <v>8.029999999999999</v>
       </c>
       <c r="F29" t="n">
-        <v>0.47</v>
+        <v>0.37</v>
       </c>
       <c r="G29" t="n">
-        <v>1.14</v>
+        <v>399.94</v>
       </c>
       <c r="H29" t="n">
-        <v>2.77</v>
+        <v>17.37</v>
       </c>
       <c r="I29" t="n">
-        <v>40.6</v>
+        <v>2142.26</v>
       </c>
       <c r="J29" t="n">
-        <v>41.34</v>
+        <v>2402.23</v>
       </c>
       <c r="K29" t="n">
-        <v>39.35</v>
+        <v>1702.33</v>
       </c>
       <c r="L29" t="n">
-        <v>43.9</v>
+        <v>3302.1</v>
       </c>
       <c r="M29" t="n">
-        <v>27.28</v>
+        <v>54.7</v>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>BAJO</t>
-        </is>
-      </c>
-      <c r="O29" t="inlineStr"/>
+          <t>ALTO</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>🔥</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>NO COMPRAR</t>
+          <t>VIGILAR</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>COIN</t>
+          <t>MU</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Cripto / Trading</t>
+          <t>Memoria / Chips</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>156.28</v>
+        <v>917.15</v>
       </c>
       <c r="D30" t="n">
-        <v>28</v>
+        <v>72</v>
       </c>
       <c r="E30" t="n">
-        <v>-4.25</v>
+        <v>-7.92</v>
       </c>
       <c r="F30" t="n">
-        <v>0.37</v>
+        <v>0.5</v>
       </c>
       <c r="G30" t="n">
-        <v>10.92</v>
+        <v>81.61</v>
       </c>
       <c r="H30" t="n">
-        <v>6.99</v>
+        <v>8.9</v>
       </c>
       <c r="I30" t="n">
-        <v>151.91</v>
+        <v>884.51</v>
       </c>
       <c r="J30" t="n">
-        <v>159.01</v>
+        <v>937.55</v>
       </c>
       <c r="K30" t="n">
-        <v>139.9</v>
+        <v>794.74</v>
       </c>
       <c r="L30" t="n">
-        <v>183.57</v>
+        <v>1121.18</v>
       </c>
       <c r="M30" t="n">
-        <v>31.15</v>
+        <v>60.58</v>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>MEDIO</t>
+          <t>ALTO</t>
         </is>
       </c>
       <c r="O30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>NO COMPRAR</t>
+          <t>VIGILAR</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>MU</t>
+          <t>ARM</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Memoria / Chips</t>
+          <t>Chips</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>896</v>
+        <v>325.76</v>
       </c>
       <c r="D31" t="n">
         <v>72</v>
       </c>
       <c r="E31" t="n">
-        <v>-17</v>
+        <v>-17.2</v>
       </c>
       <c r="F31" t="n">
-        <v>0.62</v>
+        <v>0.37</v>
       </c>
       <c r="G31" t="n">
-        <v>80.62</v>
+        <v>38.51</v>
       </c>
       <c r="H31" t="n">
-        <v>9</v>
+        <v>11.82</v>
       </c>
       <c r="I31" t="n">
-        <v>863.75</v>
+        <v>310.35</v>
       </c>
       <c r="J31" t="n">
-        <v>916.16</v>
+        <v>335.39</v>
       </c>
       <c r="K31" t="n">
-        <v>775.0700000000001</v>
+        <v>267.99</v>
       </c>
       <c r="L31" t="n">
-        <v>1097.55</v>
+        <v>422.04</v>
       </c>
       <c r="M31" t="n">
-        <v>61.18</v>
+        <v>54.71</v>
       </c>
       <c r="N31" t="inlineStr">
         <is>
@@ -2209,46 +2209,46 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>ARM</t>
+          <t>SMCI</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Chips</t>
+          <t>Servidores IA</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>307.81</v>
+        <v>30.33</v>
       </c>
       <c r="D32" t="n">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="E32" t="n">
-        <v>-25.26</v>
+        <v>-35.34</v>
       </c>
       <c r="F32" t="n">
-        <v>0.37</v>
+        <v>3.1</v>
       </c>
       <c r="G32" t="n">
-        <v>39.46</v>
+        <v>4.51</v>
       </c>
       <c r="H32" t="n">
-        <v>12.82</v>
+        <v>14.88</v>
       </c>
       <c r="I32" t="n">
-        <v>292.03</v>
+        <v>28.52</v>
       </c>
       <c r="J32" t="n">
-        <v>317.68</v>
+        <v>31.45</v>
       </c>
       <c r="K32" t="n">
-        <v>248.62</v>
+        <v>23.55</v>
       </c>
       <c r="L32" t="n">
-        <v>406.46</v>
+        <v>41.61</v>
       </c>
       <c r="M32" t="n">
-        <v>58.1</v>
+        <v>46.39</v>
       </c>
       <c r="N32" t="inlineStr">
         <is>
@@ -2258,53 +2258,53 @@
       <c r="O32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>VIGILAR</t>
+          <t>NO COMPRAR</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>IONQ</t>
+          <t>QCOM</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Computación cuántica</t>
+          <t>Chips</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>57.65</v>
+        <v>194.39</v>
       </c>
       <c r="D33" t="n">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="E33" t="n">
-        <v>-15.5</v>
+        <v>-19.86</v>
       </c>
       <c r="F33" t="n">
-        <v>0.49</v>
+        <v>0.27</v>
       </c>
       <c r="G33" t="n">
-        <v>6.7</v>
+        <v>19.67</v>
       </c>
       <c r="H33" t="n">
-        <v>11.63</v>
+        <v>10.12</v>
       </c>
       <c r="I33" t="n">
-        <v>54.97</v>
+        <v>186.52</v>
       </c>
       <c r="J33" t="n">
-        <v>59.33</v>
+        <v>199.31</v>
       </c>
       <c r="K33" t="n">
-        <v>47.6</v>
+        <v>164.89</v>
       </c>
       <c r="L33" t="n">
-        <v>74.42</v>
+        <v>243.56</v>
       </c>
       <c r="M33" t="n">
-        <v>54.96</v>
+        <v>44.81</v>
       </c>
       <c r="N33" t="inlineStr">
         <is>
@@ -2314,53 +2314,53 @@
       <c r="O33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>VIGILAR</t>
+          <t>NO COMPRAR</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>SMCI</t>
+          <t>INTC</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Servidores IA</t>
+          <t>Chips</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>33.02</v>
+        <v>111.51</v>
       </c>
       <c r="D34" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E34" t="n">
-        <v>-30.37</v>
+        <v>-0.24</v>
       </c>
       <c r="F34" t="n">
-        <v>1.57</v>
+        <v>0.86</v>
       </c>
       <c r="G34" t="n">
-        <v>4.22</v>
+        <v>9.359999999999999</v>
       </c>
       <c r="H34" t="n">
-        <v>12.79</v>
+        <v>8.390000000000001</v>
       </c>
       <c r="I34" t="n">
-        <v>31.33</v>
+        <v>107.77</v>
       </c>
       <c r="J34" t="n">
-        <v>34.08</v>
+        <v>113.85</v>
       </c>
       <c r="K34" t="n">
-        <v>26.69</v>
+        <v>97.48</v>
       </c>
       <c r="L34" t="n">
-        <v>43.58</v>
+        <v>134.9</v>
       </c>
       <c r="M34" t="n">
-        <v>49.43</v>
+        <v>43.95</v>
       </c>
       <c r="N34" t="inlineStr">
         <is>
@@ -2377,46 +2377,46 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>QCOM</t>
+          <t>RKLB</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Chips</t>
+          <t>Espacial</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>191.27</v>
+        <v>110.74</v>
       </c>
       <c r="D35" t="n">
         <v>52</v>
       </c>
       <c r="E35" t="n">
-        <v>-23.21</v>
+        <v>-7.68</v>
       </c>
       <c r="F35" t="n">
-        <v>0.42</v>
+        <v>0.51</v>
       </c>
       <c r="G35" t="n">
-        <v>20.14</v>
+        <v>11.6</v>
       </c>
       <c r="H35" t="n">
-        <v>10.53</v>
+        <v>10.47</v>
       </c>
       <c r="I35" t="n">
-        <v>183.22</v>
+        <v>106.1</v>
       </c>
       <c r="J35" t="n">
-        <v>196.31</v>
+        <v>113.64</v>
       </c>
       <c r="K35" t="n">
-        <v>161.07</v>
+        <v>93.34999999999999</v>
       </c>
       <c r="L35" t="n">
-        <v>241.62</v>
+        <v>139.73</v>
       </c>
       <c r="M35" t="n">
-        <v>47.14</v>
+        <v>42.27</v>
       </c>
       <c r="N35" t="inlineStr">
         <is>
@@ -2433,46 +2433,46 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>INTC</t>
+          <t>IONQ</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Chips</t>
+          <t>Computación cuántica</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>105.39</v>
+        <v>55.99</v>
       </c>
       <c r="D36" t="n">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="E36" t="n">
-        <v>-6.49</v>
+        <v>-14.73</v>
       </c>
       <c r="F36" t="n">
-        <v>0.57</v>
+        <v>0.44</v>
       </c>
       <c r="G36" t="n">
-        <v>8.890000000000001</v>
+        <v>6.28</v>
       </c>
       <c r="H36" t="n">
-        <v>8.43</v>
+        <v>11.22</v>
       </c>
       <c r="I36" t="n">
-        <v>101.83</v>
+        <v>53.48</v>
       </c>
       <c r="J36" t="n">
-        <v>107.61</v>
+        <v>57.56</v>
       </c>
       <c r="K36" t="n">
-        <v>92.06</v>
+        <v>46.57</v>
       </c>
       <c r="L36" t="n">
-        <v>127.61</v>
+        <v>71.69</v>
       </c>
       <c r="M36" t="n">
-        <v>37.75</v>
+        <v>46.82</v>
       </c>
       <c r="N36" t="inlineStr">
         <is>
@@ -2489,46 +2489,46 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>RKLB</t>
+          <t>SOUN</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Espacial</t>
+          <t>IA</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>106.6</v>
+        <v>6.74</v>
       </c>
       <c r="D37" t="n">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="E37" t="n">
-        <v>-7.06</v>
+        <v>-15.92</v>
       </c>
       <c r="F37" t="n">
-        <v>0.28</v>
+        <v>0.55</v>
       </c>
       <c r="G37" t="n">
-        <v>11.81</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H37" t="n">
-        <v>11.08</v>
+        <v>8.27</v>
       </c>
       <c r="I37" t="n">
-        <v>101.87</v>
+        <v>6.51</v>
       </c>
       <c r="J37" t="n">
-        <v>109.55</v>
+        <v>6.87</v>
       </c>
       <c r="K37" t="n">
-        <v>88.88</v>
+        <v>5.9</v>
       </c>
       <c r="L37" t="n">
-        <v>136.13</v>
+        <v>8.130000000000001</v>
       </c>
       <c r="M37" t="n">
-        <v>35.69</v>
+        <v>30.79</v>
       </c>
       <c r="N37" t="inlineStr">
         <is>

--- a/analisis_acciones.xlsx
+++ b/analisis_acciones.xlsx
@@ -501,7 +501,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ASML</t>
+          <t>TSM</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -510,41 +510,41 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1815.1</v>
+        <v>424.04</v>
       </c>
       <c r="D2" t="n">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="E2" t="n">
-        <v>3.28</v>
+        <v>2.38</v>
       </c>
       <c r="F2" t="n">
-        <v>0.85</v>
+        <v>0.45</v>
       </c>
       <c r="G2" t="n">
-        <v>81.86</v>
+        <v>18.83</v>
       </c>
       <c r="H2" t="n">
-        <v>4.51</v>
+        <v>4.44</v>
       </c>
       <c r="I2" t="n">
-        <v>1782.36</v>
+        <v>416.51</v>
       </c>
       <c r="J2" t="n">
-        <v>1835.57</v>
+        <v>428.75</v>
       </c>
       <c r="K2" t="n">
-        <v>1692.31</v>
+        <v>395.8</v>
       </c>
       <c r="L2" t="n">
-        <v>2019.75</v>
+        <v>471.11</v>
       </c>
       <c r="M2" t="n">
-        <v>68.23</v>
+        <v>56.78</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>MEDIO</t>
+          <t>BAJO</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -561,50 +561,50 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>LRCX</t>
+          <t>QQQ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Equipos chips</t>
+          <t>ETF Nasdaq</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>344.86</v>
+        <v>719.86</v>
       </c>
       <c r="D3" t="n">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="E3" t="n">
-        <v>2.51</v>
+        <v>2.1</v>
       </c>
       <c r="F3" t="n">
-        <v>0.65</v>
+        <v>0.68</v>
       </c>
       <c r="G3" t="n">
-        <v>21.03</v>
+        <v>15.96</v>
       </c>
       <c r="H3" t="n">
-        <v>6.1</v>
+        <v>2.22</v>
       </c>
       <c r="I3" t="n">
-        <v>336.45</v>
+        <v>713.47</v>
       </c>
       <c r="J3" t="n">
-        <v>350.12</v>
+        <v>723.85</v>
       </c>
       <c r="K3" t="n">
-        <v>313.32</v>
+        <v>695.91</v>
       </c>
       <c r="L3" t="n">
-        <v>397.42</v>
+        <v>759.77</v>
       </c>
       <c r="M3" t="n">
-        <v>64.63</v>
+        <v>50.89</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>MEDIO</t>
+          <t>BAJO</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -621,46 +621,46 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AMAT</t>
+          <t>AI</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Equipos chips</t>
+          <t>IA</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>527.29</v>
+        <v>10.9</v>
       </c>
       <c r="D4" t="n">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="E4" t="n">
-        <v>5.1</v>
+        <v>4.55</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.43</v>
       </c>
       <c r="G4" t="n">
-        <v>31.08</v>
+        <v>0.82</v>
       </c>
       <c r="H4" t="n">
-        <v>5.89</v>
+        <v>7.49</v>
       </c>
       <c r="I4" t="n">
-        <v>514.86</v>
+        <v>10.58</v>
       </c>
       <c r="J4" t="n">
-        <v>535.0599999999999</v>
+        <v>11.11</v>
       </c>
       <c r="K4" t="n">
-        <v>480.67</v>
+        <v>9.68</v>
       </c>
       <c r="L4" t="n">
-        <v>604.98</v>
+        <v>12.95</v>
       </c>
       <c r="M4" t="n">
-        <v>73.23999999999999</v>
+        <v>66.2</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -681,7 +681,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CVX</t>
+          <t>SLB</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -690,37 +690,37 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>189.78</v>
+        <v>56.72</v>
       </c>
       <c r="D5" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="E5" t="n">
-        <v>0.76</v>
+        <v>3.38</v>
       </c>
       <c r="F5" t="n">
-        <v>0.26</v>
+        <v>0.36</v>
       </c>
       <c r="G5" t="n">
-        <v>3.89</v>
+        <v>1.91</v>
       </c>
       <c r="H5" t="n">
-        <v>2.05</v>
+        <v>3.36</v>
       </c>
       <c r="I5" t="n">
-        <v>188.22</v>
+        <v>55.96</v>
       </c>
       <c r="J5" t="n">
-        <v>190.75</v>
+        <v>57.2</v>
       </c>
       <c r="K5" t="n">
-        <v>183.94</v>
+        <v>53.86</v>
       </c>
       <c r="L5" t="n">
-        <v>199.51</v>
+        <v>61.5</v>
       </c>
       <c r="M5" t="n">
-        <v>47.79</v>
+        <v>49.14</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
@@ -729,7 +729,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>🔥</t>
+          <t>🔥🔥</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -741,50 +741,50 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>HOOD</t>
+          <t>CVX</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Trading</t>
+          <t>Energía</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>88.44</v>
+        <v>188.1</v>
       </c>
       <c r="D6" t="n">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="E6" t="n">
-        <v>0.12</v>
+        <v>0.42</v>
       </c>
       <c r="F6" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.42</v>
       </c>
       <c r="G6" t="n">
-        <v>6.4</v>
+        <v>4.29</v>
       </c>
       <c r="H6" t="n">
-        <v>7.23</v>
+        <v>2.28</v>
       </c>
       <c r="I6" t="n">
-        <v>85.88</v>
+        <v>186.38</v>
       </c>
       <c r="J6" t="n">
-        <v>90.04000000000001</v>
+        <v>189.17</v>
       </c>
       <c r="K6" t="n">
-        <v>78.84</v>
+        <v>181.66</v>
       </c>
       <c r="L6" t="n">
-        <v>104.43</v>
+        <v>198.83</v>
       </c>
       <c r="M6" t="n">
-        <v>61.54</v>
+        <v>45.04</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>MEDIO</t>
+          <t>BAJO</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -801,46 +801,46 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AI</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>IA</t>
+          <t>IA / Chips</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>10.94</v>
+        <v>512.97</v>
       </c>
       <c r="D7" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E7" t="n">
-        <v>3.45</v>
+        <v>9.99</v>
       </c>
       <c r="F7" t="n">
-        <v>0.43</v>
+        <v>0.57</v>
       </c>
       <c r="G7" t="n">
-        <v>0.8</v>
+        <v>34.78</v>
       </c>
       <c r="H7" t="n">
-        <v>7.35</v>
+        <v>6.78</v>
       </c>
       <c r="I7" t="n">
-        <v>10.62</v>
+        <v>499.05</v>
       </c>
       <c r="J7" t="n">
-        <v>11.15</v>
+        <v>521.66</v>
       </c>
       <c r="K7" t="n">
-        <v>9.74</v>
+        <v>460.8</v>
       </c>
       <c r="L7" t="n">
-        <v>12.95</v>
+        <v>599.91</v>
       </c>
       <c r="M7" t="n">
-        <v>68.63</v>
+        <v>57.42</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -861,53 +861,57 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>SOXX</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Chips</t>
+          <t>ETF Chips</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>410.06</v>
+        <v>597.52</v>
       </c>
       <c r="D8" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="E8" t="n">
-        <v>-7.84</v>
+        <v>10.7</v>
       </c>
       <c r="F8" t="n">
-        <v>0.52</v>
+        <v>0.54</v>
       </c>
       <c r="G8" t="n">
-        <v>18.66</v>
+        <v>35.29</v>
       </c>
       <c r="H8" t="n">
-        <v>4.55</v>
+        <v>5.91</v>
       </c>
       <c r="I8" t="n">
-        <v>402.6</v>
+        <v>583.4</v>
       </c>
       <c r="J8" t="n">
-        <v>414.73</v>
+        <v>606.34</v>
       </c>
       <c r="K8" t="n">
-        <v>382.07</v>
+        <v>544.59</v>
       </c>
       <c r="L8" t="n">
-        <v>456.71</v>
+        <v>685.75</v>
       </c>
       <c r="M8" t="n">
-        <v>51.05</v>
+        <v>60.56</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>BAJO</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr"/>
+          <t>MEDIO</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>🔥</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>POSIBLE COMPRA</t>
@@ -917,109 +921,117 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SOXX</t>
+          <t>UPST</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ETF Chips</t>
+          <t>Fintech IA</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>559.3200000000001</v>
+        <v>30.37</v>
       </c>
       <c r="D9" t="n">
-        <v>76</v>
+        <v>66</v>
       </c>
       <c r="E9" t="n">
-        <v>-7.2</v>
+        <v>2.12</v>
       </c>
       <c r="F9" t="n">
-        <v>0.52</v>
+        <v>0.5</v>
       </c>
       <c r="G9" t="n">
-        <v>33.71</v>
+        <v>2.27</v>
       </c>
       <c r="H9" t="n">
-        <v>6.03</v>
+        <v>7.49</v>
       </c>
       <c r="I9" t="n">
-        <v>545.84</v>
+        <v>29.46</v>
       </c>
       <c r="J9" t="n">
-        <v>567.75</v>
+        <v>30.94</v>
       </c>
       <c r="K9" t="n">
-        <v>508.76</v>
+        <v>26.96</v>
       </c>
       <c r="L9" t="n">
-        <v>643.59</v>
+        <v>36.06</v>
       </c>
       <c r="M9" t="n">
-        <v>56.67</v>
+        <v>54.96</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
           <t>MEDIO</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr"/>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>🔥</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>POSIBLE COMPRA</t>
+          <t>VIGILAR</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>SOFI</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>IA / Chips</t>
+          <t>Fintech</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>462.42</v>
+        <v>16.47</v>
       </c>
       <c r="D10" t="n">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="E10" t="n">
-        <v>-11.62</v>
+        <v>2.74</v>
       </c>
       <c r="F10" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="G10" t="n">
-        <v>34.22</v>
+        <v>1.08</v>
       </c>
       <c r="H10" t="n">
-        <v>7.4</v>
+        <v>6.58</v>
       </c>
       <c r="I10" t="n">
-        <v>448.73</v>
+        <v>16.04</v>
       </c>
       <c r="J10" t="n">
-        <v>470.97</v>
+        <v>16.74</v>
       </c>
       <c r="K10" t="n">
-        <v>411.1</v>
+        <v>14.84</v>
       </c>
       <c r="L10" t="n">
-        <v>547.96</v>
+        <v>19.18</v>
       </c>
       <c r="M10" t="n">
-        <v>52.34</v>
+        <v>54.97</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
           <t>MEDIO</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr"/>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>🔥</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>VIGILAR</t>
@@ -1029,56 +1041,60 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>XOM</t>
+          <t>COIN</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Energía</t>
+          <t>Cripto / Trading</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>150.24</v>
+        <v>160.2</v>
       </c>
       <c r="D11" t="n">
-        <v>64</v>
+        <v>36</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.18</v>
+        <v>5.12</v>
       </c>
       <c r="F11" t="n">
-        <v>0.33</v>
+        <v>0.4</v>
       </c>
       <c r="G11" t="n">
-        <v>3.49</v>
+        <v>10.95</v>
       </c>
       <c r="H11" t="n">
-        <v>2.32</v>
+        <v>6.83</v>
       </c>
       <c r="I11" t="n">
-        <v>148.84</v>
+        <v>155.82</v>
       </c>
       <c r="J11" t="n">
-        <v>151.11</v>
+        <v>162.94</v>
       </c>
       <c r="K11" t="n">
-        <v>145</v>
+        <v>143.78</v>
       </c>
       <c r="L11" t="n">
-        <v>158.97</v>
+        <v>187.57</v>
       </c>
       <c r="M11" t="n">
-        <v>40.53</v>
+        <v>36.14</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>BAJO</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr"/>
+          <t>MEDIO</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>🔥</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>VIGILAR</t>
+          <t>NO COMPRAR</t>
         </is>
       </c>
     </row>
@@ -1094,37 +1110,37 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>57.33</v>
+        <v>57.01</v>
       </c>
       <c r="D12" t="n">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.82</v>
+        <v>0.6</v>
       </c>
       <c r="F12" t="n">
-        <v>0.34</v>
+        <v>0.57</v>
       </c>
       <c r="G12" t="n">
-        <v>1.69</v>
+        <v>1.92</v>
       </c>
       <c r="H12" t="n">
-        <v>2.95</v>
+        <v>3.37</v>
       </c>
       <c r="I12" t="n">
-        <v>56.66</v>
+        <v>56.24</v>
       </c>
       <c r="J12" t="n">
-        <v>57.76</v>
+        <v>57.49</v>
       </c>
       <c r="K12" t="n">
-        <v>54.8</v>
+        <v>54.13</v>
       </c>
       <c r="L12" t="n">
-        <v>61.57</v>
+        <v>61.81</v>
       </c>
       <c r="M12" t="n">
-        <v>44.56</v>
+        <v>44.61</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
@@ -1141,46 +1157,46 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>SLB</t>
+          <t>SPY</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Energía</t>
+          <t>ETF Mercado</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>55.24</v>
+        <v>740.51</v>
       </c>
       <c r="D13" t="n">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="E13" t="n">
-        <v>-4.78</v>
+        <v>0.4</v>
       </c>
       <c r="F13" t="n">
-        <v>0.27</v>
+        <v>0.5</v>
       </c>
       <c r="G13" t="n">
-        <v>1.92</v>
+        <v>9.49</v>
       </c>
       <c r="H13" t="n">
-        <v>3.47</v>
+        <v>1.28</v>
       </c>
       <c r="I13" t="n">
-        <v>54.47</v>
+        <v>736.72</v>
       </c>
       <c r="J13" t="n">
-        <v>55.71</v>
+        <v>742.88</v>
       </c>
       <c r="K13" t="n">
-        <v>52.36</v>
+        <v>726.28</v>
       </c>
       <c r="L13" t="n">
-        <v>60.03</v>
+        <v>764.23</v>
       </c>
       <c r="M13" t="n">
-        <v>43.88</v>
+        <v>46.46</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
@@ -1197,46 +1213,46 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>QQQ</t>
+          <t>NVDA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>ETF Nasdaq</t>
+          <t>IA / Chips</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>699.36</v>
+        <v>204.96</v>
       </c>
       <c r="D14" t="n">
         <v>64</v>
       </c>
       <c r="E14" t="n">
-        <v>-5.57</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="F14" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.33</v>
       </c>
       <c r="G14" t="n">
-        <v>14.74</v>
+        <v>8.33</v>
       </c>
       <c r="H14" t="n">
-        <v>2.11</v>
+        <v>4.06</v>
       </c>
       <c r="I14" t="n">
-        <v>693.46</v>
+        <v>201.63</v>
       </c>
       <c r="J14" t="n">
-        <v>703.04</v>
+        <v>207.04</v>
       </c>
       <c r="K14" t="n">
-        <v>677.24</v>
+        <v>192.47</v>
       </c>
       <c r="L14" t="n">
-        <v>736.21</v>
+        <v>225.78</v>
       </c>
       <c r="M14" t="n">
-        <v>43.32</v>
+        <v>42.13</v>
       </c>
       <c r="N14" t="inlineStr">
         <is>
@@ -1253,46 +1269,46 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>UPST</t>
+          <t>AVGO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Fintech IA</t>
+          <t>IA / Chips</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>29.42</v>
+        <v>380.26</v>
       </c>
       <c r="D15" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E15" t="n">
-        <v>-8.83</v>
+        <v>-1.42</v>
       </c>
       <c r="F15" t="n">
-        <v>0.48</v>
+        <v>0.35</v>
       </c>
       <c r="G15" t="n">
-        <v>2.09</v>
+        <v>25.94</v>
       </c>
       <c r="H15" t="n">
-        <v>7.1</v>
+        <v>6.82</v>
       </c>
       <c r="I15" t="n">
-        <v>28.58</v>
+        <v>369.88</v>
       </c>
       <c r="J15" t="n">
-        <v>29.94</v>
+        <v>386.74</v>
       </c>
       <c r="K15" t="n">
-        <v>26.29</v>
+        <v>341.34</v>
       </c>
       <c r="L15" t="n">
-        <v>34.64</v>
+        <v>445.11</v>
       </c>
       <c r="M15" t="n">
-        <v>51.73</v>
+        <v>42.22</v>
       </c>
       <c r="N15" t="inlineStr">
         <is>
@@ -1309,46 +1325,46 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>NVDA</t>
+          <t>AAPL</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>IA / Chips</t>
+          <t>Tecnología</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>200.35</v>
+        <v>291.65</v>
       </c>
       <c r="D16" t="n">
         <v>56</v>
       </c>
       <c r="E16" t="n">
-        <v>-8.369999999999999</v>
+        <v>-5.11</v>
       </c>
       <c r="F16" t="n">
-        <v>0.38</v>
+        <v>0.35</v>
       </c>
       <c r="G16" t="n">
-        <v>8.369999999999999</v>
+        <v>7.56</v>
       </c>
       <c r="H16" t="n">
-        <v>4.18</v>
+        <v>2.59</v>
       </c>
       <c r="I16" t="n">
-        <v>197</v>
+        <v>288.62</v>
       </c>
       <c r="J16" t="n">
-        <v>202.44</v>
+        <v>293.54</v>
       </c>
       <c r="K16" t="n">
-        <v>187.8</v>
+        <v>280.3</v>
       </c>
       <c r="L16" t="n">
-        <v>221.27</v>
+        <v>310.56</v>
       </c>
       <c r="M16" t="n">
-        <v>35.23</v>
+        <v>34.51</v>
       </c>
       <c r="N16" t="inlineStr">
         <is>
@@ -1365,50 +1381,50 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>AVGO</t>
+          <t>AMZN</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>IA / Chips</t>
+          <t>Tecnología</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>376.56</v>
+        <v>236.32</v>
       </c>
       <c r="D17" t="n">
         <v>56</v>
       </c>
       <c r="E17" t="n">
-        <v>-10.11</v>
+        <v>-3.95</v>
       </c>
       <c r="F17" t="n">
-        <v>0.37</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="G17" t="n">
-        <v>25.42</v>
+        <v>7.76</v>
       </c>
       <c r="H17" t="n">
-        <v>6.75</v>
+        <v>3.28</v>
       </c>
       <c r="I17" t="n">
-        <v>366.39</v>
+        <v>233.21</v>
       </c>
       <c r="J17" t="n">
-        <v>382.91</v>
+        <v>238.26</v>
       </c>
       <c r="K17" t="n">
-        <v>338.43</v>
+        <v>224.67</v>
       </c>
       <c r="L17" t="n">
-        <v>440.11</v>
+        <v>255.72</v>
       </c>
       <c r="M17" t="n">
-        <v>40.68</v>
+        <v>25.8</v>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>MEDIO</t>
+          <t>BAJO</t>
         </is>
       </c>
       <c r="O17" t="inlineStr"/>
@@ -1421,7 +1437,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>GOOGL</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1430,37 +1446,37 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>293.42</v>
+        <v>361.33</v>
       </c>
       <c r="D18" t="n">
         <v>56</v>
       </c>
       <c r="E18" t="n">
-        <v>-5.72</v>
+        <v>-1.9</v>
       </c>
       <c r="F18" t="n">
-        <v>0.35</v>
+        <v>0.42</v>
       </c>
       <c r="G18" t="n">
-        <v>7.33</v>
+        <v>10.66</v>
       </c>
       <c r="H18" t="n">
-        <v>2.5</v>
+        <v>2.95</v>
       </c>
       <c r="I18" t="n">
-        <v>290.49</v>
+        <v>357.06</v>
       </c>
       <c r="J18" t="n">
-        <v>295.25</v>
+        <v>363.99</v>
       </c>
       <c r="K18" t="n">
-        <v>282.42</v>
+        <v>345.34</v>
       </c>
       <c r="L18" t="n">
-        <v>311.75</v>
+        <v>387.97</v>
       </c>
       <c r="M18" t="n">
-        <v>39.1</v>
+        <v>35.53</v>
       </c>
       <c r="N18" t="inlineStr">
         <is>
@@ -1477,46 +1493,46 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>AMZN</t>
+          <t>XOM</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Tecnología</t>
+          <t>Energía</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>236.07</v>
+        <v>148.45</v>
       </c>
       <c r="D19" t="n">
         <v>56</v>
       </c>
       <c r="E19" t="n">
-        <v>-6.98</v>
+        <v>-0.98</v>
       </c>
       <c r="F19" t="n">
-        <v>0.46</v>
+        <v>0.48</v>
       </c>
       <c r="G19" t="n">
-        <v>7.08</v>
+        <v>3.84</v>
       </c>
       <c r="H19" t="n">
-        <v>3</v>
+        <v>2.58</v>
       </c>
       <c r="I19" t="n">
-        <v>233.24</v>
+        <v>146.92</v>
       </c>
       <c r="J19" t="n">
-        <v>237.84</v>
+        <v>149.41</v>
       </c>
       <c r="K19" t="n">
-        <v>225.45</v>
+        <v>142.7</v>
       </c>
       <c r="L19" t="n">
-        <v>253.77</v>
+        <v>158.04</v>
       </c>
       <c r="M19" t="n">
-        <v>21.76</v>
+        <v>39.82</v>
       </c>
       <c r="N19" t="inlineStr">
         <is>
@@ -1533,46 +1549,46 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>GOOGL</t>
+          <t>TSLA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Tecnología</t>
+          <t>Autos / Tech</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>347.41</v>
+        <v>395.75</v>
       </c>
       <c r="D20" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E20" t="n">
-        <v>-6.6</v>
+        <v>1.21</v>
       </c>
       <c r="F20" t="n">
-        <v>0.57</v>
+        <v>0.72</v>
       </c>
       <c r="G20" t="n">
-        <v>10.22</v>
+        <v>17.6</v>
       </c>
       <c r="H20" t="n">
-        <v>2.94</v>
+        <v>4.45</v>
       </c>
       <c r="I20" t="n">
-        <v>343.32</v>
+        <v>388.71</v>
       </c>
       <c r="J20" t="n">
-        <v>349.97</v>
+        <v>400.15</v>
       </c>
       <c r="K20" t="n">
-        <v>332.07</v>
+        <v>369.35</v>
       </c>
       <c r="L20" t="n">
-        <v>372.97</v>
+        <v>439.75</v>
       </c>
       <c r="M20" t="n">
-        <v>25.81</v>
+        <v>39.86</v>
       </c>
       <c r="N20" t="inlineStr">
         <is>
@@ -1589,46 +1605,46 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>SPY</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>ETF Mercado</t>
+          <t>Tecnología</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>726.33</v>
+        <v>387.75</v>
       </c>
       <c r="D21" t="n">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="E21" t="n">
-        <v>-4.06</v>
+        <v>-6.94</v>
       </c>
       <c r="F21" t="n">
-        <v>0.58</v>
+        <v>0.51</v>
       </c>
       <c r="G21" t="n">
-        <v>8.66</v>
+        <v>13.16</v>
       </c>
       <c r="H21" t="n">
-        <v>1.19</v>
+        <v>3.39</v>
       </c>
       <c r="I21" t="n">
-        <v>722.87</v>
+        <v>382.49</v>
       </c>
       <c r="J21" t="n">
-        <v>728.49</v>
+        <v>391.04</v>
       </c>
       <c r="K21" t="n">
-        <v>713.34</v>
+        <v>368.01</v>
       </c>
       <c r="L21" t="n">
-        <v>747.98</v>
+        <v>420.64</v>
       </c>
       <c r="M21" t="n">
-        <v>36.61</v>
+        <v>37.95</v>
       </c>
       <c r="N21" t="inlineStr">
         <is>
@@ -1645,46 +1661,46 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>SOFI</t>
+          <t>SOUN</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Fintech</t>
+          <t>IA</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>15.87</v>
+        <v>6.99</v>
       </c>
       <c r="D22" t="n">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="E22" t="n">
-        <v>-7.46</v>
+        <v>-5.42</v>
       </c>
       <c r="F22" t="n">
-        <v>0.5</v>
+        <v>0.54</v>
       </c>
       <c r="G22" t="n">
-        <v>1.03</v>
+        <v>0.54</v>
       </c>
       <c r="H22" t="n">
-        <v>6.49</v>
+        <v>7.69</v>
       </c>
       <c r="I22" t="n">
-        <v>15.46</v>
+        <v>6.77</v>
       </c>
       <c r="J22" t="n">
-        <v>16.13</v>
+        <v>7.12</v>
       </c>
       <c r="K22" t="n">
-        <v>14.32</v>
+        <v>6.18</v>
       </c>
       <c r="L22" t="n">
-        <v>18.45</v>
+        <v>8.33</v>
       </c>
       <c r="M22" t="n">
-        <v>51.45</v>
+        <v>36.02</v>
       </c>
       <c r="N22" t="inlineStr">
         <is>
@@ -1701,7 +1717,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>META</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1710,37 +1726,37 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>385.39</v>
+        <v>571.1799999999999</v>
       </c>
       <c r="D23" t="n">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="E23" t="n">
-        <v>-9.970000000000001</v>
+        <v>-3.68</v>
       </c>
       <c r="F23" t="n">
-        <v>0.53</v>
+        <v>0.35</v>
       </c>
       <c r="G23" t="n">
-        <v>12.97</v>
+        <v>20.49</v>
       </c>
       <c r="H23" t="n">
-        <v>3.37</v>
+        <v>3.59</v>
       </c>
       <c r="I23" t="n">
-        <v>380.2</v>
+        <v>562.98</v>
       </c>
       <c r="J23" t="n">
-        <v>388.63</v>
+        <v>576.3</v>
       </c>
       <c r="K23" t="n">
-        <v>365.93</v>
+        <v>540.4400000000001</v>
       </c>
       <c r="L23" t="n">
-        <v>417.82</v>
+        <v>622.41</v>
       </c>
       <c r="M23" t="n">
-        <v>37.12</v>
+        <v>37.35</v>
       </c>
       <c r="N23" t="inlineStr">
         <is>
@@ -1757,50 +1773,50 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>TSLA</t>
+          <t>PLTR</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Autos / Tech</t>
+          <t>IA / Software</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>384.96</v>
+        <v>128.04</v>
       </c>
       <c r="D24" t="n">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="E24" t="n">
-        <v>-8</v>
+        <v>-5.53</v>
       </c>
       <c r="F24" t="n">
-        <v>0.51</v>
+        <v>0.49</v>
       </c>
       <c r="G24" t="n">
-        <v>16.66</v>
+        <v>7.59</v>
       </c>
       <c r="H24" t="n">
-        <v>4.33</v>
+        <v>5.92</v>
       </c>
       <c r="I24" t="n">
-        <v>378.29</v>
+        <v>125.01</v>
       </c>
       <c r="J24" t="n">
-        <v>389.13</v>
+        <v>129.94</v>
       </c>
       <c r="K24" t="n">
-        <v>359.96</v>
+        <v>116.66</v>
       </c>
       <c r="L24" t="n">
-        <v>426.62</v>
+        <v>147.01</v>
       </c>
       <c r="M24" t="n">
-        <v>38.23</v>
+        <v>43.57</v>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>BAJO</t>
+          <t>MEDIO</t>
         </is>
       </c>
       <c r="O24" t="inlineStr"/>
@@ -1813,46 +1829,46 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>META</t>
+          <t>PYPL</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Tecnología</t>
+          <t>Pagos</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>559.8</v>
+        <v>41.26</v>
       </c>
       <c r="D25" t="n">
         <v>36</v>
       </c>
       <c r="E25" t="n">
-        <v>-10.8</v>
+        <v>-0.06</v>
       </c>
       <c r="F25" t="n">
-        <v>0.45</v>
+        <v>0.35</v>
       </c>
       <c r="G25" t="n">
-        <v>19.89</v>
+        <v>1.15</v>
       </c>
       <c r="H25" t="n">
-        <v>3.55</v>
+        <v>2.79</v>
       </c>
       <c r="I25" t="n">
-        <v>551.85</v>
+        <v>40.8</v>
       </c>
       <c r="J25" t="n">
-        <v>564.78</v>
+        <v>41.55</v>
       </c>
       <c r="K25" t="n">
-        <v>529.98</v>
+        <v>39.54</v>
       </c>
       <c r="L25" t="n">
-        <v>609.52</v>
+        <v>44.14</v>
       </c>
       <c r="M25" t="n">
-        <v>35.43</v>
+        <v>31.83</v>
       </c>
       <c r="N25" t="inlineStr">
         <is>
@@ -1869,225 +1885,233 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>PLTR</t>
+          <t>ASML</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>IA / Software</t>
+          <t>Chips</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>129.05</v>
+        <v>1876.61</v>
       </c>
       <c r="D26" t="n">
-        <v>36</v>
+        <v>95</v>
       </c>
       <c r="E26" t="n">
-        <v>-8.93</v>
+        <v>14.31</v>
       </c>
       <c r="F26" t="n">
-        <v>0.34</v>
+        <v>0.93</v>
       </c>
       <c r="G26" t="n">
-        <v>7.54</v>
+        <v>86.98999999999999</v>
       </c>
       <c r="H26" t="n">
-        <v>5.85</v>
+        <v>4.64</v>
       </c>
       <c r="I26" t="n">
-        <v>126.03</v>
+        <v>1841.82</v>
       </c>
       <c r="J26" t="n">
-        <v>130.94</v>
+        <v>1898.36</v>
       </c>
       <c r="K26" t="n">
-        <v>117.73</v>
+        <v>1746.13</v>
       </c>
       <c r="L26" t="n">
-        <v>147.91</v>
+        <v>2094.08</v>
       </c>
       <c r="M26" t="n">
-        <v>43.71</v>
+        <v>67.97</v>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>MEDIO</t>
-        </is>
-      </c>
-      <c r="O26" t="inlineStr"/>
+          <t>ALTO</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>🔥</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>NO COMPRAR</t>
+          <t>VIGILAR</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>PYPL</t>
+          <t>LRCX</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Pagos</t>
+          <t>Equipos chips</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>40.35</v>
+        <v>369.36</v>
       </c>
       <c r="D27" t="n">
-        <v>36</v>
+        <v>89</v>
       </c>
       <c r="E27" t="n">
-        <v>-5.61</v>
+        <v>21.79</v>
       </c>
       <c r="F27" t="n">
-        <v>0.38</v>
+        <v>0.44</v>
       </c>
       <c r="G27" t="n">
-        <v>1.15</v>
+        <v>22.81</v>
       </c>
       <c r="H27" t="n">
-        <v>2.85</v>
+        <v>6.18</v>
       </c>
       <c r="I27" t="n">
-        <v>39.89</v>
+        <v>360.23</v>
       </c>
       <c r="J27" t="n">
-        <v>40.64</v>
+        <v>375.06</v>
       </c>
       <c r="K27" t="n">
-        <v>38.62</v>
+        <v>335.14</v>
       </c>
       <c r="L27" t="n">
-        <v>43.23</v>
+        <v>426.39</v>
       </c>
       <c r="M27" t="n">
-        <v>25.02</v>
+        <v>69.16</v>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>BAJO</t>
-        </is>
-      </c>
-      <c r="O27" t="inlineStr"/>
+          <t>ALTO</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>🔥</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>NO COMPRAR</t>
+          <t>VIGILAR</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>COIN</t>
+          <t>ARM</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Cripto / Trading</t>
+          <t>Chips</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>153.62</v>
+        <v>370.29</v>
       </c>
       <c r="D28" t="n">
-        <v>28</v>
+        <v>80</v>
       </c>
       <c r="E28" t="n">
-        <v>-6.4</v>
+        <v>7.98</v>
       </c>
       <c r="F28" t="n">
-        <v>0.29</v>
+        <v>0.79</v>
       </c>
       <c r="G28" t="n">
-        <v>10.74</v>
+        <v>40.14</v>
       </c>
       <c r="H28" t="n">
-        <v>6.99</v>
+        <v>10.84</v>
       </c>
       <c r="I28" t="n">
-        <v>149.33</v>
+        <v>354.23</v>
       </c>
       <c r="J28" t="n">
-        <v>156.3</v>
+        <v>380.33</v>
       </c>
       <c r="K28" t="n">
-        <v>137.51</v>
+        <v>310.07</v>
       </c>
       <c r="L28" t="n">
-        <v>180.46</v>
+        <v>470.65</v>
       </c>
       <c r="M28" t="n">
-        <v>28.22</v>
+        <v>59.7</v>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>MEDIO</t>
-        </is>
-      </c>
-      <c r="O28" t="inlineStr"/>
+          <t>ALTO</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>🔥</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>NO COMPRAR</t>
+          <t>VIGILAR</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>KLAC</t>
+          <t>INTC</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Equipos chips</t>
+          <t>Chips</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>2302.24</v>
+        <v>124.04</v>
       </c>
       <c r="D29" t="n">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="E29" t="n">
-        <v>8.029999999999999</v>
+        <v>25.08</v>
       </c>
       <c r="F29" t="n">
-        <v>0.37</v>
+        <v>0.67</v>
       </c>
       <c r="G29" t="n">
-        <v>399.94</v>
+        <v>9.73</v>
       </c>
       <c r="H29" t="n">
-        <v>17.37</v>
+        <v>7.84</v>
       </c>
       <c r="I29" t="n">
-        <v>2142.26</v>
+        <v>120.15</v>
       </c>
       <c r="J29" t="n">
-        <v>2402.23</v>
+        <v>126.47</v>
       </c>
       <c r="K29" t="n">
-        <v>1702.33</v>
+        <v>109.45</v>
       </c>
       <c r="L29" t="n">
-        <v>3302.1</v>
+        <v>148.36</v>
       </c>
       <c r="M29" t="n">
-        <v>54.7</v>
+        <v>53.05</v>
       </c>
       <c r="N29" t="inlineStr">
         <is>
           <t>ALTO</t>
         </is>
       </c>
-      <c r="O29" t="inlineStr">
-        <is>
-          <t>🔥</t>
-        </is>
-      </c>
+      <c r="O29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>VIGILAR</t>
@@ -2097,46 +2121,46 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>MU</t>
+          <t>HOOD</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Memoria / Chips</t>
+          <t>Trading</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>917.15</v>
+        <v>93.20999999999999</v>
       </c>
       <c r="D30" t="n">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="E30" t="n">
-        <v>-7.92</v>
+        <v>13.03</v>
       </c>
       <c r="F30" t="n">
-        <v>0.5</v>
+        <v>0.68</v>
       </c>
       <c r="G30" t="n">
-        <v>81.61</v>
+        <v>6.78</v>
       </c>
       <c r="H30" t="n">
-        <v>8.9</v>
+        <v>7.27</v>
       </c>
       <c r="I30" t="n">
-        <v>884.51</v>
+        <v>90.5</v>
       </c>
       <c r="J30" t="n">
-        <v>937.55</v>
+        <v>94.91</v>
       </c>
       <c r="K30" t="n">
-        <v>794.74</v>
+        <v>83.05</v>
       </c>
       <c r="L30" t="n">
-        <v>1121.18</v>
+        <v>110.16</v>
       </c>
       <c r="M30" t="n">
-        <v>60.58</v>
+        <v>67.25</v>
       </c>
       <c r="N30" t="inlineStr">
         <is>
@@ -2153,46 +2177,46 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>ARM</t>
+          <t>MU</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Chips</t>
+          <t>Memoria / Chips</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>325.76</v>
+        <v>991.6799999999999</v>
       </c>
       <c r="D31" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="E31" t="n">
-        <v>-17.2</v>
+        <v>14.78</v>
       </c>
       <c r="F31" t="n">
-        <v>0.37</v>
+        <v>0.5</v>
       </c>
       <c r="G31" t="n">
-        <v>38.51</v>
+        <v>87.66</v>
       </c>
       <c r="H31" t="n">
-        <v>11.82</v>
+        <v>8.84</v>
       </c>
       <c r="I31" t="n">
-        <v>310.35</v>
+        <v>956.61</v>
       </c>
       <c r="J31" t="n">
-        <v>335.39</v>
+        <v>1013.6</v>
       </c>
       <c r="K31" t="n">
-        <v>267.99</v>
+        <v>860.1900000000001</v>
       </c>
       <c r="L31" t="n">
-        <v>422.04</v>
+        <v>1210.84</v>
       </c>
       <c r="M31" t="n">
-        <v>54.71</v>
+        <v>64.95</v>
       </c>
       <c r="N31" t="inlineStr">
         <is>
@@ -2209,46 +2233,46 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>SMCI</t>
+          <t>AMAT</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Servidores IA</t>
+          <t>Equipos chips</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>30.33</v>
+        <v>565.51</v>
       </c>
       <c r="D32" t="n">
-        <v>54</v>
+        <v>72</v>
       </c>
       <c r="E32" t="n">
-        <v>-35.34</v>
+        <v>24.83</v>
       </c>
       <c r="F32" t="n">
-        <v>3.1</v>
+        <v>0.43</v>
       </c>
       <c r="G32" t="n">
-        <v>4.51</v>
+        <v>33.39</v>
       </c>
       <c r="H32" t="n">
-        <v>14.88</v>
+        <v>5.9</v>
       </c>
       <c r="I32" t="n">
-        <v>28.52</v>
+        <v>552.15</v>
       </c>
       <c r="J32" t="n">
-        <v>31.45</v>
+        <v>573.85</v>
       </c>
       <c r="K32" t="n">
-        <v>23.55</v>
+        <v>515.42</v>
       </c>
       <c r="L32" t="n">
-        <v>41.61</v>
+        <v>648.99</v>
       </c>
       <c r="M32" t="n">
-        <v>46.39</v>
+        <v>76.84</v>
       </c>
       <c r="N32" t="inlineStr">
         <is>
@@ -2258,53 +2282,53 @@
       <c r="O32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>NO COMPRAR</t>
+          <t>VIGILAR</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>QCOM</t>
+          <t>KLAC</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Chips</t>
+          <t>Equipos chips</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>194.39</v>
+        <v>250.29</v>
       </c>
       <c r="D33" t="n">
-        <v>52</v>
+        <v>72</v>
       </c>
       <c r="E33" t="n">
-        <v>-19.86</v>
+        <v>29.74</v>
       </c>
       <c r="F33" t="n">
-        <v>0.27</v>
+        <v>0.38</v>
       </c>
       <c r="G33" t="n">
-        <v>19.67</v>
+        <v>15.09</v>
       </c>
       <c r="H33" t="n">
-        <v>10.12</v>
+        <v>6.03</v>
       </c>
       <c r="I33" t="n">
-        <v>186.52</v>
+        <v>244.25</v>
       </c>
       <c r="J33" t="n">
-        <v>199.31</v>
+        <v>254.06</v>
       </c>
       <c r="K33" t="n">
-        <v>164.89</v>
+        <v>227.66</v>
       </c>
       <c r="L33" t="n">
-        <v>243.56</v>
+        <v>288.01</v>
       </c>
       <c r="M33" t="n">
-        <v>44.81</v>
+        <v>75.5</v>
       </c>
       <c r="N33" t="inlineStr">
         <is>
@@ -2314,53 +2338,53 @@
       <c r="O33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>NO COMPRAR</t>
+          <t>VIGILAR</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>INTC</t>
+          <t>IONQ</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Chips</t>
+          <t>Computación cuántica</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>111.51</v>
+        <v>58.16</v>
       </c>
       <c r="D34" t="n">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.24</v>
+        <v>2.43</v>
       </c>
       <c r="F34" t="n">
-        <v>0.86</v>
+        <v>0.36</v>
       </c>
       <c r="G34" t="n">
-        <v>9.359999999999999</v>
+        <v>6.16</v>
       </c>
       <c r="H34" t="n">
-        <v>8.390000000000001</v>
+        <v>10.59</v>
       </c>
       <c r="I34" t="n">
-        <v>107.77</v>
+        <v>55.7</v>
       </c>
       <c r="J34" t="n">
-        <v>113.85</v>
+        <v>59.7</v>
       </c>
       <c r="K34" t="n">
-        <v>97.48</v>
+        <v>48.92</v>
       </c>
       <c r="L34" t="n">
-        <v>134.9</v>
+        <v>73.55</v>
       </c>
       <c r="M34" t="n">
-        <v>43.95</v>
+        <v>43.43</v>
       </c>
       <c r="N34" t="inlineStr">
         <is>
@@ -2370,7 +2394,7 @@
       <c r="O34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>NO COMPRAR</t>
+          <t>VIGILAR</t>
         </is>
       </c>
     </row>
@@ -2386,37 +2410,37 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>110.74</v>
+        <v>106.42</v>
       </c>
       <c r="D35" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="E35" t="n">
-        <v>-7.68</v>
+        <v>-3.32</v>
       </c>
       <c r="F35" t="n">
-        <v>0.51</v>
+        <v>1.64</v>
       </c>
       <c r="G35" t="n">
-        <v>11.6</v>
+        <v>12.18</v>
       </c>
       <c r="H35" t="n">
-        <v>10.47</v>
+        <v>11.44</v>
       </c>
       <c r="I35" t="n">
-        <v>106.1</v>
+        <v>101.55</v>
       </c>
       <c r="J35" t="n">
-        <v>113.64</v>
+        <v>109.46</v>
       </c>
       <c r="K35" t="n">
-        <v>93.34999999999999</v>
+        <v>88.16</v>
       </c>
       <c r="L35" t="n">
-        <v>139.73</v>
+        <v>136.86</v>
       </c>
       <c r="M35" t="n">
-        <v>42.27</v>
+        <v>34.91</v>
       </c>
       <c r="N35" t="inlineStr">
         <is>
@@ -2433,46 +2457,46 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>IONQ</t>
+          <t>QCOM</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Computación cuántica</t>
+          <t>Chips</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>55.99</v>
+        <v>213.35</v>
       </c>
       <c r="D36" t="n">
         <v>52</v>
       </c>
       <c r="E36" t="n">
-        <v>-14.73</v>
+        <v>-1.2</v>
       </c>
       <c r="F36" t="n">
-        <v>0.44</v>
+        <v>0.35</v>
       </c>
       <c r="G36" t="n">
-        <v>6.28</v>
+        <v>18.93</v>
       </c>
       <c r="H36" t="n">
-        <v>11.22</v>
+        <v>8.869999999999999</v>
       </c>
       <c r="I36" t="n">
-        <v>53.48</v>
+        <v>205.77</v>
       </c>
       <c r="J36" t="n">
-        <v>57.56</v>
+        <v>218.08</v>
       </c>
       <c r="K36" t="n">
-        <v>46.57</v>
+        <v>184.94</v>
       </c>
       <c r="L36" t="n">
-        <v>71.69</v>
+        <v>260.68</v>
       </c>
       <c r="M36" t="n">
-        <v>46.82</v>
+        <v>42.96</v>
       </c>
       <c r="N36" t="inlineStr">
         <is>
@@ -2489,46 +2513,46 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>SOUN</t>
+          <t>SMCI</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>IA</t>
+          <t>Servidores IA</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>6.74</v>
+        <v>30.59</v>
       </c>
       <c r="D37" t="n">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="E37" t="n">
-        <v>-15.92</v>
+        <v>-26.54</v>
       </c>
       <c r="F37" t="n">
-        <v>0.55</v>
+        <v>0.84</v>
       </c>
       <c r="G37" t="n">
-        <v>0.5600000000000001</v>
+        <v>4.64</v>
       </c>
       <c r="H37" t="n">
-        <v>8.27</v>
+        <v>15.16</v>
       </c>
       <c r="I37" t="n">
-        <v>6.51</v>
+        <v>28.73</v>
       </c>
       <c r="J37" t="n">
-        <v>6.87</v>
+        <v>31.75</v>
       </c>
       <c r="K37" t="n">
-        <v>5.9</v>
+        <v>23.63</v>
       </c>
       <c r="L37" t="n">
-        <v>8.130000000000001</v>
+        <v>42.18</v>
       </c>
       <c r="M37" t="n">
-        <v>30.79</v>
+        <v>44.36</v>
       </c>
       <c r="N37" t="inlineStr">
         <is>
